--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z37"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,10 +539,15 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>Senal Bot</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>Razones</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Alertas</t>
         </is>
@@ -551,68 +556,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>216.6</v>
+        <v>421.22</v>
       </c>
       <c r="D2" t="n">
         <v>96</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7</v>
+        <v>2.53</v>
       </c>
       <c r="F2" t="n">
-        <v>24.1</v>
+        <v>6.47</v>
       </c>
       <c r="G2" t="n">
-        <v>53.52</v>
+        <v>18.83</v>
       </c>
       <c r="H2" t="n">
-        <v>8.57</v>
+        <v>-4.98</v>
       </c>
       <c r="I2" t="n">
-        <v>1.31</v>
+        <v>0.61</v>
       </c>
       <c r="J2" t="n">
-        <v>12.22</v>
+        <v>18.91</v>
       </c>
       <c r="K2" t="n">
-        <v>5.64</v>
+        <v>4.49</v>
       </c>
       <c r="L2" t="n">
-        <v>212.32</v>
+        <v>414.6</v>
       </c>
       <c r="M2" t="n">
-        <v>218.43</v>
+        <v>424.06</v>
       </c>
       <c r="N2" t="n">
-        <v>200.11</v>
+        <v>395.69</v>
       </c>
       <c r="O2" t="n">
-        <v>243.48</v>
+        <v>462.82</v>
       </c>
       <c r="P2" t="n">
         <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>61</v>
+        <v>54.9</v>
       </c>
       <c r="R2" t="n">
-        <v>9.42</v>
+        <v>4.19</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.57</v>
+        <v>-6.07</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -622,91 +627,96 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>COMPRA FUERTE</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Momentum 5D extendido; Algo extendida sobre MA20</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>428.43</v>
+        <v>283.1</v>
       </c>
       <c r="D3" t="n">
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="F3" t="n">
-        <v>12.82</v>
+        <v>3.92</v>
       </c>
       <c r="G3" t="n">
-        <v>29.64</v>
+        <v>20.34</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.71</v>
+        <v>-7.53</v>
       </c>
       <c r="I3" t="n">
-        <v>0.83</v>
+        <v>0.41</v>
       </c>
       <c r="J3" t="n">
-        <v>15.4</v>
+        <v>14.39</v>
       </c>
       <c r="K3" t="n">
-        <v>3.59</v>
+        <v>5.08</v>
       </c>
       <c r="L3" t="n">
-        <v>423.04</v>
+        <v>278.06</v>
       </c>
       <c r="M3" t="n">
-        <v>430.74</v>
+        <v>285.26</v>
       </c>
       <c r="N3" t="n">
-        <v>407.64</v>
+        <v>263.67</v>
       </c>
       <c r="O3" t="n">
-        <v>462.31</v>
+        <v>314.77</v>
       </c>
       <c r="P3" t="n">
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>60.96</v>
+        <v>57.37</v>
       </c>
       <c r="R3" t="n">
-        <v>3.83</v>
+        <v>5.39</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.11</v>
+        <v>-5.63</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -735,76 +745,81 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>MACD sin confirmar</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.48</v>
+        <v>1493.25</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>2.82</v>
+        <v>3.49</v>
       </c>
       <c r="F4" t="n">
-        <v>11.92</v>
+        <v>-1.44</v>
       </c>
       <c r="G4" t="n">
-        <v>-8.67</v>
+        <v>6.39</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.61</v>
+        <v>-12.89</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>0.66</v>
       </c>
       <c r="J4" t="n">
-        <v>0.43</v>
+        <v>60.71</v>
       </c>
       <c r="K4" t="n">
-        <v>4.57</v>
+        <v>4.07</v>
       </c>
       <c r="L4" t="n">
-        <v>9.33</v>
+        <v>1472</v>
       </c>
       <c r="M4" t="n">
-        <v>9.550000000000001</v>
+        <v>1502.36</v>
       </c>
       <c r="N4" t="n">
-        <v>8.890000000000001</v>
+        <v>1411.29</v>
       </c>
       <c r="O4" t="n">
-        <v>10.43</v>
+        <v>1626.81</v>
       </c>
       <c r="P4" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>54.55</v>
+        <v>54.37</v>
       </c>
       <c r="R4" t="n">
-        <v>3.38</v>
+        <v>2.28</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.63</v>
+        <v>-6.4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -833,12 +848,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Débil vs QQQ</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -854,55 +874,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>54.93</v>
+        <v>55.68</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.26</v>
+        <v>-0.57</v>
       </c>
       <c r="F5" t="n">
-        <v>5.8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>8.470000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="H5" t="n">
-        <v>-9.73</v>
+        <v>-3.31</v>
       </c>
       <c r="I5" t="n">
-        <v>0.68</v>
+        <v>0.38</v>
       </c>
       <c r="J5" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="K5" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="L5" t="n">
-        <v>54.34</v>
+        <v>55.11</v>
       </c>
       <c r="M5" t="n">
-        <v>55.18</v>
+        <v>55.92</v>
       </c>
       <c r="N5" t="n">
-        <v>52.65</v>
+        <v>53.49</v>
       </c>
       <c r="O5" t="n">
-        <v>58.65</v>
+        <v>59.25</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>58.59</v>
+        <v>55.66</v>
       </c>
       <c r="R5" t="n">
-        <v>1.08</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.97</v>
+        <v>-2.66</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -927,10 +947,15 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
+        <is>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
@@ -939,7 +964,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -948,55 +973,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>212.65</v>
+        <v>392.55</v>
       </c>
       <c r="D6" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E6" t="n">
-        <v>4.62</v>
+        <v>-0.47</v>
       </c>
       <c r="F6" t="n">
-        <v>34.95</v>
+        <v>3.33</v>
       </c>
       <c r="G6" t="n">
-        <v>74.03</v>
+        <v>7.45</v>
       </c>
       <c r="H6" t="n">
-        <v>19.42</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="J6" t="n">
-        <v>18.49</v>
+        <v>15.57</v>
       </c>
       <c r="K6" t="n">
-        <v>8.699999999999999</v>
+        <v>3.97</v>
       </c>
       <c r="L6" t="n">
-        <v>206.18</v>
+        <v>387.1</v>
       </c>
       <c r="M6" t="n">
-        <v>215.42</v>
+        <v>394.89</v>
       </c>
       <c r="N6" t="n">
-        <v>187.69</v>
+        <v>371.53</v>
       </c>
       <c r="O6" t="n">
-        <v>253.33</v>
+        <v>426.81</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>60.64</v>
+        <v>52.36</v>
       </c>
       <c r="R6" t="n">
-        <v>7.33</v>
+        <v>0.15</v>
       </c>
       <c r="S6" t="n">
-        <v>-11.21</v>
+        <v>-6.54</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1010,14 +1035,10 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1025,76 +1046,81 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Algo extendida sobre MA20; Volatilidad alta</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1845.19</v>
+        <v>264.04</v>
       </c>
       <c r="D7" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="E7" t="n">
-        <v>7.7</v>
+        <v>-3.48</v>
       </c>
       <c r="F7" t="n">
-        <v>4.32</v>
+        <v>6.03</v>
       </c>
       <c r="G7" t="n">
-        <v>27.35</v>
+        <v>32.82</v>
       </c>
       <c r="H7" t="n">
-        <v>-11.21</v>
+        <v>-5.42</v>
       </c>
       <c r="I7" t="n">
-        <v>1.16</v>
+        <v>0.43</v>
       </c>
       <c r="J7" t="n">
-        <v>83.20999999999999</v>
+        <v>7.26</v>
       </c>
       <c r="K7" t="n">
-        <v>4.51</v>
+        <v>2.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1816.06</v>
+        <v>261.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1857.67</v>
+        <v>265.13</v>
       </c>
       <c r="N7" t="n">
-        <v>1732.85</v>
+        <v>254.24</v>
       </c>
       <c r="O7" t="n">
-        <v>2028.26</v>
+        <v>280</v>
       </c>
       <c r="P7" t="n">
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>54.45</v>
+        <v>60.15</v>
       </c>
       <c r="R7" t="n">
-        <v>2.61</v>
+        <v>0.86</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.86</v>
+        <v>-5.21</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1108,14 +1134,10 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1123,76 +1145,81 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Momentum 5D extendido; Débil vs QQQ</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.449999999999999</v>
+        <v>150.85</v>
       </c>
       <c r="D8" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E8" t="n">
-        <v>-10.77</v>
+        <v>-2.6</v>
       </c>
       <c r="F8" t="n">
-        <v>23.54</v>
+        <v>1.08</v>
       </c>
       <c r="G8" t="n">
-        <v>13.27</v>
+        <v>1.62</v>
       </c>
       <c r="H8" t="n">
-        <v>8.01</v>
+        <v>-10.37</v>
       </c>
       <c r="I8" t="n">
-        <v>0.97</v>
+        <v>0.46</v>
       </c>
       <c r="J8" t="n">
-        <v>0.65</v>
+        <v>4.02</v>
       </c>
       <c r="K8" t="n">
-        <v>7.65</v>
+        <v>2.67</v>
       </c>
       <c r="L8" t="n">
-        <v>8.220000000000001</v>
+        <v>149.44</v>
       </c>
       <c r="M8" t="n">
-        <v>8.550000000000001</v>
+        <v>151.45</v>
       </c>
       <c r="N8" t="n">
-        <v>7.58</v>
+        <v>145.42</v>
       </c>
       <c r="O8" t="n">
-        <v>9.869999999999999</v>
+        <v>159.7</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>55.4</v>
+        <v>52.21</v>
       </c>
       <c r="R8" t="n">
-        <v>0.96</v>
+        <v>0.5</v>
       </c>
       <c r="S8" t="n">
-        <v>-15.88</v>
+        <v>-3.11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1206,14 +1233,10 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1221,76 +1244,81 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Momentum negativo; Volatilidad alta</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; Tendencia larga positiva; RSI saludable; Histograma MACD mejora</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>404.54</v>
+        <v>503.79</v>
       </c>
       <c r="D9" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E9" t="n">
-        <v>0.73</v>
+        <v>4.36</v>
       </c>
       <c r="F9" t="n">
-        <v>9.460000000000001</v>
+        <v>25.56</v>
       </c>
       <c r="G9" t="n">
-        <v>10.21</v>
+        <v>42.14</v>
       </c>
       <c r="H9" t="n">
-        <v>-6.07</v>
+        <v>14.11</v>
       </c>
       <c r="I9" t="n">
-        <v>0.98</v>
+        <v>1.39</v>
       </c>
       <c r="J9" t="n">
-        <v>15.67</v>
+        <v>19.23</v>
       </c>
       <c r="K9" t="n">
-        <v>3.87</v>
+        <v>3.82</v>
       </c>
       <c r="L9" t="n">
-        <v>399.05</v>
+        <v>497.06</v>
       </c>
       <c r="M9" t="n">
-        <v>406.89</v>
+        <v>506.67</v>
       </c>
       <c r="N9" t="n">
-        <v>383.38</v>
+        <v>477.83</v>
       </c>
       <c r="O9" t="n">
-        <v>439.02</v>
+        <v>546.1</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>65.77</v>
+        <v>66.97</v>
       </c>
       <c r="R9" t="n">
-        <v>3.38</v>
+        <v>9.9</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.68</v>
+        <v>-5.61</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1307,7 +1335,11 @@
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1315,77 +1347,82 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>RSI algo alto; Débil vs QQQ</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>RSI algo alto; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>80.78</v>
+        <v>734.6799999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="E10" t="n">
-        <v>5.53</v>
+        <v>1.51</v>
       </c>
       <c r="F10" t="n">
-        <v>12.71</v>
+        <v>5.79</v>
       </c>
       <c r="G10" t="n">
-        <v>13.58</v>
+        <v>8.06</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.82</v>
+        <v>-5.66</v>
       </c>
       <c r="I10" t="n">
-        <v>0.74</v>
+        <v>0.58</v>
       </c>
       <c r="J10" t="n">
-        <v>4.22</v>
+        <v>6.74</v>
       </c>
       <c r="K10" t="n">
-        <v>5.23</v>
+        <v>0.92</v>
       </c>
       <c r="L10" t="n">
-        <v>79.3</v>
+        <v>732.3200000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>81.41</v>
+        <v>735.6900000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>75.08</v>
+        <v>725.58</v>
       </c>
       <c r="O10" t="n">
-        <v>90.06999999999999</v>
+        <v>749.51</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>42.3</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="R10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S10" t="n">
         <v>-0.82</v>
       </c>
-      <c r="S10" t="n">
-        <v>-13.44</v>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>MEDIA</t>
@@ -1398,87 +1435,96 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; MACD mejorando; Momentum 5D sano</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>RSI algo alto; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>117.35</v>
+        <v>204.97</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E11" t="n">
-        <v>46.12</v>
+        <v>3.65</v>
       </c>
       <c r="F11" t="n">
-        <v>66.17</v>
+        <v>11.15</v>
       </c>
       <c r="G11" t="n">
-        <v>77.78</v>
+        <v>24.74</v>
       </c>
       <c r="H11" t="n">
-        <v>50.64</v>
+        <v>-0.3</v>
       </c>
       <c r="I11" t="n">
-        <v>2.02</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
-        <v>8.640000000000001</v>
+        <v>12.37</v>
       </c>
       <c r="K11" t="n">
-        <v>7.36</v>
+        <v>6.04</v>
       </c>
       <c r="L11" t="n">
-        <v>114.33</v>
+        <v>200.64</v>
       </c>
       <c r="M11" t="n">
-        <v>118.65</v>
+        <v>206.83</v>
       </c>
       <c r="N11" t="n">
-        <v>105.69</v>
+        <v>188.26</v>
       </c>
       <c r="O11" t="n">
-        <v>136.36</v>
+        <v>232.19</v>
       </c>
       <c r="P11" t="n">
         <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>68.15000000000001</v>
+        <v>49.33</v>
       </c>
       <c r="R11" t="n">
-        <v>39.01</v>
+        <v>3.01</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.32</v>
+        <v>-6.17</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1492,7 +1538,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>ALTO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1502,81 +1548,86 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>RSI algo alto; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Tendencia larga débil; Volumen bajo; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>388.64</v>
+        <v>204.41</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E12" t="n">
-        <v>1.41</v>
+        <v>-2.12</v>
       </c>
       <c r="F12" t="n">
-        <v>20.95</v>
+        <v>26.79</v>
       </c>
       <c r="G12" t="n">
-        <v>25.86</v>
+        <v>63.16</v>
       </c>
       <c r="H12" t="n">
-        <v>5.42</v>
+        <v>15.34</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1</v>
+        <v>0.51</v>
       </c>
       <c r="J12" t="n">
-        <v>10.65</v>
+        <v>18.09</v>
       </c>
       <c r="K12" t="n">
-        <v>2.74</v>
+        <v>8.85</v>
       </c>
       <c r="L12" t="n">
-        <v>384.91</v>
+        <v>198.08</v>
       </c>
       <c r="M12" t="n">
-        <v>390.24</v>
+        <v>207.12</v>
       </c>
       <c r="N12" t="n">
-        <v>374.26</v>
+        <v>179.98</v>
       </c>
       <c r="O12" t="n">
-        <v>412.07</v>
+        <v>244.22</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>82.15000000000001</v>
+        <v>52.42</v>
       </c>
       <c r="R12" t="n">
-        <v>7.69</v>
+        <v>2.06</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.32</v>
+        <v>-14.65</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1590,7 +1641,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>ALTO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1600,81 +1651,86 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Algo extendida sobre MA20</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>MACD sin confirmar; Volumen bajo; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>713.29</v>
+        <v>427.91</v>
       </c>
       <c r="D13" t="n">
         <v>86</v>
       </c>
       <c r="E13" t="n">
-        <v>6.01</v>
+        <v>9.9</v>
       </c>
       <c r="F13" t="n">
-        <v>15.53</v>
+        <v>17.49</v>
       </c>
       <c r="G13" t="n">
-        <v>18.9</v>
+        <v>2.51</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.88</v>
+        <v>0.65</v>
       </c>
       <c r="J13" t="n">
-        <v>9.84</v>
+        <v>16.76</v>
       </c>
       <c r="K13" t="n">
-        <v>1.38</v>
+        <v>3.92</v>
       </c>
       <c r="L13" t="n">
-        <v>709.84</v>
+        <v>422.04</v>
       </c>
       <c r="M13" t="n">
-        <v>714.77</v>
+        <v>430.42</v>
       </c>
       <c r="N13" t="n">
-        <v>700</v>
+        <v>405.28</v>
       </c>
       <c r="O13" t="n">
-        <v>734.95</v>
+        <v>464.78</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>86.72</v>
+        <v>66.81</v>
       </c>
       <c r="R13" t="n">
-        <v>7.17</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.18</v>
+        <v>-4.73</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1688,7 +1744,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>ALTO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1698,81 +1754,86 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Momentum 5D extendido; Algo extendida sobre MA20</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Fuerte vs QQQ</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Tendencia larga débil; RSI algo alto; Volumen bajo; Momentum 5D extendido; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>795.33</v>
+        <v>294.15</v>
       </c>
       <c r="D14" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E14" t="n">
-        <v>37.97</v>
+        <v>3.6</v>
       </c>
       <c r="F14" t="n">
-        <v>86.45</v>
+        <v>13.75</v>
       </c>
       <c r="G14" t="n">
-        <v>92.2</v>
+        <v>15.11</v>
       </c>
       <c r="H14" t="n">
-        <v>70.92</v>
+        <v>2.3</v>
       </c>
       <c r="I14" t="n">
-        <v>1.56</v>
+        <v>0.48</v>
       </c>
       <c r="J14" t="n">
-        <v>45.86</v>
+        <v>6.25</v>
       </c>
       <c r="K14" t="n">
-        <v>5.77</v>
+        <v>2.13</v>
       </c>
       <c r="L14" t="n">
-        <v>779.28</v>
+        <v>291.96</v>
       </c>
       <c r="M14" t="n">
-        <v>802.21</v>
+        <v>295.09</v>
       </c>
       <c r="N14" t="n">
-        <v>733.41</v>
+        <v>285.71</v>
       </c>
       <c r="O14" t="n">
-        <v>896.23</v>
+        <v>307.91</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>89.27</v>
+        <v>75.62</v>
       </c>
       <c r="R14" t="n">
-        <v>46.25</v>
+        <v>6.41</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.85</v>
+        <v>-0.25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1801,12 +1862,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -1822,55 +1888,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>219.44</v>
+        <v>218.52</v>
       </c>
       <c r="D15" t="n">
         <v>96</v>
       </c>
       <c r="E15" t="n">
-        <v>10.56</v>
+        <v>11.21</v>
       </c>
       <c r="F15" t="n">
-        <v>15.92</v>
+        <v>11.2</v>
       </c>
       <c r="G15" t="n">
-        <v>17.39</v>
+        <v>19.54</v>
       </c>
       <c r="H15" t="n">
-        <v>0.39</v>
+        <v>-0.25</v>
       </c>
       <c r="I15" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="J15" t="n">
-        <v>7.7</v>
+        <v>8.08</v>
       </c>
       <c r="K15" t="n">
-        <v>3.51</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
-        <v>216.75</v>
+        <v>215.69</v>
       </c>
       <c r="M15" t="n">
-        <v>220.59</v>
+        <v>219.73</v>
       </c>
       <c r="N15" t="n">
-        <v>209.05</v>
+        <v>207.62</v>
       </c>
       <c r="O15" t="n">
-        <v>236.37</v>
+        <v>236.29</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>64.92</v>
+        <v>62.54</v>
       </c>
       <c r="R15" t="n">
-        <v>7.21</v>
+        <v>6.19</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.29</v>
+        <v>-2.34</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1895,80 +1961,85 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Subida muy extendida 5D; Algo extendida sobre MA20</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Volumen bajo; Subida muy extendida 5D</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>443.62</v>
+        <v>700.5599999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E16" t="n">
-        <v>13.35</v>
+        <v>2.78</v>
       </c>
       <c r="F16" t="n">
-        <v>12.1</v>
+        <v>11.45</v>
       </c>
       <c r="G16" t="n">
-        <v>35.26</v>
+        <v>16.53</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.43</v>
+        <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>1.18</v>
+        <v>0.76</v>
       </c>
       <c r="J16" t="n">
-        <v>17.89</v>
+        <v>10.25</v>
       </c>
       <c r="K16" t="n">
-        <v>4.03</v>
+        <v>1.46</v>
       </c>
       <c r="L16" t="n">
-        <v>437.36</v>
+        <v>696.97</v>
       </c>
       <c r="M16" t="n">
-        <v>446.3</v>
+        <v>702.09</v>
       </c>
       <c r="N16" t="n">
-        <v>419.47</v>
+        <v>686.72</v>
       </c>
       <c r="O16" t="n">
-        <v>482.98</v>
+        <v>723.1</v>
       </c>
       <c r="P16" t="n">
         <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>64.68000000000001</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>10.08</v>
+        <v>4.69</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.08</v>
+        <v>-1.96</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1989,76 +2060,81 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Subida muy extendida 5D; Débil vs QQQ; Algo extendida sobre MA20</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1565.81</v>
+        <v>117.43</v>
       </c>
       <c r="D17" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E17" t="n">
-        <v>12.96</v>
+        <v>49.09</v>
       </c>
       <c r="F17" t="n">
-        <v>4.6</v>
+        <v>62.59</v>
       </c>
       <c r="G17" t="n">
-        <v>11.54</v>
+        <v>74.12</v>
       </c>
       <c r="H17" t="n">
-        <v>-10.93</v>
+        <v>51.14</v>
       </c>
       <c r="I17" t="n">
-        <v>1.16</v>
+        <v>0.92</v>
       </c>
       <c r="J17" t="n">
-        <v>61.22</v>
+        <v>8.81</v>
       </c>
       <c r="K17" t="n">
-        <v>3.91</v>
+        <v>7.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1544.38</v>
+        <v>114.34</v>
       </c>
       <c r="M17" t="n">
-        <v>1574.99</v>
+        <v>118.75</v>
       </c>
       <c r="N17" t="n">
-        <v>1483.16</v>
+        <v>105.54</v>
       </c>
       <c r="O17" t="n">
-        <v>1700.5</v>
+        <v>136.8</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>60.07</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>7.17</v>
+        <v>35.48</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.85</v>
+        <v>-5.26</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2083,19 +2159,24 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Subida muy extendida 5D; Débil vs QQQ; Algo extendida sobre MA20</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>RSI algo alto; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2104,55 +2185,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>292.68</v>
+        <v>384.89</v>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E18" t="n">
-        <v>5.73</v>
+        <v>-0.91</v>
       </c>
       <c r="F18" t="n">
-        <v>12.92</v>
+        <v>15.61</v>
       </c>
       <c r="G18" t="n">
-        <v>11.83</v>
+        <v>25.98</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.61</v>
+        <v>4.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.51</v>
       </c>
       <c r="J18" t="n">
-        <v>6.64</v>
+        <v>10.53</v>
       </c>
       <c r="K18" t="n">
-        <v>2.27</v>
+        <v>2.74</v>
       </c>
       <c r="L18" t="n">
-        <v>290.36</v>
+        <v>381.2</v>
       </c>
       <c r="M18" t="n">
-        <v>293.68</v>
+        <v>386.47</v>
       </c>
       <c r="N18" t="n">
-        <v>283.72</v>
+        <v>370.67</v>
       </c>
       <c r="O18" t="n">
-        <v>307.28</v>
+        <v>408.06</v>
       </c>
       <c r="P18" t="n">
         <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>78.04000000000001</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>6.47</v>
+        <v>5.89</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.71</v>
+        <v>-4.26</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2177,76 +2258,81 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>296.05</v>
+        <v>116.66</v>
       </c>
       <c r="D19" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E19" t="n">
-        <v>14.5</v>
+        <v>7.87</v>
       </c>
       <c r="F19" t="n">
-        <v>10.75</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>28.15</v>
+        <v>149.33</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.78</v>
+        <v>71.37</v>
       </c>
       <c r="I19" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="J19" t="n">
-        <v>13.7</v>
+        <v>9.15</v>
       </c>
       <c r="K19" t="n">
-        <v>4.63</v>
+        <v>7.84</v>
       </c>
       <c r="L19" t="n">
-        <v>291.25</v>
+        <v>113.46</v>
       </c>
       <c r="M19" t="n">
-        <v>298.11</v>
+        <v>118.03</v>
       </c>
       <c r="N19" t="n">
-        <v>277.55</v>
+        <v>104.31</v>
       </c>
       <c r="O19" t="n">
-        <v>326.19</v>
+        <v>136.79</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>66.63</v>
+        <v>77.66</v>
       </c>
       <c r="R19" t="n">
-        <v>10.43</v>
+        <v>29.3</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.32</v>
+        <v>-12.12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2271,76 +2357,81 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>RSI algo alto; Subida muy extendida 5D; Débil vs QQQ; Algo extendida sobre MA20</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado; Momentum 5D extendido; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>739.3</v>
+        <v>32.13</v>
       </c>
       <c r="D20" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E20" t="n">
-        <v>2.97</v>
+        <v>15.45</v>
       </c>
       <c r="F20" t="n">
-        <v>7.75</v>
+        <v>18.13</v>
       </c>
       <c r="G20" t="n">
-        <v>8.81</v>
+        <v>5.21</v>
       </c>
       <c r="H20" t="n">
-        <v>-7.78</v>
+        <v>6.68</v>
       </c>
       <c r="I20" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="J20" t="n">
-        <v>6.73</v>
+        <v>2.43</v>
       </c>
       <c r="K20" t="n">
-        <v>0.91</v>
+        <v>7.56</v>
       </c>
       <c r="L20" t="n">
-        <v>736.9400000000001</v>
+        <v>31.28</v>
       </c>
       <c r="M20" t="n">
-        <v>740.3099999999999</v>
+        <v>32.49</v>
       </c>
       <c r="N20" t="n">
-        <v>730.21</v>
+        <v>28.85</v>
       </c>
       <c r="O20" t="n">
-        <v>754.11</v>
+        <v>37.47</v>
       </c>
       <c r="P20" t="n">
         <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>80.52</v>
+        <v>56.5</v>
       </c>
       <c r="R20" t="n">
-        <v>3.29</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2</v>
+        <v>-11.66</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2365,12 +2456,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Débil vs QQQ</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Tendencia larga débil; Volumen bajo; Subida muy extendida 5D; Algo extendida sobre MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -2386,55 +2482,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>56.89</v>
+        <v>53.75</v>
       </c>
       <c r="D21" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E21" t="n">
-        <v>24.35</v>
+        <v>11.98</v>
       </c>
       <c r="F21" t="n">
-        <v>91.16</v>
+        <v>50.31</v>
       </c>
       <c r="G21" t="n">
-        <v>81.76000000000001</v>
+        <v>57.58</v>
       </c>
       <c r="H21" t="n">
-        <v>75.63</v>
+        <v>38.86</v>
       </c>
       <c r="I21" t="n">
-        <v>1.47</v>
+        <v>0.78</v>
       </c>
       <c r="J21" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K21" t="n">
-        <v>7.56</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>55.38</v>
+        <v>52.14</v>
       </c>
       <c r="M21" t="n">
-        <v>57.54</v>
+        <v>54.44</v>
       </c>
       <c r="N21" t="n">
-        <v>51.08</v>
+        <v>47.54</v>
       </c>
       <c r="O21" t="n">
-        <v>66.34999999999999</v>
+        <v>63.86</v>
       </c>
       <c r="P21" t="n">
         <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>65.56</v>
+        <v>58.84</v>
       </c>
       <c r="R21" t="n">
-        <v>23.87</v>
+        <v>14.79</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.82</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2459,76 +2555,81 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI algo alto; Subida muy extendida 5D; Muy alejada de MA20</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Tendencia larga débil; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>532.76</v>
+        <v>204.84</v>
       </c>
       <c r="D22" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E22" t="n">
-        <v>15.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>35.45</v>
+        <v>54.2</v>
       </c>
       <c r="G22" t="n">
-        <v>51.66</v>
+        <v>46.52</v>
       </c>
       <c r="H22" t="n">
-        <v>19.92</v>
+        <v>42.75</v>
       </c>
       <c r="I22" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>17.4</v>
+        <v>18.85</v>
       </c>
       <c r="K22" t="n">
-        <v>3.27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>526.67</v>
+        <v>198.24</v>
       </c>
       <c r="M22" t="n">
-        <v>535.37</v>
+        <v>207.67</v>
       </c>
       <c r="N22" t="n">
-        <v>509.27</v>
+        <v>179.39</v>
       </c>
       <c r="O22" t="n">
-        <v>571.05</v>
+        <v>246.31</v>
       </c>
       <c r="P22" t="n">
         <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>78.84999999999999</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>17.53</v>
+        <v>23.4</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.18</v>
+        <v>-17.37</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2553,76 +2654,81 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Fuerte vs QQQ</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Tendencia larga débil; RSI algo alto; Momentum 5D extendido; Muy alejada de MA20; Volatilidad muy alta</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>458.79</v>
+        <v>732.46</v>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E23" t="n">
-        <v>34.33</v>
+        <v>14.41</v>
       </c>
       <c r="F23" t="n">
-        <v>85.87</v>
+        <v>57.3</v>
       </c>
       <c r="G23" t="n">
-        <v>122.78</v>
+        <v>78</v>
       </c>
       <c r="H23" t="n">
-        <v>70.34</v>
+        <v>45.85</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="J23" t="n">
-        <v>27.39</v>
+        <v>49.16</v>
       </c>
       <c r="K23" t="n">
-        <v>5.97</v>
+        <v>6.71</v>
       </c>
       <c r="L23" t="n">
-        <v>449.2</v>
+        <v>715.26</v>
       </c>
       <c r="M23" t="n">
-        <v>462.9</v>
+        <v>739.83</v>
       </c>
       <c r="N23" t="n">
-        <v>421.82</v>
+        <v>666.1</v>
       </c>
       <c r="O23" t="n">
-        <v>519.04</v>
+        <v>840.61</v>
       </c>
       <c r="P23" t="n">
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>80.33</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="R23" t="n">
-        <v>36.21</v>
+        <v>31.46</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.22</v>
+        <v>-10.53</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2647,76 +2753,81 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>129.44</v>
+        <v>436.53</v>
       </c>
       <c r="D24" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>35.14</v>
+        <v>22.88</v>
       </c>
       <c r="F24" t="n">
-        <v>98.59</v>
+        <v>71.14</v>
       </c>
       <c r="G24" t="n">
-        <v>178.49</v>
+        <v>110.56</v>
       </c>
       <c r="H24" t="n">
-        <v>83.06</v>
+        <v>59.69</v>
       </c>
       <c r="I24" t="n">
-        <v>1.18</v>
+        <v>0.58</v>
       </c>
       <c r="J24" t="n">
-        <v>8.390000000000001</v>
+        <v>28.31</v>
       </c>
       <c r="K24" t="n">
-        <v>6.48</v>
+        <v>6.49</v>
       </c>
       <c r="L24" t="n">
-        <v>126.5</v>
+        <v>426.62</v>
       </c>
       <c r="M24" t="n">
-        <v>130.7</v>
+        <v>440.78</v>
       </c>
       <c r="N24" t="n">
-        <v>118.12</v>
+        <v>398.31</v>
       </c>
       <c r="O24" t="n">
-        <v>147.89</v>
+        <v>498.82</v>
       </c>
       <c r="P24" t="n">
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>88.95</v>
+        <v>72.89</v>
       </c>
       <c r="R24" t="n">
-        <v>47.8</v>
+        <v>26.2</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.49</v>
+        <v>-6.97</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2741,76 +2852,81 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>RSI sobrecomprado; Volumen bajo; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>33.52</v>
+        <v>1766.88</v>
       </c>
       <c r="D25" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E25" t="n">
-        <v>20.06</v>
+        <v>1.96</v>
       </c>
       <c r="F25" t="n">
-        <v>29.07</v>
+        <v>-1.62</v>
       </c>
       <c r="G25" t="n">
-        <v>10.15</v>
+        <v>20.83</v>
       </c>
       <c r="H25" t="n">
-        <v>13.54</v>
+        <v>-13.07</v>
       </c>
       <c r="I25" t="n">
-        <v>1.02</v>
+        <v>0.48</v>
       </c>
       <c r="J25" t="n">
-        <v>2.34</v>
+        <v>87.83</v>
       </c>
       <c r="K25" t="n">
-        <v>6.98</v>
+        <v>4.97</v>
       </c>
       <c r="L25" t="n">
-        <v>32.7</v>
+        <v>1736.14</v>
       </c>
       <c r="M25" t="n">
-        <v>33.87</v>
+        <v>1780.06</v>
       </c>
       <c r="N25" t="n">
-        <v>30.36</v>
+        <v>1648.3</v>
       </c>
       <c r="O25" t="n">
-        <v>38.66</v>
+        <v>1960.12</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>61.54</v>
+        <v>46.88</v>
       </c>
       <c r="R25" t="n">
-        <v>15.08</v>
+        <v>-1.67</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.84</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2824,91 +2940,96 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>ALTO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>SELL / EVITAR</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; Tendencia larga positiva; Momentum 5D sano</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>445</v>
+        <v>412.11</v>
       </c>
       <c r="D26" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="E26" t="n">
-        <v>13.37</v>
+        <v>-3.57</v>
       </c>
       <c r="F26" t="n">
-        <v>26.27</v>
+        <v>8.23</v>
       </c>
       <c r="G26" t="n">
-        <v>6.7</v>
+        <v>27</v>
       </c>
       <c r="H26" t="n">
-        <v>10.74</v>
+        <v>-3.22</v>
       </c>
       <c r="I26" t="n">
-        <v>1.17</v>
+        <v>0.54</v>
       </c>
       <c r="J26" t="n">
-        <v>15.49</v>
+        <v>15.39</v>
       </c>
       <c r="K26" t="n">
-        <v>3.48</v>
+        <v>3.73</v>
       </c>
       <c r="L26" t="n">
-        <v>439.58</v>
+        <v>406.73</v>
       </c>
       <c r="M26" t="n">
-        <v>447.32</v>
+        <v>414.42</v>
       </c>
       <c r="N26" t="n">
-        <v>424.09</v>
+        <v>391.34</v>
       </c>
       <c r="O26" t="n">
-        <v>479.07</v>
+        <v>445.98</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>78.11</v>
+        <v>45.45</v>
       </c>
       <c r="R26" t="n">
-        <v>13.7</v>
+        <v>-0.5</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.93</v>
+        <v>-5.84</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -2918,91 +3039,96 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>ALTO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>SELL / EVITAR</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; Tendencia larga positiva</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>268.99</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.12</v>
+        <v>-5.58</v>
       </c>
       <c r="F27" t="n">
-        <v>12.13</v>
+        <v>5.77</v>
       </c>
       <c r="G27" t="n">
-        <v>34.76</v>
+        <v>-17.58</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.4</v>
+        <v>-5.68</v>
       </c>
       <c r="I27" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
-        <v>7.23</v>
+        <v>0.46</v>
       </c>
       <c r="K27" t="n">
-        <v>2.69</v>
+        <v>5.21</v>
       </c>
       <c r="L27" t="n">
-        <v>266.46</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>270.07</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>259.23</v>
+        <v>8.26</v>
       </c>
       <c r="O27" t="n">
-        <v>284.9</v>
+        <v>9.9</v>
       </c>
       <c r="P27" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>72.06</v>
+        <v>42.75</v>
       </c>
       <c r="R27" t="n">
-        <v>3.04</v>
+        <v>-3.36</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.44</v>
+        <v>-10.61</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3012,87 +3138,92 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>ALTO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>SELL / EVITAR</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; MACD sin confirmar; Débil vs QQQ</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; MACD positivo</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; Momentum negativo; Débil vs QQQ; Lejos del máximo 20D</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>237.53</v>
+        <v>186.6</v>
       </c>
       <c r="D28" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E28" t="n">
-        <v>41.07</v>
+        <v>-3.14</v>
       </c>
       <c r="F28" t="n">
-        <v>80.98999999999999</v>
+        <v>-0.22</v>
       </c>
       <c r="G28" t="n">
-        <v>72.64</v>
+        <v>2.55</v>
       </c>
       <c r="H28" t="n">
-        <v>65.45999999999999</v>
+        <v>-11.67</v>
       </c>
       <c r="I28" t="n">
-        <v>1.73</v>
+        <v>0.36</v>
       </c>
       <c r="J28" t="n">
-        <v>16.45</v>
+        <v>4.52</v>
       </c>
       <c r="K28" t="n">
-        <v>6.93</v>
+        <v>2.42</v>
       </c>
       <c r="L28" t="n">
-        <v>231.77</v>
+        <v>185.02</v>
       </c>
       <c r="M28" t="n">
-        <v>240</v>
+        <v>187.28</v>
       </c>
       <c r="N28" t="n">
-        <v>215.32</v>
+        <v>180.49</v>
       </c>
       <c r="O28" t="n">
-        <v>273.72</v>
+        <v>196.55</v>
       </c>
       <c r="P28" t="n">
         <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>89.48</v>
+        <v>50.42</v>
       </c>
       <c r="R28" t="n">
-        <v>46.26</v>
+        <v>-0.22</v>
       </c>
       <c r="S28" t="n">
-        <v>-4.18</v>
+        <v>-3.88</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3106,30 +3237,35 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>ALTO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>SELL / EVITAR</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20</t>
+          <t>Mercado ALCISTA; Tendencia larga positiva; RSI saludable; Histograma MACD mejora</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3138,55 +3274,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>149.68</v>
+        <v>56.18</v>
       </c>
       <c r="D29" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.61</v>
+        <v>-5.33</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.94</v>
+        <v>1.44</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.17</v>
+        <v>22.52</v>
       </c>
       <c r="H29" t="n">
-        <v>-17.47</v>
+        <v>-10.01</v>
       </c>
       <c r="I29" t="n">
-        <v>0.82</v>
+        <v>0.44</v>
       </c>
       <c r="J29" t="n">
-        <v>4.05</v>
+        <v>1.87</v>
       </c>
       <c r="K29" t="n">
-        <v>2.71</v>
+        <v>3.32</v>
       </c>
       <c r="L29" t="n">
-        <v>148.26</v>
+        <v>55.53</v>
       </c>
       <c r="M29" t="n">
-        <v>150.29</v>
+        <v>56.46</v>
       </c>
       <c r="N29" t="n">
-        <v>144.21</v>
+        <v>53.66</v>
       </c>
       <c r="O29" t="n">
-        <v>158.59</v>
+        <v>60.29</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>52.17</v>
+        <v>47.73</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.22</v>
+        <v>-1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>-3.86</v>
+        <v>-7.58</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3211,80 +3347,85 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Tendencia larga positiva; RSI saludable; MACD mejorando</t>
+          <t>SELL / EVITAR</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Débil vs QQQ</t>
+          <t>Mercado ALCISTA; Tendencia larga positiva; Histograma MACD mejora</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>184.74</v>
+        <v>45.68</v>
       </c>
       <c r="D30" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.92</v>
+        <v>-1.74</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.67</v>
+        <v>-4.77</v>
       </c>
       <c r="G30" t="n">
-        <v>2.27</v>
+        <v>13.72</v>
       </c>
       <c r="H30" t="n">
-        <v>-19.2</v>
+        <v>-16.22</v>
       </c>
       <c r="I30" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="J30" t="n">
-        <v>4.61</v>
+        <v>1.61</v>
       </c>
       <c r="K30" t="n">
-        <v>2.49</v>
+        <v>3.52</v>
       </c>
       <c r="L30" t="n">
-        <v>183.13</v>
+        <v>45.12</v>
       </c>
       <c r="M30" t="n">
-        <v>185.43</v>
+        <v>45.92</v>
       </c>
       <c r="N30" t="n">
-        <v>178.52</v>
+        <v>43.51</v>
       </c>
       <c r="O30" t="n">
-        <v>194.88</v>
+        <v>49.22</v>
       </c>
       <c r="P30" t="n">
         <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>48.05</v>
+        <v>25.74</v>
       </c>
       <c r="R30" t="n">
-        <v>-1.23</v>
+        <v>-6.81</v>
       </c>
       <c r="S30" t="n">
-        <v>-4.84</v>
+        <v>-12.66</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3305,12 +3446,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Tendencia larga positiva; RSI saludable; MACD mejorando</t>
+          <t>SELL / EVITAR</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Momentum negativo; Débil vs QQQ</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -3326,59 +3472,59 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>412.66</v>
+        <v>409.3</v>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.23</v>
+        <v>-0.51</v>
       </c>
       <c r="F31" t="n">
-        <v>7.36</v>
+        <v>4.12</v>
       </c>
       <c r="G31" t="n">
-        <v>2.93</v>
+        <v>2.22</v>
       </c>
       <c r="H31" t="n">
-        <v>-8.17</v>
+        <v>-7.33</v>
       </c>
       <c r="I31" t="n">
-        <v>0.96</v>
+        <v>0.45</v>
       </c>
       <c r="J31" t="n">
-        <v>11.8</v>
+        <v>11.72</v>
       </c>
       <c r="K31" t="n">
         <v>2.86</v>
       </c>
       <c r="L31" t="n">
-        <v>408.53</v>
+        <v>405.2</v>
       </c>
       <c r="M31" t="n">
-        <v>414.43</v>
+        <v>411.06</v>
       </c>
       <c r="N31" t="n">
-        <v>396.73</v>
+        <v>393.48</v>
       </c>
       <c r="O31" t="n">
-        <v>438.62</v>
+        <v>435.08</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>43.47</v>
+        <v>35.72</v>
       </c>
       <c r="R31" t="n">
-        <v>-1.17</v>
+        <v>-2.17</v>
       </c>
       <c r="S31" t="n">
-        <v>-4.85</v>
+        <v>-5.63</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3399,76 +3545,81 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
+          <t>SELL / EVITAR</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
           <t>Mercado ALCISTA; MA20 sobre MA50</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Débil vs QQQ</t>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>55.14</v>
+        <v>77.72</v>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E32" t="n">
-        <v>-8.51</v>
+        <v>0.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-5.03</v>
+        <v>-1.73</v>
       </c>
       <c r="G32" t="n">
-        <v>21.79</v>
+        <v>2.3</v>
       </c>
       <c r="H32" t="n">
-        <v>-20.56</v>
+        <v>-13.18</v>
       </c>
       <c r="I32" t="n">
-        <v>1.04</v>
+        <v>0.34</v>
       </c>
       <c r="J32" t="n">
-        <v>1.85</v>
+        <v>4.26</v>
       </c>
       <c r="K32" t="n">
-        <v>3.36</v>
+        <v>5.49</v>
       </c>
       <c r="L32" t="n">
-        <v>54.49</v>
+        <v>76.23</v>
       </c>
       <c r="M32" t="n">
-        <v>55.42</v>
+        <v>78.36</v>
       </c>
       <c r="N32" t="n">
-        <v>52.64</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>59.21</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P32" t="n">
         <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>46.84</v>
+        <v>35.81</v>
       </c>
       <c r="R32" t="n">
-        <v>-3.05</v>
+        <v>-4.49</v>
       </c>
       <c r="S32" t="n">
-        <v>-9.289999999999999</v>
+        <v>-16.72</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3493,76 +3644,81 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Tendencia larga positiva; MACD mejorando</t>
+          <t>SELL / EVITAR</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Momentum negativo; Débil vs QQQ</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16.26</v>
+        <v>599.88</v>
       </c>
       <c r="D33" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E33" t="n">
-        <v>0.37</v>
+        <v>-0.84</v>
       </c>
       <c r="F33" t="n">
-        <v>-4.63</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>-15.75</v>
+        <v>-6.15</v>
       </c>
       <c r="H33" t="n">
-        <v>-20.16</v>
+        <v>-20.9</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.44</v>
       </c>
       <c r="J33" t="n">
-        <v>0.82</v>
+        <v>18.43</v>
       </c>
       <c r="K33" t="n">
-        <v>5.02</v>
+        <v>3.07</v>
       </c>
       <c r="L33" t="n">
-        <v>15.97</v>
+        <v>593.4299999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>16.38</v>
+        <v>602.64</v>
       </c>
       <c r="N33" t="n">
-        <v>15.16</v>
+        <v>575</v>
       </c>
       <c r="O33" t="n">
-        <v>18.06</v>
+        <v>640.4299999999999</v>
       </c>
       <c r="P33" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>32.4</v>
+        <v>23.8</v>
       </c>
       <c r="R33" t="n">
-        <v>-7.35</v>
+        <v>-6.84</v>
       </c>
       <c r="S33" t="n">
-        <v>-19.23</v>
+        <v>-13.25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3587,76 +3743,81 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; MACD mejorando</t>
+          <t>SELL / EVITAR</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>136.89</v>
+        <v>15.72</v>
       </c>
       <c r="D34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E34" t="n">
-        <v>-6.26</v>
+        <v>-1.9</v>
       </c>
       <c r="F34" t="n">
-        <v>3.41</v>
+        <v>-12.26</v>
       </c>
       <c r="G34" t="n">
-        <v>6.01</v>
+        <v>-19.86</v>
       </c>
       <c r="H34" t="n">
-        <v>-12.12</v>
+        <v>-23.71</v>
       </c>
       <c r="I34" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="J34" t="n">
-        <v>6.24</v>
+        <v>0.83</v>
       </c>
       <c r="K34" t="n">
-        <v>4.56</v>
+        <v>5.27</v>
       </c>
       <c r="L34" t="n">
-        <v>134.71</v>
+        <v>15.43</v>
       </c>
       <c r="M34" t="n">
-        <v>137.83</v>
+        <v>15.84</v>
       </c>
       <c r="N34" t="n">
-        <v>128.47</v>
+        <v>14.6</v>
       </c>
       <c r="O34" t="n">
-        <v>150.62</v>
+        <v>17.54</v>
       </c>
       <c r="P34" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q34" t="n">
-        <v>40.84</v>
+        <v>28.04</v>
       </c>
       <c r="R34" t="n">
-        <v>-3.23</v>
+        <v>-9.9</v>
       </c>
       <c r="S34" t="n">
-        <v>-10.34</v>
+        <v>-21.93</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3681,76 +3842,81 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MACD mejorando</t>
+          <t>SELL / EVITAR</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Momentum negativo</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>598.86</v>
+        <v>134.46</v>
       </c>
       <c r="D35" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.89</v>
+        <v>-1.07</v>
       </c>
       <c r="F35" t="n">
-        <v>-5.62</v>
+        <v>-0.92</v>
       </c>
       <c r="G35" t="n">
-        <v>-7.76</v>
+        <v>2.32</v>
       </c>
       <c r="H35" t="n">
-        <v>-21.15</v>
+        <v>-12.37</v>
       </c>
       <c r="I35" t="n">
-        <v>0.92</v>
+        <v>0.49</v>
       </c>
       <c r="J35" t="n">
-        <v>18.32</v>
+        <v>6.04</v>
       </c>
       <c r="K35" t="n">
-        <v>3.06</v>
+        <v>4.5</v>
       </c>
       <c r="L35" t="n">
-        <v>592.45</v>
+        <v>132.34</v>
       </c>
       <c r="M35" t="n">
-        <v>601.61</v>
+        <v>135.36</v>
       </c>
       <c r="N35" t="n">
-        <v>574.13</v>
+        <v>126.3</v>
       </c>
       <c r="O35" t="n">
-        <v>639.17</v>
+        <v>147.75</v>
       </c>
       <c r="P35" t="n">
         <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>26.31</v>
+        <v>29.98</v>
       </c>
       <c r="R35" t="n">
-        <v>-7.45</v>
+        <v>-4.9</v>
       </c>
       <c r="S35" t="n">
-        <v>-13.4</v>
+        <v>-11.94</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3775,76 +3941,81 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50</t>
+          <t>SELL / EVITAR</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar</t>
+          <t>Mercado ALCISTA</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>45.07</v>
+        <v>8.01</v>
       </c>
       <c r="D36" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E36" t="n">
-        <v>-10.56</v>
+        <v>-12.36</v>
       </c>
       <c r="F36" t="n">
-        <v>-5.14</v>
+        <v>14.92</v>
       </c>
       <c r="G36" t="n">
-        <v>15.68</v>
+        <v>7.37</v>
       </c>
       <c r="H36" t="n">
-        <v>-20.67</v>
+        <v>3.47</v>
       </c>
       <c r="I36" t="n">
-        <v>1.12</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
-        <v>1.56</v>
+        <v>0.65</v>
       </c>
       <c r="K36" t="n">
-        <v>3.46</v>
+        <v>8.08</v>
       </c>
       <c r="L36" t="n">
-        <v>44.52</v>
+        <v>7.78</v>
       </c>
       <c r="M36" t="n">
-        <v>45.3</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>42.96</v>
+        <v>7.14</v>
       </c>
       <c r="O36" t="n">
-        <v>48.5</v>
+        <v>9.43</v>
       </c>
       <c r="P36" t="n">
         <v>1.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>23.95</v>
+        <v>48.13</v>
       </c>
       <c r="R36" t="n">
-        <v>-8.27</v>
+        <v>-4.89</v>
       </c>
       <c r="S36" t="n">
-        <v>-13.82</v>
+        <v>-20.26</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3858,7 +4029,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
@@ -3869,12 +4040,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50</t>
+          <t>SELL / EVITAR</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; RSI saludable; Fuerte vs QQQ</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>
@@ -3890,55 +4066,55 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>28.69</v>
+        <v>27.92</v>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>-10.57</v>
+        <v>-10.43</v>
       </c>
       <c r="F37" t="n">
-        <v>2.25</v>
+        <v>-5.45</v>
       </c>
       <c r="G37" t="n">
-        <v>-4.97</v>
+        <v>-9</v>
       </c>
       <c r="H37" t="n">
-        <v>-13.28</v>
+        <v>-16.9</v>
       </c>
       <c r="I37" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="K37" t="n">
-        <v>6.31</v>
+        <v>6.32</v>
       </c>
       <c r="L37" t="n">
-        <v>28.06</v>
+        <v>27.3</v>
       </c>
       <c r="M37" t="n">
-        <v>28.96</v>
+        <v>28.18</v>
       </c>
       <c r="N37" t="n">
-        <v>26.25</v>
+        <v>25.54</v>
       </c>
       <c r="O37" t="n">
-        <v>32.67</v>
+        <v>31.8</v>
       </c>
       <c r="P37" t="n">
         <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>33.95</v>
+        <v>24.32</v>
       </c>
       <c r="R37" t="n">
-        <v>-10.21</v>
+        <v>-12.4</v>
       </c>
       <c r="S37" t="n">
-        <v>-19.86</v>
+        <v>-22.01</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3963,12 +4139,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
+          <t>SELL / EVITAR</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
           <t>Mercado ALCISTA; MA20 sobre MA50</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar</t>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -565,55 +565,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>421.22</v>
+        <v>427.29</v>
       </c>
       <c r="D2" t="n">
         <v>96</v>
       </c>
       <c r="E2" t="n">
-        <v>2.53</v>
+        <v>4.01</v>
       </c>
       <c r="F2" t="n">
-        <v>6.47</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>18.83</v>
+        <v>20.54</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.98</v>
+        <v>-3.93</v>
       </c>
       <c r="I2" t="n">
-        <v>0.61</v>
+        <v>0.79</v>
       </c>
       <c r="J2" t="n">
         <v>18.91</v>
       </c>
       <c r="K2" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
       <c r="L2" t="n">
-        <v>414.6</v>
+        <v>420.67</v>
       </c>
       <c r="M2" t="n">
-        <v>424.06</v>
+        <v>430.13</v>
       </c>
       <c r="N2" t="n">
-        <v>395.69</v>
+        <v>401.76</v>
       </c>
       <c r="O2" t="n">
-        <v>462.82</v>
+        <v>468.89</v>
       </c>
       <c r="P2" t="n">
         <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>54.9</v>
+        <v>56.8</v>
       </c>
       <c r="R2" t="n">
-        <v>4.19</v>
+        <v>5.62</v>
       </c>
       <c r="S2" t="n">
-        <v>-6.07</v>
+        <v>-4.72</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Volumen bajo; Débil vs QQQ</t>
+          <t>Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -668,55 +668,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>283.1</v>
+        <v>286.55</v>
       </c>
       <c r="D3" t="n">
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="F3" t="n">
-        <v>3.92</v>
+        <v>5.19</v>
       </c>
       <c r="G3" t="n">
-        <v>20.34</v>
+        <v>21.81</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.53</v>
+        <v>-6.74</v>
       </c>
       <c r="I3" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="J3" t="n">
         <v>14.39</v>
       </c>
       <c r="K3" t="n">
-        <v>5.08</v>
+        <v>5.02</v>
       </c>
       <c r="L3" t="n">
-        <v>278.06</v>
+        <v>281.51</v>
       </c>
       <c r="M3" t="n">
-        <v>285.26</v>
+        <v>288.71</v>
       </c>
       <c r="N3" t="n">
-        <v>263.67</v>
+        <v>267.12</v>
       </c>
       <c r="O3" t="n">
-        <v>314.77</v>
+        <v>318.22</v>
       </c>
       <c r="P3" t="n">
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>57.37</v>
+        <v>59.08</v>
       </c>
       <c r="R3" t="n">
-        <v>5.39</v>
+        <v>6.61</v>
       </c>
       <c r="S3" t="n">
-        <v>-5.63</v>
+        <v>-4.48</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -771,55 +771,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1493.25</v>
+        <v>1506.82</v>
       </c>
       <c r="D4" t="n">
         <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>3.49</v>
+        <v>4.43</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.44</v>
+        <v>-0.54</v>
       </c>
       <c r="G4" t="n">
-        <v>6.39</v>
+        <v>7.36</v>
       </c>
       <c r="H4" t="n">
-        <v>-12.89</v>
+        <v>-12.47</v>
       </c>
       <c r="I4" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="J4" t="n">
         <v>60.71</v>
       </c>
       <c r="K4" t="n">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="L4" t="n">
-        <v>1472</v>
+        <v>1485.58</v>
       </c>
       <c r="M4" t="n">
-        <v>1502.36</v>
+        <v>1515.93</v>
       </c>
       <c r="N4" t="n">
-        <v>1411.29</v>
+        <v>1424.87</v>
       </c>
       <c r="O4" t="n">
-        <v>1626.81</v>
+        <v>1640.38</v>
       </c>
       <c r="P4" t="n">
         <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>54.37</v>
+        <v>55.62</v>
       </c>
       <c r="R4" t="n">
-        <v>2.28</v>
+        <v>3.16</v>
       </c>
       <c r="S4" t="n">
-        <v>-6.4</v>
+        <v>-5.55</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Volumen bajo; Débil vs QQQ</t>
+          <t>Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -874,55 +874,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55.68</v>
+        <v>56.21</v>
       </c>
       <c r="D5" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.57</v>
+        <v>0.37</v>
       </c>
       <c r="F5" t="n">
-        <v>8.140000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="G5" t="n">
-        <v>10.5</v>
+        <v>11.55</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.31</v>
+        <v>-2.76</v>
       </c>
       <c r="I5" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="J5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="K5" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="L5" t="n">
-        <v>55.11</v>
+        <v>55.63</v>
       </c>
       <c r="M5" t="n">
-        <v>55.92</v>
+        <v>56.46</v>
       </c>
       <c r="N5" t="n">
-        <v>53.49</v>
+        <v>53.98</v>
       </c>
       <c r="O5" t="n">
-        <v>59.25</v>
+        <v>59.85</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>55.66</v>
+        <v>57.57</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>2.99</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.66</v>
+        <v>-1.73</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -973,55 +973,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>392.55</v>
+        <v>395.64</v>
       </c>
       <c r="D6" t="n">
         <v>86</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.47</v>
+        <v>0.31</v>
       </c>
       <c r="F6" t="n">
-        <v>3.33</v>
+        <v>4.14</v>
       </c>
       <c r="G6" t="n">
-        <v>7.45</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-8.119999999999999</v>
+        <v>-7.79</v>
       </c>
       <c r="I6" t="n">
-        <v>0.89</v>
+        <v>1.03</v>
       </c>
       <c r="J6" t="n">
         <v>15.57</v>
       </c>
       <c r="K6" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="L6" t="n">
-        <v>387.1</v>
+        <v>390.18</v>
       </c>
       <c r="M6" t="n">
-        <v>394.89</v>
+        <v>397.97</v>
       </c>
       <c r="N6" t="n">
-        <v>371.53</v>
+        <v>374.61</v>
       </c>
       <c r="O6" t="n">
-        <v>426.81</v>
+        <v>429.89</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>52.36</v>
+        <v>53.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="S6" t="n">
-        <v>-6.54</v>
+        <v>-5.8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1063,64 +1063,64 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>264.04</v>
+        <v>151.36</v>
       </c>
       <c r="D7" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.48</v>
+        <v>-2.27</v>
       </c>
       <c r="F7" t="n">
-        <v>6.03</v>
+        <v>1.42</v>
       </c>
       <c r="G7" t="n">
-        <v>32.82</v>
+        <v>1.96</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.42</v>
+        <v>-10.51</v>
       </c>
       <c r="I7" t="n">
-        <v>0.43</v>
+        <v>0.58</v>
       </c>
       <c r="J7" t="n">
-        <v>7.26</v>
+        <v>4.02</v>
       </c>
       <c r="K7" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="L7" t="n">
-        <v>261.5</v>
+        <v>149.95</v>
       </c>
       <c r="M7" t="n">
-        <v>265.13</v>
+        <v>151.96</v>
       </c>
       <c r="N7" t="n">
-        <v>254.24</v>
+        <v>145.93</v>
       </c>
       <c r="O7" t="n">
-        <v>280</v>
+        <v>160.21</v>
       </c>
       <c r="P7" t="n">
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>60.15</v>
+        <v>53</v>
       </c>
       <c r="R7" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.21</v>
+        <v>-2.78</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1150,76 +1150,76 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; Tendencia larga positiva; RSI saludable; Histograma MACD mejora</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>150.85</v>
+        <v>264.71</v>
       </c>
       <c r="D8" t="n">
         <v>75</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6</v>
+        <v>-3.23</v>
       </c>
       <c r="F8" t="n">
-        <v>1.08</v>
+        <v>6.3</v>
       </c>
       <c r="G8" t="n">
-        <v>1.62</v>
+        <v>33.16</v>
       </c>
       <c r="H8" t="n">
-        <v>-10.37</v>
+        <v>-5.63</v>
       </c>
       <c r="I8" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="J8" t="n">
-        <v>4.02</v>
+        <v>7.26</v>
       </c>
       <c r="K8" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="L8" t="n">
-        <v>149.44</v>
+        <v>262.17</v>
       </c>
       <c r="M8" t="n">
-        <v>151.45</v>
+        <v>265.8</v>
       </c>
       <c r="N8" t="n">
-        <v>145.42</v>
+        <v>254.91</v>
       </c>
       <c r="O8" t="n">
-        <v>159.7</v>
+        <v>280.67</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>52.21</v>
+        <v>61.11</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.11</v>
+        <v>-4.97</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1249,76 +1249,76 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; Tendencia larga positiva; RSI saludable; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>503.79</v>
+        <v>415.2</v>
       </c>
       <c r="D9" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="E9" t="n">
-        <v>4.36</v>
+        <v>-2.85</v>
       </c>
       <c r="F9" t="n">
-        <v>25.56</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>42.14</v>
+        <v>27.95</v>
       </c>
       <c r="H9" t="n">
-        <v>14.11</v>
+        <v>-2.89</v>
       </c>
       <c r="I9" t="n">
-        <v>1.39</v>
+        <v>0.65</v>
       </c>
       <c r="J9" t="n">
-        <v>19.23</v>
+        <v>15.39</v>
       </c>
       <c r="K9" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="L9" t="n">
-        <v>497.06</v>
+        <v>409.81</v>
       </c>
       <c r="M9" t="n">
-        <v>506.67</v>
+        <v>417.51</v>
       </c>
       <c r="N9" t="n">
-        <v>477.83</v>
+        <v>394.42</v>
       </c>
       <c r="O9" t="n">
-        <v>546.1</v>
+        <v>449.06</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>66.97</v>
+        <v>46.69</v>
       </c>
       <c r="R9" t="n">
-        <v>9.9</v>
+        <v>0.21</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.61</v>
+        <v>-5.14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1332,14 +1332,10 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1352,76 +1348,76 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RSI algo alto; Algo extendida sobre MA20</t>
+          <t>MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>734.6799999999999</v>
+        <v>508.96</v>
       </c>
       <c r="D10" t="n">
         <v>96</v>
       </c>
       <c r="E10" t="n">
-        <v>1.51</v>
+        <v>5.43</v>
       </c>
       <c r="F10" t="n">
-        <v>5.79</v>
+        <v>26.85</v>
       </c>
       <c r="G10" t="n">
-        <v>8.06</v>
+        <v>43.59</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.66</v>
+        <v>14.92</v>
       </c>
       <c r="I10" t="n">
-        <v>0.58</v>
+        <v>1.71</v>
       </c>
       <c r="J10" t="n">
-        <v>6.74</v>
+        <v>19.23</v>
       </c>
       <c r="K10" t="n">
-        <v>0.92</v>
+        <v>3.78</v>
       </c>
       <c r="L10" t="n">
-        <v>732.3200000000001</v>
+        <v>502.23</v>
       </c>
       <c r="M10" t="n">
-        <v>735.6900000000001</v>
+        <v>511.84</v>
       </c>
       <c r="N10" t="n">
-        <v>725.58</v>
+        <v>483</v>
       </c>
       <c r="O10" t="n">
-        <v>749.51</v>
+        <v>551.27</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>71.26000000000001</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>2.36</v>
+        <v>10.96</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.82</v>
+        <v>-4.64</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1440,7 +1436,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1460,7 +1456,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RSI algo alto; Volumen bajo; Débil vs QQQ</t>
+          <t>RSI algo alto; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
@@ -1476,55 +1472,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>204.97</v>
+        <v>204.59</v>
       </c>
       <c r="D11" t="n">
         <v>87</v>
       </c>
       <c r="E11" t="n">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="F11" t="n">
-        <v>11.15</v>
+        <v>10.94</v>
       </c>
       <c r="G11" t="n">
-        <v>24.74</v>
+        <v>24.5</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3</v>
+        <v>-0.99</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="J11" t="n">
         <v>12.37</v>
       </c>
       <c r="K11" t="n">
-        <v>6.04</v>
+        <v>6.05</v>
       </c>
       <c r="L11" t="n">
-        <v>200.64</v>
+        <v>200.25</v>
       </c>
       <c r="M11" t="n">
-        <v>206.83</v>
+        <v>206.44</v>
       </c>
       <c r="N11" t="n">
-        <v>188.26</v>
+        <v>187.88</v>
       </c>
       <c r="O11" t="n">
-        <v>232.19</v>
+        <v>231.81</v>
       </c>
       <c r="P11" t="n">
         <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>49.33</v>
+        <v>49.13</v>
       </c>
       <c r="R11" t="n">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.17</v>
+        <v>-6.35</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1579,55 +1575,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>204.41</v>
+        <v>205.09</v>
       </c>
       <c r="D12" t="n">
         <v>86</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.12</v>
+        <v>-1.8</v>
       </c>
       <c r="F12" t="n">
-        <v>26.79</v>
+        <v>27.21</v>
       </c>
       <c r="G12" t="n">
-        <v>63.16</v>
+        <v>63.71</v>
       </c>
       <c r="H12" t="n">
-        <v>15.34</v>
+        <v>15.28</v>
       </c>
       <c r="I12" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="J12" t="n">
         <v>18.09</v>
       </c>
       <c r="K12" t="n">
-        <v>8.85</v>
+        <v>8.82</v>
       </c>
       <c r="L12" t="n">
-        <v>198.08</v>
+        <v>198.76</v>
       </c>
       <c r="M12" t="n">
-        <v>207.12</v>
+        <v>207.8</v>
       </c>
       <c r="N12" t="n">
-        <v>179.98</v>
+        <v>180.66</v>
       </c>
       <c r="O12" t="n">
-        <v>244.22</v>
+        <v>244.9</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>52.42</v>
+        <v>52.64</v>
       </c>
       <c r="R12" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="S12" t="n">
-        <v>-14.65</v>
+        <v>-14.37</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1673,64 +1669,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>427.91</v>
+        <v>294.51</v>
       </c>
       <c r="D13" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>9.9</v>
+        <v>3.73</v>
       </c>
       <c r="F13" t="n">
-        <v>17.49</v>
+        <v>13.89</v>
       </c>
       <c r="G13" t="n">
-        <v>2.51</v>
+        <v>15.25</v>
       </c>
       <c r="H13" t="n">
-        <v>6.04</v>
+        <v>1.96</v>
       </c>
       <c r="I13" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="J13" t="n">
-        <v>16.76</v>
+        <v>6.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.92</v>
+        <v>2.12</v>
       </c>
       <c r="L13" t="n">
-        <v>422.04</v>
+        <v>292.32</v>
       </c>
       <c r="M13" t="n">
-        <v>430.42</v>
+        <v>295.45</v>
       </c>
       <c r="N13" t="n">
-        <v>405.28</v>
+        <v>286.07</v>
       </c>
       <c r="O13" t="n">
-        <v>464.78</v>
+        <v>308.27</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>66.81</v>
+        <v>75.83</v>
       </c>
       <c r="R13" t="n">
-        <v>8.449999999999999</v>
+        <v>6.54</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.73</v>
+        <v>-0.13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1744,7 +1740,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1754,86 +1750,86 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Fuerte vs QQQ</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI algo alto; Volumen bajo; Momentum 5D extendido; Algo extendida sobre MA20</t>
+          <t>RSI sobrecomprado; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>294.15</v>
+        <v>220.46</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6</v>
+        <v>12.19</v>
       </c>
       <c r="F14" t="n">
-        <v>13.75</v>
+        <v>12.19</v>
       </c>
       <c r="G14" t="n">
-        <v>15.11</v>
+        <v>20.6</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3</v>
+        <v>0.26</v>
       </c>
       <c r="I14" t="n">
-        <v>0.48</v>
+        <v>0.84</v>
       </c>
       <c r="J14" t="n">
-        <v>6.25</v>
+        <v>8.08</v>
       </c>
       <c r="K14" t="n">
-        <v>2.13</v>
+        <v>3.66</v>
       </c>
       <c r="L14" t="n">
-        <v>291.96</v>
+        <v>217.63</v>
       </c>
       <c r="M14" t="n">
-        <v>295.09</v>
+        <v>221.67</v>
       </c>
       <c r="N14" t="n">
-        <v>285.71</v>
+        <v>209.56</v>
       </c>
       <c r="O14" t="n">
-        <v>307.91</v>
+        <v>238.23</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>75.62</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>6.41</v>
+        <v>7.08</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.25</v>
+        <v>-1.47</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1850,11 +1846,7 @@
           <t>ALTO</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1867,76 +1859,76 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo</t>
+          <t>Subida muy extendida 5D; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>218.52</v>
+        <v>703.51</v>
       </c>
       <c r="D15" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E15" t="n">
-        <v>11.21</v>
+        <v>3.21</v>
       </c>
       <c r="F15" t="n">
-        <v>11.2</v>
+        <v>11.92</v>
       </c>
       <c r="G15" t="n">
-        <v>19.54</v>
+        <v>17.03</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.25</v>
+        <v>-0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.71</v>
+        <v>0.92</v>
       </c>
       <c r="J15" t="n">
-        <v>8.08</v>
+        <v>10.25</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>1.46</v>
       </c>
       <c r="L15" t="n">
-        <v>215.69</v>
+        <v>699.92</v>
       </c>
       <c r="M15" t="n">
-        <v>219.73</v>
+        <v>705.05</v>
       </c>
       <c r="N15" t="n">
-        <v>207.62</v>
+        <v>689.6799999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>236.29</v>
+        <v>726.05</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>62.54</v>
+        <v>76.05</v>
       </c>
       <c r="R15" t="n">
-        <v>6.19</v>
+        <v>5.11</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.34</v>
+        <v>-1.55</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1966,76 +1958,76 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Volumen bajo; Subida muy extendida 5D</t>
+          <t>RSI sobrecomprado</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>700.5599999999999</v>
+        <v>119.12</v>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E16" t="n">
-        <v>2.78</v>
+        <v>51.24</v>
       </c>
       <c r="F16" t="n">
-        <v>11.45</v>
+        <v>64.94</v>
       </c>
       <c r="G16" t="n">
-        <v>16.53</v>
+        <v>76.63</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>53.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.76</v>
+        <v>1.05</v>
       </c>
       <c r="J16" t="n">
-        <v>10.25</v>
+        <v>8.81</v>
       </c>
       <c r="K16" t="n">
-        <v>1.46</v>
+        <v>7.39</v>
       </c>
       <c r="L16" t="n">
-        <v>696.97</v>
+        <v>116.04</v>
       </c>
       <c r="M16" t="n">
-        <v>702.09</v>
+        <v>120.44</v>
       </c>
       <c r="N16" t="n">
-        <v>686.72</v>
+        <v>107.23</v>
       </c>
       <c r="O16" t="n">
-        <v>723.1</v>
+        <v>138.49</v>
       </c>
       <c r="P16" t="n">
         <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>73.70999999999999</v>
+        <v>67.52</v>
       </c>
       <c r="R16" t="n">
-        <v>4.69</v>
+        <v>37.3</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.96</v>
+        <v>-3.89</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2070,71 +2062,71 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado</t>
+          <t>RSI algo alto; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>117.43</v>
+        <v>385.97</v>
       </c>
       <c r="D17" t="n">
         <v>86</v>
       </c>
       <c r="E17" t="n">
-        <v>49.09</v>
+        <v>-0.63</v>
       </c>
       <c r="F17" t="n">
-        <v>62.59</v>
+        <v>15.94</v>
       </c>
       <c r="G17" t="n">
-        <v>74.12</v>
+        <v>26.34</v>
       </c>
       <c r="H17" t="n">
-        <v>51.14</v>
+        <v>4.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.92</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
-        <v>8.81</v>
+        <v>10.53</v>
       </c>
       <c r="K17" t="n">
-        <v>7.5</v>
+        <v>2.73</v>
       </c>
       <c r="L17" t="n">
-        <v>114.34</v>
+        <v>382.28</v>
       </c>
       <c r="M17" t="n">
-        <v>118.75</v>
+        <v>387.55</v>
       </c>
       <c r="N17" t="n">
-        <v>105.54</v>
+        <v>371.75</v>
       </c>
       <c r="O17" t="n">
-        <v>136.8</v>
+        <v>409.14</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>66.84999999999999</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>35.48</v>
+        <v>6.17</v>
       </c>
       <c r="S17" t="n">
-        <v>-5.26</v>
+        <v>-3.99</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2169,71 +2161,71 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RSI algo alto; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>RSI sobrecomprado; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>384.89</v>
+        <v>736.67</v>
       </c>
       <c r="D18" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.91</v>
+        <v>1.78</v>
       </c>
       <c r="F18" t="n">
-        <v>15.61</v>
+        <v>6.08</v>
       </c>
       <c r="G18" t="n">
-        <v>25.98</v>
+        <v>8.35</v>
       </c>
       <c r="H18" t="n">
-        <v>4.16</v>
+        <v>-5.85</v>
       </c>
       <c r="I18" t="n">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
       <c r="J18" t="n">
-        <v>10.53</v>
+        <v>6.74</v>
       </c>
       <c r="K18" t="n">
-        <v>2.74</v>
+        <v>0.92</v>
       </c>
       <c r="L18" t="n">
-        <v>381.2</v>
+        <v>734.3099999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>386.47</v>
+        <v>737.6799999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>370.67</v>
+        <v>727.5700000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>408.06</v>
+        <v>751.5</v>
       </c>
       <c r="P18" t="n">
         <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>77.01000000000001</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>5.89</v>
+        <v>2.62</v>
       </c>
       <c r="S18" t="n">
-        <v>-4.26</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2268,71 +2260,71 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo</t>
+          <t>RSI sobrecomprado; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>116.66</v>
+        <v>431.81</v>
       </c>
       <c r="D19" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E19" t="n">
-        <v>7.87</v>
+        <v>10.9</v>
       </c>
       <c r="F19" t="n">
-        <v>82.81999999999999</v>
+        <v>18.56</v>
       </c>
       <c r="G19" t="n">
-        <v>149.33</v>
+        <v>3.44</v>
       </c>
       <c r="H19" t="n">
-        <v>71.37</v>
+        <v>6.63</v>
       </c>
       <c r="I19" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="J19" t="n">
-        <v>9.15</v>
+        <v>16.76</v>
       </c>
       <c r="K19" t="n">
-        <v>7.84</v>
+        <v>3.88</v>
       </c>
       <c r="L19" t="n">
-        <v>113.46</v>
+        <v>425.94</v>
       </c>
       <c r="M19" t="n">
-        <v>118.03</v>
+        <v>434.32</v>
       </c>
       <c r="N19" t="n">
-        <v>104.31</v>
+        <v>409.18</v>
       </c>
       <c r="O19" t="n">
-        <v>136.79</v>
+        <v>468.68</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>77.66</v>
+        <v>69.05</v>
       </c>
       <c r="R19" t="n">
-        <v>29.3</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>-12.12</v>
+        <v>-3.86</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2362,76 +2354,76 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Fuerte vs QQQ</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Momentum 5D extendido; Muy alejada de MA20; Volatilidad alta</t>
+          <t>Tendencia larga débil; RSI algo alto; Subida muy extendida 5D; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32.13</v>
+        <v>54.84</v>
       </c>
       <c r="D20" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E20" t="n">
-        <v>15.45</v>
+        <v>14.25</v>
       </c>
       <c r="F20" t="n">
-        <v>18.13</v>
+        <v>53.36</v>
       </c>
       <c r="G20" t="n">
-        <v>5.21</v>
+        <v>60.77</v>
       </c>
       <c r="H20" t="n">
-        <v>6.68</v>
+        <v>41.43</v>
       </c>
       <c r="I20" t="n">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="J20" t="n">
-        <v>2.43</v>
+        <v>4.6</v>
       </c>
       <c r="K20" t="n">
-        <v>7.56</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>31.28</v>
+        <v>53.23</v>
       </c>
       <c r="M20" t="n">
-        <v>32.49</v>
+        <v>55.53</v>
       </c>
       <c r="N20" t="n">
-        <v>28.85</v>
+        <v>48.63</v>
       </c>
       <c r="O20" t="n">
-        <v>37.47</v>
+        <v>64.95</v>
       </c>
       <c r="P20" t="n">
         <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>56.5</v>
+        <v>60.67</v>
       </c>
       <c r="R20" t="n">
-        <v>9.390000000000001</v>
+        <v>16.98</v>
       </c>
       <c r="S20" t="n">
-        <v>-11.66</v>
+        <v>-7.29</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2466,71 +2458,71 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Volumen bajo; Subida muy extendida 5D; Algo extendida sobre MA20; Volatilidad alta</t>
+          <t>Tendencia larga débil; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53.75</v>
+        <v>118.34</v>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E21" t="n">
-        <v>11.98</v>
+        <v>9.42</v>
       </c>
       <c r="F21" t="n">
-        <v>50.31</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>57.58</v>
+        <v>152.92</v>
       </c>
       <c r="H21" t="n">
-        <v>38.86</v>
+        <v>73.53</v>
       </c>
       <c r="I21" t="n">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="J21" t="n">
-        <v>4.6</v>
+        <v>9.15</v>
       </c>
       <c r="K21" t="n">
-        <v>8.550000000000001</v>
+        <v>7.73</v>
       </c>
       <c r="L21" t="n">
-        <v>52.14</v>
+        <v>115.14</v>
       </c>
       <c r="M21" t="n">
-        <v>54.44</v>
+        <v>119.71</v>
       </c>
       <c r="N21" t="n">
-        <v>47.54</v>
+        <v>105.99</v>
       </c>
       <c r="O21" t="n">
-        <v>63.86</v>
+        <v>138.47</v>
       </c>
       <c r="P21" t="n">
         <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>58.84</v>
+        <v>79.09</v>
       </c>
       <c r="R21" t="n">
-        <v>14.79</v>
+        <v>31.04</v>
       </c>
       <c r="S21" t="n">
-        <v>-9.130000000000001</v>
+        <v>-10.85</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2560,76 +2552,76 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>RSI sobrecomprado; Momentum 5D extendido; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>204.84</v>
+        <v>32.47</v>
       </c>
       <c r="D22" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E22" t="n">
-        <v>9.800000000000001</v>
+        <v>16.67</v>
       </c>
       <c r="F22" t="n">
-        <v>54.2</v>
+        <v>19.38</v>
       </c>
       <c r="G22" t="n">
-        <v>46.52</v>
+        <v>6.32</v>
       </c>
       <c r="H22" t="n">
-        <v>42.75</v>
+        <v>7.45</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="J22" t="n">
-        <v>18.85</v>
+        <v>2.43</v>
       </c>
       <c r="K22" t="n">
-        <v>9.199999999999999</v>
+        <v>7.48</v>
       </c>
       <c r="L22" t="n">
-        <v>198.24</v>
+        <v>31.62</v>
       </c>
       <c r="M22" t="n">
-        <v>207.67</v>
+        <v>32.83</v>
       </c>
       <c r="N22" t="n">
-        <v>179.39</v>
+        <v>29.19</v>
       </c>
       <c r="O22" t="n">
-        <v>246.31</v>
+        <v>37.81</v>
       </c>
       <c r="P22" t="n">
         <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>71.31999999999999</v>
+        <v>57.36</v>
       </c>
       <c r="R22" t="n">
-        <v>23.4</v>
+        <v>10.48</v>
       </c>
       <c r="S22" t="n">
-        <v>-17.37</v>
+        <v>-10.72</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2659,12 +2651,12 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Fuerte vs QQQ</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI algo alto; Momentum 5D extendido; Muy alejada de MA20; Volatilidad muy alta</t>
+          <t>Tendencia larga débil; Volumen bajo; Subida muy extendida 5D; Algo extendida sobre MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -2680,55 +2672,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>732.46</v>
+        <v>749.47</v>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E23" t="n">
-        <v>14.41</v>
+        <v>17.07</v>
       </c>
       <c r="F23" t="n">
-        <v>57.3</v>
+        <v>60.95</v>
       </c>
       <c r="G23" t="n">
-        <v>78</v>
+        <v>82.14</v>
       </c>
       <c r="H23" t="n">
-        <v>45.85</v>
+        <v>49.02</v>
       </c>
       <c r="I23" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>49.16</v>
       </c>
       <c r="K23" t="n">
-        <v>6.71</v>
+        <v>6.56</v>
       </c>
       <c r="L23" t="n">
-        <v>715.26</v>
+        <v>732.26</v>
       </c>
       <c r="M23" t="n">
-        <v>739.83</v>
+        <v>756.84</v>
       </c>
       <c r="N23" t="n">
-        <v>666.1</v>
+        <v>683.1</v>
       </c>
       <c r="O23" t="n">
-        <v>840.61</v>
+        <v>857.61</v>
       </c>
       <c r="P23" t="n">
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>76.31999999999999</v>
+        <v>79.22</v>
       </c>
       <c r="R23" t="n">
-        <v>31.46</v>
+        <v>34.31</v>
       </c>
       <c r="S23" t="n">
-        <v>-10.53</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2779,55 +2771,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>436.53</v>
+        <v>440.17</v>
       </c>
       <c r="D24" t="n">
         <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>22.88</v>
+        <v>23.9</v>
       </c>
       <c r="F24" t="n">
-        <v>71.14</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>110.56</v>
+        <v>112.31</v>
       </c>
       <c r="H24" t="n">
-        <v>59.69</v>
+        <v>60.64</v>
       </c>
       <c r="I24" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="J24" t="n">
         <v>28.31</v>
       </c>
       <c r="K24" t="n">
-        <v>6.49</v>
+        <v>6.43</v>
       </c>
       <c r="L24" t="n">
-        <v>426.62</v>
+        <v>430.26</v>
       </c>
       <c r="M24" t="n">
-        <v>440.78</v>
+        <v>444.42</v>
       </c>
       <c r="N24" t="n">
-        <v>398.31</v>
+        <v>401.95</v>
       </c>
       <c r="O24" t="n">
-        <v>498.82</v>
+        <v>502.46</v>
       </c>
       <c r="P24" t="n">
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>72.89</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="R24" t="n">
-        <v>26.2</v>
+        <v>27.19</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.97</v>
+        <v>-6.19</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2869,64 +2861,64 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1766.88</v>
+        <v>56.37</v>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E25" t="n">
-        <v>1.96</v>
+        <v>-5.01</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.62</v>
+        <v>1.78</v>
       </c>
       <c r="G25" t="n">
-        <v>20.83</v>
+        <v>22.93</v>
       </c>
       <c r="H25" t="n">
-        <v>-13.07</v>
+        <v>-10.15</v>
       </c>
       <c r="I25" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="J25" t="n">
-        <v>87.83</v>
+        <v>1.88</v>
       </c>
       <c r="K25" t="n">
-        <v>4.97</v>
+        <v>3.33</v>
       </c>
       <c r="L25" t="n">
-        <v>1736.14</v>
+        <v>55.71</v>
       </c>
       <c r="M25" t="n">
-        <v>1780.06</v>
+        <v>56.65</v>
       </c>
       <c r="N25" t="n">
-        <v>1648.3</v>
+        <v>53.83</v>
       </c>
       <c r="O25" t="n">
-        <v>1960.12</v>
+        <v>60.49</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>46.88</v>
+        <v>48.23</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.67</v>
+        <v>-0.98</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.890000000000001</v>
+        <v>-7.28</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2956,76 +2948,76 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; Tendencia larga positiva; Momentum 5D sano</t>
+          <t>Mercado ALCISTA; Tendencia larga positiva; RSI saludable; Histograma MACD mejora</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>412.11</v>
+        <v>1778.52</v>
       </c>
       <c r="D26" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.57</v>
+        <v>2.63</v>
       </c>
       <c r="F26" t="n">
-        <v>8.23</v>
+        <v>-0.97</v>
       </c>
       <c r="G26" t="n">
-        <v>27</v>
+        <v>21.63</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.22</v>
+        <v>-12.9</v>
       </c>
       <c r="I26" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="J26" t="n">
-        <v>15.39</v>
+        <v>87.83</v>
       </c>
       <c r="K26" t="n">
-        <v>3.73</v>
+        <v>4.94</v>
       </c>
       <c r="L26" t="n">
-        <v>406.73</v>
+        <v>1747.77</v>
       </c>
       <c r="M26" t="n">
-        <v>414.42</v>
+        <v>1791.69</v>
       </c>
       <c r="N26" t="n">
-        <v>391.34</v>
+        <v>1659.94</v>
       </c>
       <c r="O26" t="n">
-        <v>445.98</v>
+        <v>1971.75</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>45.45</v>
+        <v>47.64</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.5</v>
+        <v>-1.05</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.84</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3055,12 +3047,12 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; Tendencia larga positiva; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -3076,55 +3068,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.890000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="D27" t="n">
         <v>47</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.58</v>
+        <v>-6.22</v>
       </c>
       <c r="F27" t="n">
-        <v>5.77</v>
+        <v>5.06</v>
       </c>
       <c r="G27" t="n">
-        <v>-17.58</v>
+        <v>-18.14</v>
       </c>
       <c r="H27" t="n">
-        <v>-5.68</v>
+        <v>-6.87</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="K27" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="L27" t="n">
-        <v>8.720000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="M27" t="n">
-        <v>8.949999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>8.26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>9.9</v>
+        <v>9.85</v>
       </c>
       <c r="P27" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q27" t="n">
-        <v>42.75</v>
+        <v>42.03</v>
       </c>
       <c r="R27" t="n">
-        <v>-3.36</v>
+        <v>-3.98</v>
       </c>
       <c r="S27" t="n">
-        <v>-10.61</v>
+        <v>-11.22</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3175,55 +3167,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>186.6</v>
+        <v>186.44</v>
       </c>
       <c r="D28" t="n">
         <v>46</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.14</v>
+        <v>-3.22</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.22</v>
+        <v>-0.31</v>
       </c>
       <c r="G28" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="H28" t="n">
-        <v>-11.67</v>
+        <v>-12.24</v>
       </c>
       <c r="I28" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="J28" t="n">
         <v>4.52</v>
       </c>
       <c r="K28" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="L28" t="n">
-        <v>185.02</v>
+        <v>184.86</v>
       </c>
       <c r="M28" t="n">
-        <v>187.28</v>
+        <v>187.12</v>
       </c>
       <c r="N28" t="n">
-        <v>180.49</v>
+        <v>180.33</v>
       </c>
       <c r="O28" t="n">
-        <v>196.55</v>
+        <v>196.39</v>
       </c>
       <c r="P28" t="n">
         <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>50.42</v>
+        <v>50.18</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.22</v>
+        <v>-0.3</v>
       </c>
       <c r="S28" t="n">
-        <v>-3.88</v>
+        <v>-3.96</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3265,68 +3257,68 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>56.18</v>
+        <v>45.51</v>
       </c>
       <c r="D29" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.33</v>
+        <v>-2.1</v>
       </c>
       <c r="F29" t="n">
-        <v>1.44</v>
+        <v>-5.12</v>
       </c>
       <c r="G29" t="n">
-        <v>22.52</v>
+        <v>13.31</v>
       </c>
       <c r="H29" t="n">
-        <v>-10.01</v>
+        <v>-17.05</v>
       </c>
       <c r="I29" t="n">
-        <v>0.44</v>
+        <v>1.17</v>
       </c>
       <c r="J29" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="K29" t="n">
-        <v>3.32</v>
+        <v>3.53</v>
       </c>
       <c r="L29" t="n">
-        <v>55.53</v>
+        <v>44.95</v>
       </c>
       <c r="M29" t="n">
-        <v>56.46</v>
+        <v>45.76</v>
       </c>
       <c r="N29" t="n">
-        <v>53.66</v>
+        <v>43.34</v>
       </c>
       <c r="O29" t="n">
-        <v>60.29</v>
+        <v>49.05</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>47.73</v>
+        <v>24.66</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.29</v>
+        <v>-7.13</v>
       </c>
       <c r="S29" t="n">
-        <v>-7.58</v>
+        <v>-12.97</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3352,76 +3344,76 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Tendencia larga positiva; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>45.68</v>
+        <v>15.77</v>
       </c>
       <c r="D30" t="n">
         <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.74</v>
+        <v>-1.53</v>
       </c>
       <c r="F30" t="n">
-        <v>-4.77</v>
+        <v>-11.92</v>
       </c>
       <c r="G30" t="n">
-        <v>13.72</v>
+        <v>-19.56</v>
       </c>
       <c r="H30" t="n">
-        <v>-16.22</v>
+        <v>-23.85</v>
       </c>
       <c r="I30" t="n">
-        <v>1.06</v>
+        <v>0.76</v>
       </c>
       <c r="J30" t="n">
-        <v>1.61</v>
+        <v>0.83</v>
       </c>
       <c r="K30" t="n">
-        <v>3.52</v>
+        <v>5.25</v>
       </c>
       <c r="L30" t="n">
-        <v>45.12</v>
+        <v>15.49</v>
       </c>
       <c r="M30" t="n">
-        <v>45.92</v>
+        <v>15.9</v>
       </c>
       <c r="N30" t="n">
-        <v>43.51</v>
+        <v>14.66</v>
       </c>
       <c r="O30" t="n">
-        <v>49.22</v>
+        <v>17.6</v>
       </c>
       <c r="P30" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>25.74</v>
+        <v>28.26</v>
       </c>
       <c r="R30" t="n">
-        <v>-6.81</v>
+        <v>-9.57</v>
       </c>
       <c r="S30" t="n">
-        <v>-12.66</v>
+        <v>-21.63</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3472,55 +3464,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>409.3</v>
+        <v>408.28</v>
       </c>
       <c r="D31" t="n">
         <v>27</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.51</v>
+        <v>-0.75</v>
       </c>
       <c r="F31" t="n">
-        <v>4.12</v>
+        <v>3.86</v>
       </c>
       <c r="G31" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="H31" t="n">
-        <v>-7.33</v>
+        <v>-8.07</v>
       </c>
       <c r="I31" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="J31" t="n">
         <v>11.72</v>
       </c>
       <c r="K31" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="L31" t="n">
-        <v>405.2</v>
+        <v>404.18</v>
       </c>
       <c r="M31" t="n">
-        <v>411.06</v>
+        <v>410.04</v>
       </c>
       <c r="N31" t="n">
-        <v>393.48</v>
+        <v>392.46</v>
       </c>
       <c r="O31" t="n">
-        <v>435.08</v>
+        <v>434.06</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>35.72</v>
+        <v>35.29</v>
       </c>
       <c r="R31" t="n">
-        <v>-2.17</v>
+        <v>-2.4</v>
       </c>
       <c r="S31" t="n">
-        <v>-5.63</v>
+        <v>-5.86</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3586,10 +3578,10 @@
         <v>2.3</v>
       </c>
       <c r="H32" t="n">
-        <v>-13.18</v>
+        <v>-13.66</v>
       </c>
       <c r="I32" t="n">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="J32" t="n">
         <v>4.26</v>
@@ -3670,25 +3662,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>599.88</v>
+        <v>601.15</v>
       </c>
       <c r="D33" t="n">
         <v>24</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.84</v>
+        <v>-0.63</v>
       </c>
       <c r="F33" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.26</v>
       </c>
       <c r="G33" t="n">
-        <v>-6.15</v>
+        <v>-5.96</v>
       </c>
       <c r="H33" t="n">
-        <v>-20.9</v>
+        <v>-21.19</v>
       </c>
       <c r="I33" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="J33" t="n">
         <v>18.43</v>
@@ -3697,28 +3689,28 @@
         <v>3.07</v>
       </c>
       <c r="L33" t="n">
-        <v>593.4299999999999</v>
+        <v>594.7</v>
       </c>
       <c r="M33" t="n">
-        <v>602.64</v>
+        <v>603.92</v>
       </c>
       <c r="N33" t="n">
-        <v>575</v>
+        <v>576.27</v>
       </c>
       <c r="O33" t="n">
-        <v>640.4299999999999</v>
+        <v>641.7</v>
       </c>
       <c r="P33" t="n">
         <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>23.8</v>
+        <v>24.47</v>
       </c>
       <c r="R33" t="n">
-        <v>-6.84</v>
+        <v>-6.65</v>
       </c>
       <c r="S33" t="n">
-        <v>-13.25</v>
+        <v>-13.07</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3760,64 +3752,64 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>15.72</v>
+        <v>133.95</v>
       </c>
       <c r="D34" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.9</v>
+        <v>-1.44</v>
       </c>
       <c r="F34" t="n">
-        <v>-12.26</v>
+        <v>-1.29</v>
       </c>
       <c r="G34" t="n">
-        <v>-19.86</v>
+        <v>1.93</v>
       </c>
       <c r="H34" t="n">
-        <v>-23.71</v>
+        <v>-13.22</v>
       </c>
       <c r="I34" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="J34" t="n">
-        <v>0.83</v>
+        <v>6.04</v>
       </c>
       <c r="K34" t="n">
-        <v>5.27</v>
+        <v>4.51</v>
       </c>
       <c r="L34" t="n">
-        <v>15.43</v>
+        <v>131.83</v>
       </c>
       <c r="M34" t="n">
-        <v>15.84</v>
+        <v>134.86</v>
       </c>
       <c r="N34" t="n">
-        <v>14.6</v>
+        <v>125.79</v>
       </c>
       <c r="O34" t="n">
-        <v>17.54</v>
+        <v>147.25</v>
       </c>
       <c r="P34" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>28.04</v>
+        <v>29.65</v>
       </c>
       <c r="R34" t="n">
-        <v>-9.9</v>
+        <v>-5.24</v>
       </c>
       <c r="S34" t="n">
-        <v>-21.93</v>
+        <v>-12.27</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3847,7 +3839,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3859,64 +3851,64 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>134.46</v>
+        <v>7.99</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.07</v>
+        <v>-12.53</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.92</v>
+        <v>14.71</v>
       </c>
       <c r="G35" t="n">
-        <v>2.32</v>
+        <v>7.17</v>
       </c>
       <c r="H35" t="n">
-        <v>-12.37</v>
+        <v>2.78</v>
       </c>
       <c r="I35" t="n">
-        <v>0.49</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>6.04</v>
+        <v>0.65</v>
       </c>
       <c r="K35" t="n">
-        <v>4.5</v>
+        <v>8.1</v>
       </c>
       <c r="L35" t="n">
-        <v>132.34</v>
+        <v>7.77</v>
       </c>
       <c r="M35" t="n">
-        <v>135.36</v>
+        <v>8.09</v>
       </c>
       <c r="N35" t="n">
-        <v>126.3</v>
+        <v>7.12</v>
       </c>
       <c r="O35" t="n">
-        <v>147.75</v>
+        <v>9.42</v>
       </c>
       <c r="P35" t="n">
         <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>29.98</v>
+        <v>48.01</v>
       </c>
       <c r="R35" t="n">
-        <v>-4.9</v>
+        <v>-5.06</v>
       </c>
       <c r="S35" t="n">
-        <v>-11.94</v>
+        <v>-20.41</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3930,7 +3922,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
@@ -3946,76 +3938,76 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; RSI saludable; Fuerte vs QQQ</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8.01</v>
+        <v>27.84</v>
       </c>
       <c r="D36" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>-12.36</v>
+        <v>-10.68</v>
       </c>
       <c r="F36" t="n">
-        <v>14.92</v>
+        <v>-5.72</v>
       </c>
       <c r="G36" t="n">
-        <v>7.37</v>
+        <v>-9.26</v>
       </c>
       <c r="H36" t="n">
-        <v>3.47</v>
+        <v>-17.65</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
-        <v>0.65</v>
+        <v>1.76</v>
       </c>
       <c r="K36" t="n">
-        <v>8.08</v>
+        <v>6.34</v>
       </c>
       <c r="L36" t="n">
-        <v>7.78</v>
+        <v>27.22</v>
       </c>
       <c r="M36" t="n">
-        <v>8.109999999999999</v>
+        <v>28.1</v>
       </c>
       <c r="N36" t="n">
-        <v>7.14</v>
+        <v>25.46</v>
       </c>
       <c r="O36" t="n">
-        <v>9.43</v>
+        <v>31.72</v>
       </c>
       <c r="P36" t="n">
         <v>1.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>48.13</v>
+        <v>24.18</v>
       </c>
       <c r="R36" t="n">
-        <v>-4.89</v>
+        <v>-12.64</v>
       </c>
       <c r="S36" t="n">
-        <v>-20.26</v>
+        <v>-22.23</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4045,80 +4037,80 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; RSI saludable; Fuerte vs QQQ</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>27.92</v>
+        <v>208.69</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="E37" t="n">
-        <v>-10.43</v>
+        <v>11.87</v>
       </c>
       <c r="F37" t="n">
-        <v>-5.45</v>
+        <v>57.1</v>
       </c>
       <c r="G37" t="n">
-        <v>-9</v>
+        <v>49.27</v>
       </c>
       <c r="H37" t="n">
-        <v>-16.9</v>
+        <v>45.17</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>1.19</v>
       </c>
       <c r="J37" t="n">
-        <v>1.76</v>
+        <v>18.85</v>
       </c>
       <c r="K37" t="n">
-        <v>6.32</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>27.3</v>
+        <v>202.09</v>
       </c>
       <c r="M37" t="n">
-        <v>28.18</v>
+        <v>211.52</v>
       </c>
       <c r="N37" t="n">
-        <v>25.54</v>
+        <v>183.24</v>
       </c>
       <c r="O37" t="n">
-        <v>31.8</v>
+        <v>250.16</v>
       </c>
       <c r="P37" t="n">
         <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>24.32</v>
+        <v>73.06</v>
       </c>
       <c r="R37" t="n">
-        <v>-12.4</v>
+        <v>25.57</v>
       </c>
       <c r="S37" t="n">
-        <v>-22.01</v>
+        <v>-15.82</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>BAJA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4128,7 +4120,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
@@ -4144,12 +4136,12 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Fuerte vs QQQ</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Tendencia larga débil; RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad muy alta</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -556,64 +556,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>427.29</v>
+        <v>207.64</v>
       </c>
       <c r="D2" t="n">
         <v>96</v>
       </c>
       <c r="E2" t="n">
-        <v>4.01</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>12.6</v>
       </c>
       <c r="G2" t="n">
-        <v>20.54</v>
+        <v>26.36</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.93</v>
+        <v>0.09</v>
       </c>
       <c r="I2" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="J2" t="n">
-        <v>18.91</v>
+        <v>12.37</v>
       </c>
       <c r="K2" t="n">
-        <v>4.43</v>
+        <v>5.96</v>
       </c>
       <c r="L2" t="n">
-        <v>420.67</v>
+        <v>203.31</v>
       </c>
       <c r="M2" t="n">
-        <v>430.13</v>
+        <v>209.5</v>
       </c>
       <c r="N2" t="n">
-        <v>401.76</v>
+        <v>190.93</v>
       </c>
       <c r="O2" t="n">
-        <v>468.89</v>
+        <v>234.86</v>
       </c>
       <c r="P2" t="n">
         <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>56.8</v>
+        <v>50.76</v>
       </c>
       <c r="R2" t="n">
-        <v>5.62</v>
+        <v>4.28</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.72</v>
+        <v>-4.95</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -647,19 +647,19 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Débil vs QQQ</t>
+          <t>Tendencia larga débil</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -668,55 +668,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>286.55</v>
+        <v>431.2</v>
       </c>
       <c r="D3" t="n">
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9</v>
+        <v>4.96</v>
       </c>
       <c r="F3" t="n">
-        <v>5.19</v>
+        <v>8.99</v>
       </c>
       <c r="G3" t="n">
-        <v>21.81</v>
+        <v>21.65</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.74</v>
+        <v>-3.52</v>
       </c>
       <c r="I3" t="n">
-        <v>0.53</v>
+        <v>1.38</v>
       </c>
       <c r="J3" t="n">
-        <v>14.39</v>
+        <v>18.91</v>
       </c>
       <c r="K3" t="n">
-        <v>5.02</v>
+        <v>4.38</v>
       </c>
       <c r="L3" t="n">
-        <v>281.51</v>
+        <v>424.58</v>
       </c>
       <c r="M3" t="n">
-        <v>288.71</v>
+        <v>434.04</v>
       </c>
       <c r="N3" t="n">
-        <v>267.12</v>
+        <v>405.67</v>
       </c>
       <c r="O3" t="n">
-        <v>318.22</v>
+        <v>472.8</v>
       </c>
       <c r="P3" t="n">
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>59.08</v>
+        <v>58.1</v>
       </c>
       <c r="R3" t="n">
-        <v>6.61</v>
+        <v>6.53</v>
       </c>
       <c r="S3" t="n">
-        <v>-4.48</v>
+        <v>-3.85</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Volumen bajo; Débil vs QQQ</t>
+          <t>Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -771,55 +771,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1506.82</v>
+        <v>1520.94</v>
       </c>
       <c r="D4" t="n">
         <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>4.43</v>
+        <v>5.41</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.54</v>
+        <v>0.39</v>
       </c>
       <c r="G4" t="n">
-        <v>7.36</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-12.47</v>
+        <v>-12.12</v>
       </c>
       <c r="I4" t="n">
-        <v>0.78</v>
+        <v>0.97</v>
       </c>
       <c r="J4" t="n">
         <v>60.71</v>
       </c>
       <c r="K4" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="L4" t="n">
-        <v>1485.58</v>
+        <v>1499.69</v>
       </c>
       <c r="M4" t="n">
-        <v>1515.93</v>
+        <v>1530.05</v>
       </c>
       <c r="N4" t="n">
-        <v>1424.87</v>
+        <v>1438.98</v>
       </c>
       <c r="O4" t="n">
-        <v>1640.38</v>
+        <v>1654.5</v>
       </c>
       <c r="P4" t="n">
         <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>55.62</v>
+        <v>56.98</v>
       </c>
       <c r="R4" t="n">
-        <v>3.16</v>
+        <v>4.07</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.55</v>
+        <v>-4.66</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -865,64 +865,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>56.21</v>
+        <v>1811.35</v>
       </c>
       <c r="D5" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E5" t="n">
-        <v>0.37</v>
+        <v>4.53</v>
       </c>
       <c r="F5" t="n">
-        <v>9.17</v>
+        <v>0.86</v>
       </c>
       <c r="G5" t="n">
-        <v>11.55</v>
+        <v>23.88</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.76</v>
+        <v>-11.65</v>
       </c>
       <c r="I5" t="n">
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="J5" t="n">
-        <v>1.65</v>
+        <v>87.83</v>
       </c>
       <c r="K5" t="n">
-        <v>2.94</v>
+        <v>4.85</v>
       </c>
       <c r="L5" t="n">
-        <v>55.63</v>
+        <v>1780.61</v>
       </c>
       <c r="M5" t="n">
-        <v>56.46</v>
+        <v>1824.53</v>
       </c>
       <c r="N5" t="n">
-        <v>53.98</v>
+        <v>1692.77</v>
       </c>
       <c r="O5" t="n">
-        <v>59.85</v>
+        <v>2004.59</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>57.57</v>
+        <v>49.95</v>
       </c>
       <c r="R5" t="n">
-        <v>2.99</v>
+        <v>0.68</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.73</v>
+        <v>-6.6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -939,7 +939,11 @@
           <t>BAJO</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -957,71 +961,71 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo</t>
+          <t>MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>395.64</v>
+        <v>419.3</v>
       </c>
       <c r="D6" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E6" t="n">
-        <v>0.31</v>
+        <v>-1.89</v>
       </c>
       <c r="F6" t="n">
-        <v>4.14</v>
+        <v>10.12</v>
       </c>
       <c r="G6" t="n">
-        <v>8.300000000000001</v>
+        <v>29.22</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.79</v>
+        <v>-2.39</v>
       </c>
       <c r="I6" t="n">
-        <v>1.03</v>
+        <v>0.89</v>
       </c>
       <c r="J6" t="n">
-        <v>15.57</v>
+        <v>15.39</v>
       </c>
       <c r="K6" t="n">
-        <v>3.94</v>
+        <v>3.67</v>
       </c>
       <c r="L6" t="n">
-        <v>390.18</v>
+        <v>413.91</v>
       </c>
       <c r="M6" t="n">
-        <v>397.97</v>
+        <v>421.61</v>
       </c>
       <c r="N6" t="n">
-        <v>374.61</v>
+        <v>398.52</v>
       </c>
       <c r="O6" t="n">
-        <v>429.89</v>
+        <v>453.16</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>53.9</v>
+        <v>48.46</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9</v>
+        <v>1.15</v>
       </c>
       <c r="S6" t="n">
-        <v>-5.8</v>
+        <v>-4.2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1056,14 +1060,14 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Débil vs QQQ</t>
+          <t>MACD sin confirmar</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1072,55 +1076,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>151.36</v>
+        <v>55.64</v>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.27</v>
+        <v>-0.64</v>
       </c>
       <c r="F7" t="n">
-        <v>1.42</v>
+        <v>8.06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.96</v>
+        <v>10.42</v>
       </c>
       <c r="H7" t="n">
-        <v>-10.51</v>
+        <v>-4.45</v>
       </c>
       <c r="I7" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
       <c r="J7" t="n">
-        <v>4.02</v>
+        <v>1.65</v>
       </c>
       <c r="K7" t="n">
-        <v>2.66</v>
+        <v>2.97</v>
       </c>
       <c r="L7" t="n">
-        <v>149.95</v>
+        <v>55.06</v>
       </c>
       <c r="M7" t="n">
-        <v>151.96</v>
+        <v>55.89</v>
       </c>
       <c r="N7" t="n">
-        <v>145.93</v>
+        <v>53.41</v>
       </c>
       <c r="O7" t="n">
-        <v>160.21</v>
+        <v>59.28</v>
       </c>
       <c r="P7" t="n">
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>53</v>
+        <v>55.51</v>
       </c>
       <c r="R7" t="n">
-        <v>0.83</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.78</v>
+        <v>-2.73</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1150,7 +1154,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; Tendencia larga positiva; RSI saludable; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1171,55 +1175,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>264.71</v>
+        <v>265.82</v>
       </c>
       <c r="D8" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.23</v>
+        <v>-2.83</v>
       </c>
       <c r="F8" t="n">
-        <v>6.3</v>
+        <v>6.75</v>
       </c>
       <c r="G8" t="n">
-        <v>33.16</v>
+        <v>33.72</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.63</v>
+        <v>-5.76</v>
       </c>
       <c r="I8" t="n">
-        <v>0.52</v>
+        <v>0.78</v>
       </c>
       <c r="J8" t="n">
         <v>7.26</v>
       </c>
       <c r="K8" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="L8" t="n">
-        <v>262.17</v>
+        <v>263.28</v>
       </c>
       <c r="M8" t="n">
-        <v>265.8</v>
+        <v>266.91</v>
       </c>
       <c r="N8" t="n">
-        <v>254.91</v>
+        <v>256.02</v>
       </c>
       <c r="O8" t="n">
-        <v>280.67</v>
+        <v>281.78</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>61.11</v>
+        <v>62.77</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.97</v>
+        <v>-4.57</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1254,71 +1258,71 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>415.2</v>
+        <v>397.28</v>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.85</v>
+        <v>0.73</v>
       </c>
       <c r="F9" t="n">
-        <v>9.039999999999999</v>
+        <v>4.58</v>
       </c>
       <c r="G9" t="n">
-        <v>27.95</v>
+        <v>8.75</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.89</v>
+        <v>-7.93</v>
       </c>
       <c r="I9" t="n">
-        <v>0.65</v>
+        <v>1.19</v>
       </c>
       <c r="J9" t="n">
-        <v>15.39</v>
+        <v>15.57</v>
       </c>
       <c r="K9" t="n">
-        <v>3.71</v>
+        <v>3.92</v>
       </c>
       <c r="L9" t="n">
-        <v>409.81</v>
+        <v>391.83</v>
       </c>
       <c r="M9" t="n">
-        <v>417.51</v>
+        <v>399.62</v>
       </c>
       <c r="N9" t="n">
-        <v>394.42</v>
+        <v>376.26</v>
       </c>
       <c r="O9" t="n">
-        <v>449.06</v>
+        <v>431.54</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>46.69</v>
+        <v>54.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0.21</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.14</v>
+        <v>-5.41</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1348,76 +1352,76 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo</t>
+          <t>MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>508.96</v>
+        <v>150.63</v>
       </c>
       <c r="D10" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="E10" t="n">
-        <v>5.43</v>
+        <v>-2.74</v>
       </c>
       <c r="F10" t="n">
-        <v>26.85</v>
+        <v>0.93</v>
       </c>
       <c r="G10" t="n">
-        <v>43.59</v>
+        <v>1.47</v>
       </c>
       <c r="H10" t="n">
-        <v>14.92</v>
+        <v>-11.58</v>
       </c>
       <c r="I10" t="n">
-        <v>1.71</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
-        <v>19.23</v>
+        <v>4.02</v>
       </c>
       <c r="K10" t="n">
-        <v>3.78</v>
+        <v>2.67</v>
       </c>
       <c r="L10" t="n">
-        <v>502.23</v>
+        <v>149.22</v>
       </c>
       <c r="M10" t="n">
-        <v>511.84</v>
+        <v>151.23</v>
       </c>
       <c r="N10" t="n">
-        <v>483</v>
+        <v>145.2</v>
       </c>
       <c r="O10" t="n">
-        <v>551.27</v>
+        <v>159.48</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>68.65000000000001</v>
+        <v>51.87</v>
       </c>
       <c r="R10" t="n">
-        <v>10.96</v>
+        <v>0.37</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.64</v>
+        <v>-3.25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1431,14 +1435,10 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1451,76 +1451,76 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; Tendencia larga positiva; RSI saludable; Histograma MACD mejora</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RSI algo alto; Algo extendida sobre MA20</t>
+          <t>MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>204.59</v>
+        <v>289.24</v>
       </c>
       <c r="D11" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E11" t="n">
-        <v>3.46</v>
+        <v>4.87</v>
       </c>
       <c r="F11" t="n">
-        <v>10.94</v>
+        <v>6.18</v>
       </c>
       <c r="G11" t="n">
-        <v>24.5</v>
+        <v>22.95</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.99</v>
+        <v>-6.33</v>
       </c>
       <c r="I11" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="J11" t="n">
-        <v>12.37</v>
+        <v>14.39</v>
       </c>
       <c r="K11" t="n">
-        <v>6.05</v>
+        <v>4.98</v>
       </c>
       <c r="L11" t="n">
-        <v>200.25</v>
+        <v>284.2</v>
       </c>
       <c r="M11" t="n">
-        <v>206.44</v>
+        <v>291.4</v>
       </c>
       <c r="N11" t="n">
-        <v>187.88</v>
+        <v>269.81</v>
       </c>
       <c r="O11" t="n">
-        <v>231.81</v>
+        <v>320.91</v>
       </c>
       <c r="P11" t="n">
         <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>49.13</v>
+        <v>60.49</v>
       </c>
       <c r="R11" t="n">
-        <v>2.83</v>
+        <v>7.55</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.35</v>
+        <v>-3.59</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Volumen bajo; Volatilidad alta</t>
+          <t>Débil vs QQQ; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
@@ -1575,55 +1575,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>205.09</v>
+        <v>207.92</v>
       </c>
       <c r="D12" t="n">
         <v>86</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8</v>
+        <v>-0.44</v>
       </c>
       <c r="F12" t="n">
-        <v>27.21</v>
+        <v>28.97</v>
       </c>
       <c r="G12" t="n">
-        <v>63.71</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>15.28</v>
+        <v>16.46</v>
       </c>
       <c r="I12" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="J12" t="n">
         <v>18.09</v>
       </c>
       <c r="K12" t="n">
-        <v>8.82</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>198.76</v>
+        <v>201.59</v>
       </c>
       <c r="M12" t="n">
-        <v>207.8</v>
+        <v>210.63</v>
       </c>
       <c r="N12" t="n">
-        <v>180.66</v>
+        <v>183.49</v>
       </c>
       <c r="O12" t="n">
-        <v>244.9</v>
+        <v>247.73</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>52.64</v>
+        <v>53.59</v>
       </c>
       <c r="R12" t="n">
-        <v>2.38</v>
+        <v>3.72</v>
       </c>
       <c r="S12" t="n">
-        <v>-14.37</v>
+        <v>-13.19</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1669,64 +1669,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>294.51</v>
+        <v>515.99</v>
       </c>
       <c r="D13" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E13" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="F13" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>45.58</v>
+      </c>
+      <c r="H13" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.73</v>
       </c>
-      <c r="F13" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="G13" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J13" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.12</v>
-      </c>
       <c r="L13" t="n">
-        <v>292.32</v>
+        <v>509.26</v>
       </c>
       <c r="M13" t="n">
-        <v>295.45</v>
+        <v>518.87</v>
       </c>
       <c r="N13" t="n">
-        <v>286.07</v>
+        <v>490.03</v>
       </c>
       <c r="O13" t="n">
-        <v>308.27</v>
+        <v>558.3</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>75.83</v>
+        <v>71.06</v>
       </c>
       <c r="R13" t="n">
-        <v>6.54</v>
+        <v>12.41</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.13</v>
+        <v>-3.33</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1765,71 +1765,71 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo</t>
+          <t>RSI algo alto; Momentum 5D extendido; Muy alejada de MA20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>220.46</v>
+        <v>294.8</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E14" t="n">
-        <v>12.19</v>
+        <v>3.83</v>
       </c>
       <c r="F14" t="n">
-        <v>12.19</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>20.6</v>
+        <v>15.36</v>
       </c>
       <c r="H14" t="n">
-        <v>0.26</v>
+        <v>1.49</v>
       </c>
       <c r="I14" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
-        <v>8.08</v>
+        <v>6.28</v>
       </c>
       <c r="K14" t="n">
-        <v>3.66</v>
+        <v>2.13</v>
       </c>
       <c r="L14" t="n">
-        <v>217.63</v>
+        <v>292.6</v>
       </c>
       <c r="M14" t="n">
-        <v>221.67</v>
+        <v>295.74</v>
       </c>
       <c r="N14" t="n">
-        <v>209.56</v>
+        <v>286.32</v>
       </c>
       <c r="O14" t="n">
-        <v>238.23</v>
+        <v>308.62</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>64.04000000000001</v>
+        <v>76</v>
       </c>
       <c r="R14" t="n">
-        <v>7.08</v>
+        <v>6.64</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.47</v>
+        <v>-0.16</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1846,7 +1846,11 @@
           <t>ALTO</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1859,76 +1863,76 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Subida muy extendida 5D; Algo extendida sobre MA20</t>
+          <t>RSI sobrecomprado</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>703.51</v>
+        <v>117.56</v>
       </c>
       <c r="D15" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E15" t="n">
-        <v>3.21</v>
+        <v>49.26</v>
       </c>
       <c r="F15" t="n">
-        <v>11.92</v>
+        <v>62.78</v>
       </c>
       <c r="G15" t="n">
-        <v>17.03</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.01</v>
+        <v>50.27</v>
       </c>
       <c r="I15" t="n">
-        <v>0.92</v>
+        <v>1.25</v>
       </c>
       <c r="J15" t="n">
-        <v>10.25</v>
+        <v>8.81</v>
       </c>
       <c r="K15" t="n">
-        <v>1.46</v>
+        <v>7.49</v>
       </c>
       <c r="L15" t="n">
-        <v>699.92</v>
+        <v>114.48</v>
       </c>
       <c r="M15" t="n">
-        <v>705.05</v>
+        <v>118.88</v>
       </c>
       <c r="N15" t="n">
-        <v>689.6799999999999</v>
+        <v>105.67</v>
       </c>
       <c r="O15" t="n">
-        <v>726.05</v>
+        <v>136.93</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>76.05</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>5.11</v>
+        <v>35.62</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.55</v>
+        <v>-5.15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1945,7 +1949,11 @@
           <t>ALTO</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1963,71 +1971,71 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado</t>
+          <t>RSI algo alto; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>119.12</v>
+        <v>707.24</v>
       </c>
       <c r="D16" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E16" t="n">
-        <v>51.24</v>
+        <v>3.76</v>
       </c>
       <c r="F16" t="n">
-        <v>64.94</v>
+        <v>12.51</v>
       </c>
       <c r="G16" t="n">
-        <v>76.63</v>
+        <v>17.65</v>
       </c>
       <c r="H16" t="n">
-        <v>53.01</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="J16" t="n">
-        <v>8.81</v>
+        <v>10.25</v>
       </c>
       <c r="K16" t="n">
-        <v>7.39</v>
+        <v>1.45</v>
       </c>
       <c r="L16" t="n">
-        <v>116.04</v>
+        <v>703.65</v>
       </c>
       <c r="M16" t="n">
-        <v>120.44</v>
+        <v>708.78</v>
       </c>
       <c r="N16" t="n">
-        <v>107.23</v>
+        <v>693.41</v>
       </c>
       <c r="O16" t="n">
-        <v>138.49</v>
+        <v>729.78</v>
       </c>
       <c r="P16" t="n">
         <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>67.52</v>
+        <v>79.23</v>
       </c>
       <c r="R16" t="n">
-        <v>37.3</v>
+        <v>5.63</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.89</v>
+        <v>-1.03</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2044,7 +2052,11 @@
           <t>ALTO</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2062,71 +2074,71 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RSI algo alto; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>RSI sobrecomprado</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>385.97</v>
+        <v>220.78</v>
       </c>
       <c r="D17" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.63</v>
+        <v>12.36</v>
       </c>
       <c r="F17" t="n">
-        <v>15.94</v>
+        <v>12.35</v>
       </c>
       <c r="G17" t="n">
-        <v>26.34</v>
+        <v>20.78</v>
       </c>
       <c r="H17" t="n">
-        <v>4.01</v>
+        <v>-0.16</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>1.04</v>
       </c>
       <c r="J17" t="n">
-        <v>10.53</v>
+        <v>8.08</v>
       </c>
       <c r="K17" t="n">
-        <v>2.73</v>
+        <v>3.66</v>
       </c>
       <c r="L17" t="n">
-        <v>382.28</v>
+        <v>217.95</v>
       </c>
       <c r="M17" t="n">
-        <v>387.55</v>
+        <v>221.99</v>
       </c>
       <c r="N17" t="n">
-        <v>371.75</v>
+        <v>209.88</v>
       </c>
       <c r="O17" t="n">
-        <v>409.14</v>
+        <v>238.55</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>78.01000000000001</v>
+        <v>64.22</v>
       </c>
       <c r="R17" t="n">
-        <v>6.17</v>
+        <v>7.23</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.99</v>
+        <v>-1.33</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2156,76 +2168,76 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo</t>
+          <t>Subida muy extendida 5D; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>736.67</v>
+        <v>387.35</v>
       </c>
       <c r="D18" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E18" t="n">
-        <v>1.78</v>
+        <v>-0.28</v>
       </c>
       <c r="F18" t="n">
-        <v>6.08</v>
+        <v>16.35</v>
       </c>
       <c r="G18" t="n">
-        <v>8.35</v>
+        <v>26.79</v>
       </c>
       <c r="H18" t="n">
-        <v>-5.85</v>
+        <v>3.84</v>
       </c>
       <c r="I18" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="J18" t="n">
-        <v>6.74</v>
+        <v>10.53</v>
       </c>
       <c r="K18" t="n">
-        <v>0.92</v>
+        <v>2.72</v>
       </c>
       <c r="L18" t="n">
-        <v>734.3099999999999</v>
+        <v>383.66</v>
       </c>
       <c r="M18" t="n">
-        <v>737.6799999999999</v>
+        <v>388.93</v>
       </c>
       <c r="N18" t="n">
-        <v>727.5700000000001</v>
+        <v>373.13</v>
       </c>
       <c r="O18" t="n">
-        <v>751.5</v>
+        <v>410.52</v>
       </c>
       <c r="P18" t="n">
         <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>73.93000000000001</v>
+        <v>79.33</v>
       </c>
       <c r="R18" t="n">
-        <v>2.62</v>
+        <v>6.53</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-3.64</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2260,71 +2272,71 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Débil vs QQQ</t>
+          <t>RSI sobrecomprado</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>431.81</v>
+        <v>738.1799999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E19" t="n">
-        <v>10.9</v>
+        <v>1.99</v>
       </c>
       <c r="F19" t="n">
-        <v>18.56</v>
+        <v>6.3</v>
       </c>
       <c r="G19" t="n">
-        <v>3.44</v>
+        <v>8.57</v>
       </c>
       <c r="H19" t="n">
-        <v>6.63</v>
+        <v>-6.21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.78</v>
+        <v>1.06</v>
       </c>
       <c r="J19" t="n">
-        <v>16.76</v>
+        <v>6.74</v>
       </c>
       <c r="K19" t="n">
-        <v>3.88</v>
+        <v>0.91</v>
       </c>
       <c r="L19" t="n">
-        <v>425.94</v>
+        <v>735.8200000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>434.32</v>
+        <v>739.1900000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>409.18</v>
+        <v>729.08</v>
       </c>
       <c r="O19" t="n">
-        <v>468.68</v>
+        <v>753.01</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>69.05</v>
+        <v>76.09</v>
       </c>
       <c r="R19" t="n">
-        <v>9.380000000000001</v>
+        <v>2.82</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.86</v>
+        <v>-0.35</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2354,76 +2366,76 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Fuerte vs QQQ</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI algo alto; Subida muy extendida 5D; Algo extendida sobre MA20</t>
+          <t>RSI sobrecomprado; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>54.84</v>
+        <v>433.45</v>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E20" t="n">
-        <v>14.25</v>
+        <v>11.32</v>
       </c>
       <c r="F20" t="n">
-        <v>53.36</v>
+        <v>19.01</v>
       </c>
       <c r="G20" t="n">
-        <v>60.77</v>
+        <v>3.84</v>
       </c>
       <c r="H20" t="n">
-        <v>41.43</v>
+        <v>6.5</v>
       </c>
       <c r="I20" t="n">
         <v>0.92</v>
       </c>
       <c r="J20" t="n">
-        <v>4.6</v>
+        <v>16.76</v>
       </c>
       <c r="K20" t="n">
-        <v>8.380000000000001</v>
+        <v>3.87</v>
       </c>
       <c r="L20" t="n">
-        <v>53.23</v>
+        <v>427.58</v>
       </c>
       <c r="M20" t="n">
-        <v>55.53</v>
+        <v>435.96</v>
       </c>
       <c r="N20" t="n">
-        <v>48.63</v>
+        <v>410.82</v>
       </c>
       <c r="O20" t="n">
-        <v>64.95</v>
+        <v>470.32</v>
       </c>
       <c r="P20" t="n">
         <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>60.67</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>16.98</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-7.29</v>
+        <v>-3.5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2453,76 +2465,76 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Fuerte vs QQQ</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>Tendencia larga débil; RSI algo alto; Subida muy extendida 5D; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>118.34</v>
+        <v>55.87</v>
       </c>
       <c r="D21" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E21" t="n">
-        <v>9.42</v>
+        <v>16.4</v>
       </c>
       <c r="F21" t="n">
-        <v>85.45999999999999</v>
+        <v>56.24</v>
       </c>
       <c r="G21" t="n">
-        <v>152.92</v>
+        <v>63.79</v>
       </c>
       <c r="H21" t="n">
-        <v>73.53</v>
+        <v>43.73</v>
       </c>
       <c r="I21" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="J21" t="n">
-        <v>9.15</v>
+        <v>4.6</v>
       </c>
       <c r="K21" t="n">
-        <v>7.73</v>
+        <v>8.23</v>
       </c>
       <c r="L21" t="n">
-        <v>115.14</v>
+        <v>54.26</v>
       </c>
       <c r="M21" t="n">
-        <v>119.71</v>
+        <v>56.56</v>
       </c>
       <c r="N21" t="n">
-        <v>105.99</v>
+        <v>49.66</v>
       </c>
       <c r="O21" t="n">
-        <v>138.47</v>
+        <v>65.98</v>
       </c>
       <c r="P21" t="n">
         <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>79.09</v>
+        <v>62.5</v>
       </c>
       <c r="R21" t="n">
-        <v>31.04</v>
+        <v>19.04</v>
       </c>
       <c r="S21" t="n">
-        <v>-10.85</v>
+        <v>-5.55</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2552,12 +2564,12 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Momentum 5D extendido; Muy alejada de MA20; Volatilidad alta</t>
+          <t>Tendencia larga débil; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -2573,55 +2585,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>32.47</v>
+        <v>32.79</v>
       </c>
       <c r="D22" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E22" t="n">
-        <v>16.67</v>
+        <v>17.82</v>
       </c>
       <c r="F22" t="n">
-        <v>19.38</v>
+        <v>20.55</v>
       </c>
       <c r="G22" t="n">
-        <v>6.32</v>
+        <v>7.37</v>
       </c>
       <c r="H22" t="n">
-        <v>7.45</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.72</v>
+        <v>0.88</v>
       </c>
       <c r="J22" t="n">
         <v>2.43</v>
       </c>
       <c r="K22" t="n">
-        <v>7.48</v>
+        <v>7.41</v>
       </c>
       <c r="L22" t="n">
-        <v>31.62</v>
+        <v>31.94</v>
       </c>
       <c r="M22" t="n">
-        <v>32.83</v>
+        <v>33.15</v>
       </c>
       <c r="N22" t="n">
-        <v>29.19</v>
+        <v>29.51</v>
       </c>
       <c r="O22" t="n">
-        <v>37.81</v>
+        <v>38.13</v>
       </c>
       <c r="P22" t="n">
         <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>57.36</v>
+        <v>58.19</v>
       </c>
       <c r="R22" t="n">
-        <v>10.48</v>
+        <v>11.51</v>
       </c>
       <c r="S22" t="n">
-        <v>-10.72</v>
+        <v>-9.84</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2656,7 +2668,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Volumen bajo; Subida muy extendida 5D; Algo extendida sobre MA20; Volatilidad alta</t>
+          <t>Tendencia larga débil; Subida muy extendida 5D; Algo extendida sobre MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -2672,55 +2684,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>749.47</v>
+        <v>766.58</v>
       </c>
       <c r="D23" t="n">
         <v>70</v>
       </c>
       <c r="E23" t="n">
-        <v>17.07</v>
+        <v>19.74</v>
       </c>
       <c r="F23" t="n">
-        <v>60.95</v>
+        <v>64.62</v>
       </c>
       <c r="G23" t="n">
-        <v>82.14</v>
+        <v>86.3</v>
       </c>
       <c r="H23" t="n">
-        <v>49.02</v>
+        <v>52.11</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="J23" t="n">
         <v>49.16</v>
       </c>
       <c r="K23" t="n">
-        <v>6.56</v>
+        <v>6.41</v>
       </c>
       <c r="L23" t="n">
-        <v>732.26</v>
+        <v>749.38</v>
       </c>
       <c r="M23" t="n">
-        <v>756.84</v>
+        <v>773.95</v>
       </c>
       <c r="N23" t="n">
-        <v>683.1</v>
+        <v>700.22</v>
       </c>
       <c r="O23" t="n">
-        <v>857.61</v>
+        <v>874.73</v>
       </c>
       <c r="P23" t="n">
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>79.22</v>
+        <v>82.36</v>
       </c>
       <c r="R23" t="n">
-        <v>34.31</v>
+        <v>37.16</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.449999999999999</v>
+        <v>-6.36</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2762,64 +2774,64 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>440.17</v>
+        <v>120.61</v>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E24" t="n">
-        <v>23.9</v>
+        <v>11.52</v>
       </c>
       <c r="F24" t="n">
-        <v>72.56999999999999</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>112.31</v>
+        <v>157.77</v>
       </c>
       <c r="H24" t="n">
-        <v>60.64</v>
+        <v>76.5</v>
       </c>
       <c r="I24" t="n">
-        <v>0.67</v>
+        <v>1.11</v>
       </c>
       <c r="J24" t="n">
-        <v>28.31</v>
+        <v>9.15</v>
       </c>
       <c r="K24" t="n">
-        <v>6.43</v>
+        <v>7.59</v>
       </c>
       <c r="L24" t="n">
-        <v>430.26</v>
+        <v>117.41</v>
       </c>
       <c r="M24" t="n">
-        <v>444.42</v>
+        <v>121.98</v>
       </c>
       <c r="N24" t="n">
-        <v>401.95</v>
+        <v>108.26</v>
       </c>
       <c r="O24" t="n">
-        <v>502.46</v>
+        <v>140.74</v>
       </c>
       <c r="P24" t="n">
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>73.81999999999999</v>
+        <v>81.11</v>
       </c>
       <c r="R24" t="n">
-        <v>27.19</v>
+        <v>33.39</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.19</v>
+        <v>-9.15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2854,71 +2866,71 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>56.37</v>
+        <v>448.29</v>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.01</v>
+        <v>26.19</v>
       </c>
       <c r="F25" t="n">
-        <v>1.78</v>
+        <v>75.75</v>
       </c>
       <c r="G25" t="n">
-        <v>22.93</v>
+        <v>116.23</v>
       </c>
       <c r="H25" t="n">
-        <v>-10.15</v>
+        <v>63.24</v>
       </c>
       <c r="I25" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="J25" t="n">
-        <v>1.88</v>
+        <v>28.31</v>
       </c>
       <c r="K25" t="n">
-        <v>3.33</v>
+        <v>6.32</v>
       </c>
       <c r="L25" t="n">
-        <v>55.71</v>
+        <v>438.38</v>
       </c>
       <c r="M25" t="n">
-        <v>56.65</v>
+        <v>452.54</v>
       </c>
       <c r="N25" t="n">
-        <v>53.83</v>
+        <v>410.07</v>
       </c>
       <c r="O25" t="n">
-        <v>60.49</v>
+        <v>510.58</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>48.23</v>
+        <v>75.97</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.98</v>
+        <v>29.38</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.28</v>
+        <v>-4.46</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2932,92 +2944,92 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>SELL / EVITAR</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Tendencia larga positiva; RSI saludable; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
+          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1778.52</v>
+        <v>185.95</v>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E26" t="n">
-        <v>2.63</v>
+        <v>-3.47</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.97</v>
+        <v>-0.57</v>
       </c>
       <c r="G26" t="n">
-        <v>21.63</v>
+        <v>2.19</v>
       </c>
       <c r="H26" t="n">
-        <v>-12.9</v>
+        <v>-13.08</v>
       </c>
       <c r="I26" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>87.83</v>
+        <v>4.52</v>
       </c>
       <c r="K26" t="n">
-        <v>4.94</v>
+        <v>2.43</v>
       </c>
       <c r="L26" t="n">
-        <v>1747.77</v>
+        <v>184.37</v>
       </c>
       <c r="M26" t="n">
-        <v>1791.69</v>
+        <v>186.63</v>
       </c>
       <c r="N26" t="n">
-        <v>1659.94</v>
+        <v>179.84</v>
       </c>
       <c r="O26" t="n">
-        <v>1971.75</v>
+        <v>195.9</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>47.64</v>
+        <v>49.43</v>
       </c>
       <c r="R26" t="n">
-        <v>-1.05</v>
+        <v>-0.55</v>
       </c>
       <c r="S26" t="n">
-        <v>-8.289999999999999</v>
+        <v>-4.21</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3047,12 +3059,12 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; Tendencia larga positiva; Momentum 5D sano</t>
+          <t>Mercado ALCISTA; Tendencia larga positiva; RSI saludable; Histograma MACD mejora</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -3068,55 +3080,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.82</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="D27" t="n">
         <v>47</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.22</v>
+        <v>-6.59</v>
       </c>
       <c r="F27" t="n">
-        <v>5.06</v>
+        <v>4.64</v>
       </c>
       <c r="G27" t="n">
-        <v>-18.14</v>
+        <v>-18.46</v>
       </c>
       <c r="H27" t="n">
-        <v>-6.87</v>
+        <v>-7.87</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="J27" t="n">
         <v>0.47</v>
       </c>
       <c r="K27" t="n">
-        <v>5.27</v>
+        <v>5.34</v>
       </c>
       <c r="L27" t="n">
-        <v>8.66</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>8.890000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="O27" t="n">
-        <v>9.85</v>
+        <v>9.82</v>
       </c>
       <c r="P27" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>42.03</v>
+        <v>41.62</v>
       </c>
       <c r="R27" t="n">
-        <v>-3.98</v>
+        <v>-4.35</v>
       </c>
       <c r="S27" t="n">
-        <v>-11.22</v>
+        <v>-11.57</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3158,7 +3170,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3167,55 +3179,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>186.44</v>
+        <v>56.27</v>
       </c>
       <c r="D28" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.22</v>
+        <v>-5.17</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.31</v>
+        <v>1.61</v>
       </c>
       <c r="G28" t="n">
-        <v>2.46</v>
+        <v>22.72</v>
       </c>
       <c r="H28" t="n">
-        <v>-12.24</v>
+        <v>-10.9</v>
       </c>
       <c r="I28" t="n">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
-        <v>4.52</v>
+        <v>1.88</v>
       </c>
       <c r="K28" t="n">
-        <v>2.43</v>
+        <v>3.34</v>
       </c>
       <c r="L28" t="n">
-        <v>184.86</v>
+        <v>55.61</v>
       </c>
       <c r="M28" t="n">
-        <v>187.12</v>
+        <v>56.55</v>
       </c>
       <c r="N28" t="n">
-        <v>180.33</v>
+        <v>53.74</v>
       </c>
       <c r="O28" t="n">
-        <v>196.39</v>
+        <v>60.4</v>
       </c>
       <c r="P28" t="n">
         <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>50.18</v>
+        <v>47.97</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.3</v>
+        <v>-1.14</v>
       </c>
       <c r="S28" t="n">
-        <v>-3.96</v>
+        <v>-7.44</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3245,76 +3257,76 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Tendencia larga positiva; RSI saludable; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; Tendencia larga positiva; Histograma MACD mejora</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>45.51</v>
+        <v>78.27</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.1</v>
+        <v>1.61</v>
       </c>
       <c r="F29" t="n">
-        <v>-5.12</v>
+        <v>-1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>13.31</v>
+        <v>3.03</v>
       </c>
       <c r="H29" t="n">
-        <v>-17.05</v>
+        <v>-13.55</v>
       </c>
       <c r="I29" t="n">
-        <v>1.17</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
-        <v>1.61</v>
+        <v>4.26</v>
       </c>
       <c r="K29" t="n">
-        <v>3.53</v>
+        <v>5.45</v>
       </c>
       <c r="L29" t="n">
-        <v>44.95</v>
+        <v>76.78</v>
       </c>
       <c r="M29" t="n">
-        <v>45.76</v>
+        <v>78.91</v>
       </c>
       <c r="N29" t="n">
-        <v>43.34</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>49.05</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>24.66</v>
+        <v>36.34</v>
       </c>
       <c r="R29" t="n">
-        <v>-7.13</v>
+        <v>-3.85</v>
       </c>
       <c r="S29" t="n">
-        <v>-12.97</v>
+        <v>-16.13</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3344,76 +3356,76 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.77</v>
+        <v>407.77</v>
       </c>
       <c r="D30" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.53</v>
+        <v>-0.88</v>
       </c>
       <c r="F30" t="n">
-        <v>-11.92</v>
+        <v>3.73</v>
       </c>
       <c r="G30" t="n">
-        <v>-19.56</v>
+        <v>1.84</v>
       </c>
       <c r="H30" t="n">
-        <v>-23.85</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>0.76</v>
+        <v>1.04</v>
       </c>
       <c r="J30" t="n">
-        <v>0.83</v>
+        <v>11.72</v>
       </c>
       <c r="K30" t="n">
-        <v>5.25</v>
+        <v>2.87</v>
       </c>
       <c r="L30" t="n">
-        <v>15.49</v>
+        <v>403.67</v>
       </c>
       <c r="M30" t="n">
-        <v>15.9</v>
+        <v>409.53</v>
       </c>
       <c r="N30" t="n">
-        <v>14.66</v>
+        <v>391.95</v>
       </c>
       <c r="O30" t="n">
-        <v>17.6</v>
+        <v>433.55</v>
       </c>
       <c r="P30" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>28.26</v>
+        <v>35.07</v>
       </c>
       <c r="R30" t="n">
-        <v>-9.57</v>
+        <v>-2.52</v>
       </c>
       <c r="S30" t="n">
-        <v>-21.63</v>
+        <v>-5.98</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3443,7 +3455,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3455,64 +3467,64 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>408.28</v>
+        <v>45.44</v>
       </c>
       <c r="D31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.75</v>
+        <v>-2.26</v>
       </c>
       <c r="F31" t="n">
-        <v>3.86</v>
+        <v>-5.27</v>
       </c>
       <c r="G31" t="n">
-        <v>1.97</v>
+        <v>13.12</v>
       </c>
       <c r="H31" t="n">
-        <v>-8.07</v>
+        <v>-17.78</v>
       </c>
       <c r="I31" t="n">
-        <v>0.55</v>
+        <v>1.68</v>
       </c>
       <c r="J31" t="n">
-        <v>11.72</v>
+        <v>1.61</v>
       </c>
       <c r="K31" t="n">
-        <v>2.87</v>
+        <v>3.54</v>
       </c>
       <c r="L31" t="n">
-        <v>404.18</v>
+        <v>44.88</v>
       </c>
       <c r="M31" t="n">
-        <v>410.04</v>
+        <v>45.68</v>
       </c>
       <c r="N31" t="n">
-        <v>392.46</v>
+        <v>43.27</v>
       </c>
       <c r="O31" t="n">
-        <v>434.06</v>
+        <v>48.98</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>35.29</v>
+        <v>24.15</v>
       </c>
       <c r="R31" t="n">
-        <v>-2.4</v>
+        <v>-7.28</v>
       </c>
       <c r="S31" t="n">
-        <v>-5.86</v>
+        <v>-13.12</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3542,76 +3554,76 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>77.72</v>
+        <v>15.9</v>
       </c>
       <c r="D32" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9</v>
+        <v>-0.75</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.73</v>
+        <v>-11.22</v>
       </c>
       <c r="G32" t="n">
-        <v>2.3</v>
+        <v>-18.92</v>
       </c>
       <c r="H32" t="n">
-        <v>-13.66</v>
+        <v>-23.73</v>
       </c>
       <c r="I32" t="n">
-        <v>0.41</v>
+        <v>0.89</v>
       </c>
       <c r="J32" t="n">
-        <v>4.26</v>
+        <v>0.83</v>
       </c>
       <c r="K32" t="n">
-        <v>5.49</v>
+        <v>5.21</v>
       </c>
       <c r="L32" t="n">
-        <v>76.23</v>
+        <v>15.61</v>
       </c>
       <c r="M32" t="n">
-        <v>78.36</v>
+        <v>16.02</v>
       </c>
       <c r="N32" t="n">
-        <v>71.95999999999999</v>
+        <v>14.78</v>
       </c>
       <c r="O32" t="n">
-        <v>87.09999999999999</v>
+        <v>17.72</v>
       </c>
       <c r="P32" t="n">
         <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>35.81</v>
+        <v>28.73</v>
       </c>
       <c r="R32" t="n">
-        <v>-4.49</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="S32" t="n">
-        <v>-16.72</v>
+        <v>-21.01</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3646,7 +3658,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -3662,55 +3674,55 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>601.15</v>
+        <v>603</v>
       </c>
       <c r="D33" t="n">
         <v>24</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.63</v>
+        <v>-0.32</v>
       </c>
       <c r="F33" t="n">
-        <v>-9.26</v>
+        <v>-8.98</v>
       </c>
       <c r="G33" t="n">
-        <v>-5.96</v>
+        <v>-5.67</v>
       </c>
       <c r="H33" t="n">
-        <v>-21.19</v>
+        <v>-21.49</v>
       </c>
       <c r="I33" t="n">
-        <v>0.52</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>18.43</v>
       </c>
       <c r="K33" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="L33" t="n">
-        <v>594.7</v>
+        <v>596.55</v>
       </c>
       <c r="M33" t="n">
-        <v>603.92</v>
+        <v>605.76</v>
       </c>
       <c r="N33" t="n">
-        <v>576.27</v>
+        <v>578.12</v>
       </c>
       <c r="O33" t="n">
-        <v>641.7</v>
+        <v>643.55</v>
       </c>
       <c r="P33" t="n">
         <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>24.47</v>
+        <v>25.43</v>
       </c>
       <c r="R33" t="n">
-        <v>-6.65</v>
+        <v>-6.38</v>
       </c>
       <c r="S33" t="n">
-        <v>-13.07</v>
+        <v>-12.8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3761,55 +3773,55 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>133.95</v>
+        <v>136</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.44</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.29</v>
+        <v>0.22</v>
       </c>
       <c r="G34" t="n">
-        <v>1.93</v>
+        <v>3.49</v>
       </c>
       <c r="H34" t="n">
-        <v>-13.22</v>
+        <v>-12.29</v>
       </c>
       <c r="I34" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>6.04</v>
       </c>
       <c r="K34" t="n">
-        <v>4.51</v>
+        <v>4.44</v>
       </c>
       <c r="L34" t="n">
-        <v>131.83</v>
+        <v>133.88</v>
       </c>
       <c r="M34" t="n">
-        <v>134.86</v>
+        <v>136.91</v>
       </c>
       <c r="N34" t="n">
-        <v>125.79</v>
+        <v>127.84</v>
       </c>
       <c r="O34" t="n">
-        <v>147.25</v>
+        <v>149.3</v>
       </c>
       <c r="P34" t="n">
         <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>29.65</v>
+        <v>31.04</v>
       </c>
       <c r="R34" t="n">
-        <v>-5.24</v>
+        <v>-3.86</v>
       </c>
       <c r="S34" t="n">
-        <v>-12.27</v>
+        <v>-10.92</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3844,7 +3856,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -3860,55 +3872,55 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7.99</v>
+        <v>8.06</v>
       </c>
       <c r="D35" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E35" t="n">
-        <v>-12.53</v>
+        <v>-11.82</v>
       </c>
       <c r="F35" t="n">
-        <v>14.71</v>
+        <v>15.64</v>
       </c>
       <c r="G35" t="n">
-        <v>7.17</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>2.78</v>
+        <v>3.13</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="J35" t="n">
         <v>0.65</v>
       </c>
       <c r="K35" t="n">
-        <v>8.1</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>7.77</v>
+        <v>7.83</v>
       </c>
       <c r="M35" t="n">
-        <v>8.09</v>
+        <v>8.16</v>
       </c>
       <c r="N35" t="n">
-        <v>7.12</v>
+        <v>7.19</v>
       </c>
       <c r="O35" t="n">
-        <v>9.42</v>
+        <v>9.48</v>
       </c>
       <c r="P35" t="n">
         <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>48.01</v>
+        <v>48.57</v>
       </c>
       <c r="R35" t="n">
-        <v>-5.06</v>
+        <v>-4.32</v>
       </c>
       <c r="S35" t="n">
-        <v>-20.41</v>
+        <v>-19.76</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3943,7 +3955,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Momentum negativo; Lejos del máximo 20D</t>
         </is>
       </c>
     </row>
@@ -3974,10 +3986,10 @@
         <v>-9.26</v>
       </c>
       <c r="H36" t="n">
-        <v>-17.65</v>
+        <v>-18.23</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>1.76</v>
@@ -4058,55 +4070,55 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>208.69</v>
+        <v>210.31</v>
       </c>
       <c r="D37" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E37" t="n">
-        <v>11.87</v>
+        <v>12.74</v>
       </c>
       <c r="F37" t="n">
-        <v>57.1</v>
+        <v>58.32</v>
       </c>
       <c r="G37" t="n">
-        <v>49.27</v>
+        <v>50.43</v>
       </c>
       <c r="H37" t="n">
-        <v>45.17</v>
+        <v>45.81</v>
       </c>
       <c r="I37" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="J37" t="n">
         <v>18.85</v>
       </c>
       <c r="K37" t="n">
-        <v>9.029999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>202.09</v>
+        <v>203.71</v>
       </c>
       <c r="M37" t="n">
-        <v>211.52</v>
+        <v>213.14</v>
       </c>
       <c r="N37" t="n">
-        <v>183.24</v>
+        <v>184.86</v>
       </c>
       <c r="O37" t="n">
-        <v>250.16</v>
+        <v>251.78</v>
       </c>
       <c r="P37" t="n">
         <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>73.06</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="R37" t="n">
-        <v>25.57</v>
+        <v>26.48</v>
       </c>
       <c r="S37" t="n">
-        <v>-15.82</v>
+        <v>-15.16</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4136,12 +4148,12 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Fuerte vs QQQ</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Volumen confirma</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad muy alta</t>
+          <t>Tendencia larga débil; RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -556,64 +556,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>207.64</v>
+        <v>1856.66</v>
       </c>
       <c r="D2" t="n">
         <v>96</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>2.22</v>
       </c>
       <c r="F2" t="n">
-        <v>12.6</v>
+        <v>6.21</v>
       </c>
       <c r="G2" t="n">
-        <v>26.36</v>
+        <v>26.29</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09</v>
+        <v>-6</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="n">
-        <v>12.37</v>
+        <v>88.45</v>
       </c>
       <c r="K2" t="n">
-        <v>5.96</v>
+        <v>4.76</v>
       </c>
       <c r="L2" t="n">
-        <v>203.31</v>
+        <v>1825.7</v>
       </c>
       <c r="M2" t="n">
-        <v>209.5</v>
+        <v>1869.92</v>
       </c>
       <c r="N2" t="n">
-        <v>190.93</v>
+        <v>1737.24</v>
       </c>
       <c r="O2" t="n">
-        <v>234.86</v>
+        <v>2051.25</v>
       </c>
       <c r="P2" t="n">
         <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>50.76</v>
+        <v>52.86</v>
       </c>
       <c r="R2" t="n">
-        <v>4.28</v>
+        <v>2.89</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.95</v>
+        <v>-4.26</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -647,76 +647,76 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Tendencia larga débil</t>
+          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>431.2</v>
+        <v>151.41</v>
       </c>
       <c r="D3" t="n">
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>4.96</v>
+        <v>1.83</v>
       </c>
       <c r="F3" t="n">
-        <v>8.99</v>
+        <v>1.61</v>
       </c>
       <c r="G3" t="n">
-        <v>21.65</v>
+        <v>3.57</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.52</v>
+        <v>-10.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1.38</v>
+        <v>0.43</v>
       </c>
       <c r="J3" t="n">
-        <v>18.91</v>
+        <v>3.98</v>
       </c>
       <c r="K3" t="n">
-        <v>4.38</v>
+        <v>2.63</v>
       </c>
       <c r="L3" t="n">
-        <v>424.58</v>
+        <v>150.02</v>
       </c>
       <c r="M3" t="n">
-        <v>434.04</v>
+        <v>152.01</v>
       </c>
       <c r="N3" t="n">
-        <v>405.67</v>
+        <v>146.04</v>
       </c>
       <c r="O3" t="n">
-        <v>472.8</v>
+        <v>160.16</v>
       </c>
       <c r="P3" t="n">
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>58.1</v>
+        <v>51.47</v>
       </c>
       <c r="R3" t="n">
-        <v>6.53</v>
+        <v>0.8</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.85</v>
+        <v>-2.75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -750,76 +750,76 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; Tendencia larga positiva; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Débil vs QQQ</t>
+          <t>Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1520.94</v>
+        <v>55.56</v>
       </c>
       <c r="D4" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>5.41</v>
+        <v>0.72</v>
       </c>
       <c r="F4" t="n">
-        <v>0.39</v>
+        <v>5.98</v>
       </c>
       <c r="G4" t="n">
-        <v>8.359999999999999</v>
+        <v>11.47</v>
       </c>
       <c r="H4" t="n">
-        <v>-12.12</v>
+        <v>-6.23</v>
       </c>
       <c r="I4" t="n">
-        <v>0.97</v>
+        <v>0.37</v>
       </c>
       <c r="J4" t="n">
-        <v>60.71</v>
+        <v>1.65</v>
       </c>
       <c r="K4" t="n">
-        <v>3.99</v>
+        <v>2.98</v>
       </c>
       <c r="L4" t="n">
-        <v>1499.69</v>
+        <v>54.98</v>
       </c>
       <c r="M4" t="n">
-        <v>1530.05</v>
+        <v>55.8</v>
       </c>
       <c r="N4" t="n">
-        <v>1438.98</v>
+        <v>53.32</v>
       </c>
       <c r="O4" t="n">
-        <v>1654.5</v>
+        <v>59.19</v>
       </c>
       <c r="P4" t="n">
         <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>56.98</v>
+        <v>53.57</v>
       </c>
       <c r="R4" t="n">
-        <v>4.07</v>
+        <v>1.55</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.66</v>
+        <v>-2.88</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -836,11 +836,7 @@
           <t>BAJO</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -858,71 +854,71 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1811.35</v>
+        <v>418.18</v>
       </c>
       <c r="D5" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E5" t="n">
-        <v>4.53</v>
+        <v>-1.71</v>
       </c>
       <c r="F5" t="n">
-        <v>0.86</v>
+        <v>5.41</v>
       </c>
       <c r="G5" t="n">
-        <v>23.88</v>
+        <v>26.02</v>
       </c>
       <c r="H5" t="n">
-        <v>-11.65</v>
+        <v>-6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.96</v>
+        <v>0.59</v>
       </c>
       <c r="J5" t="n">
-        <v>87.83</v>
+        <v>15.61</v>
       </c>
       <c r="K5" t="n">
-        <v>4.85</v>
+        <v>3.73</v>
       </c>
       <c r="L5" t="n">
-        <v>1780.61</v>
+        <v>412.72</v>
       </c>
       <c r="M5" t="n">
-        <v>1824.53</v>
+        <v>420.53</v>
       </c>
       <c r="N5" t="n">
-        <v>1692.77</v>
+        <v>397.12</v>
       </c>
       <c r="O5" t="n">
-        <v>2004.59</v>
+        <v>452.52</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>49.95</v>
+        <v>49.18</v>
       </c>
       <c r="R5" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="S5" t="n">
-        <v>-6.6</v>
+        <v>-4.45</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -939,11 +935,7 @@
           <t>BAJO</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -961,71 +953,71 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>419.3</v>
+        <v>400.75</v>
       </c>
       <c r="D6" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.89</v>
+        <v>-4.47</v>
       </c>
       <c r="F6" t="n">
-        <v>10.12</v>
+        <v>6.84</v>
       </c>
       <c r="G6" t="n">
-        <v>29.22</v>
+        <v>10.34</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.39</v>
+        <v>-5.37</v>
       </c>
       <c r="I6" t="n">
-        <v>0.89</v>
+        <v>0.68</v>
       </c>
       <c r="J6" t="n">
-        <v>15.39</v>
+        <v>15.59</v>
       </c>
       <c r="K6" t="n">
-        <v>3.67</v>
+        <v>3.89</v>
       </c>
       <c r="L6" t="n">
-        <v>413.91</v>
+        <v>395.29</v>
       </c>
       <c r="M6" t="n">
-        <v>421.61</v>
+        <v>403.08</v>
       </c>
       <c r="N6" t="n">
-        <v>398.52</v>
+        <v>379.7</v>
       </c>
       <c r="O6" t="n">
-        <v>453.16</v>
+        <v>435.04</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>48.46</v>
+        <v>58.85</v>
       </c>
       <c r="R6" t="n">
-        <v>1.15</v>
+        <v>1.85</v>
       </c>
       <c r="S6" t="n">
-        <v>-4.2</v>
+        <v>-4.58</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1060,71 +1052,71 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>MACD sin confirmar</t>
+          <t>MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55.64</v>
+        <v>226.34</v>
       </c>
       <c r="D7" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.64</v>
+        <v>8.91</v>
       </c>
       <c r="F7" t="n">
-        <v>8.06</v>
+        <v>13.81</v>
       </c>
       <c r="G7" t="n">
-        <v>10.42</v>
+        <v>22.37</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.45</v>
+        <v>1.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="J7" t="n">
-        <v>1.65</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>2.97</v>
+        <v>3.58</v>
       </c>
       <c r="L7" t="n">
-        <v>55.06</v>
+        <v>223.5</v>
       </c>
       <c r="M7" t="n">
-        <v>55.89</v>
+        <v>227.56</v>
       </c>
       <c r="N7" t="n">
-        <v>53.41</v>
+        <v>215.39</v>
       </c>
       <c r="O7" t="n">
-        <v>59.28</v>
+        <v>244.18</v>
       </c>
       <c r="P7" t="n">
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>55.51</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.73</v>
+        <v>-0.66</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1138,10 +1130,14 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1154,76 +1150,76 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>RSI algo alto; Momentum 5D extendido; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>265.82</v>
+        <v>436.86</v>
       </c>
       <c r="D8" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.83</v>
+        <v>1.92</v>
       </c>
       <c r="F8" t="n">
-        <v>6.75</v>
+        <v>10.81</v>
       </c>
       <c r="G8" t="n">
-        <v>33.72</v>
+        <v>21.8</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.76</v>
+        <v>-1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>0.78</v>
+        <v>0.62</v>
       </c>
       <c r="J8" t="n">
-        <v>7.26</v>
+        <v>19.02</v>
       </c>
       <c r="K8" t="n">
-        <v>2.73</v>
+        <v>4.35</v>
       </c>
       <c r="L8" t="n">
-        <v>263.28</v>
+        <v>430.2</v>
       </c>
       <c r="M8" t="n">
-        <v>266.91</v>
+        <v>439.71</v>
       </c>
       <c r="N8" t="n">
-        <v>256.02</v>
+        <v>411.19</v>
       </c>
       <c r="O8" t="n">
-        <v>281.78</v>
+        <v>478.7</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>62.77</v>
+        <v>59.34</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>7.36</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.57</v>
+        <v>-2.58</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1237,10 +1233,14 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1258,14 +1258,14 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Débil vs QQQ</t>
+          <t>Volumen bajo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1274,55 +1274,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>397.28</v>
+        <v>1580.99</v>
       </c>
       <c r="D9" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E9" t="n">
-        <v>0.73</v>
+        <v>2.35</v>
       </c>
       <c r="F9" t="n">
-        <v>4.58</v>
+        <v>6.93</v>
       </c>
       <c r="G9" t="n">
-        <v>8.75</v>
+        <v>11.6</v>
       </c>
       <c r="H9" t="n">
-        <v>-7.93</v>
+        <v>-5.28</v>
       </c>
       <c r="I9" t="n">
-        <v>1.19</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="n">
-        <v>15.57</v>
+        <v>62.71</v>
       </c>
       <c r="K9" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
       <c r="L9" t="n">
-        <v>391.83</v>
+        <v>1559.04</v>
       </c>
       <c r="M9" t="n">
-        <v>399.62</v>
+        <v>1590.4</v>
       </c>
       <c r="N9" t="n">
-        <v>376.26</v>
+        <v>1496.33</v>
       </c>
       <c r="O9" t="n">
-        <v>431.54</v>
+        <v>1718.95</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>54.75</v>
+        <v>63.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>7.81</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.41</v>
+        <v>-1.35</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1336,10 +1336,14 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1357,71 +1361,71 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Débil vs QQQ</t>
+          <t>Débil vs QQQ; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>150.63</v>
+        <v>297.09</v>
       </c>
       <c r="D10" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.74</v>
+        <v>-0.03</v>
       </c>
       <c r="F10" t="n">
-        <v>0.93</v>
+        <v>12.04</v>
       </c>
       <c r="G10" t="n">
-        <v>1.47</v>
+        <v>26.26</v>
       </c>
       <c r="H10" t="n">
-        <v>-11.58</v>
+        <v>-0.17</v>
       </c>
       <c r="I10" t="n">
-        <v>0.96</v>
+        <v>0.45</v>
       </c>
       <c r="J10" t="n">
-        <v>4.02</v>
+        <v>13.84</v>
       </c>
       <c r="K10" t="n">
-        <v>2.67</v>
+        <v>4.66</v>
       </c>
       <c r="L10" t="n">
-        <v>149.22</v>
+        <v>292.25</v>
       </c>
       <c r="M10" t="n">
-        <v>151.23</v>
+        <v>299.17</v>
       </c>
       <c r="N10" t="n">
-        <v>145.2</v>
+        <v>278.41</v>
       </c>
       <c r="O10" t="n">
-        <v>159.48</v>
+        <v>327.54</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>51.87</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>0.37</v>
+        <v>9.82</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.25</v>
+        <v>-0.97</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1435,7 +1439,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -1451,76 +1455,76 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; Tendencia larga positiva; RSI saludable; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Débil vs QQQ</t>
+          <t>RSI algo alto; Volumen bajo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>289.24</v>
+        <v>201.9</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E11" t="n">
-        <v>4.87</v>
+        <v>1.99</v>
       </c>
       <c r="F11" t="n">
-        <v>6.18</v>
+        <v>3.07</v>
       </c>
       <c r="G11" t="n">
-        <v>22.95</v>
+        <v>21.61</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.33</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.88</v>
+        <v>0.62</v>
       </c>
       <c r="J11" t="n">
-        <v>14.39</v>
+        <v>12.22</v>
       </c>
       <c r="K11" t="n">
-        <v>4.98</v>
+        <v>6.05</v>
       </c>
       <c r="L11" t="n">
-        <v>284.2</v>
+        <v>197.63</v>
       </c>
       <c r="M11" t="n">
-        <v>291.4</v>
+        <v>203.74</v>
       </c>
       <c r="N11" t="n">
-        <v>269.81</v>
+        <v>185.41</v>
       </c>
       <c r="O11" t="n">
-        <v>320.91</v>
+        <v>228.79</v>
       </c>
       <c r="P11" t="n">
         <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>60.49</v>
+        <v>52.21</v>
       </c>
       <c r="R11" t="n">
-        <v>7.55</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.59</v>
+        <v>-7.58</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1537,11 +1541,7 @@
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Débil vs QQQ; Algo extendida sobre MA20</t>
+          <t>Tendencia larga débil; Volumen bajo; Débil vs QQQ; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -1575,55 +1575,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>207.92</v>
+        <v>219.97</v>
       </c>
       <c r="D12" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.44</v>
+        <v>-7.3</v>
       </c>
       <c r="F12" t="n">
-        <v>28.97</v>
+        <v>38.05</v>
       </c>
       <c r="G12" t="n">
-        <v>65.95999999999999</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>16.46</v>
+        <v>25.84</v>
       </c>
       <c r="I12" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="J12" t="n">
-        <v>18.09</v>
+        <v>17.81</v>
       </c>
       <c r="K12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="L12" t="n">
-        <v>201.59</v>
+        <v>213.74</v>
       </c>
       <c r="M12" t="n">
-        <v>210.63</v>
+        <v>222.64</v>
       </c>
       <c r="N12" t="n">
-        <v>183.49</v>
+        <v>195.93</v>
       </c>
       <c r="O12" t="n">
-        <v>247.73</v>
+        <v>259.14</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>53.59</v>
+        <v>54.73</v>
       </c>
       <c r="R12" t="n">
-        <v>3.72</v>
+        <v>8.1</v>
       </c>
       <c r="S12" t="n">
-        <v>-13.19</v>
+        <v>-8.15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1640,11 +1640,7 @@
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1662,71 +1658,71 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Volatilidad alta</t>
+          <t>MACD sin confirmar; Volumen bajo; Momentum negativo; Algo extendida sobre MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>515.99</v>
+        <v>269.48</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="E13" t="n">
-        <v>6.89</v>
+        <v>-2.01</v>
       </c>
       <c r="F13" t="n">
-        <v>28.6</v>
+        <v>8.44</v>
       </c>
       <c r="G13" t="n">
-        <v>45.58</v>
+        <v>33.97</v>
       </c>
       <c r="H13" t="n">
-        <v>16.09</v>
+        <v>-3.77</v>
       </c>
       <c r="I13" t="n">
-        <v>1.97</v>
+        <v>0.57</v>
       </c>
       <c r="J13" t="n">
-        <v>19.23</v>
+        <v>7.36</v>
       </c>
       <c r="K13" t="n">
-        <v>3.73</v>
+        <v>2.73</v>
       </c>
       <c r="L13" t="n">
-        <v>509.26</v>
+        <v>266.9</v>
       </c>
       <c r="M13" t="n">
-        <v>518.87</v>
+        <v>270.58</v>
       </c>
       <c r="N13" t="n">
-        <v>490.03</v>
+        <v>259.54</v>
       </c>
       <c r="O13" t="n">
-        <v>558.3</v>
+        <v>285.67</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>71.06</v>
+        <v>66.23</v>
       </c>
       <c r="R13" t="n">
-        <v>12.41</v>
+        <v>2.49</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.33</v>
+        <v>-3.26</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1740,96 +1736,92 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RSI algo alto; Momentum 5D extendido; Muy alejada de MA20</t>
+          <t>RSI algo alto; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>294.8</v>
+        <v>32.21</v>
       </c>
       <c r="D14" t="n">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E14" t="n">
-        <v>3.83</v>
+        <v>-7.07</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>18.03</v>
       </c>
       <c r="G14" t="n">
-        <v>15.36</v>
+        <v>6.97</v>
       </c>
       <c r="H14" t="n">
-        <v>1.49</v>
+        <v>5.82</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.51</v>
       </c>
       <c r="J14" t="n">
-        <v>6.28</v>
+        <v>2.29</v>
       </c>
       <c r="K14" t="n">
-        <v>2.13</v>
+        <v>7.12</v>
       </c>
       <c r="L14" t="n">
-        <v>292.6</v>
+        <v>31.41</v>
       </c>
       <c r="M14" t="n">
-        <v>295.74</v>
+        <v>32.55</v>
       </c>
       <c r="N14" t="n">
-        <v>286.32</v>
+        <v>29.11</v>
       </c>
       <c r="O14" t="n">
-        <v>308.62</v>
+        <v>37.26</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>76</v>
+        <v>63.53</v>
       </c>
       <c r="R14" t="n">
-        <v>6.64</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.16</v>
+        <v>-11.44</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1843,96 +1835,92 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado</t>
+          <t>Tendencia larga débil; Volumen bajo; Momentum negativo; Algo extendida sobre MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>117.56</v>
+        <v>529.62</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E15" t="n">
-        <v>49.26</v>
+        <v>4.49</v>
       </c>
       <c r="F15" t="n">
-        <v>62.78</v>
+        <v>31.79</v>
       </c>
       <c r="G15" t="n">
-        <v>74.31999999999999</v>
+        <v>49.66</v>
       </c>
       <c r="H15" t="n">
-        <v>50.27</v>
+        <v>19.58</v>
       </c>
       <c r="I15" t="n">
-        <v>1.25</v>
+        <v>0.82</v>
       </c>
       <c r="J15" t="n">
-        <v>8.81</v>
+        <v>19.33</v>
       </c>
       <c r="K15" t="n">
-        <v>7.49</v>
+        <v>3.65</v>
       </c>
       <c r="L15" t="n">
-        <v>114.48</v>
+        <v>522.85</v>
       </c>
       <c r="M15" t="n">
-        <v>118.88</v>
+        <v>532.52</v>
       </c>
       <c r="N15" t="n">
-        <v>105.67</v>
+        <v>503.52</v>
       </c>
       <c r="O15" t="n">
-        <v>136.93</v>
+        <v>572.16</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>66.90000000000001</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>35.62</v>
+        <v>13.8</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.15</v>
+        <v>-0.77</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1971,71 +1959,71 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RSI algo alto; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>RSI algo alto; Muy alejada de MA20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>707.24</v>
+        <v>402.29</v>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E16" t="n">
-        <v>3.76</v>
+        <v>1.07</v>
       </c>
       <c r="F16" t="n">
-        <v>12.51</v>
+        <v>19.33</v>
       </c>
       <c r="G16" t="n">
-        <v>17.65</v>
+        <v>33.29</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="I16" t="n">
-        <v>1.09</v>
+        <v>0.71</v>
       </c>
       <c r="J16" t="n">
-        <v>10.25</v>
+        <v>11.45</v>
       </c>
       <c r="K16" t="n">
-        <v>1.45</v>
+        <v>2.85</v>
       </c>
       <c r="L16" t="n">
-        <v>703.65</v>
+        <v>398.28</v>
       </c>
       <c r="M16" t="n">
-        <v>708.78</v>
+        <v>404.01</v>
       </c>
       <c r="N16" t="n">
-        <v>693.41</v>
+        <v>386.83</v>
       </c>
       <c r="O16" t="n">
-        <v>729.78</v>
+        <v>427.49</v>
       </c>
       <c r="P16" t="n">
         <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>79.23</v>
+        <v>82.88</v>
       </c>
       <c r="R16" t="n">
-        <v>5.63</v>
+        <v>9.66</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.03</v>
+        <v>-0.35</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2074,71 +2062,71 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado</t>
+          <t>RSI sobrecomprado; Volumen bajo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>220.78</v>
+        <v>298.77</v>
       </c>
       <c r="D17" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E17" t="n">
-        <v>12.36</v>
+        <v>4.01</v>
       </c>
       <c r="F17" t="n">
-        <v>12.35</v>
+        <v>12.24</v>
       </c>
       <c r="G17" t="n">
-        <v>20.78</v>
+        <v>13.33</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.16</v>
+        <v>0.03</v>
       </c>
       <c r="I17" t="n">
-        <v>1.04</v>
+        <v>0.71</v>
       </c>
       <c r="J17" t="n">
-        <v>8.08</v>
+        <v>6.52</v>
       </c>
       <c r="K17" t="n">
-        <v>3.66</v>
+        <v>2.18</v>
       </c>
       <c r="L17" t="n">
-        <v>217.95</v>
+        <v>296.49</v>
       </c>
       <c r="M17" t="n">
-        <v>221.99</v>
+        <v>299.75</v>
       </c>
       <c r="N17" t="n">
-        <v>209.88</v>
+        <v>289.97</v>
       </c>
       <c r="O17" t="n">
-        <v>238.55</v>
+        <v>313.11</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>64.22</v>
+        <v>77.94</v>
       </c>
       <c r="R17" t="n">
-        <v>7.23</v>
+        <v>7.44</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.33</v>
+        <v>-0.71</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2155,7 +2143,11 @@
           <t>ALTO</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2168,76 +2160,76 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Subida muy extendida 5D; Algo extendida sobre MA20</t>
+          <t>RSI sobrecomprado; Volumen bajo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>387.35</v>
+        <v>715.22</v>
       </c>
       <c r="D18" t="n">
         <v>90</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.28</v>
+        <v>2.8</v>
       </c>
       <c r="F18" t="n">
-        <v>16.35</v>
+        <v>12.21</v>
       </c>
       <c r="G18" t="n">
-        <v>26.79</v>
+        <v>19.1</v>
       </c>
       <c r="H18" t="n">
-        <v>3.84</v>
+        <v>-0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="J18" t="n">
-        <v>10.53</v>
+        <v>10.28</v>
       </c>
       <c r="K18" t="n">
-        <v>2.72</v>
+        <v>1.44</v>
       </c>
       <c r="L18" t="n">
-        <v>383.66</v>
+        <v>711.62</v>
       </c>
       <c r="M18" t="n">
-        <v>388.93</v>
+        <v>716.76</v>
       </c>
       <c r="N18" t="n">
-        <v>373.13</v>
+        <v>701.34</v>
       </c>
       <c r="O18" t="n">
-        <v>410.52</v>
+        <v>737.83</v>
       </c>
       <c r="P18" t="n">
         <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>79.33</v>
+        <v>84.13</v>
       </c>
       <c r="R18" t="n">
-        <v>6.53</v>
+        <v>6.21</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.64</v>
+        <v>-0.2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2288,55 +2280,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>738.1799999999999</v>
+        <v>743.14</v>
       </c>
       <c r="D19" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E19" t="n">
-        <v>1.99</v>
+        <v>1.27</v>
       </c>
       <c r="F19" t="n">
-        <v>6.3</v>
+        <v>6.17</v>
       </c>
       <c r="G19" t="n">
-        <v>8.57</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.21</v>
+        <v>-6.04</v>
       </c>
       <c r="I19" t="n">
-        <v>1.06</v>
+        <v>0.59</v>
       </c>
       <c r="J19" t="n">
-        <v>6.74</v>
+        <v>6.62</v>
       </c>
       <c r="K19" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="L19" t="n">
-        <v>735.8200000000001</v>
+        <v>740.8200000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>739.1900000000001</v>
+        <v>744.13</v>
       </c>
       <c r="N19" t="n">
-        <v>729.08</v>
+        <v>734.2</v>
       </c>
       <c r="O19" t="n">
-        <v>753.01</v>
+        <v>757.72</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>76.09</v>
+        <v>82.19</v>
       </c>
       <c r="R19" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.35</v>
+        <v>-0.1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2371,71 +2363,71 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Débil vs QQQ</t>
+          <t>RSI sobrecomprado; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>433.45</v>
+        <v>54.72</v>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E20" t="n">
-        <v>11.32</v>
+        <v>4.1</v>
       </c>
       <c r="F20" t="n">
-        <v>19.01</v>
+        <v>26.53</v>
       </c>
       <c r="G20" t="n">
-        <v>3.84</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>6.5</v>
+        <v>14.32</v>
       </c>
       <c r="I20" t="n">
-        <v>0.92</v>
+        <v>0.54</v>
       </c>
       <c r="J20" t="n">
-        <v>16.76</v>
+        <v>4.41</v>
       </c>
       <c r="K20" t="n">
-        <v>3.87</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>427.58</v>
+        <v>53.18</v>
       </c>
       <c r="M20" t="n">
-        <v>435.96</v>
+        <v>55.39</v>
       </c>
       <c r="N20" t="n">
-        <v>410.82</v>
+        <v>48.78</v>
       </c>
       <c r="O20" t="n">
-        <v>470.32</v>
+        <v>64.42</v>
       </c>
       <c r="P20" t="n">
         <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>70.04000000000001</v>
+        <v>67.64</v>
       </c>
       <c r="R20" t="n">
-        <v>9.779999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="S20" t="n">
-        <v>-3.5</v>
+        <v>-7.48</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2465,76 +2457,76 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Fuerte vs QQQ</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI algo alto; Subida muy extendida 5D; Algo extendida sobre MA20</t>
+          <t>Tendencia larga débil; RSI algo alto; Volumen bajo; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>55.87</v>
+        <v>806.02</v>
       </c>
       <c r="D21" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E21" t="n">
-        <v>16.4</v>
+        <v>20.92</v>
       </c>
       <c r="F21" t="n">
-        <v>56.24</v>
+        <v>76.67</v>
       </c>
       <c r="G21" t="n">
-        <v>63.79</v>
+        <v>101.7</v>
       </c>
       <c r="H21" t="n">
-        <v>43.73</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>4.6</v>
+        <v>51.05</v>
       </c>
       <c r="K21" t="n">
-        <v>8.23</v>
+        <v>6.33</v>
       </c>
       <c r="L21" t="n">
-        <v>54.26</v>
+        <v>788.15</v>
       </c>
       <c r="M21" t="n">
-        <v>56.56</v>
+        <v>813.6799999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>49.66</v>
+        <v>737.1</v>
       </c>
       <c r="O21" t="n">
-        <v>65.98</v>
+        <v>918.34</v>
       </c>
       <c r="P21" t="n">
         <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>62.5</v>
+        <v>84.88</v>
       </c>
       <c r="R21" t="n">
-        <v>19.04</v>
+        <v>39.85</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.55</v>
+        <v>-1.55</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2564,76 +2556,76 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>32.79</v>
+        <v>126.45</v>
       </c>
       <c r="D22" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E22" t="n">
-        <v>17.82</v>
+        <v>49.38</v>
       </c>
       <c r="F22" t="n">
-        <v>20.55</v>
+        <v>71.81</v>
       </c>
       <c r="G22" t="n">
-        <v>7.37</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>8.039999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="I22" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="J22" t="n">
-        <v>2.43</v>
+        <v>8.94</v>
       </c>
       <c r="K22" t="n">
-        <v>7.41</v>
+        <v>7.07</v>
       </c>
       <c r="L22" t="n">
-        <v>31.94</v>
+        <v>123.32</v>
       </c>
       <c r="M22" t="n">
-        <v>33.15</v>
+        <v>127.79</v>
       </c>
       <c r="N22" t="n">
-        <v>29.51</v>
+        <v>114.38</v>
       </c>
       <c r="O22" t="n">
-        <v>38.13</v>
+        <v>146.12</v>
       </c>
       <c r="P22" t="n">
         <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>58.19</v>
+        <v>74.66</v>
       </c>
       <c r="R22" t="n">
-        <v>11.51</v>
+        <v>41.56</v>
       </c>
       <c r="S22" t="n">
-        <v>-9.84</v>
+        <v>-0.61</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2663,76 +2655,76 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Subida muy extendida 5D; Algo extendida sobre MA20; Volatilidad alta</t>
+          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>766.58</v>
+        <v>121.07</v>
       </c>
       <c r="D23" t="n">
         <v>70</v>
       </c>
       <c r="E23" t="n">
-        <v>19.74</v>
+        <v>7.13</v>
       </c>
       <c r="F23" t="n">
-        <v>64.62</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>86.3</v>
+        <v>162.17</v>
       </c>
       <c r="H23" t="n">
-        <v>52.11</v>
+        <v>74.22</v>
       </c>
       <c r="I23" t="n">
-        <v>1.57</v>
+        <v>0.62</v>
       </c>
       <c r="J23" t="n">
-        <v>49.16</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>6.41</v>
+        <v>7.89</v>
       </c>
       <c r="L23" t="n">
-        <v>749.38</v>
+        <v>117.73</v>
       </c>
       <c r="M23" t="n">
-        <v>773.95</v>
+        <v>122.5</v>
       </c>
       <c r="N23" t="n">
-        <v>700.22</v>
+        <v>108.18</v>
       </c>
       <c r="O23" t="n">
-        <v>874.73</v>
+        <v>142.07</v>
       </c>
       <c r="P23" t="n">
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>82.36</v>
+        <v>80.89</v>
       </c>
       <c r="R23" t="n">
-        <v>37.16</v>
+        <v>29.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.36</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2767,71 +2759,71 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>RSI sobrecomprado; Volumen bajo; Momentum 5D extendido; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>120.61</v>
+        <v>447.89</v>
       </c>
       <c r="D24" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E24" t="n">
-        <v>11.52</v>
+        <v>6.29</v>
       </c>
       <c r="F24" t="n">
-        <v>89.01000000000001</v>
+        <v>73.52</v>
       </c>
       <c r="G24" t="n">
-        <v>157.77</v>
+        <v>120.55</v>
       </c>
       <c r="H24" t="n">
-        <v>76.5</v>
+        <v>61.31</v>
       </c>
       <c r="I24" t="n">
-        <v>1.11</v>
+        <v>0.47</v>
       </c>
       <c r="J24" t="n">
-        <v>9.15</v>
+        <v>29.48</v>
       </c>
       <c r="K24" t="n">
-        <v>7.59</v>
+        <v>6.58</v>
       </c>
       <c r="L24" t="n">
-        <v>117.41</v>
+        <v>437.57</v>
       </c>
       <c r="M24" t="n">
-        <v>121.98</v>
+        <v>452.31</v>
       </c>
       <c r="N24" t="n">
-        <v>108.26</v>
+        <v>408.09</v>
       </c>
       <c r="O24" t="n">
-        <v>140.74</v>
+        <v>512.75</v>
       </c>
       <c r="P24" t="n">
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>81.11</v>
+        <v>75.69</v>
       </c>
       <c r="R24" t="n">
-        <v>33.39</v>
+        <v>25.82</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.15</v>
+        <v>-4.55</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2866,71 +2858,71 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>RSI sobrecomprado; Volumen bajo; Momentum 5D extendido; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>448.29</v>
+        <v>444.98</v>
       </c>
       <c r="D25" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E25" t="n">
-        <v>26.19</v>
+        <v>11.6</v>
       </c>
       <c r="F25" t="n">
-        <v>75.75</v>
+        <v>13.53</v>
       </c>
       <c r="G25" t="n">
-        <v>116.23</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>63.24</v>
+        <v>1.32</v>
       </c>
       <c r="I25" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="J25" t="n">
-        <v>28.31</v>
+        <v>17.05</v>
       </c>
       <c r="K25" t="n">
-        <v>6.32</v>
+        <v>3.83</v>
       </c>
       <c r="L25" t="n">
-        <v>438.38</v>
+        <v>439.01</v>
       </c>
       <c r="M25" t="n">
-        <v>452.54</v>
+        <v>447.53</v>
       </c>
       <c r="N25" t="n">
-        <v>410.07</v>
+        <v>421.96</v>
       </c>
       <c r="O25" t="n">
-        <v>510.58</v>
+        <v>482.49</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>75.97</v>
+        <v>81.7</v>
       </c>
       <c r="R25" t="n">
-        <v>29.38</v>
+        <v>11.94</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.46</v>
+        <v>-1.86</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2960,19 +2952,19 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Histograma MACD mejora</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>Tendencia larga débil; RSI sobrecomprado; Subida muy extendida 5D; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2981,55 +2973,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>185.95</v>
+        <v>56.1</v>
       </c>
       <c r="D26" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.47</v>
+        <v>1.79</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.57</v>
+        <v>0.49</v>
       </c>
       <c r="G26" t="n">
-        <v>2.19</v>
+        <v>22.71</v>
       </c>
       <c r="H26" t="n">
-        <v>-13.08</v>
+        <v>-11.72</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="J26" t="n">
-        <v>4.52</v>
+        <v>1.85</v>
       </c>
       <c r="K26" t="n">
-        <v>2.43</v>
+        <v>3.3</v>
       </c>
       <c r="L26" t="n">
-        <v>184.37</v>
+        <v>55.46</v>
       </c>
       <c r="M26" t="n">
-        <v>186.63</v>
+        <v>56.38</v>
       </c>
       <c r="N26" t="n">
-        <v>179.84</v>
+        <v>53.6</v>
       </c>
       <c r="O26" t="n">
-        <v>195.9</v>
+        <v>60.18</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>49.43</v>
+        <v>45.36</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.55</v>
+        <v>-1.45</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.21</v>
+        <v>-7.71</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3059,80 +3051,80 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Tendencia larga positiva; RSI saludable; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; Tendencia larga positiva; Histograma MACD mejora; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Momentum negativo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.789999999999999</v>
+        <v>185.46</v>
       </c>
       <c r="D27" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.59</v>
+        <v>0.16</v>
       </c>
       <c r="F27" t="n">
-        <v>4.64</v>
+        <v>0.3</v>
       </c>
       <c r="G27" t="n">
-        <v>-18.46</v>
+        <v>2.72</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.87</v>
+        <v>-11.91</v>
       </c>
       <c r="I27" t="n">
-        <v>1.38</v>
+        <v>0.4</v>
       </c>
       <c r="J27" t="n">
-        <v>0.47</v>
+        <v>4.46</v>
       </c>
       <c r="K27" t="n">
-        <v>5.34</v>
+        <v>2.4</v>
       </c>
       <c r="L27" t="n">
-        <v>8.630000000000001</v>
+        <v>183.9</v>
       </c>
       <c r="M27" t="n">
-        <v>8.859999999999999</v>
+        <v>186.13</v>
       </c>
       <c r="N27" t="n">
-        <v>8.16</v>
+        <v>179.44</v>
       </c>
       <c r="O27" t="n">
-        <v>9.82</v>
+        <v>195.27</v>
       </c>
       <c r="P27" t="n">
         <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>41.62</v>
+        <v>46.64</v>
       </c>
       <c r="R27" t="n">
-        <v>-4.35</v>
+        <v>-0.83</v>
       </c>
       <c r="S27" t="n">
-        <v>-11.57</v>
+        <v>-4.47</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>BAJA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3158,80 +3150,80 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Tendencia larga positiva; Histograma MACD mejora</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; Momentum negativo; Débil vs QQQ; Lejos del máximo 20D</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>56.27</v>
+        <v>8.68</v>
       </c>
       <c r="D28" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.17</v>
+        <v>-9.59</v>
       </c>
       <c r="F28" t="n">
-        <v>1.61</v>
+        <v>-8.83</v>
       </c>
       <c r="G28" t="n">
-        <v>22.72</v>
+        <v>-16.54</v>
       </c>
       <c r="H28" t="n">
-        <v>-10.9</v>
+        <v>-21.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="J28" t="n">
-        <v>1.88</v>
+        <v>0.43</v>
       </c>
       <c r="K28" t="n">
-        <v>3.34</v>
+        <v>4.91</v>
       </c>
       <c r="L28" t="n">
-        <v>55.61</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>56.55</v>
+        <v>8.74</v>
       </c>
       <c r="N28" t="n">
-        <v>53.74</v>
+        <v>8.1</v>
       </c>
       <c r="O28" t="n">
-        <v>60.4</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>47.97</v>
+        <v>52.46</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.14</v>
+        <v>-5.11</v>
       </c>
       <c r="S28" t="n">
-        <v>-7.44</v>
+        <v>-12.68</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3257,76 +3249,76 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Tendencia larga positiva; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Momentum negativo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>78.27</v>
+        <v>404.62</v>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>1.61</v>
+        <v>-2.26</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.04</v>
+        <v>-1.6</v>
       </c>
       <c r="G29" t="n">
-        <v>3.03</v>
+        <v>2.19</v>
       </c>
       <c r="H29" t="n">
-        <v>-13.55</v>
+        <v>-13.81</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="J29" t="n">
-        <v>4.26</v>
+        <v>10.66</v>
       </c>
       <c r="K29" t="n">
-        <v>5.45</v>
+        <v>2.64</v>
       </c>
       <c r="L29" t="n">
-        <v>76.78</v>
+        <v>400.89</v>
       </c>
       <c r="M29" t="n">
-        <v>78.91</v>
+        <v>406.22</v>
       </c>
       <c r="N29" t="n">
-        <v>72.51000000000001</v>
+        <v>390.23</v>
       </c>
       <c r="O29" t="n">
-        <v>87.65000000000001</v>
+        <v>428.08</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>36.34</v>
+        <v>42.08</v>
       </c>
       <c r="R29" t="n">
-        <v>-3.85</v>
+        <v>-3.19</v>
       </c>
       <c r="S29" t="n">
-        <v>-16.13</v>
+        <v>-6.7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3356,76 +3348,76 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora; Momentum 5D sano</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>407.77</v>
+        <v>76.88</v>
       </c>
       <c r="D30" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.88</v>
+        <v>-2.75</v>
       </c>
       <c r="F30" t="n">
-        <v>3.73</v>
+        <v>-11.96</v>
       </c>
       <c r="G30" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="H30" t="n">
-        <v>-8.779999999999999</v>
+        <v>-24.17</v>
       </c>
       <c r="I30" t="n">
-        <v>1.04</v>
+        <v>0.39</v>
       </c>
       <c r="J30" t="n">
-        <v>11.72</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>2.87</v>
+        <v>5.2</v>
       </c>
       <c r="L30" t="n">
-        <v>403.67</v>
+        <v>75.48</v>
       </c>
       <c r="M30" t="n">
-        <v>409.53</v>
+        <v>77.48</v>
       </c>
       <c r="N30" t="n">
-        <v>391.95</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>433.55</v>
+        <v>85.67</v>
       </c>
       <c r="P30" t="n">
         <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>35.07</v>
+        <v>40.12</v>
       </c>
       <c r="R30" t="n">
-        <v>-2.52</v>
+        <v>-4.95</v>
       </c>
       <c r="S30" t="n">
-        <v>-5.98</v>
+        <v>-17.62</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3460,7 +3452,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -3476,55 +3468,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>45.44</v>
+        <v>45.6</v>
       </c>
       <c r="D31" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.26</v>
+        <v>-1.44</v>
       </c>
       <c r="F31" t="n">
-        <v>-5.27</v>
+        <v>-8</v>
       </c>
       <c r="G31" t="n">
-        <v>13.12</v>
+        <v>12.08</v>
       </c>
       <c r="H31" t="n">
-        <v>-17.78</v>
+        <v>-20.21</v>
       </c>
       <c r="I31" t="n">
-        <v>1.68</v>
+        <v>0.72</v>
       </c>
       <c r="J31" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="K31" t="n">
-        <v>3.54</v>
+        <v>3.39</v>
       </c>
       <c r="L31" t="n">
-        <v>44.88</v>
+        <v>45.06</v>
       </c>
       <c r="M31" t="n">
-        <v>45.68</v>
+        <v>45.83</v>
       </c>
       <c r="N31" t="n">
-        <v>43.27</v>
+        <v>43.52</v>
       </c>
       <c r="O31" t="n">
-        <v>48.98</v>
+        <v>49</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>24.15</v>
+        <v>28.99</v>
       </c>
       <c r="R31" t="n">
-        <v>-7.28</v>
+        <v>-6.57</v>
       </c>
       <c r="S31" t="n">
-        <v>-13.12</v>
+        <v>-12.81</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3559,71 +3551,71 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>15.9</v>
+        <v>616.5599999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F32" t="n">
-        <v>-11.22</v>
+        <v>-8.19</v>
       </c>
       <c r="G32" t="n">
-        <v>-18.92</v>
+        <v>-3.47</v>
       </c>
       <c r="H32" t="n">
-        <v>-23.73</v>
+        <v>-20.4</v>
       </c>
       <c r="I32" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
-        <v>0.83</v>
+        <v>18.55</v>
       </c>
       <c r="K32" t="n">
-        <v>5.21</v>
+        <v>3.01</v>
       </c>
       <c r="L32" t="n">
-        <v>15.61</v>
+        <v>610.0700000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>16.02</v>
+        <v>619.34</v>
       </c>
       <c r="N32" t="n">
-        <v>14.78</v>
+        <v>591.52</v>
       </c>
       <c r="O32" t="n">
-        <v>17.72</v>
+        <v>657.37</v>
       </c>
       <c r="P32" t="n">
         <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>28.73</v>
+        <v>35.21</v>
       </c>
       <c r="R32" t="n">
-        <v>-8.880000000000001</v>
+        <v>-3.86</v>
       </c>
       <c r="S32" t="n">
-        <v>-21.01</v>
+        <v>-10.84</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3658,71 +3650,71 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>603</v>
+        <v>15.38</v>
       </c>
       <c r="D33" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.32</v>
+        <v>-5.64</v>
       </c>
       <c r="F33" t="n">
-        <v>-8.98</v>
+        <v>-18.15</v>
       </c>
       <c r="G33" t="n">
-        <v>-5.67</v>
+        <v>-21.17</v>
       </c>
       <c r="H33" t="n">
-        <v>-21.49</v>
+        <v>-30.36</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="J33" t="n">
-        <v>18.43</v>
+        <v>0.8</v>
       </c>
       <c r="K33" t="n">
-        <v>3.06</v>
+        <v>5.18</v>
       </c>
       <c r="L33" t="n">
-        <v>596.55</v>
+        <v>15.1</v>
       </c>
       <c r="M33" t="n">
-        <v>605.76</v>
+        <v>15.5</v>
       </c>
       <c r="N33" t="n">
-        <v>578.12</v>
+        <v>14.31</v>
       </c>
       <c r="O33" t="n">
-        <v>643.55</v>
+        <v>17.13</v>
       </c>
       <c r="P33" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q33" t="n">
-        <v>25.43</v>
+        <v>29.61</v>
       </c>
       <c r="R33" t="n">
-        <v>-6.38</v>
+        <v>-10.99</v>
       </c>
       <c r="S33" t="n">
-        <v>-12.8</v>
+        <v>-23.6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3752,7 +3744,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3773,55 +3765,55 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>136</v>
+        <v>130.07</v>
       </c>
       <c r="D34" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.78</v>
       </c>
       <c r="F34" t="n">
-        <v>0.22</v>
+        <v>-8.5</v>
       </c>
       <c r="G34" t="n">
-        <v>3.49</v>
+        <v>-2.22</v>
       </c>
       <c r="H34" t="n">
-        <v>-12.29</v>
+        <v>-20.71</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="J34" t="n">
-        <v>6.04</v>
+        <v>5.73</v>
       </c>
       <c r="K34" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="L34" t="n">
-        <v>133.88</v>
+        <v>128.07</v>
       </c>
       <c r="M34" t="n">
-        <v>136.91</v>
+        <v>130.93</v>
       </c>
       <c r="N34" t="n">
-        <v>127.84</v>
+        <v>122.34</v>
       </c>
       <c r="O34" t="n">
-        <v>149.3</v>
+        <v>142.67</v>
       </c>
       <c r="P34" t="n">
         <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>31.04</v>
+        <v>35.14</v>
       </c>
       <c r="R34" t="n">
-        <v>-3.86</v>
+        <v>-7.66</v>
       </c>
       <c r="S34" t="n">
-        <v>-10.92</v>
+        <v>-14.81</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3872,55 +3864,55 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8.06</v>
+        <v>8.41</v>
       </c>
       <c r="D35" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E35" t="n">
-        <v>-11.82</v>
+        <v>-10.19</v>
       </c>
       <c r="F35" t="n">
-        <v>15.64</v>
+        <v>7.2</v>
       </c>
       <c r="G35" t="n">
-        <v>8.039999999999999</v>
+        <v>14.96</v>
       </c>
       <c r="H35" t="n">
-        <v>3.13</v>
+        <v>-5.01</v>
       </c>
       <c r="I35" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="J35" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="K35" t="n">
-        <v>8.029999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="L35" t="n">
-        <v>7.83</v>
+        <v>8.18</v>
       </c>
       <c r="M35" t="n">
-        <v>8.16</v>
+        <v>8.51</v>
       </c>
       <c r="N35" t="n">
-        <v>7.19</v>
+        <v>7.52</v>
       </c>
       <c r="O35" t="n">
-        <v>9.48</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="P35" t="n">
         <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>48.57</v>
+        <v>55.37</v>
       </c>
       <c r="R35" t="n">
-        <v>-4.32</v>
+        <v>-0.44</v>
       </c>
       <c r="S35" t="n">
-        <v>-19.76</v>
+        <v>-16.23</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3950,12 +3942,12 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; RSI saludable; Fuerte vs QQQ</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Momentum negativo; Lejos del máximo 20D</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>
@@ -3971,55 +3963,55 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>27.84</v>
+        <v>26.85</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>-10.68</v>
+        <v>-6.44</v>
       </c>
       <c r="F36" t="n">
-        <v>-5.72</v>
+        <v>-19.51</v>
       </c>
       <c r="G36" t="n">
-        <v>-9.26</v>
+        <v>-16.01</v>
       </c>
       <c r="H36" t="n">
-        <v>-18.23</v>
+        <v>-31.72</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="J36" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="K36" t="n">
-        <v>6.34</v>
+        <v>6.27</v>
       </c>
       <c r="L36" t="n">
-        <v>27.22</v>
+        <v>26.26</v>
       </c>
       <c r="M36" t="n">
-        <v>28.1</v>
+        <v>27.1</v>
       </c>
       <c r="N36" t="n">
-        <v>25.46</v>
+        <v>24.58</v>
       </c>
       <c r="O36" t="n">
-        <v>31.72</v>
+        <v>30.56</v>
       </c>
       <c r="P36" t="n">
         <v>1.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>24.18</v>
+        <v>25.99</v>
       </c>
       <c r="R36" t="n">
-        <v>-12.64</v>
+        <v>-14.87</v>
       </c>
       <c r="S36" t="n">
-        <v>-22.23</v>
+        <v>-24.99</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4070,55 +4062,55 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>210.31</v>
+        <v>213.55</v>
       </c>
       <c r="D37" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E37" t="n">
-        <v>12.74</v>
+        <v>10.89</v>
       </c>
       <c r="F37" t="n">
-        <v>58.32</v>
+        <v>60.5</v>
       </c>
       <c r="G37" t="n">
-        <v>50.43</v>
+        <v>50.68</v>
       </c>
       <c r="H37" t="n">
-        <v>45.81</v>
+        <v>48.29</v>
       </c>
       <c r="I37" t="n">
-        <v>1.42</v>
+        <v>0.73</v>
       </c>
       <c r="J37" t="n">
-        <v>18.85</v>
+        <v>19.38</v>
       </c>
       <c r="K37" t="n">
-        <v>8.960000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="L37" t="n">
-        <v>203.71</v>
+        <v>206.77</v>
       </c>
       <c r="M37" t="n">
-        <v>213.14</v>
+        <v>216.46</v>
       </c>
       <c r="N37" t="n">
-        <v>184.86</v>
+        <v>187.39</v>
       </c>
       <c r="O37" t="n">
-        <v>251.78</v>
+        <v>256.18</v>
       </c>
       <c r="P37" t="n">
         <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>73.81999999999999</v>
+        <v>75.36</v>
       </c>
       <c r="R37" t="n">
-        <v>26.48</v>
+        <v>25.4</v>
       </c>
       <c r="S37" t="n">
-        <v>-15.16</v>
+        <v>-13.86</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4148,12 +4140,12 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Volumen confirma</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; MACD positivo; Fuerte vs QQQ</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>Tendencia larga débil; RSI sobrecomprado; Volumen bajo; Subida muy extendida 5D; Muy alejada de MA20</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -565,55 +565,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1856.66</v>
+        <v>1849.71</v>
       </c>
       <c r="D2" t="n">
         <v>96</v>
       </c>
       <c r="E2" t="n">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="F2" t="n">
-        <v>6.21</v>
+        <v>5.81</v>
       </c>
       <c r="G2" t="n">
-        <v>26.29</v>
+        <v>25.81</v>
       </c>
       <c r="H2" t="n">
-        <v>-6</v>
+        <v>-6.32</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="J2" t="n">
-        <v>88.45</v>
+        <v>88.84</v>
       </c>
       <c r="K2" t="n">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1825.7</v>
+        <v>1818.62</v>
       </c>
       <c r="M2" t="n">
-        <v>1869.92</v>
+        <v>1863.04</v>
       </c>
       <c r="N2" t="n">
-        <v>1737.24</v>
+        <v>1729.78</v>
       </c>
       <c r="O2" t="n">
-        <v>2051.25</v>
+        <v>2045.16</v>
       </c>
       <c r="P2" t="n">
         <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>52.86</v>
+        <v>52.4</v>
       </c>
       <c r="R2" t="n">
-        <v>2.89</v>
+        <v>2.53</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.26</v>
+        <v>-4.62</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -668,55 +668,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>151.41</v>
+        <v>151.57</v>
       </c>
       <c r="D3" t="n">
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="F3" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="G3" t="n">
-        <v>3.57</v>
+        <v>3.68</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.6</v>
+        <v>-10.41</v>
       </c>
       <c r="I3" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
       </c>
       <c r="J3" t="n">
         <v>3.98</v>
       </c>
       <c r="K3" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="L3" t="n">
-        <v>150.02</v>
+        <v>150.18</v>
       </c>
       <c r="M3" t="n">
-        <v>152.01</v>
+        <v>152.17</v>
       </c>
       <c r="N3" t="n">
-        <v>146.04</v>
+        <v>146.2</v>
       </c>
       <c r="O3" t="n">
-        <v>160.16</v>
+        <v>160.32</v>
       </c>
       <c r="P3" t="n">
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>51.47</v>
+        <v>51.72</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.75</v>
+        <v>-2.65</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -771,25 +771,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>55.56</v>
+        <v>55.38</v>
       </c>
       <c r="D4" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E4" t="n">
-        <v>0.72</v>
+        <v>0.4</v>
       </c>
       <c r="F4" t="n">
-        <v>5.98</v>
+        <v>5.65</v>
       </c>
       <c r="G4" t="n">
-        <v>11.47</v>
+        <v>11.12</v>
       </c>
       <c r="H4" t="n">
-        <v>-6.23</v>
+        <v>-6.48</v>
       </c>
       <c r="I4" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="J4" t="n">
         <v>1.65</v>
@@ -798,28 +798,28 @@
         <v>2.98</v>
       </c>
       <c r="L4" t="n">
-        <v>54.98</v>
+        <v>54.8</v>
       </c>
       <c r="M4" t="n">
-        <v>55.8</v>
+        <v>55.63</v>
       </c>
       <c r="N4" t="n">
-        <v>53.32</v>
+        <v>53.15</v>
       </c>
       <c r="O4" t="n">
-        <v>59.19</v>
+        <v>59.02</v>
       </c>
       <c r="P4" t="n">
         <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>53.57</v>
+        <v>52.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.88</v>
+        <v>-3.18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -870,55 +870,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>418.18</v>
+        <v>416.79</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.71</v>
+        <v>-2.03</v>
       </c>
       <c r="F5" t="n">
-        <v>5.41</v>
+        <v>5.06</v>
       </c>
       <c r="G5" t="n">
-        <v>26.02</v>
+        <v>25.6</v>
       </c>
       <c r="H5" t="n">
-        <v>-6.8</v>
+        <v>-7.07</v>
       </c>
       <c r="I5" t="n">
-        <v>0.59</v>
+        <v>0.83</v>
       </c>
       <c r="J5" t="n">
         <v>15.61</v>
       </c>
       <c r="K5" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="L5" t="n">
-        <v>412.72</v>
+        <v>411.33</v>
       </c>
       <c r="M5" t="n">
-        <v>420.53</v>
+        <v>419.13</v>
       </c>
       <c r="N5" t="n">
-        <v>397.12</v>
+        <v>395.72</v>
       </c>
       <c r="O5" t="n">
-        <v>452.52</v>
+        <v>451.12</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>49.18</v>
+        <v>48.55</v>
       </c>
       <c r="R5" t="n">
-        <v>0.62</v>
+        <v>0.3</v>
       </c>
       <c r="S5" t="n">
-        <v>-4.45</v>
+        <v>-4.77</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -969,55 +969,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>400.75</v>
+        <v>399.8</v>
       </c>
       <c r="D6" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.47</v>
+        <v>-4.7</v>
       </c>
       <c r="F6" t="n">
-        <v>6.84</v>
+        <v>6.58</v>
       </c>
       <c r="G6" t="n">
-        <v>10.34</v>
+        <v>10.08</v>
       </c>
       <c r="H6" t="n">
-        <v>-5.37</v>
+        <v>-5.55</v>
       </c>
       <c r="I6" t="n">
-        <v>0.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>15.59</v>
       </c>
       <c r="K6" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>395.29</v>
+        <v>394.34</v>
       </c>
       <c r="M6" t="n">
-        <v>403.08</v>
+        <v>402.14</v>
       </c>
       <c r="N6" t="n">
-        <v>379.7</v>
+        <v>378.75</v>
       </c>
       <c r="O6" t="n">
-        <v>435.04</v>
+        <v>434.1</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>58.85</v>
+        <v>58.46</v>
       </c>
       <c r="R6" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="S6" t="n">
-        <v>-4.58</v>
+        <v>-4.81</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -1068,55 +1068,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>226.34</v>
+        <v>225.83</v>
       </c>
       <c r="D7" t="n">
         <v>96</v>
       </c>
       <c r="E7" t="n">
-        <v>8.91</v>
+        <v>8.66</v>
       </c>
       <c r="F7" t="n">
-        <v>13.81</v>
+        <v>13.56</v>
       </c>
       <c r="G7" t="n">
-        <v>22.37</v>
+        <v>22.1</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="I7" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="J7" t="n">
         <v>8.109999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="L7" t="n">
-        <v>223.5</v>
+        <v>222.99</v>
       </c>
       <c r="M7" t="n">
-        <v>227.56</v>
+        <v>227.05</v>
       </c>
       <c r="N7" t="n">
-        <v>215.39</v>
+        <v>214.88</v>
       </c>
       <c r="O7" t="n">
-        <v>244.18</v>
+        <v>243.67</v>
       </c>
       <c r="P7" t="n">
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>69.93000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="R7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.66</v>
+        <v>-0.88</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1171,55 +1171,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>436.86</v>
+        <v>436.61</v>
       </c>
       <c r="D8" t="n">
         <v>96</v>
       </c>
       <c r="E8" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="F8" t="n">
-        <v>10.81</v>
+        <v>10.74</v>
       </c>
       <c r="G8" t="n">
-        <v>21.8</v>
+        <v>21.73</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4</v>
+        <v>-1.39</v>
       </c>
       <c r="I8" t="n">
-        <v>0.62</v>
+        <v>0.91</v>
       </c>
       <c r="J8" t="n">
         <v>19.02</v>
       </c>
       <c r="K8" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="L8" t="n">
-        <v>430.2</v>
+        <v>429.95</v>
       </c>
       <c r="M8" t="n">
-        <v>439.71</v>
+        <v>439.46</v>
       </c>
       <c r="N8" t="n">
-        <v>411.19</v>
+        <v>410.94</v>
       </c>
       <c r="O8" t="n">
-        <v>478.7</v>
+        <v>478.45</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>59.34</v>
+        <v>59.28</v>
       </c>
       <c r="R8" t="n">
-        <v>7.36</v>
+        <v>7.31</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.58</v>
+        <v>-2.64</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Volumen bajo; Algo extendida sobre MA20</t>
+          <t>Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
@@ -1274,55 +1274,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1580.99</v>
+        <v>1581.58</v>
       </c>
       <c r="D9" t="n">
         <v>96</v>
       </c>
       <c r="E9" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="F9" t="n">
-        <v>6.93</v>
+        <v>6.97</v>
       </c>
       <c r="G9" t="n">
-        <v>11.6</v>
+        <v>11.64</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.28</v>
+        <v>-5.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8</v>
+        <v>0.96</v>
       </c>
       <c r="J9" t="n">
         <v>62.71</v>
       </c>
       <c r="K9" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="L9" t="n">
-        <v>1559.04</v>
+        <v>1559.63</v>
       </c>
       <c r="M9" t="n">
-        <v>1590.4</v>
+        <v>1590.99</v>
       </c>
       <c r="N9" t="n">
-        <v>1496.33</v>
+        <v>1496.92</v>
       </c>
       <c r="O9" t="n">
-        <v>1718.95</v>
+        <v>1719.54</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>63.62</v>
+        <v>63.66</v>
       </c>
       <c r="R9" t="n">
-        <v>7.81</v>
+        <v>7.84</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.35</v>
+        <v>-1.31</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1368,64 +1368,64 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>297.09</v>
+        <v>201.8</v>
       </c>
       <c r="D10" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.03</v>
+        <v>1.94</v>
       </c>
       <c r="F10" t="n">
-        <v>12.04</v>
+        <v>3.01</v>
       </c>
       <c r="G10" t="n">
-        <v>26.26</v>
+        <v>21.55</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.17</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="J10" t="n">
-        <v>13.84</v>
+        <v>12.22</v>
       </c>
       <c r="K10" t="n">
-        <v>4.66</v>
+        <v>6.06</v>
       </c>
       <c r="L10" t="n">
-        <v>292.25</v>
+        <v>197.52</v>
       </c>
       <c r="M10" t="n">
-        <v>299.17</v>
+        <v>203.63</v>
       </c>
       <c r="N10" t="n">
-        <v>278.41</v>
+        <v>185.3</v>
       </c>
       <c r="O10" t="n">
-        <v>327.54</v>
+        <v>228.69</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>66.93000000000001</v>
+        <v>52.15</v>
       </c>
       <c r="R10" t="n">
-        <v>9.82</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.97</v>
+        <v>-7.63</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1442,7 +1442,11 @@
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1455,76 +1459,76 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RSI algo alto; Volumen bajo; Algo extendida sobre MA20</t>
+          <t>Tendencia larga débil; Débil vs QQQ; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>201.9</v>
+        <v>295.44</v>
       </c>
       <c r="D11" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E11" t="n">
-        <v>1.99</v>
+        <v>-0.58</v>
       </c>
       <c r="F11" t="n">
-        <v>3.07</v>
+        <v>11.42</v>
       </c>
       <c r="G11" t="n">
-        <v>21.61</v>
+        <v>25.56</v>
       </c>
       <c r="H11" t="n">
-        <v>-9.140000000000001</v>
+        <v>-0.71</v>
       </c>
       <c r="I11" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="J11" t="n">
-        <v>12.22</v>
+        <v>13.84</v>
       </c>
       <c r="K11" t="n">
-        <v>6.05</v>
+        <v>4.68</v>
       </c>
       <c r="L11" t="n">
-        <v>197.63</v>
+        <v>290.6</v>
       </c>
       <c r="M11" t="n">
-        <v>203.74</v>
+        <v>297.52</v>
       </c>
       <c r="N11" t="n">
-        <v>185.41</v>
+        <v>276.76</v>
       </c>
       <c r="O11" t="n">
-        <v>228.79</v>
+        <v>325.89</v>
       </c>
       <c r="P11" t="n">
         <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>52.21</v>
+        <v>66.44</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>9.24</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.58</v>
+        <v>-1.52</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1554,12 +1558,12 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
+          <t>Mercado ALCISTA; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Volumen bajo; Débil vs QQQ; Volatilidad alta</t>
+          <t>RSI algo alto; Volumen bajo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
@@ -1575,55 +1579,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>219.97</v>
+        <v>221.21</v>
       </c>
       <c r="D12" t="n">
         <v>80</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.3</v>
+        <v>-6.78</v>
       </c>
       <c r="F12" t="n">
-        <v>38.05</v>
+        <v>38.83</v>
       </c>
       <c r="G12" t="n">
-        <v>73.34999999999999</v>
+        <v>74.33</v>
       </c>
       <c r="H12" t="n">
-        <v>25.84</v>
+        <v>26.7</v>
       </c>
       <c r="I12" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="J12" t="n">
         <v>17.81</v>
       </c>
       <c r="K12" t="n">
-        <v>8.1</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>213.74</v>
+        <v>214.98</v>
       </c>
       <c r="M12" t="n">
-        <v>222.64</v>
+        <v>223.88</v>
       </c>
       <c r="N12" t="n">
-        <v>195.93</v>
+        <v>197.17</v>
       </c>
       <c r="O12" t="n">
-        <v>259.14</v>
+        <v>260.38</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>54.73</v>
+        <v>55.08</v>
       </c>
       <c r="R12" t="n">
-        <v>8.1</v>
+        <v>8.67</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.15</v>
+        <v>-7.64</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1674,55 +1678,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>269.48</v>
+        <v>270.13</v>
       </c>
       <c r="D13" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.01</v>
+        <v>-1.77</v>
       </c>
       <c r="F13" t="n">
-        <v>8.44</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>33.97</v>
+        <v>34.29</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.77</v>
+        <v>-3.43</v>
       </c>
       <c r="I13" t="n">
-        <v>0.57</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
-        <v>7.36</v>
+        <v>7.38</v>
       </c>
       <c r="K13" t="n">
         <v>2.73</v>
       </c>
       <c r="L13" t="n">
-        <v>266.9</v>
+        <v>267.55</v>
       </c>
       <c r="M13" t="n">
-        <v>270.58</v>
+        <v>271.24</v>
       </c>
       <c r="N13" t="n">
-        <v>259.54</v>
+        <v>260.16</v>
       </c>
       <c r="O13" t="n">
-        <v>285.67</v>
+        <v>286.38</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>66.23</v>
+        <v>66.73</v>
       </c>
       <c r="R13" t="n">
-        <v>2.49</v>
+        <v>2.72</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.26</v>
+        <v>-3.03</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1757,7 +1761,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RSI algo alto; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>RSI algo alto; MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -1773,55 +1777,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32.21</v>
+        <v>32</v>
       </c>
       <c r="D14" t="n">
         <v>74</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.07</v>
+        <v>-7.67</v>
       </c>
       <c r="F14" t="n">
-        <v>18.03</v>
+        <v>17.26</v>
       </c>
       <c r="G14" t="n">
-        <v>6.97</v>
+        <v>6.28</v>
       </c>
       <c r="H14" t="n">
-        <v>5.82</v>
+        <v>5.13</v>
       </c>
       <c r="I14" t="n">
-        <v>0.51</v>
+        <v>0.66</v>
       </c>
       <c r="J14" t="n">
         <v>2.29</v>
       </c>
       <c r="K14" t="n">
-        <v>7.12</v>
+        <v>7.17</v>
       </c>
       <c r="L14" t="n">
-        <v>31.41</v>
+        <v>31.2</v>
       </c>
       <c r="M14" t="n">
-        <v>32.55</v>
+        <v>32.34</v>
       </c>
       <c r="N14" t="n">
-        <v>29.11</v>
+        <v>28.9</v>
       </c>
       <c r="O14" t="n">
-        <v>37.26</v>
+        <v>37.05</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>63.53</v>
+        <v>62.87</v>
       </c>
       <c r="R14" t="n">
-        <v>8.630000000000001</v>
+        <v>7.96</v>
       </c>
       <c r="S14" t="n">
-        <v>-11.44</v>
+        <v>-12.02</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1872,55 +1876,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>529.62</v>
+        <v>528.29</v>
       </c>
       <c r="D15" t="n">
         <v>96</v>
       </c>
       <c r="E15" t="n">
-        <v>4.49</v>
+        <v>4.23</v>
       </c>
       <c r="F15" t="n">
-        <v>31.79</v>
+        <v>31.46</v>
       </c>
       <c r="G15" t="n">
-        <v>49.66</v>
+        <v>49.28</v>
       </c>
       <c r="H15" t="n">
-        <v>19.58</v>
+        <v>19.33</v>
       </c>
       <c r="I15" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="J15" t="n">
         <v>19.33</v>
       </c>
       <c r="K15" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="L15" t="n">
-        <v>522.85</v>
+        <v>521.52</v>
       </c>
       <c r="M15" t="n">
-        <v>532.52</v>
+        <v>531.1900000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>503.52</v>
+        <v>502.19</v>
       </c>
       <c r="O15" t="n">
-        <v>572.16</v>
+        <v>570.83</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>71.68000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="R15" t="n">
-        <v>13.8</v>
+        <v>13.53</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.77</v>
+        <v>-1.02</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1975,55 +1979,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>402.29</v>
+        <v>402.62</v>
       </c>
       <c r="D16" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E16" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="F16" t="n">
-        <v>19.33</v>
+        <v>19.43</v>
       </c>
       <c r="G16" t="n">
-        <v>33.29</v>
+        <v>33.4</v>
       </c>
       <c r="H16" t="n">
-        <v>7.12</v>
+        <v>7.3</v>
       </c>
       <c r="I16" t="n">
-        <v>0.71</v>
+        <v>0.98</v>
       </c>
       <c r="J16" t="n">
         <v>11.45</v>
       </c>
       <c r="K16" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="L16" t="n">
-        <v>398.28</v>
+        <v>398.61</v>
       </c>
       <c r="M16" t="n">
-        <v>404.01</v>
+        <v>404.34</v>
       </c>
       <c r="N16" t="n">
-        <v>386.83</v>
+        <v>387.16</v>
       </c>
       <c r="O16" t="n">
-        <v>427.49</v>
+        <v>427.82</v>
       </c>
       <c r="P16" t="n">
         <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>82.88</v>
+        <v>82.94</v>
       </c>
       <c r="R16" t="n">
-        <v>9.66</v>
+        <v>9.74</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.35</v>
+        <v>-0.27</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2062,7 +2066,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo; Algo extendida sobre MA20</t>
+          <t>RSI sobrecomprado; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
@@ -2078,25 +2082,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>298.77</v>
+        <v>298.87</v>
       </c>
       <c r="D17" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E17" t="n">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="F17" t="n">
-        <v>12.24</v>
+        <v>12.28</v>
       </c>
       <c r="G17" t="n">
-        <v>13.33</v>
+        <v>13.36</v>
       </c>
       <c r="H17" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.71</v>
+        <v>0.93</v>
       </c>
       <c r="J17" t="n">
         <v>6.52</v>
@@ -2105,28 +2109,28 @@
         <v>2.18</v>
       </c>
       <c r="L17" t="n">
-        <v>296.49</v>
+        <v>296.59</v>
       </c>
       <c r="M17" t="n">
-        <v>299.75</v>
+        <v>299.85</v>
       </c>
       <c r="N17" t="n">
-        <v>289.97</v>
+        <v>290.07</v>
       </c>
       <c r="O17" t="n">
-        <v>313.11</v>
+        <v>313.21</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>77.94</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>7.44</v>
+        <v>7.47</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.71</v>
+        <v>-0.68</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2165,7 +2169,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo; Algo extendida sobre MA20</t>
+          <t>RSI sobrecomprado; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
@@ -2181,25 +2185,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>715.22</v>
+        <v>714.71</v>
       </c>
       <c r="D18" t="n">
         <v>90</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="F18" t="n">
-        <v>12.21</v>
+        <v>12.13</v>
       </c>
       <c r="G18" t="n">
-        <v>19.1</v>
+        <v>19.01</v>
       </c>
       <c r="H18" t="n">
         <v>-0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J18" t="n">
         <v>10.28</v>
@@ -2208,28 +2212,28 @@
         <v>1.44</v>
       </c>
       <c r="L18" t="n">
-        <v>711.62</v>
+        <v>711.11</v>
       </c>
       <c r="M18" t="n">
-        <v>716.76</v>
+        <v>716.25</v>
       </c>
       <c r="N18" t="n">
-        <v>701.34</v>
+        <v>700.83</v>
       </c>
       <c r="O18" t="n">
-        <v>737.83</v>
+        <v>737.3200000000001</v>
       </c>
       <c r="P18" t="n">
         <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>84.13</v>
+        <v>84.05</v>
       </c>
       <c r="R18" t="n">
-        <v>6.21</v>
+        <v>6.14</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2</v>
+        <v>-0.27</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2280,25 +2284,25 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>743.14</v>
+        <v>742.3099999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E19" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="F19" t="n">
-        <v>6.17</v>
+        <v>6.05</v>
       </c>
       <c r="G19" t="n">
-        <v>9.130000000000001</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.04</v>
+        <v>-6.08</v>
       </c>
       <c r="I19" t="n">
-        <v>0.59</v>
+        <v>0.77</v>
       </c>
       <c r="J19" t="n">
         <v>6.62</v>
@@ -2307,28 +2311,28 @@
         <v>0.89</v>
       </c>
       <c r="L19" t="n">
-        <v>740.8200000000001</v>
+        <v>739.99</v>
       </c>
       <c r="M19" t="n">
-        <v>744.13</v>
+        <v>743.3</v>
       </c>
       <c r="N19" t="n">
-        <v>734.2</v>
+        <v>733.37</v>
       </c>
       <c r="O19" t="n">
-        <v>757.72</v>
+        <v>756.88</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>82.19</v>
+        <v>81.91</v>
       </c>
       <c r="R19" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1</v>
+        <v>-0.21</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2363,7 +2367,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo; Débil vs QQQ</t>
+          <t>RSI sobrecomprado; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -2379,55 +2383,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>54.72</v>
+        <v>55.26</v>
       </c>
       <c r="D20" t="n">
         <v>77</v>
       </c>
       <c r="E20" t="n">
-        <v>4.1</v>
+        <v>5.12</v>
       </c>
       <c r="F20" t="n">
-        <v>26.53</v>
+        <v>27.77</v>
       </c>
       <c r="G20" t="n">
-        <v>64.93000000000001</v>
+        <v>66.55</v>
       </c>
       <c r="H20" t="n">
-        <v>14.32</v>
+        <v>15.64</v>
       </c>
       <c r="I20" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="J20" t="n">
         <v>4.41</v>
       </c>
       <c r="K20" t="n">
-        <v>8.050000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="L20" t="n">
-        <v>53.18</v>
+        <v>53.72</v>
       </c>
       <c r="M20" t="n">
-        <v>55.39</v>
+        <v>55.92</v>
       </c>
       <c r="N20" t="n">
-        <v>48.78</v>
+        <v>49.31</v>
       </c>
       <c r="O20" t="n">
-        <v>64.42</v>
+        <v>64.95</v>
       </c>
       <c r="P20" t="n">
         <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>67.64</v>
+        <v>68.81</v>
       </c>
       <c r="R20" t="n">
-        <v>15.2</v>
+        <v>16.26</v>
       </c>
       <c r="S20" t="n">
-        <v>-7.48</v>
+        <v>-6.58</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2469,64 +2473,64 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>806.02</v>
+        <v>445.5</v>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E21" t="n">
-        <v>20.92</v>
+        <v>5.72</v>
       </c>
       <c r="F21" t="n">
-        <v>76.67</v>
+        <v>72.59</v>
       </c>
       <c r="G21" t="n">
-        <v>101.7</v>
+        <v>119.37</v>
       </c>
       <c r="H21" t="n">
-        <v>64.45999999999999</v>
+        <v>60.46</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.59</v>
       </c>
       <c r="J21" t="n">
-        <v>51.05</v>
+        <v>29.48</v>
       </c>
       <c r="K21" t="n">
-        <v>6.33</v>
+        <v>6.62</v>
       </c>
       <c r="L21" t="n">
-        <v>788.15</v>
+        <v>435.18</v>
       </c>
       <c r="M21" t="n">
-        <v>813.6799999999999</v>
+        <v>449.92</v>
       </c>
       <c r="N21" t="n">
-        <v>737.1</v>
+        <v>405.7</v>
       </c>
       <c r="O21" t="n">
-        <v>918.34</v>
+        <v>510.36</v>
       </c>
       <c r="P21" t="n">
         <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>84.88</v>
+        <v>75.05</v>
       </c>
       <c r="R21" t="n">
-        <v>39.85</v>
+        <v>25.19</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.55</v>
+        <v>-5.06</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2561,7 +2565,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
+          <t>RSI sobrecomprado; Volumen bajo; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -2577,55 +2581,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>126.45</v>
+        <v>124.15</v>
       </c>
       <c r="D22" t="n">
         <v>72</v>
       </c>
       <c r="E22" t="n">
-        <v>49.38</v>
+        <v>46.66</v>
       </c>
       <c r="F22" t="n">
-        <v>71.81</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>80.93000000000001</v>
+        <v>77.64</v>
       </c>
       <c r="H22" t="n">
-        <v>59.6</v>
+        <v>56.55</v>
       </c>
       <c r="I22" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="J22" t="n">
         <v>8.94</v>
       </c>
       <c r="K22" t="n">
-        <v>7.07</v>
+        <v>7.2</v>
       </c>
       <c r="L22" t="n">
-        <v>123.32</v>
+        <v>121.02</v>
       </c>
       <c r="M22" t="n">
-        <v>127.79</v>
+        <v>125.49</v>
       </c>
       <c r="N22" t="n">
-        <v>114.38</v>
+        <v>112.08</v>
       </c>
       <c r="O22" t="n">
-        <v>146.12</v>
+        <v>143.82</v>
       </c>
       <c r="P22" t="n">
         <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>74.66</v>
+        <v>73.95</v>
       </c>
       <c r="R22" t="n">
-        <v>41.56</v>
+        <v>39.17</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.61</v>
+        <v>-2.41</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2676,55 +2680,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>121.07</v>
+        <v>120.29</v>
       </c>
       <c r="D23" t="n">
         <v>70</v>
       </c>
       <c r="E23" t="n">
-        <v>7.13</v>
+        <v>6.44</v>
       </c>
       <c r="F23" t="n">
-        <v>86.43000000000001</v>
+        <v>85.23</v>
       </c>
       <c r="G23" t="n">
-        <v>162.17</v>
+        <v>160.48</v>
       </c>
       <c r="H23" t="n">
-        <v>74.22</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="J23" t="n">
         <v>9.550000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>7.89</v>
+        <v>7.94</v>
       </c>
       <c r="L23" t="n">
-        <v>117.73</v>
+        <v>116.95</v>
       </c>
       <c r="M23" t="n">
-        <v>122.5</v>
+        <v>121.72</v>
       </c>
       <c r="N23" t="n">
-        <v>108.18</v>
+        <v>107.4</v>
       </c>
       <c r="O23" t="n">
-        <v>142.07</v>
+        <v>141.29</v>
       </c>
       <c r="P23" t="n">
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>80.89</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="R23" t="n">
-        <v>29.87</v>
+        <v>29.09</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2766,64 +2770,64 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>447.89</v>
+        <v>803.63</v>
       </c>
       <c r="D24" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E24" t="n">
-        <v>6.29</v>
+        <v>20.56</v>
       </c>
       <c r="F24" t="n">
-        <v>73.52</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>120.55</v>
+        <v>101.1</v>
       </c>
       <c r="H24" t="n">
-        <v>61.31</v>
+        <v>64.02</v>
       </c>
       <c r="I24" t="n">
-        <v>0.47</v>
+        <v>1.16</v>
       </c>
       <c r="J24" t="n">
-        <v>29.48</v>
+        <v>51.05</v>
       </c>
       <c r="K24" t="n">
-        <v>6.58</v>
+        <v>6.35</v>
       </c>
       <c r="L24" t="n">
-        <v>437.57</v>
+        <v>785.76</v>
       </c>
       <c r="M24" t="n">
-        <v>452.31</v>
+        <v>811.29</v>
       </c>
       <c r="N24" t="n">
-        <v>408.09</v>
+        <v>734.71</v>
       </c>
       <c r="O24" t="n">
-        <v>512.75</v>
+        <v>915.95</v>
       </c>
       <c r="P24" t="n">
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>75.69</v>
+        <v>84.8</v>
       </c>
       <c r="R24" t="n">
-        <v>25.82</v>
+        <v>39.46</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.55</v>
+        <v>-1.84</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2858,7 +2862,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo; Momentum 5D extendido; Muy alejada de MA20; Volatilidad alta</t>
+          <t>RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -2874,25 +2878,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>444.98</v>
+        <v>445.27</v>
       </c>
       <c r="D25" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E25" t="n">
-        <v>11.6</v>
+        <v>11.67</v>
       </c>
       <c r="F25" t="n">
-        <v>13.53</v>
+        <v>13.6</v>
       </c>
       <c r="G25" t="n">
-        <v>8.359999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="H25" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="I25" t="n">
-        <v>0.92</v>
+        <v>1.03</v>
       </c>
       <c r="J25" t="n">
         <v>17.05</v>
@@ -2901,28 +2905,28 @@
         <v>3.83</v>
       </c>
       <c r="L25" t="n">
-        <v>439.01</v>
+        <v>439.3</v>
       </c>
       <c r="M25" t="n">
-        <v>447.53</v>
+        <v>447.83</v>
       </c>
       <c r="N25" t="n">
-        <v>421.96</v>
+        <v>422.25</v>
       </c>
       <c r="O25" t="n">
-        <v>482.49</v>
+        <v>482.78</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>81.7</v>
+        <v>81.75</v>
       </c>
       <c r="R25" t="n">
-        <v>11.94</v>
+        <v>12.01</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.86</v>
+        <v>-1.79</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2957,7 +2961,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI sobrecomprado; Subida muy extendida 5D; Algo extendida sobre MA20</t>
+          <t>Tendencia larga débil; RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20</t>
         </is>
       </c>
     </row>
@@ -2973,25 +2977,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>56.1</v>
+        <v>56.18</v>
       </c>
       <c r="D26" t="n">
         <v>56</v>
       </c>
       <c r="E26" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="F26" t="n">
-        <v>0.49</v>
+        <v>0.63</v>
       </c>
       <c r="G26" t="n">
-        <v>22.71</v>
+        <v>22.87</v>
       </c>
       <c r="H26" t="n">
-        <v>-11.72</v>
+        <v>-11.5</v>
       </c>
       <c r="I26" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="J26" t="n">
         <v>1.85</v>
@@ -3000,28 +3004,28 @@
         <v>3.3</v>
       </c>
       <c r="L26" t="n">
-        <v>55.46</v>
+        <v>55.53</v>
       </c>
       <c r="M26" t="n">
-        <v>56.38</v>
+        <v>56.46</v>
       </c>
       <c r="N26" t="n">
-        <v>53.6</v>
+        <v>53.68</v>
       </c>
       <c r="O26" t="n">
-        <v>60.18</v>
+        <v>60.26</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>45.36</v>
+        <v>45.55</v>
       </c>
       <c r="R26" t="n">
-        <v>-1.45</v>
+        <v>-1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.71</v>
+        <v>-7.58</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3072,25 +3076,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>185.46</v>
+        <v>186</v>
       </c>
       <c r="D27" t="n">
         <v>48</v>
       </c>
       <c r="E27" t="n">
-        <v>0.16</v>
+        <v>0.45</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3</v>
+        <v>0.59</v>
       </c>
       <c r="G27" t="n">
-        <v>2.72</v>
+        <v>3.02</v>
       </c>
       <c r="H27" t="n">
-        <v>-11.91</v>
+        <v>-11.54</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="J27" t="n">
         <v>4.46</v>
@@ -3099,28 +3103,28 @@
         <v>2.4</v>
       </c>
       <c r="L27" t="n">
-        <v>183.9</v>
+        <v>184.44</v>
       </c>
       <c r="M27" t="n">
-        <v>186.13</v>
+        <v>186.67</v>
       </c>
       <c r="N27" t="n">
-        <v>179.44</v>
+        <v>179.98</v>
       </c>
       <c r="O27" t="n">
-        <v>195.27</v>
+        <v>195.81</v>
       </c>
       <c r="P27" t="n">
         <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>46.64</v>
+        <v>47.46</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.83</v>
+        <v>-0.55</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.47</v>
+        <v>-4.19</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3171,55 +3175,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="D28" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E28" t="n">
-        <v>-9.59</v>
+        <v>-9.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-8.83</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>-16.54</v>
+        <v>-16.83</v>
       </c>
       <c r="H28" t="n">
-        <v>-21.04</v>
+        <v>-21.27</v>
       </c>
       <c r="I28" t="n">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
       <c r="J28" t="n">
         <v>0.43</v>
       </c>
       <c r="K28" t="n">
-        <v>4.91</v>
+        <v>4.93</v>
       </c>
       <c r="L28" t="n">
-        <v>8.529999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="M28" t="n">
-        <v>8.74</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>8.1</v>
+        <v>8.07</v>
       </c>
       <c r="O28" t="n">
-        <v>9.619999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="P28" t="n">
         <v>1.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>52.46</v>
+        <v>51.92</v>
       </c>
       <c r="R28" t="n">
-        <v>-5.11</v>
+        <v>-5.42</v>
       </c>
       <c r="S28" t="n">
-        <v>-12.68</v>
+        <v>-12.98</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3254,14 +3258,14 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3270,55 +3274,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>404.62</v>
+        <v>616.63</v>
       </c>
       <c r="D29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.26</v>
+        <v>0.61</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.6</v>
+        <v>-8.18</v>
       </c>
       <c r="G29" t="n">
-        <v>2.19</v>
+        <v>-3.46</v>
       </c>
       <c r="H29" t="n">
-        <v>-13.81</v>
+        <v>-20.31</v>
       </c>
       <c r="I29" t="n">
-        <v>0.51</v>
+        <v>0.91</v>
       </c>
       <c r="J29" t="n">
-        <v>10.66</v>
+        <v>18.55</v>
       </c>
       <c r="K29" t="n">
-        <v>2.64</v>
+        <v>3.01</v>
       </c>
       <c r="L29" t="n">
-        <v>400.89</v>
+        <v>610.14</v>
       </c>
       <c r="M29" t="n">
-        <v>406.22</v>
+        <v>619.41</v>
       </c>
       <c r="N29" t="n">
-        <v>390.23</v>
+        <v>591.59</v>
       </c>
       <c r="O29" t="n">
-        <v>428.08</v>
+        <v>657.4400000000001</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>42.08</v>
+        <v>35.24</v>
       </c>
       <c r="R29" t="n">
-        <v>-3.19</v>
+        <v>-3.85</v>
       </c>
       <c r="S29" t="n">
-        <v>-6.7</v>
+        <v>-10.83</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3348,76 +3352,76 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>76.88</v>
+        <v>45.23</v>
       </c>
       <c r="D30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.75</v>
+        <v>-2.25</v>
       </c>
       <c r="F30" t="n">
-        <v>-11.96</v>
+        <v>-8.76</v>
       </c>
       <c r="G30" t="n">
-        <v>1.91</v>
+        <v>11.17</v>
       </c>
       <c r="H30" t="n">
-        <v>-24.17</v>
+        <v>-20.89</v>
       </c>
       <c r="I30" t="n">
-        <v>0.39</v>
+        <v>1.02</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>1.54</v>
       </c>
       <c r="K30" t="n">
-        <v>5.2</v>
+        <v>3.41</v>
       </c>
       <c r="L30" t="n">
-        <v>75.48</v>
+        <v>44.69</v>
       </c>
       <c r="M30" t="n">
-        <v>77.48</v>
+        <v>45.46</v>
       </c>
       <c r="N30" t="n">
-        <v>71.48999999999999</v>
+        <v>43.15</v>
       </c>
       <c r="O30" t="n">
-        <v>85.67</v>
+        <v>48.63</v>
       </c>
       <c r="P30" t="n">
         <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>40.12</v>
+        <v>27.22</v>
       </c>
       <c r="R30" t="n">
-        <v>-4.95</v>
+        <v>-7.3</v>
       </c>
       <c r="S30" t="n">
-        <v>-17.62</v>
+        <v>-13.52</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3447,76 +3451,76 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>45.6</v>
+        <v>405.21</v>
       </c>
       <c r="D31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.44</v>
+        <v>-2.11</v>
       </c>
       <c r="F31" t="n">
-        <v>-8</v>
+        <v>-1.46</v>
       </c>
       <c r="G31" t="n">
-        <v>12.08</v>
+        <v>2.34</v>
       </c>
       <c r="H31" t="n">
-        <v>-20.21</v>
+        <v>-13.59</v>
       </c>
       <c r="I31" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
-        <v>1.54</v>
+        <v>10.66</v>
       </c>
       <c r="K31" t="n">
-        <v>3.39</v>
+        <v>2.63</v>
       </c>
       <c r="L31" t="n">
-        <v>45.06</v>
+        <v>401.48</v>
       </c>
       <c r="M31" t="n">
-        <v>45.83</v>
+        <v>406.81</v>
       </c>
       <c r="N31" t="n">
-        <v>43.52</v>
+        <v>390.82</v>
       </c>
       <c r="O31" t="n">
-        <v>49</v>
+        <v>428.67</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>28.99</v>
+        <v>42.43</v>
       </c>
       <c r="R31" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="S31" t="n">
         <v>-6.57</v>
-      </c>
-      <c r="S31" t="n">
-        <v>-12.81</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3546,76 +3550,76 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>616.5599999999999</v>
+        <v>76.75</v>
       </c>
       <c r="D32" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6</v>
+        <v>-2.91</v>
       </c>
       <c r="F32" t="n">
-        <v>-8.19</v>
+        <v>-12.1</v>
       </c>
       <c r="G32" t="n">
-        <v>-3.47</v>
+        <v>1.74</v>
       </c>
       <c r="H32" t="n">
-        <v>-20.4</v>
+        <v>-24.23</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.47</v>
       </c>
       <c r="J32" t="n">
-        <v>18.55</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>3.01</v>
+        <v>5.21</v>
       </c>
       <c r="L32" t="n">
-        <v>610.0700000000001</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>619.34</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>591.52</v>
+        <v>71.36</v>
       </c>
       <c r="O32" t="n">
-        <v>657.37</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="P32" t="n">
         <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>35.21</v>
+        <v>39.96</v>
       </c>
       <c r="R32" t="n">
-        <v>-3.86</v>
+        <v>-5.1</v>
       </c>
       <c r="S32" t="n">
-        <v>-10.84</v>
+        <v>-17.76</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3645,12 +3649,12 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -3666,55 +3670,55 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>15.38</v>
+        <v>15.31</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>-5.64</v>
+        <v>-6.07</v>
       </c>
       <c r="F33" t="n">
-        <v>-18.15</v>
+        <v>-18.52</v>
       </c>
       <c r="G33" t="n">
-        <v>-21.17</v>
+        <v>-21.53</v>
       </c>
       <c r="H33" t="n">
-        <v>-30.36</v>
+        <v>-30.65</v>
       </c>
       <c r="I33" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="J33" t="n">
         <v>0.8</v>
       </c>
       <c r="K33" t="n">
-        <v>5.18</v>
+        <v>5.2</v>
       </c>
       <c r="L33" t="n">
-        <v>15.1</v>
+        <v>15.03</v>
       </c>
       <c r="M33" t="n">
-        <v>15.5</v>
+        <v>15.43</v>
       </c>
       <c r="N33" t="n">
-        <v>14.31</v>
+        <v>14.24</v>
       </c>
       <c r="O33" t="n">
-        <v>17.13</v>
+        <v>17.06</v>
       </c>
       <c r="P33" t="n">
         <v>1.64</v>
       </c>
       <c r="Q33" t="n">
-        <v>29.61</v>
+        <v>29.33</v>
       </c>
       <c r="R33" t="n">
-        <v>-10.99</v>
+        <v>-11.38</v>
       </c>
       <c r="S33" t="n">
-        <v>-23.6</v>
+        <v>-23.94</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3749,7 +3753,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Momentum negativo</t>
         </is>
       </c>
     </row>
@@ -3765,25 +3769,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>130.07</v>
+        <v>130.05</v>
       </c>
       <c r="D34" t="n">
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.78</v>
+        <v>-2.8</v>
       </c>
       <c r="F34" t="n">
-        <v>-8.5</v>
+        <v>-8.51</v>
       </c>
       <c r="G34" t="n">
-        <v>-2.22</v>
+        <v>-2.23</v>
       </c>
       <c r="H34" t="n">
-        <v>-20.71</v>
+        <v>-20.64</v>
       </c>
       <c r="I34" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="J34" t="n">
         <v>5.73</v>
@@ -3792,28 +3796,28 @@
         <v>4.4</v>
       </c>
       <c r="L34" t="n">
-        <v>128.07</v>
+        <v>128.05</v>
       </c>
       <c r="M34" t="n">
-        <v>130.93</v>
+        <v>130.91</v>
       </c>
       <c r="N34" t="n">
-        <v>122.34</v>
+        <v>122.32</v>
       </c>
       <c r="O34" t="n">
-        <v>142.67</v>
+        <v>142.65</v>
       </c>
       <c r="P34" t="n">
         <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>35.14</v>
+        <v>35.12</v>
       </c>
       <c r="R34" t="n">
-        <v>-7.66</v>
+        <v>-7.68</v>
       </c>
       <c r="S34" t="n">
-        <v>-14.81</v>
+        <v>-14.82</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3864,40 +3868,40 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8.41</v>
+        <v>8.42</v>
       </c>
       <c r="D35" t="n">
         <v>33</v>
       </c>
       <c r="E35" t="n">
-        <v>-10.19</v>
+        <v>-10.14</v>
       </c>
       <c r="F35" t="n">
-        <v>7.2</v>
+        <v>7.26</v>
       </c>
       <c r="G35" t="n">
-        <v>14.96</v>
+        <v>15.03</v>
       </c>
       <c r="H35" t="n">
-        <v>-5.01</v>
+        <v>-4.87</v>
       </c>
       <c r="I35" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="J35" t="n">
         <v>0.66</v>
       </c>
       <c r="K35" t="n">
-        <v>7.86</v>
+        <v>7.85</v>
       </c>
       <c r="L35" t="n">
-        <v>8.18</v>
+        <v>8.19</v>
       </c>
       <c r="M35" t="n">
-        <v>8.51</v>
+        <v>8.52</v>
       </c>
       <c r="N35" t="n">
-        <v>7.52</v>
+        <v>7.53</v>
       </c>
       <c r="O35" t="n">
         <v>9.869999999999999</v>
@@ -3906,13 +3910,13 @@
         <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>55.37</v>
+        <v>55.42</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.44</v>
+        <v>-0.38</v>
       </c>
       <c r="S35" t="n">
-        <v>-16.23</v>
+        <v>-16.18</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3963,55 +3967,55 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>26.85</v>
+        <v>26.99</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>-6.44</v>
+        <v>-5.96</v>
       </c>
       <c r="F36" t="n">
-        <v>-19.51</v>
+        <v>-19.09</v>
       </c>
       <c r="G36" t="n">
-        <v>-16.01</v>
+        <v>-15.58</v>
       </c>
       <c r="H36" t="n">
-        <v>-31.72</v>
+        <v>-31.22</v>
       </c>
       <c r="I36" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="J36" t="n">
         <v>1.68</v>
       </c>
       <c r="K36" t="n">
-        <v>6.27</v>
+        <v>6.24</v>
       </c>
       <c r="L36" t="n">
-        <v>26.26</v>
+        <v>26.4</v>
       </c>
       <c r="M36" t="n">
-        <v>27.1</v>
+        <v>27.24</v>
       </c>
       <c r="N36" t="n">
-        <v>24.58</v>
+        <v>24.72</v>
       </c>
       <c r="O36" t="n">
-        <v>30.56</v>
+        <v>30.69</v>
       </c>
       <c r="P36" t="n">
         <v>1.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>25.99</v>
+        <v>26.28</v>
       </c>
       <c r="R36" t="n">
-        <v>-14.87</v>
+        <v>-14.45</v>
       </c>
       <c r="S36" t="n">
-        <v>-24.99</v>
+        <v>-24.61</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4046,7 +4050,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Momentum negativo</t>
         </is>
       </c>
     </row>
@@ -4062,55 +4066,55 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>213.55</v>
+        <v>213.17</v>
       </c>
       <c r="D37" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E37" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="F37" t="n">
-        <v>60.5</v>
+        <v>60.22</v>
       </c>
       <c r="G37" t="n">
-        <v>50.68</v>
+        <v>50.42</v>
       </c>
       <c r="H37" t="n">
-        <v>48.29</v>
+        <v>48.09</v>
       </c>
       <c r="I37" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="J37" t="n">
         <v>19.38</v>
       </c>
       <c r="K37" t="n">
-        <v>9.07</v>
+        <v>9.09</v>
       </c>
       <c r="L37" t="n">
-        <v>206.77</v>
+        <v>206.39</v>
       </c>
       <c r="M37" t="n">
-        <v>216.46</v>
+        <v>216.08</v>
       </c>
       <c r="N37" t="n">
-        <v>187.39</v>
+        <v>187.01</v>
       </c>
       <c r="O37" t="n">
-        <v>256.18</v>
+        <v>255.8</v>
       </c>
       <c r="P37" t="n">
         <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>75.36</v>
+        <v>75.3</v>
       </c>
       <c r="R37" t="n">
-        <v>25.4</v>
+        <v>25.19</v>
       </c>
       <c r="S37" t="n">
-        <v>-13.86</v>
+        <v>-14.01</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4145,7 +4149,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI sobrecomprado; Volumen bajo; Subida muy extendida 5D; Muy alejada de MA20</t>
+          <t>Tendencia larga débil; RSI sobrecomprado; Subida muy extendida 5D; Muy alejada de MA20; Volatilidad muy alta</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -987,7 +987,7 @@
         <v>-5.55</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="J6" t="n">
         <v>15.59</v>
@@ -1395,7 +1395,7 @@
         <v>-9.119999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="J10" t="n">
         <v>12.22</v>
@@ -1696,7 +1696,7 @@
         <v>-3.43</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>7.38</v>
@@ -2599,7 +2599,7 @@
         <v>56.55</v>
       </c>
       <c r="I22" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="J22" t="n">
         <v>8.94</v>
@@ -3265,7 +3265,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3274,55 +3274,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>616.63</v>
+        <v>405.21</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E29" t="n">
-        <v>0.61</v>
+        <v>-2.11</v>
       </c>
       <c r="F29" t="n">
-        <v>-8.18</v>
+        <v>-1.46</v>
       </c>
       <c r="G29" t="n">
-        <v>-3.46</v>
+        <v>2.34</v>
       </c>
       <c r="H29" t="n">
-        <v>-20.31</v>
+        <v>-13.59</v>
       </c>
       <c r="I29" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="J29" t="n">
-        <v>18.55</v>
+        <v>10.66</v>
       </c>
       <c r="K29" t="n">
-        <v>3.01</v>
+        <v>2.63</v>
       </c>
       <c r="L29" t="n">
-        <v>610.14</v>
+        <v>401.48</v>
       </c>
       <c r="M29" t="n">
-        <v>619.41</v>
+        <v>406.81</v>
       </c>
       <c r="N29" t="n">
-        <v>591.59</v>
+        <v>390.82</v>
       </c>
       <c r="O29" t="n">
-        <v>657.4400000000001</v>
+        <v>428.67</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>35.24</v>
+        <v>42.43</v>
       </c>
       <c r="R29" t="n">
-        <v>-3.85</v>
+        <v>-3.06</v>
       </c>
       <c r="S29" t="n">
-        <v>-10.83</v>
+        <v>-6.57</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3352,76 +3352,76 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Débil vs QQQ; Lejos del máximo 20D</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>45.23</v>
+        <v>616.63</v>
       </c>
       <c r="D30" t="n">
         <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.25</v>
+        <v>0.61</v>
       </c>
       <c r="F30" t="n">
-        <v>-8.76</v>
+        <v>-8.18</v>
       </c>
       <c r="G30" t="n">
-        <v>11.17</v>
+        <v>-3.46</v>
       </c>
       <c r="H30" t="n">
-        <v>-20.89</v>
+        <v>-20.31</v>
       </c>
       <c r="I30" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="J30" t="n">
-        <v>1.54</v>
+        <v>18.55</v>
       </c>
       <c r="K30" t="n">
-        <v>3.41</v>
+        <v>3.01</v>
       </c>
       <c r="L30" t="n">
-        <v>44.69</v>
+        <v>610.14</v>
       </c>
       <c r="M30" t="n">
-        <v>45.46</v>
+        <v>619.41</v>
       </c>
       <c r="N30" t="n">
-        <v>43.15</v>
+        <v>591.59</v>
       </c>
       <c r="O30" t="n">
-        <v>48.63</v>
+        <v>657.4400000000001</v>
       </c>
       <c r="P30" t="n">
         <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>27.22</v>
+        <v>35.24</v>
       </c>
       <c r="R30" t="n">
-        <v>-7.3</v>
+        <v>-3.85</v>
       </c>
       <c r="S30" t="n">
-        <v>-13.52</v>
+        <v>-10.83</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3463,64 +3463,64 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>405.21</v>
+        <v>45.23</v>
       </c>
       <c r="D31" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.11</v>
+        <v>-2.25</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.46</v>
+        <v>-8.76</v>
       </c>
       <c r="G31" t="n">
-        <v>2.34</v>
+        <v>11.17</v>
       </c>
       <c r="H31" t="n">
-        <v>-13.59</v>
+        <v>-20.89</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>1.02</v>
       </c>
       <c r="J31" t="n">
-        <v>10.66</v>
+        <v>1.54</v>
       </c>
       <c r="K31" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="L31" t="n">
-        <v>401.48</v>
+        <v>44.69</v>
       </c>
       <c r="M31" t="n">
-        <v>406.81</v>
+        <v>45.46</v>
       </c>
       <c r="N31" t="n">
-        <v>390.82</v>
+        <v>43.15</v>
       </c>
       <c r="O31" t="n">
-        <v>428.67</v>
+        <v>48.63</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>42.43</v>
+        <v>27.22</v>
       </c>
       <c r="R31" t="n">
-        <v>-3.06</v>
+        <v>-7.3</v>
       </c>
       <c r="S31" t="n">
-        <v>-6.57</v>
+        <v>-13.52</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3550,12 +3550,12 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; MA20 sobre MA50</t>
+          <t>Mercado ALCISTA; MA20 sobre MA50; Histograma MACD mejora</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
         <v>48.09</v>
       </c>
       <c r="I37" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J37" t="n">
         <v>19.38</v>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -575,25 +575,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41.22</v>
+        <v>41.27</v>
       </c>
       <c r="D2" t="n">
         <v>96</v>
       </c>
       <c r="E2" t="n">
-        <v>3.49</v>
+        <v>3.62</v>
       </c>
       <c r="F2" t="n">
-        <v>10.96</v>
+        <v>11.09</v>
       </c>
       <c r="G2" t="n">
-        <v>17.1</v>
+        <v>17.25</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="I2" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="J2" t="n">
         <v>1.08</v>
@@ -602,28 +602,28 @@
         <v>2.63</v>
       </c>
       <c r="L2" t="n">
-        <v>40.84</v>
+        <v>40.89</v>
       </c>
       <c r="M2" t="n">
-        <v>41.38</v>
+        <v>41.43</v>
       </c>
       <c r="N2" t="n">
-        <v>39.76</v>
+        <v>39.81</v>
       </c>
       <c r="O2" t="n">
-        <v>43.61</v>
+        <v>43.66</v>
       </c>
       <c r="P2" t="n">
         <v>1.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>55.68</v>
+        <v>55.97</v>
       </c>
       <c r="R2" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.92</v>
+        <v>-2.8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>XLE 7.15% · CL=F 20.35%</t>
+          <t>XLE 7.28% · CL=F 20.52%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.15% · CL=F 20.35%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.28% · CL=F 20.52%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -688,25 +688,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>59.01</v>
+        <v>59.03</v>
       </c>
       <c r="D3" t="n">
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>5.94</v>
+        <v>5.98</v>
       </c>
       <c r="F3" t="n">
-        <v>7.25</v>
+        <v>7.29</v>
       </c>
       <c r="G3" t="n">
-        <v>7.64</v>
+        <v>7.68</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.21</v>
+        <v>-2.13</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="J3" t="n">
         <v>1.32</v>
@@ -715,28 +715,28 @@
         <v>2.23</v>
       </c>
       <c r="L3" t="n">
-        <v>58.55</v>
+        <v>58.57</v>
       </c>
       <c r="M3" t="n">
-        <v>59.21</v>
+        <v>59.23</v>
       </c>
       <c r="N3" t="n">
-        <v>57.23</v>
+        <v>57.25</v>
       </c>
       <c r="O3" t="n">
-        <v>61.9</v>
+        <v>61.92</v>
       </c>
       <c r="P3" t="n">
         <v>1.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>59.88</v>
+        <v>59.95</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.39</v>
+        <v>-1.35</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>XLE 7.15% · CL=F 20.35%</t>
+          <t>XLE 7.28% · CL=F 20.52%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.15% · CL=F 20.35%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.28% · CL=F 20.52%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -801,25 +801,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>55.39</v>
+        <v>55.5</v>
       </c>
       <c r="D4" t="n">
         <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>3.98</v>
+        <v>4.19</v>
       </c>
       <c r="F4" t="n">
-        <v>5.18</v>
+        <v>5.39</v>
       </c>
       <c r="G4" t="n">
-        <v>7.47</v>
+        <v>7.68</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.28</v>
+        <v>-4.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="J4" t="n">
         <v>1.44</v>
@@ -828,28 +828,28 @@
         <v>2.59</v>
       </c>
       <c r="L4" t="n">
-        <v>54.89</v>
+        <v>55</v>
       </c>
       <c r="M4" t="n">
-        <v>55.61</v>
+        <v>55.72</v>
       </c>
       <c r="N4" t="n">
-        <v>53.45</v>
+        <v>53.56</v>
       </c>
       <c r="O4" t="n">
-        <v>58.55</v>
+        <v>58.66</v>
       </c>
       <c r="P4" t="n">
         <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>50.8</v>
+        <v>51.37</v>
       </c>
       <c r="R4" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.16</v>
+        <v>-2.97</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>XLE 7.15% · CL=F 20.35%</t>
+          <t>XLE 7.28% · CL=F 20.52%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.15% · CL=F 20.35%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.28% · CL=F 20.52%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -914,25 +914,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>188.99</v>
+        <v>189.2</v>
       </c>
       <c r="D5" t="n">
         <v>96</v>
       </c>
       <c r="E5" t="n">
-        <v>4.06</v>
+        <v>4.17</v>
       </c>
       <c r="F5" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="G5" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="H5" t="n">
-        <v>-6.74</v>
+        <v>-6.59</v>
       </c>
       <c r="I5" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="J5" t="n">
         <v>4.21</v>
@@ -941,28 +941,28 @@
         <v>2.23</v>
       </c>
       <c r="L5" t="n">
-        <v>187.52</v>
+        <v>187.72</v>
       </c>
       <c r="M5" t="n">
-        <v>189.62</v>
+        <v>189.83</v>
       </c>
       <c r="N5" t="n">
-        <v>183.3</v>
+        <v>183.51</v>
       </c>
       <c r="O5" t="n">
-        <v>198.26</v>
+        <v>198.47</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>56.66</v>
+        <v>56.95</v>
       </c>
       <c r="R5" t="n">
-        <v>0.95</v>
+        <v>1.06</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.65</v>
+        <v>-2.54</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>XLE 7.15% · CL=F 20.35%</t>
+          <t>XLE 7.28% · CL=F 20.52%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.15% · CL=F 20.35%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.28% · CL=F 20.52%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1027,22 +1027,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>81.70999999999999</v>
+        <v>81.75</v>
       </c>
       <c r="D6" t="n">
         <v>96</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.61</v>
+        <v>-2.56</v>
       </c>
       <c r="F6" t="n">
-        <v>13.09</v>
+        <v>13.15</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="H6" t="n">
-        <v>3.63</v>
+        <v>3.73</v>
       </c>
       <c r="I6" t="n">
         <v>0.23</v>
@@ -1054,28 +1054,28 @@
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>80.54000000000001</v>
+        <v>80.58</v>
       </c>
       <c r="M6" t="n">
-        <v>82.20999999999999</v>
+        <v>82.25</v>
       </c>
       <c r="N6" t="n">
-        <v>77.19</v>
+        <v>77.23</v>
       </c>
       <c r="O6" t="n">
-        <v>89.08</v>
+        <v>89.12</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>62.27</v>
+        <v>62.34</v>
       </c>
       <c r="R6" t="n">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.53</v>
+        <v>-3.48</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>419.45</v>
+        <v>418.99</v>
       </c>
       <c r="D7" t="n">
         <v>96</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="F7" t="n">
-        <v>12.92</v>
+        <v>12.8</v>
       </c>
       <c r="G7" t="n">
-        <v>21.85</v>
+        <v>21.72</v>
       </c>
       <c r="H7" t="n">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="I7" t="n">
         <v>0.36</v>
@@ -1167,28 +1167,28 @@
         <v>2.8</v>
       </c>
       <c r="L7" t="n">
-        <v>415.34</v>
+        <v>414.88</v>
       </c>
       <c r="M7" t="n">
-        <v>421.21</v>
+        <v>420.75</v>
       </c>
       <c r="N7" t="n">
-        <v>403.59</v>
+        <v>403.13</v>
       </c>
       <c r="O7" t="n">
-        <v>445.29</v>
+        <v>444.83</v>
       </c>
       <c r="P7" t="n">
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>63.13</v>
+        <v>62.85</v>
       </c>
       <c r="R7" t="n">
-        <v>3.96</v>
+        <v>3.85</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.73</v>
+        <v>-3.84</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1253,55 +1253,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>434.8</v>
+        <v>436.34</v>
       </c>
       <c r="D8" t="n">
         <v>96</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.15</v>
+        <v>0.21</v>
       </c>
       <c r="F8" t="n">
-        <v>9.539999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="G8" t="n">
-        <v>17.57</v>
+        <v>17.98</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08</v>
+        <v>0.51</v>
       </c>
       <c r="I8" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="J8" t="n">
         <v>18.51</v>
       </c>
       <c r="K8" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="L8" t="n">
-        <v>428.32</v>
+        <v>429.86</v>
       </c>
       <c r="M8" t="n">
-        <v>437.58</v>
+        <v>439.12</v>
       </c>
       <c r="N8" t="n">
-        <v>409.81</v>
+        <v>411.35</v>
       </c>
       <c r="O8" t="n">
-        <v>475.52</v>
+        <v>477.06</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>59.32</v>
+        <v>59.9</v>
       </c>
       <c r="R8" t="n">
-        <v>5.71</v>
+        <v>6.07</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.04</v>
+        <v>-2.7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1362,22 +1362,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>94.53</v>
+        <v>94.61</v>
       </c>
       <c r="D9" t="n">
         <v>91</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.6</v>
+        <v>-4.52</v>
       </c>
       <c r="F9" t="n">
-        <v>20.02</v>
+        <v>20.12</v>
       </c>
       <c r="G9" t="n">
-        <v>23.23</v>
+        <v>23.34</v>
       </c>
       <c r="H9" t="n">
-        <v>10.56</v>
+        <v>10.7</v>
       </c>
       <c r="I9" t="n">
         <v>0.22</v>
@@ -1386,31 +1386,31 @@
         <v>4.27</v>
       </c>
       <c r="K9" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
       <c r="L9" t="n">
-        <v>93.04000000000001</v>
+        <v>93.12</v>
       </c>
       <c r="M9" t="n">
-        <v>95.17</v>
+        <v>95.25</v>
       </c>
       <c r="N9" t="n">
-        <v>88.77</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>103.92</v>
+        <v>104</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>62.69</v>
+        <v>62.86</v>
       </c>
       <c r="R9" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="S9" t="n">
-        <v>-10.74</v>
+        <v>-10.67</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1475,22 +1475,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>192.93</v>
+        <v>192.75</v>
       </c>
       <c r="D10" t="n">
         <v>91</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.54</v>
+        <v>-1.63</v>
       </c>
       <c r="F10" t="n">
-        <v>10.21</v>
+        <v>10.11</v>
       </c>
       <c r="G10" t="n">
-        <v>23.68</v>
+        <v>23.56</v>
       </c>
       <c r="H10" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>0.3</v>
@@ -1502,28 +1502,28 @@
         <v>4.77</v>
       </c>
       <c r="L10" t="n">
-        <v>189.71</v>
+        <v>189.53</v>
       </c>
       <c r="M10" t="n">
-        <v>194.31</v>
+        <v>194.13</v>
       </c>
       <c r="N10" t="n">
-        <v>180.52</v>
+        <v>180.34</v>
       </c>
       <c r="O10" t="n">
-        <v>213.16</v>
+        <v>212.98</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>64.97</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>5.98</v>
+        <v>5.88</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.88</v>
+        <v>-3.97</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1588,55 +1588,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>405.73</v>
+        <v>406.21</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.45</v>
+        <v>-1.33</v>
       </c>
       <c r="F11" t="n">
-        <v>9.51</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>12.9</v>
+        <v>13.03</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="I11" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="J11" t="n">
         <v>15.44</v>
       </c>
       <c r="K11" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
-        <v>400.33</v>
+        <v>400.81</v>
       </c>
       <c r="M11" t="n">
-        <v>408.05</v>
+        <v>408.53</v>
       </c>
       <c r="N11" t="n">
-        <v>384.89</v>
+        <v>385.37</v>
       </c>
       <c r="O11" t="n">
-        <v>439.69</v>
+        <v>440.17</v>
       </c>
       <c r="P11" t="n">
         <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>50.34</v>
+        <v>50.57</v>
       </c>
       <c r="R11" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.85</v>
+        <v>-3.73</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1701,25 +1701,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>423.58</v>
+        <v>424.14</v>
       </c>
       <c r="D12" t="n">
         <v>87</v>
       </c>
       <c r="E12" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="F12" t="n">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="G12" t="n">
-        <v>6.31</v>
+        <v>6.44</v>
       </c>
       <c r="H12" t="n">
-        <v>-9.27</v>
+        <v>-9.1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="J12" t="n">
         <v>11.28</v>
@@ -1728,28 +1728,28 @@
         <v>2.66</v>
       </c>
       <c r="L12" t="n">
-        <v>419.64</v>
+        <v>420.19</v>
       </c>
       <c r="M12" t="n">
-        <v>425.28</v>
+        <v>425.83</v>
       </c>
       <c r="N12" t="n">
-        <v>408.36</v>
+        <v>408.91</v>
       </c>
       <c r="O12" t="n">
-        <v>448.4</v>
+        <v>448.95</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>49.22</v>
+        <v>49.57</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.33</v>
+        <v>-2.2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1814,55 +1814,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1515.76</v>
+        <v>1517.47</v>
       </c>
       <c r="D13" t="n">
         <v>93</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.79</v>
+        <v>-4.68</v>
       </c>
       <c r="F13" t="n">
-        <v>4.06</v>
+        <v>4.18</v>
       </c>
       <c r="G13" t="n">
-        <v>4.12</v>
+        <v>4.24</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.4</v>
+        <v>-5.24</v>
       </c>
       <c r="I13" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="J13" t="n">
         <v>65.62</v>
       </c>
       <c r="K13" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="L13" t="n">
-        <v>1492.79</v>
+        <v>1494.51</v>
       </c>
       <c r="M13" t="n">
-        <v>1525.6</v>
+        <v>1527.32</v>
       </c>
       <c r="N13" t="n">
-        <v>1427.18</v>
+        <v>1428.89</v>
       </c>
       <c r="O13" t="n">
-        <v>1660.11</v>
+        <v>1661.83</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>56.71</v>
+        <v>56.87</v>
       </c>
       <c r="R13" t="n">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.47</v>
+        <v>-5.36</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1927,22 +1927,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>428.27</v>
+        <v>428.04</v>
       </c>
       <c r="D14" t="n">
         <v>85</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4</v>
+        <v>-0.46</v>
       </c>
       <c r="F14" t="n">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="G14" t="n">
-        <v>28.5</v>
+        <v>28.43</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.11</v>
+        <v>-4.13</v>
       </c>
       <c r="I14" t="n">
         <v>0.44</v>
@@ -1954,28 +1954,28 @@
         <v>3.98</v>
       </c>
       <c r="L14" t="n">
-        <v>422.3</v>
+        <v>422.07</v>
       </c>
       <c r="M14" t="n">
-        <v>430.83</v>
+        <v>430.6</v>
       </c>
       <c r="N14" t="n">
-        <v>405.25</v>
+        <v>405.02</v>
       </c>
       <c r="O14" t="n">
-        <v>465.79</v>
+        <v>465.56</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>53.72</v>
+        <v>53.63</v>
       </c>
       <c r="R14" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.19</v>
+        <v>-3.24</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2040,25 +2040,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>95.3</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="D15" t="n">
         <v>77</v>
       </c>
       <c r="E15" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.41</v>
+        <v>-1.42</v>
       </c>
       <c r="G15" t="n">
-        <v>-11.24</v>
+        <v>-11.26</v>
       </c>
       <c r="H15" t="n">
-        <v>-10.87</v>
+        <v>-10.84</v>
       </c>
       <c r="I15" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="J15" t="n">
         <v>4.29</v>
@@ -2067,28 +2067,28 @@
         <v>4.51</v>
       </c>
       <c r="L15" t="n">
-        <v>93.8</v>
+        <v>93.78</v>
       </c>
       <c r="M15" t="n">
-        <v>95.94</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>89.5</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>104.75</v>
+        <v>104.73</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>58.41</v>
+        <v>58.39</v>
       </c>
       <c r="R15" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.82</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; RSI saludable; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2153,55 +2153,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1567.05</v>
+        <v>1569.39</v>
       </c>
       <c r="D16" t="n">
         <v>78</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.11</v>
+        <v>-1.96</v>
       </c>
       <c r="F16" t="n">
-        <v>6.72</v>
+        <v>6.88</v>
       </c>
       <c r="G16" t="n">
-        <v>33.61</v>
+        <v>33.81</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.74</v>
+        <v>-2.54</v>
       </c>
       <c r="I16" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>76.48999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>4.88</v>
+        <v>4.87</v>
       </c>
       <c r="L16" t="n">
-        <v>1540.28</v>
+        <v>1542.62</v>
       </c>
       <c r="M16" t="n">
-        <v>1578.52</v>
+        <v>1580.86</v>
       </c>
       <c r="N16" t="n">
-        <v>1463.79</v>
+        <v>1466.13</v>
       </c>
       <c r="O16" t="n">
-        <v>1735.33</v>
+        <v>1737.67</v>
       </c>
       <c r="P16" t="n">
         <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>48.47</v>
+        <v>48.64</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.02</v>
+        <v>-0.88</v>
       </c>
       <c r="S16" t="n">
-        <v>-6.47</v>
+        <v>-6.33</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2262,25 +2262,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>326.83</v>
+        <v>326.43</v>
       </c>
       <c r="D17" t="n">
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="F17" t="n">
-        <v>3.31</v>
+        <v>3.18</v>
       </c>
       <c r="G17" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.15</v>
+        <v>-6.24</v>
       </c>
       <c r="I17" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J17" t="n">
         <v>7.83</v>
@@ -2289,28 +2289,28 @@
         <v>2.4</v>
       </c>
       <c r="L17" t="n">
-        <v>324.09</v>
+        <v>323.69</v>
       </c>
       <c r="M17" t="n">
-        <v>328</v>
+        <v>327.61</v>
       </c>
       <c r="N17" t="n">
-        <v>316.26</v>
+        <v>315.86</v>
       </c>
       <c r="O17" t="n">
-        <v>344.06</v>
+        <v>343.67</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.15</v>
+        <v>62.93</v>
       </c>
       <c r="R17" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.23</v>
+        <v>-4.35</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2375,22 +2375,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>950.66</v>
+        <v>951.49</v>
       </c>
       <c r="D18" t="n">
         <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="F18" t="n">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="G18" t="n">
-        <v>4.26</v>
+        <v>4.35</v>
       </c>
       <c r="H18" t="n">
-        <v>-6.79</v>
+        <v>-6.66</v>
       </c>
       <c r="I18" t="n">
         <v>0.49</v>
@@ -2402,28 +2402,28 @@
         <v>2.48</v>
       </c>
       <c r="L18" t="n">
-        <v>942.4</v>
+        <v>943.24</v>
       </c>
       <c r="M18" t="n">
-        <v>954.2</v>
+        <v>955.03</v>
       </c>
       <c r="N18" t="n">
-        <v>918.8099999999999</v>
+        <v>919.64</v>
       </c>
       <c r="O18" t="n">
-        <v>1002.57</v>
+        <v>1003.4</v>
       </c>
       <c r="P18" t="n">
         <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>53.61</v>
+        <v>53.87</v>
       </c>
       <c r="R18" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.56</v>
+        <v>-2.48</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2488,55 +2488,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>883.33</v>
+        <v>884.77</v>
       </c>
       <c r="D19" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.57</v>
+        <v>-1.41</v>
       </c>
       <c r="F19" t="n">
-        <v>11.37</v>
+        <v>11.55</v>
       </c>
       <c r="G19" t="n">
-        <v>16.37</v>
+        <v>16.56</v>
       </c>
       <c r="H19" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="J19" t="n">
         <v>32.06</v>
       </c>
       <c r="K19" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="L19" t="n">
-        <v>872.11</v>
+        <v>873.55</v>
       </c>
       <c r="M19" t="n">
-        <v>888.14</v>
+        <v>889.58</v>
       </c>
       <c r="N19" t="n">
-        <v>840.05</v>
+        <v>841.49</v>
       </c>
       <c r="O19" t="n">
-        <v>953.86</v>
+        <v>955.3</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.86</v>
+        <v>59.13</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="S19" t="n">
-        <v>-5.16</v>
+        <v>-5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>228.5</v>
+        <v>228.74</v>
       </c>
       <c r="D20" t="n">
         <v>88</v>
       </c>
       <c r="E20" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.43</v>
+        <v>-2.32</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.96</v>
+        <v>-6.87</v>
       </c>
       <c r="H20" t="n">
-        <v>-11.89</v>
+        <v>-11.74</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="J20" t="n">
         <v>3.89</v>
@@ -2628,28 +2628,28 @@
         <v>1.7</v>
       </c>
       <c r="L20" t="n">
-        <v>227.14</v>
+        <v>227.38</v>
       </c>
       <c r="M20" t="n">
-        <v>229.08</v>
+        <v>229.32</v>
       </c>
       <c r="N20" t="n">
-        <v>223.25</v>
+        <v>223.49</v>
       </c>
       <c r="O20" t="n">
-        <v>237.06</v>
+        <v>237.3</v>
       </c>
       <c r="P20" t="n">
         <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>55.56</v>
+        <v>56.04</v>
       </c>
       <c r="R20" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.87</v>
+        <v>-2.77</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,22 +2714,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>145.42</v>
+        <v>145.47</v>
       </c>
       <c r="D21" t="n">
         <v>82</v>
       </c>
       <c r="E21" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.27</v>
+        <v>-2.24</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.15</v>
+        <v>-7.12</v>
       </c>
       <c r="H21" t="n">
-        <v>-11.73</v>
+        <v>-11.66</v>
       </c>
       <c r="I21" t="n">
         <v>0.5</v>
@@ -2738,31 +2738,31 @@
         <v>1.88</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="L21" t="n">
-        <v>144.76</v>
+        <v>144.81</v>
       </c>
       <c r="M21" t="n">
-        <v>145.7</v>
+        <v>145.75</v>
       </c>
       <c r="N21" t="n">
-        <v>142.88</v>
+        <v>142.93</v>
       </c>
       <c r="O21" t="n">
-        <v>149.56</v>
+        <v>149.61</v>
       </c>
       <c r="P21" t="n">
         <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>57.11</v>
+        <v>57.32</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.23</v>
+        <v>-2.2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2827,22 +2827,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>285.23</v>
+        <v>285.88</v>
       </c>
       <c r="D22" t="n">
         <v>96</v>
       </c>
       <c r="E22" t="n">
-        <v>-3</v>
+        <v>-2.78</v>
       </c>
       <c r="F22" t="n">
-        <v>6.59</v>
+        <v>6.83</v>
       </c>
       <c r="G22" t="n">
-        <v>20.3</v>
+        <v>20.57</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.87</v>
+        <v>-2.59</v>
       </c>
       <c r="I22" t="n">
         <v>0.55</v>
@@ -2851,31 +2851,31 @@
         <v>13.74</v>
       </c>
       <c r="K22" t="n">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="L22" t="n">
-        <v>280.42</v>
+        <v>281.07</v>
       </c>
       <c r="M22" t="n">
-        <v>287.29</v>
+        <v>287.94</v>
       </c>
       <c r="N22" t="n">
-        <v>266.69</v>
+        <v>267.33</v>
       </c>
       <c r="O22" t="n">
-        <v>315.45</v>
+        <v>316.09</v>
       </c>
       <c r="P22" t="n">
         <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>61.48</v>
+        <v>61.83</v>
       </c>
       <c r="R22" t="n">
-        <v>4.39</v>
+        <v>4.61</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.55</v>
+        <v>-5.34</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2936,22 +2936,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>131.22</v>
+        <v>131.32</v>
       </c>
       <c r="D23" t="n">
         <v>96</v>
       </c>
       <c r="E23" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="F23" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="G23" t="n">
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.35</v>
+        <v>-6.23</v>
       </c>
       <c r="I23" t="n">
         <v>0.51</v>
@@ -2963,28 +2963,28 @@
         <v>2.01</v>
       </c>
       <c r="L23" t="n">
-        <v>130.3</v>
+        <v>130.39</v>
       </c>
       <c r="M23" t="n">
-        <v>131.61</v>
+        <v>131.71</v>
       </c>
       <c r="N23" t="n">
-        <v>127.67</v>
+        <v>127.76</v>
       </c>
       <c r="O23" t="n">
-        <v>137.01</v>
+        <v>137.11</v>
       </c>
       <c r="P23" t="n">
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>61.63</v>
+        <v>61.99</v>
       </c>
       <c r="R23" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.04</v>
+        <v>-1.97</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3045,25 +3045,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1084.3</v>
+        <v>1084.6</v>
       </c>
       <c r="D24" t="n">
         <v>85</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="F24" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="G24" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="H24" t="n">
-        <v>-6.4</v>
+        <v>-6.34</v>
       </c>
       <c r="I24" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="J24" t="n">
         <v>22.32</v>
@@ -3072,28 +3072,28 @@
         <v>2.06</v>
       </c>
       <c r="L24" t="n">
-        <v>1076.49</v>
+        <v>1076.78</v>
       </c>
       <c r="M24" t="n">
-        <v>1087.65</v>
+        <v>1087.94</v>
       </c>
       <c r="N24" t="n">
-        <v>1054.17</v>
+        <v>1054.47</v>
       </c>
       <c r="O24" t="n">
-        <v>1133.4</v>
+        <v>1133.69</v>
       </c>
       <c r="P24" t="n">
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>58.91</v>
+        <v>59.03</v>
       </c>
       <c r="R24" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.41</v>
+        <v>-2.38</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3154,25 +3154,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>192.47</v>
+        <v>192.43</v>
       </c>
       <c r="D25" t="n">
         <v>85</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.32</v>
+        <v>-0.34</v>
       </c>
       <c r="F25" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>10.97</v>
+        <v>10.95</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.98</v>
+        <v>-6.96</v>
       </c>
       <c r="I25" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="J25" t="n">
         <v>4.39</v>
@@ -3181,28 +3181,28 @@
         <v>2.28</v>
       </c>
       <c r="L25" t="n">
-        <v>190.93</v>
+        <v>190.89</v>
       </c>
       <c r="M25" t="n">
-        <v>193.13</v>
+        <v>193.09</v>
       </c>
       <c r="N25" t="n">
-        <v>186.55</v>
+        <v>186.51</v>
       </c>
       <c r="O25" t="n">
-        <v>202.12</v>
+        <v>202.08</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>55.61</v>
+        <v>55.54</v>
       </c>
       <c r="R25" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.55</v>
+        <v>-2.57</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3263,25 +3263,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>495.71</v>
+        <v>495.93</v>
       </c>
       <c r="D26" t="n">
         <v>85</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G26" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="H26" t="n">
-        <v>-9.16</v>
+        <v>-9.07</v>
       </c>
       <c r="I26" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>5.07</v>
@@ -3290,28 +3290,28 @@
         <v>1.02</v>
       </c>
       <c r="L26" t="n">
-        <v>493.94</v>
+        <v>494.16</v>
       </c>
       <c r="M26" t="n">
-        <v>496.47</v>
+        <v>496.7</v>
       </c>
       <c r="N26" t="n">
-        <v>488.87</v>
+        <v>489.09</v>
       </c>
       <c r="O26" t="n">
-        <v>506.86</v>
+        <v>507.09</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>54.58</v>
+        <v>54.87</v>
       </c>
       <c r="R26" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.28</v>
+        <v>-1.24</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3372,25 +3372,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>90.58</v>
+        <v>90.67</v>
       </c>
       <c r="D27" t="n">
         <v>74</v>
       </c>
       <c r="E27" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.48</v>
+        <v>-1.39</v>
       </c>
       <c r="G27" t="n">
-        <v>-3.15</v>
+        <v>-3.06</v>
       </c>
       <c r="H27" t="n">
-        <v>-10.94</v>
+        <v>-10.81</v>
       </c>
       <c r="I27" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J27" t="n">
         <v>2.18</v>
@@ -3399,28 +3399,28 @@
         <v>2.4</v>
       </c>
       <c r="L27" t="n">
-        <v>89.81999999999999</v>
+        <v>89.91</v>
       </c>
       <c r="M27" t="n">
-        <v>90.91</v>
+        <v>91</v>
       </c>
       <c r="N27" t="n">
-        <v>87.65000000000001</v>
+        <v>87.73</v>
       </c>
       <c r="O27" t="n">
-        <v>95.37</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="P27" t="n">
         <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>50.6</v>
+        <v>50.94</v>
       </c>
       <c r="R27" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.45</v>
+        <v>-3.36</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3481,25 +3481,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>202.68</v>
+        <v>203.12</v>
       </c>
       <c r="D28" t="n">
         <v>96</v>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>8.23</v>
       </c>
       <c r="F28" t="n">
-        <v>13.05</v>
+        <v>13.3</v>
       </c>
       <c r="G28" t="n">
-        <v>17.34</v>
+        <v>17.59</v>
       </c>
       <c r="H28" t="n">
-        <v>3.59</v>
+        <v>3.88</v>
       </c>
       <c r="I28" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="J28" t="n">
         <v>6.37</v>
@@ -3508,28 +3508,28 @@
         <v>3.14</v>
       </c>
       <c r="L28" t="n">
-        <v>200.45</v>
+        <v>200.89</v>
       </c>
       <c r="M28" t="n">
-        <v>203.64</v>
+        <v>204.08</v>
       </c>
       <c r="N28" t="n">
-        <v>194.08</v>
+        <v>194.52</v>
       </c>
       <c r="O28" t="n">
-        <v>216.69</v>
+        <v>217.13</v>
       </c>
       <c r="P28" t="n">
         <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>56.43</v>
+        <v>56.76</v>
       </c>
       <c r="R28" t="n">
-        <v>2.74</v>
+        <v>2.95</v>
       </c>
       <c r="S28" t="n">
-        <v>-5</v>
+        <v>-4.79</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>XLE 7.15% · CL=F 20.35%</t>
+          <t>XLE 7.28% · CL=F 20.52%</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.15% · CL=F 20.35%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.28% · CL=F 20.52%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3594,55 +3594,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>48.64</v>
+        <v>48.72</v>
       </c>
       <c r="D29" t="n">
         <v>96</v>
       </c>
       <c r="E29" t="n">
-        <v>6.64</v>
+        <v>6.83</v>
       </c>
       <c r="F29" t="n">
-        <v>9.970000000000001</v>
+        <v>10.16</v>
       </c>
       <c r="G29" t="n">
-        <v>9.48</v>
+        <v>9.67</v>
       </c>
       <c r="H29" t="n">
-        <v>0.51</v>
+        <v>0.74</v>
       </c>
       <c r="I29" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J29" t="n">
         <v>1.69</v>
       </c>
       <c r="K29" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="L29" t="n">
-        <v>48.05</v>
+        <v>48.13</v>
       </c>
       <c r="M29" t="n">
-        <v>48.89</v>
+        <v>48.98</v>
       </c>
       <c r="N29" t="n">
-        <v>46.36</v>
+        <v>46.45</v>
       </c>
       <c r="O29" t="n">
-        <v>52.35</v>
+        <v>52.44</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>51.58</v>
+        <v>51.87</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>-6.37</v>
+        <v>-6.21</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>XLE 7.15% · CL=F 20.35%</t>
+          <t>XLE 7.28% · CL=F 20.52%</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.15% · CL=F 20.35%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.28% · CL=F 20.52%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3707,25 +3707,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>139.23</v>
+        <v>139.33</v>
       </c>
       <c r="D30" t="n">
         <v>96</v>
       </c>
       <c r="E30" t="n">
-        <v>7.07</v>
+        <v>7.15</v>
       </c>
       <c r="F30" t="n">
-        <v>8.41</v>
+        <v>8.49</v>
       </c>
       <c r="G30" t="n">
-        <v>13.27</v>
+        <v>13.35</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.05</v>
+        <v>-0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="J30" t="n">
         <v>3.77</v>
@@ -3734,28 +3734,28 @@
         <v>2.71</v>
       </c>
       <c r="L30" t="n">
-        <v>137.91</v>
+        <v>138.01</v>
       </c>
       <c r="M30" t="n">
-        <v>139.79</v>
+        <v>139.9</v>
       </c>
       <c r="N30" t="n">
-        <v>134.14</v>
+        <v>134.24</v>
       </c>
       <c r="O30" t="n">
-        <v>147.52</v>
+        <v>147.62</v>
       </c>
       <c r="P30" t="n">
         <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>59.27</v>
+        <v>59.4</v>
       </c>
       <c r="R30" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="S30" t="n">
-        <v>-2.54</v>
+        <v>-2.46</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>XLE 7.15% · CL=F 20.35%</t>
+          <t>XLE 7.28% · CL=F 20.52%</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.15% · CL=F 20.35%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.28% · CL=F 20.52%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3820,22 +3820,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>121.69</v>
+        <v>121.76</v>
       </c>
       <c r="D31" t="n">
         <v>85</v>
       </c>
       <c r="E31" t="n">
-        <v>7.66</v>
+        <v>7.72</v>
       </c>
       <c r="F31" t="n">
-        <v>5.65</v>
+        <v>5.71</v>
       </c>
       <c r="G31" t="n">
-        <v>9.859999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="H31" t="n">
-        <v>-3.81</v>
+        <v>-3.71</v>
       </c>
       <c r="I31" t="n">
         <v>0.32</v>
@@ -3847,28 +3847,28 @@
         <v>2.7</v>
       </c>
       <c r="L31" t="n">
-        <v>120.54</v>
+        <v>120.61</v>
       </c>
       <c r="M31" t="n">
-        <v>122.18</v>
+        <v>122.25</v>
       </c>
       <c r="N31" t="n">
-        <v>117.26</v>
+        <v>117.33</v>
       </c>
       <c r="O31" t="n">
-        <v>128.92</v>
+        <v>128.99</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>51.34</v>
+        <v>51.44</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>-4.43</v>
+        <v>-4.38</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>XLE 7.15% · CL=F 20.35%</t>
+          <t>XLE 7.28% · CL=F 20.52%</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.15% · CL=F 20.35%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.28% · CL=F 20.52%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3933,25 +3933,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>156.14</v>
+        <v>156.27</v>
       </c>
       <c r="D32" t="n">
         <v>96</v>
       </c>
       <c r="E32" t="n">
-        <v>8</v>
+        <v>8.09</v>
       </c>
       <c r="F32" t="n">
-        <v>6.62</v>
+        <v>6.71</v>
       </c>
       <c r="G32" t="n">
-        <v>3.42</v>
+        <v>3.51</v>
       </c>
       <c r="H32" t="n">
-        <v>-2.84</v>
+        <v>-2.71</v>
       </c>
       <c r="I32" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J32" t="n">
         <v>3.89</v>
@@ -3960,28 +3960,28 @@
         <v>2.49</v>
       </c>
       <c r="L32" t="n">
-        <v>154.78</v>
+        <v>154.91</v>
       </c>
       <c r="M32" t="n">
-        <v>156.72</v>
+        <v>156.85</v>
       </c>
       <c r="N32" t="n">
-        <v>150.88</v>
+        <v>151.01</v>
       </c>
       <c r="O32" t="n">
-        <v>164.71</v>
+        <v>164.84</v>
       </c>
       <c r="P32" t="n">
         <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>62.26</v>
+        <v>62.42</v>
       </c>
       <c r="R32" t="n">
-        <v>3.59</v>
+        <v>3.67</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.24</v>
+        <v>-0.16</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>XLE 7.15% · CL=F 20.35%</t>
+          <t>XLE 7.28% · CL=F 20.52%</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.15% · CL=F 20.35%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.28% · CL=F 20.52%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4046,25 +4046,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>113.21</v>
+        <v>113.32</v>
       </c>
       <c r="D33" t="n">
         <v>96</v>
       </c>
       <c r="E33" t="n">
-        <v>9.699999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="F33" t="n">
-        <v>36.38</v>
+        <v>36.51</v>
       </c>
       <c r="G33" t="n">
-        <v>66.27</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>26.92</v>
+        <v>27.09</v>
       </c>
       <c r="I33" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="J33" t="n">
         <v>6.18</v>
@@ -4073,28 +4073,28 @@
         <v>5.46</v>
       </c>
       <c r="L33" t="n">
-        <v>111.05</v>
+        <v>111.16</v>
       </c>
       <c r="M33" t="n">
-        <v>114.14</v>
+        <v>114.25</v>
       </c>
       <c r="N33" t="n">
-        <v>104.86</v>
+        <v>104.97</v>
       </c>
       <c r="O33" t="n">
-        <v>126.81</v>
+        <v>126.92</v>
       </c>
       <c r="P33" t="n">
         <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>64.17</v>
+        <v>64.3</v>
       </c>
       <c r="R33" t="n">
-        <v>11.83</v>
+        <v>11.94</v>
       </c>
       <c r="S33" t="n">
-        <v>-4.95</v>
+        <v>-4.85</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>179.15</v>
+        <v>179.13</v>
       </c>
       <c r="D34" t="n">
         <v>96</v>
       </c>
       <c r="E34" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="F34" t="n">
-        <v>28.25</v>
+        <v>28.24</v>
       </c>
       <c r="G34" t="n">
-        <v>125.15</v>
+        <v>125.13</v>
       </c>
       <c r="H34" t="n">
-        <v>18.79</v>
+        <v>18.82</v>
       </c>
       <c r="I34" t="n">
         <v>0.45</v>
@@ -4186,25 +4186,25 @@
         <v>5.94</v>
       </c>
       <c r="L34" t="n">
-        <v>175.43</v>
+        <v>175.41</v>
       </c>
       <c r="M34" t="n">
-        <v>180.75</v>
+        <v>180.73</v>
       </c>
       <c r="N34" t="n">
-        <v>164.79</v>
+        <v>164.77</v>
       </c>
       <c r="O34" t="n">
-        <v>202.55</v>
+        <v>202.54</v>
       </c>
       <c r="P34" t="n">
         <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>63.47</v>
+        <v>63.46</v>
       </c>
       <c r="R34" t="n">
-        <v>8.77</v>
+        <v>8.76</v>
       </c>
       <c r="S34" t="n">
         <v>-6.77</v>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4272,25 +4272,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>512.42</v>
+        <v>512.9400000000001</v>
       </c>
       <c r="D35" t="n">
         <v>96</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.51</v>
+        <v>-1.41</v>
       </c>
       <c r="F35" t="n">
-        <v>23.27</v>
+        <v>23.39</v>
       </c>
       <c r="G35" t="n">
-        <v>44.09</v>
+        <v>44.24</v>
       </c>
       <c r="H35" t="n">
-        <v>13.81</v>
+        <v>13.97</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="J35" t="n">
         <v>19.17</v>
@@ -4299,28 +4299,28 @@
         <v>3.74</v>
       </c>
       <c r="L35" t="n">
-        <v>505.71</v>
+        <v>506.23</v>
       </c>
       <c r="M35" t="n">
-        <v>515.3</v>
+        <v>515.8200000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>486.54</v>
+        <v>487.06</v>
       </c>
       <c r="O35" t="n">
-        <v>554.61</v>
+        <v>555.12</v>
       </c>
       <c r="P35" t="n">
         <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>64.58</v>
+        <v>64.75</v>
       </c>
       <c r="R35" t="n">
-        <v>7.56</v>
+        <v>7.67</v>
       </c>
       <c r="S35" t="n">
-        <v>-3.99</v>
+        <v>-3.9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4385,22 +4385,22 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>240.45</v>
+        <v>240.6</v>
       </c>
       <c r="D36" t="n">
         <v>96</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.68</v>
+        <v>-7.62</v>
       </c>
       <c r="F36" t="n">
-        <v>22.71</v>
+        <v>22.79</v>
       </c>
       <c r="G36" t="n">
-        <v>102.58</v>
+        <v>102.71</v>
       </c>
       <c r="H36" t="n">
-        <v>13.25</v>
+        <v>13.37</v>
       </c>
       <c r="I36" t="n">
         <v>0.27</v>
@@ -4409,31 +4409,31 @@
         <v>13.94</v>
       </c>
       <c r="K36" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="L36" t="n">
-        <v>235.57</v>
+        <v>235.72</v>
       </c>
       <c r="M36" t="n">
-        <v>242.54</v>
+        <v>242.69</v>
       </c>
       <c r="N36" t="n">
-        <v>221.63</v>
+        <v>221.78</v>
       </c>
       <c r="O36" t="n">
-        <v>271.12</v>
+        <v>271.27</v>
       </c>
       <c r="P36" t="n">
         <v>1.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>60.19</v>
+        <v>60.27</v>
       </c>
       <c r="R36" t="n">
-        <v>7.31</v>
+        <v>7.38</v>
       </c>
       <c r="S36" t="n">
-        <v>-8.92</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4498,25 +4498,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>558.98</v>
+        <v>559.63</v>
       </c>
       <c r="D37" t="n">
         <v>96</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.33</v>
+        <v>-1.22</v>
       </c>
       <c r="F37" t="n">
-        <v>20.43</v>
+        <v>20.57</v>
       </c>
       <c r="G37" t="n">
-        <v>36.27</v>
+        <v>36.43</v>
       </c>
       <c r="H37" t="n">
-        <v>10.97</v>
+        <v>11.15</v>
       </c>
       <c r="I37" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="J37" t="n">
         <v>18.08</v>
@@ -4525,28 +4525,28 @@
         <v>3.23</v>
       </c>
       <c r="L37" t="n">
-        <v>552.65</v>
+        <v>553.3</v>
       </c>
       <c r="M37" t="n">
-        <v>561.6900000000001</v>
+        <v>562.34</v>
       </c>
       <c r="N37" t="n">
-        <v>534.58</v>
+        <v>535.23</v>
       </c>
       <c r="O37" t="n">
-        <v>598.75</v>
+        <v>599.4</v>
       </c>
       <c r="P37" t="n">
         <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>64.89</v>
+        <v>65.13</v>
       </c>
       <c r="R37" t="n">
-        <v>7.08</v>
+        <v>7.2</v>
       </c>
       <c r="S37" t="n">
-        <v>-3.82</v>
+        <v>-3.71</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4590,12 +4590,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Volumen bajo; Algo extendida sobre MA20</t>
+          <t>RSI algo alto; Volumen bajo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
@@ -4611,25 +4611,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>227.62</v>
+        <v>227.49</v>
       </c>
       <c r="D38" t="n">
         <v>96</v>
       </c>
       <c r="E38" t="n">
-        <v>5.77</v>
+        <v>5.71</v>
       </c>
       <c r="F38" t="n">
-        <v>12.86</v>
+        <v>12.8</v>
       </c>
       <c r="G38" t="n">
-        <v>21.15</v>
+        <v>21.08</v>
       </c>
       <c r="H38" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="I38" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>8.210000000000001</v>
@@ -4638,28 +4638,28 @@
         <v>3.61</v>
       </c>
       <c r="L38" t="n">
-        <v>224.75</v>
+        <v>224.62</v>
       </c>
       <c r="M38" t="n">
-        <v>228.85</v>
+        <v>228.72</v>
       </c>
       <c r="N38" t="n">
-        <v>216.54</v>
+        <v>216.41</v>
       </c>
       <c r="O38" t="n">
-        <v>245.68</v>
+        <v>245.55</v>
       </c>
       <c r="P38" t="n">
         <v>1.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>58.15</v>
+        <v>58.04</v>
       </c>
       <c r="R38" t="n">
-        <v>8.18</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S38" t="n">
-        <v>-3.77</v>
+        <v>-3.83</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4724,55 +4724,55 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>499.11</v>
+        <v>497.5</v>
       </c>
       <c r="D39" t="n">
         <v>93</v>
       </c>
       <c r="E39" t="n">
-        <v>6.52</v>
+        <v>6.18</v>
       </c>
       <c r="F39" t="n">
-        <v>4.59</v>
+        <v>4.25</v>
       </c>
       <c r="G39" t="n">
-        <v>21.14</v>
+        <v>20.75</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.87</v>
+        <v>-5.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>29.61</v>
       </c>
       <c r="K39" t="n">
-        <v>5.93</v>
+        <v>5.95</v>
       </c>
       <c r="L39" t="n">
-        <v>488.75</v>
+        <v>487.14</v>
       </c>
       <c r="M39" t="n">
-        <v>503.56</v>
+        <v>501.94</v>
       </c>
       <c r="N39" t="n">
-        <v>459.14</v>
+        <v>457.53</v>
       </c>
       <c r="O39" t="n">
-        <v>564.25</v>
+        <v>562.64</v>
       </c>
       <c r="P39" t="n">
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>58.59</v>
+        <v>58.29</v>
       </c>
       <c r="R39" t="n">
-        <v>6.13</v>
+        <v>5.81</v>
       </c>
       <c r="S39" t="n">
-        <v>-2.65</v>
+        <v>-2.96</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4837,55 +4837,55 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>108.36</v>
+        <v>108.4</v>
       </c>
       <c r="D40" t="n">
         <v>92</v>
       </c>
       <c r="E40" t="n">
-        <v>-13.25</v>
+        <v>-13.22</v>
       </c>
       <c r="F40" t="n">
-        <v>58.2</v>
+        <v>58.25</v>
       </c>
       <c r="G40" t="n">
-        <v>142.86</v>
+        <v>142.95</v>
       </c>
       <c r="H40" t="n">
-        <v>48.74</v>
+        <v>48.83</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="J40" t="n">
         <v>9.119999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>8.42</v>
+        <v>8.41</v>
       </c>
       <c r="L40" t="n">
-        <v>105.17</v>
+        <v>105.21</v>
       </c>
       <c r="M40" t="n">
-        <v>109.73</v>
+        <v>109.77</v>
       </c>
       <c r="N40" t="n">
-        <v>96.05</v>
+        <v>96.09</v>
       </c>
       <c r="O40" t="n">
-        <v>128.43</v>
+        <v>128.47</v>
       </c>
       <c r="P40" t="n">
         <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>64.34999999999999</v>
+        <v>64.38</v>
       </c>
       <c r="R40" t="n">
-        <v>11.09</v>
+        <v>11.12</v>
       </c>
       <c r="S40" t="n">
-        <v>-18.37</v>
+        <v>-18.34</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -4950,22 +4950,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>291.38</v>
+        <v>291.49</v>
       </c>
       <c r="D41" t="n">
         <v>91</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.14</v>
+        <v>-1.11</v>
       </c>
       <c r="F41" t="n">
-        <v>34.88</v>
+        <v>34.93</v>
       </c>
       <c r="G41" t="n">
-        <v>26.19</v>
+        <v>26.23</v>
       </c>
       <c r="H41" t="n">
-        <v>25.42</v>
+        <v>25.51</v>
       </c>
       <c r="I41" t="n">
         <v>0.17</v>
@@ -4974,31 +4974,31 @@
         <v>14.82</v>
       </c>
       <c r="K41" t="n">
-        <v>5.09</v>
+        <v>5.08</v>
       </c>
       <c r="L41" t="n">
-        <v>286.19</v>
+        <v>286.3</v>
       </c>
       <c r="M41" t="n">
-        <v>293.6</v>
+        <v>293.71</v>
       </c>
       <c r="N41" t="n">
-        <v>271.37</v>
+        <v>271.48</v>
       </c>
       <c r="O41" t="n">
-        <v>323.98</v>
+        <v>324.09</v>
       </c>
       <c r="P41" t="n">
         <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>69.38</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="R41" t="n">
-        <v>6.77</v>
+        <v>6.81</v>
       </c>
       <c r="S41" t="n">
-        <v>-4.97</v>
+        <v>-4.93</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5063,25 +5063,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>157.96</v>
+        <v>157.88</v>
       </c>
       <c r="D42" t="n">
         <v>90</v>
       </c>
       <c r="E42" t="n">
-        <v>3.61</v>
+        <v>3.57</v>
       </c>
       <c r="F42" t="n">
-        <v>9.710000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="G42" t="n">
-        <v>-11.86</v>
+        <v>-11.89</v>
       </c>
       <c r="H42" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="I42" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="J42" t="n">
         <v>7.7</v>
@@ -5090,28 +5090,28 @@
         <v>4.87</v>
       </c>
       <c r="L42" t="n">
-        <v>155.26</v>
+        <v>155.19</v>
       </c>
       <c r="M42" t="n">
-        <v>159.11</v>
+        <v>159.04</v>
       </c>
       <c r="N42" t="n">
-        <v>147.57</v>
+        <v>147.5</v>
       </c>
       <c r="O42" t="n">
-        <v>174.89</v>
+        <v>174.82</v>
       </c>
       <c r="P42" t="n">
         <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>64.94</v>
+        <v>64.89</v>
       </c>
       <c r="R42" t="n">
-        <v>7.25</v>
+        <v>7.21</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.2</v>
+        <v>-0.24</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; RSI saludable; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5176,22 +5176,22 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>211.31</v>
+        <v>212</v>
       </c>
       <c r="D43" t="n">
         <v>89</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.92</v>
+        <v>-0.6</v>
       </c>
       <c r="F43" t="n">
-        <v>26.74</v>
+        <v>27.15</v>
       </c>
       <c r="G43" t="n">
-        <v>66.48</v>
+        <v>67.02</v>
       </c>
       <c r="H43" t="n">
-        <v>17.28</v>
+        <v>17.73</v>
       </c>
       <c r="I43" t="n">
         <v>0.48</v>
@@ -5200,31 +5200,31 @@
         <v>16.2</v>
       </c>
       <c r="K43" t="n">
-        <v>7.67</v>
+        <v>7.64</v>
       </c>
       <c r="L43" t="n">
-        <v>205.64</v>
+        <v>206.33</v>
       </c>
       <c r="M43" t="n">
-        <v>213.74</v>
+        <v>214.43</v>
       </c>
       <c r="N43" t="n">
-        <v>189.43</v>
+        <v>190.12</v>
       </c>
       <c r="O43" t="n">
-        <v>246.96</v>
+        <v>247.65</v>
       </c>
       <c r="P43" t="n">
         <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>48.35</v>
+        <v>48.6</v>
       </c>
       <c r="R43" t="n">
-        <v>1.06</v>
+        <v>1.37</v>
       </c>
       <c r="S43" t="n">
-        <v>-11.77</v>
+        <v>-11.48</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5289,55 +5289,55 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>424.48</v>
+        <v>423.73</v>
       </c>
       <c r="D44" t="n">
         <v>78</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.9</v>
+        <v>-1.08</v>
       </c>
       <c r="F44" t="n">
-        <v>5.96</v>
+        <v>5.77</v>
       </c>
       <c r="G44" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="H44" t="n">
-        <v>-3.5</v>
+        <v>-3.65</v>
       </c>
       <c r="I44" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="J44" t="n">
-        <v>17.15</v>
+        <v>17.17</v>
       </c>
       <c r="K44" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="L44" t="n">
-        <v>418.48</v>
+        <v>417.72</v>
       </c>
       <c r="M44" t="n">
-        <v>427.05</v>
+        <v>426.31</v>
       </c>
       <c r="N44" t="n">
-        <v>401.32</v>
+        <v>400.55</v>
       </c>
       <c r="O44" t="n">
-        <v>462.22</v>
+        <v>461.5</v>
       </c>
       <c r="P44" t="n">
         <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>67.81999999999999</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="R44" t="n">
-        <v>5.74</v>
+        <v>5.56</v>
       </c>
       <c r="S44" t="n">
-        <v>-6.38</v>
+        <v>-6.54</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5398,55 +5398,55 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>30.91</v>
+        <v>30.95</v>
       </c>
       <c r="D45" t="n">
         <v>75</v>
       </c>
       <c r="E45" t="n">
-        <v>-12.61</v>
+        <v>-12.48</v>
       </c>
       <c r="F45" t="n">
-        <v>8.23</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>-3.89</v>
+        <v>-3.75</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.23</v>
+        <v>-1.03</v>
       </c>
       <c r="I45" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>2.29</v>
       </c>
       <c r="K45" t="n">
-        <v>7.4</v>
+        <v>7.39</v>
       </c>
       <c r="L45" t="n">
-        <v>30.11</v>
+        <v>30.15</v>
       </c>
       <c r="M45" t="n">
-        <v>31.25</v>
+        <v>31.3</v>
       </c>
       <c r="N45" t="n">
-        <v>27.82</v>
+        <v>27.87</v>
       </c>
       <c r="O45" t="n">
-        <v>35.94</v>
+        <v>35.99</v>
       </c>
       <c r="P45" t="n">
         <v>1.63</v>
       </c>
       <c r="Q45" t="n">
-        <v>57.66</v>
+        <v>57.79</v>
       </c>
       <c r="R45" t="n">
-        <v>3.07</v>
+        <v>3.21</v>
       </c>
       <c r="S45" t="n">
-        <v>-15.01</v>
+        <v>-14.89</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5507,55 +5507,55 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1041.52</v>
+        <v>1042.45</v>
       </c>
       <c r="D46" t="n">
         <v>96</v>
       </c>
       <c r="E46" t="n">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="F46" t="n">
-        <v>4.31</v>
+        <v>4.41</v>
       </c>
       <c r="G46" t="n">
-        <v>5.59</v>
+        <v>5.68</v>
       </c>
       <c r="H46" t="n">
-        <v>-5.15</v>
+        <v>-5.01</v>
       </c>
       <c r="I46" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="J46" t="n">
         <v>20.47</v>
       </c>
       <c r="K46" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="L46" t="n">
-        <v>1034.35</v>
+        <v>1035.29</v>
       </c>
       <c r="M46" t="n">
-        <v>1044.59</v>
+        <v>1045.53</v>
       </c>
       <c r="N46" t="n">
-        <v>1013.88</v>
+        <v>1014.82</v>
       </c>
       <c r="O46" t="n">
-        <v>1086.55</v>
+        <v>1087.49</v>
       </c>
       <c r="P46" t="n">
         <v>1.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>68.39</v>
+        <v>68.63</v>
       </c>
       <c r="R46" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="S46" t="n">
-        <v>-1.51</v>
+        <v>-1.42</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5620,22 +5620,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>680.34</v>
+        <v>681.1</v>
       </c>
       <c r="D47" t="n">
         <v>89</v>
       </c>
       <c r="E47" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="F47" t="n">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="G47" t="n">
-        <v>8.41</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>-5.24</v>
+        <v>-5.08</v>
       </c>
       <c r="I47" t="n">
         <v>0.66</v>
@@ -5647,28 +5647,28 @@
         <v>0.97</v>
       </c>
       <c r="L47" t="n">
-        <v>678.03</v>
+        <v>678.79</v>
       </c>
       <c r="M47" t="n">
-        <v>681.33</v>
+        <v>682.09</v>
       </c>
       <c r="N47" t="n">
-        <v>671.42</v>
+        <v>672.17</v>
       </c>
       <c r="O47" t="n">
-        <v>694.89</v>
+        <v>695.64</v>
       </c>
       <c r="P47" t="n">
         <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>70.81</v>
+        <v>71.8</v>
       </c>
       <c r="R47" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="S47" t="n">
-        <v>-1.27</v>
+        <v>-1.16</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5729,25 +5729,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>740.01</v>
+        <v>740.83</v>
       </c>
       <c r="D48" t="n">
         <v>89</v>
       </c>
       <c r="E48" t="n">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="F48" t="n">
-        <v>4.21</v>
+        <v>4.32</v>
       </c>
       <c r="G48" t="n">
-        <v>8.41</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>-5.25</v>
+        <v>-5.1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="J48" t="n">
         <v>7.2</v>
@@ -5756,28 +5756,28 @@
         <v>0.97</v>
       </c>
       <c r="L48" t="n">
-        <v>737.49</v>
+        <v>738.3099999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>741.09</v>
+        <v>741.91</v>
       </c>
       <c r="N48" t="n">
-        <v>730.29</v>
+        <v>731.11</v>
       </c>
       <c r="O48" t="n">
-        <v>755.86</v>
+        <v>756.6799999999999</v>
       </c>
       <c r="P48" t="n">
         <v>1.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>70.58</v>
+        <v>71.55</v>
       </c>
       <c r="R48" t="n">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="S48" t="n">
-        <v>-1.27</v>
+        <v>-1.16</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5838,55 +5838,55 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>210</v>
+        <v>210.03</v>
       </c>
       <c r="D49" t="n">
         <v>79</v>
       </c>
       <c r="E49" t="n">
-        <v>4.19</v>
+        <v>4.21</v>
       </c>
       <c r="F49" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="G49" t="n">
-        <v>-5.62</v>
+        <v>-5.61</v>
       </c>
       <c r="H49" t="n">
-        <v>-8.68</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="J49" t="n">
         <v>5.76</v>
       </c>
       <c r="K49" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="L49" t="n">
-        <v>207.98</v>
+        <v>208.01</v>
       </c>
       <c r="M49" t="n">
-        <v>210.86</v>
+        <v>210.89</v>
       </c>
       <c r="N49" t="n">
-        <v>202.22</v>
+        <v>202.25</v>
       </c>
       <c r="O49" t="n">
-        <v>222.68</v>
+        <v>222.71</v>
       </c>
       <c r="P49" t="n">
         <v>1.63</v>
       </c>
       <c r="Q49" t="n">
-        <v>67.14</v>
+        <v>67.19</v>
       </c>
       <c r="R49" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="S49" t="n">
-        <v>-2.29</v>
+        <v>-2.28</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5947,22 +5947,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10.3</v>
+        <v>10.32</v>
       </c>
       <c r="D50" t="n">
         <v>74</v>
       </c>
       <c r="E50" t="n">
-        <v>-5.29</v>
+        <v>-5.01</v>
       </c>
       <c r="F50" t="n">
-        <v>11.66</v>
+        <v>11.98</v>
       </c>
       <c r="G50" t="n">
-        <v>0.44</v>
+        <v>0.73</v>
       </c>
       <c r="H50" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="I50" t="n">
         <v>0.31</v>
@@ -5971,31 +5971,31 @@
         <v>0.79</v>
       </c>
       <c r="K50" t="n">
-        <v>7.72</v>
+        <v>7.69</v>
       </c>
       <c r="L50" t="n">
-        <v>10.02</v>
+        <v>10.05</v>
       </c>
       <c r="M50" t="n">
-        <v>10.41</v>
+        <v>10.44</v>
       </c>
       <c r="N50" t="n">
-        <v>9.220000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="O50" t="n">
-        <v>12.04</v>
+        <v>12.07</v>
       </c>
       <c r="P50" t="n">
         <v>1.62</v>
       </c>
       <c r="Q50" t="n">
-        <v>59.83</v>
+        <v>60.11</v>
       </c>
       <c r="R50" t="n">
-        <v>7.51</v>
+        <v>7.81</v>
       </c>
       <c r="S50" t="n">
-        <v>-8</v>
+        <v>-7.73</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6056,22 +6056,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>44.44</v>
+        <v>44.51</v>
       </c>
       <c r="D51" t="n">
         <v>74</v>
       </c>
       <c r="E51" t="n">
-        <v>-3.54</v>
+        <v>-3.38</v>
       </c>
       <c r="F51" t="n">
-        <v>9.67</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>-4.91</v>
+        <v>-4.75</v>
       </c>
       <c r="H51" t="n">
-        <v>0.21</v>
+        <v>0.44</v>
       </c>
       <c r="I51" t="n">
         <v>0.49</v>
@@ -6083,28 +6083,28 @@
         <v>3.13</v>
       </c>
       <c r="L51" t="n">
-        <v>43.95</v>
+        <v>44.03</v>
       </c>
       <c r="M51" t="n">
-        <v>44.65</v>
+        <v>44.72</v>
       </c>
       <c r="N51" t="n">
-        <v>42.56</v>
+        <v>42.63</v>
       </c>
       <c r="O51" t="n">
-        <v>47.5</v>
+        <v>47.58</v>
       </c>
       <c r="P51" t="n">
         <v>1.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>65.67</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="R51" t="n">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="S51" t="n">
-        <v>-7.01</v>
+        <v>-6.85</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6165,22 +6165,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1829.82</v>
+        <v>1831.59</v>
       </c>
       <c r="D52" t="n">
         <v>71</v>
       </c>
       <c r="E52" t="n">
-        <v>-2.11</v>
+        <v>-2.01</v>
       </c>
       <c r="F52" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="G52" t="n">
-        <v>24.49</v>
+        <v>24.61</v>
       </c>
       <c r="H52" t="n">
-        <v>-7.32</v>
+        <v>-7.18</v>
       </c>
       <c r="I52" t="n">
         <v>0.36</v>
@@ -6189,31 +6189,31 @@
         <v>87.39</v>
       </c>
       <c r="K52" t="n">
-        <v>4.78</v>
+        <v>4.77</v>
       </c>
       <c r="L52" t="n">
-        <v>1799.23</v>
+        <v>1801</v>
       </c>
       <c r="M52" t="n">
-        <v>1842.93</v>
+        <v>1844.7</v>
       </c>
       <c r="N52" t="n">
-        <v>1711.84</v>
+        <v>1713.61</v>
       </c>
       <c r="O52" t="n">
-        <v>2022.08</v>
+        <v>2023.85</v>
       </c>
       <c r="P52" t="n">
         <v>1.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>44.73</v>
+        <v>44.85</v>
       </c>
       <c r="R52" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="S52" t="n">
-        <v>-5.65</v>
+        <v>-5.56</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6274,55 +6274,55 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>262.24</v>
+        <v>261.87</v>
       </c>
       <c r="D53" t="n">
         <v>65</v>
       </c>
       <c r="E53" t="n">
-        <v>-3.83</v>
+        <v>-3.96</v>
       </c>
       <c r="F53" t="n">
-        <v>4.66</v>
+        <v>4.51</v>
       </c>
       <c r="G53" t="n">
-        <v>28.01</v>
+        <v>27.83</v>
       </c>
       <c r="H53" t="n">
-        <v>-4.8</v>
+        <v>-4.91</v>
       </c>
       <c r="I53" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J53" t="n">
         <v>7.19</v>
       </c>
       <c r="K53" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="L53" t="n">
-        <v>259.72</v>
+        <v>259.35</v>
       </c>
       <c r="M53" t="n">
-        <v>263.32</v>
+        <v>262.95</v>
       </c>
       <c r="N53" t="n">
-        <v>252.54</v>
+        <v>252.17</v>
       </c>
       <c r="O53" t="n">
-        <v>278.05</v>
+        <v>277.68</v>
       </c>
       <c r="P53" t="n">
         <v>1.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>51.36</v>
+        <v>50.9</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.83</v>
+        <v>-0.96</v>
       </c>
       <c r="S53" t="n">
-        <v>-5.86</v>
+        <v>-5.99</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6383,25 +6383,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>277.75</v>
+        <v>278.09</v>
       </c>
       <c r="D54" t="n">
         <v>65</v>
       </c>
       <c r="E54" t="n">
-        <v>-2.26</v>
+        <v>-2.14</v>
       </c>
       <c r="F54" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="G54" t="n">
-        <v>5.16</v>
+        <v>5.29</v>
       </c>
       <c r="H54" t="n">
-        <v>-8.75</v>
+        <v>-8.58</v>
       </c>
       <c r="I54" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="J54" t="n">
         <v>4.68</v>
@@ -6410,28 +6410,28 @@
         <v>1.68</v>
       </c>
       <c r="L54" t="n">
-        <v>276.11</v>
+        <v>276.45</v>
       </c>
       <c r="M54" t="n">
-        <v>278.45</v>
+        <v>278.79</v>
       </c>
       <c r="N54" t="n">
-        <v>271.44</v>
+        <v>271.78</v>
       </c>
       <c r="O54" t="n">
-        <v>288.04</v>
+        <v>288.38</v>
       </c>
       <c r="P54" t="n">
         <v>1.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>50.73</v>
+        <v>51.15</v>
       </c>
       <c r="R54" t="n">
-        <v>-0.58</v>
+        <v>-0.46</v>
       </c>
       <c r="S54" t="n">
-        <v>-3.42</v>
+        <v>-3.3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6492,22 +6492,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>86.23</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="D55" t="n">
         <v>70</v>
       </c>
       <c r="E55" t="n">
-        <v>-5.86</v>
+        <v>-5.88</v>
       </c>
       <c r="F55" t="n">
-        <v>28.82</v>
+        <v>28.79</v>
       </c>
       <c r="G55" t="n">
-        <v>7.44</v>
+        <v>7.41</v>
       </c>
       <c r="H55" t="n">
-        <v>19.36</v>
+        <v>19.37</v>
       </c>
       <c r="I55" t="n">
         <v>0.25</v>
@@ -6519,28 +6519,28 @@
         <v>7.81</v>
       </c>
       <c r="L55" t="n">
-        <v>83.87</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>87.23999999999999</v>
+        <v>87.22</v>
       </c>
       <c r="N55" t="n">
-        <v>77.14</v>
+        <v>77.12</v>
       </c>
       <c r="O55" t="n">
-        <v>101.05</v>
+        <v>101.03</v>
       </c>
       <c r="P55" t="n">
         <v>1.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>66.04000000000001</v>
+        <v>66.03</v>
       </c>
       <c r="R55" t="n">
-        <v>7.72</v>
+        <v>7.69</v>
       </c>
       <c r="S55" t="n">
-        <v>-10.47</v>
+        <v>-10.49</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6605,25 +6605,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>58.65</v>
+        <v>58.72</v>
       </c>
       <c r="D56" t="n">
         <v>95</v>
       </c>
       <c r="E56" t="n">
-        <v>10.6</v>
+        <v>10.73</v>
       </c>
       <c r="F56" t="n">
-        <v>9.039999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="G56" t="n">
-        <v>14.36</v>
+        <v>14.49</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.42</v>
+        <v>-0.25</v>
       </c>
       <c r="I56" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="J56" t="n">
         <v>1.97</v>
@@ -6632,28 +6632,28 @@
         <v>3.35</v>
       </c>
       <c r="L56" t="n">
-        <v>57.96</v>
+        <v>58.03</v>
       </c>
       <c r="M56" t="n">
-        <v>58.95</v>
+        <v>59.02</v>
       </c>
       <c r="N56" t="n">
-        <v>55.99</v>
+        <v>56.06</v>
       </c>
       <c r="O56" t="n">
-        <v>62.98</v>
+        <v>63.05</v>
       </c>
       <c r="P56" t="n">
         <v>1.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>53.43</v>
+        <v>53.59</v>
       </c>
       <c r="R56" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="S56" t="n">
-        <v>-3.52</v>
+        <v>-3.41</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>XLE 7.15% · CL=F 20.35%</t>
+          <t>XLE 7.28% · CL=F 20.52%</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.15% · CL=F 20.35%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.28% · CL=F 20.52%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -6714,25 +6714,25 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>113.68</v>
+        <v>113.86</v>
       </c>
       <c r="D57" t="n">
         <v>96</v>
       </c>
       <c r="E57" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="F57" t="n">
-        <v>12.89</v>
+        <v>13.07</v>
       </c>
       <c r="G57" t="n">
-        <v>23.92</v>
+        <v>24.12</v>
       </c>
       <c r="H57" t="n">
-        <v>3.43</v>
+        <v>3.65</v>
       </c>
       <c r="I57" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J57" t="n">
         <v>2.27</v>
@@ -6741,28 +6741,28 @@
         <v>2</v>
       </c>
       <c r="L57" t="n">
-        <v>112.88</v>
+        <v>113.06</v>
       </c>
       <c r="M57" t="n">
-        <v>114.02</v>
+        <v>114.2</v>
       </c>
       <c r="N57" t="n">
-        <v>110.61</v>
+        <v>110.79</v>
       </c>
       <c r="O57" t="n">
-        <v>118.68</v>
+        <v>118.86</v>
       </c>
       <c r="P57" t="n">
         <v>1.63</v>
       </c>
       <c r="Q57" t="n">
-        <v>75.09999999999999</v>
+        <v>75.84</v>
       </c>
       <c r="R57" t="n">
-        <v>6.21</v>
+        <v>6.37</v>
       </c>
       <c r="S57" t="n">
-        <v>-1.68</v>
+        <v>-1.52</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6827,22 +6827,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>300.95</v>
+        <v>301.13</v>
       </c>
       <c r="D58" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E58" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="F58" t="n">
-        <v>11.47</v>
+        <v>11.54</v>
       </c>
       <c r="G58" t="n">
-        <v>15.6</v>
+        <v>15.67</v>
       </c>
       <c r="H58" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="I58" t="n">
         <v>0.49</v>
@@ -6854,28 +6854,28 @@
         <v>2.2</v>
       </c>
       <c r="L58" t="n">
-        <v>298.63</v>
+        <v>298.81</v>
       </c>
       <c r="M58" t="n">
-        <v>301.95</v>
+        <v>302.13</v>
       </c>
       <c r="N58" t="n">
-        <v>292</v>
+        <v>292.17</v>
       </c>
       <c r="O58" t="n">
-        <v>315.55</v>
+        <v>315.72</v>
       </c>
       <c r="P58" t="n">
         <v>1.63</v>
       </c>
       <c r="Q58" t="n">
-        <v>88.62</v>
+        <v>88.67</v>
       </c>
       <c r="R58" t="n">
-        <v>6.95</v>
+        <v>7.01</v>
       </c>
       <c r="S58" t="n">
-        <v>-0.61</v>
+        <v>-0.55</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo</t>
+          <t>RSI sobrecomprado; Volumen bajo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
@@ -6955,7 +6955,7 @@
         <v>40.77</v>
       </c>
       <c r="H59" t="n">
-        <v>24.1</v>
+        <v>24.14</v>
       </c>
       <c r="I59" t="n">
         <v>0.26</v>
@@ -6970,25 +6970,25 @@
         <v>302.16</v>
       </c>
       <c r="M59" t="n">
-        <v>306.8</v>
+        <v>306.79</v>
       </c>
       <c r="N59" t="n">
         <v>292.89</v>
       </c>
       <c r="O59" t="n">
-        <v>325.8</v>
+        <v>325.79</v>
       </c>
       <c r="P59" t="n">
         <v>1.63</v>
       </c>
       <c r="Q59" t="n">
-        <v>78.36</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="R59" t="n">
         <v>10.04</v>
       </c>
       <c r="S59" t="n">
-        <v>-1.57</v>
+        <v>-1.58</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7053,22 +7053,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>52.01</v>
+        <v>51.97</v>
       </c>
       <c r="D60" t="n">
         <v>87</v>
       </c>
       <c r="E60" t="n">
-        <v>5.63</v>
+        <v>5.54</v>
       </c>
       <c r="F60" t="n">
-        <v>12.84</v>
+        <v>12.76</v>
       </c>
       <c r="G60" t="n">
-        <v>55.58</v>
+        <v>55.46</v>
       </c>
       <c r="H60" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="I60" t="n">
         <v>0.48</v>
@@ -7077,31 +7077,31 @@
         <v>4.72</v>
       </c>
       <c r="K60" t="n">
-        <v>9.07</v>
+        <v>9.08</v>
       </c>
       <c r="L60" t="n">
-        <v>50.36</v>
+        <v>50.32</v>
       </c>
       <c r="M60" t="n">
-        <v>52.72</v>
+        <v>52.68</v>
       </c>
       <c r="N60" t="n">
-        <v>45.64</v>
+        <v>45.6</v>
       </c>
       <c r="O60" t="n">
-        <v>62.39</v>
+        <v>62.35</v>
       </c>
       <c r="P60" t="n">
         <v>1.63</v>
       </c>
       <c r="Q60" t="n">
-        <v>61.19</v>
+        <v>61.13</v>
       </c>
       <c r="R60" t="n">
-        <v>7.31</v>
+        <v>7.23</v>
       </c>
       <c r="S60" t="n">
-        <v>-12.07</v>
+        <v>-12.14</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7166,25 +7166,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>121.76</v>
+        <v>121.78</v>
       </c>
       <c r="D61" t="n">
         <v>85</v>
       </c>
       <c r="E61" t="n">
-        <v>6.74</v>
+        <v>6.76</v>
       </c>
       <c r="F61" t="n">
-        <v>48.78</v>
+        <v>48.8</v>
       </c>
       <c r="G61" t="n">
-        <v>49.09</v>
+        <v>49.11</v>
       </c>
       <c r="H61" t="n">
-        <v>39.32</v>
+        <v>39.38</v>
       </c>
       <c r="I61" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="J61" t="n">
         <v>4.97</v>
@@ -7193,28 +7193,28 @@
         <v>4.08</v>
       </c>
       <c r="L61" t="n">
-        <v>120.02</v>
+        <v>120.04</v>
       </c>
       <c r="M61" t="n">
-        <v>122.51</v>
+        <v>122.53</v>
       </c>
       <c r="N61" t="n">
-        <v>115.05</v>
+        <v>115.07</v>
       </c>
       <c r="O61" t="n">
-        <v>132.7</v>
+        <v>132.72</v>
       </c>
       <c r="P61" t="n">
         <v>1.63</v>
       </c>
       <c r="Q61" t="n">
-        <v>91.94</v>
+        <v>91.98</v>
       </c>
       <c r="R61" t="n">
-        <v>26.05</v>
+        <v>26.07</v>
       </c>
       <c r="S61" t="n">
-        <v>-0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7279,55 +7279,55 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>176.81</v>
+        <v>177.07</v>
       </c>
       <c r="D62" t="n">
         <v>96</v>
       </c>
       <c r="E62" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="F62" t="n">
-        <v>14.55</v>
+        <v>14.72</v>
       </c>
       <c r="G62" t="n">
-        <v>26.26</v>
+        <v>26.45</v>
       </c>
       <c r="H62" t="n">
-        <v>5.09</v>
+        <v>5.3</v>
       </c>
       <c r="I62" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="J62" t="n">
         <v>3.76</v>
       </c>
       <c r="K62" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="L62" t="n">
-        <v>175.49</v>
+        <v>175.76</v>
       </c>
       <c r="M62" t="n">
-        <v>177.37</v>
+        <v>177.64</v>
       </c>
       <c r="N62" t="n">
-        <v>171.73</v>
+        <v>172</v>
       </c>
       <c r="O62" t="n">
-        <v>185.08</v>
+        <v>185.35</v>
       </c>
       <c r="P62" t="n">
         <v>1.63</v>
       </c>
       <c r="Q62" t="n">
-        <v>74.53</v>
+        <v>75.13</v>
       </c>
       <c r="R62" t="n">
-        <v>6.79</v>
+        <v>6.94</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.89</v>
+        <v>-1.75</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -7392,22 +7392,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>396.13</v>
+        <v>396.05</v>
       </c>
       <c r="D63" t="n">
         <v>92</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.17</v>
+        <v>-1.19</v>
       </c>
       <c r="F63" t="n">
-        <v>15.94</v>
+        <v>15.91</v>
       </c>
       <c r="G63" t="n">
-        <v>30.89</v>
+        <v>30.86</v>
       </c>
       <c r="H63" t="n">
-        <v>6.48</v>
+        <v>6.49</v>
       </c>
       <c r="I63" t="n">
         <v>0.34</v>
@@ -7419,28 +7419,28 @@
         <v>2.8</v>
       </c>
       <c r="L63" t="n">
-        <v>392.25</v>
+        <v>392.17</v>
       </c>
       <c r="M63" t="n">
-        <v>397.79</v>
+        <v>397.71</v>
       </c>
       <c r="N63" t="n">
-        <v>381.18</v>
+        <v>381.1</v>
       </c>
       <c r="O63" t="n">
-        <v>420.49</v>
+        <v>420.4</v>
       </c>
       <c r="P63" t="n">
         <v>1.63</v>
       </c>
       <c r="Q63" t="n">
-        <v>74.95</v>
+        <v>74.88</v>
       </c>
       <c r="R63" t="n">
-        <v>6.24</v>
+        <v>6.22</v>
       </c>
       <c r="S63" t="n">
-        <v>-1.88</v>
+        <v>-1.9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7505,55 +7505,55 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>731.5</v>
+        <v>732.98</v>
       </c>
       <c r="D64" t="n">
         <v>87</v>
       </c>
       <c r="E64" t="n">
-        <v>-2.05</v>
+        <v>-1.85</v>
       </c>
       <c r="F64" t="n">
-        <v>60.74</v>
+        <v>61.07</v>
       </c>
       <c r="G64" t="n">
-        <v>75.34999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="H64" t="n">
-        <v>51.28</v>
+        <v>51.65</v>
       </c>
       <c r="I64" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="J64" t="n">
         <v>53.45</v>
       </c>
       <c r="K64" t="n">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="L64" t="n">
-        <v>712.79</v>
+        <v>714.27</v>
       </c>
       <c r="M64" t="n">
-        <v>739.52</v>
+        <v>741</v>
       </c>
       <c r="N64" t="n">
-        <v>659.35</v>
+        <v>660.83</v>
       </c>
       <c r="O64" t="n">
-        <v>849.08</v>
+        <v>850.5599999999999</v>
       </c>
       <c r="P64" t="n">
         <v>1.63</v>
       </c>
       <c r="Q64" t="n">
-        <v>71.04000000000001</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="R64" t="n">
-        <v>20.71</v>
+        <v>20.94</v>
       </c>
       <c r="S64" t="n">
-        <v>-10.65</v>
+        <v>-10.47</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -7618,22 +7618,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>311.1</v>
+        <v>311.51</v>
       </c>
       <c r="D65" t="n">
         <v>75</v>
       </c>
       <c r="E65" t="n">
-        <v>3.88</v>
+        <v>4.02</v>
       </c>
       <c r="F65" t="n">
-        <v>18.12</v>
+        <v>18.27</v>
       </c>
       <c r="G65" t="n">
-        <v>-12.59</v>
+        <v>-12.47</v>
       </c>
       <c r="H65" t="n">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="I65" t="n">
         <v>0.35</v>
@@ -7642,31 +7642,31 @@
         <v>16.08</v>
       </c>
       <c r="K65" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
       <c r="L65" t="n">
-        <v>305.47</v>
+        <v>305.88</v>
       </c>
       <c r="M65" t="n">
-        <v>313.51</v>
+        <v>313.92</v>
       </c>
       <c r="N65" t="n">
-        <v>289.4</v>
+        <v>289.81</v>
       </c>
       <c r="O65" t="n">
-        <v>346.47</v>
+        <v>346.88</v>
       </c>
       <c r="P65" t="n">
         <v>1.63</v>
       </c>
       <c r="Q65" t="n">
-        <v>73.86</v>
+        <v>73.97</v>
       </c>
       <c r="R65" t="n">
-        <v>12.88</v>
+        <v>13.02</v>
       </c>
       <c r="S65" t="n">
-        <v>-1.93</v>
+        <v>-1.8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7731,25 +7731,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>159.01</v>
+        <v>159.19</v>
       </c>
       <c r="D66" t="n">
         <v>73</v>
       </c>
       <c r="E66" t="n">
-        <v>4.53</v>
+        <v>4.64</v>
       </c>
       <c r="F66" t="n">
-        <v>18.07</v>
+        <v>18.2</v>
       </c>
       <c r="G66" t="n">
-        <v>-5.9</v>
+        <v>-5.8</v>
       </c>
       <c r="H66" t="n">
-        <v>8.609999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J66" t="n">
         <v>7.56</v>
@@ -7758,28 +7758,28 @@
         <v>4.75</v>
       </c>
       <c r="L66" t="n">
-        <v>156.37</v>
+        <v>156.54</v>
       </c>
       <c r="M66" t="n">
-        <v>160.15</v>
+        <v>160.32</v>
       </c>
       <c r="N66" t="n">
-        <v>148.81</v>
+        <v>148.98</v>
       </c>
       <c r="O66" t="n">
-        <v>175.65</v>
+        <v>175.82</v>
       </c>
       <c r="P66" t="n">
         <v>1.63</v>
       </c>
       <c r="Q66" t="n">
-        <v>72.37</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="R66" t="n">
-        <v>11.65</v>
+        <v>11.77</v>
       </c>
       <c r="S66" t="n">
-        <v>-0.21</v>
+        <v>-0.1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MACD positivo; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7844,22 +7844,22 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>206.45</v>
+        <v>206.3</v>
       </c>
       <c r="D67" t="n">
         <v>71</v>
       </c>
       <c r="E67" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="F67" t="n">
-        <v>63.06</v>
+        <v>62.94</v>
       </c>
       <c r="G67" t="n">
-        <v>71.19</v>
+        <v>71.06</v>
       </c>
       <c r="H67" t="n">
-        <v>53.6</v>
+        <v>53.52</v>
       </c>
       <c r="I67" t="n">
         <v>0.3</v>
@@ -7871,28 +7871,28 @@
         <v>5.67</v>
       </c>
       <c r="L67" t="n">
-        <v>202.35</v>
+        <v>202.2</v>
       </c>
       <c r="M67" t="n">
-        <v>208.21</v>
+        <v>208.05</v>
       </c>
       <c r="N67" t="n">
-        <v>190.65</v>
+        <v>190.5</v>
       </c>
       <c r="O67" t="n">
-        <v>232.2</v>
+        <v>232.04</v>
       </c>
       <c r="P67" t="n">
         <v>1.63</v>
       </c>
       <c r="Q67" t="n">
-        <v>88.73</v>
+        <v>88.72</v>
       </c>
       <c r="R67" t="n">
-        <v>30.61</v>
+        <v>30.52</v>
       </c>
       <c r="S67" t="n">
-        <v>-0.75</v>
+        <v>-0.82</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -7957,22 +7957,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>431.91</v>
+        <v>430.81</v>
       </c>
       <c r="D68" t="n">
         <v>80</v>
       </c>
       <c r="E68" t="n">
-        <v>-5.11</v>
+        <v>-5.36</v>
       </c>
       <c r="F68" t="n">
-        <v>55.15</v>
+        <v>54.75</v>
       </c>
       <c r="G68" t="n">
-        <v>112.38</v>
+        <v>111.84</v>
       </c>
       <c r="H68" t="n">
-        <v>45.69</v>
+        <v>45.33</v>
       </c>
       <c r="I68" t="n">
         <v>0.32</v>
@@ -7981,31 +7981,31 @@
         <v>27.56</v>
       </c>
       <c r="K68" t="n">
-        <v>6.38</v>
+        <v>6.4</v>
       </c>
       <c r="L68" t="n">
-        <v>422.26</v>
+        <v>421.16</v>
       </c>
       <c r="M68" t="n">
-        <v>436.04</v>
+        <v>434.94</v>
       </c>
       <c r="N68" t="n">
-        <v>394.7</v>
+        <v>393.6</v>
       </c>
       <c r="O68" t="n">
-        <v>492.54</v>
+        <v>491.44</v>
       </c>
       <c r="P68" t="n">
         <v>1.63</v>
       </c>
       <c r="Q68" t="n">
-        <v>69.76000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="R68" t="n">
-        <v>16.07</v>
+        <v>15.79</v>
       </c>
       <c r="S68" t="n">
-        <v>-7.95</v>
+        <v>-8.19</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8066,25 +8066,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>239.45</v>
+        <v>239.7</v>
       </c>
       <c r="D69" t="n">
         <v>65</v>
       </c>
       <c r="E69" t="n">
-        <v>15.19</v>
+        <v>15.31</v>
       </c>
       <c r="F69" t="n">
-        <v>42.66</v>
+        <v>42.81</v>
       </c>
       <c r="G69" t="n">
-        <v>58.59</v>
+        <v>58.75</v>
       </c>
       <c r="H69" t="n">
-        <v>33.2</v>
+        <v>33.39</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>9.119999999999999</v>
@@ -8093,28 +8093,28 @@
         <v>3.81</v>
       </c>
       <c r="L69" t="n">
-        <v>236.26</v>
+        <v>236.51</v>
       </c>
       <c r="M69" t="n">
-        <v>240.82</v>
+        <v>241.07</v>
       </c>
       <c r="N69" t="n">
-        <v>227.13</v>
+        <v>227.38</v>
       </c>
       <c r="O69" t="n">
-        <v>259.52</v>
+        <v>259.77</v>
       </c>
       <c r="P69" t="n">
         <v>1.63</v>
       </c>
       <c r="Q69" t="n">
-        <v>92.47</v>
+        <v>92.5</v>
       </c>
       <c r="R69" t="n">
-        <v>23.6</v>
+        <v>23.72</v>
       </c>
       <c r="S69" t="n">
-        <v>-0.41</v>
+        <v>-0.3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8175,25 +8175,25 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>587.97</v>
+        <v>587.87</v>
       </c>
       <c r="D70" t="n">
         <v>65</v>
       </c>
       <c r="E70" t="n">
-        <v>11.41</v>
+        <v>11.39</v>
       </c>
       <c r="F70" t="n">
-        <v>38.69</v>
+        <v>38.66</v>
       </c>
       <c r="G70" t="n">
-        <v>39.28</v>
+        <v>39.26</v>
       </c>
       <c r="H70" t="n">
-        <v>29.23</v>
+        <v>29.24</v>
       </c>
       <c r="I70" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="J70" t="n">
         <v>22.24</v>
@@ -8202,16 +8202,16 @@
         <v>3.78</v>
       </c>
       <c r="L70" t="n">
-        <v>580.1900000000001</v>
+        <v>580.09</v>
       </c>
       <c r="M70" t="n">
-        <v>591.3099999999999</v>
+        <v>591.21</v>
       </c>
       <c r="N70" t="n">
-        <v>557.9400000000001</v>
+        <v>557.84</v>
       </c>
       <c r="O70" t="n">
-        <v>636.9</v>
+        <v>636.8</v>
       </c>
       <c r="P70" t="n">
         <v>1.63</v>
@@ -8220,10 +8220,10 @@
         <v>89.51000000000001</v>
       </c>
       <c r="R70" t="n">
-        <v>20.33</v>
+        <v>20.31</v>
       </c>
       <c r="S70" t="n">
-        <v>-0.41</v>
+        <v>-0.43</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -8284,22 +8284,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>200.58</v>
+        <v>200.78</v>
       </c>
       <c r="D71" t="n">
         <v>60</v>
       </c>
       <c r="E71" t="n">
-        <v>-8.449999999999999</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>47.27</v>
+        <v>47.42</v>
       </c>
       <c r="G71" t="n">
-        <v>42.9</v>
+        <v>43.04</v>
       </c>
       <c r="H71" t="n">
-        <v>37.81</v>
+        <v>38</v>
       </c>
       <c r="I71" t="n">
         <v>0.4</v>
@@ -8308,31 +8308,31 @@
         <v>18.68</v>
       </c>
       <c r="K71" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>194.04</v>
+        <v>194.24</v>
       </c>
       <c r="M71" t="n">
-        <v>203.38</v>
+        <v>203.58</v>
       </c>
       <c r="N71" t="n">
-        <v>175.36</v>
+        <v>175.56</v>
       </c>
       <c r="O71" t="n">
-        <v>241.67</v>
+        <v>241.87</v>
       </c>
       <c r="P71" t="n">
         <v>1.63</v>
       </c>
       <c r="Q71" t="n">
-        <v>66.34999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="R71" t="n">
-        <v>13.46</v>
+        <v>13.57</v>
       </c>
       <c r="S71" t="n">
-        <v>-19.09</v>
+        <v>-19.01</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>SOXX 23.39% · QQQ 9.46%</t>
+          <t>SOXX 23.2% · QQQ 9.42%</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.39% · QQQ 9.46%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: SOXX 23.2% · QQQ 9.42%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8393,22 +8393,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>392.86</v>
+        <v>393.1</v>
       </c>
       <c r="D72" t="n">
         <v>96</v>
       </c>
       <c r="E72" t="n">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="F72" t="n">
-        <v>21.02</v>
+        <v>21.09</v>
       </c>
       <c r="G72" t="n">
-        <v>36.56</v>
+        <v>36.64</v>
       </c>
       <c r="H72" t="n">
-        <v>11.56</v>
+        <v>11.67</v>
       </c>
       <c r="I72" t="n">
         <v>0.38</v>
@@ -8420,28 +8420,28 @@
         <v>2.28</v>
       </c>
       <c r="L72" t="n">
-        <v>389.73</v>
+        <v>389.97</v>
       </c>
       <c r="M72" t="n">
-        <v>394.21</v>
+        <v>394.44</v>
       </c>
       <c r="N72" t="n">
-        <v>380.79</v>
+        <v>381.02</v>
       </c>
       <c r="O72" t="n">
-        <v>412.54</v>
+        <v>412.78</v>
       </c>
       <c r="P72" t="n">
         <v>1.63</v>
       </c>
       <c r="Q72" t="n">
-        <v>76.34999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="R72" t="n">
-        <v>6.33</v>
+        <v>6.39</v>
       </c>
       <c r="S72" t="n">
-        <v>-2.79</v>
+        <v>-2.73</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8506,22 +8506,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1003.79</v>
+        <v>1004.27</v>
       </c>
       <c r="D73" t="n">
         <v>90</v>
       </c>
       <c r="E73" t="n">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
       <c r="F73" t="n">
-        <v>8.279999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="G73" t="n">
-        <v>-1.9</v>
+        <v>-1.85</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.18</v>
+        <v>-1.09</v>
       </c>
       <c r="I73" t="n">
         <v>0.28</v>
@@ -8533,28 +8533,28 @@
         <v>3.21</v>
       </c>
       <c r="L73" t="n">
-        <v>992.5</v>
+        <v>992.98</v>
       </c>
       <c r="M73" t="n">
-        <v>1008.63</v>
+        <v>1009.1</v>
       </c>
       <c r="N73" t="n">
-        <v>960.26</v>
+        <v>960.74</v>
       </c>
       <c r="O73" t="n">
-        <v>1074.73</v>
+        <v>1075.2</v>
       </c>
       <c r="P73" t="n">
         <v>1.63</v>
       </c>
       <c r="Q73" t="n">
-        <v>73.7</v>
+        <v>73.83</v>
       </c>
       <c r="R73" t="n">
-        <v>6.29</v>
+        <v>6.34</v>
       </c>
       <c r="S73" t="n">
-        <v>-1.86</v>
+        <v>-1.81</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8606,64 +8606,64 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>106.38</v>
+        <v>86.92</v>
       </c>
       <c r="D74" t="n">
         <v>84</v>
       </c>
       <c r="E74" t="n">
-        <v>1.38</v>
+        <v>2.96</v>
       </c>
       <c r="F74" t="n">
         <v>6.38</v>
       </c>
       <c r="G74" t="n">
-        <v>11.04</v>
+        <v>17.6</v>
       </c>
       <c r="H74" t="n">
-        <v>-3.08</v>
+        <v>-3.04</v>
       </c>
       <c r="I74" t="n">
         <v>0.38</v>
       </c>
       <c r="J74" t="n">
-        <v>3.03</v>
+        <v>2.56</v>
       </c>
       <c r="K74" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="L74" t="n">
-        <v>105.32</v>
+        <v>86.02</v>
       </c>
       <c r="M74" t="n">
-        <v>106.83</v>
+        <v>87.3</v>
       </c>
       <c r="N74" t="n">
-        <v>102.29</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="O74" t="n">
-        <v>113.04</v>
+        <v>92.56</v>
       </c>
       <c r="P74" t="n">
         <v>1.63</v>
       </c>
       <c r="Q74" t="n">
-        <v>74.08</v>
+        <v>72.83</v>
       </c>
       <c r="R74" t="n">
-        <v>3.13</v>
+        <v>6.38</v>
       </c>
       <c r="S74" t="n">
-        <v>-2.3</v>
+        <v>-1.72</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8715,64 +8715,64 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Consumo</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>86.78</v>
+        <v>106.24</v>
       </c>
       <c r="D75" t="n">
         <v>84</v>
       </c>
       <c r="E75" t="n">
-        <v>2.79</v>
+        <v>1.24</v>
       </c>
       <c r="F75" t="n">
-        <v>6.2</v>
+        <v>6.24</v>
       </c>
       <c r="G75" t="n">
-        <v>17.41</v>
+        <v>10.89</v>
       </c>
       <c r="H75" t="n">
-        <v>-3.26</v>
+        <v>-3.18</v>
       </c>
       <c r="I75" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J75" t="n">
-        <v>2.56</v>
+        <v>3.03</v>
       </c>
       <c r="K75" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="L75" t="n">
-        <v>85.88</v>
+        <v>105.18</v>
       </c>
       <c r="M75" t="n">
-        <v>87.16</v>
+        <v>106.69</v>
       </c>
       <c r="N75" t="n">
-        <v>83.31</v>
+        <v>102.15</v>
       </c>
       <c r="O75" t="n">
-        <v>92.42</v>
+        <v>112.9</v>
       </c>
       <c r="P75" t="n">
         <v>1.63</v>
       </c>
       <c r="Q75" t="n">
-        <v>72.31999999999999</v>
+        <v>73.47</v>
       </c>
       <c r="R75" t="n">
-        <v>6.21</v>
+        <v>3</v>
       </c>
       <c r="S75" t="n">
-        <v>-1.88</v>
+        <v>-2.43</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8833,25 +8833,25 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>709.84</v>
+        <v>710.71</v>
       </c>
       <c r="D76" t="n">
         <v>78</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F76" t="n">
-        <v>9.4</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>17.77</v>
+        <v>17.92</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.06</v>
+        <v>0.11</v>
       </c>
       <c r="I76" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="J76" t="n">
         <v>10.65</v>
@@ -8860,28 +8860,28 @@
         <v>1.5</v>
       </c>
       <c r="L76" t="n">
-        <v>706.11</v>
+        <v>706.98</v>
       </c>
       <c r="M76" t="n">
-        <v>711.4400000000001</v>
+        <v>712.3099999999999</v>
       </c>
       <c r="N76" t="n">
-        <v>695.46</v>
+        <v>696.33</v>
       </c>
       <c r="O76" t="n">
-        <v>733.27</v>
+        <v>734.14</v>
       </c>
       <c r="P76" t="n">
         <v>1.63</v>
       </c>
       <c r="Q76" t="n">
-        <v>73.95999999999999</v>
+        <v>74.64</v>
       </c>
       <c r="R76" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="S76" t="n">
-        <v>-1.69</v>
+        <v>-1.57</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8942,22 +8942,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>23.31</v>
+        <v>23.3</v>
       </c>
       <c r="D77" t="n">
         <v>69</v>
       </c>
       <c r="E77" t="n">
-        <v>-3.2</v>
+        <v>-3.24</v>
       </c>
       <c r="F77" t="n">
-        <v>28.71</v>
+        <v>28.66</v>
       </c>
       <c r="G77" t="n">
-        <v>43.71</v>
+        <v>43.65</v>
       </c>
       <c r="H77" t="n">
-        <v>19.25</v>
+        <v>19.24</v>
       </c>
       <c r="I77" t="n">
         <v>0.32</v>
@@ -8969,28 +8969,28 @@
         <v>7.15</v>
       </c>
       <c r="L77" t="n">
-        <v>22.73</v>
+        <v>22.72</v>
       </c>
       <c r="M77" t="n">
-        <v>23.56</v>
+        <v>23.55</v>
       </c>
       <c r="N77" t="n">
-        <v>21.06</v>
+        <v>21.05</v>
       </c>
       <c r="O77" t="n">
-        <v>26.97</v>
+        <v>26.96</v>
       </c>
       <c r="P77" t="n">
         <v>1.63</v>
       </c>
       <c r="Q77" t="n">
-        <v>67.26000000000001</v>
+        <v>67.22</v>
       </c>
       <c r="R77" t="n">
-        <v>13.43</v>
+        <v>13.38</v>
       </c>
       <c r="S77" t="n">
-        <v>-9.859999999999999</v>
+        <v>-9.9</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>BTC-USD 2.01% · ETH-USD -4.15%</t>
+          <t>BTC-USD 2.0% · ETH-USD -4.11%</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 2.01% · ETH-USD -4.15%; RSI algo alto; Volumen bajo; Momentum negativo; Muy alejada de MA20</t>
+          <t>Sector no acompaña: BTC-USD 2.0% · ETH-USD -4.11%; RSI algo alto; Volumen bajo; Momentum negativo; Muy alejada de MA20</t>
         </is>
       </c>
     </row>
@@ -9051,55 +9051,55 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>242.52</v>
+        <v>242.24</v>
       </c>
       <c r="D78" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E78" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="F78" t="n">
-        <v>-3.18</v>
+        <v>-3.29</v>
       </c>
       <c r="G78" t="n">
-        <v>7.47</v>
+        <v>7.34</v>
       </c>
       <c r="H78" t="n">
-        <v>-12.64</v>
+        <v>-12.71</v>
       </c>
       <c r="I78" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="J78" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="L78" t="n">
-        <v>239.61</v>
+        <v>239.33</v>
       </c>
       <c r="M78" t="n">
-        <v>243.77</v>
+        <v>243.49</v>
       </c>
       <c r="N78" t="n">
-        <v>231.31</v>
+        <v>231.03</v>
       </c>
       <c r="O78" t="n">
-        <v>260.79</v>
+        <v>260.51</v>
       </c>
       <c r="P78" t="n">
         <v>1.63</v>
       </c>
       <c r="Q78" t="n">
-        <v>38.15</v>
+        <v>37.89</v>
       </c>
       <c r="R78" t="n">
-        <v>-5.14</v>
+        <v>-5.24</v>
       </c>
       <c r="S78" t="n">
-        <v>-11.75</v>
+        <v>-11.85</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>XLE 7.15% · CL=F 20.35%</t>
+          <t>XLE 7.28% · CL=F 20.52%</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.15% · CL=F 20.35%; Tendencia larga positiva; MACD mejorando; Momentum 5D sano</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.28% · CL=F 20.52%; Tendencia larga positiva; MACD mejorando; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ; Lejos del máximo 20D</t>
+          <t>Precio bajo MA20; RSI débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -9164,22 +9164,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>144.74</v>
+        <v>144.77</v>
       </c>
       <c r="D79" t="n">
         <v>46</v>
       </c>
       <c r="E79" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="F79" t="n">
-        <v>-11.87</v>
+        <v>-11.85</v>
       </c>
       <c r="G79" t="n">
-        <v>5.47</v>
+        <v>5.49</v>
       </c>
       <c r="H79" t="n">
-        <v>-21.33</v>
+        <v>-21.27</v>
       </c>
       <c r="I79" t="n">
         <v>0.34</v>
@@ -9191,28 +9191,28 @@
         <v>5.95</v>
       </c>
       <c r="L79" t="n">
-        <v>141.72</v>
+        <v>141.76</v>
       </c>
       <c r="M79" t="n">
-        <v>146.03</v>
+        <v>146.06</v>
       </c>
       <c r="N79" t="n">
-        <v>133.12</v>
+        <v>133.15</v>
       </c>
       <c r="O79" t="n">
-        <v>163.68</v>
+        <v>163.71</v>
       </c>
       <c r="P79" t="n">
         <v>1.63</v>
       </c>
       <c r="Q79" t="n">
-        <v>29.93</v>
+        <v>29.94</v>
       </c>
       <c r="R79" t="n">
-        <v>-9.66</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="S79" t="n">
-        <v>-19.5</v>
+        <v>-19.48</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -9277,22 +9277,22 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>393.69</v>
+        <v>393.38</v>
       </c>
       <c r="D80" t="n">
         <v>50</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.66</v>
+        <v>-0.74</v>
       </c>
       <c r="F80" t="n">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="G80" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="H80" t="n">
-        <v>-9.35</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="I80" t="n">
         <v>0.46</v>
@@ -9304,28 +9304,28 @@
         <v>4.29</v>
       </c>
       <c r="L80" t="n">
-        <v>387.78</v>
+        <v>387.47</v>
       </c>
       <c r="M80" t="n">
-        <v>396.22</v>
+        <v>395.91</v>
       </c>
       <c r="N80" t="n">
-        <v>370.9</v>
+        <v>370.59</v>
       </c>
       <c r="O80" t="n">
-        <v>430.83</v>
+        <v>430.52</v>
       </c>
       <c r="P80" t="n">
         <v>1.63</v>
       </c>
       <c r="Q80" t="n">
-        <v>51.4</v>
+        <v>51.29</v>
       </c>
       <c r="R80" t="n">
-        <v>-0.23</v>
+        <v>-0.31</v>
       </c>
       <c r="S80" t="n">
-        <v>-6.04</v>
+        <v>-6.11</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; RSI saludable; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; RSI saludable; MACD mejorando</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -9386,25 +9386,25 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>245.29</v>
+        <v>245.32</v>
       </c>
       <c r="D81" t="n">
         <v>43</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.06</v>
+        <v>-3.05</v>
       </c>
       <c r="F81" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="G81" t="n">
-        <v>-5.37</v>
+        <v>-5.36</v>
       </c>
       <c r="H81" t="n">
-        <v>-9.109999999999999</v>
+        <v>-9.06</v>
       </c>
       <c r="I81" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>8.26</v>
@@ -9413,28 +9413,28 @@
         <v>3.37</v>
       </c>
       <c r="L81" t="n">
-        <v>242.4</v>
+        <v>242.43</v>
       </c>
       <c r="M81" t="n">
-        <v>246.53</v>
+        <v>246.56</v>
       </c>
       <c r="N81" t="n">
-        <v>234.14</v>
+        <v>234.17</v>
       </c>
       <c r="O81" t="n">
-        <v>263.47</v>
+        <v>263.5</v>
       </c>
       <c r="P81" t="n">
         <v>1.63</v>
       </c>
       <c r="Q81" t="n">
-        <v>55.18</v>
+        <v>55.2</v>
       </c>
       <c r="R81" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="S81" t="n">
-        <v>-5.45</v>
+        <v>-5.44</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; RSI saludable; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; RSI saludable; MACD mejorando</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -9501,31 +9501,31 @@
         <v>36</v>
       </c>
       <c r="E82" t="n">
-        <v>-12.01</v>
+        <v>-11.96</v>
       </c>
       <c r="F82" t="n">
-        <v>-6.01</v>
+        <v>-5.95</v>
       </c>
       <c r="G82" t="n">
-        <v>-18.83</v>
+        <v>-18.79</v>
       </c>
       <c r="H82" t="n">
-        <v>-15.47</v>
+        <v>-15.37</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="J82" t="n">
         <v>0.45</v>
       </c>
       <c r="K82" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="L82" t="n">
         <v>8.529999999999999</v>
       </c>
       <c r="M82" t="n">
-        <v>8.75</v>
+        <v>8.76</v>
       </c>
       <c r="N82" t="n">
         <v>8.08</v>
@@ -9534,16 +9534,16 @@
         <v>9.68</v>
       </c>
       <c r="P82" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q82" t="n">
-        <v>48.43</v>
+        <v>48.5</v>
       </c>
       <c r="R82" t="n">
-        <v>-4.6</v>
+        <v>-4.55</v>
       </c>
       <c r="S82" t="n">
-        <v>-12.1</v>
+        <v>-12.04</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9604,25 +9604,25 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>74.73999999999999</v>
+        <v>74.75</v>
       </c>
       <c r="D83" t="n">
         <v>29</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.95</v>
+        <v>-0.93</v>
       </c>
       <c r="F83" t="n">
-        <v>-3.09</v>
+        <v>-3.07</v>
       </c>
       <c r="G83" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H83" t="n">
-        <v>-12.55</v>
+        <v>-12.49</v>
       </c>
       <c r="I83" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>2.59</v>
@@ -9631,28 +9631,28 @@
         <v>3.47</v>
       </c>
       <c r="L83" t="n">
-        <v>73.83</v>
+        <v>73.84</v>
       </c>
       <c r="M83" t="n">
-        <v>75.12</v>
+        <v>75.14</v>
       </c>
       <c r="N83" t="n">
-        <v>71.23999999999999</v>
+        <v>71.25</v>
       </c>
       <c r="O83" t="n">
-        <v>80.44</v>
+        <v>80.45</v>
       </c>
       <c r="P83" t="n">
         <v>1.63</v>
       </c>
       <c r="Q83" t="n">
-        <v>45.71</v>
+        <v>45.76</v>
       </c>
       <c r="R83" t="n">
-        <v>-0.96</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S83" t="n">
-        <v>-7.54</v>
+        <v>-7.52</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MA20 sobre MA50</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>613.52</v>
+        <v>613.51</v>
       </c>
       <c r="D84" t="n">
         <v>27</v>
@@ -9728,10 +9728,10 @@
         <v>-4.77</v>
       </c>
       <c r="H84" t="n">
-        <v>-20.36</v>
+        <v>-20.32</v>
       </c>
       <c r="I84" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="J84" t="n">
         <v>17.08</v>
@@ -9740,16 +9740,16 @@
         <v>2.78</v>
       </c>
       <c r="L84" t="n">
-        <v>607.54</v>
+        <v>607.53</v>
       </c>
       <c r="M84" t="n">
-        <v>616.08</v>
+        <v>616.0700000000001</v>
       </c>
       <c r="N84" t="n">
-        <v>590.47</v>
+        <v>590.46</v>
       </c>
       <c r="O84" t="n">
-        <v>651.09</v>
+        <v>651.08</v>
       </c>
       <c r="P84" t="n">
         <v>1.63</v>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MA20 sobre MA50; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MA20 sobre MA50; MACD mejorando</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -9822,25 +9822,25 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>75.09</v>
+        <v>75.25</v>
       </c>
       <c r="D85" t="n">
         <v>22</v>
       </c>
       <c r="E85" t="n">
-        <v>-5.09</v>
+        <v>-4.89</v>
       </c>
       <c r="F85" t="n">
-        <v>-5.23</v>
+        <v>-5.02</v>
       </c>
       <c r="G85" t="n">
-        <v>3.95</v>
+        <v>4.17</v>
       </c>
       <c r="H85" t="n">
-        <v>-14.69</v>
+        <v>-14.44</v>
       </c>
       <c r="I85" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="J85" t="n">
         <v>2.46</v>
@@ -9849,28 +9849,28 @@
         <v>3.28</v>
       </c>
       <c r="L85" t="n">
-        <v>74.23</v>
+        <v>74.39</v>
       </c>
       <c r="M85" t="n">
-        <v>75.45999999999999</v>
+        <v>75.62</v>
       </c>
       <c r="N85" t="n">
-        <v>71.76000000000001</v>
+        <v>71.92</v>
       </c>
       <c r="O85" t="n">
-        <v>80.51000000000001</v>
+        <v>80.67</v>
       </c>
       <c r="P85" t="n">
         <v>1.63</v>
       </c>
       <c r="Q85" t="n">
-        <v>46.53</v>
+        <v>46.89</v>
       </c>
       <c r="R85" t="n">
-        <v>-2.99</v>
+        <v>-2.79</v>
       </c>
       <c r="S85" t="n">
-        <v>-6.93</v>
+        <v>-6.74</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MA20 sobre MA50</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -9931,22 +9931,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>134.15</v>
+        <v>134.23</v>
       </c>
       <c r="D86" t="n">
         <v>22</v>
       </c>
       <c r="E86" t="n">
-        <v>-2.65</v>
+        <v>-2.59</v>
       </c>
       <c r="F86" t="n">
-        <v>-8.359999999999999</v>
+        <v>-8.31</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.55</v>
+        <v>-0.49</v>
       </c>
       <c r="H86" t="n">
-        <v>-17.82</v>
+        <v>-17.73</v>
       </c>
       <c r="I86" t="n">
         <v>0.38</v>
@@ -9958,28 +9958,28 @@
         <v>4.23</v>
       </c>
       <c r="L86" t="n">
-        <v>132.16</v>
+        <v>132.24</v>
       </c>
       <c r="M86" t="n">
-        <v>135</v>
+        <v>135.08</v>
       </c>
       <c r="N86" t="n">
-        <v>126.49</v>
+        <v>126.56</v>
       </c>
       <c r="O86" t="n">
-        <v>146.63</v>
+        <v>146.71</v>
       </c>
       <c r="P86" t="n">
         <v>1.63</v>
       </c>
       <c r="Q86" t="n">
-        <v>39.16</v>
+        <v>39.27</v>
       </c>
       <c r="R86" t="n">
-        <v>-4.04</v>
+        <v>-3.99</v>
       </c>
       <c r="S86" t="n">
-        <v>-12.14</v>
+        <v>-12.09</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -10040,22 +10040,22 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>174.12</v>
+        <v>174.15</v>
       </c>
       <c r="D87" t="n">
         <v>15</v>
       </c>
       <c r="E87" t="n">
-        <v>-4.23</v>
+        <v>-4.22</v>
       </c>
       <c r="F87" t="n">
-        <v>-4.4</v>
+        <v>-4.39</v>
       </c>
       <c r="G87" t="n">
-        <v>-5.79</v>
+        <v>-5.78</v>
       </c>
       <c r="H87" t="n">
-        <v>-13.86</v>
+        <v>-13.81</v>
       </c>
       <c r="I87" t="n">
         <v>0.47</v>
@@ -10067,28 +10067,28 @@
         <v>3.91</v>
       </c>
       <c r="L87" t="n">
-        <v>171.74</v>
+        <v>171.76</v>
       </c>
       <c r="M87" t="n">
-        <v>175.14</v>
+        <v>175.17</v>
       </c>
       <c r="N87" t="n">
-        <v>164.93</v>
+        <v>164.96</v>
       </c>
       <c r="O87" t="n">
-        <v>189.1</v>
+        <v>189.12</v>
       </c>
       <c r="P87" t="n">
         <v>1.63</v>
       </c>
       <c r="Q87" t="n">
-        <v>44.6</v>
+        <v>44.63</v>
       </c>
       <c r="R87" t="n">
-        <v>-3.16</v>
+        <v>-3.14</v>
       </c>
       <c r="S87" t="n">
-        <v>-10.04</v>
+        <v>-10.03</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -10149,19 +10149,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>218.76</v>
+        <v>218.65</v>
       </c>
       <c r="D88" t="n">
         <v>15</v>
       </c>
       <c r="E88" t="n">
-        <v>-4.79</v>
+        <v>-4.84</v>
       </c>
       <c r="F88" t="n">
-        <v>-13.06</v>
+        <v>-13.1</v>
       </c>
       <c r="G88" t="n">
-        <v>-14.01</v>
+        <v>-14.06</v>
       </c>
       <c r="H88" t="n">
         <v>-22.52</v>
@@ -10176,28 +10176,28 @@
         <v>2.56</v>
       </c>
       <c r="L88" t="n">
-        <v>216.8</v>
+        <v>216.69</v>
       </c>
       <c r="M88" t="n">
-        <v>219.59</v>
+        <v>219.49</v>
       </c>
       <c r="N88" t="n">
-        <v>211.2</v>
+        <v>211.09</v>
       </c>
       <c r="O88" t="n">
-        <v>231.07</v>
+        <v>230.97</v>
       </c>
       <c r="P88" t="n">
         <v>1.63</v>
       </c>
       <c r="Q88" t="n">
-        <v>41.92</v>
+        <v>41.79</v>
       </c>
       <c r="R88" t="n">
-        <v>-4.71</v>
+        <v>-4.76</v>
       </c>
       <c r="S88" t="n">
-        <v>-14.75</v>
+        <v>-14.79</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -10258,55 +10258,55 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>167.38</v>
+        <v>167.5</v>
       </c>
       <c r="D89" t="n">
         <v>15</v>
       </c>
       <c r="E89" t="n">
-        <v>-7.23</v>
+        <v>-7.16</v>
       </c>
       <c r="F89" t="n">
-        <v>-15.31</v>
+        <v>-15.25</v>
       </c>
       <c r="G89" t="n">
-        <v>-21.47</v>
+        <v>-21.41</v>
       </c>
       <c r="H89" t="n">
-        <v>-24.77</v>
+        <v>-24.67</v>
       </c>
       <c r="I89" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="J89" t="n">
         <v>6.81</v>
       </c>
       <c r="K89" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="L89" t="n">
-        <v>165</v>
+        <v>165.12</v>
       </c>
       <c r="M89" t="n">
-        <v>168.4</v>
+        <v>168.52</v>
       </c>
       <c r="N89" t="n">
-        <v>158.19</v>
+        <v>158.31</v>
       </c>
       <c r="O89" t="n">
-        <v>182.36</v>
+        <v>182.48</v>
       </c>
       <c r="P89" t="n">
         <v>1.63</v>
       </c>
       <c r="Q89" t="n">
-        <v>39.61</v>
+        <v>39.77</v>
       </c>
       <c r="R89" t="n">
-        <v>-5.89</v>
+        <v>-5.83</v>
       </c>
       <c r="S89" t="n">
-        <v>-16.13</v>
+        <v>-16.07</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -10367,22 +10367,22 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>87.09999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="D90" t="n">
         <v>14</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.45</v>
+        <v>-0.49</v>
       </c>
       <c r="F90" t="n">
-        <v>-10.5</v>
+        <v>-10.53</v>
       </c>
       <c r="G90" t="n">
-        <v>13.11</v>
+        <v>13.07</v>
       </c>
       <c r="H90" t="n">
-        <v>-19.96</v>
+        <v>-19.95</v>
       </c>
       <c r="I90" t="n">
         <v>0.41</v>
@@ -10394,28 +10394,28 @@
         <v>2.7</v>
       </c>
       <c r="L90" t="n">
-        <v>86.27</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="M90" t="n">
-        <v>87.45</v>
+        <v>87.42</v>
       </c>
       <c r="N90" t="n">
-        <v>83.92</v>
+        <v>83.89</v>
       </c>
       <c r="O90" t="n">
-        <v>92.27</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="P90" t="n">
         <v>1.63</v>
       </c>
       <c r="Q90" t="n">
-        <v>35.3</v>
+        <v>35.17</v>
       </c>
       <c r="R90" t="n">
-        <v>-3.49</v>
+        <v>-3.53</v>
       </c>
       <c r="S90" t="n">
-        <v>-10.76</v>
+        <v>-10.79</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -10476,25 +10476,25 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>111.51</v>
+        <v>111.5</v>
       </c>
       <c r="D91" t="n">
         <v>57</v>
       </c>
       <c r="E91" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F91" t="n">
-        <v>-6.35</v>
+        <v>-6.36</v>
       </c>
       <c r="G91" t="n">
         <v>-7.82</v>
       </c>
       <c r="H91" t="n">
-        <v>-15.81</v>
+        <v>-15.78</v>
       </c>
       <c r="I91" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="J91" t="n">
         <v>2.66</v>
@@ -10503,28 +10503,28 @@
         <v>2.39</v>
       </c>
       <c r="L91" t="n">
-        <v>110.58</v>
+        <v>110.57</v>
       </c>
       <c r="M91" t="n">
-        <v>111.91</v>
+        <v>111.9</v>
       </c>
       <c r="N91" t="n">
-        <v>107.92</v>
+        <v>107.91</v>
       </c>
       <c r="O91" t="n">
-        <v>117.37</v>
+        <v>117.36</v>
       </c>
       <c r="P91" t="n">
         <v>1.63</v>
       </c>
       <c r="Q91" t="n">
-        <v>54.69</v>
+        <v>54.65</v>
       </c>
       <c r="R91" t="n">
-        <v>-0.75</v>
+        <v>-0.76</v>
       </c>
       <c r="S91" t="n">
-        <v>-6.58</v>
+        <v>-6.59</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10585,22 +10585,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>283.06</v>
+        <v>282.99</v>
       </c>
       <c r="D92" t="n">
         <v>35</v>
       </c>
       <c r="E92" t="n">
-        <v>-4.74</v>
+        <v>-4.76</v>
       </c>
       <c r="F92" t="n">
-        <v>-6.93</v>
+        <v>-6.95</v>
       </c>
       <c r="G92" t="n">
-        <v>-15.32</v>
+        <v>-15.34</v>
       </c>
       <c r="H92" t="n">
-        <v>-16.39</v>
+        <v>-16.37</v>
       </c>
       <c r="I92" t="n">
         <v>0.3</v>
@@ -10612,28 +10612,28 @@
         <v>3.39</v>
       </c>
       <c r="L92" t="n">
-        <v>279.7</v>
+        <v>279.64</v>
       </c>
       <c r="M92" t="n">
-        <v>284.5</v>
+        <v>284.43</v>
       </c>
       <c r="N92" t="n">
-        <v>270.11</v>
+        <v>270.05</v>
       </c>
       <c r="O92" t="n">
-        <v>304.16</v>
+        <v>304.1</v>
       </c>
       <c r="P92" t="n">
         <v>1.63</v>
       </c>
       <c r="Q92" t="n">
-        <v>49.08</v>
+        <v>49.04</v>
       </c>
       <c r="R92" t="n">
-        <v>-2.52</v>
+        <v>-2.54</v>
       </c>
       <c r="S92" t="n">
-        <v>-8.69</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10694,25 +10694,25 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>70.56999999999999</v>
+        <v>70.64</v>
       </c>
       <c r="D93" t="n">
         <v>33</v>
       </c>
       <c r="E93" t="n">
-        <v>-5.72</v>
+        <v>-5.62</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.98</v>
+        <v>-0.86</v>
       </c>
       <c r="G93" t="n">
-        <v>33.42</v>
+        <v>33.57</v>
       </c>
       <c r="H93" t="n">
-        <v>-10.44</v>
+        <v>-10.28</v>
       </c>
       <c r="I93" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="J93" t="n">
         <v>2.58</v>
@@ -10721,28 +10721,28 @@
         <v>3.66</v>
       </c>
       <c r="L93" t="n">
-        <v>69.66</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="M93" t="n">
-        <v>70.95</v>
+        <v>71.03</v>
       </c>
       <c r="N93" t="n">
-        <v>67.08</v>
+        <v>67.16</v>
       </c>
       <c r="O93" t="n">
-        <v>76.25</v>
+        <v>76.33</v>
       </c>
       <c r="P93" t="n">
         <v>1.63</v>
       </c>
       <c r="Q93" t="n">
-        <v>48.07</v>
+        <v>48.28</v>
       </c>
       <c r="R93" t="n">
-        <v>-1.2</v>
+        <v>-1.09</v>
       </c>
       <c r="S93" t="n">
-        <v>-8.550000000000001</v>
+        <v>-8.44</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10803,22 +10803,22 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>123.08</v>
+        <v>123.19</v>
       </c>
       <c r="D94" t="n">
         <v>33</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.97</v>
+        <v>-1.88</v>
       </c>
       <c r="F94" t="n">
-        <v>-6.44</v>
+        <v>-6.36</v>
       </c>
       <c r="G94" t="n">
-        <v>7.02</v>
+        <v>7.12</v>
       </c>
       <c r="H94" t="n">
-        <v>-15.9</v>
+        <v>-15.78</v>
       </c>
       <c r="I94" t="n">
         <v>0.22</v>
@@ -10830,28 +10830,28 @@
         <v>2.69</v>
       </c>
       <c r="L94" t="n">
-        <v>121.92</v>
+        <v>122.03</v>
       </c>
       <c r="M94" t="n">
-        <v>123.58</v>
+        <v>123.69</v>
       </c>
       <c r="N94" t="n">
-        <v>118.61</v>
+        <v>118.72</v>
       </c>
       <c r="O94" t="n">
-        <v>130.36</v>
+        <v>130.47</v>
       </c>
       <c r="P94" t="n">
         <v>1.63</v>
       </c>
       <c r="Q94" t="n">
-        <v>34.1</v>
+        <v>34.32</v>
       </c>
       <c r="R94" t="n">
-        <v>-3.31</v>
+        <v>-3.22</v>
       </c>
       <c r="S94" t="n">
-        <v>-8.59</v>
+        <v>-8.51</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10912,25 +10912,25 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>51.11</v>
+        <v>51.13</v>
       </c>
       <c r="D95" t="n">
         <v>28</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="F95" t="n">
-        <v>-2.52</v>
+        <v>-2.47</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.49</v>
+        <v>-1.44</v>
       </c>
       <c r="H95" t="n">
-        <v>-11.98</v>
+        <v>-11.89</v>
       </c>
       <c r="I95" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0.64</v>
@@ -10939,28 +10939,28 @@
         <v>1.24</v>
       </c>
       <c r="L95" t="n">
-        <v>50.89</v>
+        <v>50.91</v>
       </c>
       <c r="M95" t="n">
-        <v>51.21</v>
+        <v>51.23</v>
       </c>
       <c r="N95" t="n">
-        <v>50.25</v>
+        <v>50.28</v>
       </c>
       <c r="O95" t="n">
-        <v>52.51</v>
+        <v>52.53</v>
       </c>
       <c r="P95" t="n">
         <v>1.63</v>
       </c>
       <c r="Q95" t="n">
-        <v>39.26</v>
+        <v>39.57</v>
       </c>
       <c r="R95" t="n">
-        <v>-1.14</v>
+        <v>-1.09</v>
       </c>
       <c r="S95" t="n">
-        <v>-3.91</v>
+        <v>-3.86</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11021,22 +11021,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>557.66</v>
+        <v>558.0700000000001</v>
       </c>
       <c r="D96" t="n">
         <v>28</v>
       </c>
       <c r="E96" t="n">
-        <v>-2.99</v>
+        <v>-2.92</v>
       </c>
       <c r="F96" t="n">
-        <v>-5.56</v>
+        <v>-5.49</v>
       </c>
       <c r="G96" t="n">
-        <v>-15.52</v>
+        <v>-15.45</v>
       </c>
       <c r="H96" t="n">
-        <v>-15.02</v>
+        <v>-14.91</v>
       </c>
       <c r="I96" t="n">
         <v>0.33</v>
@@ -11048,28 +11048,28 @@
         <v>2.68</v>
       </c>
       <c r="L96" t="n">
-        <v>552.42</v>
+        <v>552.84</v>
       </c>
       <c r="M96" t="n">
-        <v>559.9</v>
+        <v>560.3099999999999</v>
       </c>
       <c r="N96" t="n">
-        <v>537.46</v>
+        <v>537.88</v>
       </c>
       <c r="O96" t="n">
-        <v>590.5599999999999</v>
+        <v>590.97</v>
       </c>
       <c r="P96" t="n">
         <v>1.63</v>
       </c>
       <c r="Q96" t="n">
-        <v>46.21</v>
+        <v>46.36</v>
       </c>
       <c r="R96" t="n">
-        <v>-3.58</v>
+        <v>-3.51</v>
       </c>
       <c r="S96" t="n">
-        <v>-6.85</v>
+        <v>-6.78</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11130,22 +11130,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>84.64</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="D97" t="n">
         <v>26</v>
       </c>
       <c r="E97" t="n">
-        <v>0.38</v>
+        <v>0.52</v>
       </c>
       <c r="F97" t="n">
-        <v>-12.57</v>
+        <v>-12.45</v>
       </c>
       <c r="G97" t="n">
-        <v>-24.08</v>
+        <v>-23.98</v>
       </c>
       <c r="H97" t="n">
-        <v>-22.03</v>
+        <v>-21.87</v>
       </c>
       <c r="I97" t="n">
         <v>0.44</v>
@@ -11157,28 +11157,28 @@
         <v>2.44</v>
       </c>
       <c r="L97" t="n">
-        <v>83.92</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="M97" t="n">
-        <v>84.95</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N97" t="n">
-        <v>81.84999999999999</v>
+        <v>81.97</v>
       </c>
       <c r="O97" t="n">
-        <v>89.19</v>
+        <v>89.31</v>
       </c>
       <c r="P97" t="n">
         <v>1.63</v>
       </c>
       <c r="Q97" t="n">
-        <v>26.58</v>
+        <v>26.76</v>
       </c>
       <c r="R97" t="n">
-        <v>-4.63</v>
+        <v>-4.5</v>
       </c>
       <c r="S97" t="n">
-        <v>-13.03</v>
+        <v>-12.91</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11239,19 +11239,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>44.93</v>
+        <v>44.91</v>
       </c>
       <c r="D98" t="n">
         <v>24</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.97</v>
+        <v>-1.01</v>
       </c>
       <c r="F98" t="n">
-        <v>-11.57</v>
+        <v>-11.61</v>
       </c>
       <c r="G98" t="n">
-        <v>7.99</v>
+        <v>7.95</v>
       </c>
       <c r="H98" t="n">
         <v>-21.03</v>
@@ -11263,31 +11263,31 @@
         <v>1.51</v>
       </c>
       <c r="K98" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="L98" t="n">
-        <v>44.4</v>
+        <v>44.38</v>
       </c>
       <c r="M98" t="n">
-        <v>45.16</v>
+        <v>45.14</v>
       </c>
       <c r="N98" t="n">
-        <v>42.89</v>
+        <v>42.87</v>
       </c>
       <c r="O98" t="n">
-        <v>48.26</v>
+        <v>48.24</v>
       </c>
       <c r="P98" t="n">
         <v>1.63</v>
       </c>
       <c r="Q98" t="n">
-        <v>22.44</v>
+        <v>22.39</v>
       </c>
       <c r="R98" t="n">
-        <v>-6.9</v>
+        <v>-6.94</v>
       </c>
       <c r="S98" t="n">
-        <v>-14.09</v>
+        <v>-14.13</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11348,55 +11348,55 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>76.62</v>
+        <v>76.77</v>
       </c>
       <c r="D99" t="n">
         <v>22</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.53</v>
+        <v>-0.34</v>
       </c>
       <c r="F99" t="n">
-        <v>-15.57</v>
+        <v>-15.4</v>
       </c>
       <c r="G99" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="H99" t="n">
-        <v>-25.03</v>
+        <v>-24.82</v>
       </c>
       <c r="I99" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="J99" t="n">
         <v>4.44</v>
       </c>
       <c r="K99" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="L99" t="n">
-        <v>75.06999999999999</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="M99" t="n">
-        <v>77.29000000000001</v>
+        <v>77.44</v>
       </c>
       <c r="N99" t="n">
-        <v>70.62</v>
+        <v>70.77</v>
       </c>
       <c r="O99" t="n">
-        <v>86.39</v>
+        <v>86.55</v>
       </c>
       <c r="P99" t="n">
         <v>1.63</v>
       </c>
       <c r="Q99" t="n">
-        <v>40.82</v>
+        <v>40.98</v>
       </c>
       <c r="R99" t="n">
-        <v>-4.06</v>
+        <v>-3.88</v>
       </c>
       <c r="S99" t="n">
-        <v>-17.06</v>
+        <v>-16.9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>-3.93</v>
       </c>
       <c r="H100" t="n">
-        <v>-15.83</v>
+        <v>-15.79</v>
       </c>
       <c r="I100" t="n">
         <v>0.43</v>
@@ -11566,22 +11566,22 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>222.35</v>
+        <v>222.67</v>
       </c>
       <c r="D101" t="n">
         <v>19</v>
       </c>
       <c r="E101" t="n">
-        <v>-6.32</v>
+        <v>-6.19</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.46</v>
+        <v>-0.32</v>
       </c>
       <c r="G101" t="n">
-        <v>-4.86</v>
+        <v>-4.72</v>
       </c>
       <c r="H101" t="n">
-        <v>-9.92</v>
+        <v>-9.74</v>
       </c>
       <c r="I101" t="n">
         <v>0.63</v>
@@ -11590,31 +11590,31 @@
         <v>7.22</v>
       </c>
       <c r="K101" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="L101" t="n">
-        <v>219.83</v>
+        <v>220.14</v>
       </c>
       <c r="M101" t="n">
-        <v>223.44</v>
+        <v>223.75</v>
       </c>
       <c r="N101" t="n">
-        <v>212.61</v>
+        <v>212.92</v>
       </c>
       <c r="O101" t="n">
-        <v>238.24</v>
+        <v>238.55</v>
       </c>
       <c r="P101" t="n">
         <v>1.63</v>
       </c>
       <c r="Q101" t="n">
-        <v>42.53</v>
+        <v>42.76</v>
       </c>
       <c r="R101" t="n">
-        <v>-3.24</v>
+        <v>-3.11</v>
       </c>
       <c r="S101" t="n">
-        <v>-8.9</v>
+        <v>-8.77</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11675,22 +11675,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>497.31</v>
+        <v>496.6</v>
       </c>
       <c r="D102" t="n">
         <v>19</v>
       </c>
       <c r="E102" t="n">
-        <v>0.37</v>
+        <v>0.23</v>
       </c>
       <c r="F102" t="n">
-        <v>-4.6</v>
+        <v>-4.74</v>
       </c>
       <c r="G102" t="n">
-        <v>-4.25</v>
+        <v>-4.38</v>
       </c>
       <c r="H102" t="n">
-        <v>-14.06</v>
+        <v>-14.16</v>
       </c>
       <c r="I102" t="n">
         <v>0.4</v>
@@ -11702,28 +11702,28 @@
         <v>2.64</v>
       </c>
       <c r="L102" t="n">
-        <v>492.72</v>
+        <v>492.01</v>
       </c>
       <c r="M102" t="n">
-        <v>499.28</v>
+        <v>498.57</v>
       </c>
       <c r="N102" t="n">
-        <v>479.62</v>
+        <v>478.91</v>
       </c>
       <c r="O102" t="n">
-        <v>526.14</v>
+        <v>525.4299999999999</v>
       </c>
       <c r="P102" t="n">
         <v>1.63</v>
       </c>
       <c r="Q102" t="n">
-        <v>45.73</v>
+        <v>45.37</v>
       </c>
       <c r="R102" t="n">
-        <v>-1.01</v>
+        <v>-1.15</v>
       </c>
       <c r="S102" t="n">
-        <v>-6.91</v>
+        <v>-7.04</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11784,22 +11784,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>297</v>
+        <v>297.27</v>
       </c>
       <c r="D103" t="n">
         <v>18</v>
       </c>
       <c r="E103" t="n">
-        <v>-1.69</v>
+        <v>-1.6</v>
       </c>
       <c r="F103" t="n">
-        <v>-4.28</v>
+        <v>-4.2</v>
       </c>
       <c r="G103" t="n">
-        <v>-3.09</v>
+        <v>-3.01</v>
       </c>
       <c r="H103" t="n">
-        <v>-13.74</v>
+        <v>-13.62</v>
       </c>
       <c r="I103" t="n">
         <v>0.41</v>
@@ -11808,31 +11808,31 @@
         <v>6.08</v>
       </c>
       <c r="K103" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="L103" t="n">
-        <v>294.87</v>
+        <v>295.14</v>
       </c>
       <c r="M103" t="n">
-        <v>297.91</v>
+        <v>298.18</v>
       </c>
       <c r="N103" t="n">
-        <v>288.8</v>
+        <v>289.07</v>
       </c>
       <c r="O103" t="n">
-        <v>310.37</v>
+        <v>310.64</v>
       </c>
       <c r="P103" t="n">
         <v>1.63</v>
       </c>
       <c r="Q103" t="n">
-        <v>34.39</v>
+        <v>34.59</v>
       </c>
       <c r="R103" t="n">
-        <v>-3.62</v>
+        <v>-3.54</v>
       </c>
       <c r="S103" t="n">
-        <v>-7.26</v>
+        <v>-7.17</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11893,22 +11893,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>49.44</v>
+        <v>49.47</v>
       </c>
       <c r="D104" t="n">
         <v>11</v>
       </c>
       <c r="E104" t="n">
-        <v>-3.65</v>
+        <v>-3.6</v>
       </c>
       <c r="F104" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.25</v>
       </c>
       <c r="G104" t="n">
-        <v>-5.79</v>
+        <v>-5.73</v>
       </c>
       <c r="H104" t="n">
-        <v>-17.76</v>
+        <v>-17.67</v>
       </c>
       <c r="I104" t="n">
         <v>0.49</v>
@@ -11920,28 +11920,28 @@
         <v>2.36</v>
       </c>
       <c r="L104" t="n">
-        <v>49.03</v>
+        <v>49.06</v>
       </c>
       <c r="M104" t="n">
-        <v>49.61</v>
+        <v>49.64</v>
       </c>
       <c r="N104" t="n">
-        <v>47.86</v>
+        <v>47.89</v>
       </c>
       <c r="O104" t="n">
-        <v>52</v>
+        <v>52.03</v>
       </c>
       <c r="P104" t="n">
         <v>1.63</v>
       </c>
       <c r="Q104" t="n">
-        <v>30.41</v>
+        <v>30.52</v>
       </c>
       <c r="R104" t="n">
-        <v>-5.24</v>
+        <v>-5.18</v>
       </c>
       <c r="S104" t="n">
-        <v>-9.539999999999999</v>
+        <v>-9.49</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12002,22 +12002,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>276.2</v>
+        <v>275.8</v>
       </c>
       <c r="D105" t="n">
         <v>11</v>
       </c>
       <c r="E105" t="n">
-        <v>0.16</v>
+        <v>0.02</v>
       </c>
       <c r="F105" t="n">
-        <v>-11.29</v>
+        <v>-11.42</v>
       </c>
       <c r="G105" t="n">
-        <v>-15.09</v>
+        <v>-15.21</v>
       </c>
       <c r="H105" t="n">
-        <v>-20.75</v>
+        <v>-20.84</v>
       </c>
       <c r="I105" t="n">
         <v>0.33</v>
@@ -12029,28 +12029,28 @@
         <v>2.01</v>
       </c>
       <c r="L105" t="n">
-        <v>274.26</v>
+        <v>273.86</v>
       </c>
       <c r="M105" t="n">
-        <v>277.03</v>
+        <v>276.63</v>
       </c>
       <c r="N105" t="n">
-        <v>268.71</v>
+        <v>268.31</v>
       </c>
       <c r="O105" t="n">
-        <v>288.4</v>
+        <v>288</v>
       </c>
       <c r="P105" t="n">
         <v>1.63</v>
       </c>
       <c r="Q105" t="n">
-        <v>28.24</v>
+        <v>27.34</v>
       </c>
       <c r="R105" t="n">
-        <v>-3.98</v>
+        <v>-4.11</v>
       </c>
       <c r="S105" t="n">
-        <v>-11.62</v>
+        <v>-11.75</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>-19.51</v>
       </c>
       <c r="H106" t="n">
-        <v>-29.51</v>
+        <v>-29.47</v>
       </c>
       <c r="I106" t="n">
         <v>0.39</v>
@@ -12220,22 +12220,22 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>72.95999999999999</v>
+        <v>73</v>
       </c>
       <c r="D107" t="n">
         <v>4</v>
       </c>
       <c r="E107" t="n">
-        <v>-3.54</v>
+        <v>-3.49</v>
       </c>
       <c r="F107" t="n">
-        <v>-9.859999999999999</v>
+        <v>-9.82</v>
       </c>
       <c r="G107" t="n">
-        <v>-16.2</v>
+        <v>-16.16</v>
       </c>
       <c r="H107" t="n">
-        <v>-19.32</v>
+        <v>-19.24</v>
       </c>
       <c r="I107" t="n">
         <v>0.31</v>
@@ -12244,31 +12244,31 @@
         <v>1.9</v>
       </c>
       <c r="K107" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="L107" t="n">
-        <v>72.3</v>
+        <v>72.33</v>
       </c>
       <c r="M107" t="n">
-        <v>73.25</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="N107" t="n">
-        <v>70.40000000000001</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="O107" t="n">
-        <v>77.15000000000001</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="P107" t="n">
         <v>1.63</v>
       </c>
       <c r="Q107" t="n">
-        <v>28.56</v>
+        <v>28.62</v>
       </c>
       <c r="R107" t="n">
-        <v>-6.91</v>
+        <v>-6.86</v>
       </c>
       <c r="S107" t="n">
-        <v>-11.69</v>
+        <v>-11.65</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12329,25 +12329,25 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>219.77</v>
+        <v>219.84</v>
       </c>
       <c r="D108" t="n">
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>-4.11</v>
+        <v>-4.08</v>
       </c>
       <c r="F108" t="n">
-        <v>-12.27</v>
+        <v>-12.25</v>
       </c>
       <c r="G108" t="n">
-        <v>-20.62</v>
+        <v>-20.59</v>
       </c>
       <c r="H108" t="n">
-        <v>-21.73</v>
+        <v>-21.67</v>
       </c>
       <c r="I108" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="J108" t="n">
         <v>6.07</v>
@@ -12356,28 +12356,28 @@
         <v>2.76</v>
       </c>
       <c r="L108" t="n">
-        <v>217.64</v>
+        <v>217.71</v>
       </c>
       <c r="M108" t="n">
-        <v>220.68</v>
+        <v>220.75</v>
       </c>
       <c r="N108" t="n">
-        <v>211.57</v>
+        <v>211.64</v>
       </c>
       <c r="O108" t="n">
-        <v>233.13</v>
+        <v>233.2</v>
       </c>
       <c r="P108" t="n">
         <v>1.63</v>
       </c>
       <c r="Q108" t="n">
-        <v>30.69</v>
+        <v>30.72</v>
       </c>
       <c r="R108" t="n">
-        <v>-6.15</v>
+        <v>-6.12</v>
       </c>
       <c r="S108" t="n">
-        <v>-14.11</v>
+        <v>-14.08</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12438,25 +12438,25 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>299.76</v>
+        <v>299.65</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>-5.57</v>
+        <v>-5.61</v>
       </c>
       <c r="F109" t="n">
-        <v>-14.21</v>
+        <v>-14.24</v>
       </c>
       <c r="G109" t="n">
-        <v>-20.29</v>
+        <v>-20.32</v>
       </c>
       <c r="H109" t="n">
-        <v>-23.67</v>
+        <v>-23.66</v>
       </c>
       <c r="I109" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="J109" t="n">
         <v>7.81</v>
@@ -12465,28 +12465,28 @@
         <v>2.61</v>
       </c>
       <c r="L109" t="n">
-        <v>297.03</v>
+        <v>296.92</v>
       </c>
       <c r="M109" t="n">
-        <v>300.93</v>
+        <v>300.82</v>
       </c>
       <c r="N109" t="n">
-        <v>289.21</v>
+        <v>289.1</v>
       </c>
       <c r="O109" t="n">
-        <v>316.95</v>
+        <v>316.84</v>
       </c>
       <c r="P109" t="n">
         <v>1.63</v>
       </c>
       <c r="Q109" t="n">
-        <v>26.55</v>
+        <v>26.51</v>
       </c>
       <c r="R109" t="n">
-        <v>-7.29</v>
+        <v>-7.33</v>
       </c>
       <c r="S109" t="n">
-        <v>-15.21</v>
+        <v>-15.25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12547,55 +12547,55 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>440.9</v>
+        <v>441.14</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>-5.18</v>
+        <v>-5.13</v>
       </c>
       <c r="F110" t="n">
-        <v>-16.27</v>
+        <v>-16.23</v>
       </c>
       <c r="G110" t="n">
-        <v>-14.32</v>
+        <v>-14.28</v>
       </c>
       <c r="H110" t="n">
-        <v>-25.73</v>
+        <v>-25.65</v>
       </c>
       <c r="I110" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J110" t="n">
         <v>13.7</v>
       </c>
       <c r="K110" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="L110" t="n">
-        <v>436.11</v>
+        <v>436.35</v>
       </c>
       <c r="M110" t="n">
-        <v>442.95</v>
+        <v>443.19</v>
       </c>
       <c r="N110" t="n">
-        <v>422.41</v>
+        <v>422.65</v>
       </c>
       <c r="O110" t="n">
-        <v>471.03</v>
+        <v>471.27</v>
       </c>
       <c r="P110" t="n">
         <v>1.63</v>
       </c>
       <c r="Q110" t="n">
-        <v>36.21</v>
+        <v>36.3</v>
       </c>
       <c r="R110" t="n">
-        <v>-6.61</v>
+        <v>-6.57</v>
       </c>
       <c r="S110" t="n">
-        <v>-18.11</v>
+        <v>-18.07</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12656,22 +12656,22 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>198.65</v>
+        <v>198.27</v>
       </c>
       <c r="D111" t="n">
         <v>49</v>
       </c>
       <c r="E111" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="F111" t="n">
-        <v>-1.16</v>
+        <v>-1.35</v>
       </c>
       <c r="G111" t="n">
-        <v>3.12</v>
+        <v>2.93</v>
       </c>
       <c r="H111" t="n">
-        <v>-10.62</v>
+        <v>-10.77</v>
       </c>
       <c r="I111" t="n">
         <v>0.27</v>
@@ -12680,31 +12680,31 @@
         <v>15.26</v>
       </c>
       <c r="K111" t="n">
-        <v>7.68</v>
+        <v>7.69</v>
       </c>
       <c r="L111" t="n">
-        <v>193.31</v>
+        <v>192.94</v>
       </c>
       <c r="M111" t="n">
-        <v>200.94</v>
+        <v>200.56</v>
       </c>
       <c r="N111" t="n">
-        <v>178.05</v>
+        <v>177.68</v>
       </c>
       <c r="O111" t="n">
-        <v>232.21</v>
+        <v>231.84</v>
       </c>
       <c r="P111" t="n">
         <v>1.63</v>
       </c>
       <c r="Q111" t="n">
-        <v>45.44</v>
+        <v>45.33</v>
       </c>
       <c r="R111" t="n">
-        <v>-6.05</v>
+        <v>-6.22</v>
       </c>
       <c r="S111" t="n">
-        <v>-23.27</v>
+        <v>-23.41</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -12769,22 +12769,22 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>122.2</v>
+        <v>122.28</v>
       </c>
       <c r="D112" t="n">
         <v>32</v>
       </c>
       <c r="E112" t="n">
-        <v>6.33</v>
+        <v>6.4</v>
       </c>
       <c r="F112" t="n">
-        <v>-10.43</v>
+        <v>-10.37</v>
       </c>
       <c r="G112" t="n">
-        <v>-23.17</v>
+        <v>-23.12</v>
       </c>
       <c r="H112" t="n">
-        <v>-19.89</v>
+        <v>-19.79</v>
       </c>
       <c r="I112" t="n">
         <v>0.35</v>
@@ -12796,28 +12796,28 @@
         <v>4.81</v>
       </c>
       <c r="L112" t="n">
-        <v>120.14</v>
+        <v>120.22</v>
       </c>
       <c r="M112" t="n">
-        <v>123.08</v>
+        <v>123.16</v>
       </c>
       <c r="N112" t="n">
-        <v>114.26</v>
+        <v>114.34</v>
       </c>
       <c r="O112" t="n">
-        <v>135.13</v>
+        <v>135.21</v>
       </c>
       <c r="P112" t="n">
         <v>1.63</v>
       </c>
       <c r="Q112" t="n">
-        <v>33.9</v>
+        <v>34.01</v>
       </c>
       <c r="R112" t="n">
-        <v>-2.3</v>
+        <v>-2.24</v>
       </c>
       <c r="S112" t="n">
-        <v>-14.2</v>
+        <v>-14.15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MACD positivo; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -12882,22 +12882,22 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>8.390000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="D113" t="n">
         <v>36</v>
       </c>
       <c r="E113" t="n">
+        <v>-5.46</v>
+      </c>
+      <c r="F113" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G113" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="H113" t="n">
         <v>-5.52</v>
-      </c>
-      <c r="F113" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="G113" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="H113" t="n">
-        <v>-5.62</v>
       </c>
       <c r="I113" t="n">
         <v>0.25</v>
@@ -12909,7 +12909,7 @@
         <v>7.79</v>
       </c>
       <c r="L113" t="n">
-        <v>8.16</v>
+        <v>8.17</v>
       </c>
       <c r="M113" t="n">
         <v>8.49</v>
@@ -12921,16 +12921,16 @@
         <v>9.83</v>
       </c>
       <c r="P113" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q113" t="n">
-        <v>52.14</v>
+        <v>52.19</v>
       </c>
       <c r="R113" t="n">
-        <v>-1.4</v>
+        <v>-1.34</v>
       </c>
       <c r="S113" t="n">
-        <v>-16.48</v>
+        <v>-16.43</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -12991,55 +12991,55 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>17.95</v>
+        <v>17.91</v>
       </c>
       <c r="D114" t="n">
         <v>32</v>
       </c>
       <c r="E114" t="n">
-        <v>-5.25</v>
+        <v>-5.46</v>
       </c>
       <c r="F114" t="n">
-        <v>-9.41</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="G114" t="n">
-        <v>8.109999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="H114" t="n">
-        <v>-18.87</v>
+        <v>-19.04</v>
       </c>
       <c r="I114" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="J114" t="n">
         <v>1.6</v>
       </c>
       <c r="K114" t="n">
-        <v>8.91</v>
+        <v>8.93</v>
       </c>
       <c r="L114" t="n">
-        <v>17.39</v>
+        <v>17.35</v>
       </c>
       <c r="M114" t="n">
-        <v>18.19</v>
+        <v>18.14</v>
       </c>
       <c r="N114" t="n">
-        <v>15.79</v>
+        <v>15.75</v>
       </c>
       <c r="O114" t="n">
-        <v>21.46</v>
+        <v>21.42</v>
       </c>
       <c r="P114" t="n">
         <v>1.63</v>
       </c>
       <c r="Q114" t="n">
-        <v>53.98</v>
+        <v>53.8</v>
       </c>
       <c r="R114" t="n">
-        <v>-1.02</v>
+        <v>-1.24</v>
       </c>
       <c r="S114" t="n">
-        <v>-14.62</v>
+        <v>-14.82</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -13100,22 +13100,22 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>155.47</v>
+        <v>155.58</v>
       </c>
       <c r="D115" t="n">
         <v>20</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.21</v>
+        <v>-0.14</v>
       </c>
       <c r="F115" t="n">
-        <v>-5.09</v>
+        <v>-5.02</v>
       </c>
       <c r="G115" t="n">
-        <v>6.39</v>
+        <v>6.47</v>
       </c>
       <c r="H115" t="n">
-        <v>-14.55</v>
+        <v>-14.44</v>
       </c>
       <c r="I115" t="n">
         <v>0.27</v>
@@ -13127,28 +13127,28 @@
         <v>6.45</v>
       </c>
       <c r="L115" t="n">
-        <v>151.96</v>
+        <v>152.07</v>
       </c>
       <c r="M115" t="n">
-        <v>156.97</v>
+        <v>157.08</v>
       </c>
       <c r="N115" t="n">
-        <v>141.93</v>
+        <v>142.04</v>
       </c>
       <c r="O115" t="n">
-        <v>177.54</v>
+        <v>177.65</v>
       </c>
       <c r="P115" t="n">
         <v>1.63</v>
       </c>
       <c r="Q115" t="n">
-        <v>46.56</v>
+        <v>46.63</v>
       </c>
       <c r="R115" t="n">
-        <v>-1.9</v>
+        <v>-1.83</v>
       </c>
       <c r="S115" t="n">
-        <v>-12.23</v>
+        <v>-12.17</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MA20 sobre MA50</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -13209,55 +13209,55 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>28.63</v>
+        <v>28.46</v>
       </c>
       <c r="D116" t="n">
         <v>18</v>
       </c>
       <c r="E116" t="n">
-        <v>-1.14</v>
+        <v>-1.73</v>
       </c>
       <c r="F116" t="n">
-        <v>-17.18</v>
+        <v>-17.67</v>
       </c>
       <c r="G116" t="n">
-        <v>-6.59</v>
+        <v>-7.15</v>
       </c>
       <c r="H116" t="n">
-        <v>-26.64</v>
+        <v>-27.09</v>
       </c>
       <c r="I116" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="J116" t="n">
         <v>1.83</v>
       </c>
       <c r="K116" t="n">
-        <v>6.38</v>
+        <v>6.42</v>
       </c>
       <c r="L116" t="n">
-        <v>27.99</v>
+        <v>27.82</v>
       </c>
       <c r="M116" t="n">
-        <v>28.9</v>
+        <v>28.73</v>
       </c>
       <c r="N116" t="n">
-        <v>26.16</v>
+        <v>25.99</v>
       </c>
       <c r="O116" t="n">
-        <v>32.65</v>
+        <v>32.48</v>
       </c>
       <c r="P116" t="n">
         <v>1.63</v>
       </c>
       <c r="Q116" t="n">
-        <v>35.11</v>
+        <v>34.71</v>
       </c>
       <c r="R116" t="n">
-        <v>-7.89</v>
+        <v>-8.41</v>
       </c>
       <c r="S116" t="n">
-        <v>-20.03</v>
+        <v>-20.5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MA20 sobre MA50; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MA20 sobre MA50; MACD mejorando</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -13318,22 +13318,22 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>20.74</v>
+        <v>20.75</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>-10.14</v>
+        <v>-10.1</v>
       </c>
       <c r="F117" t="n">
-        <v>-7.7</v>
+        <v>-7.65</v>
       </c>
       <c r="G117" t="n">
-        <v>-17.83</v>
+        <v>-17.79</v>
       </c>
       <c r="H117" t="n">
-        <v>-17.16</v>
+        <v>-17.07</v>
       </c>
       <c r="I117" t="n">
         <v>0.33</v>
@@ -13342,31 +13342,31 @@
         <v>1.25</v>
       </c>
       <c r="K117" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="L117" t="n">
-        <v>20.3</v>
+        <v>20.31</v>
       </c>
       <c r="M117" t="n">
-        <v>20.93</v>
+        <v>20.94</v>
       </c>
       <c r="N117" t="n">
-        <v>19.06</v>
+        <v>19.07</v>
       </c>
       <c r="O117" t="n">
-        <v>23.49</v>
+        <v>23.5</v>
       </c>
       <c r="P117" t="n">
         <v>1.64</v>
       </c>
       <c r="Q117" t="n">
-        <v>34.69</v>
+        <v>34.78</v>
       </c>
       <c r="R117" t="n">
-        <v>-9.74</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="S117" t="n">
-        <v>-16.61</v>
+        <v>-16.57</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -13427,25 +13427,25 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>99.93000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>-9.5</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="F118" t="n">
-        <v>-23.81</v>
+        <v>-23.79</v>
       </c>
       <c r="G118" t="n">
-        <v>-19.29</v>
+        <v>-19.26</v>
       </c>
       <c r="H118" t="n">
-        <v>-33.27</v>
+        <v>-33.21</v>
       </c>
       <c r="I118" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="J118" t="n">
         <v>6.29</v>
@@ -13454,28 +13454,28 @@
         <v>6.29</v>
       </c>
       <c r="L118" t="n">
-        <v>97.73</v>
+        <v>97.75</v>
       </c>
       <c r="M118" t="n">
-        <v>100.87</v>
+        <v>100.89</v>
       </c>
       <c r="N118" t="n">
-        <v>91.44</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="O118" t="n">
-        <v>113.75</v>
+        <v>113.78</v>
       </c>
       <c r="P118" t="n">
         <v>1.63</v>
       </c>
       <c r="Q118" t="n">
-        <v>29.41</v>
+        <v>29.44</v>
       </c>
       <c r="R118" t="n">
-        <v>-13.95</v>
+        <v>-13.93</v>
       </c>
       <c r="S118" t="n">
-        <v>-27.22</v>
+        <v>-27.2</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -13536,22 +13536,22 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6.08</v>
+        <v>6.09</v>
       </c>
       <c r="D119" t="n">
         <v>57</v>
       </c>
       <c r="E119" t="n">
-        <v>-6.22</v>
+        <v>-5.94</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.54</v>
+        <v>-0.25</v>
       </c>
       <c r="G119" t="n">
-        <v>-15.95</v>
+        <v>-15.7</v>
       </c>
       <c r="H119" t="n">
-        <v>-10</v>
+        <v>-9.67</v>
       </c>
       <c r="I119" t="n">
         <v>0.47</v>
@@ -13560,31 +13560,31 @@
         <v>0.39</v>
       </c>
       <c r="K119" t="n">
-        <v>6.49</v>
+        <v>6.47</v>
       </c>
       <c r="L119" t="n">
-        <v>5.94</v>
+        <v>5.96</v>
       </c>
       <c r="M119" t="n">
-        <v>6.14</v>
+        <v>6.15</v>
       </c>
       <c r="N119" t="n">
-        <v>5.54</v>
+        <v>5.56</v>
       </c>
       <c r="O119" t="n">
-        <v>6.95</v>
+        <v>6.96</v>
       </c>
       <c r="P119" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q119" t="n">
-        <v>53.65</v>
+        <v>54.05</v>
       </c>
       <c r="R119" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="S119" t="n">
-        <v>-9.970000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13645,22 +13645,22 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>12.3</v>
+        <v>12.35</v>
       </c>
       <c r="D120" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E120" t="n">
-        <v>-4.97</v>
+        <v>-4.6</v>
       </c>
       <c r="F120" t="n">
-        <v>6.01</v>
+        <v>6.42</v>
       </c>
       <c r="G120" t="n">
-        <v>54.49</v>
+        <v>55.09</v>
       </c>
       <c r="H120" t="n">
-        <v>-3.45</v>
+        <v>-3</v>
       </c>
       <c r="I120" t="n">
         <v>0.46</v>
@@ -13669,31 +13669,31 @@
         <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>8.119999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="L120" t="n">
-        <v>11.95</v>
+        <v>12</v>
       </c>
       <c r="M120" t="n">
-        <v>12.45</v>
+        <v>12.49</v>
       </c>
       <c r="N120" t="n">
-        <v>10.95</v>
+        <v>11</v>
       </c>
       <c r="O120" t="n">
-        <v>14.5</v>
+        <v>14.54</v>
       </c>
       <c r="P120" t="n">
         <v>1.63</v>
       </c>
       <c r="Q120" t="n">
-        <v>57.89</v>
+        <v>58.28</v>
       </c>
       <c r="R120" t="n">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="S120" t="n">
-        <v>-10.89</v>
+        <v>-10.54</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>BTC-USD 2.01% · ETH-USD -4.15%</t>
+          <t>BTC-USD 2.0% · ETH-USD -4.11%</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 2.01% · ETH-USD -4.15%; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
+          <t>Sector no acompaña: BTC-USD 2.0% · ETH-USD -4.11%; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>
@@ -13754,55 +13754,55 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>193.29</v>
+        <v>194.14</v>
       </c>
       <c r="D121" t="n">
         <v>35</v>
       </c>
       <c r="E121" t="n">
-        <v>-3.91</v>
+        <v>-3.49</v>
       </c>
       <c r="F121" t="n">
-        <v>-6.32</v>
+        <v>-5.91</v>
       </c>
       <c r="G121" t="n">
-        <v>16.48</v>
+        <v>16.99</v>
       </c>
       <c r="H121" t="n">
-        <v>-15.78</v>
+        <v>-15.33</v>
       </c>
       <c r="I121" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="J121" t="n">
         <v>14.49</v>
       </c>
       <c r="K121" t="n">
-        <v>7.49</v>
+        <v>7.46</v>
       </c>
       <c r="L121" t="n">
-        <v>188.22</v>
+        <v>189.07</v>
       </c>
       <c r="M121" t="n">
-        <v>195.47</v>
+        <v>196.31</v>
       </c>
       <c r="N121" t="n">
-        <v>173.74</v>
+        <v>174.58</v>
       </c>
       <c r="O121" t="n">
-        <v>225.17</v>
+        <v>226.01</v>
       </c>
       <c r="P121" t="n">
         <v>1.63</v>
       </c>
       <c r="Q121" t="n">
-        <v>48.52</v>
+        <v>48.88</v>
       </c>
       <c r="R121" t="n">
-        <v>-3.04</v>
+        <v>-2.64</v>
       </c>
       <c r="S121" t="n">
-        <v>-13.07</v>
+        <v>-12.69</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>BTC-USD 2.01% · ETH-USD -4.15%</t>
+          <t>BTC-USD 2.0% · ETH-USD -4.11%</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 2.01% · ETH-USD -4.15%; Precio bajo MA20; Tendencia larga débil; Momentum negativo; Débil vs QQQ</t>
+          <t>Sector no acompaña: BTC-USD 2.0% · ETH-USD -4.11%; Precio bajo MA20; Tendencia larga débil; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -13863,55 +13863,55 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>174.48</v>
+        <v>174.44</v>
       </c>
       <c r="D122" t="n">
         <v>30</v>
       </c>
       <c r="E122" t="n">
-        <v>-6.99</v>
+        <v>-7.01</v>
       </c>
       <c r="F122" t="n">
-        <v>4.78</v>
+        <v>4.76</v>
       </c>
       <c r="G122" t="n">
-        <v>34.78</v>
+        <v>34.75</v>
       </c>
       <c r="H122" t="n">
-        <v>-4.68</v>
+        <v>-4.66</v>
       </c>
       <c r="I122" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J122" t="n">
-        <v>11.4</v>
+        <v>11.44</v>
       </c>
       <c r="K122" t="n">
-        <v>6.54</v>
+        <v>6.56</v>
       </c>
       <c r="L122" t="n">
-        <v>170.48</v>
+        <v>170.44</v>
       </c>
       <c r="M122" t="n">
-        <v>176.19</v>
+        <v>176.16</v>
       </c>
       <c r="N122" t="n">
-        <v>159.08</v>
+        <v>158.99</v>
       </c>
       <c r="O122" t="n">
-        <v>199.56</v>
+        <v>199.61</v>
       </c>
       <c r="P122" t="n">
         <v>1.63</v>
       </c>
       <c r="Q122" t="n">
-        <v>52.58</v>
+        <v>52.56</v>
       </c>
       <c r="R122" t="n">
-        <v>-1.37</v>
+        <v>-1.39</v>
       </c>
       <c r="S122" t="n">
-        <v>-11.43</v>
+        <v>-11.45</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>BTC-USD 2.01% · ETH-USD -4.15%</t>
+          <t>BTC-USD 2.0% · ETH-USD -4.11%</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 2.01% · ETH-USD -4.15%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Sector no acompaña: BTC-USD 2.0% · ETH-USD -4.11%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -13972,22 +13972,22 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>20.62</v>
+        <v>20.59</v>
       </c>
       <c r="D123" t="n">
         <v>27</v>
       </c>
       <c r="E123" t="n">
-        <v>-8.619999999999999</v>
+        <v>-8.77</v>
       </c>
       <c r="F123" t="n">
-        <v>-4.91</v>
+        <v>-5.07</v>
       </c>
       <c r="G123" t="n">
-        <v>6.42</v>
+        <v>6.24</v>
       </c>
       <c r="H123" t="n">
-        <v>-14.37</v>
+        <v>-14.49</v>
       </c>
       <c r="I123" t="n">
         <v>0.44</v>
@@ -13996,31 +13996,31 @@
         <v>1.88</v>
       </c>
       <c r="K123" t="n">
-        <v>9.1</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L123" t="n">
-        <v>19.97</v>
+        <v>19.93</v>
       </c>
       <c r="M123" t="n">
-        <v>20.91</v>
+        <v>20.87</v>
       </c>
       <c r="N123" t="n">
-        <v>18.09</v>
+        <v>18.06</v>
       </c>
       <c r="O123" t="n">
-        <v>24.76</v>
+        <v>24.72</v>
       </c>
       <c r="P123" t="n">
         <v>1.63</v>
       </c>
       <c r="Q123" t="n">
-        <v>56.05</v>
+        <v>55.92</v>
       </c>
       <c r="R123" t="n">
-        <v>-1.42</v>
+        <v>-1.58</v>
       </c>
       <c r="S123" t="n">
-        <v>-16.77</v>
+        <v>-16.91</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -14081,55 +14081,55 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>197.95</v>
+        <v>197.76</v>
       </c>
       <c r="D124" t="n">
         <v>12</v>
       </c>
       <c r="E124" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="F124" t="n">
-        <v>-11.03</v>
+        <v>-11.12</v>
       </c>
       <c r="G124" t="n">
-        <v>-17.3</v>
+        <v>-17.39</v>
       </c>
       <c r="H124" t="n">
-        <v>-20.49</v>
+        <v>-20.54</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="J124" t="n">
         <v>18.01</v>
       </c>
       <c r="K124" t="n">
-        <v>9.1</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="L124" t="n">
-        <v>191.65</v>
+        <v>191.45</v>
       </c>
       <c r="M124" t="n">
-        <v>200.65</v>
+        <v>200.46</v>
       </c>
       <c r="N124" t="n">
-        <v>173.64</v>
+        <v>173.45</v>
       </c>
       <c r="O124" t="n">
-        <v>237.57</v>
+        <v>237.37</v>
       </c>
       <c r="P124" t="n">
         <v>1.63</v>
       </c>
       <c r="Q124" t="n">
-        <v>40.16</v>
+        <v>40.08</v>
       </c>
       <c r="R124" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="S124" t="n">
-        <v>-22.37</v>
+        <v>-22.45</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>QQQ 9.46% · ARKK -5.16% · SPY 4.23%</t>
+          <t>QQQ 9.42% · ARKK -5.19% · SPY 4.25%</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
@@ -14169,7 +14169,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.46% · ARKK -5.16% · SPY 4.23%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.42% · ARKK -5.19% · SPY 4.25%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -14190,25 +14190,25 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>123.57</v>
+        <v>123.56</v>
       </c>
       <c r="D125" t="n">
         <v>59</v>
       </c>
       <c r="E125" t="n">
-        <v>17.16</v>
+        <v>17.15</v>
       </c>
       <c r="F125" t="n">
-        <v>45.72</v>
+        <v>45.7</v>
       </c>
       <c r="G125" t="n">
-        <v>61.36</v>
+        <v>61.34</v>
       </c>
       <c r="H125" t="n">
-        <v>36.26</v>
+        <v>36.28</v>
       </c>
       <c r="I125" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>9.65</v>
@@ -14217,28 +14217,28 @@
         <v>7.81</v>
       </c>
       <c r="L125" t="n">
-        <v>120.19</v>
+        <v>120.18</v>
       </c>
       <c r="M125" t="n">
-        <v>125.02</v>
+        <v>125</v>
       </c>
       <c r="N125" t="n">
-        <v>110.55</v>
+        <v>110.53</v>
       </c>
       <c r="O125" t="n">
-        <v>144.79</v>
+        <v>144.78</v>
       </c>
       <c r="P125" t="n">
         <v>1.63</v>
       </c>
       <c r="Q125" t="n">
-        <v>72.33</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="R125" t="n">
-        <v>31.98</v>
+        <v>31.96</v>
       </c>
       <c r="S125" t="n">
-        <v>-7.22</v>
+        <v>-7.23</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -575,25 +575,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>420.76</v>
+        <v>420.57</v>
       </c>
       <c r="D2" t="n">
         <v>96</v>
       </c>
       <c r="E2" t="n">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="F2" t="n">
-        <v>13.28</v>
+        <v>13.22</v>
       </c>
       <c r="G2" t="n">
-        <v>22.24</v>
+        <v>22.18</v>
       </c>
       <c r="H2" t="n">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
       <c r="I2" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J2" t="n">
         <v>11.75</v>
@@ -602,28 +602,28 @@
         <v>2.79</v>
       </c>
       <c r="L2" t="n">
-        <v>416.65</v>
+        <v>416.46</v>
       </c>
       <c r="M2" t="n">
-        <v>422.52</v>
+        <v>422.33</v>
       </c>
       <c r="N2" t="n">
-        <v>404.9</v>
+        <v>404.71</v>
       </c>
       <c r="O2" t="n">
-        <v>446.6</v>
+        <v>446.41</v>
       </c>
       <c r="P2" t="n">
         <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>63.95</v>
+        <v>63.83</v>
       </c>
       <c r="R2" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.43</v>
+        <v>-3.48</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -688,25 +688,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41.39</v>
+        <v>41.38</v>
       </c>
       <c r="D3" t="n">
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="F3" t="n">
-        <v>11.41</v>
+        <v>11.4</v>
       </c>
       <c r="G3" t="n">
-        <v>17.59</v>
+        <v>17.57</v>
       </c>
       <c r="H3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I3" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="J3" t="n">
         <v>1.08</v>
@@ -721,22 +721,22 @@
         <v>41.55</v>
       </c>
       <c r="N3" t="n">
-        <v>39.93</v>
+        <v>39.92</v>
       </c>
       <c r="O3" t="n">
-        <v>43.78</v>
+        <v>43.77</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>56.55</v>
+        <v>56.53</v>
       </c>
       <c r="R3" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.52</v>
+        <v>-2.53</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>XLE 7.49% · CL=F 20.16%</t>
+          <t>XLE 7.33% · CL=F 19.77%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.49% · CL=F 20.16%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.33% · CL=F 19.77%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -801,55 +801,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>436.96</v>
+        <v>435.98</v>
       </c>
       <c r="D4" t="n">
         <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>0.35</v>
+        <v>0.13</v>
       </c>
       <c r="F4" t="n">
-        <v>10.08</v>
+        <v>9.84</v>
       </c>
       <c r="G4" t="n">
-        <v>18.15</v>
+        <v>17.89</v>
       </c>
       <c r="H4" t="n">
-        <v>0.35</v>
+        <v>0.13</v>
       </c>
       <c r="I4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="J4" t="n">
         <v>18.55</v>
       </c>
       <c r="K4" t="n">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="L4" t="n">
-        <v>430.47</v>
+        <v>429.49</v>
       </c>
       <c r="M4" t="n">
-        <v>439.74</v>
+        <v>438.77</v>
       </c>
       <c r="N4" t="n">
-        <v>411.92</v>
+        <v>410.95</v>
       </c>
       <c r="O4" t="n">
-        <v>477.77</v>
+        <v>476.79</v>
       </c>
       <c r="P4" t="n">
         <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>60.13</v>
+        <v>59.76</v>
       </c>
       <c r="R4" t="n">
-        <v>6.21</v>
+        <v>5.98</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.56</v>
+        <v>-2.78</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>55.63</v>
+        <v>55.59</v>
       </c>
       <c r="D5" t="n">
         <v>96</v>
       </c>
       <c r="E5" t="n">
-        <v>4.43</v>
+        <v>4.36</v>
       </c>
       <c r="F5" t="n">
-        <v>5.64</v>
+        <v>5.56</v>
       </c>
       <c r="G5" t="n">
-        <v>7.94</v>
+        <v>7.86</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.09</v>
+        <v>-4.15</v>
       </c>
       <c r="I5" t="n">
         <v>0.31</v>
@@ -937,28 +937,28 @@
         <v>2.58</v>
       </c>
       <c r="L5" t="n">
-        <v>55.13</v>
+        <v>55.09</v>
       </c>
       <c r="M5" t="n">
-        <v>55.85</v>
+        <v>55.81</v>
       </c>
       <c r="N5" t="n">
-        <v>53.69</v>
+        <v>53.65</v>
       </c>
       <c r="O5" t="n">
-        <v>58.79</v>
+        <v>58.75</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>52.05</v>
+        <v>51.84</v>
       </c>
       <c r="R5" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.74</v>
+        <v>-2.81</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>XLE 7.49% · CL=F 20.16%</t>
+          <t>XLE 7.33% · CL=F 19.77%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.49% · CL=F 20.16%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.33% · CL=F 19.77%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1023,25 +1023,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>189.78</v>
+        <v>189.76</v>
       </c>
       <c r="D6" t="n">
         <v>96</v>
       </c>
       <c r="E6" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
       <c r="F6" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.58</v>
+        <v>-6.57</v>
       </c>
       <c r="I6" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="J6" t="n">
         <v>4.21</v>
@@ -1050,28 +1050,28 @@
         <v>2.22</v>
       </c>
       <c r="L6" t="n">
-        <v>188.3</v>
+        <v>188.28</v>
       </c>
       <c r="M6" t="n">
-        <v>190.41</v>
+        <v>190.39</v>
       </c>
       <c r="N6" t="n">
-        <v>184.09</v>
+        <v>184.07</v>
       </c>
       <c r="O6" t="n">
-        <v>199.05</v>
+        <v>199.03</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>57.72</v>
+        <v>57.69</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.24</v>
+        <v>-2.25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>XLE 7.49% · CL=F 20.16%</t>
+          <t>XLE 7.33% · CL=F 19.77%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.49% · CL=F 20.16%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.33% · CL=F 19.77%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1136,25 +1136,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>94.88</v>
+        <v>94.87</v>
       </c>
       <c r="D7" t="n">
         <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.25</v>
+        <v>-4.26</v>
       </c>
       <c r="F7" t="n">
-        <v>20.47</v>
+        <v>20.45</v>
       </c>
       <c r="G7" t="n">
-        <v>23.69</v>
+        <v>23.68</v>
       </c>
       <c r="H7" t="n">
         <v>10.74</v>
       </c>
       <c r="I7" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="J7" t="n">
         <v>4.27</v>
@@ -1163,28 +1163,28 @@
         <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>93.39</v>
+        <v>93.38</v>
       </c>
       <c r="M7" t="n">
-        <v>95.52</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>89.12</v>
+        <v>89.11</v>
       </c>
       <c r="O7" t="n">
-        <v>104.27</v>
+        <v>104.26</v>
       </c>
       <c r="P7" t="n">
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>63.43</v>
+        <v>63.41</v>
       </c>
       <c r="R7" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>-10.41</v>
+        <v>-10.42</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1249,55 +1249,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>406.7</v>
+        <v>1517.78</v>
       </c>
       <c r="D8" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.21</v>
+        <v>-4.66</v>
       </c>
       <c r="F8" t="n">
-        <v>9.77</v>
+        <v>4.2</v>
       </c>
       <c r="G8" t="n">
-        <v>13.17</v>
+        <v>4.26</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04</v>
+        <v>-5.51</v>
       </c>
       <c r="I8" t="n">
-        <v>0.51</v>
+        <v>0.67</v>
       </c>
       <c r="J8" t="n">
-        <v>15.44</v>
+        <v>65.62</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>4.32</v>
       </c>
       <c r="L8" t="n">
-        <v>401.3</v>
+        <v>1494.81</v>
       </c>
       <c r="M8" t="n">
-        <v>409.02</v>
+        <v>1527.62</v>
       </c>
       <c r="N8" t="n">
-        <v>385.86</v>
+        <v>1429.19</v>
       </c>
       <c r="O8" t="n">
-        <v>440.66</v>
+        <v>1662.13</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>50.8</v>
+        <v>56.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.62</v>
+        <v>-5.35</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1341,19 +1341,19 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo</t>
+          <t>Volumen bajo; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1362,55 +1362,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1518.85</v>
+        <v>406.48</v>
       </c>
       <c r="D9" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.6</v>
+        <v>-1.26</v>
       </c>
       <c r="F9" t="n">
-        <v>4.27</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>4.33</v>
+        <v>13.11</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.46</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="J9" t="n">
-        <v>65.62</v>
+        <v>15.44</v>
       </c>
       <c r="K9" t="n">
-        <v>4.32</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1495.89</v>
+        <v>401.07</v>
       </c>
       <c r="M9" t="n">
-        <v>1528.7</v>
+        <v>408.79</v>
       </c>
       <c r="N9" t="n">
-        <v>1430.27</v>
+        <v>385.63</v>
       </c>
       <c r="O9" t="n">
-        <v>1663.21</v>
+        <v>440.44</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>57</v>
+        <v>50.69</v>
       </c>
       <c r="R9" t="n">
-        <v>2.73</v>
+        <v>2.14</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.28</v>
+        <v>-3.67</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Volumen bajo; Momentum negativo; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -1475,25 +1475,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>428.82</v>
+        <v>428.4</v>
       </c>
       <c r="D10" t="n">
         <v>89</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.27</v>
+        <v>-0.37</v>
       </c>
       <c r="F10" t="n">
-        <v>5.48</v>
+        <v>5.38</v>
       </c>
       <c r="G10" t="n">
-        <v>28.66</v>
+        <v>28.54</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.25</v>
+        <v>-4.33</v>
       </c>
       <c r="I10" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="J10" t="n">
         <v>17.05</v>
@@ -1502,28 +1502,28 @@
         <v>3.98</v>
       </c>
       <c r="L10" t="n">
-        <v>422.85</v>
+        <v>422.43</v>
       </c>
       <c r="M10" t="n">
-        <v>431.38</v>
+        <v>430.96</v>
       </c>
       <c r="N10" t="n">
-        <v>405.8</v>
+        <v>405.38</v>
       </c>
       <c r="O10" t="n">
-        <v>466.34</v>
+        <v>465.92</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>53.94</v>
+        <v>53.77</v>
       </c>
       <c r="R10" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.06</v>
+        <v>-3.16</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1588,25 +1588,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1565.21</v>
+        <v>1565.73</v>
       </c>
       <c r="D11" t="n">
         <v>76</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.23</v>
+        <v>-2.19</v>
       </c>
       <c r="F11" t="n">
-        <v>6.6</v>
+        <v>6.63</v>
       </c>
       <c r="G11" t="n">
-        <v>33.45</v>
+        <v>33.5</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.13</v>
+        <v>-3.08</v>
       </c>
       <c r="I11" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="J11" t="n">
         <v>76.48999999999999</v>
@@ -1615,28 +1615,28 @@
         <v>4.89</v>
       </c>
       <c r="L11" t="n">
-        <v>1538.44</v>
+        <v>1538.96</v>
       </c>
       <c r="M11" t="n">
-        <v>1576.69</v>
+        <v>1577.21</v>
       </c>
       <c r="N11" t="n">
-        <v>1461.95</v>
+        <v>1462.47</v>
       </c>
       <c r="O11" t="n">
-        <v>1733.49</v>
+        <v>1734.01</v>
       </c>
       <c r="P11" t="n">
         <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>48.34</v>
+        <v>48.38</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.13</v>
+        <v>-1.1</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.58</v>
+        <v>-6.55</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1697,22 +1697,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1821.84</v>
+        <v>1818.98</v>
       </c>
       <c r="D12" t="n">
         <v>75</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.53</v>
+        <v>-2.69</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="G12" t="n">
-        <v>23.94</v>
+        <v>23.75</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.029999999999999</v>
+        <v>-8.17</v>
       </c>
       <c r="I12" t="n">
         <v>0.41</v>
@@ -1724,28 +1724,28 @@
         <v>4.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1791.25</v>
+        <v>1788.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1834.95</v>
+        <v>1832.09</v>
       </c>
       <c r="N12" t="n">
-        <v>1703.86</v>
+        <v>1701.01</v>
       </c>
       <c r="O12" t="n">
-        <v>2014.1</v>
+        <v>2011.24</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>44.2</v>
+        <v>44.01</v>
       </c>
       <c r="R12" t="n">
-        <v>0.46</v>
+        <v>0.31</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.06</v>
+        <v>-6.21</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1806,55 +1806,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>82.25</v>
+        <v>82.5</v>
       </c>
       <c r="D13" t="n">
         <v>96</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.97</v>
+        <v>-1.67</v>
       </c>
       <c r="F13" t="n">
-        <v>13.84</v>
+        <v>14.19</v>
       </c>
       <c r="G13" t="n">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="H13" t="n">
-        <v>4.11</v>
+        <v>4.48</v>
       </c>
       <c r="I13" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="J13" t="n">
         <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="L13" t="n">
-        <v>81.08</v>
+        <v>81.33</v>
       </c>
       <c r="M13" t="n">
-        <v>82.75</v>
+        <v>83</v>
       </c>
       <c r="N13" t="n">
-        <v>77.73</v>
+        <v>77.98</v>
       </c>
       <c r="O13" t="n">
-        <v>89.62</v>
+        <v>89.87</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>63.15</v>
+        <v>63.54</v>
       </c>
       <c r="R13" t="n">
-        <v>5.35</v>
+        <v>5.65</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.89</v>
+        <v>-2.6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1919,22 +1919,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>424.77</v>
+        <v>424.6</v>
       </c>
       <c r="D14" t="n">
         <v>91</v>
       </c>
       <c r="E14" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="F14" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="G14" t="n">
-        <v>6.6</v>
+        <v>6.56</v>
       </c>
       <c r="H14" t="n">
-        <v>-9.26</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>0.84</v>
@@ -1946,28 +1946,28 @@
         <v>2.66</v>
       </c>
       <c r="L14" t="n">
-        <v>420.81</v>
+        <v>420.65</v>
       </c>
       <c r="M14" t="n">
-        <v>426.46</v>
+        <v>426.29</v>
       </c>
       <c r="N14" t="n">
-        <v>409.53</v>
+        <v>409.36</v>
       </c>
       <c r="O14" t="n">
-        <v>449.6</v>
+        <v>449.43</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>49.97</v>
+        <v>49.86</v>
       </c>
       <c r="R14" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.06</v>
+        <v>-2.1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2032,22 +2032,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>95.64</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9</v>
+        <v>4.78</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.05</v>
+        <v>-1.16</v>
       </c>
       <c r="G15" t="n">
-        <v>-10.92</v>
+        <v>-11.02</v>
       </c>
       <c r="H15" t="n">
-        <v>-10.78</v>
+        <v>-10.87</v>
       </c>
       <c r="I15" t="n">
         <v>0.76</v>
@@ -2059,28 +2059,28 @@
         <v>4.53</v>
       </c>
       <c r="L15" t="n">
-        <v>94.13</v>
+        <v>94.02</v>
       </c>
       <c r="M15" t="n">
-        <v>96.29000000000001</v>
+        <v>96.19</v>
       </c>
       <c r="N15" t="n">
-        <v>89.8</v>
+        <v>89.69</v>
       </c>
       <c r="O15" t="n">
-        <v>105.17</v>
+        <v>105.07</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>58.9</v>
+        <v>58.75</v>
       </c>
       <c r="R15" t="n">
-        <v>4.04</v>
+        <v>3.93</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.57</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; RSI saludable; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2145,22 +2145,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>327.08</v>
+        <v>326.97</v>
       </c>
       <c r="D16" t="n">
         <v>96</v>
       </c>
       <c r="E16" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="F16" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="G16" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="H16" t="n">
-        <v>-6.34</v>
+        <v>-6.36</v>
       </c>
       <c r="I16" t="n">
         <v>0.44</v>
@@ -2169,31 +2169,31 @@
         <v>7.83</v>
       </c>
       <c r="K16" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="L16" t="n">
-        <v>324.34</v>
+        <v>324.23</v>
       </c>
       <c r="M16" t="n">
-        <v>328.26</v>
+        <v>328.15</v>
       </c>
       <c r="N16" t="n">
-        <v>316.51</v>
+        <v>316.4</v>
       </c>
       <c r="O16" t="n">
-        <v>344.32</v>
+        <v>344.21</v>
       </c>
       <c r="P16" t="n">
         <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>63.29</v>
+        <v>63.23</v>
       </c>
       <c r="R16" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="S16" t="n">
-        <v>-4.16</v>
+        <v>-4.19</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2258,55 +2258,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>954.35</v>
+        <v>953.11</v>
       </c>
       <c r="D17" t="n">
         <v>96</v>
       </c>
       <c r="E17" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="F17" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="G17" t="n">
-        <v>4.66</v>
+        <v>4.52</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.66</v>
+        <v>-6.78</v>
       </c>
       <c r="I17" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="J17" t="n">
         <v>23.59</v>
       </c>
       <c r="K17" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="L17" t="n">
-        <v>946.09</v>
+        <v>944.85</v>
       </c>
       <c r="M17" t="n">
-        <v>957.89</v>
+        <v>956.65</v>
       </c>
       <c r="N17" t="n">
-        <v>922.5</v>
+        <v>921.26</v>
       </c>
       <c r="O17" t="n">
-        <v>1006.26</v>
+        <v>1005.02</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>54.75</v>
+        <v>54.36</v>
       </c>
       <c r="R17" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.18</v>
+        <v>-2.31</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2371,22 +2371,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>887.52</v>
+        <v>886.6</v>
       </c>
       <c r="D18" t="n">
         <v>95</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.11</v>
+        <v>-1.21</v>
       </c>
       <c r="F18" t="n">
-        <v>11.9</v>
+        <v>11.78</v>
       </c>
       <c r="G18" t="n">
-        <v>16.92</v>
+        <v>16.8</v>
       </c>
       <c r="H18" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="I18" t="n">
         <v>0.62</v>
@@ -2395,31 +2395,31 @@
         <v>32.06</v>
       </c>
       <c r="K18" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="L18" t="n">
-        <v>876.29</v>
+        <v>875.38</v>
       </c>
       <c r="M18" t="n">
-        <v>892.3200000000001</v>
+        <v>891.41</v>
       </c>
       <c r="N18" t="n">
-        <v>844.23</v>
+        <v>843.3200000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>958.05</v>
+        <v>957.13</v>
       </c>
       <c r="P18" t="n">
         <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>59.67</v>
+        <v>59.49</v>
       </c>
       <c r="R18" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="S18" t="n">
-        <v>-4.71</v>
+        <v>-4.8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2484,25 +2484,25 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>228.71</v>
+        <v>228.77</v>
       </c>
       <c r="D19" t="n">
         <v>88</v>
       </c>
       <c r="E19" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.34</v>
+        <v>-2.31</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.88</v>
+        <v>-6.85</v>
       </c>
       <c r="H19" t="n">
-        <v>-12.07</v>
+        <v>-12.02</v>
       </c>
       <c r="I19" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J19" t="n">
         <v>3.89</v>
@@ -2511,28 +2511,28 @@
         <v>1.7</v>
       </c>
       <c r="L19" t="n">
-        <v>227.35</v>
+        <v>227.41</v>
       </c>
       <c r="M19" t="n">
-        <v>229.29</v>
+        <v>229.35</v>
       </c>
       <c r="N19" t="n">
-        <v>223.46</v>
+        <v>223.52</v>
       </c>
       <c r="O19" t="n">
-        <v>237.27</v>
+        <v>237.33</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>55.98</v>
+        <v>56.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.78</v>
+        <v>-2.76</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2597,25 +2597,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>145.32</v>
+        <v>145.38</v>
       </c>
       <c r="D20" t="n">
         <v>82</v>
       </c>
       <c r="E20" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.34</v>
+        <v>-2.3</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.21</v>
+        <v>-7.17</v>
       </c>
       <c r="H20" t="n">
-        <v>-12.07</v>
+        <v>-12.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="J20" t="n">
         <v>1.89</v>
@@ -2624,28 +2624,28 @@
         <v>1.3</v>
       </c>
       <c r="L20" t="n">
-        <v>144.66</v>
+        <v>144.72</v>
       </c>
       <c r="M20" t="n">
-        <v>145.61</v>
+        <v>145.67</v>
       </c>
       <c r="N20" t="n">
-        <v>142.78</v>
+        <v>142.84</v>
       </c>
       <c r="O20" t="n">
-        <v>149.48</v>
+        <v>149.54</v>
       </c>
       <c r="P20" t="n">
         <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>56.72</v>
+        <v>56.97</v>
       </c>
       <c r="R20" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.3</v>
+        <v>-2.26</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2710,25 +2710,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>131.4</v>
+        <v>131.42</v>
       </c>
       <c r="D21" t="n">
         <v>96</v>
       </c>
       <c r="E21" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="F21" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="G21" t="n">
-        <v>5.65</v>
+        <v>5.66</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.47</v>
+        <v>-6.44</v>
       </c>
       <c r="I21" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="J21" t="n">
         <v>2.64</v>
@@ -2737,28 +2737,28 @@
         <v>2.01</v>
       </c>
       <c r="L21" t="n">
-        <v>130.48</v>
+        <v>130.5</v>
       </c>
       <c r="M21" t="n">
-        <v>131.8</v>
+        <v>131.82</v>
       </c>
       <c r="N21" t="n">
-        <v>127.84</v>
+        <v>127.86</v>
       </c>
       <c r="O21" t="n">
-        <v>137.2</v>
+        <v>137.22</v>
       </c>
       <c r="P21" t="n">
         <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>62.31</v>
+        <v>62.38</v>
       </c>
       <c r="R21" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9</v>
+        <v>-1.89</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2819,25 +2819,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>285.01</v>
+        <v>284.78</v>
       </c>
       <c r="D22" t="n">
         <v>90</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.07</v>
+        <v>-3.15</v>
       </c>
       <c r="F22" t="n">
-        <v>6.51</v>
+        <v>6.42</v>
       </c>
       <c r="G22" t="n">
-        <v>20.2</v>
+        <v>20.11</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.22</v>
+        <v>-3.29</v>
       </c>
       <c r="I22" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J22" t="n">
         <v>13.74</v>
@@ -2846,28 +2846,28 @@
         <v>4.82</v>
       </c>
       <c r="L22" t="n">
-        <v>280.2</v>
+        <v>279.97</v>
       </c>
       <c r="M22" t="n">
-        <v>287.07</v>
+        <v>286.84</v>
       </c>
       <c r="N22" t="n">
-        <v>266.47</v>
+        <v>266.24</v>
       </c>
       <c r="O22" t="n">
-        <v>315.23</v>
+        <v>315</v>
       </c>
       <c r="P22" t="n">
         <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>61.36</v>
+        <v>61.23</v>
       </c>
       <c r="R22" t="n">
-        <v>4.31</v>
+        <v>4.23</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.63</v>
+        <v>-5.7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2928,22 +2928,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1084.83</v>
+        <v>1084.52</v>
       </c>
       <c r="D23" t="n">
         <v>85</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="F23" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="G23" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.62</v>
+        <v>-6.63</v>
       </c>
       <c r="I23" t="n">
         <v>0.34</v>
@@ -2955,28 +2955,28 @@
         <v>2.06</v>
       </c>
       <c r="L23" t="n">
-        <v>1077.02</v>
+        <v>1076.71</v>
       </c>
       <c r="M23" t="n">
-        <v>1088.18</v>
+        <v>1087.87</v>
       </c>
       <c r="N23" t="n">
-        <v>1054.71</v>
+        <v>1054.39</v>
       </c>
       <c r="O23" t="n">
-        <v>1133.93</v>
+        <v>1133.62</v>
       </c>
       <c r="P23" t="n">
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>59.12</v>
+        <v>59</v>
       </c>
       <c r="R23" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.36</v>
+        <v>-2.39</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3037,22 +3037,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>193.29</v>
+        <v>193.05</v>
       </c>
       <c r="D24" t="n">
         <v>85</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="F24" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="G24" t="n">
-        <v>11.45</v>
+        <v>11.31</v>
       </c>
       <c r="H24" t="n">
-        <v>-6.81</v>
+        <v>-6.92</v>
       </c>
       <c r="I24" t="n">
         <v>0.61</v>
@@ -3064,28 +3064,28 @@
         <v>2.27</v>
       </c>
       <c r="L24" t="n">
-        <v>191.75</v>
+        <v>191.52</v>
       </c>
       <c r="M24" t="n">
-        <v>193.95</v>
+        <v>193.71</v>
       </c>
       <c r="N24" t="n">
-        <v>187.37</v>
+        <v>187.13</v>
       </c>
       <c r="O24" t="n">
-        <v>202.94</v>
+        <v>202.7</v>
       </c>
       <c r="P24" t="n">
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>57.21</v>
+        <v>56.74</v>
       </c>
       <c r="R24" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.13</v>
+        <v>-2.25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3146,22 +3146,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>496.65</v>
+        <v>496.36</v>
       </c>
       <c r="D25" t="n">
         <v>85</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F25" t="n">
-        <v>0.49</v>
+        <v>0.43</v>
       </c>
       <c r="G25" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.24</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>0.88</v>
@@ -3173,28 +3173,28 @@
         <v>1.02</v>
       </c>
       <c r="L25" t="n">
-        <v>494.88</v>
+        <v>494.59</v>
       </c>
       <c r="M25" t="n">
-        <v>497.41</v>
+        <v>497.12</v>
       </c>
       <c r="N25" t="n">
-        <v>489.81</v>
+        <v>489.52</v>
       </c>
       <c r="O25" t="n">
-        <v>507.8</v>
+        <v>507.51</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>55.82</v>
+        <v>55.43</v>
       </c>
       <c r="R25" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1</v>
+        <v>-1.16</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3255,25 +3255,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>91.15000000000001</v>
+        <v>91</v>
       </c>
       <c r="D26" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E26" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.87</v>
+        <v>-1.03</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.55</v>
+        <v>-2.7</v>
       </c>
       <c r="H26" t="n">
-        <v>-10.6</v>
+        <v>-10.74</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="J26" t="n">
         <v>2.18</v>
@@ -3282,28 +3282,28 @@
         <v>2.39</v>
       </c>
       <c r="L26" t="n">
-        <v>90.39</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>91.48</v>
+        <v>91.33</v>
       </c>
       <c r="N26" t="n">
-        <v>88.20999999999999</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>95.94</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>52.75</v>
+        <v>52.22</v>
       </c>
       <c r="R26" t="n">
-        <v>0.74</v>
+        <v>0.59</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.85</v>
+        <v>-3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3364,22 +3364,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>108.08</v>
+        <v>108.18</v>
       </c>
       <c r="D27" t="n">
         <v>96</v>
       </c>
       <c r="E27" t="n">
-        <v>-13.48</v>
+        <v>-13.4</v>
       </c>
       <c r="F27" t="n">
-        <v>57.79</v>
+        <v>57.92</v>
       </c>
       <c r="G27" t="n">
-        <v>142.23</v>
+        <v>142.44</v>
       </c>
       <c r="H27" t="n">
-        <v>48.06</v>
+        <v>48.21</v>
       </c>
       <c r="I27" t="n">
         <v>0.55</v>
@@ -3388,31 +3388,31 @@
         <v>9.119999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>8.44</v>
+        <v>8.43</v>
       </c>
       <c r="L27" t="n">
-        <v>104.89</v>
+        <v>104.98</v>
       </c>
       <c r="M27" t="n">
-        <v>109.45</v>
+        <v>109.54</v>
       </c>
       <c r="N27" t="n">
-        <v>95.77</v>
+        <v>95.86</v>
       </c>
       <c r="O27" t="n">
-        <v>128.15</v>
+        <v>128.24</v>
       </c>
       <c r="P27" t="n">
         <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>64.13</v>
+        <v>64.2</v>
       </c>
       <c r="R27" t="n">
-        <v>10.81</v>
+        <v>10.9</v>
       </c>
       <c r="S27" t="n">
-        <v>-18.58</v>
+        <v>-18.51</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3477,22 +3477,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>179.17</v>
+        <v>178.84</v>
       </c>
       <c r="D28" t="n">
         <v>96</v>
       </c>
       <c r="E28" t="n">
-        <v>5.31</v>
+        <v>5.12</v>
       </c>
       <c r="F28" t="n">
-        <v>28.26</v>
+        <v>28.02</v>
       </c>
       <c r="G28" t="n">
-        <v>125.17</v>
+        <v>124.75</v>
       </c>
       <c r="H28" t="n">
-        <v>18.53</v>
+        <v>18.31</v>
       </c>
       <c r="I28" t="n">
         <v>0.49</v>
@@ -3501,31 +3501,31 @@
         <v>10.64</v>
       </c>
       <c r="K28" t="n">
-        <v>5.94</v>
+        <v>5.95</v>
       </c>
       <c r="L28" t="n">
-        <v>175.45</v>
+        <v>175.11</v>
       </c>
       <c r="M28" t="n">
-        <v>180.77</v>
+        <v>180.43</v>
       </c>
       <c r="N28" t="n">
-        <v>164.81</v>
+        <v>164.47</v>
       </c>
       <c r="O28" t="n">
-        <v>202.57</v>
+        <v>202.24</v>
       </c>
       <c r="P28" t="n">
         <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>63.49</v>
+        <v>63.22</v>
       </c>
       <c r="R28" t="n">
-        <v>8.779999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="S28" t="n">
-        <v>-6.76</v>
+        <v>-6.93</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3590,25 +3590,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>514.12</v>
+        <v>513.78</v>
       </c>
       <c r="D29" t="n">
         <v>96</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.19</v>
+        <v>-1.25</v>
       </c>
       <c r="F29" t="n">
-        <v>23.67</v>
+        <v>23.59</v>
       </c>
       <c r="G29" t="n">
-        <v>44.57</v>
+        <v>44.48</v>
       </c>
       <c r="H29" t="n">
-        <v>13.94</v>
+        <v>13.88</v>
       </c>
       <c r="I29" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="J29" t="n">
         <v>19.17</v>
@@ -3617,28 +3617,28 @@
         <v>3.73</v>
       </c>
       <c r="L29" t="n">
-        <v>507.41</v>
+        <v>507.07</v>
       </c>
       <c r="M29" t="n">
-        <v>517</v>
+        <v>516.66</v>
       </c>
       <c r="N29" t="n">
-        <v>488.24</v>
+        <v>487.9</v>
       </c>
       <c r="O29" t="n">
-        <v>556.3</v>
+        <v>555.97</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>65.14</v>
+        <v>65.03</v>
       </c>
       <c r="R29" t="n">
-        <v>7.9</v>
+        <v>7.83</v>
       </c>
       <c r="S29" t="n">
-        <v>-3.68</v>
+        <v>-3.74</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3703,25 +3703,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>560.75</v>
+        <v>560.51</v>
       </c>
       <c r="D30" t="n">
         <v>96</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.02</v>
+        <v>-1.06</v>
       </c>
       <c r="F30" t="n">
-        <v>20.81</v>
+        <v>20.76</v>
       </c>
       <c r="G30" t="n">
-        <v>36.7</v>
+        <v>36.64</v>
       </c>
       <c r="H30" t="n">
-        <v>11.08</v>
+        <v>11.05</v>
       </c>
       <c r="I30" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="J30" t="n">
         <v>18.08</v>
@@ -3730,28 +3730,28 @@
         <v>3.22</v>
       </c>
       <c r="L30" t="n">
-        <v>554.42</v>
+        <v>554.1799999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>563.46</v>
+        <v>563.22</v>
       </c>
       <c r="N30" t="n">
-        <v>536.35</v>
+        <v>536.11</v>
       </c>
       <c r="O30" t="n">
-        <v>600.52</v>
+        <v>600.28</v>
       </c>
       <c r="P30" t="n">
         <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>65.54000000000001</v>
+        <v>65.45</v>
       </c>
       <c r="R30" t="n">
-        <v>7.4</v>
+        <v>7.36</v>
       </c>
       <c r="S30" t="n">
-        <v>-3.51</v>
+        <v>-3.55</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3816,19 +3816,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>203.07</v>
+        <v>203.03</v>
       </c>
       <c r="D31" t="n">
         <v>96</v>
       </c>
       <c r="E31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="F31" t="n">
-        <v>13.26</v>
+        <v>13.24</v>
       </c>
       <c r="G31" t="n">
-        <v>17.56</v>
+        <v>17.54</v>
       </c>
       <c r="H31" t="n">
         <v>3.53</v>
@@ -3843,28 +3843,28 @@
         <v>3.14</v>
       </c>
       <c r="L31" t="n">
-        <v>200.84</v>
+        <v>200.8</v>
       </c>
       <c r="M31" t="n">
-        <v>204.02</v>
+        <v>203.99</v>
       </c>
       <c r="N31" t="n">
-        <v>194.47</v>
+        <v>194.43</v>
       </c>
       <c r="O31" t="n">
-        <v>217.08</v>
+        <v>217.04</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>56.72</v>
+        <v>56.69</v>
       </c>
       <c r="R31" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="S31" t="n">
-        <v>-4.81</v>
+        <v>-4.83</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>XLE 7.49% · CL=F 20.16%</t>
+          <t>XLE 7.33% · CL=F 19.77%</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.49% · CL=F 20.16%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.33% · CL=F 19.77%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3929,25 +3929,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>228.33</v>
+        <v>228.37</v>
       </c>
       <c r="D32" t="n">
         <v>96</v>
       </c>
       <c r="E32" t="n">
-        <v>6.1</v>
+        <v>6.12</v>
       </c>
       <c r="F32" t="n">
-        <v>13.21</v>
+        <v>13.23</v>
       </c>
       <c r="G32" t="n">
-        <v>21.52</v>
+        <v>21.54</v>
       </c>
       <c r="H32" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="I32" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="J32" t="n">
         <v>8.210000000000001</v>
@@ -3956,28 +3956,28 @@
         <v>3.6</v>
       </c>
       <c r="L32" t="n">
-        <v>225.46</v>
+        <v>225.5</v>
       </c>
       <c r="M32" t="n">
-        <v>229.56</v>
+        <v>229.6</v>
       </c>
       <c r="N32" t="n">
-        <v>217.25</v>
+        <v>217.29</v>
       </c>
       <c r="O32" t="n">
-        <v>246.39</v>
+        <v>246.43</v>
       </c>
       <c r="P32" t="n">
         <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>58.77</v>
+        <v>58.81</v>
       </c>
       <c r="R32" t="n">
-        <v>8.5</v>
+        <v>8.51</v>
       </c>
       <c r="S32" t="n">
-        <v>-3.47</v>
+        <v>-3.45</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4042,22 +4042,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>49.01</v>
+        <v>48.97</v>
       </c>
       <c r="D33" t="n">
         <v>96</v>
       </c>
       <c r="E33" t="n">
-        <v>7.45</v>
+        <v>7.38</v>
       </c>
       <c r="F33" t="n">
-        <v>10.81</v>
+        <v>10.73</v>
       </c>
       <c r="G33" t="n">
-        <v>10.31</v>
+        <v>10.23</v>
       </c>
       <c r="H33" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="I33" t="n">
         <v>0.53</v>
@@ -4069,28 +4069,28 @@
         <v>3.47</v>
       </c>
       <c r="L33" t="n">
-        <v>48.41</v>
+        <v>48.38</v>
       </c>
       <c r="M33" t="n">
-        <v>49.26</v>
+        <v>49.23</v>
       </c>
       <c r="N33" t="n">
-        <v>46.71</v>
+        <v>46.68</v>
       </c>
       <c r="O33" t="n">
-        <v>52.75</v>
+        <v>52.71</v>
       </c>
       <c r="P33" t="n">
         <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>52.83</v>
+        <v>52.71</v>
       </c>
       <c r="R33" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="S33" t="n">
-        <v>-5.66</v>
+        <v>-5.73</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>XLE 7.49% · CL=F 20.16%</t>
+          <t>XLE 7.33% · CL=F 19.77%</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.49% · CL=F 20.16%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.33% · CL=F 19.77%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4155,22 +4155,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>139.57</v>
+        <v>139.48</v>
       </c>
       <c r="D34" t="n">
         <v>96</v>
       </c>
       <c r="E34" t="n">
-        <v>7.34</v>
+        <v>7.26</v>
       </c>
       <c r="F34" t="n">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="G34" t="n">
-        <v>13.55</v>
+        <v>13.47</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.06</v>
+        <v>-1.11</v>
       </c>
       <c r="I34" t="n">
         <v>0.38</v>
@@ -4182,28 +4182,28 @@
         <v>2.71</v>
       </c>
       <c r="L34" t="n">
-        <v>138.25</v>
+        <v>138.15</v>
       </c>
       <c r="M34" t="n">
-        <v>140.14</v>
+        <v>140.04</v>
       </c>
       <c r="N34" t="n">
-        <v>134.47</v>
+        <v>134.38</v>
       </c>
       <c r="O34" t="n">
-        <v>147.88</v>
+        <v>147.78</v>
       </c>
       <c r="P34" t="n">
         <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>59.69</v>
+        <v>59.58</v>
       </c>
       <c r="R34" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="S34" t="n">
-        <v>-2.3</v>
+        <v>-2.36</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>XLE 7.49% · CL=F 20.16%</t>
+          <t>XLE 7.33% · CL=F 19.77%</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.49% · CL=F 20.16%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.33% · CL=F 19.77%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4274,25 +4274,25 @@
         <v>96</v>
       </c>
       <c r="E35" t="n">
-        <v>6.1</v>
+        <v>6.11</v>
       </c>
       <c r="F35" t="n">
         <v>7.42</v>
       </c>
       <c r="G35" t="n">
-        <v>7.8</v>
+        <v>7.81</v>
       </c>
       <c r="H35" t="n">
-        <v>-2.31</v>
+        <v>-2.29</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="J35" t="n">
         <v>1.32</v>
       </c>
       <c r="K35" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="L35" t="n">
         <v>58.64</v>
@@ -4301,22 +4301,22 @@
         <v>59.3</v>
       </c>
       <c r="N35" t="n">
-        <v>57.32</v>
+        <v>57.33</v>
       </c>
       <c r="O35" t="n">
-        <v>61.99</v>
+        <v>62</v>
       </c>
       <c r="P35" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>60.19</v>
+        <v>60.21</v>
       </c>
       <c r="R35" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="S35" t="n">
-        <v>-1.24</v>
+        <v>-1.23</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>XLE 7.49% · CL=F 20.16%</t>
+          <t>XLE 7.33% · CL=F 19.77%</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.49% · CL=F 20.16%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.33% · CL=F 19.77%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4381,55 +4381,55 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>211.99</v>
+        <v>211.65</v>
       </c>
       <c r="D36" t="n">
         <v>93</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6</v>
+        <v>-0.76</v>
       </c>
       <c r="F36" t="n">
-        <v>27.15</v>
+        <v>26.94</v>
       </c>
       <c r="G36" t="n">
-        <v>67.01000000000001</v>
+        <v>66.75</v>
       </c>
       <c r="H36" t="n">
-        <v>17.42</v>
+        <v>17.23</v>
       </c>
       <c r="I36" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="J36" t="n">
         <v>16.2</v>
       </c>
       <c r="K36" t="n">
-        <v>7.64</v>
+        <v>7.66</v>
       </c>
       <c r="L36" t="n">
-        <v>206.32</v>
+        <v>205.98</v>
       </c>
       <c r="M36" t="n">
-        <v>214.42</v>
+        <v>214.08</v>
       </c>
       <c r="N36" t="n">
-        <v>190.11</v>
+        <v>189.78</v>
       </c>
       <c r="O36" t="n">
-        <v>247.64</v>
+        <v>247.3</v>
       </c>
       <c r="P36" t="n">
         <v>1.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>48.59</v>
+        <v>48.47</v>
       </c>
       <c r="R36" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="S36" t="n">
-        <v>-11.49</v>
+        <v>-11.63</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4494,22 +4494,22 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>293.41</v>
+        <v>292.95</v>
       </c>
       <c r="D37" t="n">
         <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.45</v>
+        <v>-0.61</v>
       </c>
       <c r="F37" t="n">
-        <v>35.82</v>
+        <v>35.6</v>
       </c>
       <c r="G37" t="n">
-        <v>27.07</v>
+        <v>26.86</v>
       </c>
       <c r="H37" t="n">
-        <v>26.09</v>
+        <v>25.89</v>
       </c>
       <c r="I37" t="n">
         <v>0.21</v>
@@ -4518,31 +4518,31 @@
         <v>14.83</v>
       </c>
       <c r="K37" t="n">
-        <v>5.05</v>
+        <v>5.06</v>
       </c>
       <c r="L37" t="n">
-        <v>288.22</v>
+        <v>287.76</v>
       </c>
       <c r="M37" t="n">
-        <v>295.63</v>
+        <v>295.17</v>
       </c>
       <c r="N37" t="n">
-        <v>273.4</v>
+        <v>272.93</v>
       </c>
       <c r="O37" t="n">
-        <v>326.03</v>
+        <v>325.56</v>
       </c>
       <c r="P37" t="n">
         <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>70.39</v>
+        <v>70.16</v>
       </c>
       <c r="R37" t="n">
-        <v>7.48</v>
+        <v>7.32</v>
       </c>
       <c r="S37" t="n">
-        <v>-4.31</v>
+        <v>-4.46</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4607,25 +4607,25 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>121.86</v>
+        <v>121.74</v>
       </c>
       <c r="D38" t="n">
         <v>85</v>
       </c>
       <c r="E38" t="n">
-        <v>7.81</v>
+        <v>7.71</v>
       </c>
       <c r="F38" t="n">
-        <v>5.79</v>
+        <v>5.69</v>
       </c>
       <c r="G38" t="n">
-        <v>10.01</v>
+        <v>9.91</v>
       </c>
       <c r="H38" t="n">
-        <v>-3.94</v>
+        <v>-4.02</v>
       </c>
       <c r="I38" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="J38" t="n">
         <v>3.28</v>
@@ -4634,28 +4634,28 @@
         <v>2.7</v>
       </c>
       <c r="L38" t="n">
-        <v>120.71</v>
+        <v>120.59</v>
       </c>
       <c r="M38" t="n">
-        <v>122.35</v>
+        <v>122.23</v>
       </c>
       <c r="N38" t="n">
-        <v>117.42</v>
+        <v>117.31</v>
       </c>
       <c r="O38" t="n">
-        <v>129.08</v>
+        <v>128.97</v>
       </c>
       <c r="P38" t="n">
         <v>1.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>51.58</v>
+        <v>51.41</v>
       </c>
       <c r="R38" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="S38" t="n">
-        <v>-4.3</v>
+        <v>-4.39</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>XLE 7.49% · CL=F 20.16%</t>
+          <t>XLE 7.33% · CL=F 19.77%</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.49% · CL=F 20.16%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.33% · CL=F 19.77%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4720,22 +4720,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>156.2</v>
+        <v>156.26</v>
       </c>
       <c r="D39" t="n">
         <v>96</v>
       </c>
       <c r="E39" t="n">
-        <v>8.039999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="F39" t="n">
-        <v>6.66</v>
+        <v>6.7</v>
       </c>
       <c r="G39" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="H39" t="n">
-        <v>-3.07</v>
+        <v>-3.01</v>
       </c>
       <c r="I39" t="n">
         <v>0.7</v>
@@ -4747,28 +4747,28 @@
         <v>2.49</v>
       </c>
       <c r="L39" t="n">
-        <v>154.84</v>
+        <v>154.89</v>
       </c>
       <c r="M39" t="n">
-        <v>156.78</v>
+        <v>156.84</v>
       </c>
       <c r="N39" t="n">
-        <v>150.94</v>
+        <v>151</v>
       </c>
       <c r="O39" t="n">
-        <v>164.77</v>
+        <v>164.82</v>
       </c>
       <c r="P39" t="n">
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>62.33</v>
+        <v>62.4</v>
       </c>
       <c r="R39" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="S39" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>XLE 7.49% · CL=F 20.16%</t>
+          <t>XLE 7.33% · CL=F 19.77%</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.49% · CL=F 20.16%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.33% · CL=F 19.77%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4833,55 +4833,55 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>241.71</v>
+        <v>241.85</v>
       </c>
       <c r="D40" t="n">
         <v>96</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.2</v>
+        <v>-7.14</v>
       </c>
       <c r="F40" t="n">
-        <v>23.36</v>
+        <v>23.43</v>
       </c>
       <c r="G40" t="n">
-        <v>103.64</v>
+        <v>103.77</v>
       </c>
       <c r="H40" t="n">
-        <v>13.63</v>
+        <v>13.72</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="J40" t="n">
         <v>13.94</v>
       </c>
       <c r="K40" t="n">
-        <v>5.77</v>
+        <v>5.76</v>
       </c>
       <c r="L40" t="n">
-        <v>236.83</v>
+        <v>236.98</v>
       </c>
       <c r="M40" t="n">
-        <v>243.8</v>
+        <v>243.95</v>
       </c>
       <c r="N40" t="n">
-        <v>222.89</v>
+        <v>223.04</v>
       </c>
       <c r="O40" t="n">
-        <v>272.38</v>
+        <v>272.52</v>
       </c>
       <c r="P40" t="n">
         <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>60.83</v>
+        <v>60.91</v>
       </c>
       <c r="R40" t="n">
-        <v>7.85</v>
+        <v>7.91</v>
       </c>
       <c r="S40" t="n">
-        <v>-8.44</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -4946,55 +4946,55 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>501.17</v>
+        <v>497.87</v>
       </c>
       <c r="D41" t="n">
         <v>93</v>
       </c>
       <c r="E41" t="n">
-        <v>6.96</v>
+        <v>6.26</v>
       </c>
       <c r="F41" t="n">
-        <v>5.02</v>
+        <v>4.33</v>
       </c>
       <c r="G41" t="n">
-        <v>21.64</v>
+        <v>20.84</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.71</v>
+        <v>-5.38</v>
       </c>
       <c r="I41" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J41" t="n">
         <v>29.7</v>
       </c>
       <c r="K41" t="n">
-        <v>5.93</v>
+        <v>5.97</v>
       </c>
       <c r="L41" t="n">
-        <v>490.77</v>
+        <v>487.47</v>
       </c>
       <c r="M41" t="n">
-        <v>505.62</v>
+        <v>502.33</v>
       </c>
       <c r="N41" t="n">
-        <v>461.06</v>
+        <v>457.77</v>
       </c>
       <c r="O41" t="n">
-        <v>566.51</v>
+        <v>563.22</v>
       </c>
       <c r="P41" t="n">
         <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>58.96</v>
+        <v>58.36</v>
       </c>
       <c r="R41" t="n">
-        <v>6.54</v>
+        <v>5.88</v>
       </c>
       <c r="S41" t="n">
-        <v>-2.25</v>
+        <v>-2.89</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5059,25 +5059,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>193.91</v>
+        <v>193.81</v>
       </c>
       <c r="D42" t="n">
         <v>84</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.04</v>
+        <v>-1.09</v>
       </c>
       <c r="F42" t="n">
-        <v>10.77</v>
+        <v>10.71</v>
       </c>
       <c r="G42" t="n">
-        <v>24.31</v>
+        <v>24.24</v>
       </c>
       <c r="H42" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="J42" t="n">
         <v>9.199999999999999</v>
@@ -5086,28 +5086,28 @@
         <v>4.74</v>
       </c>
       <c r="L42" t="n">
-        <v>190.69</v>
+        <v>190.59</v>
       </c>
       <c r="M42" t="n">
-        <v>195.29</v>
+        <v>195.19</v>
       </c>
       <c r="N42" t="n">
-        <v>181.5</v>
+        <v>181.4</v>
       </c>
       <c r="O42" t="n">
-        <v>214.14</v>
+        <v>214.04</v>
       </c>
       <c r="P42" t="n">
         <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>65.94</v>
+        <v>65.84</v>
       </c>
       <c r="R42" t="n">
-        <v>6.49</v>
+        <v>6.44</v>
       </c>
       <c r="S42" t="n">
-        <v>-3.39</v>
+        <v>-3.44</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5172,55 +5172,55 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>158.54</v>
+        <v>158.18</v>
       </c>
       <c r="D43" t="n">
         <v>83</v>
       </c>
       <c r="E43" t="n">
-        <v>3.99</v>
+        <v>3.76</v>
       </c>
       <c r="F43" t="n">
-        <v>10.11</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>-11.53</v>
+        <v>-11.73</v>
       </c>
       <c r="H43" t="n">
-        <v>0.38</v>
+        <v>0.15</v>
       </c>
       <c r="I43" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="J43" t="n">
         <v>7.78</v>
       </c>
       <c r="K43" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="L43" t="n">
-        <v>155.82</v>
+        <v>155.46</v>
       </c>
       <c r="M43" t="n">
-        <v>159.71</v>
+        <v>159.35</v>
       </c>
       <c r="N43" t="n">
-        <v>148.03</v>
+        <v>147.67</v>
       </c>
       <c r="O43" t="n">
-        <v>175.66</v>
+        <v>175.3</v>
       </c>
       <c r="P43" t="n">
         <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>65.38</v>
+        <v>65.11</v>
       </c>
       <c r="R43" t="n">
-        <v>7.63</v>
+        <v>7.4</v>
       </c>
       <c r="S43" t="n">
-        <v>-0.61</v>
+        <v>-0.83</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MACD positivo; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5285,22 +5285,22 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>87.06999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="D44" t="n">
         <v>76</v>
       </c>
       <c r="E44" t="n">
-        <v>-4.95</v>
+        <v>-4.8</v>
       </c>
       <c r="F44" t="n">
-        <v>30.07</v>
+        <v>30.27</v>
       </c>
       <c r="G44" t="n">
-        <v>8.48</v>
+        <v>8.65</v>
       </c>
       <c r="H44" t="n">
-        <v>20.34</v>
+        <v>20.56</v>
       </c>
       <c r="I44" t="n">
         <v>0.31</v>
@@ -5309,31 +5309,31 @@
         <v>6.79</v>
       </c>
       <c r="K44" t="n">
-        <v>7.8</v>
+        <v>7.79</v>
       </c>
       <c r="L44" t="n">
-        <v>84.69</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>88.09</v>
+        <v>88.22</v>
       </c>
       <c r="N44" t="n">
-        <v>77.90000000000001</v>
+        <v>78.03</v>
       </c>
       <c r="O44" t="n">
-        <v>102.01</v>
+        <v>102.14</v>
       </c>
       <c r="P44" t="n">
         <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>66.56999999999999</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="R44" t="n">
-        <v>8.710000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="S44" t="n">
-        <v>-9.6</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5398,25 +5398,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>426.68</v>
+        <v>426.94</v>
       </c>
       <c r="D45" t="n">
         <v>78</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.39</v>
+        <v>-0.33</v>
       </c>
       <c r="F45" t="n">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="G45" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="H45" t="n">
-        <v>-3.23</v>
+        <v>-3.14</v>
       </c>
       <c r="I45" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="J45" t="n">
         <v>17.19</v>
@@ -5425,28 +5425,28 @@
         <v>4.03</v>
       </c>
       <c r="L45" t="n">
-        <v>420.66</v>
+        <v>420.92</v>
       </c>
       <c r="M45" t="n">
-        <v>429.25</v>
+        <v>429.52</v>
       </c>
       <c r="N45" t="n">
-        <v>403.47</v>
+        <v>403.74</v>
       </c>
       <c r="O45" t="n">
-        <v>464.49</v>
+        <v>464.75</v>
       </c>
       <c r="P45" t="n">
         <v>1.63</v>
       </c>
       <c r="Q45" t="n">
-        <v>69</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="R45" t="n">
-        <v>6.26</v>
+        <v>6.32</v>
       </c>
       <c r="S45" t="n">
-        <v>-5.89</v>
+        <v>-5.84</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5507,22 +5507,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>31.23</v>
+        <v>31.21</v>
       </c>
       <c r="D46" t="n">
         <v>75</v>
       </c>
       <c r="E46" t="n">
-        <v>-11.7</v>
+        <v>-11.76</v>
       </c>
       <c r="F46" t="n">
-        <v>9.35</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>-2.89</v>
+        <v>-2.95</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.38</v>
+        <v>-0.43</v>
       </c>
       <c r="I46" t="n">
         <v>0.43</v>
@@ -5534,28 +5534,28 @@
         <v>7.33</v>
       </c>
       <c r="L46" t="n">
-        <v>30.43</v>
+        <v>30.41</v>
       </c>
       <c r="M46" t="n">
-        <v>31.57</v>
+        <v>31.55</v>
       </c>
       <c r="N46" t="n">
-        <v>28.14</v>
+        <v>28.12</v>
       </c>
       <c r="O46" t="n">
-        <v>36.26</v>
+        <v>36.24</v>
       </c>
       <c r="P46" t="n">
         <v>1.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>58.6</v>
+        <v>58.54</v>
       </c>
       <c r="R46" t="n">
-        <v>4.08</v>
+        <v>4.01</v>
       </c>
       <c r="S46" t="n">
-        <v>-14.13</v>
+        <v>-14.19</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5616,22 +5616,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1046.34</v>
+        <v>1047.89</v>
       </c>
       <c r="D47" t="n">
         <v>96</v>
       </c>
       <c r="E47" t="n">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="F47" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="G47" t="n">
-        <v>6.08</v>
+        <v>6.23</v>
       </c>
       <c r="H47" t="n">
-        <v>-4.93</v>
+        <v>-4.76</v>
       </c>
       <c r="I47" t="n">
         <v>0.59</v>
@@ -5640,31 +5640,31 @@
         <v>20.47</v>
       </c>
       <c r="K47" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="L47" t="n">
-        <v>1039.18</v>
+        <v>1040.73</v>
       </c>
       <c r="M47" t="n">
-        <v>1049.42</v>
+        <v>1050.96</v>
       </c>
       <c r="N47" t="n">
-        <v>1018.71</v>
+        <v>1020.26</v>
       </c>
       <c r="O47" t="n">
-        <v>1091.38</v>
+        <v>1092.92</v>
       </c>
       <c r="P47" t="n">
         <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>69.59</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="R47" t="n">
-        <v>3.47</v>
+        <v>3.62</v>
       </c>
       <c r="S47" t="n">
-        <v>-1.05</v>
+        <v>-0.91</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5729,22 +5729,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>209.71</v>
+        <v>209.85</v>
       </c>
       <c r="D48" t="n">
         <v>79</v>
       </c>
       <c r="E48" t="n">
-        <v>4.05</v>
+        <v>4.12</v>
       </c>
       <c r="F48" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="G48" t="n">
-        <v>-5.75</v>
+        <v>-5.68</v>
       </c>
       <c r="H48" t="n">
-        <v>-9.09</v>
+        <v>-9</v>
       </c>
       <c r="I48" t="n">
         <v>0.33</v>
@@ -5753,31 +5753,31 @@
         <v>5.82</v>
       </c>
       <c r="K48" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="L48" t="n">
-        <v>207.67</v>
+        <v>207.82</v>
       </c>
       <c r="M48" t="n">
-        <v>210.58</v>
+        <v>210.73</v>
       </c>
       <c r="N48" t="n">
-        <v>201.85</v>
+        <v>202</v>
       </c>
       <c r="O48" t="n">
-        <v>222.51</v>
+        <v>222.66</v>
       </c>
       <c r="P48" t="n">
         <v>1.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>66.59999999999999</v>
+        <v>66.87</v>
       </c>
       <c r="R48" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="S48" t="n">
-        <v>-2.43</v>
+        <v>-2.36</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5838,55 +5838,55 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>10.31</v>
+        <v>10.34</v>
       </c>
       <c r="D49" t="n">
         <v>74</v>
       </c>
       <c r="E49" t="n">
-        <v>-5.15</v>
+        <v>-4.92</v>
       </c>
       <c r="F49" t="n">
-        <v>11.82</v>
+        <v>12.09</v>
       </c>
       <c r="G49" t="n">
-        <v>0.59</v>
+        <v>0.83</v>
       </c>
       <c r="H49" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="I49" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="J49" t="n">
         <v>0.79</v>
       </c>
       <c r="K49" t="n">
-        <v>7.7</v>
+        <v>7.69</v>
       </c>
       <c r="L49" t="n">
-        <v>10.03</v>
+        <v>10.06</v>
       </c>
       <c r="M49" t="n">
-        <v>10.43</v>
+        <v>10.45</v>
       </c>
       <c r="N49" t="n">
-        <v>9.24</v>
+        <v>9.26</v>
       </c>
       <c r="O49" t="n">
-        <v>12.06</v>
+        <v>12.08</v>
       </c>
       <c r="P49" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q49" t="n">
-        <v>59.97</v>
+        <v>60.2</v>
       </c>
       <c r="R49" t="n">
-        <v>7.66</v>
+        <v>7.91</v>
       </c>
       <c r="S49" t="n">
-        <v>-7.86</v>
+        <v>-7.64</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5947,22 +5947,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>44.56</v>
+        <v>44.6</v>
       </c>
       <c r="D50" t="n">
         <v>74</v>
       </c>
       <c r="E50" t="n">
-        <v>-3.29</v>
+        <v>-3.2</v>
       </c>
       <c r="F50" t="n">
-        <v>9.960000000000001</v>
+        <v>10.06</v>
       </c>
       <c r="G50" t="n">
-        <v>-4.67</v>
+        <v>-4.58</v>
       </c>
       <c r="H50" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="I50" t="n">
         <v>0.53</v>
@@ -5971,31 +5971,31 @@
         <v>1.39</v>
       </c>
       <c r="K50" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="L50" t="n">
-        <v>44.07</v>
+        <v>44.11</v>
       </c>
       <c r="M50" t="n">
-        <v>44.76</v>
+        <v>44.8</v>
       </c>
       <c r="N50" t="n">
-        <v>42.67</v>
+        <v>42.71</v>
       </c>
       <c r="O50" t="n">
-        <v>47.62</v>
+        <v>47.66</v>
       </c>
       <c r="P50" t="n">
         <v>1.63</v>
       </c>
       <c r="Q50" t="n">
-        <v>66.41</v>
+        <v>66.67</v>
       </c>
       <c r="R50" t="n">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="S50" t="n">
-        <v>-6.77</v>
+        <v>-6.69</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6056,22 +6056,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>262.47</v>
+        <v>262.38</v>
       </c>
       <c r="D51" t="n">
         <v>65</v>
       </c>
       <c r="E51" t="n">
-        <v>-3.74</v>
+        <v>-3.78</v>
       </c>
       <c r="F51" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="G51" t="n">
-        <v>28.12</v>
+        <v>28.08</v>
       </c>
       <c r="H51" t="n">
-        <v>-4.98</v>
+        <v>-4.99</v>
       </c>
       <c r="I51" t="n">
         <v>0.54</v>
@@ -6083,28 +6083,28 @@
         <v>2.74</v>
       </c>
       <c r="L51" t="n">
-        <v>259.95</v>
+        <v>259.86</v>
       </c>
       <c r="M51" t="n">
-        <v>263.55</v>
+        <v>263.46</v>
       </c>
       <c r="N51" t="n">
-        <v>252.77</v>
+        <v>252.68</v>
       </c>
       <c r="O51" t="n">
-        <v>278.28</v>
+        <v>278.19</v>
       </c>
       <c r="P51" t="n">
         <v>1.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>51.65</v>
+        <v>51.54</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.75</v>
+        <v>-0.78</v>
       </c>
       <c r="S51" t="n">
-        <v>-5.78</v>
+        <v>-5.81</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6165,22 +6165,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>394.51</v>
+        <v>394.61</v>
       </c>
       <c r="D52" t="n">
         <v>65</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.45</v>
+        <v>-0.43</v>
       </c>
       <c r="F52" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="G52" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="H52" t="n">
-        <v>-9.41</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="I52" t="n">
         <v>0.53</v>
@@ -6192,28 +6192,28 @@
         <v>4.28</v>
       </c>
       <c r="L52" t="n">
-        <v>388.6</v>
+        <v>388.7</v>
       </c>
       <c r="M52" t="n">
-        <v>397.04</v>
+        <v>397.14</v>
       </c>
       <c r="N52" t="n">
-        <v>371.72</v>
+        <v>371.82</v>
       </c>
       <c r="O52" t="n">
-        <v>431.65</v>
+        <v>431.75</v>
       </c>
       <c r="P52" t="n">
         <v>1.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>51.7</v>
+        <v>51.73</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="S52" t="n">
-        <v>-5.84</v>
+        <v>-5.82</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; RSI saludable; MACD positivo; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; RSI saludable; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6274,22 +6274,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>247.12</v>
+        <v>246.9</v>
       </c>
       <c r="D53" t="n">
         <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>-2.34</v>
+        <v>-2.43</v>
       </c>
       <c r="F53" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>-4.66</v>
+        <v>-4.75</v>
       </c>
       <c r="H53" t="n">
-        <v>-8.640000000000001</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="I53" t="n">
         <v>0.57</v>
@@ -6298,31 +6298,31 @@
         <v>8.359999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="L53" t="n">
-        <v>244.19</v>
+        <v>243.97</v>
       </c>
       <c r="M53" t="n">
-        <v>248.37</v>
+        <v>248.15</v>
       </c>
       <c r="N53" t="n">
-        <v>235.84</v>
+        <v>235.61</v>
       </c>
       <c r="O53" t="n">
-        <v>265.51</v>
+        <v>265.29</v>
       </c>
       <c r="P53" t="n">
         <v>1.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>56.55</v>
+        <v>56.39</v>
       </c>
       <c r="R53" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="S53" t="n">
-        <v>-4.75</v>
+        <v>-4.83</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; RSI saludable; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; RSI saludable; MACD mejorando</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6383,25 +6383,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>278.11</v>
+        <v>278.02</v>
       </c>
       <c r="D54" t="n">
         <v>69</v>
       </c>
       <c r="E54" t="n">
-        <v>-2.13</v>
+        <v>-2.16</v>
       </c>
       <c r="F54" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>5.29</v>
+        <v>5.26</v>
       </c>
       <c r="H54" t="n">
-        <v>-8.890000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="I54" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="J54" t="n">
         <v>4.68</v>
@@ -6410,28 +6410,28 @@
         <v>1.68</v>
       </c>
       <c r="L54" t="n">
-        <v>276.47</v>
+        <v>276.38</v>
       </c>
       <c r="M54" t="n">
-        <v>278.81</v>
+        <v>278.72</v>
       </c>
       <c r="N54" t="n">
-        <v>271.8</v>
+        <v>271.71</v>
       </c>
       <c r="O54" t="n">
-        <v>288.4</v>
+        <v>288.31</v>
       </c>
       <c r="P54" t="n">
         <v>1.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>51.18</v>
+        <v>51.07</v>
       </c>
       <c r="R54" t="n">
-        <v>-0.46</v>
+        <v>-0.49</v>
       </c>
       <c r="S54" t="n">
-        <v>-3.29</v>
+        <v>-3.32</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6492,22 +6492,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>305.7</v>
+        <v>305.74</v>
       </c>
       <c r="D55" t="n">
         <v>94</v>
       </c>
       <c r="E55" t="n">
-        <v>6.22</v>
+        <v>6.23</v>
       </c>
       <c r="F55" t="n">
-        <v>33.69</v>
+        <v>33.71</v>
       </c>
       <c r="G55" t="n">
-        <v>40.91</v>
+        <v>40.93</v>
       </c>
       <c r="H55" t="n">
-        <v>23.96</v>
+        <v>24</v>
       </c>
       <c r="I55" t="n">
         <v>0.29</v>
@@ -6519,28 +6519,28 @@
         <v>3.03</v>
       </c>
       <c r="L55" t="n">
-        <v>302.46</v>
+        <v>302.5</v>
       </c>
       <c r="M55" t="n">
-        <v>307.09</v>
+        <v>307.13</v>
       </c>
       <c r="N55" t="n">
-        <v>293.19</v>
+        <v>293.23</v>
       </c>
       <c r="O55" t="n">
-        <v>326.09</v>
+        <v>326.13</v>
       </c>
       <c r="P55" t="n">
         <v>1.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>78.70999999999999</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="R55" t="n">
-        <v>10.14</v>
+        <v>10.15</v>
       </c>
       <c r="S55" t="n">
-        <v>-1.48</v>
+        <v>-1.47</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6605,22 +6605,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>114.15</v>
+        <v>114.35</v>
       </c>
       <c r="D56" t="n">
         <v>92</v>
       </c>
       <c r="E56" t="n">
-        <v>10.61</v>
+        <v>10.8</v>
       </c>
       <c r="F56" t="n">
-        <v>37.51</v>
+        <v>37.75</v>
       </c>
       <c r="G56" t="n">
-        <v>67.65000000000001</v>
+        <v>67.94</v>
       </c>
       <c r="H56" t="n">
-        <v>27.78</v>
+        <v>28.04</v>
       </c>
       <c r="I56" t="n">
         <v>0.35</v>
@@ -6629,31 +6629,31 @@
         <v>6.18</v>
       </c>
       <c r="K56" t="n">
-        <v>5.42</v>
+        <v>5.41</v>
       </c>
       <c r="L56" t="n">
-        <v>111.99</v>
+        <v>112.19</v>
       </c>
       <c r="M56" t="n">
-        <v>115.08</v>
+        <v>115.28</v>
       </c>
       <c r="N56" t="n">
-        <v>105.8</v>
+        <v>106</v>
       </c>
       <c r="O56" t="n">
-        <v>127.75</v>
+        <v>127.95</v>
       </c>
       <c r="P56" t="n">
         <v>1.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>65.31999999999999</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R56" t="n">
-        <v>12.71</v>
+        <v>12.9</v>
       </c>
       <c r="S56" t="n">
-        <v>-4.16</v>
+        <v>-3.99</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -6718,22 +6718,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>432.42</v>
+        <v>431.63</v>
       </c>
       <c r="D57" t="n">
         <v>84</v>
       </c>
       <c r="E57" t="n">
-        <v>-5</v>
+        <v>-5.18</v>
       </c>
       <c r="F57" t="n">
-        <v>55.33</v>
+        <v>55.05</v>
       </c>
       <c r="G57" t="n">
-        <v>112.63</v>
+        <v>112.24</v>
       </c>
       <c r="H57" t="n">
-        <v>45.6</v>
+        <v>45.34</v>
       </c>
       <c r="I57" t="n">
         <v>0.35</v>
@@ -6742,31 +6742,31 @@
         <v>27.56</v>
       </c>
       <c r="K57" t="n">
-        <v>6.37</v>
+        <v>6.39</v>
       </c>
       <c r="L57" t="n">
-        <v>422.77</v>
+        <v>421.98</v>
       </c>
       <c r="M57" t="n">
-        <v>436.55</v>
+        <v>435.76</v>
       </c>
       <c r="N57" t="n">
-        <v>395.21</v>
+        <v>394.42</v>
       </c>
       <c r="O57" t="n">
-        <v>493.05</v>
+        <v>492.26</v>
       </c>
       <c r="P57" t="n">
         <v>1.63</v>
       </c>
       <c r="Q57" t="n">
-        <v>69.91</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="R57" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="S57" t="n">
-        <v>-7.84</v>
+        <v>-8.01</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6831,55 +6831,55 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>58.84</v>
+        <v>58.8</v>
       </c>
       <c r="D58" t="n">
         <v>96</v>
       </c>
       <c r="E58" t="n">
-        <v>10.96</v>
+        <v>10.88</v>
       </c>
       <c r="F58" t="n">
-        <v>9.390000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="G58" t="n">
-        <v>14.73</v>
+        <v>14.65</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="I58" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="J58" t="n">
         <v>1.97</v>
       </c>
       <c r="K58" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="L58" t="n">
-        <v>58.15</v>
+        <v>58.11</v>
       </c>
       <c r="M58" t="n">
-        <v>59.14</v>
+        <v>59.1</v>
       </c>
       <c r="N58" t="n">
-        <v>56.18</v>
+        <v>56.14</v>
       </c>
       <c r="O58" t="n">
-        <v>63.17</v>
+        <v>63.13</v>
       </c>
       <c r="P58" t="n">
         <v>1.63</v>
       </c>
       <c r="Q58" t="n">
-        <v>53.86</v>
+        <v>53.77</v>
       </c>
       <c r="R58" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="S58" t="n">
-        <v>-3.21</v>
+        <v>-3.27</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>XLE 7.49% · CL=F 20.16%</t>
+          <t>XLE 7.33% · CL=F 19.77%</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.49% · CL=F 20.16%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.33% · CL=F 19.77%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -6940,25 +6940,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>738.33</v>
+        <v>738.38</v>
       </c>
       <c r="D59" t="n">
         <v>74</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.14</v>
+        <v>-1.13</v>
       </c>
       <c r="F59" t="n">
-        <v>62.25</v>
+        <v>62.26</v>
       </c>
       <c r="G59" t="n">
-        <v>76.98</v>
+        <v>77</v>
       </c>
       <c r="H59" t="n">
-        <v>52.52</v>
+        <v>52.55</v>
       </c>
       <c r="I59" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J59" t="n">
         <v>53.45</v>
@@ -6967,22 +6967,22 @@
         <v>7.24</v>
       </c>
       <c r="L59" t="n">
-        <v>719.62</v>
+        <v>719.67</v>
       </c>
       <c r="M59" t="n">
-        <v>746.35</v>
+        <v>746.4</v>
       </c>
       <c r="N59" t="n">
-        <v>666.1799999999999</v>
+        <v>666.23</v>
       </c>
       <c r="O59" t="n">
-        <v>855.91</v>
+        <v>855.96</v>
       </c>
       <c r="P59" t="n">
         <v>1.63</v>
       </c>
       <c r="Q59" t="n">
-        <v>72.04000000000001</v>
+        <v>72.05</v>
       </c>
       <c r="R59" t="n">
         <v>21.77</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7049,22 +7049,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>203.06</v>
+        <v>202.95</v>
       </c>
       <c r="D60" t="n">
         <v>64</v>
       </c>
       <c r="E60" t="n">
-        <v>-7.32</v>
+        <v>-7.37</v>
       </c>
       <c r="F60" t="n">
-        <v>49.09</v>
+        <v>49.01</v>
       </c>
       <c r="G60" t="n">
-        <v>44.66</v>
+        <v>44.58</v>
       </c>
       <c r="H60" t="n">
-        <v>39.36</v>
+        <v>39.3</v>
       </c>
       <c r="I60" t="n">
         <v>0.46</v>
@@ -7076,28 +7076,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>196.52</v>
+        <v>196.41</v>
       </c>
       <c r="M60" t="n">
-        <v>205.86</v>
+        <v>205.75</v>
       </c>
       <c r="N60" t="n">
-        <v>177.84</v>
+        <v>177.73</v>
       </c>
       <c r="O60" t="n">
-        <v>244.15</v>
+        <v>244.04</v>
       </c>
       <c r="P60" t="n">
         <v>1.63</v>
       </c>
       <c r="Q60" t="n">
-        <v>66.89</v>
+        <v>66.86</v>
       </c>
       <c r="R60" t="n">
-        <v>14.79</v>
+        <v>14.72</v>
       </c>
       <c r="S60" t="n">
-        <v>-18.09</v>
+        <v>-18.13</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>SOXX 23.68% · QQQ 9.73%</t>
+          <t>SOXX 23.62% · QQQ 9.71%</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.68% · QQQ 9.73%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 23.62% · QQQ 9.71%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7158,22 +7158,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>177.46</v>
+        <v>177.39</v>
       </c>
       <c r="D61" t="n">
         <v>96</v>
       </c>
       <c r="E61" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="F61" t="n">
-        <v>14.97</v>
+        <v>14.93</v>
       </c>
       <c r="G61" t="n">
-        <v>26.72</v>
+        <v>26.67</v>
       </c>
       <c r="H61" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="I61" t="n">
         <v>0.84</v>
@@ -7185,28 +7185,28 @@
         <v>2.12</v>
       </c>
       <c r="L61" t="n">
-        <v>176.14</v>
+        <v>176.07</v>
       </c>
       <c r="M61" t="n">
-        <v>178.02</v>
+        <v>177.95</v>
       </c>
       <c r="N61" t="n">
-        <v>172.38</v>
+        <v>172.31</v>
       </c>
       <c r="O61" t="n">
-        <v>185.73</v>
+        <v>185.66</v>
       </c>
       <c r="P61" t="n">
         <v>1.63</v>
       </c>
       <c r="Q61" t="n">
-        <v>76.02</v>
+        <v>75.86</v>
       </c>
       <c r="R61" t="n">
-        <v>7.16</v>
+        <v>7.12</v>
       </c>
       <c r="S61" t="n">
-        <v>-1.53</v>
+        <v>-1.57</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7271,25 +7271,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>114.1</v>
+        <v>114.07</v>
       </c>
       <c r="D62" t="n">
         <v>96</v>
       </c>
       <c r="E62" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="F62" t="n">
-        <v>13.31</v>
+        <v>13.28</v>
       </c>
       <c r="G62" t="n">
-        <v>24.38</v>
+        <v>24.35</v>
       </c>
       <c r="H62" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="I62" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="J62" t="n">
         <v>2.27</v>
@@ -7298,28 +7298,28 @@
         <v>1.99</v>
       </c>
       <c r="L62" t="n">
-        <v>113.3</v>
+        <v>113.27</v>
       </c>
       <c r="M62" t="n">
-        <v>114.44</v>
+        <v>114.41</v>
       </c>
       <c r="N62" t="n">
-        <v>111.03</v>
+        <v>111</v>
       </c>
       <c r="O62" t="n">
-        <v>119.1</v>
+        <v>119.07</v>
       </c>
       <c r="P62" t="n">
         <v>1.63</v>
       </c>
       <c r="Q62" t="n">
-        <v>76.84</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="R62" t="n">
-        <v>6.58</v>
+        <v>6.55</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.32</v>
+        <v>-1.34</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -7384,25 +7384,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>302.42</v>
+        <v>302.57</v>
       </c>
       <c r="D63" t="n">
         <v>96</v>
       </c>
       <c r="E63" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="F63" t="n">
-        <v>12.02</v>
+        <v>12.07</v>
       </c>
       <c r="G63" t="n">
-        <v>16.16</v>
+        <v>16.22</v>
       </c>
       <c r="H63" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="J63" t="n">
         <v>6.63</v>
@@ -7411,28 +7411,28 @@
         <v>2.19</v>
       </c>
       <c r="L63" t="n">
-        <v>300.1</v>
+        <v>300.25</v>
       </c>
       <c r="M63" t="n">
-        <v>303.42</v>
+        <v>303.57</v>
       </c>
       <c r="N63" t="n">
-        <v>293.46</v>
+        <v>293.61</v>
       </c>
       <c r="O63" t="n">
-        <v>317.01</v>
+        <v>317.16</v>
       </c>
       <c r="P63" t="n">
         <v>1.63</v>
       </c>
       <c r="Q63" t="n">
-        <v>89</v>
+        <v>89.03</v>
       </c>
       <c r="R63" t="n">
-        <v>7.44</v>
+        <v>7.5</v>
       </c>
       <c r="S63" t="n">
-        <v>-0.12</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7497,55 +7497,55 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>52.03</v>
+        <v>51.94</v>
       </c>
       <c r="D64" t="n">
         <v>87</v>
       </c>
       <c r="E64" t="n">
-        <v>5.66</v>
+        <v>5.47</v>
       </c>
       <c r="F64" t="n">
-        <v>12.88</v>
+        <v>12.68</v>
       </c>
       <c r="G64" t="n">
-        <v>55.63</v>
+        <v>55.35</v>
       </c>
       <c r="H64" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="I64" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="J64" t="n">
         <v>4.72</v>
       </c>
       <c r="K64" t="n">
-        <v>9.07</v>
+        <v>9.08</v>
       </c>
       <c r="L64" t="n">
-        <v>50.38</v>
+        <v>50.28</v>
       </c>
       <c r="M64" t="n">
-        <v>52.74</v>
+        <v>52.64</v>
       </c>
       <c r="N64" t="n">
-        <v>45.66</v>
+        <v>45.57</v>
       </c>
       <c r="O64" t="n">
-        <v>62.41</v>
+        <v>62.31</v>
       </c>
       <c r="P64" t="n">
         <v>1.63</v>
       </c>
       <c r="Q64" t="n">
-        <v>61.23</v>
+        <v>61.07</v>
       </c>
       <c r="R64" t="n">
-        <v>7.34</v>
+        <v>7.16</v>
       </c>
       <c r="S64" t="n">
-        <v>-12.04</v>
+        <v>-12.2</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -7610,25 +7610,25 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>122.19</v>
+        <v>122.26</v>
       </c>
       <c r="D65" t="n">
         <v>85</v>
       </c>
       <c r="E65" t="n">
-        <v>7.12</v>
+        <v>7.18</v>
       </c>
       <c r="F65" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="G65" t="n">
-        <v>49.61</v>
+        <v>49.71</v>
       </c>
       <c r="H65" t="n">
-        <v>39.57</v>
+        <v>39.69</v>
       </c>
       <c r="I65" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="J65" t="n">
         <v>4.97</v>
@@ -7637,28 +7637,28 @@
         <v>4.07</v>
       </c>
       <c r="L65" t="n">
-        <v>120.45</v>
+        <v>120.52</v>
       </c>
       <c r="M65" t="n">
-        <v>122.94</v>
+        <v>123.01</v>
       </c>
       <c r="N65" t="n">
-        <v>115.48</v>
+        <v>115.55</v>
       </c>
       <c r="O65" t="n">
-        <v>133.13</v>
+        <v>133.21</v>
       </c>
       <c r="P65" t="n">
         <v>1.63</v>
       </c>
       <c r="Q65" t="n">
-        <v>92.20999999999999</v>
+        <v>92.22</v>
       </c>
       <c r="R65" t="n">
-        <v>26.47</v>
+        <v>26.54</v>
       </c>
       <c r="S65" t="n">
-        <v>-0.3</v>
+        <v>-0.24</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>397.1</v>
+        <v>397.12</v>
       </c>
       <c r="D66" t="n">
         <v>92</v>
@@ -7732,13 +7732,13 @@
         <v>-0.92</v>
       </c>
       <c r="F66" t="n">
-        <v>16.22</v>
+        <v>16.23</v>
       </c>
       <c r="G66" t="n">
-        <v>31.21</v>
+        <v>31.22</v>
       </c>
       <c r="H66" t="n">
-        <v>6.49</v>
+        <v>6.52</v>
       </c>
       <c r="I66" t="n">
         <v>0.38</v>
@@ -7750,22 +7750,22 @@
         <v>2.79</v>
       </c>
       <c r="L66" t="n">
-        <v>393.22</v>
+        <v>393.25</v>
       </c>
       <c r="M66" t="n">
-        <v>398.76</v>
+        <v>398.79</v>
       </c>
       <c r="N66" t="n">
-        <v>382.15</v>
+        <v>382.18</v>
       </c>
       <c r="O66" t="n">
-        <v>421.46</v>
+        <v>421.48</v>
       </c>
       <c r="P66" t="n">
         <v>1.63</v>
       </c>
       <c r="Q66" t="n">
-        <v>75.75</v>
+        <v>75.77</v>
       </c>
       <c r="R66" t="n">
         <v>6.49</v>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7836,55 +7836,55 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>310.59</v>
+        <v>310.76</v>
       </c>
       <c r="D67" t="n">
         <v>75</v>
       </c>
       <c r="E67" t="n">
-        <v>3.71</v>
+        <v>3.77</v>
       </c>
       <c r="F67" t="n">
-        <v>17.92</v>
+        <v>17.99</v>
       </c>
       <c r="G67" t="n">
-        <v>-12.73</v>
+        <v>-12.68</v>
       </c>
       <c r="H67" t="n">
-        <v>8.19</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J67" t="n">
         <v>16.11</v>
       </c>
       <c r="K67" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="L67" t="n">
-        <v>304.95</v>
+        <v>305.12</v>
       </c>
       <c r="M67" t="n">
-        <v>313.01</v>
+        <v>313.18</v>
       </c>
       <c r="N67" t="n">
-        <v>288.84</v>
+        <v>289.01</v>
       </c>
       <c r="O67" t="n">
-        <v>346.03</v>
+        <v>346.2</v>
       </c>
       <c r="P67" t="n">
         <v>1.63</v>
       </c>
       <c r="Q67" t="n">
-        <v>73.72</v>
+        <v>73.77</v>
       </c>
       <c r="R67" t="n">
-        <v>12.71</v>
+        <v>12.76</v>
       </c>
       <c r="S67" t="n">
-        <v>-2.09</v>
+        <v>-2.03</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -7949,25 +7949,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>159.51</v>
+        <v>159.54</v>
       </c>
       <c r="D68" t="n">
         <v>73</v>
       </c>
       <c r="E68" t="n">
-        <v>4.85</v>
+        <v>4.87</v>
       </c>
       <c r="F68" t="n">
-        <v>18.44</v>
+        <v>18.46</v>
       </c>
       <c r="G68" t="n">
-        <v>-5.61</v>
+        <v>-5.59</v>
       </c>
       <c r="H68" t="n">
-        <v>8.710000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="I68" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="J68" t="n">
         <v>7.63</v>
@@ -7976,28 +7976,28 @@
         <v>4.78</v>
       </c>
       <c r="L68" t="n">
-        <v>156.84</v>
+        <v>156.87</v>
       </c>
       <c r="M68" t="n">
-        <v>160.65</v>
+        <v>160.68</v>
       </c>
       <c r="N68" t="n">
-        <v>149.22</v>
+        <v>149.25</v>
       </c>
       <c r="O68" t="n">
-        <v>176.29</v>
+        <v>176.32</v>
       </c>
       <c r="P68" t="n">
         <v>1.63</v>
       </c>
       <c r="Q68" t="n">
-        <v>72.61</v>
+        <v>72.63</v>
       </c>
       <c r="R68" t="n">
-        <v>11.98</v>
+        <v>12</v>
       </c>
       <c r="S68" t="n">
-        <v>-0.47</v>
+        <v>-0.45</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MACD positivo; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8062,55 +8062,55 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>209.22</v>
+        <v>208.52</v>
       </c>
       <c r="D69" t="n">
         <v>71</v>
       </c>
       <c r="E69" t="n">
-        <v>4.53</v>
+        <v>4.18</v>
       </c>
       <c r="F69" t="n">
-        <v>65.25</v>
+        <v>64.7</v>
       </c>
       <c r="G69" t="n">
-        <v>73.48</v>
+        <v>72.91</v>
       </c>
       <c r="H69" t="n">
-        <v>55.52</v>
+        <v>54.99</v>
       </c>
       <c r="I69" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="J69" t="n">
         <v>11.79</v>
       </c>
       <c r="K69" t="n">
-        <v>5.64</v>
+        <v>5.66</v>
       </c>
       <c r="L69" t="n">
-        <v>205.09</v>
+        <v>204.4</v>
       </c>
       <c r="M69" t="n">
-        <v>210.99</v>
+        <v>210.29</v>
       </c>
       <c r="N69" t="n">
-        <v>193.3</v>
+        <v>192.61</v>
       </c>
       <c r="O69" t="n">
-        <v>235.16</v>
+        <v>234.47</v>
       </c>
       <c r="P69" t="n">
         <v>1.63</v>
       </c>
       <c r="Q69" t="n">
-        <v>89.05</v>
+        <v>88.98</v>
       </c>
       <c r="R69" t="n">
-        <v>32.25</v>
+        <v>31.84</v>
       </c>
       <c r="S69" t="n">
-        <v>-0.01</v>
+        <v>-0.35</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8175,55 +8175,55 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>242.92</v>
+        <v>243.17</v>
       </c>
       <c r="D70" t="n">
         <v>69</v>
       </c>
       <c r="E70" t="n">
-        <v>16.86</v>
+        <v>16.98</v>
       </c>
       <c r="F70" t="n">
-        <v>44.72</v>
+        <v>44.87</v>
       </c>
       <c r="G70" t="n">
-        <v>60.88</v>
+        <v>61.05</v>
       </c>
       <c r="H70" t="n">
-        <v>34.99</v>
+        <v>35.16</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="J70" t="n">
-        <v>9.31</v>
+        <v>9.32</v>
       </c>
       <c r="K70" t="n">
         <v>3.83</v>
       </c>
       <c r="L70" t="n">
-        <v>239.66</v>
+        <v>239.91</v>
       </c>
       <c r="M70" t="n">
-        <v>244.32</v>
+        <v>244.57</v>
       </c>
       <c r="N70" t="n">
-        <v>230.35</v>
+        <v>230.59</v>
       </c>
       <c r="O70" t="n">
-        <v>263.41</v>
+        <v>263.67</v>
       </c>
       <c r="P70" t="n">
         <v>1.63</v>
       </c>
       <c r="Q70" t="n">
-        <v>92.84999999999999</v>
+        <v>92.87</v>
       </c>
       <c r="R70" t="n">
-        <v>25.28</v>
+        <v>25.4</v>
       </c>
       <c r="S70" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -8284,22 +8284,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>591.2</v>
+        <v>591.3099999999999</v>
       </c>
       <c r="D71" t="n">
         <v>65</v>
       </c>
       <c r="E71" t="n">
-        <v>12.02</v>
+        <v>12.04</v>
       </c>
       <c r="F71" t="n">
-        <v>39.45</v>
+        <v>39.48</v>
       </c>
       <c r="G71" t="n">
-        <v>40.05</v>
+        <v>40.07</v>
       </c>
       <c r="H71" t="n">
-        <v>29.72</v>
+        <v>29.77</v>
       </c>
       <c r="I71" t="n">
         <v>0.61</v>
@@ -8311,28 +8311,28 @@
         <v>3.78</v>
       </c>
       <c r="L71" t="n">
-        <v>583.38</v>
+        <v>583.49</v>
       </c>
       <c r="M71" t="n">
-        <v>594.55</v>
+        <v>594.66</v>
       </c>
       <c r="N71" t="n">
-        <v>561.02</v>
+        <v>561.13</v>
       </c>
       <c r="O71" t="n">
-        <v>640.38</v>
+        <v>640.49</v>
       </c>
       <c r="P71" t="n">
         <v>1.63</v>
       </c>
       <c r="Q71" t="n">
-        <v>89.70999999999999</v>
+        <v>89.72</v>
       </c>
       <c r="R71" t="n">
-        <v>20.95</v>
+        <v>20.97</v>
       </c>
       <c r="S71" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8393,22 +8393,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>392.56</v>
+        <v>392.45</v>
       </c>
       <c r="D72" t="n">
         <v>96</v>
       </c>
       <c r="E72" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="F72" t="n">
-        <v>20.93</v>
+        <v>20.89</v>
       </c>
       <c r="G72" t="n">
-        <v>36.45</v>
+        <v>36.41</v>
       </c>
       <c r="H72" t="n">
-        <v>11.2</v>
+        <v>11.18</v>
       </c>
       <c r="I72" t="n">
         <v>0.44</v>
@@ -8420,28 +8420,28 @@
         <v>2.29</v>
       </c>
       <c r="L72" t="n">
-        <v>389.42</v>
+        <v>389.31</v>
       </c>
       <c r="M72" t="n">
-        <v>393.91</v>
+        <v>393.8</v>
       </c>
       <c r="N72" t="n">
-        <v>380.44</v>
+        <v>380.33</v>
       </c>
       <c r="O72" t="n">
-        <v>412.31</v>
+        <v>412.2</v>
       </c>
       <c r="P72" t="n">
         <v>1.63</v>
       </c>
       <c r="Q72" t="n">
-        <v>76.03</v>
+        <v>75.91</v>
       </c>
       <c r="R72" t="n">
-        <v>6.25</v>
+        <v>6.22</v>
       </c>
       <c r="S72" t="n">
-        <v>-2.87</v>
+        <v>-2.89</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8506,22 +8506,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1000</v>
+        <v>1001.99</v>
       </c>
       <c r="D73" t="n">
         <v>90</v>
       </c>
       <c r="E73" t="n">
-        <v>5.44</v>
+        <v>5.65</v>
       </c>
       <c r="F73" t="n">
-        <v>7.87</v>
+        <v>8.09</v>
       </c>
       <c r="G73" t="n">
-        <v>-2.27</v>
+        <v>-2.07</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.86</v>
+        <v>-1.62</v>
       </c>
       <c r="I73" t="n">
         <v>0.33</v>
@@ -8530,31 +8530,31 @@
         <v>32.41</v>
       </c>
       <c r="K73" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="L73" t="n">
-        <v>988.66</v>
+        <v>990.65</v>
       </c>
       <c r="M73" t="n">
-        <v>1004.86</v>
+        <v>1006.86</v>
       </c>
       <c r="N73" t="n">
-        <v>956.25</v>
+        <v>958.24</v>
       </c>
       <c r="O73" t="n">
-        <v>1071.3</v>
+        <v>1073.29</v>
       </c>
       <c r="P73" t="n">
         <v>1.63</v>
       </c>
       <c r="Q73" t="n">
-        <v>72.73999999999999</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="R73" t="n">
-        <v>5.91</v>
+        <v>6.11</v>
       </c>
       <c r="S73" t="n">
-        <v>-2.23</v>
+        <v>-2.04</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8615,25 +8615,25 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>87.31999999999999</v>
+        <v>87.34</v>
       </c>
       <c r="D74" t="n">
         <v>90</v>
       </c>
       <c r="E74" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="F74" t="n">
-        <v>6.87</v>
+        <v>6.89</v>
       </c>
       <c r="G74" t="n">
-        <v>18.14</v>
+        <v>18.17</v>
       </c>
       <c r="H74" t="n">
-        <v>-2.86</v>
+        <v>-2.82</v>
       </c>
       <c r="I74" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="J74" t="n">
         <v>2.56</v>
@@ -8642,28 +8642,28 @@
         <v>2.94</v>
       </c>
       <c r="L74" t="n">
-        <v>86.42</v>
+        <v>86.44</v>
       </c>
       <c r="M74" t="n">
-        <v>87.7</v>
+        <v>87.73</v>
       </c>
       <c r="N74" t="n">
-        <v>83.86</v>
+        <v>83.88</v>
       </c>
       <c r="O74" t="n">
-        <v>92.95999999999999</v>
+        <v>92.98</v>
       </c>
       <c r="P74" t="n">
         <v>1.63</v>
       </c>
       <c r="Q74" t="n">
-        <v>74.29000000000001</v>
+        <v>74.37</v>
       </c>
       <c r="R74" t="n">
-        <v>6.84</v>
+        <v>6.86</v>
       </c>
       <c r="S74" t="n">
-        <v>-1.27</v>
+        <v>-1.24</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8724,25 +8724,25 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>106.19</v>
+        <v>106.09</v>
       </c>
       <c r="D75" t="n">
         <v>84</v>
       </c>
       <c r="E75" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="F75" t="n">
-        <v>6.19</v>
+        <v>6.09</v>
       </c>
       <c r="G75" t="n">
-        <v>10.85</v>
+        <v>10.74</v>
       </c>
       <c r="H75" t="n">
-        <v>-3.54</v>
+        <v>-3.62</v>
       </c>
       <c r="I75" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="J75" t="n">
         <v>3.03</v>
@@ -8751,28 +8751,28 @@
         <v>2.85</v>
       </c>
       <c r="L75" t="n">
-        <v>105.13</v>
+        <v>105.03</v>
       </c>
       <c r="M75" t="n">
-        <v>106.65</v>
+        <v>106.54</v>
       </c>
       <c r="N75" t="n">
-        <v>102.1</v>
+        <v>102</v>
       </c>
       <c r="O75" t="n">
-        <v>112.85</v>
+        <v>112.75</v>
       </c>
       <c r="P75" t="n">
         <v>1.63</v>
       </c>
       <c r="Q75" t="n">
-        <v>73.29000000000001</v>
+        <v>72.88</v>
       </c>
       <c r="R75" t="n">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="S75" t="n">
-        <v>-2.47</v>
+        <v>-2.56</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8833,22 +8833,22 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>712.05</v>
+        <v>711.79</v>
       </c>
       <c r="D76" t="n">
         <v>82</v>
       </c>
       <c r="E76" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="F76" t="n">
-        <v>9.74</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>18.14</v>
+        <v>18.1</v>
       </c>
       <c r="H76" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="I76" t="n">
         <v>0.76</v>
@@ -8860,28 +8860,28 @@
         <v>1.5</v>
       </c>
       <c r="L76" t="n">
-        <v>708.3200000000001</v>
+        <v>708.0599999999999</v>
       </c>
       <c r="M76" t="n">
-        <v>713.65</v>
+        <v>713.39</v>
       </c>
       <c r="N76" t="n">
-        <v>697.67</v>
+        <v>697.41</v>
       </c>
       <c r="O76" t="n">
-        <v>735.48</v>
+        <v>735.22</v>
       </c>
       <c r="P76" t="n">
         <v>1.63</v>
       </c>
       <c r="Q76" t="n">
-        <v>75.72</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="R76" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="S76" t="n">
-        <v>-1.38</v>
+        <v>-1.42</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8942,25 +8942,25 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>681.9299999999999</v>
+        <v>681.5700000000001</v>
       </c>
       <c r="D77" t="n">
         <v>72</v>
       </c>
       <c r="E77" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="F77" t="n">
-        <v>4.47</v>
+        <v>4.41</v>
       </c>
       <c r="G77" t="n">
-        <v>8.67</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>-5.26</v>
+        <v>-5.3</v>
       </c>
       <c r="I77" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="J77" t="n">
         <v>6.61</v>
@@ -8969,28 +8969,28 @@
         <v>0.97</v>
       </c>
       <c r="L77" t="n">
-        <v>679.62</v>
+        <v>679.26</v>
       </c>
       <c r="M77" t="n">
-        <v>682.92</v>
+        <v>682.5599999999999</v>
       </c>
       <c r="N77" t="n">
-        <v>673</v>
+        <v>672.64</v>
       </c>
       <c r="O77" t="n">
-        <v>696.47</v>
+        <v>696.11</v>
       </c>
       <c r="P77" t="n">
         <v>1.63</v>
       </c>
       <c r="Q77" t="n">
-        <v>72.92</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="R77" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="S77" t="n">
-        <v>-1.04</v>
+        <v>-1.09</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9051,22 +9051,22 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>741.75</v>
+        <v>741.39</v>
       </c>
       <c r="D78" t="n">
         <v>72</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="F78" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="G78" t="n">
-        <v>8.66</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>-5.28</v>
+        <v>-5.31</v>
       </c>
       <c r="I78" t="n">
         <v>0.61</v>
@@ -9078,28 +9078,28 @@
         <v>0.97</v>
       </c>
       <c r="L78" t="n">
-        <v>739.23</v>
+        <v>738.87</v>
       </c>
       <c r="M78" t="n">
-        <v>742.83</v>
+        <v>742.47</v>
       </c>
       <c r="N78" t="n">
-        <v>732.03</v>
+        <v>731.67</v>
       </c>
       <c r="O78" t="n">
-        <v>757.6</v>
+        <v>757.24</v>
       </c>
       <c r="P78" t="n">
         <v>1.63</v>
       </c>
       <c r="Q78" t="n">
-        <v>72.67</v>
+        <v>72.23</v>
       </c>
       <c r="R78" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="S78" t="n">
-        <v>-1.04</v>
+        <v>-1.09</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9160,22 +9160,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>23.36</v>
+        <v>23.33</v>
       </c>
       <c r="D79" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.99</v>
+        <v>-3.11</v>
       </c>
       <c r="F79" t="n">
-        <v>28.99</v>
+        <v>28.82</v>
       </c>
       <c r="G79" t="n">
-        <v>44.02</v>
+        <v>43.83</v>
       </c>
       <c r="H79" t="n">
-        <v>19.26</v>
+        <v>19.11</v>
       </c>
       <c r="I79" t="n">
         <v>0.36</v>
@@ -9184,31 +9184,31 @@
         <v>1.67</v>
       </c>
       <c r="K79" t="n">
-        <v>7.13</v>
+        <v>7.14</v>
       </c>
       <c r="L79" t="n">
-        <v>22.78</v>
+        <v>22.75</v>
       </c>
       <c r="M79" t="n">
-        <v>23.61</v>
+        <v>23.58</v>
       </c>
       <c r="N79" t="n">
-        <v>21.11</v>
+        <v>21.08</v>
       </c>
       <c r="O79" t="n">
-        <v>27.02</v>
+        <v>26.99</v>
       </c>
       <c r="P79" t="n">
         <v>1.63</v>
       </c>
       <c r="Q79" t="n">
-        <v>67.48999999999999</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="R79" t="n">
-        <v>13.66</v>
+        <v>13.52</v>
       </c>
       <c r="S79" t="n">
-        <v>-9.67</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>BTC-USD 2.14% · ETH-USD -3.91%</t>
+          <t>BTC-USD 2.1% · ETH-USD -4.0%</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 2.14% · ETH-USD -3.91%; RSI algo alto; Volumen bajo; Muy alejada de MA20; Volatilidad alta</t>
+          <t>Sector no acompaña: BTC-USD 2.1% · ETH-USD -4.0%; RSI algo alto; Volumen bajo; Momentum negativo; Muy alejada de MA20</t>
         </is>
       </c>
     </row>
@@ -9269,25 +9269,25 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>242.26</v>
+        <v>242.36</v>
       </c>
       <c r="D80" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E80" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="F80" t="n">
-        <v>-3.28</v>
+        <v>-3.25</v>
       </c>
       <c r="G80" t="n">
-        <v>7.36</v>
+        <v>7.4</v>
       </c>
       <c r="H80" t="n">
-        <v>-13.01</v>
+        <v>-12.96</v>
       </c>
       <c r="I80" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="J80" t="n">
         <v>8.300000000000001</v>
@@ -9296,28 +9296,28 @@
         <v>3.43</v>
       </c>
       <c r="L80" t="n">
-        <v>239.36</v>
+        <v>239.45</v>
       </c>
       <c r="M80" t="n">
-        <v>243.51</v>
+        <v>243.61</v>
       </c>
       <c r="N80" t="n">
-        <v>231.05</v>
+        <v>231.15</v>
       </c>
       <c r="O80" t="n">
-        <v>260.54</v>
+        <v>260.63</v>
       </c>
       <c r="P80" t="n">
         <v>1.63</v>
       </c>
       <c r="Q80" t="n">
-        <v>37.91</v>
+        <v>38</v>
       </c>
       <c r="R80" t="n">
-        <v>-5.23</v>
+        <v>-5.2</v>
       </c>
       <c r="S80" t="n">
-        <v>-11.84</v>
+        <v>-11.81</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>XLE 7.49% · CL=F 20.16%</t>
+          <t>XLE 7.33% · CL=F 19.77%</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.49% · CL=F 20.16%; Tendencia larga positiva; MACD mejorando; Momentum 5D sano</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.33% · CL=F 19.77%; Tendencia larga positiva; MACD mejorando; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; RSI débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ; Lejos del máximo 20D</t>
         </is>
       </c>
     </row>
@@ -9382,25 +9382,25 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>145.01</v>
+        <v>144.81</v>
       </c>
       <c r="D81" t="n">
         <v>46</v>
       </c>
       <c r="E81" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="F81" t="n">
-        <v>-11.7</v>
+        <v>-11.82</v>
       </c>
       <c r="G81" t="n">
-        <v>5.67</v>
+        <v>5.52</v>
       </c>
       <c r="H81" t="n">
-        <v>-21.43</v>
+        <v>-21.53</v>
       </c>
       <c r="I81" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J81" t="n">
         <v>8.609999999999999</v>
@@ -9409,28 +9409,28 @@
         <v>5.94</v>
       </c>
       <c r="L81" t="n">
-        <v>142</v>
+        <v>141.8</v>
       </c>
       <c r="M81" t="n">
-        <v>146.3</v>
+        <v>146.1</v>
       </c>
       <c r="N81" t="n">
-        <v>133.39</v>
+        <v>133.19</v>
       </c>
       <c r="O81" t="n">
-        <v>163.95</v>
+        <v>163.75</v>
       </c>
       <c r="P81" t="n">
         <v>1.63</v>
       </c>
       <c r="Q81" t="n">
-        <v>30.04</v>
+        <v>29.96</v>
       </c>
       <c r="R81" t="n">
-        <v>-9.5</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="S81" t="n">
-        <v>-19.35</v>
+        <v>-19.46</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -9495,22 +9495,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>616.33</v>
+        <v>617.28</v>
       </c>
       <c r="D82" t="n">
         <v>35</v>
       </c>
       <c r="E82" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="F82" t="n">
-        <v>-10.49</v>
+        <v>-10.35</v>
       </c>
       <c r="G82" t="n">
-        <v>-4.33</v>
+        <v>-4.18</v>
       </c>
       <c r="H82" t="n">
-        <v>-20.22</v>
+        <v>-20.06</v>
       </c>
       <c r="I82" t="n">
         <v>0.41</v>
@@ -9522,28 +9522,28 @@
         <v>2.77</v>
       </c>
       <c r="L82" t="n">
-        <v>610.35</v>
+        <v>611.3</v>
       </c>
       <c r="M82" t="n">
-        <v>618.89</v>
+        <v>619.84</v>
       </c>
       <c r="N82" t="n">
-        <v>593.27</v>
+        <v>594.23</v>
       </c>
       <c r="O82" t="n">
-        <v>653.89</v>
+        <v>654.85</v>
       </c>
       <c r="P82" t="n">
         <v>1.63</v>
       </c>
       <c r="Q82" t="n">
-        <v>25.75</v>
+        <v>25.95</v>
       </c>
       <c r="R82" t="n">
-        <v>-2.91</v>
+        <v>-2.77</v>
       </c>
       <c r="S82" t="n">
-        <v>-9.81</v>
+        <v>-9.67</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MA20 sobre MA50; MACD mejorando; Momentum 5D sano</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MA20 sobre MA50; MACD mejorando; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9608,22 +9608,22 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8.710000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="D83" t="n">
         <v>36</v>
       </c>
       <c r="E83" t="n">
-        <v>-11.75</v>
+        <v>-12.06</v>
       </c>
       <c r="F83" t="n">
-        <v>-5.74</v>
+        <v>-6.06</v>
       </c>
       <c r="G83" t="n">
-        <v>-18.6</v>
+        <v>-18.88</v>
       </c>
       <c r="H83" t="n">
-        <v>-15.47</v>
+        <v>-15.77</v>
       </c>
       <c r="I83" t="n">
         <v>0.59</v>
@@ -9632,31 +9632,31 @@
         <v>0.45</v>
       </c>
       <c r="K83" t="n">
-        <v>5.18</v>
+        <v>5.2</v>
       </c>
       <c r="L83" t="n">
-        <v>8.550000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="M83" t="n">
-        <v>8.779999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="N83" t="n">
-        <v>8.1</v>
+        <v>8.07</v>
       </c>
       <c r="O83" t="n">
-        <v>9.699999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="P83" t="n">
         <v>1.62</v>
       </c>
       <c r="Q83" t="n">
-        <v>48.8</v>
+        <v>48.36</v>
       </c>
       <c r="R83" t="n">
-        <v>-4.34</v>
+        <v>-4.65</v>
       </c>
       <c r="S83" t="n">
-        <v>-11.84</v>
+        <v>-12.15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9717,22 +9717,22 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>74.87</v>
+        <v>74.81</v>
       </c>
       <c r="D84" t="n">
         <v>29</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.77</v>
+        <v>-0.85</v>
       </c>
       <c r="F84" t="n">
-        <v>-2.92</v>
+        <v>-3</v>
       </c>
       <c r="G84" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="H84" t="n">
-        <v>-12.65</v>
+        <v>-12.71</v>
       </c>
       <c r="I84" t="n">
         <v>0.49</v>
@@ -9744,28 +9744,28 @@
         <v>3.5</v>
       </c>
       <c r="L84" t="n">
-        <v>73.95</v>
+        <v>73.89</v>
       </c>
       <c r="M84" t="n">
-        <v>75.26000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="N84" t="n">
-        <v>71.33</v>
+        <v>71.27</v>
       </c>
       <c r="O84" t="n">
-        <v>80.63</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="P84" t="n">
         <v>1.63</v>
       </c>
       <c r="Q84" t="n">
-        <v>46.12</v>
+        <v>45.94</v>
       </c>
       <c r="R84" t="n">
-        <v>-0.79</v>
+        <v>-0.86</v>
       </c>
       <c r="S84" t="n">
-        <v>-7.37</v>
+        <v>-7.45</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MA20 sobre MA50</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -9841,10 +9841,10 @@
         <v>4.11</v>
       </c>
       <c r="H85" t="n">
-        <v>-14.8</v>
+        <v>-14.78</v>
       </c>
       <c r="I85" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="J85" t="n">
         <v>2.47</v>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MA20 sobre MA50</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -9935,22 +9935,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>134.62</v>
+        <v>134.46</v>
       </c>
       <c r="D86" t="n">
         <v>22</v>
       </c>
       <c r="E86" t="n">
-        <v>-2.31</v>
+        <v>-2.42</v>
       </c>
       <c r="F86" t="n">
-        <v>-8.039999999999999</v>
+        <v>-8.15</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.2</v>
+        <v>-0.32</v>
       </c>
       <c r="H86" t="n">
-        <v>-17.77</v>
+        <v>-17.86</v>
       </c>
       <c r="I86" t="n">
         <v>0.43</v>
@@ -9959,31 +9959,31 @@
         <v>5.67</v>
       </c>
       <c r="K86" t="n">
-        <v>4.21</v>
+        <v>4.22</v>
       </c>
       <c r="L86" t="n">
-        <v>132.63</v>
+        <v>132.47</v>
       </c>
       <c r="M86" t="n">
-        <v>135.47</v>
+        <v>135.31</v>
       </c>
       <c r="N86" t="n">
-        <v>126.96</v>
+        <v>126.8</v>
       </c>
       <c r="O86" t="n">
-        <v>147.1</v>
+        <v>146.94</v>
       </c>
       <c r="P86" t="n">
         <v>1.63</v>
       </c>
       <c r="Q86" t="n">
-        <v>39.85</v>
+        <v>39.62</v>
       </c>
       <c r="R86" t="n">
-        <v>-3.72</v>
+        <v>-3.83</v>
       </c>
       <c r="S86" t="n">
-        <v>-11.83</v>
+        <v>-11.93</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -10044,22 +10044,22 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>174.87</v>
+        <v>174.57</v>
       </c>
       <c r="D87" t="n">
         <v>15</v>
       </c>
       <c r="E87" t="n">
-        <v>-3.82</v>
+        <v>-3.99</v>
       </c>
       <c r="F87" t="n">
-        <v>-3.99</v>
+        <v>-4.16</v>
       </c>
       <c r="G87" t="n">
-        <v>-5.39</v>
+        <v>-5.55</v>
       </c>
       <c r="H87" t="n">
-        <v>-13.72</v>
+        <v>-13.87</v>
       </c>
       <c r="I87" t="n">
         <v>0.55</v>
@@ -10068,31 +10068,31 @@
         <v>6.87</v>
       </c>
       <c r="K87" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="L87" t="n">
-        <v>172.46</v>
+        <v>172.16</v>
       </c>
       <c r="M87" t="n">
-        <v>175.9</v>
+        <v>175.6</v>
       </c>
       <c r="N87" t="n">
-        <v>165.59</v>
+        <v>165.29</v>
       </c>
       <c r="O87" t="n">
-        <v>189.99</v>
+        <v>189.69</v>
       </c>
       <c r="P87" t="n">
         <v>1.63</v>
       </c>
       <c r="Q87" t="n">
-        <v>45.33</v>
+        <v>45.04</v>
       </c>
       <c r="R87" t="n">
-        <v>-2.76</v>
+        <v>-2.92</v>
       </c>
       <c r="S87" t="n">
-        <v>-9.66</v>
+        <v>-9.81</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -10153,25 +10153,25 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>219.59</v>
+        <v>219.43</v>
       </c>
       <c r="D88" t="n">
         <v>15</v>
       </c>
       <c r="E88" t="n">
-        <v>-4.43</v>
+        <v>-4.5</v>
       </c>
       <c r="F88" t="n">
-        <v>-12.73</v>
+        <v>-12.79</v>
       </c>
       <c r="G88" t="n">
-        <v>-13.69</v>
+        <v>-13.75</v>
       </c>
       <c r="H88" t="n">
-        <v>-22.46</v>
+        <v>-22.5</v>
       </c>
       <c r="I88" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J88" t="n">
         <v>5.6</v>
@@ -10180,28 +10180,28 @@
         <v>2.55</v>
       </c>
       <c r="L88" t="n">
-        <v>217.63</v>
+        <v>217.47</v>
       </c>
       <c r="M88" t="n">
-        <v>220.43</v>
+        <v>220.26</v>
       </c>
       <c r="N88" t="n">
-        <v>212.03</v>
+        <v>211.87</v>
       </c>
       <c r="O88" t="n">
-        <v>231.91</v>
+        <v>231.74</v>
       </c>
       <c r="P88" t="n">
         <v>1.63</v>
       </c>
       <c r="Q88" t="n">
-        <v>42.93</v>
+        <v>42.74</v>
       </c>
       <c r="R88" t="n">
-        <v>-4.37</v>
+        <v>-4.43</v>
       </c>
       <c r="S88" t="n">
-        <v>-14.43</v>
+        <v>-14.49</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -10262,19 +10262,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>167.54</v>
+        <v>167.51</v>
       </c>
       <c r="D89" t="n">
         <v>15</v>
       </c>
       <c r="E89" t="n">
-        <v>-7.14</v>
+        <v>-7.16</v>
       </c>
       <c r="F89" t="n">
-        <v>-15.23</v>
+        <v>-15.25</v>
       </c>
       <c r="G89" t="n">
-        <v>-21.4</v>
+        <v>-21.41</v>
       </c>
       <c r="H89" t="n">
         <v>-24.96</v>
@@ -10289,28 +10289,28 @@
         <v>4.06</v>
       </c>
       <c r="L89" t="n">
-        <v>165.16</v>
+        <v>165.13</v>
       </c>
       <c r="M89" t="n">
-        <v>168.56</v>
+        <v>168.53</v>
       </c>
       <c r="N89" t="n">
-        <v>158.35</v>
+        <v>158.32</v>
       </c>
       <c r="O89" t="n">
-        <v>182.52</v>
+        <v>182.49</v>
       </c>
       <c r="P89" t="n">
         <v>1.63</v>
       </c>
       <c r="Q89" t="n">
-        <v>39.82</v>
+        <v>39.78</v>
       </c>
       <c r="R89" t="n">
-        <v>-5.81</v>
+        <v>-5.82</v>
       </c>
       <c r="S89" t="n">
-        <v>-16.05</v>
+        <v>-16.07</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -10371,22 +10371,22 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>87.29000000000001</v>
+        <v>87.17</v>
       </c>
       <c r="D90" t="n">
         <v>14</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.23</v>
+        <v>-0.37</v>
       </c>
       <c r="F90" t="n">
-        <v>-10.3</v>
+        <v>-10.43</v>
       </c>
       <c r="G90" t="n">
-        <v>13.36</v>
+        <v>13.2</v>
       </c>
       <c r="H90" t="n">
-        <v>-20.03</v>
+        <v>-20.14</v>
       </c>
       <c r="I90" t="n">
         <v>0.47</v>
@@ -10398,28 +10398,28 @@
         <v>2.7</v>
       </c>
       <c r="L90" t="n">
-        <v>86.45999999999999</v>
+        <v>86.34</v>
       </c>
       <c r="M90" t="n">
-        <v>87.64</v>
+        <v>87.52</v>
       </c>
       <c r="N90" t="n">
-        <v>84.11</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="O90" t="n">
-        <v>92.45999999999999</v>
+        <v>92.34</v>
       </c>
       <c r="P90" t="n">
         <v>1.63</v>
       </c>
       <c r="Q90" t="n">
-        <v>36.14</v>
+        <v>35.61</v>
       </c>
       <c r="R90" t="n">
-        <v>-3.29</v>
+        <v>-3.42</v>
       </c>
       <c r="S90" t="n">
-        <v>-10.57</v>
+        <v>-10.69</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -10480,22 +10480,22 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>111.56</v>
+        <v>111.57</v>
       </c>
       <c r="D91" t="n">
         <v>57</v>
       </c>
       <c r="E91" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F91" t="n">
-        <v>-6.31</v>
+        <v>-6.3</v>
       </c>
       <c r="G91" t="n">
         <v>-7.77</v>
       </c>
       <c r="H91" t="n">
-        <v>-16.04</v>
+        <v>-16.01</v>
       </c>
       <c r="I91" t="n">
         <v>0.44</v>
@@ -10507,25 +10507,25 @@
         <v>2.39</v>
       </c>
       <c r="L91" t="n">
-        <v>110.63</v>
+        <v>110.64</v>
       </c>
       <c r="M91" t="n">
-        <v>111.96</v>
+        <v>111.97</v>
       </c>
       <c r="N91" t="n">
-        <v>107.97</v>
+        <v>107.98</v>
       </c>
       <c r="O91" t="n">
-        <v>117.42</v>
+        <v>117.43</v>
       </c>
       <c r="P91" t="n">
         <v>1.63</v>
       </c>
       <c r="Q91" t="n">
-        <v>54.89</v>
+        <v>54.93</v>
       </c>
       <c r="R91" t="n">
-        <v>-0.71</v>
+        <v>-0.7</v>
       </c>
       <c r="S91" t="n">
         <v>-6.53</v>
@@ -10589,22 +10589,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>282.87</v>
+        <v>282.76</v>
       </c>
       <c r="D92" t="n">
         <v>35</v>
       </c>
       <c r="E92" t="n">
-        <v>-4.81</v>
+        <v>-4.84</v>
       </c>
       <c r="F92" t="n">
-        <v>-6.99</v>
+        <v>-7.03</v>
       </c>
       <c r="G92" t="n">
-        <v>-15.37</v>
+        <v>-15.41</v>
       </c>
       <c r="H92" t="n">
-        <v>-16.72</v>
+        <v>-16.74</v>
       </c>
       <c r="I92" t="n">
         <v>0.36</v>
@@ -10616,28 +10616,28 @@
         <v>3.41</v>
       </c>
       <c r="L92" t="n">
-        <v>279.49</v>
+        <v>279.38</v>
       </c>
       <c r="M92" t="n">
-        <v>284.32</v>
+        <v>284.21</v>
       </c>
       <c r="N92" t="n">
-        <v>269.84</v>
+        <v>269.73</v>
       </c>
       <c r="O92" t="n">
-        <v>304.11</v>
+        <v>304</v>
       </c>
       <c r="P92" t="n">
         <v>1.63</v>
       </c>
       <c r="Q92" t="n">
-        <v>48.96</v>
+        <v>48.9</v>
       </c>
       <c r="R92" t="n">
-        <v>-2.58</v>
+        <v>-2.62</v>
       </c>
       <c r="S92" t="n">
-        <v>-8.75</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10698,55 +10698,55 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>70.79000000000001</v>
+        <v>70.59</v>
       </c>
       <c r="D93" t="n">
         <v>33</v>
       </c>
       <c r="E93" t="n">
-        <v>-5.42</v>
+        <v>-5.69</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.66</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>33.84</v>
+        <v>33.47</v>
       </c>
       <c r="H93" t="n">
-        <v>-10.39</v>
+        <v>-10.65</v>
       </c>
       <c r="I93" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="J93" t="n">
         <v>2.58</v>
       </c>
       <c r="K93" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="L93" t="n">
-        <v>69.89</v>
+        <v>69.69</v>
       </c>
       <c r="M93" t="n">
-        <v>71.18000000000001</v>
+        <v>70.98</v>
       </c>
       <c r="N93" t="n">
-        <v>67.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="O93" t="n">
-        <v>76.47</v>
+        <v>76.27</v>
       </c>
       <c r="P93" t="n">
         <v>1.63</v>
       </c>
       <c r="Q93" t="n">
-        <v>48.66</v>
+        <v>48.13</v>
       </c>
       <c r="R93" t="n">
-        <v>-0.9</v>
+        <v>-1.17</v>
       </c>
       <c r="S93" t="n">
-        <v>-8.26</v>
+        <v>-8.51</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10807,22 +10807,22 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>123.66</v>
+        <v>123.55</v>
       </c>
       <c r="D94" t="n">
         <v>33</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.51</v>
+        <v>-1.59</v>
       </c>
       <c r="F94" t="n">
-        <v>-6</v>
+        <v>-6.09</v>
       </c>
       <c r="G94" t="n">
-        <v>7.52</v>
+        <v>7.43</v>
       </c>
       <c r="H94" t="n">
-        <v>-15.73</v>
+        <v>-15.8</v>
       </c>
       <c r="I94" t="n">
         <v>0.26</v>
@@ -10834,28 +10834,28 @@
         <v>2.68</v>
       </c>
       <c r="L94" t="n">
-        <v>122.5</v>
+        <v>122.39</v>
       </c>
       <c r="M94" t="n">
-        <v>124.16</v>
+        <v>124.05</v>
       </c>
       <c r="N94" t="n">
-        <v>119.19</v>
+        <v>119.08</v>
       </c>
       <c r="O94" t="n">
-        <v>130.94</v>
+        <v>130.83</v>
       </c>
       <c r="P94" t="n">
         <v>1.63</v>
       </c>
       <c r="Q94" t="n">
-        <v>35.3</v>
+        <v>35.06</v>
       </c>
       <c r="R94" t="n">
-        <v>-2.87</v>
+        <v>-2.95</v>
       </c>
       <c r="S94" t="n">
-        <v>-8.16</v>
+        <v>-8.25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10916,22 +10916,22 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>51.21</v>
+        <v>51.17</v>
       </c>
       <c r="D95" t="n">
         <v>28</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="F95" t="n">
-        <v>-2.34</v>
+        <v>-2.41</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.31</v>
+        <v>-1.38</v>
       </c>
       <c r="H95" t="n">
-        <v>-12.07</v>
+        <v>-12.12</v>
       </c>
       <c r="I95" t="n">
         <v>0.44</v>
@@ -10943,28 +10943,28 @@
         <v>1.24</v>
       </c>
       <c r="L95" t="n">
-        <v>50.98</v>
+        <v>50.94</v>
       </c>
       <c r="M95" t="n">
-        <v>51.3</v>
+        <v>51.26</v>
       </c>
       <c r="N95" t="n">
-        <v>50.35</v>
+        <v>50.31</v>
       </c>
       <c r="O95" t="n">
-        <v>52.6</v>
+        <v>52.56</v>
       </c>
       <c r="P95" t="n">
         <v>1.63</v>
       </c>
       <c r="Q95" t="n">
-        <v>40.44</v>
+        <v>39.94</v>
       </c>
       <c r="R95" t="n">
-        <v>-0.96</v>
+        <v>-1.03</v>
       </c>
       <c r="S95" t="n">
-        <v>-3.73</v>
+        <v>-3.81</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11025,22 +11025,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>84.53</v>
+        <v>84.55</v>
       </c>
       <c r="D96" t="n">
         <v>26</v>
       </c>
       <c r="E96" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="F96" t="n">
-        <v>-12.69</v>
+        <v>-12.66</v>
       </c>
       <c r="G96" t="n">
-        <v>-24.19</v>
+        <v>-24.16</v>
       </c>
       <c r="H96" t="n">
-        <v>-22.42</v>
+        <v>-22.37</v>
       </c>
       <c r="I96" t="n">
         <v>0.51</v>
@@ -11052,28 +11052,28 @@
         <v>2.44</v>
       </c>
       <c r="L96" t="n">
-        <v>83.8</v>
+        <v>83.83</v>
       </c>
       <c r="M96" t="n">
-        <v>84.83</v>
+        <v>84.86</v>
       </c>
       <c r="N96" t="n">
-        <v>81.73999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="O96" t="n">
-        <v>89.06999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P96" t="n">
         <v>1.63</v>
       </c>
       <c r="Q96" t="n">
-        <v>26.4</v>
+        <v>26.44</v>
       </c>
       <c r="R96" t="n">
-        <v>-4.75</v>
+        <v>-4.72</v>
       </c>
       <c r="S96" t="n">
-        <v>-13.15</v>
+        <v>-13.12</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11134,22 +11134,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>45</v>
+        <v>44.92</v>
       </c>
       <c r="D97" t="n">
         <v>24</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.82</v>
+        <v>-0.99</v>
       </c>
       <c r="F97" t="n">
-        <v>-11.43</v>
+        <v>-11.59</v>
       </c>
       <c r="G97" t="n">
-        <v>8.16</v>
+        <v>7.97</v>
       </c>
       <c r="H97" t="n">
-        <v>-21.16</v>
+        <v>-21.3</v>
       </c>
       <c r="I97" t="n">
         <v>0.54</v>
@@ -11161,28 +11161,28 @@
         <v>3.36</v>
       </c>
       <c r="L97" t="n">
-        <v>44.47</v>
+        <v>44.39</v>
       </c>
       <c r="M97" t="n">
-        <v>45.23</v>
+        <v>45.15</v>
       </c>
       <c r="N97" t="n">
-        <v>42.96</v>
+        <v>42.88</v>
       </c>
       <c r="O97" t="n">
-        <v>48.33</v>
+        <v>48.25</v>
       </c>
       <c r="P97" t="n">
         <v>1.63</v>
       </c>
       <c r="Q97" t="n">
-        <v>22.62</v>
+        <v>22.41</v>
       </c>
       <c r="R97" t="n">
-        <v>-6.76</v>
+        <v>-6.92</v>
       </c>
       <c r="S97" t="n">
-        <v>-13.96</v>
+        <v>-14.11</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11243,55 +11243,55 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>77.36</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="D98" t="n">
         <v>22</v>
       </c>
       <c r="E98" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-14.95</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H98" t="n">
+        <v>-24.66</v>
+      </c>
+      <c r="I98" t="n">
         <v>0.43</v>
-      </c>
-      <c r="F98" t="n">
-        <v>-14.75</v>
-      </c>
-      <c r="G98" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-24.48</v>
-      </c>
-      <c r="I98" t="n">
-        <v>0.42</v>
       </c>
       <c r="J98" t="n">
         <v>4.44</v>
       </c>
       <c r="K98" t="n">
-        <v>5.75</v>
+        <v>5.76</v>
       </c>
       <c r="L98" t="n">
-        <v>75.81</v>
+        <v>75.63</v>
       </c>
       <c r="M98" t="n">
-        <v>78.03</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="N98" t="n">
-        <v>71.36</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="O98" t="n">
-        <v>87.14</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="P98" t="n">
         <v>1.63</v>
       </c>
       <c r="Q98" t="n">
-        <v>41.59</v>
+        <v>41.4</v>
       </c>
       <c r="R98" t="n">
-        <v>-3.17</v>
+        <v>-3.39</v>
       </c>
       <c r="S98" t="n">
-        <v>-16.26</v>
+        <v>-16.45</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11352,55 +11352,55 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>557.01</v>
+        <v>556.11</v>
       </c>
       <c r="D99" t="n">
         <v>21</v>
       </c>
       <c r="E99" t="n">
-        <v>-3.1</v>
+        <v>-3.26</v>
       </c>
       <c r="F99" t="n">
-        <v>-5.67</v>
+        <v>-5.82</v>
       </c>
       <c r="G99" t="n">
-        <v>-15.61</v>
+        <v>-15.75</v>
       </c>
       <c r="H99" t="n">
-        <v>-15.4</v>
+        <v>-15.53</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="J99" t="n">
-        <v>14.96</v>
+        <v>14.99</v>
       </c>
       <c r="K99" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="L99" t="n">
-        <v>551.77</v>
+        <v>550.86</v>
       </c>
       <c r="M99" t="n">
-        <v>559.25</v>
+        <v>558.36</v>
       </c>
       <c r="N99" t="n">
-        <v>536.8099999999999</v>
+        <v>535.87</v>
       </c>
       <c r="O99" t="n">
-        <v>589.91</v>
+        <v>589.09</v>
       </c>
       <c r="P99" t="n">
         <v>1.63</v>
       </c>
       <c r="Q99" t="n">
-        <v>45.98</v>
+        <v>45.68</v>
       </c>
       <c r="R99" t="n">
-        <v>-3.69</v>
+        <v>-3.83</v>
       </c>
       <c r="S99" t="n">
-        <v>-6.96</v>
+        <v>-7.11</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11461,19 +11461,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>25.39</v>
+        <v>25.38</v>
       </c>
       <c r="D100" t="n">
         <v>20</v>
       </c>
       <c r="E100" t="n">
-        <v>-1.15</v>
+        <v>-1.17</v>
       </c>
       <c r="F100" t="n">
-        <v>-6.37</v>
+        <v>-6.39</v>
       </c>
       <c r="G100" t="n">
-        <v>-3.93</v>
+        <v>-3.95</v>
       </c>
       <c r="H100" t="n">
         <v>-16.1</v>
@@ -11488,13 +11488,13 @@
         <v>2.13</v>
       </c>
       <c r="L100" t="n">
-        <v>25.2</v>
+        <v>25.19</v>
       </c>
       <c r="M100" t="n">
-        <v>25.47</v>
+        <v>25.46</v>
       </c>
       <c r="N100" t="n">
-        <v>24.66</v>
+        <v>24.65</v>
       </c>
       <c r="O100" t="n">
         <v>26.57</v>
@@ -11503,13 +11503,13 @@
         <v>1.63</v>
       </c>
       <c r="Q100" t="n">
-        <v>32.97</v>
+        <v>32.91</v>
       </c>
       <c r="R100" t="n">
-        <v>-2.74</v>
+        <v>-2.76</v>
       </c>
       <c r="S100" t="n">
-        <v>-7.35</v>
+        <v>-7.36</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11570,25 +11570,25 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>222.61</v>
+        <v>222.66</v>
       </c>
       <c r="D101" t="n">
         <v>19</v>
       </c>
       <c r="E101" t="n">
-        <v>-6.21</v>
+        <v>-6.19</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="G101" t="n">
-        <v>-4.75</v>
+        <v>-4.73</v>
       </c>
       <c r="H101" t="n">
-        <v>-10.07</v>
+        <v>-10.03</v>
       </c>
       <c r="I101" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="J101" t="n">
         <v>7.22</v>
@@ -11597,28 +11597,28 @@
         <v>3.24</v>
       </c>
       <c r="L101" t="n">
-        <v>220.08</v>
+        <v>220.13</v>
       </c>
       <c r="M101" t="n">
-        <v>223.69</v>
+        <v>223.74</v>
       </c>
       <c r="N101" t="n">
-        <v>212.86</v>
+        <v>212.91</v>
       </c>
       <c r="O101" t="n">
-        <v>238.49</v>
+        <v>238.54</v>
       </c>
       <c r="P101" t="n">
         <v>1.63</v>
       </c>
       <c r="Q101" t="n">
-        <v>42.71</v>
+        <v>42.75</v>
       </c>
       <c r="R101" t="n">
-        <v>-3.13</v>
+        <v>-3.11</v>
       </c>
       <c r="S101" t="n">
-        <v>-8.789999999999999</v>
+        <v>-8.77</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11679,25 +11679,25 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>496.28</v>
+        <v>495.93</v>
       </c>
       <c r="D102" t="n">
         <v>19</v>
       </c>
       <c r="E102" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="F102" t="n">
-        <v>-4.8</v>
+        <v>-4.87</v>
       </c>
       <c r="G102" t="n">
-        <v>-4.45</v>
+        <v>-4.51</v>
       </c>
       <c r="H102" t="n">
-        <v>-14.53</v>
+        <v>-14.58</v>
       </c>
       <c r="I102" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J102" t="n">
         <v>13.11</v>
@@ -11706,28 +11706,28 @@
         <v>2.64</v>
       </c>
       <c r="L102" t="n">
-        <v>491.69</v>
+        <v>491.35</v>
       </c>
       <c r="M102" t="n">
-        <v>498.25</v>
+        <v>497.9</v>
       </c>
       <c r="N102" t="n">
-        <v>478.59</v>
+        <v>478.24</v>
       </c>
       <c r="O102" t="n">
-        <v>525.11</v>
+        <v>524.77</v>
       </c>
       <c r="P102" t="n">
         <v>1.63</v>
       </c>
       <c r="Q102" t="n">
-        <v>45.2</v>
+        <v>45.02</v>
       </c>
       <c r="R102" t="n">
-        <v>-1.21</v>
+        <v>-1.27</v>
       </c>
       <c r="S102" t="n">
-        <v>-7.1</v>
+        <v>-7.16</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11788,25 +11788,25 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>298.14</v>
+        <v>298.06</v>
       </c>
       <c r="D103" t="n">
         <v>18</v>
       </c>
       <c r="E103" t="n">
-        <v>-1.31</v>
+        <v>-1.34</v>
       </c>
       <c r="F103" t="n">
-        <v>-3.92</v>
+        <v>-3.94</v>
       </c>
       <c r="G103" t="n">
-        <v>-2.72</v>
+        <v>-2.75</v>
       </c>
       <c r="H103" t="n">
         <v>-13.65</v>
       </c>
       <c r="I103" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="J103" t="n">
         <v>6.08</v>
@@ -11815,28 +11815,28 @@
         <v>2.04</v>
       </c>
       <c r="L103" t="n">
-        <v>296.01</v>
+        <v>295.93</v>
       </c>
       <c r="M103" t="n">
-        <v>299.05</v>
+        <v>298.97</v>
       </c>
       <c r="N103" t="n">
-        <v>289.93</v>
+        <v>289.86</v>
       </c>
       <c r="O103" t="n">
-        <v>311.5</v>
+        <v>311.43</v>
       </c>
       <c r="P103" t="n">
         <v>1.63</v>
       </c>
       <c r="Q103" t="n">
-        <v>35.24</v>
+        <v>35.18</v>
       </c>
       <c r="R103" t="n">
-        <v>-3.27</v>
+        <v>-3.3</v>
       </c>
       <c r="S103" t="n">
-        <v>-6.9</v>
+        <v>-6.93</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11897,22 +11897,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>49.6</v>
+        <v>49.55</v>
       </c>
       <c r="D104" t="n">
         <v>11</v>
       </c>
       <c r="E104" t="n">
-        <v>-3.32</v>
+        <v>-3.43</v>
       </c>
       <c r="F104" t="n">
-        <v>-7.99</v>
+        <v>-8.09</v>
       </c>
       <c r="G104" t="n">
-        <v>-5.47</v>
+        <v>-5.57</v>
       </c>
       <c r="H104" t="n">
-        <v>-17.72</v>
+        <v>-17.8</v>
       </c>
       <c r="I104" t="n">
         <v>0.55</v>
@@ -11924,28 +11924,28 @@
         <v>2.35</v>
       </c>
       <c r="L104" t="n">
-        <v>49.2</v>
+        <v>49.14</v>
       </c>
       <c r="M104" t="n">
-        <v>49.78</v>
+        <v>49.72</v>
       </c>
       <c r="N104" t="n">
-        <v>48.03</v>
+        <v>47.98</v>
       </c>
       <c r="O104" t="n">
-        <v>52.17</v>
+        <v>52.12</v>
       </c>
       <c r="P104" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q104" t="n">
-        <v>31.06</v>
+        <v>30.85</v>
       </c>
       <c r="R104" t="n">
-        <v>-4.93</v>
+        <v>-5.03</v>
       </c>
       <c r="S104" t="n">
-        <v>-9.23</v>
+        <v>-9.33</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12006,22 +12006,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>276.44</v>
+        <v>276.32</v>
       </c>
       <c r="D105" t="n">
         <v>11</v>
       </c>
       <c r="E105" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="F105" t="n">
-        <v>-11.21</v>
+        <v>-11.25</v>
       </c>
       <c r="G105" t="n">
-        <v>-15.02</v>
+        <v>-15.05</v>
       </c>
       <c r="H105" t="n">
-        <v>-20.94</v>
+        <v>-20.96</v>
       </c>
       <c r="I105" t="n">
         <v>0.4</v>
@@ -12033,28 +12033,28 @@
         <v>2.01</v>
       </c>
       <c r="L105" t="n">
-        <v>274.5</v>
+        <v>274.38</v>
       </c>
       <c r="M105" t="n">
-        <v>277.28</v>
+        <v>277.15</v>
       </c>
       <c r="N105" t="n">
-        <v>268.96</v>
+        <v>268.83</v>
       </c>
       <c r="O105" t="n">
-        <v>288.64</v>
+        <v>288.52</v>
       </c>
       <c r="P105" t="n">
         <v>1.63</v>
       </c>
       <c r="Q105" t="n">
-        <v>28.78</v>
+        <v>28.51</v>
       </c>
       <c r="R105" t="n">
-        <v>-3.9</v>
+        <v>-3.94</v>
       </c>
       <c r="S105" t="n">
-        <v>-11.55</v>
+        <v>-11.59</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12115,22 +12115,22 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>15.73</v>
+        <v>15.69</v>
       </c>
       <c r="D106" t="n">
         <v>11</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.1</v>
+        <v>-0.35</v>
       </c>
       <c r="F106" t="n">
-        <v>-19.02</v>
+        <v>-19.22</v>
       </c>
       <c r="G106" t="n">
-        <v>-18.47</v>
+        <v>-18.68</v>
       </c>
       <c r="H106" t="n">
-        <v>-28.75</v>
+        <v>-28.93</v>
       </c>
       <c r="I106" t="n">
         <v>0.46</v>
@@ -12139,31 +12139,31 @@
         <v>0.82</v>
       </c>
       <c r="K106" t="n">
-        <v>5.19</v>
+        <v>5.2</v>
       </c>
       <c r="L106" t="n">
-        <v>15.45</v>
+        <v>15.41</v>
       </c>
       <c r="M106" t="n">
-        <v>15.86</v>
+        <v>15.82</v>
       </c>
       <c r="N106" t="n">
-        <v>14.63</v>
+        <v>14.59</v>
       </c>
       <c r="O106" t="n">
-        <v>17.53</v>
+        <v>17.49</v>
       </c>
       <c r="P106" t="n">
         <v>1.62</v>
       </c>
       <c r="Q106" t="n">
-        <v>30.7</v>
+        <v>30.54</v>
       </c>
       <c r="R106" t="n">
-        <v>-7.12</v>
+        <v>-7.34</v>
       </c>
       <c r="S106" t="n">
-        <v>-20.41</v>
+        <v>-20.61</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12224,55 +12224,55 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>73.33</v>
+        <v>73.25</v>
       </c>
       <c r="D107" t="n">
         <v>4</v>
       </c>
       <c r="E107" t="n">
-        <v>-3.05</v>
+        <v>-3.16</v>
       </c>
       <c r="F107" t="n">
-        <v>-9.4</v>
+        <v>-9.51</v>
       </c>
       <c r="G107" t="n">
-        <v>-15.78</v>
+        <v>-15.87</v>
       </c>
       <c r="H107" t="n">
-        <v>-19.13</v>
+        <v>-19.22</v>
       </c>
       <c r="I107" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="J107" t="n">
         <v>1.9</v>
       </c>
       <c r="K107" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="L107" t="n">
-        <v>72.67</v>
+        <v>72.58</v>
       </c>
       <c r="M107" t="n">
-        <v>73.62</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="N107" t="n">
-        <v>70.77</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="O107" t="n">
-        <v>77.52</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="P107" t="n">
         <v>1.63</v>
       </c>
       <c r="Q107" t="n">
-        <v>29.21</v>
+        <v>29.06</v>
       </c>
       <c r="R107" t="n">
-        <v>-6.46</v>
+        <v>-6.56</v>
       </c>
       <c r="S107" t="n">
-        <v>-11.25</v>
+        <v>-11.35</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12333,22 +12333,22 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>220.71</v>
+        <v>220.2</v>
       </c>
       <c r="D108" t="n">
         <v>4</v>
       </c>
       <c r="E108" t="n">
-        <v>-3.7</v>
+        <v>-3.93</v>
       </c>
       <c r="F108" t="n">
-        <v>-11.9</v>
+        <v>-12.1</v>
       </c>
       <c r="G108" t="n">
-        <v>-20.28</v>
+        <v>-20.46</v>
       </c>
       <c r="H108" t="n">
-        <v>-21.63</v>
+        <v>-21.81</v>
       </c>
       <c r="I108" t="n">
         <v>0.42</v>
@@ -12357,31 +12357,31 @@
         <v>6.07</v>
       </c>
       <c r="K108" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="L108" t="n">
-        <v>218.58</v>
+        <v>218.07</v>
       </c>
       <c r="M108" t="n">
-        <v>221.62</v>
+        <v>221.11</v>
       </c>
       <c r="N108" t="n">
-        <v>212.51</v>
+        <v>212</v>
       </c>
       <c r="O108" t="n">
-        <v>234.07</v>
+        <v>233.55</v>
       </c>
       <c r="P108" t="n">
         <v>1.63</v>
       </c>
       <c r="Q108" t="n">
-        <v>31.19</v>
+        <v>30.91</v>
       </c>
       <c r="R108" t="n">
-        <v>-5.77</v>
+        <v>-5.98</v>
       </c>
       <c r="S108" t="n">
-        <v>-13.74</v>
+        <v>-13.94</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12442,25 +12442,25 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>299.85</v>
+        <v>299.51</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>-5.54</v>
+        <v>-5.65</v>
       </c>
       <c r="F109" t="n">
-        <v>-14.18</v>
+        <v>-14.28</v>
       </c>
       <c r="G109" t="n">
-        <v>-20.27</v>
+        <v>-20.36</v>
       </c>
       <c r="H109" t="n">
-        <v>-23.91</v>
+        <v>-23.99</v>
       </c>
       <c r="I109" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J109" t="n">
         <v>7.81</v>
@@ -12469,28 +12469,28 @@
         <v>2.61</v>
       </c>
       <c r="L109" t="n">
-        <v>297.12</v>
+        <v>296.78</v>
       </c>
       <c r="M109" t="n">
-        <v>301.02</v>
+        <v>300.68</v>
       </c>
       <c r="N109" t="n">
-        <v>289.3</v>
+        <v>288.96</v>
       </c>
       <c r="O109" t="n">
-        <v>317.04</v>
+        <v>316.7</v>
       </c>
       <c r="P109" t="n">
         <v>1.63</v>
       </c>
       <c r="Q109" t="n">
-        <v>26.58</v>
+        <v>26.45</v>
       </c>
       <c r="R109" t="n">
-        <v>-7.27</v>
+        <v>-7.37</v>
       </c>
       <c r="S109" t="n">
-        <v>-15.19</v>
+        <v>-15.28</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>442.76</v>
+        <v>442.78</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -12566,7 +12566,7 @@
         <v>-13.96</v>
       </c>
       <c r="H110" t="n">
-        <v>-25.65</v>
+        <v>-25.63</v>
       </c>
       <c r="I110" t="n">
         <v>0.44</v>
@@ -12578,28 +12578,28 @@
         <v>3.09</v>
       </c>
       <c r="L110" t="n">
-        <v>437.96</v>
+        <v>437.99</v>
       </c>
       <c r="M110" t="n">
-        <v>444.81</v>
+        <v>444.83</v>
       </c>
       <c r="N110" t="n">
-        <v>424.26</v>
+        <v>424.29</v>
       </c>
       <c r="O110" t="n">
-        <v>472.89</v>
+        <v>472.91</v>
       </c>
       <c r="P110" t="n">
         <v>1.63</v>
       </c>
       <c r="Q110" t="n">
-        <v>36.9</v>
+        <v>36.91</v>
       </c>
       <c r="R110" t="n">
-        <v>-6.24</v>
+        <v>-6.23</v>
       </c>
       <c r="S110" t="n">
-        <v>-17.77</v>
+        <v>-17.76</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12660,19 +12660,19 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>199.09</v>
+        <v>199.04</v>
       </c>
       <c r="D111" t="n">
         <v>49</v>
       </c>
       <c r="E111" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.95</v>
+        <v>-0.97</v>
       </c>
       <c r="G111" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="H111" t="n">
         <v>-10.68</v>
@@ -12687,28 +12687,28 @@
         <v>7.68</v>
       </c>
       <c r="L111" t="n">
-        <v>193.74</v>
+        <v>193.69</v>
       </c>
       <c r="M111" t="n">
-        <v>201.38</v>
+        <v>201.33</v>
       </c>
       <c r="N111" t="n">
-        <v>178.45</v>
+        <v>178.41</v>
       </c>
       <c r="O111" t="n">
-        <v>232.71</v>
+        <v>232.67</v>
       </c>
       <c r="P111" t="n">
         <v>1.63</v>
       </c>
       <c r="Q111" t="n">
-        <v>45.57</v>
+        <v>45.56</v>
       </c>
       <c r="R111" t="n">
-        <v>-5.86</v>
+        <v>-5.88</v>
       </c>
       <c r="S111" t="n">
-        <v>-23.1</v>
+        <v>-23.11</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -12773,55 +12773,55 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>29.83</v>
+        <v>29.8</v>
       </c>
       <c r="D112" t="n">
         <v>34</v>
       </c>
       <c r="E112" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F112" t="n">
-        <v>-13.71</v>
+        <v>-13.8</v>
       </c>
       <c r="G112" t="n">
-        <v>-2.68</v>
+        <v>-2.77</v>
       </c>
       <c r="H112" t="n">
-        <v>-23.44</v>
+        <v>-23.51</v>
       </c>
       <c r="I112" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J112" t="n">
         <v>1.84</v>
       </c>
       <c r="K112" t="n">
-        <v>6.15</v>
+        <v>6.17</v>
       </c>
       <c r="L112" t="n">
-        <v>29.19</v>
+        <v>29.16</v>
       </c>
       <c r="M112" t="n">
-        <v>30.11</v>
+        <v>30.08</v>
       </c>
       <c r="N112" t="n">
-        <v>27.35</v>
+        <v>27.32</v>
       </c>
       <c r="O112" t="n">
-        <v>33.87</v>
+        <v>33.85</v>
       </c>
       <c r="P112" t="n">
         <v>1.63</v>
       </c>
       <c r="Q112" t="n">
-        <v>38.35</v>
+        <v>38.22</v>
       </c>
       <c r="R112" t="n">
-        <v>-4.21</v>
+        <v>-4.31</v>
       </c>
       <c r="S112" t="n">
-        <v>-16.68</v>
+        <v>-16.76</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
@@ -12865,7 +12865,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MA20 sobre MA50; MACD mejorando; Momentum 5D sano</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MA20 sobre MA50; MACD mejorando; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -12886,55 +12886,55 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>123.42</v>
+        <v>123.01</v>
       </c>
       <c r="D113" t="n">
         <v>32</v>
       </c>
       <c r="E113" t="n">
-        <v>7.38</v>
+        <v>7.03</v>
       </c>
       <c r="F113" t="n">
-        <v>-9.539999999999999</v>
+        <v>-9.83</v>
       </c>
       <c r="G113" t="n">
-        <v>-22.4</v>
+        <v>-22.66</v>
       </c>
       <c r="H113" t="n">
-        <v>-19.27</v>
+        <v>-19.54</v>
       </c>
       <c r="I113" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="J113" t="n">
         <v>5.89</v>
       </c>
       <c r="K113" t="n">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
       <c r="L113" t="n">
-        <v>121.35</v>
+        <v>120.95</v>
       </c>
       <c r="M113" t="n">
-        <v>124.3</v>
+        <v>123.9</v>
       </c>
       <c r="N113" t="n">
-        <v>115.46</v>
+        <v>115.06</v>
       </c>
       <c r="O113" t="n">
-        <v>136.37</v>
+        <v>135.97</v>
       </c>
       <c r="P113" t="n">
         <v>1.63</v>
       </c>
       <c r="Q113" t="n">
-        <v>35.49</v>
+        <v>34.97</v>
       </c>
       <c r="R113" t="n">
-        <v>-1.37</v>
+        <v>-1.68</v>
       </c>
       <c r="S113" t="n">
-        <v>-13.35</v>
+        <v>-13.63</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MACD positivo; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -12999,22 +12999,22 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>8.470000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="D114" t="n">
         <v>36</v>
       </c>
       <c r="E114" t="n">
-        <v>-4.62</v>
+        <v>-4.95</v>
       </c>
       <c r="F114" t="n">
-        <v>4.82</v>
+        <v>4.46</v>
       </c>
       <c r="G114" t="n">
-        <v>8.16</v>
+        <v>7.79</v>
       </c>
       <c r="H114" t="n">
-        <v>-4.91</v>
+        <v>-5.25</v>
       </c>
       <c r="I114" t="n">
         <v>0.28</v>
@@ -13023,31 +13023,31 @@
         <v>0.65</v>
       </c>
       <c r="K114" t="n">
-        <v>7.72</v>
+        <v>7.74</v>
       </c>
       <c r="L114" t="n">
-        <v>8.24</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M114" t="n">
-        <v>8.57</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N114" t="n">
-        <v>7.59</v>
+        <v>7.56</v>
       </c>
       <c r="O114" t="n">
-        <v>9.91</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="P114" t="n">
         <v>1.64</v>
       </c>
       <c r="Q114" t="n">
-        <v>52.92</v>
+        <v>52.63</v>
       </c>
       <c r="R114" t="n">
-        <v>-0.51</v>
+        <v>-0.84</v>
       </c>
       <c r="S114" t="n">
-        <v>-15.69</v>
+        <v>-15.98</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -13108,55 +13108,55 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>17.92</v>
+        <v>17.91</v>
       </c>
       <c r="D115" t="n">
         <v>32</v>
       </c>
       <c r="E115" t="n">
-        <v>-5.41</v>
+        <v>-5.46</v>
       </c>
       <c r="F115" t="n">
-        <v>-9.57</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="G115" t="n">
-        <v>7.92</v>
+        <v>7.86</v>
       </c>
       <c r="H115" t="n">
-        <v>-19.3</v>
+        <v>-19.33</v>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="J115" t="n">
         <v>1.6</v>
       </c>
       <c r="K115" t="n">
-        <v>8.92</v>
+        <v>8.93</v>
       </c>
       <c r="L115" t="n">
-        <v>17.36</v>
+        <v>17.35</v>
       </c>
       <c r="M115" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="N115" t="n">
-        <v>15.76</v>
+        <v>15.75</v>
       </c>
       <c r="O115" t="n">
-        <v>21.43</v>
+        <v>21.42</v>
       </c>
       <c r="P115" t="n">
         <v>1.63</v>
       </c>
       <c r="Q115" t="n">
-        <v>53.85</v>
+        <v>53.8</v>
       </c>
       <c r="R115" t="n">
-        <v>-1.18</v>
+        <v>-1.24</v>
       </c>
       <c r="S115" t="n">
-        <v>-14.77</v>
+        <v>-14.82</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -13217,22 +13217,22 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>156.53</v>
+        <v>156.25</v>
       </c>
       <c r="D116" t="n">
         <v>26</v>
       </c>
       <c r="E116" t="n">
-        <v>0.47</v>
+        <v>0.29</v>
       </c>
       <c r="F116" t="n">
-        <v>-4.44</v>
+        <v>-4.61</v>
       </c>
       <c r="G116" t="n">
-        <v>7.12</v>
+        <v>6.93</v>
       </c>
       <c r="H116" t="n">
-        <v>-14.17</v>
+        <v>-14.32</v>
       </c>
       <c r="I116" t="n">
         <v>0.31</v>
@@ -13241,31 +13241,31 @@
         <v>10.03</v>
       </c>
       <c r="K116" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
       <c r="L116" t="n">
-        <v>153.02</v>
+        <v>152.74</v>
       </c>
       <c r="M116" t="n">
-        <v>158.03</v>
+        <v>157.75</v>
       </c>
       <c r="N116" t="n">
-        <v>142.99</v>
+        <v>142.71</v>
       </c>
       <c r="O116" t="n">
-        <v>178.6</v>
+        <v>178.32</v>
       </c>
       <c r="P116" t="n">
         <v>1.63</v>
       </c>
       <c r="Q116" t="n">
-        <v>47.3</v>
+        <v>47.09</v>
       </c>
       <c r="R116" t="n">
-        <v>-1.26</v>
+        <v>-1.43</v>
       </c>
       <c r="S116" t="n">
-        <v>-11.63</v>
+        <v>-11.79</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MA20 sobre MA50; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MA20 sobre MA50; MACD mejorando</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -13326,22 +13326,22 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>20.7</v>
+        <v>20.66</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>-10.31</v>
+        <v>-10.51</v>
       </c>
       <c r="F117" t="n">
-        <v>-7.88</v>
+        <v>-8.08</v>
       </c>
       <c r="G117" t="n">
-        <v>-17.99</v>
+        <v>-18.17</v>
       </c>
       <c r="H117" t="n">
-        <v>-17.61</v>
+        <v>-17.79</v>
       </c>
       <c r="I117" t="n">
         <v>0.36</v>
@@ -13350,31 +13350,31 @@
         <v>1.25</v>
       </c>
       <c r="K117" t="n">
-        <v>6.03</v>
+        <v>6.04</v>
       </c>
       <c r="L117" t="n">
-        <v>20.26</v>
+        <v>20.22</v>
       </c>
       <c r="M117" t="n">
-        <v>20.89</v>
+        <v>20.84</v>
       </c>
       <c r="N117" t="n">
-        <v>19.02</v>
+        <v>18.97</v>
       </c>
       <c r="O117" t="n">
-        <v>23.45</v>
+        <v>23.4</v>
       </c>
       <c r="P117" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q117" t="n">
-        <v>34.36</v>
+        <v>33.98</v>
       </c>
       <c r="R117" t="n">
-        <v>-9.91</v>
+        <v>-10.09</v>
       </c>
       <c r="S117" t="n">
-        <v>-16.77</v>
+        <v>-16.95</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -13435,22 +13435,22 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>100.87</v>
+        <v>100.65</v>
       </c>
       <c r="D118" t="n">
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>-8.640000000000001</v>
+        <v>-8.84</v>
       </c>
       <c r="F118" t="n">
-        <v>-23.09</v>
+        <v>-23.26</v>
       </c>
       <c r="G118" t="n">
-        <v>-18.52</v>
+        <v>-18.7</v>
       </c>
       <c r="H118" t="n">
-        <v>-32.82</v>
+        <v>-32.97</v>
       </c>
       <c r="I118" t="n">
         <v>0.74</v>
@@ -13459,31 +13459,31 @@
         <v>6.3</v>
       </c>
       <c r="K118" t="n">
-        <v>6.25</v>
+        <v>6.26</v>
       </c>
       <c r="L118" t="n">
-        <v>98.66</v>
+        <v>98.44</v>
       </c>
       <c r="M118" t="n">
-        <v>101.82</v>
+        <v>101.6</v>
       </c>
       <c r="N118" t="n">
-        <v>92.36</v>
+        <v>92.14</v>
       </c>
       <c r="O118" t="n">
-        <v>114.74</v>
+        <v>114.52</v>
       </c>
       <c r="P118" t="n">
         <v>1.63</v>
       </c>
       <c r="Q118" t="n">
-        <v>30.53</v>
+        <v>30.27</v>
       </c>
       <c r="R118" t="n">
-        <v>-13.17</v>
+        <v>-13.35</v>
       </c>
       <c r="S118" t="n">
-        <v>-26.53</v>
+        <v>-26.69</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -13544,55 +13544,55 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6.09</v>
+        <v>6.07</v>
       </c>
       <c r="D119" t="n">
         <v>57</v>
       </c>
       <c r="E119" t="n">
-        <v>-6.1</v>
+        <v>-6.25</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.41</v>
+        <v>-0.57</v>
       </c>
       <c r="G119" t="n">
-        <v>-15.84</v>
+        <v>-15.98</v>
       </c>
       <c r="H119" t="n">
-        <v>-10.14</v>
+        <v>-10.28</v>
       </c>
       <c r="I119" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="J119" t="n">
         <v>0.39</v>
       </c>
       <c r="K119" t="n">
-        <v>6.49</v>
+        <v>6.5</v>
       </c>
       <c r="L119" t="n">
-        <v>5.95</v>
+        <v>5.94</v>
       </c>
       <c r="M119" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
       <c r="N119" t="n">
-        <v>5.55</v>
+        <v>5.54</v>
       </c>
       <c r="O119" t="n">
-        <v>6.95</v>
+        <v>6.94</v>
       </c>
       <c r="P119" t="n">
         <v>1.62</v>
       </c>
       <c r="Q119" t="n">
-        <v>53.83</v>
+        <v>53.61</v>
       </c>
       <c r="R119" t="n">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="S119" t="n">
-        <v>-9.85</v>
+        <v>-10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13653,55 +13653,55 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>12.35</v>
+        <v>12.32</v>
       </c>
       <c r="D120" t="n">
         <v>43</v>
       </c>
       <c r="E120" t="n">
-        <v>-4.52</v>
+        <v>-4.79</v>
       </c>
       <c r="F120" t="n">
-        <v>6.51</v>
+        <v>6.21</v>
       </c>
       <c r="G120" t="n">
-        <v>55.21</v>
+        <v>54.77</v>
       </c>
       <c r="H120" t="n">
-        <v>-3.22</v>
+        <v>-3.5</v>
       </c>
       <c r="I120" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="J120" t="n">
         <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>8.09</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="L120" t="n">
-        <v>12.01</v>
+        <v>11.97</v>
       </c>
       <c r="M120" t="n">
-        <v>12.5</v>
+        <v>12.47</v>
       </c>
       <c r="N120" t="n">
-        <v>11.01</v>
+        <v>10.97</v>
       </c>
       <c r="O120" t="n">
-        <v>14.55</v>
+        <v>14.52</v>
       </c>
       <c r="P120" t="n">
         <v>1.63</v>
       </c>
       <c r="Q120" t="n">
-        <v>58.36</v>
+        <v>58.07</v>
       </c>
       <c r="R120" t="n">
-        <v>2.24</v>
+        <v>1.97</v>
       </c>
       <c r="S120" t="n">
-        <v>-10.47</v>
+        <v>-10.72</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>BTC-USD 2.14% · ETH-USD -3.91%</t>
+          <t>BTC-USD 2.1% · ETH-USD -4.0%</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 2.14% · ETH-USD -3.91%; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
+          <t>Sector no acompaña: BTC-USD 2.1% · ETH-USD -4.0%; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>
@@ -13762,25 +13762,25 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>194.49</v>
+        <v>194.32</v>
       </c>
       <c r="D121" t="n">
         <v>35</v>
       </c>
       <c r="E121" t="n">
-        <v>-3.32</v>
+        <v>-3.4</v>
       </c>
       <c r="F121" t="n">
-        <v>-5.74</v>
+        <v>-5.82</v>
       </c>
       <c r="G121" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="H121" t="n">
-        <v>-15.47</v>
+        <v>-15.53</v>
       </c>
       <c r="I121" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="J121" t="n">
         <v>14.49</v>
@@ -13789,28 +13789,28 @@
         <v>7.45</v>
       </c>
       <c r="L121" t="n">
-        <v>189.41</v>
+        <v>189.25</v>
       </c>
       <c r="M121" t="n">
-        <v>196.66</v>
+        <v>196.49</v>
       </c>
       <c r="N121" t="n">
-        <v>174.93</v>
+        <v>174.76</v>
       </c>
       <c r="O121" t="n">
-        <v>226.36</v>
+        <v>226.19</v>
       </c>
       <c r="P121" t="n">
         <v>1.63</v>
       </c>
       <c r="Q121" t="n">
-        <v>49.03</v>
+        <v>48.96</v>
       </c>
       <c r="R121" t="n">
-        <v>-2.47</v>
+        <v>-2.55</v>
       </c>
       <c r="S121" t="n">
-        <v>-12.53</v>
+        <v>-12.61</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>BTC-USD 2.14% · ETH-USD -3.91%</t>
+          <t>BTC-USD 2.1% · ETH-USD -4.0%</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 2.14% · ETH-USD -3.91%; Precio bajo MA20; Tendencia larga débil; Momentum negativo; Débil vs QQQ</t>
+          <t>Sector no acompaña: BTC-USD 2.1% · ETH-USD -4.0%; Precio bajo MA20; Tendencia larga débil; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -13871,22 +13871,22 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>175.49</v>
+        <v>175.09</v>
       </c>
       <c r="D122" t="n">
         <v>30</v>
       </c>
       <c r="E122" t="n">
-        <v>-6.45</v>
+        <v>-6.66</v>
       </c>
       <c r="F122" t="n">
-        <v>5.39</v>
+        <v>5.15</v>
       </c>
       <c r="G122" t="n">
-        <v>35.57</v>
+        <v>35.26</v>
       </c>
       <c r="H122" t="n">
-        <v>-4.34</v>
+        <v>-4.56</v>
       </c>
       <c r="I122" t="n">
         <v>0.68</v>
@@ -13895,31 +13895,31 @@
         <v>11.44</v>
       </c>
       <c r="K122" t="n">
-        <v>6.52</v>
+        <v>6.54</v>
       </c>
       <c r="L122" t="n">
-        <v>171.49</v>
+        <v>171.08</v>
       </c>
       <c r="M122" t="n">
-        <v>177.21</v>
+        <v>176.81</v>
       </c>
       <c r="N122" t="n">
-        <v>160.04</v>
+        <v>159.64</v>
       </c>
       <c r="O122" t="n">
-        <v>200.66</v>
+        <v>200.26</v>
       </c>
       <c r="P122" t="n">
         <v>1.63</v>
       </c>
       <c r="Q122" t="n">
-        <v>53.11</v>
+        <v>52.9</v>
       </c>
       <c r="R122" t="n">
-        <v>-0.83</v>
+        <v>-1.04</v>
       </c>
       <c r="S122" t="n">
-        <v>-10.92</v>
+        <v>-11.12</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>BTC-USD 2.14% · ETH-USD -3.91%</t>
+          <t>BTC-USD 2.1% · ETH-USD -4.0%</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 2.14% · ETH-USD -3.91%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Sector no acompaña: BTC-USD 2.1% · ETH-USD -4.0%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -13980,22 +13980,22 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>20.47</v>
+        <v>20.49</v>
       </c>
       <c r="D123" t="n">
         <v>27</v>
       </c>
       <c r="E123" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.24</v>
       </c>
       <c r="F123" t="n">
-        <v>-5.62</v>
+        <v>-5.56</v>
       </c>
       <c r="G123" t="n">
-        <v>5.62</v>
+        <v>5.7</v>
       </c>
       <c r="H123" t="n">
-        <v>-15.35</v>
+        <v>-15.27</v>
       </c>
       <c r="I123" t="n">
         <v>0.5</v>
@@ -14007,28 +14007,28 @@
         <v>9.17</v>
       </c>
       <c r="L123" t="n">
-        <v>19.81</v>
+        <v>19.83</v>
       </c>
       <c r="M123" t="n">
-        <v>20.75</v>
+        <v>20.77</v>
       </c>
       <c r="N123" t="n">
-        <v>17.94</v>
+        <v>17.95</v>
       </c>
       <c r="O123" t="n">
-        <v>24.6</v>
+        <v>24.62</v>
       </c>
       <c r="P123" t="n">
         <v>1.63</v>
       </c>
       <c r="Q123" t="n">
-        <v>55.48</v>
+        <v>55.54</v>
       </c>
       <c r="R123" t="n">
-        <v>-2.12</v>
+        <v>-2.05</v>
       </c>
       <c r="S123" t="n">
-        <v>-17.39</v>
+        <v>-17.33</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -14089,55 +14089,55 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>199.28</v>
+        <v>198.88</v>
       </c>
       <c r="D124" t="n">
         <v>12</v>
       </c>
       <c r="E124" t="n">
-        <v>0.98</v>
+        <v>0.78</v>
       </c>
       <c r="F124" t="n">
-        <v>-10.43</v>
+        <v>-10.61</v>
       </c>
       <c r="G124" t="n">
-        <v>-16.75</v>
+        <v>-16.92</v>
       </c>
       <c r="H124" t="n">
-        <v>-20.16</v>
+        <v>-20.32</v>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="J124" t="n">
         <v>18.04</v>
       </c>
       <c r="K124" t="n">
-        <v>9.050000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="L124" t="n">
-        <v>192.96</v>
+        <v>192.56</v>
       </c>
       <c r="M124" t="n">
-        <v>201.99</v>
+        <v>201.58</v>
       </c>
       <c r="N124" t="n">
-        <v>174.92</v>
+        <v>174.52</v>
       </c>
       <c r="O124" t="n">
-        <v>238.98</v>
+        <v>238.57</v>
       </c>
       <c r="P124" t="n">
         <v>1.63</v>
       </c>
       <c r="Q124" t="n">
-        <v>40.73</v>
+        <v>40.56</v>
       </c>
       <c r="R124" t="n">
-        <v>-8.869999999999999</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="S124" t="n">
-        <v>-21.85</v>
+        <v>-22.01</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>QQQ 9.73% · ARKK -4.98% · SPY 4.44%</t>
+          <t>QQQ 9.71% · ARKK -5.07% · SPY 4.41%</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.73% · ARKK -4.98% · SPY 4.44%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 9.71% · ARKK -5.07% · SPY 4.41%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -14198,22 +14198,22 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>123.7</v>
+        <v>123.97</v>
       </c>
       <c r="D125" t="n">
         <v>59</v>
       </c>
       <c r="E125" t="n">
-        <v>17.28</v>
+        <v>17.54</v>
       </c>
       <c r="F125" t="n">
-        <v>45.87</v>
+        <v>46.19</v>
       </c>
       <c r="G125" t="n">
-        <v>61.53</v>
+        <v>61.88</v>
       </c>
       <c r="H125" t="n">
-        <v>36.14</v>
+        <v>36.48</v>
       </c>
       <c r="I125" t="n">
         <v>0.54</v>
@@ -14222,31 +14222,31 @@
         <v>9.65</v>
       </c>
       <c r="K125" t="n">
-        <v>7.8</v>
+        <v>7.78</v>
       </c>
       <c r="L125" t="n">
-        <v>120.32</v>
+        <v>120.59</v>
       </c>
       <c r="M125" t="n">
-        <v>125.15</v>
+        <v>125.42</v>
       </c>
       <c r="N125" t="n">
-        <v>110.68</v>
+        <v>110.95</v>
       </c>
       <c r="O125" t="n">
-        <v>144.92</v>
+        <v>145.19</v>
       </c>
       <c r="P125" t="n">
         <v>1.63</v>
       </c>
       <c r="Q125" t="n">
-        <v>72.43000000000001</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="R125" t="n">
-        <v>32.11</v>
+        <v>32.38</v>
       </c>
       <c r="S125" t="n">
-        <v>-7.12</v>
+        <v>-6.92</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -575,25 +575,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>420.19</v>
+        <v>420.22</v>
       </c>
       <c r="D2" t="n">
         <v>96</v>
       </c>
       <c r="E2" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="F2" t="n">
-        <v>13.12</v>
+        <v>13.13</v>
       </c>
       <c r="G2" t="n">
-        <v>22.07</v>
+        <v>22.08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="J2" t="n">
         <v>11.75</v>
@@ -602,25 +602,25 @@
         <v>2.8</v>
       </c>
       <c r="L2" t="n">
-        <v>416.08</v>
+        <v>416.11</v>
       </c>
       <c r="M2" t="n">
-        <v>421.95</v>
+        <v>421.98</v>
       </c>
       <c r="N2" t="n">
-        <v>404.33</v>
+        <v>404.36</v>
       </c>
       <c r="O2" t="n">
-        <v>446.03</v>
+        <v>446.06</v>
       </c>
       <c r="P2" t="n">
         <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>63.59</v>
+        <v>63.61</v>
       </c>
       <c r="R2" t="n">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
       <c r="S2" t="n">
         <v>-3.56</v>
@@ -642,7 +642,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41.36</v>
+        <v>41.38</v>
       </c>
       <c r="D3" t="n">
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="F3" t="n">
-        <v>11.33</v>
+        <v>11.4</v>
       </c>
       <c r="G3" t="n">
-        <v>17.5</v>
+        <v>17.57</v>
       </c>
       <c r="H3" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="I3" t="n">
         <v>0.27</v>
@@ -715,28 +715,28 @@
         <v>2.62</v>
       </c>
       <c r="L3" t="n">
-        <v>40.98</v>
+        <v>41.01</v>
       </c>
       <c r="M3" t="n">
-        <v>41.52</v>
+        <v>41.55</v>
       </c>
       <c r="N3" t="n">
-        <v>39.9</v>
+        <v>39.92</v>
       </c>
       <c r="O3" t="n">
-        <v>43.75</v>
+        <v>43.77</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>56.41</v>
+        <v>56.53</v>
       </c>
       <c r="R3" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.59</v>
+        <v>-2.53</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>XLE 7.27% · CL=F 19.89%</t>
+          <t>XLE 7.22% · CL=F 20.0%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.27% · CL=F 19.89%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.22% · CL=F 20.0%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -801,25 +801,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>437.43</v>
+        <v>437.23</v>
       </c>
       <c r="D4" t="n">
         <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="F4" t="n">
-        <v>10.2</v>
+        <v>10.15</v>
       </c>
       <c r="G4" t="n">
-        <v>18.28</v>
+        <v>18.22</v>
       </c>
       <c r="H4" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="I4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="J4" t="n">
         <v>18.55</v>
@@ -828,28 +828,28 @@
         <v>4.24</v>
       </c>
       <c r="L4" t="n">
-        <v>430.94</v>
+        <v>430.74</v>
       </c>
       <c r="M4" t="n">
-        <v>440.21</v>
+        <v>440.01</v>
       </c>
       <c r="N4" t="n">
-        <v>412.39</v>
+        <v>412.19</v>
       </c>
       <c r="O4" t="n">
-        <v>478.24</v>
+        <v>478.04</v>
       </c>
       <c r="P4" t="n">
         <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>60.31</v>
+        <v>60.23</v>
       </c>
       <c r="R4" t="n">
-        <v>6.32</v>
+        <v>6.27</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.46</v>
+        <v>-2.5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>59.01</v>
+        <v>59.03</v>
       </c>
       <c r="D5" t="n">
         <v>96</v>
       </c>
       <c r="E5" t="n">
-        <v>5.93</v>
+        <v>5.99</v>
       </c>
       <c r="F5" t="n">
-        <v>7.24</v>
+        <v>7.3</v>
       </c>
       <c r="G5" t="n">
-        <v>7.63</v>
+        <v>7.69</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.81</v>
+        <v>-2.73</v>
       </c>
       <c r="I5" t="n">
         <v>0.59</v>
@@ -937,28 +937,28 @@
         <v>2.23</v>
       </c>
       <c r="L5" t="n">
-        <v>58.54</v>
+        <v>58.57</v>
       </c>
       <c r="M5" t="n">
-        <v>59.2</v>
+        <v>59.23</v>
       </c>
       <c r="N5" t="n">
-        <v>57.23</v>
+        <v>57.26</v>
       </c>
       <c r="O5" t="n">
-        <v>61.9</v>
+        <v>61.93</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>59.86</v>
+        <v>59.96</v>
       </c>
       <c r="R5" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4</v>
+        <v>-1.35</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>XLE 7.27% · CL=F 19.89%</t>
+          <t>XLE 7.22% · CL=F 20.0%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.27% · CL=F 19.89%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.22% · CL=F 20.0%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1023,25 +1023,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.53</v>
+        <v>55.57</v>
       </c>
       <c r="D6" t="n">
         <v>96</v>
       </c>
       <c r="E6" t="n">
-        <v>4.24</v>
+        <v>4.32</v>
       </c>
       <c r="F6" t="n">
-        <v>5.45</v>
+        <v>5.53</v>
       </c>
       <c r="G6" t="n">
-        <v>7.74</v>
+        <v>7.82</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.6</v>
+        <v>-4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="J6" t="n">
         <v>1.44</v>
@@ -1050,28 +1050,28 @@
         <v>2.58</v>
       </c>
       <c r="L6" t="n">
-        <v>55.03</v>
+        <v>55.07</v>
       </c>
       <c r="M6" t="n">
-        <v>55.75</v>
+        <v>55.79</v>
       </c>
       <c r="N6" t="n">
-        <v>53.59</v>
+        <v>53.63</v>
       </c>
       <c r="O6" t="n">
-        <v>58.69</v>
+        <v>58.73</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>51.52</v>
+        <v>51.73</v>
       </c>
       <c r="R6" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.92</v>
+        <v>-2.85</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>XLE 7.27% · CL=F 19.89%</t>
+          <t>XLE 7.22% · CL=F 20.0%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.27% · CL=F 19.89%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.22% · CL=F 20.0%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1136,22 +1136,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>189.46</v>
+        <v>189.57</v>
       </c>
       <c r="D7" t="n">
         <v>96</v>
       </c>
       <c r="E7" t="n">
-        <v>4.32</v>
+        <v>4.37</v>
       </c>
       <c r="F7" t="n">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="G7" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="H7" t="n">
-        <v>-7.07</v>
+        <v>-7</v>
       </c>
       <c r="I7" t="n">
         <v>0.45</v>
@@ -1163,28 +1163,28 @@
         <v>2.22</v>
       </c>
       <c r="L7" t="n">
-        <v>187.99</v>
+        <v>188.09</v>
       </c>
       <c r="M7" t="n">
-        <v>190.1</v>
+        <v>190.2</v>
       </c>
       <c r="N7" t="n">
-        <v>183.78</v>
+        <v>183.88</v>
       </c>
       <c r="O7" t="n">
-        <v>198.74</v>
+        <v>198.84</v>
       </c>
       <c r="P7" t="n">
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>57.3</v>
+        <v>57.43</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.4</v>
+        <v>-2.35</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>XLE 7.27% · CL=F 19.89%</t>
+          <t>XLE 7.22% · CL=F 20.0%</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.27% · CL=F 19.89%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.22% · CL=F 20.0%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1249,22 +1249,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>94.83</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="D8" t="n">
         <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.3</v>
+        <v>-4.2</v>
       </c>
       <c r="F8" t="n">
-        <v>20.4</v>
+        <v>20.53</v>
       </c>
       <c r="G8" t="n">
-        <v>23.62</v>
+        <v>23.75</v>
       </c>
       <c r="H8" t="n">
-        <v>10.35</v>
+        <v>10.5</v>
       </c>
       <c r="I8" t="n">
         <v>0.26</v>
@@ -1276,28 +1276,28 @@
         <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>93.34</v>
+        <v>93.44</v>
       </c>
       <c r="M8" t="n">
-        <v>95.47</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>89.06999999999999</v>
+        <v>89.17</v>
       </c>
       <c r="O8" t="n">
-        <v>104.22</v>
+        <v>104.32</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>63.32</v>
+        <v>63.53</v>
       </c>
       <c r="R8" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="S8" t="n">
-        <v>-10.46</v>
+        <v>-10.37</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1362,25 +1362,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>408.33</v>
+        <v>408.63</v>
       </c>
       <c r="D9" t="n">
         <v>95</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.74</v>
       </c>
       <c r="F9" t="n">
-        <v>10.21</v>
+        <v>10.29</v>
       </c>
       <c r="G9" t="n">
-        <v>13.62</v>
+        <v>13.7</v>
       </c>
       <c r="H9" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="I9" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="J9" t="n">
         <v>15.44</v>
@@ -1389,28 +1389,28 @@
         <v>3.78</v>
       </c>
       <c r="L9" t="n">
-        <v>402.93</v>
+        <v>403.23</v>
       </c>
       <c r="M9" t="n">
-        <v>410.65</v>
+        <v>410.95</v>
       </c>
       <c r="N9" t="n">
-        <v>387.49</v>
+        <v>387.79</v>
       </c>
       <c r="O9" t="n">
-        <v>442.29</v>
+        <v>442.59</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>51.58</v>
+        <v>51.72</v>
       </c>
       <c r="R9" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.23</v>
+        <v>-3.16</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1475,22 +1475,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1519.53</v>
+        <v>1519.02</v>
       </c>
       <c r="D10" t="n">
         <v>96</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.55</v>
+        <v>-4.59</v>
       </c>
       <c r="F10" t="n">
-        <v>4.32</v>
+        <v>4.28</v>
       </c>
       <c r="G10" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.73</v>
+        <v>-5.75</v>
       </c>
       <c r="I10" t="n">
         <v>0.6899999999999999</v>
@@ -1502,28 +1502,28 @@
         <v>4.32</v>
       </c>
       <c r="L10" t="n">
-        <v>1496.56</v>
+        <v>1496.05</v>
       </c>
       <c r="M10" t="n">
-        <v>1529.37</v>
+        <v>1528.86</v>
       </c>
       <c r="N10" t="n">
-        <v>1430.95</v>
+        <v>1430.44</v>
       </c>
       <c r="O10" t="n">
-        <v>1663.88</v>
+        <v>1663.37</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>57.06</v>
+        <v>57.01</v>
       </c>
       <c r="R10" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.24</v>
+        <v>-5.27</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1588,55 +1588,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>429.44</v>
+        <v>428.66</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.13</v>
+        <v>-0.31</v>
       </c>
       <c r="F11" t="n">
-        <v>5.63</v>
+        <v>5.44</v>
       </c>
       <c r="G11" t="n">
-        <v>28.85</v>
+        <v>28.62</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.42</v>
+        <v>-4.59</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="J11" t="n">
         <v>17.05</v>
       </c>
       <c r="K11" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="L11" t="n">
-        <v>423.47</v>
+        <v>422.7</v>
       </c>
       <c r="M11" t="n">
-        <v>432</v>
+        <v>431.22</v>
       </c>
       <c r="N11" t="n">
-        <v>406.42</v>
+        <v>405.64</v>
       </c>
       <c r="O11" t="n">
-        <v>466.96</v>
+        <v>466.18</v>
       </c>
       <c r="P11" t="n">
         <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>54.19</v>
+        <v>53.87</v>
       </c>
       <c r="R11" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.92</v>
+        <v>-3.1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1571.02</v>
+        <v>1573.06</v>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.86</v>
+        <v>-1.74</v>
       </c>
       <c r="F12" t="n">
-        <v>6.99</v>
+        <v>7.13</v>
       </c>
       <c r="G12" t="n">
-        <v>33.95</v>
+        <v>34.12</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.06</v>
+        <v>-2.9</v>
       </c>
       <c r="I12" t="n">
         <v>0.35</v>
@@ -1725,31 +1725,31 @@
         <v>76.48999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>4.87</v>
+        <v>4.86</v>
       </c>
       <c r="L12" t="n">
-        <v>1544.25</v>
+        <v>1546.29</v>
       </c>
       <c r="M12" t="n">
-        <v>1582.49</v>
+        <v>1584.53</v>
       </c>
       <c r="N12" t="n">
-        <v>1467.76</v>
+        <v>1469.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1739.3</v>
+        <v>1741.34</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>48.76</v>
+        <v>48.91</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.78</v>
+        <v>-0.66</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.23</v>
+        <v>-6.11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1776,7 +1776,11 @@
           <t>BAJO</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1789,12 +1793,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -1810,25 +1814,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1819.33</v>
+        <v>1820</v>
       </c>
       <c r="D13" t="n">
         <v>75</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.67</v>
+        <v>-2.63</v>
       </c>
       <c r="F13" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="G13" t="n">
-        <v>23.77</v>
+        <v>23.82</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.49</v>
+        <v>-8.44</v>
       </c>
       <c r="I13" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J13" t="n">
         <v>87.39</v>
@@ -1837,28 +1841,28 @@
         <v>4.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1788.74</v>
+        <v>1789.41</v>
       </c>
       <c r="M13" t="n">
-        <v>1832.44</v>
+        <v>1833.11</v>
       </c>
       <c r="N13" t="n">
-        <v>1701.35</v>
+        <v>1702.02</v>
       </c>
       <c r="O13" t="n">
-        <v>2011.59</v>
+        <v>2012.26</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.03</v>
+        <v>44.08</v>
       </c>
       <c r="R13" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.19</v>
+        <v>-6.15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1877,7 +1881,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1898,7 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1919,55 +1923,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>83.39</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6</v>
+        <v>-0.76</v>
       </c>
       <c r="F14" t="n">
-        <v>15.43</v>
+        <v>15.24</v>
       </c>
       <c r="G14" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="H14" t="n">
-        <v>5.38</v>
+        <v>5.21</v>
       </c>
       <c r="I14" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="J14" t="n">
         <v>3.41</v>
       </c>
       <c r="K14" t="n">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="L14" t="n">
-        <v>82.2</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>83.91</v>
+        <v>83.77</v>
       </c>
       <c r="N14" t="n">
-        <v>78.8</v>
+        <v>78.66</v>
       </c>
       <c r="O14" t="n">
-        <v>90.89</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>64.88</v>
+        <v>64.69</v>
       </c>
       <c r="R14" t="n">
-        <v>6.74</v>
+        <v>6.57</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.54</v>
+        <v>-1.7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1986,7 +1990,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2011,7 +2015,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2032,55 +2036,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>427.36</v>
+        <v>426.77</v>
       </c>
       <c r="D15" t="n">
         <v>91</v>
       </c>
       <c r="E15" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="F15" t="n">
-        <v>1.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>7.25</v>
+        <v>7.1</v>
       </c>
       <c r="H15" t="n">
-        <v>-8.970000000000001</v>
+        <v>-9.09</v>
       </c>
       <c r="I15" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="J15" t="n">
-        <v>11.37</v>
+        <v>11.38</v>
       </c>
       <c r="K15" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="L15" t="n">
-        <v>423.38</v>
+        <v>422.78</v>
       </c>
       <c r="M15" t="n">
-        <v>429.07</v>
+        <v>428.47</v>
       </c>
       <c r="N15" t="n">
-        <v>412.01</v>
+        <v>411.4</v>
       </c>
       <c r="O15" t="n">
-        <v>452.39</v>
+        <v>451.8</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>51.54</v>
+        <v>51.18</v>
       </c>
       <c r="R15" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.46</v>
+        <v>-1.6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2099,7 +2103,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2124,7 +2128,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2145,55 +2149,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>96.61</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="D16" t="n">
         <v>81</v>
       </c>
       <c r="E16" t="n">
-        <v>5.96</v>
+        <v>5.64</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.05</v>
+        <v>-0.35</v>
       </c>
       <c r="G16" t="n">
-        <v>-10.02</v>
+        <v>-10.29</v>
       </c>
       <c r="H16" t="n">
-        <v>-10.1</v>
+        <v>-10.38</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>4.38</v>
       </c>
       <c r="K16" t="n">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
       <c r="L16" t="n">
-        <v>95.08</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>97.27</v>
+        <v>96.98</v>
       </c>
       <c r="N16" t="n">
-        <v>90.70999999999999</v>
+        <v>90.42</v>
       </c>
       <c r="O16" t="n">
-        <v>106.24</v>
+        <v>105.95</v>
       </c>
       <c r="P16" t="n">
         <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.22</v>
+        <v>59.84</v>
       </c>
       <c r="R16" t="n">
-        <v>5.03</v>
+        <v>4.74</v>
       </c>
       <c r="S16" t="n">
-        <v>-7.55</v>
+        <v>-7.82</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2212,7 +2216,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2237,7 +2241,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; RSI saludable; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2258,55 +2262,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>398.89</v>
+        <v>397.94</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
       </c>
       <c r="E17" t="n">
-        <v>0.65</v>
+        <v>0.41</v>
       </c>
       <c r="F17" t="n">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="G17" t="n">
-        <v>4.87</v>
+        <v>4.62</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.619999999999999</v>
+        <v>-8.84</v>
       </c>
       <c r="I17" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J17" t="n">
         <v>17.16</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="L17" t="n">
-        <v>392.88</v>
+        <v>391.93</v>
       </c>
       <c r="M17" t="n">
-        <v>401.46</v>
+        <v>400.51</v>
       </c>
       <c r="N17" t="n">
-        <v>375.72</v>
+        <v>374.77</v>
       </c>
       <c r="O17" t="n">
-        <v>436.64</v>
+        <v>435.69</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>53.21</v>
+        <v>52.89</v>
       </c>
       <c r="R17" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.8</v>
+        <v>-5.03</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2325,7 +2329,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2346,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; RSI saludable; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2367,7 +2371,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>327.08</v>
+        <v>327.06</v>
       </c>
       <c r="D18" t="n">
         <v>96</v>
@@ -2376,16 +2380,16 @@
         <v>2.81</v>
       </c>
       <c r="F18" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="G18" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="H18" t="n">
-        <v>-6.66</v>
+        <v>-6.65</v>
       </c>
       <c r="I18" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="J18" t="n">
         <v>7.83</v>
@@ -2394,22 +2398,22 @@
         <v>2.39</v>
       </c>
       <c r="L18" t="n">
-        <v>324.34</v>
+        <v>324.32</v>
       </c>
       <c r="M18" t="n">
-        <v>328.25</v>
+        <v>328.23</v>
       </c>
       <c r="N18" t="n">
-        <v>316.51</v>
+        <v>316.49</v>
       </c>
       <c r="O18" t="n">
-        <v>344.31</v>
+        <v>344.29</v>
       </c>
       <c r="P18" t="n">
         <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>63.28</v>
+        <v>63.27</v>
       </c>
       <c r="R18" t="n">
         <v>2.49</v>
@@ -2480,22 +2484,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>954.42</v>
+        <v>954.14</v>
       </c>
       <c r="D19" t="n">
         <v>96</v>
       </c>
       <c r="E19" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="F19" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="G19" t="n">
-        <v>4.67</v>
+        <v>4.64</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.98</v>
+        <v>-6.99</v>
       </c>
       <c r="I19" t="n">
         <v>0.5600000000000001</v>
@@ -2507,28 +2511,28 @@
         <v>2.47</v>
       </c>
       <c r="L19" t="n">
-        <v>946.16</v>
+        <v>945.88</v>
       </c>
       <c r="M19" t="n">
-        <v>957.96</v>
+        <v>957.6799999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>922.5700000000001</v>
+        <v>922.29</v>
       </c>
       <c r="O19" t="n">
-        <v>1006.33</v>
+        <v>1006.05</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>54.77</v>
+        <v>54.68</v>
       </c>
       <c r="R19" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.18</v>
+        <v>-2.21</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2593,25 +2597,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>883.3</v>
+        <v>883.98</v>
       </c>
       <c r="D20" t="n">
         <v>88</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.58</v>
+        <v>-1.5</v>
       </c>
       <c r="F20" t="n">
-        <v>11.37</v>
+        <v>11.45</v>
       </c>
       <c r="G20" t="n">
-        <v>16.36</v>
+        <v>16.45</v>
       </c>
       <c r="H20" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="I20" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="J20" t="n">
         <v>32.06</v>
@@ -2620,28 +2624,28 @@
         <v>3.63</v>
       </c>
       <c r="L20" t="n">
-        <v>872.08</v>
+        <v>872.76</v>
       </c>
       <c r="M20" t="n">
-        <v>888.11</v>
+        <v>888.79</v>
       </c>
       <c r="N20" t="n">
-        <v>840.02</v>
+        <v>840.7</v>
       </c>
       <c r="O20" t="n">
-        <v>953.83</v>
+        <v>954.52</v>
       </c>
       <c r="P20" t="n">
         <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>58.85</v>
+        <v>58.98</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-5.16</v>
+        <v>-5.09</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2706,55 +2710,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>228.25</v>
+        <v>228.14</v>
       </c>
       <c r="D21" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E21" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.53</v>
+        <v>-2.58</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.07</v>
+        <v>-7.11</v>
       </c>
       <c r="H21" t="n">
-        <v>-12.58</v>
+        <v>-12.61</v>
       </c>
       <c r="I21" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="J21" t="n">
         <v>3.89</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="L21" t="n">
-        <v>226.89</v>
+        <v>226.78</v>
       </c>
       <c r="M21" t="n">
-        <v>228.83</v>
+        <v>228.72</v>
       </c>
       <c r="N21" t="n">
-        <v>223</v>
+        <v>222.89</v>
       </c>
       <c r="O21" t="n">
-        <v>236.81</v>
+        <v>236.7</v>
       </c>
       <c r="P21" t="n">
         <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>55.08</v>
+        <v>54.87</v>
       </c>
       <c r="R21" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.98</v>
+        <v>-3.03</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2819,25 +2823,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>145.21</v>
+        <v>145.14</v>
       </c>
       <c r="D22" t="n">
         <v>82</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.41</v>
+        <v>-2.46</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.28</v>
+        <v>-7.33</v>
       </c>
       <c r="H22" t="n">
-        <v>-12.46</v>
+        <v>-12.49</v>
       </c>
       <c r="I22" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J22" t="n">
         <v>1.89</v>
@@ -2846,28 +2850,28 @@
         <v>1.3</v>
       </c>
       <c r="L22" t="n">
-        <v>144.55</v>
+        <v>144.48</v>
       </c>
       <c r="M22" t="n">
-        <v>145.49</v>
+        <v>145.42</v>
       </c>
       <c r="N22" t="n">
-        <v>142.66</v>
+        <v>142.59</v>
       </c>
       <c r="O22" t="n">
-        <v>149.36</v>
+        <v>149.3</v>
       </c>
       <c r="P22" t="n">
         <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>56.25</v>
+        <v>55.97</v>
       </c>
       <c r="R22" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.37</v>
+        <v>-2.42</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2932,22 +2936,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>285.61</v>
+        <v>285.76</v>
       </c>
       <c r="D23" t="n">
         <v>96</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.87</v>
+        <v>-2.82</v>
       </c>
       <c r="F23" t="n">
-        <v>6.73</v>
+        <v>6.79</v>
       </c>
       <c r="G23" t="n">
-        <v>20.46</v>
+        <v>20.52</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.32</v>
+        <v>-3.24</v>
       </c>
       <c r="I23" t="n">
         <v>0.6</v>
@@ -2959,28 +2963,28 @@
         <v>4.81</v>
       </c>
       <c r="L23" t="n">
-        <v>280.8</v>
+        <v>280.95</v>
       </c>
       <c r="M23" t="n">
-        <v>287.67</v>
+        <v>287.82</v>
       </c>
       <c r="N23" t="n">
-        <v>267.07</v>
+        <v>267.22</v>
       </c>
       <c r="O23" t="n">
-        <v>315.83</v>
+        <v>315.98</v>
       </c>
       <c r="P23" t="n">
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>61.68</v>
+        <v>61.77</v>
       </c>
       <c r="R23" t="n">
-        <v>4.52</v>
+        <v>4.57</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.43</v>
+        <v>-5.38</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3041,22 +3045,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>131.09</v>
+        <v>131.12</v>
       </c>
       <c r="D24" t="n">
         <v>96</v>
       </c>
       <c r="E24" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="F24" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="G24" t="n">
-        <v>5.4</v>
+        <v>5.42</v>
       </c>
       <c r="H24" t="n">
-        <v>-7.04</v>
+        <v>-6.99</v>
       </c>
       <c r="I24" t="n">
         <v>0.6</v>
@@ -3068,28 +3072,28 @@
         <v>2.01</v>
       </c>
       <c r="L24" t="n">
-        <v>130.17</v>
+        <v>130.2</v>
       </c>
       <c r="M24" t="n">
-        <v>131.49</v>
+        <v>131.52</v>
       </c>
       <c r="N24" t="n">
-        <v>127.53</v>
+        <v>127.56</v>
       </c>
       <c r="O24" t="n">
-        <v>136.89</v>
+        <v>136.92</v>
       </c>
       <c r="P24" t="n">
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>61.16</v>
+        <v>61.27</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.14</v>
+        <v>-2.11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3150,22 +3154,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1084</v>
+        <v>1084.11</v>
       </c>
       <c r="D25" t="n">
         <v>85</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.02</v>
+        <v>-6.99</v>
       </c>
       <c r="I25" t="n">
         <v>0.39</v>
@@ -3177,28 +3181,28 @@
         <v>2.06</v>
       </c>
       <c r="L25" t="n">
-        <v>1076.19</v>
+        <v>1076.3</v>
       </c>
       <c r="M25" t="n">
-        <v>1087.35</v>
+        <v>1087.46</v>
       </c>
       <c r="N25" t="n">
-        <v>1053.87</v>
+        <v>1053.98</v>
       </c>
       <c r="O25" t="n">
-        <v>1133.1</v>
+        <v>1133.21</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>58.8</v>
+        <v>58.84</v>
       </c>
       <c r="R25" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.44</v>
+        <v>-2.43</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3259,25 +3263,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>193.39</v>
+        <v>193.37</v>
       </c>
       <c r="D26" t="n">
         <v>85</v>
       </c>
       <c r="E26" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="F26" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="G26" t="n">
-        <v>11.5</v>
+        <v>11.49</v>
       </c>
       <c r="H26" t="n">
-        <v>-7.08</v>
+        <v>-7.07</v>
       </c>
       <c r="I26" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="J26" t="n">
         <v>4.39</v>
@@ -3286,28 +3290,28 @@
         <v>2.27</v>
       </c>
       <c r="L26" t="n">
-        <v>191.85</v>
+        <v>191.83</v>
       </c>
       <c r="M26" t="n">
-        <v>194.05</v>
+        <v>194.02</v>
       </c>
       <c r="N26" t="n">
-        <v>187.47</v>
+        <v>187.44</v>
       </c>
       <c r="O26" t="n">
-        <v>203.04</v>
+        <v>203.01</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>57.41</v>
+        <v>57.36</v>
       </c>
       <c r="R26" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.08</v>
+        <v>-2.09</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3368,22 +3372,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>496.46</v>
+        <v>496.27</v>
       </c>
       <c r="D27" t="n">
         <v>85</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="F27" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="H27" t="n">
-        <v>-9.6</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="I27" t="n">
         <v>0.91</v>
@@ -3395,28 +3399,28 @@
         <v>1.02</v>
       </c>
       <c r="L27" t="n">
-        <v>494.69</v>
+        <v>494.49</v>
       </c>
       <c r="M27" t="n">
-        <v>497.22</v>
+        <v>497.03</v>
       </c>
       <c r="N27" t="n">
-        <v>489.62</v>
+        <v>489.42</v>
       </c>
       <c r="O27" t="n">
-        <v>507.61</v>
+        <v>507.42</v>
       </c>
       <c r="P27" t="n">
         <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>55.57</v>
+        <v>55.31</v>
       </c>
       <c r="R27" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.13</v>
+        <v>-1.17</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3477,25 +3481,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>90.98999999999999</v>
+        <v>90.92</v>
       </c>
       <c r="D28" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E28" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.04</v>
+        <v>-1.12</v>
       </c>
       <c r="G28" t="n">
-        <v>-2.72</v>
+        <v>-2.8</v>
       </c>
       <c r="H28" t="n">
-        <v>-11.09</v>
+        <v>-11.15</v>
       </c>
       <c r="I28" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="J28" t="n">
         <v>2.18</v>
@@ -3504,28 +3508,28 @@
         <v>2.39</v>
       </c>
       <c r="L28" t="n">
-        <v>90.23</v>
+        <v>90.16</v>
       </c>
       <c r="M28" t="n">
-        <v>91.31999999999999</v>
+        <v>91.25</v>
       </c>
       <c r="N28" t="n">
-        <v>88.05</v>
+        <v>87.98</v>
       </c>
       <c r="O28" t="n">
-        <v>95.78</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="P28" t="n">
         <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>52.16</v>
+        <v>51.9</v>
       </c>
       <c r="R28" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="S28" t="n">
-        <v>-3.02</v>
+        <v>-3.09</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3570,7 +3574,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Volumen bajo; Débil vs QQQ</t>
+          <t>Tendencia larga débil; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -3586,22 +3590,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>180.19</v>
+        <v>180.5</v>
       </c>
       <c r="D29" t="n">
         <v>96</v>
       </c>
       <c r="E29" t="n">
-        <v>5.91</v>
+        <v>6.1</v>
       </c>
       <c r="F29" t="n">
-        <v>28.99</v>
+        <v>29.21</v>
       </c>
       <c r="G29" t="n">
-        <v>126.45</v>
+        <v>126.84</v>
       </c>
       <c r="H29" t="n">
-        <v>18.94</v>
+        <v>19.18</v>
       </c>
       <c r="I29" t="n">
         <v>0.51</v>
@@ -3610,31 +3614,31 @@
         <v>10.64</v>
       </c>
       <c r="K29" t="n">
-        <v>5.9</v>
+        <v>5.89</v>
       </c>
       <c r="L29" t="n">
-        <v>176.47</v>
+        <v>176.78</v>
       </c>
       <c r="M29" t="n">
-        <v>181.79</v>
+        <v>182.1</v>
       </c>
       <c r="N29" t="n">
-        <v>165.83</v>
+        <v>166.14</v>
       </c>
       <c r="O29" t="n">
-        <v>203.59</v>
+        <v>203.9</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>64.34</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="R29" t="n">
-        <v>9.359999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>-6.22</v>
+        <v>-6.06</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3653,7 +3657,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -3678,12 +3682,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Algo extendida sobre MA20</t>
+          <t>MACD sin confirmar; Volumen bajo; Momentum 5D extendido; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
@@ -3699,55 +3703,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>516.45</v>
+        <v>516</v>
       </c>
       <c r="D30" t="n">
         <v>96</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.74</v>
+        <v>-0.83</v>
       </c>
       <c r="F30" t="n">
-        <v>24.23</v>
+        <v>24.12</v>
       </c>
       <c r="G30" t="n">
-        <v>45.22</v>
+        <v>45.1</v>
       </c>
       <c r="H30" t="n">
-        <v>14.18</v>
+        <v>14.09</v>
       </c>
       <c r="I30" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>19.17</v>
       </c>
       <c r="K30" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="L30" t="n">
-        <v>509.74</v>
+        <v>509.29</v>
       </c>
       <c r="M30" t="n">
-        <v>519.33</v>
+        <v>518.88</v>
       </c>
       <c r="N30" t="n">
-        <v>490.57</v>
+        <v>490.12</v>
       </c>
       <c r="O30" t="n">
-        <v>558.63</v>
+        <v>558.1799999999999</v>
       </c>
       <c r="P30" t="n">
         <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>65.93000000000001</v>
+        <v>65.78</v>
       </c>
       <c r="R30" t="n">
-        <v>8.359999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="S30" t="n">
-        <v>-3.24</v>
+        <v>-3.32</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3770,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -3791,7 +3795,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3812,22 +3816,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>563.5</v>
+        <v>563.16</v>
       </c>
       <c r="D31" t="n">
         <v>96</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.54</v>
+        <v>-0.6</v>
       </c>
       <c r="F31" t="n">
-        <v>21.4</v>
+        <v>21.33</v>
       </c>
       <c r="G31" t="n">
-        <v>37.37</v>
+        <v>37.29</v>
       </c>
       <c r="H31" t="n">
-        <v>11.35</v>
+        <v>11.3</v>
       </c>
       <c r="I31" t="n">
         <v>0.79</v>
@@ -3839,28 +3843,28 @@
         <v>3.21</v>
       </c>
       <c r="L31" t="n">
-        <v>557.17</v>
+        <v>556.83</v>
       </c>
       <c r="M31" t="n">
-        <v>566.21</v>
+        <v>565.87</v>
       </c>
       <c r="N31" t="n">
-        <v>539.1</v>
+        <v>538.76</v>
       </c>
       <c r="O31" t="n">
-        <v>603.27</v>
+        <v>602.9299999999999</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>66.59</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="R31" t="n">
-        <v>7.9</v>
+        <v>7.84</v>
       </c>
       <c r="S31" t="n">
-        <v>-3.04</v>
+        <v>-3.1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3879,7 +3883,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -3904,7 +3908,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3925,25 +3929,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>229.8</v>
+        <v>230.25</v>
       </c>
       <c r="D32" t="n">
         <v>96</v>
       </c>
       <c r="E32" t="n">
-        <v>6.78</v>
+        <v>6.99</v>
       </c>
       <c r="F32" t="n">
-        <v>13.94</v>
+        <v>14.17</v>
       </c>
       <c r="G32" t="n">
-        <v>22.31</v>
+        <v>22.55</v>
       </c>
       <c r="H32" t="n">
-        <v>3.89</v>
+        <v>4.14</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>8.210000000000001</v>
@@ -3952,28 +3956,28 @@
         <v>3.57</v>
       </c>
       <c r="L32" t="n">
-        <v>226.93</v>
+        <v>227.38</v>
       </c>
       <c r="M32" t="n">
-        <v>231.03</v>
+        <v>231.48</v>
       </c>
       <c r="N32" t="n">
-        <v>218.72</v>
+        <v>219.17</v>
       </c>
       <c r="O32" t="n">
-        <v>247.86</v>
+        <v>248.31</v>
       </c>
       <c r="P32" t="n">
         <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>60.09</v>
+        <v>60.51</v>
       </c>
       <c r="R32" t="n">
-        <v>9.16</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="S32" t="n">
-        <v>-2.85</v>
+        <v>-2.66</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3992,7 +3996,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4017,7 +4021,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4038,25 +4042,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>202.6</v>
+        <v>202.81</v>
       </c>
       <c r="D33" t="n">
         <v>96</v>
       </c>
       <c r="E33" t="n">
-        <v>7.96</v>
+        <v>8.07</v>
       </c>
       <c r="F33" t="n">
-        <v>13.01</v>
+        <v>13.12</v>
       </c>
       <c r="G33" t="n">
-        <v>17.29</v>
+        <v>17.41</v>
       </c>
       <c r="H33" t="n">
-        <v>2.96</v>
+        <v>3.09</v>
       </c>
       <c r="I33" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="J33" t="n">
         <v>6.37</v>
@@ -4065,28 +4069,28 @@
         <v>3.14</v>
       </c>
       <c r="L33" t="n">
-        <v>200.37</v>
+        <v>200.58</v>
       </c>
       <c r="M33" t="n">
-        <v>203.56</v>
+        <v>203.77</v>
       </c>
       <c r="N33" t="n">
-        <v>194</v>
+        <v>194.21</v>
       </c>
       <c r="O33" t="n">
-        <v>216.61</v>
+        <v>216.82</v>
       </c>
       <c r="P33" t="n">
         <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>56.37</v>
+        <v>56.53</v>
       </c>
       <c r="R33" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S33" t="n">
-        <v>-5.03</v>
+        <v>-4.93</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4105,7 +4109,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>XLE 7.27% · CL=F 19.89%</t>
+          <t>XLE 7.22% · CL=F 20.0%</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -4130,7 +4134,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.27% · CL=F 19.89%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.22% · CL=F 20.0%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4151,25 +4155,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>48.95</v>
+        <v>49.01</v>
       </c>
       <c r="D34" t="n">
         <v>96</v>
       </c>
       <c r="E34" t="n">
-        <v>7.32</v>
+        <v>7.45</v>
       </c>
       <c r="F34" t="n">
-        <v>10.67</v>
+        <v>10.81</v>
       </c>
       <c r="G34" t="n">
-        <v>10.18</v>
+        <v>10.31</v>
       </c>
       <c r="H34" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="J34" t="n">
         <v>1.7</v>
@@ -4178,28 +4182,28 @@
         <v>3.47</v>
       </c>
       <c r="L34" t="n">
-        <v>48.36</v>
+        <v>48.41</v>
       </c>
       <c r="M34" t="n">
-        <v>49.21</v>
+        <v>49.26</v>
       </c>
       <c r="N34" t="n">
-        <v>46.66</v>
+        <v>46.71</v>
       </c>
       <c r="O34" t="n">
-        <v>52.69</v>
+        <v>52.75</v>
       </c>
       <c r="P34" t="n">
         <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>52.63</v>
+        <v>52.83</v>
       </c>
       <c r="R34" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="S34" t="n">
-        <v>-5.77</v>
+        <v>-5.66</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4218,7 +4222,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>XLE 7.27% · CL=F 19.89%</t>
+          <t>XLE 7.22% · CL=F 20.0%</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -4243,7 +4247,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.27% · CL=F 19.89%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.22% · CL=F 20.0%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4264,22 +4268,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>139.14</v>
+        <v>139.18</v>
       </c>
       <c r="D35" t="n">
         <v>96</v>
       </c>
       <c r="E35" t="n">
-        <v>7.01</v>
+        <v>7.04</v>
       </c>
       <c r="F35" t="n">
-        <v>8.34</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>13.2</v>
+        <v>13.23</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.71</v>
+        <v>-1.66</v>
       </c>
       <c r="I35" t="n">
         <v>0.4</v>
@@ -4291,28 +4295,28 @@
         <v>2.71</v>
       </c>
       <c r="L35" t="n">
-        <v>137.82</v>
+        <v>137.86</v>
       </c>
       <c r="M35" t="n">
-        <v>139.71</v>
+        <v>139.75</v>
       </c>
       <c r="N35" t="n">
-        <v>134.04</v>
+        <v>134.08</v>
       </c>
       <c r="O35" t="n">
-        <v>147.45</v>
+        <v>147.49</v>
       </c>
       <c r="P35" t="n">
         <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.16</v>
+        <v>59.21</v>
       </c>
       <c r="R35" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="S35" t="n">
-        <v>-2.6</v>
+        <v>-2.57</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4331,7 +4335,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>XLE 7.27% · CL=F 19.89%</t>
+          <t>XLE 7.22% · CL=F 20.0%</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4356,7 +4360,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.27% · CL=F 19.89%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.22% · CL=F 20.0%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4368,64 +4372,64 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>156.06</v>
+        <v>213.2</v>
       </c>
       <c r="D36" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E36" t="n">
-        <v>7.95</v>
+        <v>-0.03</v>
       </c>
       <c r="F36" t="n">
-        <v>6.57</v>
+        <v>27.87</v>
       </c>
       <c r="G36" t="n">
-        <v>3.37</v>
+        <v>67.97</v>
       </c>
       <c r="H36" t="n">
-        <v>-3.48</v>
+        <v>17.84</v>
       </c>
       <c r="I36" t="n">
-        <v>0.73</v>
+        <v>0.55</v>
       </c>
       <c r="J36" t="n">
-        <v>3.89</v>
+        <v>16.2</v>
       </c>
       <c r="K36" t="n">
-        <v>2.49</v>
+        <v>7.6</v>
       </c>
       <c r="L36" t="n">
-        <v>154.7</v>
+        <v>207.53</v>
       </c>
       <c r="M36" t="n">
-        <v>156.64</v>
+        <v>215.63</v>
       </c>
       <c r="N36" t="n">
-        <v>150.8</v>
+        <v>191.32</v>
       </c>
       <c r="O36" t="n">
-        <v>164.63</v>
+        <v>248.85</v>
       </c>
       <c r="P36" t="n">
         <v>1.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>62.17</v>
+        <v>49.02</v>
       </c>
       <c r="R36" t="n">
-        <v>3.54</v>
+        <v>1.92</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.29</v>
+        <v>-10.98</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4444,7 +4448,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>XLE 7.27% · CL=F 19.89%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4469,19 +4473,19 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.27% · CL=F 19.89%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Volumen bajo; Momentum 5D extendido; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4490,55 +4494,55 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>212.74</v>
+        <v>293.34</v>
       </c>
       <c r="D37" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.25</v>
+        <v>-0.48</v>
       </c>
       <c r="F37" t="n">
-        <v>27.59</v>
+        <v>35.79</v>
       </c>
       <c r="G37" t="n">
-        <v>67.59999999999999</v>
+        <v>27.04</v>
       </c>
       <c r="H37" t="n">
-        <v>17.54</v>
+        <v>25.76</v>
       </c>
       <c r="I37" t="n">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="J37" t="n">
-        <v>16.2</v>
+        <v>14.83</v>
       </c>
       <c r="K37" t="n">
-        <v>7.62</v>
+        <v>5.05</v>
       </c>
       <c r="L37" t="n">
-        <v>207.06</v>
+        <v>288.15</v>
       </c>
       <c r="M37" t="n">
-        <v>215.17</v>
+        <v>295.56</v>
       </c>
       <c r="N37" t="n">
-        <v>190.86</v>
+        <v>273.33</v>
       </c>
       <c r="O37" t="n">
-        <v>248.38</v>
+        <v>325.96</v>
       </c>
       <c r="P37" t="n">
         <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>48.86</v>
+        <v>70.36</v>
       </c>
       <c r="R37" t="n">
-        <v>1.71</v>
+        <v>7.45</v>
       </c>
       <c r="S37" t="n">
-        <v>-11.18</v>
+        <v>-4.33</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4557,7 +4561,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4582,76 +4586,76 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Volatilidad alta</t>
+          <t>RSI algo alto; MACD sin confirmar; Volumen bajo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>293.26</v>
+        <v>121.36</v>
       </c>
       <c r="D38" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.51</v>
+        <v>7.37</v>
       </c>
       <c r="F38" t="n">
-        <v>35.75</v>
+        <v>5.36</v>
       </c>
       <c r="G38" t="n">
-        <v>27</v>
+        <v>9.56</v>
       </c>
       <c r="H38" t="n">
-        <v>25.7</v>
+        <v>-4.67</v>
       </c>
       <c r="I38" t="n">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
       <c r="J38" t="n">
-        <v>14.83</v>
+        <v>3.28</v>
       </c>
       <c r="K38" t="n">
-        <v>5.06</v>
+        <v>2.71</v>
       </c>
       <c r="L38" t="n">
-        <v>288.07</v>
+        <v>120.21</v>
       </c>
       <c r="M38" t="n">
-        <v>295.48</v>
+        <v>121.85</v>
       </c>
       <c r="N38" t="n">
-        <v>273.25</v>
+        <v>116.93</v>
       </c>
       <c r="O38" t="n">
-        <v>325.88</v>
+        <v>128.59</v>
       </c>
       <c r="P38" t="n">
         <v>1.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>70.31</v>
+        <v>50.86</v>
       </c>
       <c r="R38" t="n">
-        <v>7.42</v>
+        <v>1.04</v>
       </c>
       <c r="S38" t="n">
-        <v>-4.36</v>
+        <v>-4.69</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4670,7 +4674,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>XLE 7.22% · CL=F 20.0%</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -4695,19 +4699,19 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.22% · CL=F 20.0%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>RSI algo alto; MACD sin confirmar; Volumen bajo; Algo extendida sobre MA20</t>
+          <t>MACD sin confirmar; Volumen bajo; Momentum 5D extendido; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4716,55 +4720,55 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>121.29</v>
+        <v>156.16</v>
       </c>
       <c r="D39" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E39" t="n">
-        <v>7.3</v>
+        <v>8.02</v>
       </c>
       <c r="F39" t="n">
-        <v>5.3</v>
+        <v>6.64</v>
       </c>
       <c r="G39" t="n">
-        <v>9.5</v>
+        <v>3.44</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.75</v>
+        <v>-3.39</v>
       </c>
       <c r="I39" t="n">
-        <v>0.38</v>
+        <v>0.73</v>
       </c>
       <c r="J39" t="n">
-        <v>3.28</v>
+        <v>3.89</v>
       </c>
       <c r="K39" t="n">
-        <v>2.71</v>
+        <v>2.49</v>
       </c>
       <c r="L39" t="n">
-        <v>120.14</v>
+        <v>154.8</v>
       </c>
       <c r="M39" t="n">
-        <v>121.78</v>
+        <v>156.74</v>
       </c>
       <c r="N39" t="n">
-        <v>116.85</v>
+        <v>150.9</v>
       </c>
       <c r="O39" t="n">
-        <v>128.51</v>
+        <v>164.73</v>
       </c>
       <c r="P39" t="n">
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>50.75</v>
+        <v>62.29</v>
       </c>
       <c r="R39" t="n">
-        <v>0.98</v>
+        <v>3.6</v>
       </c>
       <c r="S39" t="n">
-        <v>-4.75</v>
+        <v>-0.23</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4783,7 +4787,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>XLE 7.27% · CL=F 19.89%</t>
+          <t>XLE 7.22% · CL=F 20.0%</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -4793,7 +4797,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -4808,12 +4812,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.27% · CL=F 19.89%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.22% · CL=F 20.0%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Momentum 5D extendido; Débil vs QQQ</t>
+          <t>Volumen bajo; Momentum 5D extendido; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -4829,22 +4833,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>243.07</v>
+        <v>243.57</v>
       </c>
       <c r="D40" t="n">
         <v>96</v>
       </c>
       <c r="E40" t="n">
-        <v>-6.68</v>
+        <v>-6.48</v>
       </c>
       <c r="F40" t="n">
-        <v>24.05</v>
+        <v>24.31</v>
       </c>
       <c r="G40" t="n">
-        <v>104.79</v>
+        <v>105.21</v>
       </c>
       <c r="H40" t="n">
-        <v>14</v>
+        <v>14.28</v>
       </c>
       <c r="I40" t="n">
         <v>0.33</v>
@@ -4853,31 +4857,31 @@
         <v>13.94</v>
       </c>
       <c r="K40" t="n">
-        <v>5.73</v>
+        <v>5.72</v>
       </c>
       <c r="L40" t="n">
-        <v>238.19</v>
+        <v>238.69</v>
       </c>
       <c r="M40" t="n">
-        <v>245.16</v>
+        <v>245.66</v>
       </c>
       <c r="N40" t="n">
-        <v>224.25</v>
+        <v>224.75</v>
       </c>
       <c r="O40" t="n">
-        <v>273.74</v>
+        <v>274.24</v>
       </c>
       <c r="P40" t="n">
         <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>61.54</v>
+        <v>61.8</v>
       </c>
       <c r="R40" t="n">
-        <v>8.42</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="S40" t="n">
-        <v>-7.92</v>
+        <v>-7.74</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4896,7 +4900,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -4921,7 +4925,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -4942,55 +4946,55 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>499.65</v>
+        <v>499.35</v>
       </c>
       <c r="D41" t="n">
         <v>93</v>
       </c>
       <c r="E41" t="n">
-        <v>6.64</v>
+        <v>6.57</v>
       </c>
       <c r="F41" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="G41" t="n">
-        <v>21.27</v>
+        <v>21.2</v>
       </c>
       <c r="H41" t="n">
-        <v>-5.35</v>
+        <v>-5.39</v>
       </c>
       <c r="I41" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="J41" t="n">
         <v>29.7</v>
       </c>
       <c r="K41" t="n">
-        <v>5.94</v>
+        <v>5.95</v>
       </c>
       <c r="L41" t="n">
-        <v>489.25</v>
+        <v>488.95</v>
       </c>
       <c r="M41" t="n">
-        <v>504.11</v>
+        <v>503.81</v>
       </c>
       <c r="N41" t="n">
-        <v>459.55</v>
+        <v>459.25</v>
       </c>
       <c r="O41" t="n">
-        <v>565</v>
+        <v>564.7</v>
       </c>
       <c r="P41" t="n">
         <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>58.68</v>
+        <v>58.63</v>
       </c>
       <c r="R41" t="n">
-        <v>6.24</v>
+        <v>6.18</v>
       </c>
       <c r="S41" t="n">
-        <v>-2.54</v>
+        <v>-2.6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5009,7 +5013,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -5034,7 +5038,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5055,55 +5059,55 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>52.87</v>
+        <v>52.7</v>
       </c>
       <c r="D42" t="n">
         <v>87</v>
       </c>
       <c r="E42" t="n">
-        <v>7.37</v>
+        <v>7.03</v>
       </c>
       <c r="F42" t="n">
-        <v>14.71</v>
+        <v>14.34</v>
       </c>
       <c r="G42" t="n">
-        <v>58.15</v>
+        <v>57.65</v>
       </c>
       <c r="H42" t="n">
-        <v>4.66</v>
+        <v>4.31</v>
       </c>
       <c r="I42" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J42" t="n">
         <v>4.72</v>
       </c>
       <c r="K42" t="n">
-        <v>8.92</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>51.22</v>
+        <v>51.05</v>
       </c>
       <c r="M42" t="n">
-        <v>53.58</v>
+        <v>53.41</v>
       </c>
       <c r="N42" t="n">
-        <v>46.5</v>
+        <v>46.33</v>
       </c>
       <c r="O42" t="n">
-        <v>63.25</v>
+        <v>63.08</v>
       </c>
       <c r="P42" t="n">
         <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>62.67</v>
+        <v>62.38</v>
       </c>
       <c r="R42" t="n">
-        <v>8.98</v>
+        <v>8.65</v>
       </c>
       <c r="S42" t="n">
-        <v>-10.62</v>
+        <v>-10.9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5122,7 +5126,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -5147,7 +5151,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5168,22 +5172,22 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>159.7</v>
+        <v>159.07</v>
       </c>
       <c r="D43" t="n">
         <v>83</v>
       </c>
       <c r="E43" t="n">
-        <v>4.76</v>
+        <v>4.34</v>
       </c>
       <c r="F43" t="n">
-        <v>10.92</v>
+        <v>10.48</v>
       </c>
       <c r="G43" t="n">
-        <v>-10.88</v>
+        <v>-11.23</v>
       </c>
       <c r="H43" t="n">
-        <v>0.87</v>
+        <v>0.45</v>
       </c>
       <c r="I43" t="n">
         <v>0.6899999999999999</v>
@@ -5192,31 +5196,31 @@
         <v>7.81</v>
       </c>
       <c r="K43" t="n">
-        <v>4.89</v>
+        <v>4.91</v>
       </c>
       <c r="L43" t="n">
-        <v>156.97</v>
+        <v>156.34</v>
       </c>
       <c r="M43" t="n">
-        <v>160.87</v>
+        <v>160.24</v>
       </c>
       <c r="N43" t="n">
-        <v>149.16</v>
+        <v>148.53</v>
       </c>
       <c r="O43" t="n">
-        <v>176.87</v>
+        <v>176.24</v>
       </c>
       <c r="P43" t="n">
         <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>66.23</v>
+        <v>65.77</v>
       </c>
       <c r="R43" t="n">
-        <v>8.369999999999999</v>
+        <v>7.97</v>
       </c>
       <c r="S43" t="n">
-        <v>-0.06</v>
+        <v>-0.46</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5235,7 +5239,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -5260,7 +5264,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MACD positivo; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5281,55 +5285,55 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>195.77</v>
+        <v>195.4</v>
       </c>
       <c r="D44" t="n">
         <v>82</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.09</v>
+        <v>-0.28</v>
       </c>
       <c r="F44" t="n">
-        <v>11.83</v>
+        <v>11.62</v>
       </c>
       <c r="G44" t="n">
-        <v>25.5</v>
+        <v>25.26</v>
       </c>
       <c r="H44" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="I44" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="J44" t="n">
         <v>9.220000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="L44" t="n">
-        <v>192.55</v>
+        <v>192.17</v>
       </c>
       <c r="M44" t="n">
-        <v>197.16</v>
+        <v>196.78</v>
       </c>
       <c r="N44" t="n">
-        <v>183.32</v>
+        <v>182.95</v>
       </c>
       <c r="O44" t="n">
-        <v>216.07</v>
+        <v>215.69</v>
       </c>
       <c r="P44" t="n">
         <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>67.77</v>
+        <v>67.47</v>
       </c>
       <c r="R44" t="n">
-        <v>7.46</v>
+        <v>7.26</v>
       </c>
       <c r="S44" t="n">
-        <v>-2.46</v>
+        <v>-2.65</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5348,7 +5352,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -5373,7 +5377,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5385,64 +5389,64 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>429.25</v>
+        <v>88.69</v>
       </c>
       <c r="D45" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E45" t="n">
-        <v>0.21</v>
+        <v>-3.18</v>
       </c>
       <c r="F45" t="n">
-        <v>7.15</v>
+        <v>32.49</v>
       </c>
       <c r="G45" t="n">
-        <v>4.26</v>
+        <v>10.5</v>
       </c>
       <c r="H45" t="n">
-        <v>-2.9</v>
+        <v>22.46</v>
       </c>
       <c r="I45" t="n">
-        <v>0.57</v>
+        <v>0.36</v>
       </c>
       <c r="J45" t="n">
-        <v>17.19</v>
+        <v>6.91</v>
       </c>
       <c r="K45" t="n">
-        <v>4</v>
+        <v>7.79</v>
       </c>
       <c r="L45" t="n">
-        <v>423.23</v>
+        <v>86.27</v>
       </c>
       <c r="M45" t="n">
-        <v>431.83</v>
+        <v>89.73</v>
       </c>
       <c r="N45" t="n">
-        <v>406.05</v>
+        <v>79.36</v>
       </c>
       <c r="O45" t="n">
-        <v>467.06</v>
+        <v>103.9</v>
       </c>
       <c r="P45" t="n">
         <v>1.63</v>
       </c>
       <c r="Q45" t="n">
-        <v>70.44</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="R45" t="n">
-        <v>6.87</v>
+        <v>10.62</v>
       </c>
       <c r="S45" t="n">
-        <v>-5.33</v>
+        <v>-7.92</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5461,7 +5465,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5486,76 +5490,76 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI algo alto; Volumen bajo</t>
+          <t>Tendencia larga débil; RSI algo alto; Volumen bajo; Momentum negativo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>88.84</v>
+        <v>31.53</v>
       </c>
       <c r="D46" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E46" t="n">
-        <v>-3.01</v>
+        <v>-10.86</v>
       </c>
       <c r="F46" t="n">
-        <v>32.72</v>
+        <v>10.4</v>
       </c>
       <c r="G46" t="n">
-        <v>10.69</v>
+        <v>-1.96</v>
       </c>
       <c r="H46" t="n">
-        <v>22.67</v>
+        <v>0.37</v>
       </c>
       <c r="I46" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="J46" t="n">
-        <v>6.91</v>
+        <v>2.29</v>
       </c>
       <c r="K46" t="n">
-        <v>7.78</v>
+        <v>7.26</v>
       </c>
       <c r="L46" t="n">
-        <v>86.42</v>
+        <v>30.73</v>
       </c>
       <c r="M46" t="n">
-        <v>89.88</v>
+        <v>31.87</v>
       </c>
       <c r="N46" t="n">
-        <v>79.51000000000001</v>
+        <v>28.44</v>
       </c>
       <c r="O46" t="n">
-        <v>104.05</v>
+        <v>36.56</v>
       </c>
       <c r="P46" t="n">
         <v>1.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>67.63</v>
+        <v>59.5</v>
       </c>
       <c r="R46" t="n">
-        <v>10.8</v>
+        <v>5.02</v>
       </c>
       <c r="S46" t="n">
-        <v>-7.76</v>
+        <v>-13.31</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5574,7 +5578,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -5599,76 +5603,76 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI algo alto; Volumen bajo; Momentum negativo; Algo extendida sobre MA20</t>
+          <t>Tendencia larga débil; Volumen bajo; Momentum negativo; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>31.57</v>
+        <v>428.52</v>
       </c>
       <c r="D47" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E47" t="n">
-        <v>-10.74</v>
+        <v>0.04</v>
       </c>
       <c r="F47" t="n">
-        <v>10.54</v>
+        <v>6.96</v>
       </c>
       <c r="G47" t="n">
-        <v>-1.83</v>
+        <v>4.08</v>
       </c>
       <c r="H47" t="n">
-        <v>0.49</v>
+        <v>-3.07</v>
       </c>
       <c r="I47" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="J47" t="n">
-        <v>2.29</v>
+        <v>17.19</v>
       </c>
       <c r="K47" t="n">
-        <v>7.25</v>
+        <v>4.01</v>
       </c>
       <c r="L47" t="n">
-        <v>30.77</v>
+        <v>422.5</v>
       </c>
       <c r="M47" t="n">
-        <v>31.91</v>
+        <v>431.1</v>
       </c>
       <c r="N47" t="n">
-        <v>28.48</v>
+        <v>405.32</v>
       </c>
       <c r="O47" t="n">
-        <v>36.6</v>
+        <v>466.33</v>
       </c>
       <c r="P47" t="n">
         <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>59.63</v>
+        <v>70.02</v>
       </c>
       <c r="R47" t="n">
-        <v>5.15</v>
+        <v>6.69</v>
       </c>
       <c r="S47" t="n">
-        <v>-13.2</v>
+        <v>-5.49</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5687,7 +5691,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -5695,11 +5699,7 @@
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Volumen bajo; Momentum negativo; Volatilidad alta</t>
+          <t>Tendencia larga débil; RSI algo alto; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -5733,25 +5733,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1045.02</v>
+        <v>1045.27</v>
       </c>
       <c r="D48" t="n">
         <v>96</v>
       </c>
       <c r="E48" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="F48" t="n">
-        <v>4.67</v>
+        <v>4.69</v>
       </c>
       <c r="G48" t="n">
-        <v>5.94</v>
+        <v>5.97</v>
       </c>
       <c r="H48" t="n">
-        <v>-5.38</v>
+        <v>-5.34</v>
       </c>
       <c r="I48" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J48" t="n">
         <v>20.47</v>
@@ -5760,28 +5760,28 @@
         <v>1.96</v>
       </c>
       <c r="L48" t="n">
-        <v>1037.86</v>
+        <v>1038.11</v>
       </c>
       <c r="M48" t="n">
-        <v>1048.09</v>
+        <v>1048.34</v>
       </c>
       <c r="N48" t="n">
-        <v>1017.39</v>
+        <v>1017.64</v>
       </c>
       <c r="O48" t="n">
-        <v>1090.05</v>
+        <v>1090.3</v>
       </c>
       <c r="P48" t="n">
         <v>1.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>69.27</v>
+        <v>69.33</v>
       </c>
       <c r="R48" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="S48" t="n">
-        <v>-1.18</v>
+        <v>-1.16</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5846,25 +5846,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>209.32</v>
+        <v>209.62</v>
       </c>
       <c r="D49" t="n">
         <v>79</v>
       </c>
       <c r="E49" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="G49" t="n">
-        <v>-5.92</v>
+        <v>-5.79</v>
       </c>
       <c r="H49" t="n">
-        <v>-9.6</v>
+        <v>-9.43</v>
       </c>
       <c r="I49" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="J49" t="n">
         <v>5.82</v>
@@ -5873,28 +5873,28 @@
         <v>2.78</v>
       </c>
       <c r="L49" t="n">
-        <v>207.29</v>
+        <v>207.58</v>
       </c>
       <c r="M49" t="n">
-        <v>210.2</v>
+        <v>210.49</v>
       </c>
       <c r="N49" t="n">
-        <v>201.47</v>
+        <v>201.76</v>
       </c>
       <c r="O49" t="n">
-        <v>222.13</v>
+        <v>222.42</v>
       </c>
       <c r="P49" t="n">
         <v>1.63</v>
       </c>
       <c r="Q49" t="n">
-        <v>65.93000000000001</v>
+        <v>66.45</v>
       </c>
       <c r="R49" t="n">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="S49" t="n">
-        <v>-2.6</v>
+        <v>-2.47</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5955,55 +5955,55 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10.47</v>
+        <v>10.45</v>
       </c>
       <c r="D50" t="n">
         <v>74</v>
       </c>
       <c r="E50" t="n">
-        <v>-3.73</v>
+        <v>-3.82</v>
       </c>
       <c r="F50" t="n">
-        <v>13.5</v>
+        <v>13.39</v>
       </c>
       <c r="G50" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="I50" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="J50" t="n">
         <v>0.79</v>
       </c>
       <c r="K50" t="n">
-        <v>7.59</v>
+        <v>7.6</v>
       </c>
       <c r="L50" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="M50" t="n">
-        <v>10.58</v>
+        <v>10.57</v>
       </c>
       <c r="N50" t="n">
-        <v>9.390000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>12.21</v>
+        <v>12.2</v>
       </c>
       <c r="P50" t="n">
         <v>1.62</v>
       </c>
       <c r="Q50" t="n">
-        <v>61.46</v>
+        <v>61.37</v>
       </c>
       <c r="R50" t="n">
-        <v>9.19</v>
+        <v>9.09</v>
       </c>
       <c r="S50" t="n">
-        <v>-6.48</v>
+        <v>-6.57</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6064,25 +6064,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>44.51</v>
+        <v>44.47</v>
       </c>
       <c r="D51" t="n">
         <v>74</v>
       </c>
       <c r="E51" t="n">
-        <v>-3.39</v>
+        <v>-3.48</v>
       </c>
       <c r="F51" t="n">
-        <v>9.85</v>
+        <v>9.74</v>
       </c>
       <c r="G51" t="n">
-        <v>-4.76</v>
+        <v>-4.86</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.2</v>
+        <v>-0.29</v>
       </c>
       <c r="I51" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J51" t="n">
         <v>1.39</v>
@@ -6091,28 +6091,28 @@
         <v>3.13</v>
       </c>
       <c r="L51" t="n">
-        <v>44.02</v>
+        <v>43.98</v>
       </c>
       <c r="M51" t="n">
-        <v>44.72</v>
+        <v>44.67</v>
       </c>
       <c r="N51" t="n">
-        <v>42.63</v>
+        <v>42.58</v>
       </c>
       <c r="O51" t="n">
-        <v>47.57</v>
+        <v>47.53</v>
       </c>
       <c r="P51" t="n">
         <v>1.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>66.12</v>
+        <v>65.83</v>
       </c>
       <c r="R51" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="S51" t="n">
-        <v>-6.86</v>
+        <v>-6.96</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6173,22 +6173,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>263.67</v>
+        <v>263.89</v>
       </c>
       <c r="D52" t="n">
         <v>65</v>
       </c>
       <c r="E52" t="n">
-        <v>-3.3</v>
+        <v>-3.22</v>
       </c>
       <c r="F52" t="n">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="G52" t="n">
-        <v>28.71</v>
+        <v>28.82</v>
       </c>
       <c r="H52" t="n">
-        <v>-4.82</v>
+        <v>-4.71</v>
       </c>
       <c r="I52" t="n">
         <v>0.57</v>
@@ -6197,31 +6197,31 @@
         <v>7.19</v>
       </c>
       <c r="K52" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="L52" t="n">
-        <v>261.15</v>
+        <v>261.38</v>
       </c>
       <c r="M52" t="n">
-        <v>264.75</v>
+        <v>264.97</v>
       </c>
       <c r="N52" t="n">
-        <v>253.97</v>
+        <v>254.19</v>
       </c>
       <c r="O52" t="n">
-        <v>279.48</v>
+        <v>279.71</v>
       </c>
       <c r="P52" t="n">
         <v>1.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>53.21</v>
+        <v>53.52</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.32</v>
+        <v>-0.23</v>
       </c>
       <c r="S52" t="n">
-        <v>-5.35</v>
+        <v>-5.26</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6282,22 +6282,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>248.18</v>
+        <v>247.79</v>
       </c>
       <c r="D53" t="n">
         <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.92</v>
+        <v>-2.07</v>
       </c>
       <c r="F53" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="G53" t="n">
-        <v>-4.26</v>
+        <v>-4.41</v>
       </c>
       <c r="H53" t="n">
-        <v>-8.52</v>
+        <v>-8.66</v>
       </c>
       <c r="I53" t="n">
         <v>0.61</v>
@@ -6309,28 +6309,28 @@
         <v>3.41</v>
       </c>
       <c r="L53" t="n">
-        <v>245.22</v>
+        <v>244.83</v>
       </c>
       <c r="M53" t="n">
-        <v>249.45</v>
+        <v>249.06</v>
       </c>
       <c r="N53" t="n">
-        <v>236.76</v>
+        <v>236.37</v>
       </c>
       <c r="O53" t="n">
-        <v>266.79</v>
+        <v>266.4</v>
       </c>
       <c r="P53" t="n">
         <v>1.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>57.31</v>
+        <v>57.04</v>
       </c>
       <c r="R53" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="S53" t="n">
-        <v>-4.34</v>
+        <v>-4.49</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; RSI saludable; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; RSI saludable; MACD mejorando</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6391,25 +6391,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>278.45</v>
+        <v>278.26</v>
       </c>
       <c r="D54" t="n">
         <v>69</v>
       </c>
       <c r="E54" t="n">
-        <v>-2.01</v>
+        <v>-2.08</v>
       </c>
       <c r="F54" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="G54" t="n">
-        <v>5.42</v>
+        <v>5.35</v>
       </c>
       <c r="H54" t="n">
-        <v>-9.08</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="J54" t="n">
         <v>4.68</v>
@@ -6418,28 +6418,28 @@
         <v>1.68</v>
       </c>
       <c r="L54" t="n">
-        <v>276.81</v>
+        <v>276.62</v>
       </c>
       <c r="M54" t="n">
-        <v>279.15</v>
+        <v>278.96</v>
       </c>
       <c r="N54" t="n">
-        <v>272.14</v>
+        <v>271.94</v>
       </c>
       <c r="O54" t="n">
-        <v>288.74</v>
+        <v>288.54</v>
       </c>
       <c r="P54" t="n">
         <v>1.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>51.6</v>
+        <v>51.36</v>
       </c>
       <c r="R54" t="n">
-        <v>-0.34</v>
+        <v>-0.41</v>
       </c>
       <c r="S54" t="n">
-        <v>-3.17</v>
+        <v>-3.24</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6500,22 +6500,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>18.29</v>
+        <v>18.23</v>
       </c>
       <c r="D55" t="n">
         <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>-3.44</v>
+        <v>-3.75</v>
       </c>
       <c r="F55" t="n">
-        <v>-7.68</v>
+        <v>-7.98</v>
       </c>
       <c r="G55" t="n">
-        <v>10.17</v>
+        <v>9.82</v>
       </c>
       <c r="H55" t="n">
-        <v>-17.73</v>
+        <v>-18.01</v>
       </c>
       <c r="I55" t="n">
         <v>0.64</v>
@@ -6524,31 +6524,31 @@
         <v>1.6</v>
       </c>
       <c r="K55" t="n">
-        <v>8.74</v>
+        <v>8.77</v>
       </c>
       <c r="L55" t="n">
-        <v>17.73</v>
+        <v>17.67</v>
       </c>
       <c r="M55" t="n">
-        <v>18.53</v>
+        <v>18.47</v>
       </c>
       <c r="N55" t="n">
-        <v>16.13</v>
+        <v>16.07</v>
       </c>
       <c r="O55" t="n">
-        <v>21.81</v>
+        <v>21.75</v>
       </c>
       <c r="P55" t="n">
         <v>1.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>55.43</v>
+        <v>55.18</v>
       </c>
       <c r="R55" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="S55" t="n">
-        <v>-12.99</v>
+        <v>-13.27</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6609,55 +6609,55 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
       <c r="D56" t="n">
         <v>66</v>
       </c>
       <c r="E56" t="n">
-        <v>-5.25</v>
+        <v>-5.48</v>
       </c>
       <c r="F56" t="n">
-        <v>0.49</v>
+        <v>0.25</v>
       </c>
       <c r="G56" t="n">
-        <v>-15.08</v>
+        <v>-15.28</v>
       </c>
       <c r="H56" t="n">
-        <v>-9.56</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="J56" t="n">
         <v>0.39</v>
       </c>
       <c r="K56" t="n">
-        <v>6.43</v>
+        <v>6.44</v>
       </c>
       <c r="L56" t="n">
-        <v>6</v>
+        <v>5.99</v>
       </c>
       <c r="M56" t="n">
-        <v>6.2</v>
+        <v>6.18</v>
       </c>
       <c r="N56" t="n">
-        <v>5.61</v>
+        <v>5.59</v>
       </c>
       <c r="O56" t="n">
-        <v>7.01</v>
+        <v>6.99</v>
       </c>
       <c r="P56" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q56" t="n">
-        <v>55.08</v>
+        <v>54.74</v>
       </c>
       <c r="R56" t="n">
-        <v>1.23</v>
+        <v>0.99</v>
       </c>
       <c r="S56" t="n">
-        <v>-9.039999999999999</v>
+        <v>-9.26</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6718,22 +6718,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>306.42</v>
+        <v>306.53</v>
       </c>
       <c r="D57" t="n">
         <v>94</v>
       </c>
       <c r="E57" t="n">
-        <v>6.47</v>
+        <v>6.51</v>
       </c>
       <c r="F57" t="n">
-        <v>34.01</v>
+        <v>34.06</v>
       </c>
       <c r="G57" t="n">
-        <v>41.24</v>
+        <v>41.29</v>
       </c>
       <c r="H57" t="n">
-        <v>23.96</v>
+        <v>24.03</v>
       </c>
       <c r="I57" t="n">
         <v>0.3</v>
@@ -6742,31 +6742,31 @@
         <v>9.27</v>
       </c>
       <c r="K57" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="L57" t="n">
-        <v>303.17</v>
+        <v>303.29</v>
       </c>
       <c r="M57" t="n">
-        <v>307.81</v>
+        <v>307.92</v>
       </c>
       <c r="N57" t="n">
-        <v>293.9</v>
+        <v>294.02</v>
       </c>
       <c r="O57" t="n">
-        <v>326.81</v>
+        <v>326.92</v>
       </c>
       <c r="P57" t="n">
         <v>1.63</v>
       </c>
       <c r="Q57" t="n">
-        <v>79.58</v>
+        <v>79.72</v>
       </c>
       <c r="R57" t="n">
-        <v>10.38</v>
+        <v>10.42</v>
       </c>
       <c r="S57" t="n">
-        <v>-1.25</v>
+        <v>-1.21</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6831,55 +6831,55 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>115.25</v>
+        <v>115.38</v>
       </c>
       <c r="D58" t="n">
         <v>92</v>
       </c>
       <c r="E58" t="n">
-        <v>11.68</v>
+        <v>11.8</v>
       </c>
       <c r="F58" t="n">
-        <v>38.84</v>
+        <v>39</v>
       </c>
       <c r="G58" t="n">
-        <v>69.26000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="H58" t="n">
-        <v>28.79</v>
+        <v>28.97</v>
       </c>
       <c r="I58" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="J58" t="n">
         <v>6.18</v>
       </c>
       <c r="K58" t="n">
-        <v>5.37</v>
+        <v>5.36</v>
       </c>
       <c r="L58" t="n">
-        <v>113.09</v>
+        <v>113.22</v>
       </c>
       <c r="M58" t="n">
-        <v>116.18</v>
+        <v>116.31</v>
       </c>
       <c r="N58" t="n">
-        <v>106.9</v>
+        <v>107.03</v>
       </c>
       <c r="O58" t="n">
-        <v>128.85</v>
+        <v>128.98</v>
       </c>
       <c r="P58" t="n">
         <v>1.63</v>
       </c>
       <c r="Q58" t="n">
-        <v>66.70999999999999</v>
+        <v>66.88</v>
       </c>
       <c r="R58" t="n">
-        <v>13.73</v>
+        <v>13.86</v>
       </c>
       <c r="S58" t="n">
-        <v>-3.23</v>
+        <v>-3.12</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -6944,55 +6944,55 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>109.51</v>
+        <v>109.68</v>
       </c>
       <c r="D59" t="n">
         <v>84</v>
       </c>
       <c r="E59" t="n">
-        <v>-12.34</v>
+        <v>-12.2</v>
       </c>
       <c r="F59" t="n">
-        <v>59.87</v>
+        <v>60.11</v>
       </c>
       <c r="G59" t="n">
-        <v>145.43</v>
+        <v>145.8</v>
       </c>
       <c r="H59" t="n">
-        <v>49.82</v>
+        <v>50.08</v>
       </c>
       <c r="I59" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="J59" t="n">
         <v>9.119999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>8.33</v>
+        <v>8.32</v>
       </c>
       <c r="L59" t="n">
-        <v>106.32</v>
+        <v>106.48</v>
       </c>
       <c r="M59" t="n">
-        <v>110.88</v>
+        <v>111.04</v>
       </c>
       <c r="N59" t="n">
-        <v>97.2</v>
+        <v>97.36</v>
       </c>
       <c r="O59" t="n">
-        <v>129.58</v>
+        <v>129.74</v>
       </c>
       <c r="P59" t="n">
         <v>1.63</v>
       </c>
       <c r="Q59" t="n">
-        <v>65.26000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="R59" t="n">
-        <v>12.19</v>
+        <v>12.35</v>
       </c>
       <c r="S59" t="n">
-        <v>-17.51</v>
+        <v>-17.38</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7057,22 +7057,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>433.7</v>
+        <v>434.4</v>
       </c>
       <c r="D60" t="n">
         <v>84</v>
       </c>
       <c r="E60" t="n">
-        <v>-4.72</v>
+        <v>-4.57</v>
       </c>
       <c r="F60" t="n">
-        <v>55.79</v>
+        <v>56.04</v>
       </c>
       <c r="G60" t="n">
-        <v>113.26</v>
+        <v>113.6</v>
       </c>
       <c r="H60" t="n">
-        <v>45.74</v>
+        <v>46.01</v>
       </c>
       <c r="I60" t="n">
         <v>0.36</v>
@@ -7081,31 +7081,31 @@
         <v>27.56</v>
       </c>
       <c r="K60" t="n">
-        <v>6.35</v>
+        <v>6.34</v>
       </c>
       <c r="L60" t="n">
-        <v>424.05</v>
+        <v>424.75</v>
       </c>
       <c r="M60" t="n">
-        <v>437.83</v>
+        <v>438.53</v>
       </c>
       <c r="N60" t="n">
-        <v>396.49</v>
+        <v>397.19</v>
       </c>
       <c r="O60" t="n">
-        <v>494.33</v>
+        <v>495.03</v>
       </c>
       <c r="P60" t="n">
         <v>1.63</v>
       </c>
       <c r="Q60" t="n">
-        <v>70.27</v>
+        <v>70.47</v>
       </c>
       <c r="R60" t="n">
-        <v>16.53</v>
+        <v>16.7</v>
       </c>
       <c r="S60" t="n">
-        <v>-7.57</v>
+        <v>-7.42</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7176,19 +7176,19 @@
         <v>96</v>
       </c>
       <c r="E61" t="n">
-        <v>10.64</v>
+        <v>10.63</v>
       </c>
       <c r="F61" t="n">
-        <v>9.07</v>
+        <v>9.06</v>
       </c>
       <c r="G61" t="n">
-        <v>14.4</v>
+        <v>14.39</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.98</v>
+        <v>-0.97</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="J61" t="n">
         <v>1.97</v>
@@ -7200,25 +7200,25 @@
         <v>57.98</v>
       </c>
       <c r="M61" t="n">
-        <v>58.97</v>
+        <v>58.96</v>
       </c>
       <c r="N61" t="n">
         <v>56.01</v>
       </c>
       <c r="O61" t="n">
-        <v>63</v>
+        <v>62.99</v>
       </c>
       <c r="P61" t="n">
         <v>1.63</v>
       </c>
       <c r="Q61" t="n">
-        <v>53.47</v>
+        <v>53.46</v>
       </c>
       <c r="R61" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="S61" t="n">
-        <v>-3.49</v>
+        <v>-3.5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>XLE 7.27% · CL=F 19.89%</t>
+          <t>XLE 7.22% · CL=F 20.0%</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.27% · CL=F 19.89%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.22% · CL=F 20.0%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7279,55 +7279,55 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>742.66</v>
+        <v>742.85</v>
       </c>
       <c r="D62" t="n">
         <v>74</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.53</v>
       </c>
       <c r="F62" t="n">
-        <v>63.2</v>
+        <v>63.24</v>
       </c>
       <c r="G62" t="n">
-        <v>78.02</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>53.15</v>
+        <v>53.21</v>
       </c>
       <c r="I62" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="J62" t="n">
         <v>53.45</v>
       </c>
       <c r="K62" t="n">
-        <v>7.2</v>
+        <v>7.19</v>
       </c>
       <c r="L62" t="n">
-        <v>723.95</v>
+        <v>724.15</v>
       </c>
       <c r="M62" t="n">
-        <v>750.6799999999999</v>
+        <v>750.87</v>
       </c>
       <c r="N62" t="n">
-        <v>670.51</v>
+        <v>670.7</v>
       </c>
       <c r="O62" t="n">
-        <v>860.24</v>
+        <v>860.4299999999999</v>
       </c>
       <c r="P62" t="n">
         <v>1.63</v>
       </c>
       <c r="Q62" t="n">
-        <v>72.69</v>
+        <v>72.72</v>
       </c>
       <c r="R62" t="n">
-        <v>22.44</v>
+        <v>22.47</v>
       </c>
       <c r="S62" t="n">
-        <v>-9.279999999999999</v>
+        <v>-9.26</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -7388,22 +7388,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>204.04</v>
+        <v>205.12</v>
       </c>
       <c r="D63" t="n">
         <v>64</v>
       </c>
       <c r="E63" t="n">
-        <v>-6.87</v>
+        <v>-6.38</v>
       </c>
       <c r="F63" t="n">
-        <v>49.81</v>
+        <v>50.6</v>
       </c>
       <c r="G63" t="n">
-        <v>45.36</v>
+        <v>46.13</v>
       </c>
       <c r="H63" t="n">
-        <v>39.76</v>
+        <v>40.57</v>
       </c>
       <c r="I63" t="n">
         <v>0.48</v>
@@ -7412,31 +7412,31 @@
         <v>18.68</v>
       </c>
       <c r="K63" t="n">
-        <v>9.15</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>197.5</v>
+        <v>198.58</v>
       </c>
       <c r="M63" t="n">
-        <v>206.84</v>
+        <v>207.92</v>
       </c>
       <c r="N63" t="n">
-        <v>178.82</v>
+        <v>179.9</v>
       </c>
       <c r="O63" t="n">
-        <v>245.13</v>
+        <v>246.21</v>
       </c>
       <c r="P63" t="n">
         <v>1.63</v>
       </c>
       <c r="Q63" t="n">
-        <v>67.09</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="R63" t="n">
-        <v>15.31</v>
+        <v>15.88</v>
       </c>
       <c r="S63" t="n">
-        <v>-17.69</v>
+        <v>-17.26</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>SOXX 24.1% · QQQ 10.05%</t>
+          <t>SOXX 24.32% · QQQ 10.03%</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.1% · QQQ 10.05%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector acompaña: SOXX 24.32% · QQQ 10.03%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7497,25 +7497,25 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>178.24</v>
+        <v>178.02</v>
       </c>
       <c r="D64" t="n">
         <v>96</v>
       </c>
       <c r="E64" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="F64" t="n">
-        <v>15.48</v>
+        <v>15.34</v>
       </c>
       <c r="G64" t="n">
-        <v>27.28</v>
+        <v>27.12</v>
       </c>
       <c r="H64" t="n">
-        <v>5.43</v>
+        <v>5.31</v>
       </c>
       <c r="I64" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="J64" t="n">
         <v>3.76</v>
@@ -7524,28 +7524,28 @@
         <v>2.11</v>
       </c>
       <c r="L64" t="n">
-        <v>176.92</v>
+        <v>176.7</v>
       </c>
       <c r="M64" t="n">
-        <v>178.8</v>
+        <v>178.58</v>
       </c>
       <c r="N64" t="n">
-        <v>173.16</v>
+        <v>172.94</v>
       </c>
       <c r="O64" t="n">
-        <v>186.51</v>
+        <v>186.29</v>
       </c>
       <c r="P64" t="n">
         <v>1.63</v>
       </c>
       <c r="Q64" t="n">
-        <v>77.90000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="R64" t="n">
-        <v>7.6</v>
+        <v>7.48</v>
       </c>
       <c r="S64" t="n">
-        <v>-1.1</v>
+        <v>-1.22</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -7601,64 +7601,64 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>VGT</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Tecnología</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>302.69</v>
+        <v>114.51</v>
       </c>
       <c r="D65" t="n">
         <v>96</v>
       </c>
       <c r="E65" t="n">
-        <v>3.29</v>
+        <v>1.84</v>
       </c>
       <c r="F65" t="n">
-        <v>12.12</v>
+        <v>13.72</v>
       </c>
       <c r="G65" t="n">
-        <v>16.27</v>
+        <v>24.83</v>
       </c>
       <c r="H65" t="n">
-        <v>2.07</v>
+        <v>3.69</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="J65" t="n">
-        <v>6.66</v>
+        <v>2.27</v>
       </c>
       <c r="K65" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="L65" t="n">
-        <v>300.36</v>
+        <v>113.71</v>
       </c>
       <c r="M65" t="n">
-        <v>303.69</v>
+        <v>114.85</v>
       </c>
       <c r="N65" t="n">
-        <v>293.7</v>
+        <v>111.44</v>
       </c>
       <c r="O65" t="n">
-        <v>317.35</v>
+        <v>119.51</v>
       </c>
       <c r="P65" t="n">
         <v>1.63</v>
       </c>
       <c r="Q65" t="n">
-        <v>89.06</v>
+        <v>78.61</v>
       </c>
       <c r="R65" t="n">
-        <v>7.54</v>
+        <v>6.94</v>
       </c>
       <c r="S65" t="n">
-        <v>-0.17</v>
+        <v>-0.96</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -7702,76 +7702,76 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo; Algo extendida sobre MA20</t>
+          <t>RSI sobrecomprado; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VGT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ETF Tecnología</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>114.6</v>
+        <v>302.52</v>
       </c>
       <c r="D66" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E66" t="n">
-        <v>1.92</v>
+        <v>3.23</v>
       </c>
       <c r="F66" t="n">
-        <v>13.8</v>
+        <v>12.05</v>
       </c>
       <c r="G66" t="n">
-        <v>24.92</v>
+        <v>16.2</v>
       </c>
       <c r="H66" t="n">
-        <v>3.75</v>
+        <v>2.02</v>
       </c>
       <c r="I66" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="J66" t="n">
-        <v>2.27</v>
+        <v>6.66</v>
       </c>
       <c r="K66" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="L66" t="n">
-        <v>113.8</v>
+        <v>300.19</v>
       </c>
       <c r="M66" t="n">
-        <v>114.94</v>
+        <v>303.52</v>
       </c>
       <c r="N66" t="n">
-        <v>111.53</v>
+        <v>293.53</v>
       </c>
       <c r="O66" t="n">
-        <v>119.59</v>
+        <v>317.18</v>
       </c>
       <c r="P66" t="n">
         <v>1.63</v>
       </c>
       <c r="Q66" t="n">
-        <v>78.98</v>
+        <v>89.02</v>
       </c>
       <c r="R66" t="n">
-        <v>7.02</v>
+        <v>7.48</v>
       </c>
       <c r="S66" t="n">
-        <v>-0.89</v>
+        <v>-0.22</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7836,55 +7836,55 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>122.96</v>
+        <v>122.92</v>
       </c>
       <c r="D67" t="n">
         <v>85</v>
       </c>
       <c r="E67" t="n">
-        <v>7.79</v>
+        <v>7.76</v>
       </c>
       <c r="F67" t="n">
-        <v>50.24</v>
+        <v>50.2</v>
       </c>
       <c r="G67" t="n">
-        <v>50.56</v>
+        <v>50.51</v>
       </c>
       <c r="H67" t="n">
-        <v>40.19</v>
+        <v>40.17</v>
       </c>
       <c r="I67" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>5.01</v>
       </c>
       <c r="K67" t="n">
         <v>4.07</v>
       </c>
       <c r="L67" t="n">
-        <v>121.21</v>
+        <v>121.17</v>
       </c>
       <c r="M67" t="n">
-        <v>123.71</v>
+        <v>123.67</v>
       </c>
       <c r="N67" t="n">
-        <v>116.2</v>
+        <v>116.16</v>
       </c>
       <c r="O67" t="n">
-        <v>133.97</v>
+        <v>133.93</v>
       </c>
       <c r="P67" t="n">
         <v>1.63</v>
       </c>
       <c r="Q67" t="n">
-        <v>92.34999999999999</v>
+        <v>92.34</v>
       </c>
       <c r="R67" t="n">
-        <v>27.21</v>
+        <v>27.18</v>
       </c>
       <c r="S67" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -7949,22 +7949,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>398.05</v>
+        <v>397.41</v>
       </c>
       <c r="D68" t="n">
         <v>92</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.85</v>
       </c>
       <c r="F68" t="n">
-        <v>16.5</v>
+        <v>16.31</v>
       </c>
       <c r="G68" t="n">
-        <v>31.53</v>
+        <v>31.32</v>
       </c>
       <c r="H68" t="n">
-        <v>6.45</v>
+        <v>6.28</v>
       </c>
       <c r="I68" t="n">
         <v>0.4</v>
@@ -7973,31 +7973,31 @@
         <v>11.07</v>
       </c>
       <c r="K68" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="L68" t="n">
-        <v>394.17</v>
+        <v>393.53</v>
       </c>
       <c r="M68" t="n">
-        <v>399.71</v>
+        <v>399.07</v>
       </c>
       <c r="N68" t="n">
-        <v>383.1</v>
+        <v>382.46</v>
       </c>
       <c r="O68" t="n">
-        <v>422.41</v>
+        <v>421.77</v>
       </c>
       <c r="P68" t="n">
         <v>1.63</v>
       </c>
       <c r="Q68" t="n">
-        <v>76.55</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="R68" t="n">
-        <v>6.73</v>
+        <v>6.57</v>
       </c>
       <c r="S68" t="n">
-        <v>-1.4</v>
+        <v>-1.56</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8062,55 +8062,55 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>314.67</v>
+        <v>316.17</v>
       </c>
       <c r="D69" t="n">
         <v>81</v>
       </c>
       <c r="E69" t="n">
-        <v>5.08</v>
+        <v>5.57</v>
       </c>
       <c r="F69" t="n">
-        <v>19.48</v>
+        <v>20.04</v>
       </c>
       <c r="G69" t="n">
-        <v>-11.58</v>
+        <v>-11.16</v>
       </c>
       <c r="H69" t="n">
-        <v>9.43</v>
+        <v>10.01</v>
       </c>
       <c r="I69" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
-        <v>16.28</v>
+        <v>16.37</v>
       </c>
       <c r="K69" t="n">
-        <v>5.17</v>
+        <v>5.18</v>
       </c>
       <c r="L69" t="n">
-        <v>308.98</v>
+        <v>310.44</v>
       </c>
       <c r="M69" t="n">
-        <v>317.12</v>
+        <v>318.62</v>
       </c>
       <c r="N69" t="n">
-        <v>292.7</v>
+        <v>294.07</v>
       </c>
       <c r="O69" t="n">
-        <v>350.49</v>
+        <v>352.17</v>
       </c>
       <c r="P69" t="n">
         <v>1.63</v>
       </c>
       <c r="Q69" t="n">
-        <v>74.78</v>
+        <v>75.14</v>
       </c>
       <c r="R69" t="n">
-        <v>14.1</v>
+        <v>14.61</v>
       </c>
       <c r="S69" t="n">
-        <v>-0.8</v>
+        <v>-0.33</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8175,55 +8175,55 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>211.06</v>
+        <v>210.21</v>
       </c>
       <c r="D70" t="n">
         <v>71</v>
       </c>
       <c r="E70" t="n">
-        <v>5.45</v>
+        <v>5.02</v>
       </c>
       <c r="F70" t="n">
-        <v>66.7</v>
+        <v>66.03</v>
       </c>
       <c r="G70" t="n">
-        <v>75.01000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="H70" t="n">
-        <v>56.65</v>
+        <v>56</v>
       </c>
       <c r="I70" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J70" t="n">
         <v>11.94</v>
       </c>
       <c r="K70" t="n">
-        <v>5.66</v>
+        <v>5.68</v>
       </c>
       <c r="L70" t="n">
-        <v>206.88</v>
+        <v>206.03</v>
       </c>
       <c r="M70" t="n">
-        <v>212.85</v>
+        <v>212</v>
       </c>
       <c r="N70" t="n">
-        <v>194.94</v>
+        <v>194.09</v>
       </c>
       <c r="O70" t="n">
-        <v>237.32</v>
+        <v>236.47</v>
       </c>
       <c r="P70" t="n">
         <v>1.63</v>
       </c>
       <c r="Q70" t="n">
-        <v>89.25</v>
+        <v>89.16</v>
       </c>
       <c r="R70" t="n">
-        <v>33.33</v>
+        <v>32.83</v>
       </c>
       <c r="S70" t="n">
-        <v>-0.1</v>
+        <v>-0.51</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -8288,55 +8288,55 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>161.93</v>
+        <v>161.88</v>
       </c>
       <c r="D71" t="n">
         <v>63</v>
       </c>
       <c r="E71" t="n">
-        <v>6.44</v>
+        <v>6.41</v>
       </c>
       <c r="F71" t="n">
-        <v>20.23</v>
+        <v>20.19</v>
       </c>
       <c r="G71" t="n">
-        <v>-4.18</v>
+        <v>-4.21</v>
       </c>
       <c r="H71" t="n">
-        <v>10.18</v>
+        <v>10.16</v>
       </c>
       <c r="I71" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="J71" t="n">
-        <v>7.76</v>
+        <v>7.77</v>
       </c>
       <c r="K71" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="L71" t="n">
-        <v>159.21</v>
+        <v>159.15</v>
       </c>
       <c r="M71" t="n">
-        <v>163.09</v>
+        <v>163.04</v>
       </c>
       <c r="N71" t="n">
-        <v>151.45</v>
+        <v>151.38</v>
       </c>
       <c r="O71" t="n">
-        <v>179</v>
+        <v>178.98</v>
       </c>
       <c r="P71" t="n">
         <v>1.63</v>
       </c>
       <c r="Q71" t="n">
-        <v>73.73999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="R71" t="n">
-        <v>13.58</v>
+        <v>13.54</v>
       </c>
       <c r="S71" t="n">
-        <v>-0.14</v>
+        <v>-0.28</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MACD positivo; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8401,55 +8401,55 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>244.92</v>
+        <v>244.88</v>
       </c>
       <c r="D72" t="n">
         <v>69</v>
       </c>
       <c r="E72" t="n">
-        <v>17.82</v>
+        <v>17.8</v>
       </c>
       <c r="F72" t="n">
-        <v>45.92</v>
+        <v>45.89</v>
       </c>
       <c r="G72" t="n">
-        <v>62.21</v>
+        <v>62.18</v>
       </c>
       <c r="H72" t="n">
-        <v>35.87</v>
+        <v>35.86</v>
       </c>
       <c r="I72" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="J72" t="n">
-        <v>9.449999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="K72" t="n">
         <v>3.86</v>
       </c>
       <c r="L72" t="n">
-        <v>241.61</v>
+        <v>241.57</v>
       </c>
       <c r="M72" t="n">
-        <v>246.34</v>
+        <v>246.3</v>
       </c>
       <c r="N72" t="n">
-        <v>232.16</v>
+        <v>232.11</v>
       </c>
       <c r="O72" t="n">
-        <v>265.72</v>
+        <v>265.69</v>
       </c>
       <c r="P72" t="n">
         <v>1.63</v>
       </c>
       <c r="Q72" t="n">
-        <v>93.05</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="R72" t="n">
-        <v>26.24</v>
+        <v>26.22</v>
       </c>
       <c r="S72" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -8510,25 +8510,25 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>595.85</v>
+        <v>595.33</v>
       </c>
       <c r="D73" t="n">
         <v>65</v>
       </c>
       <c r="E73" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="F73" t="n">
-        <v>40.55</v>
+        <v>40.42</v>
       </c>
       <c r="G73" t="n">
-        <v>41.15</v>
+        <v>41.03</v>
       </c>
       <c r="H73" t="n">
-        <v>30.5</v>
+        <v>30.39</v>
       </c>
       <c r="I73" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="J73" t="n">
         <v>22.7</v>
@@ -8537,28 +8537,28 @@
         <v>3.81</v>
       </c>
       <c r="L73" t="n">
-        <v>587.9</v>
+        <v>587.38</v>
       </c>
       <c r="M73" t="n">
-        <v>599.26</v>
+        <v>598.73</v>
       </c>
       <c r="N73" t="n">
-        <v>565.2</v>
+        <v>564.67</v>
       </c>
       <c r="O73" t="n">
-        <v>645.8</v>
+        <v>645.27</v>
       </c>
       <c r="P73" t="n">
         <v>1.63</v>
       </c>
       <c r="Q73" t="n">
-        <v>89.98</v>
+        <v>89.95</v>
       </c>
       <c r="R73" t="n">
-        <v>21.84</v>
+        <v>21.74</v>
       </c>
       <c r="S73" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; MACD positivo</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -8619,22 +8619,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>392.49</v>
+        <v>392.08</v>
       </c>
       <c r="D74" t="n">
         <v>96</v>
       </c>
       <c r="E74" t="n">
-        <v>3.29</v>
+        <v>3.18</v>
       </c>
       <c r="F74" t="n">
-        <v>20.9</v>
+        <v>20.78</v>
       </c>
       <c r="G74" t="n">
-        <v>36.43</v>
+        <v>36.28</v>
       </c>
       <c r="H74" t="n">
-        <v>10.85</v>
+        <v>10.75</v>
       </c>
       <c r="I74" t="n">
         <v>0.46</v>
@@ -8643,31 +8643,31 @@
         <v>9</v>
       </c>
       <c r="K74" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="L74" t="n">
-        <v>389.34</v>
+        <v>388.93</v>
       </c>
       <c r="M74" t="n">
-        <v>393.84</v>
+        <v>393.43</v>
       </c>
       <c r="N74" t="n">
-        <v>380.34</v>
+        <v>379.93</v>
       </c>
       <c r="O74" t="n">
-        <v>412.29</v>
+        <v>411.88</v>
       </c>
       <c r="P74" t="n">
         <v>1.63</v>
       </c>
       <c r="Q74" t="n">
-        <v>75.95</v>
+        <v>75.53</v>
       </c>
       <c r="R74" t="n">
-        <v>6.23</v>
+        <v>6.13</v>
       </c>
       <c r="S74" t="n">
-        <v>-2.89</v>
+        <v>-2.99</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8732,19 +8732,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1000.52</v>
+        <v>1000.36</v>
       </c>
       <c r="D75" t="n">
         <v>90</v>
       </c>
       <c r="E75" t="n">
-        <v>5.49</v>
+        <v>5.47</v>
       </c>
       <c r="F75" t="n">
-        <v>7.93</v>
+        <v>7.91</v>
       </c>
       <c r="G75" t="n">
-        <v>-2.22</v>
+        <v>-2.23</v>
       </c>
       <c r="H75" t="n">
         <v>-2.12</v>
@@ -8759,28 +8759,28 @@
         <v>3.24</v>
       </c>
       <c r="L75" t="n">
-        <v>989.1799999999999</v>
+        <v>989.02</v>
       </c>
       <c r="M75" t="n">
-        <v>1005.38</v>
+        <v>1005.23</v>
       </c>
       <c r="N75" t="n">
-        <v>956.77</v>
+        <v>956.61</v>
       </c>
       <c r="O75" t="n">
-        <v>1071.82</v>
+        <v>1071.66</v>
       </c>
       <c r="P75" t="n">
         <v>1.63</v>
       </c>
       <c r="Q75" t="n">
-        <v>72.87</v>
+        <v>72.83</v>
       </c>
       <c r="R75" t="n">
-        <v>5.96</v>
+        <v>5.95</v>
       </c>
       <c r="S75" t="n">
-        <v>-2.18</v>
+        <v>-2.2</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8841,55 +8841,55 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>23.46</v>
+        <v>23.58</v>
       </c>
       <c r="D76" t="n">
         <v>84</v>
       </c>
       <c r="E76" t="n">
-        <v>-2.57</v>
+        <v>-2.08</v>
       </c>
       <c r="F76" t="n">
-        <v>29.54</v>
+        <v>30.2</v>
       </c>
       <c r="G76" t="n">
-        <v>44.64</v>
+        <v>45.38</v>
       </c>
       <c r="H76" t="n">
-        <v>19.49</v>
+        <v>20.17</v>
       </c>
       <c r="I76" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J76" t="n">
         <v>1.67</v>
       </c>
       <c r="K76" t="n">
-        <v>7.1</v>
+        <v>7.06</v>
       </c>
       <c r="L76" t="n">
-        <v>22.88</v>
+        <v>23</v>
       </c>
       <c r="M76" t="n">
-        <v>23.71</v>
+        <v>23.83</v>
       </c>
       <c r="N76" t="n">
-        <v>21.21</v>
+        <v>21.33</v>
       </c>
       <c r="O76" t="n">
-        <v>27.12</v>
+        <v>27.24</v>
       </c>
       <c r="P76" t="n">
         <v>1.63</v>
       </c>
       <c r="Q76" t="n">
-        <v>67.95999999999999</v>
+        <v>68.53</v>
       </c>
       <c r="R76" t="n">
-        <v>14.12</v>
+        <v>14.67</v>
       </c>
       <c r="S76" t="n">
-        <v>-9.279999999999999</v>
+        <v>-8.82</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>BTC-USD 2.36% · ETH-USD -3.9%</t>
+          <t>BTC-USD 2.36% · ETH-USD -3.88%</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
@@ -8950,55 +8950,55 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>87.31999999999999</v>
+        <v>87.38</v>
       </c>
       <c r="D77" t="n">
         <v>84</v>
       </c>
       <c r="E77" t="n">
-        <v>3.44</v>
+        <v>3.51</v>
       </c>
       <c r="F77" t="n">
-        <v>6.87</v>
+        <v>6.94</v>
       </c>
       <c r="G77" t="n">
-        <v>18.14</v>
+        <v>18.22</v>
       </c>
       <c r="H77" t="n">
-        <v>-3.18</v>
+        <v>-3.09</v>
       </c>
       <c r="I77" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>2.56</v>
       </c>
       <c r="K77" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="L77" t="n">
-        <v>86.42</v>
+        <v>86.48</v>
       </c>
       <c r="M77" t="n">
-        <v>87.7</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="N77" t="n">
-        <v>83.86</v>
+        <v>83.92</v>
       </c>
       <c r="O77" t="n">
-        <v>92.95999999999999</v>
+        <v>93.02</v>
       </c>
       <c r="P77" t="n">
         <v>1.63</v>
       </c>
       <c r="Q77" t="n">
-        <v>74.29000000000001</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="R77" t="n">
-        <v>6.84</v>
+        <v>6.91</v>
       </c>
       <c r="S77" t="n">
-        <v>-1.27</v>
+        <v>-1.2</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9059,22 +9059,22 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>106.21</v>
+        <v>106.18</v>
       </c>
       <c r="D78" t="n">
         <v>84</v>
       </c>
       <c r="E78" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="F78" t="n">
-        <v>6.21</v>
+        <v>6.18</v>
       </c>
       <c r="G78" t="n">
-        <v>10.86</v>
+        <v>10.84</v>
       </c>
       <c r="H78" t="n">
-        <v>-3.84</v>
+        <v>-3.85</v>
       </c>
       <c r="I78" t="n">
         <v>0.44</v>
@@ -9086,28 +9086,28 @@
         <v>2.85</v>
       </c>
       <c r="L78" t="n">
-        <v>105.15</v>
+        <v>105.12</v>
       </c>
       <c r="M78" t="n">
-        <v>106.66</v>
+        <v>106.63</v>
       </c>
       <c r="N78" t="n">
-        <v>102.12</v>
+        <v>102.09</v>
       </c>
       <c r="O78" t="n">
-        <v>112.87</v>
+        <v>112.84</v>
       </c>
       <c r="P78" t="n">
         <v>1.63</v>
       </c>
       <c r="Q78" t="n">
-        <v>73.34999999999999</v>
+        <v>73.25</v>
       </c>
       <c r="R78" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="S78" t="n">
-        <v>-2.46</v>
+        <v>-2.48</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9168,25 +9168,25 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>713.98</v>
+        <v>713.41</v>
       </c>
       <c r="D79" t="n">
         <v>82</v>
       </c>
       <c r="E79" t="n">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
       <c r="F79" t="n">
-        <v>10.04</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>18.46</v>
+        <v>18.37</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J79" t="n">
         <v>10.65</v>
@@ -9195,28 +9195,28 @@
         <v>1.49</v>
       </c>
       <c r="L79" t="n">
-        <v>710.26</v>
+        <v>709.6900000000001</v>
       </c>
       <c r="M79" t="n">
-        <v>715.58</v>
+        <v>715.01</v>
       </c>
       <c r="N79" t="n">
-        <v>699.61</v>
+        <v>699.04</v>
       </c>
       <c r="O79" t="n">
-        <v>737.42</v>
+        <v>736.85</v>
       </c>
       <c r="P79" t="n">
         <v>1.63</v>
       </c>
       <c r="Q79" t="n">
-        <v>77.33</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="R79" t="n">
-        <v>4.9</v>
+        <v>4.82</v>
       </c>
       <c r="S79" t="n">
-        <v>-1.11</v>
+        <v>-1.19</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9277,22 +9277,22 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>682.78</v>
+        <v>682.35</v>
       </c>
       <c r="D80" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="F80" t="n">
-        <v>4.6</v>
+        <v>4.53</v>
       </c>
       <c r="G80" t="n">
-        <v>8.800000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="H80" t="n">
-        <v>-5.45</v>
+        <v>-5.5</v>
       </c>
       <c r="I80" t="n">
         <v>0.75</v>
@@ -9304,28 +9304,28 @@
         <v>0.97</v>
       </c>
       <c r="L80" t="n">
-        <v>680.47</v>
+        <v>680.04</v>
       </c>
       <c r="M80" t="n">
-        <v>683.78</v>
+        <v>683.34</v>
       </c>
       <c r="N80" t="n">
-        <v>673.86</v>
+        <v>673.42</v>
       </c>
       <c r="O80" t="n">
-        <v>697.33</v>
+        <v>696.89</v>
       </c>
       <c r="P80" t="n">
         <v>1.63</v>
       </c>
       <c r="Q80" t="n">
-        <v>74.11</v>
+        <v>73.5</v>
       </c>
       <c r="R80" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="S80" t="n">
-        <v>-0.92</v>
+        <v>-0.98</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo; Débil vs QQQ</t>
+          <t>RSI sobrecomprado; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -9386,25 +9386,25 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>742.66</v>
+        <v>742.28</v>
       </c>
       <c r="D81" t="n">
         <v>72</v>
       </c>
       <c r="E81" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="F81" t="n">
-        <v>4.58</v>
+        <v>4.53</v>
       </c>
       <c r="G81" t="n">
-        <v>8.800000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="H81" t="n">
-        <v>-5.47</v>
+        <v>-5.5</v>
       </c>
       <c r="I81" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="J81" t="n">
         <v>7.2</v>
@@ -9413,28 +9413,28 @@
         <v>0.97</v>
       </c>
       <c r="L81" t="n">
-        <v>740.14</v>
+        <v>739.76</v>
       </c>
       <c r="M81" t="n">
-        <v>743.74</v>
+        <v>743.36</v>
       </c>
       <c r="N81" t="n">
-        <v>732.9299999999999</v>
+        <v>732.5599999999999</v>
       </c>
       <c r="O81" t="n">
-        <v>758.5</v>
+        <v>758.13</v>
       </c>
       <c r="P81" t="n">
         <v>1.63</v>
       </c>
       <c r="Q81" t="n">
-        <v>73.81</v>
+        <v>73.33</v>
       </c>
       <c r="R81" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="S81" t="n">
-        <v>-0.92</v>
+        <v>-0.97</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9495,22 +9495,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>241.9</v>
+        <v>241.88</v>
       </c>
       <c r="D82" t="n">
         <v>33</v>
       </c>
       <c r="E82" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="F82" t="n">
-        <v>-3.43</v>
+        <v>-3.44</v>
       </c>
       <c r="G82" t="n">
-        <v>7.2</v>
+        <v>7.18</v>
       </c>
       <c r="H82" t="n">
-        <v>-13.48</v>
+        <v>-13.47</v>
       </c>
       <c r="I82" t="n">
         <v>0.55</v>
@@ -9522,28 +9522,28 @@
         <v>3.43</v>
       </c>
       <c r="L82" t="n">
-        <v>239</v>
+        <v>238.97</v>
       </c>
       <c r="M82" t="n">
-        <v>243.15</v>
+        <v>243.13</v>
       </c>
       <c r="N82" t="n">
-        <v>230.69</v>
+        <v>230.67</v>
       </c>
       <c r="O82" t="n">
-        <v>260.18</v>
+        <v>260.15</v>
       </c>
       <c r="P82" t="n">
         <v>1.63</v>
       </c>
       <c r="Q82" t="n">
-        <v>37.59</v>
+        <v>37.56</v>
       </c>
       <c r="R82" t="n">
-        <v>-5.37</v>
+        <v>-5.38</v>
       </c>
       <c r="S82" t="n">
-        <v>-11.97</v>
+        <v>-11.98</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>XLE 7.27% · CL=F 19.89%</t>
+          <t>XLE 7.22% · CL=F 20.0%</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector acompaña: XLE 7.27% · CL=F 19.89%; Tendencia larga positiva; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector acompaña: XLE 7.22% · CL=F 20.0%; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9604,22 +9604,22 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>145.12</v>
+        <v>145.24</v>
       </c>
       <c r="D83" t="n">
         <v>46</v>
       </c>
       <c r="E83" t="n">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="F83" t="n">
-        <v>-11.63</v>
+        <v>-11.57</v>
       </c>
       <c r="G83" t="n">
-        <v>5.75</v>
+        <v>5.83</v>
       </c>
       <c r="H83" t="n">
-        <v>-21.68</v>
+        <v>-21.6</v>
       </c>
       <c r="I83" t="n">
         <v>0.43</v>
@@ -9631,28 +9631,28 @@
         <v>5.93</v>
       </c>
       <c r="L83" t="n">
-        <v>142.11</v>
+        <v>142.22</v>
       </c>
       <c r="M83" t="n">
-        <v>146.42</v>
+        <v>146.53</v>
       </c>
       <c r="N83" t="n">
-        <v>133.5</v>
+        <v>133.61</v>
       </c>
       <c r="O83" t="n">
-        <v>164.06</v>
+        <v>164.17</v>
       </c>
       <c r="P83" t="n">
         <v>1.63</v>
       </c>
       <c r="Q83" t="n">
-        <v>30.09</v>
+        <v>30.14</v>
       </c>
       <c r="R83" t="n">
-        <v>-9.43</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="S83" t="n">
-        <v>-19.29</v>
+        <v>-19.22</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9717,7 +9717,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>619.3</v>
+        <v>619.3099999999999</v>
       </c>
       <c r="D84" t="n">
         <v>35</v>
@@ -9732,10 +9732,10 @@
         <v>-3.87</v>
       </c>
       <c r="H84" t="n">
-        <v>-20.11</v>
+        <v>-20.09</v>
       </c>
       <c r="I84" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J84" t="n">
         <v>17.16</v>
@@ -9744,13 +9744,13 @@
         <v>2.77</v>
       </c>
       <c r="L84" t="n">
-        <v>613.29</v>
+        <v>613.3</v>
       </c>
       <c r="M84" t="n">
-        <v>621.87</v>
+        <v>621.88</v>
       </c>
       <c r="N84" t="n">
-        <v>596.13</v>
+        <v>596.14</v>
       </c>
       <c r="O84" t="n">
         <v>657.0599999999999</v>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MA20 sobre MA50; MACD mejorando; Momentum 5D sano</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MA20 sobre MA50; MACD mejorando; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -9830,55 +9830,55 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8.779999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="D85" t="n">
         <v>36</v>
       </c>
       <c r="E85" t="n">
-        <v>-10.99</v>
+        <v>-11.6</v>
       </c>
       <c r="F85" t="n">
-        <v>-4.92</v>
+        <v>-5.57</v>
       </c>
       <c r="G85" t="n">
-        <v>-17.9</v>
+        <v>-18.46</v>
       </c>
       <c r="H85" t="n">
-        <v>-14.97</v>
+        <v>-15.6</v>
       </c>
       <c r="I85" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="J85" t="n">
         <v>0.45</v>
       </c>
       <c r="K85" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="L85" t="n">
-        <v>8.630000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="M85" t="n">
-        <v>8.85</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="N85" t="n">
-        <v>8.18</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="O85" t="n">
-        <v>9.779999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="P85" t="n">
         <v>1.64</v>
       </c>
       <c r="Q85" t="n">
-        <v>49.92</v>
+        <v>49.02</v>
       </c>
       <c r="R85" t="n">
-        <v>-3.55</v>
+        <v>-4.18</v>
       </c>
       <c r="S85" t="n">
-        <v>-11.08</v>
+        <v>-11.69</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -9939,25 +9939,25 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>74.91</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="D86" t="n">
         <v>29</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.72</v>
+        <v>-0.65</v>
       </c>
       <c r="F86" t="n">
-        <v>-2.87</v>
+        <v>-2.8</v>
       </c>
       <c r="G86" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="H86" t="n">
-        <v>-12.92</v>
+        <v>-12.83</v>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="J86" t="n">
         <v>2.62</v>
@@ -9966,28 +9966,28 @@
         <v>3.5</v>
       </c>
       <c r="L86" t="n">
-        <v>73.98999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="M86" t="n">
-        <v>75.3</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="N86" t="n">
-        <v>71.37</v>
+        <v>71.42</v>
       </c>
       <c r="O86" t="n">
-        <v>80.67</v>
+        <v>80.72</v>
       </c>
       <c r="P86" t="n">
         <v>1.63</v>
       </c>
       <c r="Q86" t="n">
-        <v>46.24</v>
+        <v>46.39</v>
       </c>
       <c r="R86" t="n">
-        <v>-0.73</v>
+        <v>-0.67</v>
       </c>
       <c r="S86" t="n">
-        <v>-7.32</v>
+        <v>-7.26</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MA20 sobre MA50</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -10048,25 +10048,25 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>75.56999999999999</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="D87" t="n">
         <v>26</v>
       </c>
       <c r="E87" t="n">
-        <v>-4.48</v>
+        <v>-4.56</v>
       </c>
       <c r="F87" t="n">
-        <v>-4.61</v>
+        <v>-4.69</v>
       </c>
       <c r="G87" t="n">
-        <v>4.62</v>
+        <v>4.53</v>
       </c>
       <c r="H87" t="n">
-        <v>-14.66</v>
+        <v>-14.72</v>
       </c>
       <c r="I87" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="J87" t="n">
         <v>2.47</v>
@@ -10075,28 +10075,28 @@
         <v>3.27</v>
       </c>
       <c r="L87" t="n">
-        <v>74.70999999999999</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="M87" t="n">
-        <v>75.95</v>
+        <v>75.89</v>
       </c>
       <c r="N87" t="n">
-        <v>72.23999999999999</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="O87" t="n">
-        <v>81</v>
+        <v>80.94</v>
       </c>
       <c r="P87" t="n">
         <v>1.63</v>
       </c>
       <c r="Q87" t="n">
-        <v>47.63</v>
+        <v>47.49</v>
       </c>
       <c r="R87" t="n">
-        <v>-2.4</v>
+        <v>-2.47</v>
       </c>
       <c r="S87" t="n">
-        <v>-6.33</v>
+        <v>-6.41</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MA20 sobre MA50</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MA20 sobre MA50</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -10157,22 +10157,22 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>135.21</v>
+        <v>135.06</v>
       </c>
       <c r="D88" t="n">
         <v>22</v>
       </c>
       <c r="E88" t="n">
-        <v>-1.88</v>
+        <v>-1.99</v>
       </c>
       <c r="F88" t="n">
-        <v>-7.64</v>
+        <v>-7.74</v>
       </c>
       <c r="G88" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="H88" t="n">
-        <v>-17.69</v>
+        <v>-17.77</v>
       </c>
       <c r="I88" t="n">
         <v>0.48</v>
@@ -10181,31 +10181,31 @@
         <v>5.71</v>
       </c>
       <c r="K88" t="n">
-        <v>4.22</v>
+        <v>4.23</v>
       </c>
       <c r="L88" t="n">
-        <v>133.21</v>
+        <v>133.06</v>
       </c>
       <c r="M88" t="n">
-        <v>136.07</v>
+        <v>135.92</v>
       </c>
       <c r="N88" t="n">
-        <v>127.5</v>
+        <v>127.35</v>
       </c>
       <c r="O88" t="n">
-        <v>147.77</v>
+        <v>147.62</v>
       </c>
       <c r="P88" t="n">
         <v>1.63</v>
       </c>
       <c r="Q88" t="n">
-        <v>40.68</v>
+        <v>40.47</v>
       </c>
       <c r="R88" t="n">
-        <v>-3.32</v>
+        <v>-3.42</v>
       </c>
       <c r="S88" t="n">
-        <v>-11.44</v>
+        <v>-11.54</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -10266,22 +10266,22 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>175.74</v>
+        <v>175.68</v>
       </c>
       <c r="D89" t="n">
         <v>15</v>
       </c>
       <c r="E89" t="n">
-        <v>-3.34</v>
+        <v>-3.38</v>
       </c>
       <c r="F89" t="n">
-        <v>-3.51</v>
+        <v>-3.55</v>
       </c>
       <c r="G89" t="n">
-        <v>-4.92</v>
+        <v>-4.95</v>
       </c>
       <c r="H89" t="n">
-        <v>-13.56</v>
+        <v>-13.58</v>
       </c>
       <c r="I89" t="n">
         <v>0.6</v>
@@ -10293,28 +10293,28 @@
         <v>3.93</v>
       </c>
       <c r="L89" t="n">
-        <v>173.32</v>
+        <v>173.26</v>
       </c>
       <c r="M89" t="n">
-        <v>176.78</v>
+        <v>176.72</v>
       </c>
       <c r="N89" t="n">
-        <v>166.41</v>
+        <v>166.35</v>
       </c>
       <c r="O89" t="n">
-        <v>190.94</v>
+        <v>190.88</v>
       </c>
       <c r="P89" t="n">
         <v>1.63</v>
       </c>
       <c r="Q89" t="n">
-        <v>46.16</v>
+        <v>46.1</v>
       </c>
       <c r="R89" t="n">
-        <v>-2.3</v>
+        <v>-2.33</v>
       </c>
       <c r="S89" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.24</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -10375,22 +10375,22 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>220.01</v>
+        <v>220.27</v>
       </c>
       <c r="D90" t="n">
         <v>15</v>
       </c>
       <c r="E90" t="n">
-        <v>-4.24</v>
+        <v>-4.13</v>
       </c>
       <c r="F90" t="n">
-        <v>-12.56</v>
+        <v>-12.46</v>
       </c>
       <c r="G90" t="n">
-        <v>-13.52</v>
+        <v>-13.42</v>
       </c>
       <c r="H90" t="n">
-        <v>-22.61</v>
+        <v>-22.49</v>
       </c>
       <c r="I90" t="n">
         <v>0.46</v>
@@ -10399,31 +10399,31 @@
         <v>5.6</v>
       </c>
       <c r="K90" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="L90" t="n">
-        <v>218.05</v>
+        <v>218.31</v>
       </c>
       <c r="M90" t="n">
-        <v>220.85</v>
+        <v>221.11</v>
       </c>
       <c r="N90" t="n">
-        <v>212.45</v>
+        <v>212.71</v>
       </c>
       <c r="O90" t="n">
-        <v>232.33</v>
+        <v>232.59</v>
       </c>
       <c r="P90" t="n">
         <v>1.63</v>
       </c>
       <c r="Q90" t="n">
-        <v>43.43</v>
+        <v>43.73</v>
       </c>
       <c r="R90" t="n">
-        <v>-4.19</v>
+        <v>-4.08</v>
       </c>
       <c r="S90" t="n">
-        <v>-14.26</v>
+        <v>-14.16</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -10484,55 +10484,55 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>167.69</v>
+        <v>167.41</v>
       </c>
       <c r="D91" t="n">
         <v>15</v>
       </c>
       <c r="E91" t="n">
-        <v>-7.06</v>
+        <v>-7.21</v>
       </c>
       <c r="F91" t="n">
-        <v>-15.16</v>
+        <v>-15.3</v>
       </c>
       <c r="G91" t="n">
-        <v>-21.32</v>
+        <v>-21.46</v>
       </c>
       <c r="H91" t="n">
-        <v>-25.21</v>
+        <v>-25.33</v>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="J91" t="n">
         <v>6.81</v>
       </c>
       <c r="K91" t="n">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
       <c r="L91" t="n">
-        <v>165.31</v>
+        <v>165.03</v>
       </c>
       <c r="M91" t="n">
-        <v>168.71</v>
+        <v>168.43</v>
       </c>
       <c r="N91" t="n">
-        <v>158.5</v>
+        <v>158.22</v>
       </c>
       <c r="O91" t="n">
-        <v>182.67</v>
+        <v>182.39</v>
       </c>
       <c r="P91" t="n">
         <v>1.63</v>
       </c>
       <c r="Q91" t="n">
-        <v>40.02</v>
+        <v>39.65</v>
       </c>
       <c r="R91" t="n">
-        <v>-5.73</v>
+        <v>-5.88</v>
       </c>
       <c r="S91" t="n">
-        <v>-15.98</v>
+        <v>-16.12</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -10593,25 +10593,25 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>87.2</v>
+        <v>87.05</v>
       </c>
       <c r="D92" t="n">
         <v>14</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.33</v>
+        <v>-0.5</v>
       </c>
       <c r="F92" t="n">
-        <v>-10.39</v>
+        <v>-10.54</v>
       </c>
       <c r="G92" t="n">
-        <v>13.25</v>
+        <v>13.05</v>
       </c>
       <c r="H92" t="n">
-        <v>-20.44</v>
+        <v>-20.57</v>
       </c>
       <c r="I92" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>2.35</v>
@@ -10620,28 +10620,28 @@
         <v>2.7</v>
       </c>
       <c r="L92" t="n">
-        <v>86.38</v>
+        <v>86.23</v>
       </c>
       <c r="M92" t="n">
-        <v>87.56</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="N92" t="n">
-        <v>84.03</v>
+        <v>83.87</v>
       </c>
       <c r="O92" t="n">
-        <v>92.38</v>
+        <v>92.23</v>
       </c>
       <c r="P92" t="n">
         <v>1.63</v>
       </c>
       <c r="Q92" t="n">
-        <v>35.79</v>
+        <v>35.1</v>
       </c>
       <c r="R92" t="n">
-        <v>-3.38</v>
+        <v>-3.54</v>
       </c>
       <c r="S92" t="n">
-        <v>-10.65</v>
+        <v>-10.81</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -10702,55 +10702,55 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>20.84</v>
+        <v>20.81</v>
       </c>
       <c r="D93" t="n">
         <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>-7.25</v>
+        <v>-7.41</v>
       </c>
       <c r="G93" t="n">
-        <v>-17.43</v>
+        <v>-17.57</v>
       </c>
       <c r="H93" t="n">
-        <v>-17.3</v>
+        <v>-17.44</v>
       </c>
       <c r="I93" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>1.25</v>
       </c>
       <c r="K93" t="n">
-        <v>5.99</v>
+        <v>6</v>
       </c>
       <c r="L93" t="n">
-        <v>20.4</v>
+        <v>20.37</v>
       </c>
       <c r="M93" t="n">
-        <v>21.03</v>
+        <v>20.99</v>
       </c>
       <c r="N93" t="n">
-        <v>19.16</v>
+        <v>19.12</v>
       </c>
       <c r="O93" t="n">
-        <v>23.59</v>
+        <v>23.55</v>
       </c>
       <c r="P93" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q93" t="n">
-        <v>35.52</v>
+        <v>35.23</v>
       </c>
       <c r="R93" t="n">
-        <v>-9.32</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="S93" t="n">
-        <v>-16.2</v>
+        <v>-16.34</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
@@ -10790,7 +10790,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -10811,25 +10811,25 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>111.11</v>
+        <v>111.08</v>
       </c>
       <c r="D94" t="n">
         <v>57</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="F94" t="n">
-        <v>-6.69</v>
+        <v>-6.71</v>
       </c>
       <c r="G94" t="n">
-        <v>-8.15</v>
+        <v>-8.17</v>
       </c>
       <c r="H94" t="n">
         <v>-16.74</v>
       </c>
       <c r="I94" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="J94" t="n">
         <v>2.66</v>
@@ -10838,28 +10838,28 @@
         <v>2.4</v>
       </c>
       <c r="L94" t="n">
-        <v>110.18</v>
+        <v>110.15</v>
       </c>
       <c r="M94" t="n">
-        <v>111.51</v>
+        <v>111.48</v>
       </c>
       <c r="N94" t="n">
-        <v>107.52</v>
+        <v>107.49</v>
       </c>
       <c r="O94" t="n">
-        <v>116.97</v>
+        <v>116.94</v>
       </c>
       <c r="P94" t="n">
         <v>1.63</v>
       </c>
       <c r="Q94" t="n">
-        <v>53.13</v>
+        <v>53.02</v>
       </c>
       <c r="R94" t="n">
-        <v>-1.09</v>
+        <v>-1.12</v>
       </c>
       <c r="S94" t="n">
-        <v>-6.91</v>
+        <v>-6.94</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10920,22 +10920,22 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>282.35</v>
+        <v>282.14</v>
       </c>
       <c r="D95" t="n">
         <v>35</v>
       </c>
       <c r="E95" t="n">
-        <v>-4.98</v>
+        <v>-5.05</v>
       </c>
       <c r="F95" t="n">
-        <v>-7.16</v>
+        <v>-7.23</v>
       </c>
       <c r="G95" t="n">
-        <v>-15.53</v>
+        <v>-15.59</v>
       </c>
       <c r="H95" t="n">
-        <v>-17.21</v>
+        <v>-17.26</v>
       </c>
       <c r="I95" t="n">
         <v>0.38</v>
@@ -10947,28 +10947,28 @@
         <v>3.42</v>
       </c>
       <c r="L95" t="n">
-        <v>278.97</v>
+        <v>278.77</v>
       </c>
       <c r="M95" t="n">
-        <v>283.8</v>
+        <v>283.59</v>
       </c>
       <c r="N95" t="n">
-        <v>269.32</v>
+        <v>269.11</v>
       </c>
       <c r="O95" t="n">
-        <v>303.59</v>
+        <v>303.39</v>
       </c>
       <c r="P95" t="n">
         <v>1.63</v>
       </c>
       <c r="Q95" t="n">
-        <v>48.65</v>
+        <v>48.53</v>
       </c>
       <c r="R95" t="n">
-        <v>-2.75</v>
+        <v>-2.82</v>
       </c>
       <c r="S95" t="n">
-        <v>-8.92</v>
+        <v>-8.99</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11029,22 +11029,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>70.68000000000001</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="D96" t="n">
         <v>33</v>
       </c>
       <c r="E96" t="n">
-        <v>-5.58</v>
+        <v>-5.49</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.82</v>
+        <v>-0.73</v>
       </c>
       <c r="G96" t="n">
-        <v>33.63</v>
+        <v>33.75</v>
       </c>
       <c r="H96" t="n">
-        <v>-10.87</v>
+        <v>-10.76</v>
       </c>
       <c r="I96" t="n">
         <v>0.35</v>
@@ -11053,31 +11053,31 @@
         <v>2.58</v>
       </c>
       <c r="K96" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="L96" t="n">
-        <v>69.77</v>
+        <v>69.84</v>
       </c>
       <c r="M96" t="n">
-        <v>71.06</v>
+        <v>71.13</v>
       </c>
       <c r="N96" t="n">
-        <v>67.19</v>
+        <v>67.25</v>
       </c>
       <c r="O96" t="n">
-        <v>76.36</v>
+        <v>76.42</v>
       </c>
       <c r="P96" t="n">
         <v>1.63</v>
       </c>
       <c r="Q96" t="n">
-        <v>48.36</v>
+        <v>48.53</v>
       </c>
       <c r="R96" t="n">
-        <v>-1.05</v>
+        <v>-0.97</v>
       </c>
       <c r="S96" t="n">
-        <v>-8.4</v>
+        <v>-8.32</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11150,13 +11150,13 @@
         <v>-6.19</v>
       </c>
       <c r="G97" t="n">
-        <v>7.32</v>
+        <v>7.31</v>
       </c>
       <c r="H97" t="n">
-        <v>-16.24</v>
+        <v>-16.22</v>
       </c>
       <c r="I97" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="J97" t="n">
         <v>3.31</v>
@@ -11168,7 +11168,7 @@
         <v>122.26</v>
       </c>
       <c r="M97" t="n">
-        <v>123.92</v>
+        <v>123.91</v>
       </c>
       <c r="N97" t="n">
         <v>118.95</v>
@@ -11180,13 +11180,13 @@
         <v>1.63</v>
       </c>
       <c r="Q97" t="n">
-        <v>34.79</v>
+        <v>34.78</v>
       </c>
       <c r="R97" t="n">
         <v>-3.05</v>
       </c>
       <c r="S97" t="n">
-        <v>-8.34</v>
+        <v>-8.35</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>-1.4</v>
       </c>
       <c r="H98" t="n">
-        <v>-12.48</v>
+        <v>-12.46</v>
       </c>
       <c r="I98" t="n">
         <v>0.47</v>
@@ -11356,55 +11356,55 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>84.52</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="D99" t="n">
         <v>26</v>
       </c>
       <c r="E99" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="F99" t="n">
-        <v>-12.69</v>
+        <v>-12.76</v>
       </c>
       <c r="G99" t="n">
-        <v>-24.19</v>
+        <v>-24.25</v>
       </c>
       <c r="H99" t="n">
-        <v>-22.74</v>
+        <v>-22.79</v>
       </c>
       <c r="I99" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="J99" t="n">
         <v>2.07</v>
       </c>
       <c r="K99" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="L99" t="n">
-        <v>83.8</v>
+        <v>83.73</v>
       </c>
       <c r="M99" t="n">
-        <v>84.83</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="N99" t="n">
-        <v>81.73</v>
+        <v>81.67</v>
       </c>
       <c r="O99" t="n">
-        <v>89.06999999999999</v>
+        <v>89</v>
       </c>
       <c r="P99" t="n">
         <v>1.63</v>
       </c>
       <c r="Q99" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="R99" t="n">
-        <v>-4.75</v>
+        <v>-4.82</v>
       </c>
       <c r="S99" t="n">
-        <v>-13.15</v>
+        <v>-13.22</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11465,25 +11465,25 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>45</v>
+        <v>44.96</v>
       </c>
       <c r="D100" t="n">
         <v>24</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.82</v>
+        <v>-0.9</v>
       </c>
       <c r="F100" t="n">
-        <v>-11.43</v>
+        <v>-11.51</v>
       </c>
       <c r="G100" t="n">
-        <v>8.16</v>
+        <v>8.07</v>
       </c>
       <c r="H100" t="n">
-        <v>-21.48</v>
+        <v>-21.54</v>
       </c>
       <c r="I100" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J100" t="n">
         <v>1.51</v>
@@ -11492,28 +11492,28 @@
         <v>3.36</v>
       </c>
       <c r="L100" t="n">
-        <v>44.47</v>
+        <v>44.43</v>
       </c>
       <c r="M100" t="n">
-        <v>45.23</v>
+        <v>45.19</v>
       </c>
       <c r="N100" t="n">
-        <v>42.96</v>
+        <v>42.92</v>
       </c>
       <c r="O100" t="n">
-        <v>48.33</v>
+        <v>48.29</v>
       </c>
       <c r="P100" t="n">
         <v>1.63</v>
       </c>
       <c r="Q100" t="n">
-        <v>22.62</v>
+        <v>22.51</v>
       </c>
       <c r="R100" t="n">
-        <v>-6.76</v>
+        <v>-6.84</v>
       </c>
       <c r="S100" t="n">
-        <v>-13.96</v>
+        <v>-14.03</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11574,55 +11574,55 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>222.63</v>
+        <v>222.35</v>
       </c>
       <c r="D101" t="n">
         <v>23</v>
       </c>
       <c r="E101" t="n">
-        <v>-6.21</v>
+        <v>-6.32</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.34</v>
+        <v>-0.46</v>
       </c>
       <c r="G101" t="n">
-        <v>-4.74</v>
+        <v>-4.86</v>
       </c>
       <c r="H101" t="n">
-        <v>-10.39</v>
+        <v>-10.49</v>
       </c>
       <c r="I101" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="J101" t="n">
         <v>7.22</v>
       </c>
       <c r="K101" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="L101" t="n">
-        <v>220.1</v>
+        <v>219.82</v>
       </c>
       <c r="M101" t="n">
-        <v>223.71</v>
+        <v>223.43</v>
       </c>
       <c r="N101" t="n">
-        <v>212.88</v>
+        <v>212.6</v>
       </c>
       <c r="O101" t="n">
-        <v>238.51</v>
+        <v>238.23</v>
       </c>
       <c r="P101" t="n">
         <v>1.63</v>
       </c>
       <c r="Q101" t="n">
-        <v>42.73</v>
+        <v>42.53</v>
       </c>
       <c r="R101" t="n">
-        <v>-3.12</v>
+        <v>-3.24</v>
       </c>
       <c r="S101" t="n">
-        <v>-8.779999999999999</v>
+        <v>-8.9</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11683,22 +11683,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>77.73</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="D102" t="n">
         <v>22</v>
       </c>
       <c r="E102" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="F102" t="n">
-        <v>-14.35</v>
+        <v>-14.31</v>
       </c>
       <c r="G102" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="H102" t="n">
-        <v>-24.4</v>
+        <v>-24.34</v>
       </c>
       <c r="I102" t="n">
         <v>0.45</v>
@@ -11710,28 +11710,28 @@
         <v>5.72</v>
       </c>
       <c r="L102" t="n">
-        <v>76.17</v>
+        <v>76.2</v>
       </c>
       <c r="M102" t="n">
-        <v>78.40000000000001</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="N102" t="n">
-        <v>71.73</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="O102" t="n">
-        <v>87.51000000000001</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="P102" t="n">
         <v>1.63</v>
       </c>
       <c r="Q102" t="n">
-        <v>41.99</v>
+        <v>42.02</v>
       </c>
       <c r="R102" t="n">
-        <v>-2.74</v>
+        <v>-2.7</v>
       </c>
       <c r="S102" t="n">
-        <v>-15.86</v>
+        <v>-15.83</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11792,55 +11792,55 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>556.34</v>
+        <v>556.09</v>
       </c>
       <c r="D103" t="n">
         <v>21</v>
       </c>
       <c r="E103" t="n">
-        <v>-3.22</v>
+        <v>-3.26</v>
       </c>
       <c r="F103" t="n">
-        <v>-5.78</v>
+        <v>-5.82</v>
       </c>
       <c r="G103" t="n">
-        <v>-15.71</v>
+        <v>-15.75</v>
       </c>
       <c r="H103" t="n">
-        <v>-15.83</v>
+        <v>-15.85</v>
       </c>
       <c r="I103" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J103" t="n">
         <v>14.99</v>
       </c>
       <c r="K103" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="L103" t="n">
-        <v>551.09</v>
+        <v>550.85</v>
       </c>
       <c r="M103" t="n">
-        <v>558.59</v>
+        <v>558.34</v>
       </c>
       <c r="N103" t="n">
-        <v>536.1</v>
+        <v>535.86</v>
       </c>
       <c r="O103" t="n">
-        <v>589.3200000000001</v>
+        <v>589.0700000000001</v>
       </c>
       <c r="P103" t="n">
         <v>1.63</v>
       </c>
       <c r="Q103" t="n">
-        <v>45.76</v>
+        <v>45.67</v>
       </c>
       <c r="R103" t="n">
-        <v>-3.8</v>
+        <v>-3.84</v>
       </c>
       <c r="S103" t="n">
-        <v>-7.07</v>
+        <v>-7.11</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11916,10 +11916,10 @@
         <v>-4.12</v>
       </c>
       <c r="H104" t="n">
-        <v>-16.61</v>
+        <v>-16.59</v>
       </c>
       <c r="I104" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="J104" t="n">
         <v>0.54</v>
@@ -12010,22 +12010,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>496.3</v>
+        <v>496.11</v>
       </c>
       <c r="D105" t="n">
         <v>19</v>
       </c>
       <c r="E105" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="F105" t="n">
-        <v>-4.8</v>
+        <v>-4.83</v>
       </c>
       <c r="G105" t="n">
-        <v>-4.44</v>
+        <v>-4.48</v>
       </c>
       <c r="H105" t="n">
-        <v>-14.85</v>
+        <v>-14.86</v>
       </c>
       <c r="I105" t="n">
         <v>0.46</v>
@@ -12037,28 +12037,28 @@
         <v>2.64</v>
       </c>
       <c r="L105" t="n">
-        <v>491.71</v>
+        <v>491.52</v>
       </c>
       <c r="M105" t="n">
-        <v>498.27</v>
+        <v>498.08</v>
       </c>
       <c r="N105" t="n">
-        <v>478.61</v>
+        <v>478.42</v>
       </c>
       <c r="O105" t="n">
-        <v>525.13</v>
+        <v>524.9400000000001</v>
       </c>
       <c r="P105" t="n">
         <v>1.63</v>
       </c>
       <c r="Q105" t="n">
-        <v>45.21</v>
+        <v>45.11</v>
       </c>
       <c r="R105" t="n">
-        <v>-1.2</v>
+        <v>-1.24</v>
       </c>
       <c r="S105" t="n">
-        <v>-7.1</v>
+        <v>-7.13</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12119,22 +12119,22 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>297.81</v>
+        <v>297.84</v>
       </c>
       <c r="D106" t="n">
         <v>18</v>
       </c>
       <c r="E106" t="n">
-        <v>-1.42</v>
+        <v>-1.41</v>
       </c>
       <c r="F106" t="n">
-        <v>-4.02</v>
+        <v>-4.01</v>
       </c>
       <c r="G106" t="n">
-        <v>-2.83</v>
+        <v>-2.82</v>
       </c>
       <c r="H106" t="n">
-        <v>-14.07</v>
+        <v>-14.04</v>
       </c>
       <c r="I106" t="n">
         <v>0.49</v>
@@ -12146,28 +12146,28 @@
         <v>2.04</v>
       </c>
       <c r="L106" t="n">
-        <v>295.68</v>
+        <v>295.71</v>
       </c>
       <c r="M106" t="n">
-        <v>298.72</v>
+        <v>298.75</v>
       </c>
       <c r="N106" t="n">
-        <v>289.61</v>
+        <v>289.64</v>
       </c>
       <c r="O106" t="n">
-        <v>311.18</v>
+        <v>311.21</v>
       </c>
       <c r="P106" t="n">
         <v>1.63</v>
       </c>
       <c r="Q106" t="n">
-        <v>34.99</v>
+        <v>35.01</v>
       </c>
       <c r="R106" t="n">
-        <v>-3.37</v>
+        <v>-3.36</v>
       </c>
       <c r="S106" t="n">
-        <v>-7</v>
+        <v>-6.99</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12228,25 +12228,25 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>49.49</v>
+        <v>49.43</v>
       </c>
       <c r="D107" t="n">
         <v>11</v>
       </c>
       <c r="E107" t="n">
-        <v>-3.56</v>
+        <v>-3.66</v>
       </c>
       <c r="F107" t="n">
-        <v>-8.210000000000001</v>
+        <v>-8.31</v>
       </c>
       <c r="G107" t="n">
-        <v>-5.7</v>
+        <v>-5.8</v>
       </c>
       <c r="H107" t="n">
-        <v>-18.26</v>
+        <v>-18.34</v>
       </c>
       <c r="I107" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J107" t="n">
         <v>1.17</v>
@@ -12255,28 +12255,28 @@
         <v>2.36</v>
       </c>
       <c r="L107" t="n">
-        <v>49.08</v>
+        <v>49.02</v>
       </c>
       <c r="M107" t="n">
-        <v>49.66</v>
+        <v>49.6</v>
       </c>
       <c r="N107" t="n">
-        <v>47.91</v>
+        <v>47.86</v>
       </c>
       <c r="O107" t="n">
-        <v>52.05</v>
+        <v>52</v>
       </c>
       <c r="P107" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q107" t="n">
-        <v>30.6</v>
+        <v>30.39</v>
       </c>
       <c r="R107" t="n">
-        <v>-5.15</v>
+        <v>-5.25</v>
       </c>
       <c r="S107" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12337,25 +12337,25 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>276.12</v>
+        <v>276.09</v>
       </c>
       <c r="D108" t="n">
         <v>11</v>
       </c>
       <c r="E108" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F108" t="n">
-        <v>-11.32</v>
+        <v>-11.33</v>
       </c>
       <c r="G108" t="n">
-        <v>-15.12</v>
+        <v>-15.13</v>
       </c>
       <c r="H108" t="n">
-        <v>-21.37</v>
+        <v>-21.36</v>
       </c>
       <c r="I108" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="J108" t="n">
         <v>5.55</v>
@@ -12364,28 +12364,28 @@
         <v>2.01</v>
       </c>
       <c r="L108" t="n">
-        <v>274.18</v>
+        <v>274.15</v>
       </c>
       <c r="M108" t="n">
-        <v>276.95</v>
+        <v>276.92</v>
       </c>
       <c r="N108" t="n">
-        <v>268.63</v>
+        <v>268.6</v>
       </c>
       <c r="O108" t="n">
-        <v>288.32</v>
+        <v>288.29</v>
       </c>
       <c r="P108" t="n">
         <v>1.63</v>
       </c>
       <c r="Q108" t="n">
-        <v>28.06</v>
+        <v>27.99</v>
       </c>
       <c r="R108" t="n">
-        <v>-4</v>
+        <v>-4.01</v>
       </c>
       <c r="S108" t="n">
-        <v>-11.65</v>
+        <v>-11.66</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12446,22 +12446,22 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>15.81</v>
+        <v>15.8</v>
       </c>
       <c r="D109" t="n">
         <v>11</v>
       </c>
       <c r="E109" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="F109" t="n">
-        <v>-18.63</v>
+        <v>-18.68</v>
       </c>
       <c r="G109" t="n">
-        <v>-18.08</v>
+        <v>-18.13</v>
       </c>
       <c r="H109" t="n">
-        <v>-28.68</v>
+        <v>-28.71</v>
       </c>
       <c r="I109" t="n">
         <v>0.49</v>
@@ -12470,31 +12470,31 @@
         <v>0.82</v>
       </c>
       <c r="K109" t="n">
-        <v>5.16</v>
+        <v>5.17</v>
       </c>
       <c r="L109" t="n">
-        <v>15.52</v>
+        <v>15.51</v>
       </c>
       <c r="M109" t="n">
-        <v>15.93</v>
+        <v>15.92</v>
       </c>
       <c r="N109" t="n">
-        <v>14.71</v>
+        <v>14.7</v>
       </c>
       <c r="O109" t="n">
-        <v>17.61</v>
+        <v>17.6</v>
       </c>
       <c r="P109" t="n">
         <v>1.64</v>
       </c>
       <c r="Q109" t="n">
-        <v>30.99</v>
+        <v>30.95</v>
       </c>
       <c r="R109" t="n">
-        <v>-6.7</v>
+        <v>-6.75</v>
       </c>
       <c r="S109" t="n">
-        <v>-20.03</v>
+        <v>-20.08</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12555,25 +12555,25 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>73.18000000000001</v>
+        <v>73.14</v>
       </c>
       <c r="D110" t="n">
         <v>4</v>
       </c>
       <c r="E110" t="n">
-        <v>-3.26</v>
+        <v>-3.3</v>
       </c>
       <c r="F110" t="n">
-        <v>-9.6</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>-15.96</v>
+        <v>-16</v>
       </c>
       <c r="H110" t="n">
-        <v>-19.65</v>
+        <v>-19.67</v>
       </c>
       <c r="I110" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="J110" t="n">
         <v>1.9</v>
@@ -12582,28 +12582,28 @@
         <v>2.6</v>
       </c>
       <c r="L110" t="n">
-        <v>72.51000000000001</v>
+        <v>72.48</v>
       </c>
       <c r="M110" t="n">
-        <v>73.45999999999999</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="N110" t="n">
-        <v>70.61</v>
+        <v>70.58</v>
       </c>
       <c r="O110" t="n">
-        <v>77.36</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="P110" t="n">
         <v>1.63</v>
       </c>
       <c r="Q110" t="n">
-        <v>28.92</v>
+        <v>28.87</v>
       </c>
       <c r="R110" t="n">
-        <v>-6.65</v>
+        <v>-6.69</v>
       </c>
       <c r="S110" t="n">
-        <v>-11.44</v>
+        <v>-11.48</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12664,25 +12664,25 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>219.77</v>
+        <v>219.76</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>-4.11</v>
+        <v>-4.12</v>
       </c>
       <c r="F111" t="n">
-        <v>-12.27</v>
+        <v>-12.28</v>
       </c>
       <c r="G111" t="n">
         <v>-20.62</v>
       </c>
       <c r="H111" t="n">
-        <v>-22.32</v>
+        <v>-22.31</v>
       </c>
       <c r="I111" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J111" t="n">
         <v>6.07</v>
@@ -12691,25 +12691,25 @@
         <v>2.76</v>
       </c>
       <c r="L111" t="n">
-        <v>217.65</v>
+        <v>217.63</v>
       </c>
       <c r="M111" t="n">
-        <v>220.69</v>
+        <v>220.67</v>
       </c>
       <c r="N111" t="n">
-        <v>211.58</v>
+        <v>211.56</v>
       </c>
       <c r="O111" t="n">
-        <v>233.13</v>
+        <v>233.12</v>
       </c>
       <c r="P111" t="n">
         <v>1.63</v>
       </c>
       <c r="Q111" t="n">
-        <v>30.69</v>
+        <v>30.68</v>
       </c>
       <c r="R111" t="n">
-        <v>-6.15</v>
+        <v>-6.16</v>
       </c>
       <c r="S111" t="n">
         <v>-14.11</v>
@@ -12773,55 +12773,55 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>299.08</v>
+        <v>298.72</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>-5.79</v>
+        <v>-5.9</v>
       </c>
       <c r="F112" t="n">
-        <v>-14.4</v>
+        <v>-14.5</v>
       </c>
       <c r="G112" t="n">
-        <v>-20.47</v>
+        <v>-20.57</v>
       </c>
       <c r="H112" t="n">
-        <v>-24.45</v>
+        <v>-24.53</v>
       </c>
       <c r="I112" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="J112" t="n">
         <v>7.81</v>
       </c>
       <c r="K112" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="L112" t="n">
-        <v>296.35</v>
+        <v>295.99</v>
       </c>
       <c r="M112" t="n">
-        <v>300.25</v>
+        <v>299.89</v>
       </c>
       <c r="N112" t="n">
-        <v>288.53</v>
+        <v>288.17</v>
       </c>
       <c r="O112" t="n">
-        <v>316.27</v>
+        <v>315.91</v>
       </c>
       <c r="P112" t="n">
         <v>1.63</v>
       </c>
       <c r="Q112" t="n">
-        <v>26.29</v>
+        <v>26.16</v>
       </c>
       <c r="R112" t="n">
-        <v>-7.49</v>
+        <v>-7.6</v>
       </c>
       <c r="S112" t="n">
-        <v>-15.41</v>
+        <v>-15.51</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12882,22 +12882,22 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>441.76</v>
+        <v>441.63</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>-5</v>
+        <v>-5.03</v>
       </c>
       <c r="F113" t="n">
-        <v>-16.11</v>
+        <v>-16.14</v>
       </c>
       <c r="G113" t="n">
-        <v>-14.16</v>
+        <v>-14.18</v>
       </c>
       <c r="H113" t="n">
-        <v>-26.16</v>
+        <v>-26.17</v>
       </c>
       <c r="I113" t="n">
         <v>0.46</v>
@@ -12909,28 +12909,28 @@
         <v>3.1</v>
       </c>
       <c r="L113" t="n">
-        <v>436.97</v>
+        <v>436.84</v>
       </c>
       <c r="M113" t="n">
-        <v>443.81</v>
+        <v>443.68</v>
       </c>
       <c r="N113" t="n">
-        <v>423.27</v>
+        <v>423.14</v>
       </c>
       <c r="O113" t="n">
-        <v>471.89</v>
+        <v>471.76</v>
       </c>
       <c r="P113" t="n">
         <v>1.63</v>
       </c>
       <c r="Q113" t="n">
-        <v>36.53</v>
+        <v>36.48</v>
       </c>
       <c r="R113" t="n">
-        <v>-6.44</v>
+        <v>-6.47</v>
       </c>
       <c r="S113" t="n">
-        <v>-17.95</v>
+        <v>-17.98</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12991,59 +12991,59 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>157.63</v>
+        <v>200.24</v>
       </c>
       <c r="D114" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E114" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="F114" t="n">
-        <v>-3.76</v>
+        <v>-0.37</v>
       </c>
       <c r="G114" t="n">
-        <v>7.87</v>
+        <v>3.95</v>
       </c>
       <c r="H114" t="n">
-        <v>-13.81</v>
+        <v>-10.4</v>
       </c>
       <c r="I114" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="J114" t="n">
-        <v>10.03</v>
+        <v>15.31</v>
       </c>
       <c r="K114" t="n">
-        <v>6.36</v>
+        <v>7.65</v>
       </c>
       <c r="L114" t="n">
-        <v>154.12</v>
+        <v>194.88</v>
       </c>
       <c r="M114" t="n">
-        <v>159.14</v>
+        <v>202.54</v>
       </c>
       <c r="N114" t="n">
-        <v>144.09</v>
+        <v>179.57</v>
       </c>
       <c r="O114" t="n">
-        <v>179.7</v>
+        <v>233.93</v>
       </c>
       <c r="P114" t="n">
         <v>1.63</v>
       </c>
       <c r="Q114" t="n">
-        <v>48.14</v>
+        <v>45.95</v>
       </c>
       <c r="R114" t="n">
-        <v>-0.6</v>
+        <v>-5.34</v>
       </c>
       <c r="S114" t="n">
-        <v>-11.01</v>
+        <v>-22.65</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -13083,80 +13083,80 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MA20 sobre MA50; RSI saludable; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ; Lejos del máximo 20D</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>200.74</v>
+        <v>30.19</v>
       </c>
       <c r="D115" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E115" t="n">
-        <v>2.35</v>
+        <v>4.25</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.12</v>
+        <v>-12.67</v>
       </c>
       <c r="G115" t="n">
-        <v>4.2</v>
+        <v>-1.5</v>
       </c>
       <c r="H115" t="n">
-        <v>-10.17</v>
+        <v>-22.7</v>
       </c>
       <c r="I115" t="n">
-        <v>0.36</v>
+        <v>0.74</v>
       </c>
       <c r="J115" t="n">
-        <v>15.3</v>
+        <v>1.88</v>
       </c>
       <c r="K115" t="n">
-        <v>7.62</v>
+        <v>6.23</v>
       </c>
       <c r="L115" t="n">
-        <v>195.38</v>
+        <v>29.53</v>
       </c>
       <c r="M115" t="n">
-        <v>203.04</v>
+        <v>30.47</v>
       </c>
       <c r="N115" t="n">
-        <v>180.08</v>
+        <v>27.65</v>
       </c>
       <c r="O115" t="n">
-        <v>234.41</v>
+        <v>34.33</v>
       </c>
       <c r="P115" t="n">
         <v>1.63</v>
       </c>
       <c r="Q115" t="n">
-        <v>46.13</v>
+        <v>39.89</v>
       </c>
       <c r="R115" t="n">
-        <v>-5.11</v>
+        <v>-3.11</v>
       </c>
       <c r="S115" t="n">
-        <v>-22.46</v>
+        <v>-15.67</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>BAJA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
@@ -13196,80 +13196,80 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MA20 sobre MA50; MACD mejorando; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ; Lejos del máximo 20D</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>CHKP</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Ciberseguridad</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>30.36</v>
+        <v>123.99</v>
       </c>
       <c r="D116" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E116" t="n">
-        <v>4.85</v>
+        <v>7.88</v>
       </c>
       <c r="F116" t="n">
-        <v>-12.16</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.93</v>
+        <v>-22.04</v>
       </c>
       <c r="H116" t="n">
-        <v>-22.21</v>
+        <v>-19.15</v>
       </c>
       <c r="I116" t="n">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="J116" t="n">
-        <v>1.88</v>
+        <v>5.94</v>
       </c>
       <c r="K116" t="n">
-        <v>6.2</v>
+        <v>4.79</v>
       </c>
       <c r="L116" t="n">
-        <v>29.71</v>
+        <v>121.91</v>
       </c>
       <c r="M116" t="n">
-        <v>30.65</v>
+        <v>124.88</v>
       </c>
       <c r="N116" t="n">
-        <v>27.82</v>
+        <v>115.97</v>
       </c>
       <c r="O116" t="n">
-        <v>34.51</v>
+        <v>137.06</v>
       </c>
       <c r="P116" t="n">
         <v>1.63</v>
       </c>
       <c r="Q116" t="n">
-        <v>40.61</v>
+        <v>36.21</v>
       </c>
       <c r="R116" t="n">
-        <v>-2.58</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S116" t="n">
-        <v>-15.18</v>
+        <v>-12.95</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -13284,7 +13284,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -13309,76 +13309,76 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MA20 sobre MA50; MACD mejorando; Momentum 5D sano</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; Volumen bajo; Momentum 5D extendido</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CHKP</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ciberseguridad</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>124.05</v>
+        <v>8.52</v>
       </c>
       <c r="D117" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E117" t="n">
-        <v>7.94</v>
+        <v>-4</v>
       </c>
       <c r="F117" t="n">
-        <v>-9.07</v>
+        <v>5.51</v>
       </c>
       <c r="G117" t="n">
-        <v>-22.01</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H117" t="n">
-        <v>-19.12</v>
+        <v>-4.52</v>
       </c>
       <c r="I117" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="J117" t="n">
-        <v>5.94</v>
+        <v>0.65</v>
       </c>
       <c r="K117" t="n">
-        <v>4.79</v>
+        <v>7.67</v>
       </c>
       <c r="L117" t="n">
-        <v>121.97</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M117" t="n">
-        <v>124.94</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="N117" t="n">
-        <v>116.03</v>
+        <v>7.64</v>
       </c>
       <c r="O117" t="n">
-        <v>137.12</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="P117" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q117" t="n">
-        <v>36.29</v>
+        <v>53.48</v>
       </c>
       <c r="R117" t="n">
-        <v>-0.89</v>
+        <v>0.11</v>
       </c>
       <c r="S117" t="n">
-        <v>-12.9</v>
+        <v>-15.13</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -13405,11 +13405,7 @@
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
@@ -13422,80 +13418,80 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MACD positivo; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; Volumen bajo; Momentum 5D extendido</t>
+          <t>Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>8.550000000000001</v>
+        <v>157.13</v>
       </c>
       <c r="D118" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E118" t="n">
-        <v>-3.72</v>
+        <v>0.85</v>
       </c>
       <c r="F118" t="n">
-        <v>5.82</v>
+        <v>-4.07</v>
       </c>
       <c r="G118" t="n">
-        <v>9.199999999999999</v>
+        <v>7.53</v>
       </c>
       <c r="H118" t="n">
-        <v>-4.23</v>
+        <v>-14.1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="J118" t="n">
-        <v>0.65</v>
+        <v>10.03</v>
       </c>
       <c r="K118" t="n">
-        <v>7.65</v>
+        <v>6.38</v>
       </c>
       <c r="L118" t="n">
-        <v>8.32</v>
+        <v>153.62</v>
       </c>
       <c r="M118" t="n">
-        <v>8.65</v>
+        <v>158.63</v>
       </c>
       <c r="N118" t="n">
-        <v>7.67</v>
+        <v>143.59</v>
       </c>
       <c r="O118" t="n">
-        <v>9.99</v>
+        <v>179.2</v>
       </c>
       <c r="P118" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q118" t="n">
-        <v>53.7</v>
+        <v>47.76</v>
       </c>
       <c r="R118" t="n">
-        <v>0.39</v>
+        <v>-0.9</v>
       </c>
       <c r="S118" t="n">
-        <v>-14.88</v>
+        <v>-11.29</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>BAJA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -13510,7 +13506,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -13531,12 +13527,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MA20 sobre MA50; MACD mejorando</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -13552,55 +13548,55 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>101.28</v>
+        <v>101.19</v>
       </c>
       <c r="D119" t="n">
         <v>2</v>
       </c>
       <c r="E119" t="n">
-        <v>-8.27</v>
+        <v>-8.35</v>
       </c>
       <c r="F119" t="n">
-        <v>-22.78</v>
+        <v>-22.84</v>
       </c>
       <c r="G119" t="n">
-        <v>-18.19</v>
+        <v>-18.26</v>
       </c>
       <c r="H119" t="n">
-        <v>-32.83</v>
+        <v>-32.87</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J119" t="n">
         <v>6.34</v>
       </c>
       <c r="K119" t="n">
-        <v>6.26</v>
+        <v>6.27</v>
       </c>
       <c r="L119" t="n">
-        <v>99.06</v>
+        <v>98.97</v>
       </c>
       <c r="M119" t="n">
-        <v>102.23</v>
+        <v>102.14</v>
       </c>
       <c r="N119" t="n">
-        <v>92.72</v>
+        <v>92.63</v>
       </c>
       <c r="O119" t="n">
-        <v>115.23</v>
+        <v>115.14</v>
       </c>
       <c r="P119" t="n">
         <v>1.63</v>
       </c>
       <c r="Q119" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="R119" t="n">
-        <v>-12.84</v>
+        <v>-12.91</v>
       </c>
       <c r="S119" t="n">
-        <v>-26.23</v>
+        <v>-26.3</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13619,7 +13615,7 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
@@ -13640,7 +13636,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MACD mejorando</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MACD mejorando</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -13661,55 +13657,55 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>12.45</v>
+        <v>12.43</v>
       </c>
       <c r="D120" t="n">
         <v>57</v>
       </c>
       <c r="E120" t="n">
-        <v>-3.75</v>
+        <v>-3.94</v>
       </c>
       <c r="F120" t="n">
-        <v>7.37</v>
+        <v>7.16</v>
       </c>
       <c r="G120" t="n">
-        <v>56.47</v>
+        <v>56.16</v>
       </c>
       <c r="H120" t="n">
-        <v>-2.68</v>
+        <v>-2.87</v>
       </c>
       <c r="I120" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J120" t="n">
         <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>8.02</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="L120" t="n">
-        <v>12.11</v>
+        <v>12.08</v>
       </c>
       <c r="M120" t="n">
-        <v>12.6</v>
+        <v>12.58</v>
       </c>
       <c r="N120" t="n">
-        <v>11.11</v>
+        <v>11.08</v>
       </c>
       <c r="O120" t="n">
-        <v>14.65</v>
+        <v>14.63</v>
       </c>
       <c r="P120" t="n">
         <v>1.63</v>
       </c>
       <c r="Q120" t="n">
-        <v>59.21</v>
+        <v>58.99</v>
       </c>
       <c r="R120" t="n">
-        <v>3.03</v>
+        <v>2.83</v>
       </c>
       <c r="S120" t="n">
-        <v>-9.75</v>
+        <v>-9.93</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13728,7 +13724,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>BTC-USD 2.36% · ETH-USD -3.9%</t>
+          <t>BTC-USD 2.36% · ETH-USD -3.88%</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -13770,55 +13766,55 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>196.23</v>
+        <v>196.69</v>
       </c>
       <c r="D121" t="n">
         <v>55</v>
       </c>
       <c r="E121" t="n">
-        <v>-2.45</v>
+        <v>-2.22</v>
       </c>
       <c r="F121" t="n">
-        <v>-4.9</v>
+        <v>-4.67</v>
       </c>
       <c r="G121" t="n">
-        <v>18.25</v>
+        <v>18.53</v>
       </c>
       <c r="H121" t="n">
-        <v>-14.95</v>
+        <v>-14.7</v>
       </c>
       <c r="I121" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="J121" t="n">
         <v>14.49</v>
       </c>
       <c r="K121" t="n">
-        <v>7.38</v>
+        <v>7.37</v>
       </c>
       <c r="L121" t="n">
-        <v>191.15</v>
+        <v>191.62</v>
       </c>
       <c r="M121" t="n">
-        <v>198.4</v>
+        <v>198.86</v>
       </c>
       <c r="N121" t="n">
-        <v>176.67</v>
+        <v>177.13</v>
       </c>
       <c r="O121" t="n">
-        <v>228.1</v>
+        <v>228.56</v>
       </c>
       <c r="P121" t="n">
         <v>1.63</v>
       </c>
       <c r="Q121" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="R121" t="n">
-        <v>-1.65</v>
+        <v>-1.42</v>
       </c>
       <c r="S121" t="n">
-        <v>-11.75</v>
+        <v>-11.54</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13837,7 +13833,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>BTC-USD 2.36% · ETH-USD -3.9%</t>
+          <t>BTC-USD 2.36% · ETH-USD -3.88%</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -13879,22 +13875,22 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>176.68</v>
+        <v>176.83</v>
       </c>
       <c r="D122" t="n">
         <v>38</v>
       </c>
       <c r="E122" t="n">
-        <v>-5.81</v>
+        <v>-5.74</v>
       </c>
       <c r="F122" t="n">
-        <v>6.1</v>
+        <v>6.19</v>
       </c>
       <c r="G122" t="n">
-        <v>36.49</v>
+        <v>36.6</v>
       </c>
       <c r="H122" t="n">
-        <v>-3.95</v>
+        <v>-3.84</v>
       </c>
       <c r="I122" t="n">
         <v>0.71</v>
@@ -13903,31 +13899,31 @@
         <v>11.44</v>
       </c>
       <c r="K122" t="n">
-        <v>6.48</v>
+        <v>6.47</v>
       </c>
       <c r="L122" t="n">
-        <v>172.68</v>
+        <v>172.83</v>
       </c>
       <c r="M122" t="n">
-        <v>178.4</v>
+        <v>178.55</v>
       </c>
       <c r="N122" t="n">
-        <v>161.24</v>
+        <v>161.38</v>
       </c>
       <c r="O122" t="n">
-        <v>201.86</v>
+        <v>202</v>
       </c>
       <c r="P122" t="n">
         <v>1.63</v>
       </c>
       <c r="Q122" t="n">
-        <v>53.74</v>
+        <v>53.82</v>
       </c>
       <c r="R122" t="n">
-        <v>-0.19</v>
+        <v>-0.11</v>
       </c>
       <c r="S122" t="n">
-        <v>-10.31</v>
+        <v>-10.24</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13946,7 +13942,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>BTC-USD 2.36% · ETH-USD -3.9%</t>
+          <t>BTC-USD 2.36% · ETH-USD -3.88%</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -13988,22 +13984,22 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>20.82</v>
+        <v>20.67</v>
       </c>
       <c r="D123" t="n">
         <v>27</v>
       </c>
       <c r="E123" t="n">
-        <v>-7.77</v>
+        <v>-8.42</v>
       </c>
       <c r="F123" t="n">
-        <v>-4.03</v>
+        <v>-4.7</v>
       </c>
       <c r="G123" t="n">
-        <v>7.41</v>
+        <v>6.66</v>
       </c>
       <c r="H123" t="n">
-        <v>-14.08</v>
+        <v>-14.73</v>
       </c>
       <c r="I123" t="n">
         <v>0.53</v>
@@ -14012,31 +14008,31 @@
         <v>1.88</v>
       </c>
       <c r="K123" t="n">
-        <v>9.02</v>
+        <v>9.08</v>
       </c>
       <c r="L123" t="n">
-        <v>20.16</v>
+        <v>20.01</v>
       </c>
       <c r="M123" t="n">
-        <v>21.1</v>
+        <v>20.95</v>
       </c>
       <c r="N123" t="n">
-        <v>18.28</v>
+        <v>18.14</v>
       </c>
       <c r="O123" t="n">
-        <v>24.95</v>
+        <v>24.8</v>
       </c>
       <c r="P123" t="n">
         <v>1.63</v>
       </c>
       <c r="Q123" t="n">
-        <v>56.77</v>
+        <v>56.22</v>
       </c>
       <c r="R123" t="n">
-        <v>-0.55</v>
+        <v>-1.21</v>
       </c>
       <c r="S123" t="n">
-        <v>-16</v>
+        <v>-16.59</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14055,7 +14051,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -14076,7 +14072,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -14097,55 +14093,55 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>200.87</v>
+        <v>200.17</v>
       </c>
       <c r="D124" t="n">
         <v>20</v>
       </c>
       <c r="E124" t="n">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="F124" t="n">
-        <v>-9.720000000000001</v>
+        <v>-10.03</v>
       </c>
       <c r="G124" t="n">
-        <v>-16.09</v>
+        <v>-16.38</v>
       </c>
       <c r="H124" t="n">
-        <v>-19.77</v>
+        <v>-20.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="J124" t="n">
         <v>18.16</v>
       </c>
       <c r="K124" t="n">
-        <v>9.039999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="L124" t="n">
-        <v>194.51</v>
+        <v>193.82</v>
       </c>
       <c r="M124" t="n">
-        <v>203.59</v>
+        <v>202.89</v>
       </c>
       <c r="N124" t="n">
-        <v>176.35</v>
+        <v>175.66</v>
       </c>
       <c r="O124" t="n">
-        <v>240.81</v>
+        <v>240.11</v>
       </c>
       <c r="P124" t="n">
         <v>1.63</v>
       </c>
       <c r="Q124" t="n">
-        <v>41.4</v>
+        <v>41.11</v>
       </c>
       <c r="R124" t="n">
-        <v>-8.18</v>
+        <v>-8.48</v>
       </c>
       <c r="S124" t="n">
-        <v>-21.23</v>
+        <v>-21.5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14164,7 +14160,7 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>QQQ 10.05% · ARKK -4.53% · SPY 4.6%</t>
+          <t>QQQ 10.03% · ARKK -4.53% · SPY 4.57%</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
@@ -14185,7 +14181,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.05% · ARKK -4.53% · SPY 4.6%; MACD mejorando; Momentum 5D sano</t>
+          <t>Mercado ALCISTA; Sector ligeramente positivo: QQQ 10.03% · ARKK -4.53% · SPY 4.57%; MACD mejorando; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -14206,22 +14202,22 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>125.51</v>
+        <v>125.17</v>
       </c>
       <c r="D125" t="n">
         <v>59</v>
       </c>
       <c r="E125" t="n">
-        <v>19.01</v>
+        <v>18.68</v>
       </c>
       <c r="F125" t="n">
-        <v>48.01</v>
+        <v>47.61</v>
       </c>
       <c r="G125" t="n">
-        <v>63.9</v>
+        <v>63.45</v>
       </c>
       <c r="H125" t="n">
-        <v>37.96</v>
+        <v>37.58</v>
       </c>
       <c r="I125" t="n">
         <v>0.57</v>
@@ -14230,31 +14226,31 @@
         <v>9.65</v>
       </c>
       <c r="K125" t="n">
-        <v>7.69</v>
+        <v>7.71</v>
       </c>
       <c r="L125" t="n">
-        <v>122.14</v>
+        <v>121.79</v>
       </c>
       <c r="M125" t="n">
-        <v>126.96</v>
+        <v>126.62</v>
       </c>
       <c r="N125" t="n">
-        <v>112.49</v>
+        <v>112.15</v>
       </c>
       <c r="O125" t="n">
-        <v>146.74</v>
+        <v>146.39</v>
       </c>
       <c r="P125" t="n">
         <v>1.63</v>
       </c>
       <c r="Q125" t="n">
-        <v>73.89</v>
+        <v>73.61</v>
       </c>
       <c r="R125" t="n">
-        <v>33.92</v>
+        <v>33.57</v>
       </c>
       <c r="S125" t="n">
-        <v>-5.76</v>
+        <v>-6.01</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -575,22 +575,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43.03</v>
+        <v>43.15</v>
       </c>
       <c r="D2" t="n">
         <v>96</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="F2" t="n">
-        <v>12.8</v>
+        <v>13.11</v>
       </c>
       <c r="G2" t="n">
-        <v>22.71</v>
+        <v>23.04</v>
       </c>
       <c r="H2" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="I2" t="n">
         <v>0.39</v>
@@ -599,31 +599,31 @@
         <v>1.15</v>
       </c>
       <c r="K2" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="L2" t="n">
-        <v>42.63</v>
+        <v>42.75</v>
       </c>
       <c r="M2" t="n">
-        <v>43.21</v>
+        <v>43.32</v>
       </c>
       <c r="N2" t="n">
-        <v>41.48</v>
+        <v>41.6</v>
       </c>
       <c r="O2" t="n">
-        <v>45.56</v>
+        <v>45.68</v>
       </c>
       <c r="P2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>56.39</v>
+        <v>56.91</v>
       </c>
       <c r="R2" t="n">
-        <v>4.87</v>
+        <v>5.14</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.77</v>
+        <v>-0.51</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>XLE 9.61% · CL=F 12.07%</t>
+          <t>XLE 9.63% · CL=F 12.07%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.61% · CL=F 12.07%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.63% · CL=F 12.07%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -688,25 +688,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>207.51</v>
+        <v>207.26</v>
       </c>
       <c r="D3" t="n">
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3</v>
+        <v>5.17</v>
       </c>
       <c r="F3" t="n">
-        <v>9.93</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>20.76</v>
+        <v>20.61</v>
       </c>
       <c r="H3" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="I3" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="J3" t="n">
         <v>6.41</v>
@@ -715,28 +715,28 @@
         <v>3.09</v>
       </c>
       <c r="L3" t="n">
-        <v>205.27</v>
+        <v>205.01</v>
       </c>
       <c r="M3" t="n">
-        <v>208.47</v>
+        <v>208.22</v>
       </c>
       <c r="N3" t="n">
-        <v>198.86</v>
+        <v>198.6</v>
       </c>
       <c r="O3" t="n">
-        <v>221.61</v>
+        <v>221.36</v>
       </c>
       <c r="P3" t="n">
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>53.12</v>
+        <v>52.9</v>
       </c>
       <c r="R3" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.73</v>
+        <v>-2.85</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>XLE 9.61% · CL=F 12.07%</t>
+          <t>XLE 9.63% · CL=F 12.07%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.61% · CL=F 12.07%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.63% · CL=F 12.07%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>56.95</v>
+        <v>57.02</v>
       </c>
       <c r="D4" t="n">
         <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="F4" t="n">
-        <v>7.92</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>11.14</v>
+        <v>11.28</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.46</v>
+        <v>-1.26</v>
       </c>
       <c r="I4" t="n">
         <v>0.35</v>
@@ -828,28 +828,28 @@
         <v>2.56</v>
       </c>
       <c r="L4" t="n">
-        <v>56.44</v>
+        <v>56.51</v>
       </c>
       <c r="M4" t="n">
-        <v>57.17</v>
+        <v>57.24</v>
       </c>
       <c r="N4" t="n">
-        <v>54.98</v>
+        <v>55.05</v>
       </c>
       <c r="O4" t="n">
-        <v>60.16</v>
+        <v>60.23</v>
       </c>
       <c r="P4" t="n">
         <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>55.44</v>
+        <v>55.78</v>
       </c>
       <c r="R4" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.11</v>
+        <v>-0.99</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>XLE 9.61% · CL=F 12.07%</t>
+          <t>XLE 9.63% · CL=F 12.07%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.61% · CL=F 12.07%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.63% · CL=F 12.07%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -914,25 +914,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>197.01</v>
+        <v>197.09</v>
       </c>
       <c r="D5" t="n">
         <v>96</v>
       </c>
       <c r="E5" t="n">
-        <v>5.95</v>
+        <v>5.99</v>
       </c>
       <c r="F5" t="n">
-        <v>5.93</v>
+        <v>5.97</v>
       </c>
       <c r="G5" t="n">
-        <v>6.54</v>
+        <v>6.59</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.45</v>
+        <v>-3.34</v>
       </c>
       <c r="I5" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J5" t="n">
         <v>4.42</v>
@@ -941,28 +941,28 @@
         <v>2.25</v>
       </c>
       <c r="L5" t="n">
-        <v>195.46</v>
+        <v>195.54</v>
       </c>
       <c r="M5" t="n">
-        <v>197.67</v>
+        <v>197.75</v>
       </c>
       <c r="N5" t="n">
-        <v>191.04</v>
+        <v>191.12</v>
       </c>
       <c r="O5" t="n">
-        <v>206.74</v>
+        <v>206.82</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>57.44</v>
+        <v>57.55</v>
       </c>
       <c r="R5" t="n">
-        <v>4.51</v>
+        <v>4.55</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>XLE 9.61% · CL=F 12.07%</t>
+          <t>XLE 9.63% · CL=F 12.07%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.61% · CL=F 12.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.63% · CL=F 12.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1027,22 +1027,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>107</v>
+        <v>107.08</v>
       </c>
       <c r="D6" t="n">
         <v>96</v>
       </c>
       <c r="E6" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="F6" t="n">
-        <v>23.12</v>
+        <v>23.21</v>
       </c>
       <c r="G6" t="n">
-        <v>54.03</v>
+        <v>54.14</v>
       </c>
       <c r="H6" t="n">
-        <v>13.74</v>
+        <v>13.9</v>
       </c>
       <c r="I6" t="n">
         <v>0.44</v>
@@ -1054,28 +1054,28 @@
         <v>5.85</v>
       </c>
       <c r="L6" t="n">
-        <v>104.81</v>
+        <v>104.89</v>
       </c>
       <c r="M6" t="n">
-        <v>107.94</v>
+        <v>108.02</v>
       </c>
       <c r="N6" t="n">
-        <v>98.55</v>
+        <v>98.63</v>
       </c>
       <c r="O6" t="n">
-        <v>120.78</v>
+        <v>120.86</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>58.24</v>
+        <v>58.33</v>
       </c>
       <c r="R6" t="n">
-        <v>3.46</v>
+        <v>3.53</v>
       </c>
       <c r="S6" t="n">
-        <v>-10.16</v>
+        <v>-10.09</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>501.59</v>
+        <v>501.98</v>
       </c>
       <c r="D7" t="n">
         <v>96</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.79</v>
+        <v>-2.72</v>
       </c>
       <c r="F7" t="n">
-        <v>19.23</v>
+        <v>19.32</v>
       </c>
       <c r="G7" t="n">
-        <v>40.66</v>
+        <v>40.77</v>
       </c>
       <c r="H7" t="n">
-        <v>9.85</v>
+        <v>10.01</v>
       </c>
       <c r="I7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="J7" t="n">
         <v>21.02</v>
@@ -1167,28 +1167,28 @@
         <v>4.19</v>
       </c>
       <c r="L7" t="n">
-        <v>494.23</v>
+        <v>494.62</v>
       </c>
       <c r="M7" t="n">
-        <v>504.74</v>
+        <v>505.13</v>
       </c>
       <c r="N7" t="n">
-        <v>473.22</v>
+        <v>473.61</v>
       </c>
       <c r="O7" t="n">
-        <v>547.8200000000001</v>
+        <v>548.21</v>
       </c>
       <c r="P7" t="n">
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>63.59</v>
+        <v>63.66</v>
       </c>
       <c r="R7" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="S7" t="n">
-        <v>-6.02</v>
+        <v>-5.95</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1253,25 +1253,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>548.62</v>
+        <v>549.17</v>
       </c>
       <c r="D8" t="n">
         <v>96</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.25</v>
+        <v>-2.15</v>
       </c>
       <c r="F8" t="n">
-        <v>18.07</v>
+        <v>18.19</v>
       </c>
       <c r="G8" t="n">
-        <v>32.88</v>
+        <v>33.01</v>
       </c>
       <c r="H8" t="n">
-        <v>8.69</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="J8" t="n">
         <v>19.82</v>
@@ -1280,28 +1280,28 @@
         <v>3.61</v>
       </c>
       <c r="L8" t="n">
-        <v>541.6799999999999</v>
+        <v>542.23</v>
       </c>
       <c r="M8" t="n">
-        <v>551.59</v>
+        <v>552.14</v>
       </c>
       <c r="N8" t="n">
-        <v>521.86</v>
+        <v>522.41</v>
       </c>
       <c r="O8" t="n">
-        <v>592.23</v>
+        <v>592.77</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>64.52</v>
+        <v>64.63</v>
       </c>
       <c r="R8" t="n">
-        <v>3.47</v>
+        <v>3.57</v>
       </c>
       <c r="S8" t="n">
-        <v>-5.6</v>
+        <v>-5.51</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1366,22 +1366,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>222.76</v>
+        <v>222.66</v>
       </c>
       <c r="D9" t="n">
         <v>96</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F9" t="n">
-        <v>11.45</v>
+        <v>11.4</v>
       </c>
       <c r="G9" t="n">
-        <v>16.3</v>
+        <v>16.25</v>
       </c>
       <c r="H9" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="I9" t="n">
         <v>0.57</v>
@@ -1393,28 +1393,28 @@
         <v>3.82</v>
       </c>
       <c r="L9" t="n">
-        <v>219.78</v>
+        <v>219.69</v>
       </c>
       <c r="M9" t="n">
-        <v>224.04</v>
+        <v>223.94</v>
       </c>
       <c r="N9" t="n">
-        <v>211.27</v>
+        <v>211.17</v>
       </c>
       <c r="O9" t="n">
-        <v>241.49</v>
+        <v>241.39</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>60.25</v>
+        <v>60.19</v>
       </c>
       <c r="R9" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.83</v>
+        <v>-5.87</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>296.58</v>
+        <v>296.9</v>
       </c>
       <c r="D10" t="n">
         <v>94</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="F10" t="n">
-        <v>32.11</v>
+        <v>32.25</v>
       </c>
       <c r="G10" t="n">
-        <v>28.97</v>
+        <v>29.11</v>
       </c>
       <c r="H10" t="n">
-        <v>22.73</v>
+        <v>22.94</v>
       </c>
       <c r="I10" t="n">
         <v>0.3</v>
@@ -1506,28 +1506,28 @@
         <v>3.87</v>
       </c>
       <c r="L10" t="n">
-        <v>292.56</v>
+        <v>292.88</v>
       </c>
       <c r="M10" t="n">
-        <v>298.3</v>
+        <v>298.63</v>
       </c>
       <c r="N10" t="n">
-        <v>281.07</v>
+        <v>281.4</v>
       </c>
       <c r="O10" t="n">
-        <v>321.85</v>
+        <v>322.17</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>54.56</v>
+        <v>54.75</v>
       </c>
       <c r="R10" t="n">
-        <v>5.91</v>
+        <v>6.02</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.27</v>
+        <v>-3.17</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1592,22 +1592,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>92.83</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="D11" t="n">
         <v>74</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.98</v>
+        <v>-4.88</v>
       </c>
       <c r="F11" t="n">
-        <v>14.7</v>
+        <v>14.83</v>
       </c>
       <c r="G11" t="n">
-        <v>21.19</v>
+        <v>21.33</v>
       </c>
       <c r="H11" t="n">
-        <v>5.32</v>
+        <v>5.52</v>
       </c>
       <c r="I11" t="n">
         <v>0.28</v>
@@ -1619,28 +1619,28 @@
         <v>4.49</v>
       </c>
       <c r="L11" t="n">
-        <v>91.37</v>
+        <v>91.48</v>
       </c>
       <c r="M11" t="n">
-        <v>93.45999999999999</v>
+        <v>93.56</v>
       </c>
       <c r="N11" t="n">
-        <v>87.2</v>
+        <v>87.31</v>
       </c>
       <c r="O11" t="n">
-        <v>102</v>
+        <v>102.11</v>
       </c>
       <c r="P11" t="n">
         <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>55.63</v>
+        <v>55.82</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.14</v>
+        <v>-1.03</v>
       </c>
       <c r="S11" t="n">
-        <v>-12.35</v>
+        <v>-12.25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1705,55 +1705,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>395.47</v>
+        <v>395.65</v>
       </c>
       <c r="D12" t="n">
         <v>74</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.46</v>
+        <v>-0.41</v>
       </c>
       <c r="F12" t="n">
-        <v>7.44</v>
+        <v>7.49</v>
       </c>
       <c r="G12" t="n">
-        <v>7.17</v>
+        <v>7.22</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.94</v>
+        <v>-1.82</v>
       </c>
       <c r="I12" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="J12" t="n">
         <v>15.72</v>
       </c>
       <c r="K12" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="L12" t="n">
-        <v>389.97</v>
+        <v>390.15</v>
       </c>
       <c r="M12" t="n">
-        <v>397.83</v>
+        <v>398.01</v>
       </c>
       <c r="N12" t="n">
-        <v>374.25</v>
+        <v>374.43</v>
       </c>
       <c r="O12" t="n">
-        <v>430.05</v>
+        <v>430.23</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>50.78</v>
+        <v>50.87</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.3</v>
+        <v>-1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.28</v>
+        <v>-6.24</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1814,25 +1814,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>106.87</v>
+        <v>106.82</v>
       </c>
       <c r="D13" t="n">
         <v>96</v>
       </c>
       <c r="E13" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>9.91</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>13.42</v>
+        <v>13.36</v>
       </c>
       <c r="H13" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="I13" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="J13" t="n">
         <v>2.48</v>
@@ -1841,28 +1841,28 @@
         <v>2.32</v>
       </c>
       <c r="L13" t="n">
-        <v>106</v>
+        <v>105.95</v>
       </c>
       <c r="M13" t="n">
-        <v>107.24</v>
+        <v>107.19</v>
       </c>
       <c r="N13" t="n">
-        <v>103.52</v>
+        <v>103.47</v>
       </c>
       <c r="O13" t="n">
-        <v>112.33</v>
+        <v>112.28</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>59.67</v>
+        <v>59.48</v>
       </c>
       <c r="R13" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.27</v>
+        <v>-1.32</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1927,25 +1927,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>254.33</v>
+        <v>254</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
       </c>
       <c r="E14" t="n">
-        <v>5.61</v>
+        <v>5.47</v>
       </c>
       <c r="F14" t="n">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.49</v>
+        <v>-6.55</v>
       </c>
       <c r="I14" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="J14" t="n">
         <v>9.41</v>
@@ -1954,28 +1954,28 @@
         <v>3.7</v>
       </c>
       <c r="L14" t="n">
-        <v>251.04</v>
+        <v>250.7</v>
       </c>
       <c r="M14" t="n">
-        <v>255.74</v>
+        <v>255.41</v>
       </c>
       <c r="N14" t="n">
-        <v>241.63</v>
+        <v>241.3</v>
       </c>
       <c r="O14" t="n">
-        <v>275.03</v>
+        <v>274.7</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>58.26</v>
+        <v>57.96</v>
       </c>
       <c r="R14" t="n">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.06</v>
+        <v>-4.18</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2040,25 +2040,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>114.59</v>
+        <v>114.51</v>
       </c>
       <c r="D15" t="n">
         <v>96</v>
       </c>
       <c r="E15" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.77</v>
+        <v>-6.83</v>
       </c>
       <c r="H15" t="n">
-        <v>-7.58</v>
+        <v>-7.57</v>
       </c>
       <c r="I15" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="J15" t="n">
         <v>2.62</v>
@@ -2067,28 +2067,28 @@
         <v>2.28</v>
       </c>
       <c r="L15" t="n">
-        <v>113.67</v>
+        <v>113.6</v>
       </c>
       <c r="M15" t="n">
-        <v>114.98</v>
+        <v>114.91</v>
       </c>
       <c r="N15" t="n">
-        <v>111.06</v>
+        <v>110.98</v>
       </c>
       <c r="O15" t="n">
-        <v>120.35</v>
+        <v>120.27</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.46</v>
+        <v>61.28</v>
       </c>
       <c r="R15" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.44</v>
+        <v>-0.51</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2153,22 +2153,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>229.52</v>
+        <v>229.4</v>
       </c>
       <c r="D16" t="n">
         <v>93</v>
       </c>
       <c r="E16" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="F16" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.14</v>
+        <v>-6.19</v>
       </c>
       <c r="H16" t="n">
-        <v>-7.89</v>
+        <v>-7.88</v>
       </c>
       <c r="I16" t="n">
         <v>0.58</v>
@@ -2177,31 +2177,31 @@
         <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="L16" t="n">
-        <v>228.19</v>
+        <v>228.08</v>
       </c>
       <c r="M16" t="n">
-        <v>230.09</v>
+        <v>229.97</v>
       </c>
       <c r="N16" t="n">
-        <v>224.39</v>
+        <v>224.28</v>
       </c>
       <c r="O16" t="n">
-        <v>237.88</v>
+        <v>237.76</v>
       </c>
       <c r="P16" t="n">
         <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>53.6</v>
+        <v>53.43</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.13</v>
+        <v>-1.18</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2266,22 +2266,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>214.16</v>
+        <v>213.76</v>
       </c>
       <c r="D17" t="n">
         <v>82</v>
       </c>
       <c r="E17" t="n">
-        <v>3.03</v>
+        <v>2.84</v>
       </c>
       <c r="F17" t="n">
-        <v>4.41</v>
+        <v>4.21</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.9</v>
+        <v>-6.08</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.97</v>
+        <v>-5.1</v>
       </c>
       <c r="I17" t="n">
         <v>0.4</v>
@@ -2290,31 +2290,31 @@
         <v>5.32</v>
       </c>
       <c r="K17" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="L17" t="n">
-        <v>212.3</v>
+        <v>211.9</v>
       </c>
       <c r="M17" t="n">
-        <v>214.96</v>
+        <v>214.56</v>
       </c>
       <c r="N17" t="n">
-        <v>206.98</v>
+        <v>206.59</v>
       </c>
       <c r="O17" t="n">
-        <v>225.85</v>
+        <v>225.46</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>64.40000000000001</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.76</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2379,25 +2379,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>92.65000000000001</v>
+        <v>92.55</v>
       </c>
       <c r="D18" t="n">
         <v>82</v>
       </c>
       <c r="E18" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="G18" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="H18" t="n">
-        <v>-8.279999999999999</v>
+        <v>-8.32</v>
       </c>
       <c r="I18" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>2.2</v>
@@ -2406,28 +2406,28 @@
         <v>2.38</v>
       </c>
       <c r="L18" t="n">
-        <v>91.88</v>
+        <v>91.78</v>
       </c>
       <c r="M18" t="n">
-        <v>92.98</v>
+        <v>92.88</v>
       </c>
       <c r="N18" t="n">
-        <v>89.68000000000001</v>
+        <v>89.58</v>
       </c>
       <c r="O18" t="n">
-        <v>97.48999999999999</v>
+        <v>97.39</v>
       </c>
       <c r="P18" t="n">
         <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>56.45</v>
+        <v>56.14</v>
       </c>
       <c r="R18" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.83</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2492,55 +2492,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>191.96</v>
+        <v>191.83</v>
       </c>
       <c r="D19" t="n">
         <v>81</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="F19" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="G19" t="n">
-        <v>15.7</v>
+        <v>15.62</v>
       </c>
       <c r="H19" t="n">
-        <v>-7.44</v>
+        <v>-7.43</v>
       </c>
       <c r="I19" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>4.27</v>
       </c>
       <c r="K19" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="L19" t="n">
-        <v>190.47</v>
+        <v>190.34</v>
       </c>
       <c r="M19" t="n">
-        <v>192.6</v>
+        <v>192.47</v>
       </c>
       <c r="N19" t="n">
-        <v>186.2</v>
+        <v>186.07</v>
       </c>
       <c r="O19" t="n">
-        <v>201.35</v>
+        <v>201.22</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>60.94</v>
+        <v>60.64</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.81</v>
+        <v>-2.87</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2601,25 +2601,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>495.86</v>
+        <v>495.61</v>
       </c>
       <c r="D20" t="n">
         <v>81</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.35</v>
+        <v>-0.4</v>
       </c>
       <c r="F20" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="G20" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="H20" t="n">
-        <v>-8.41</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J20" t="n">
         <v>5.11</v>
@@ -2628,28 +2628,28 @@
         <v>1.03</v>
       </c>
       <c r="L20" t="n">
-        <v>494.07</v>
+        <v>493.82</v>
       </c>
       <c r="M20" t="n">
-        <v>496.63</v>
+        <v>496.38</v>
       </c>
       <c r="N20" t="n">
-        <v>488.96</v>
+        <v>488.71</v>
       </c>
       <c r="O20" t="n">
-        <v>507.11</v>
+        <v>506.86</v>
       </c>
       <c r="P20" t="n">
         <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>58.88</v>
+        <v>58.53</v>
       </c>
       <c r="R20" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2</v>
+        <v>-1.25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2710,25 +2710,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>330.87</v>
+        <v>330.56</v>
       </c>
       <c r="D21" t="n">
         <v>80</v>
       </c>
       <c r="E21" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="F21" t="n">
-        <v>6.97</v>
+        <v>6.87</v>
       </c>
       <c r="G21" t="n">
-        <v>8.17</v>
+        <v>8.07</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.41</v>
+        <v>-2.44</v>
       </c>
       <c r="I21" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>6.21</v>
@@ -2737,28 +2737,28 @@
         <v>1.88</v>
       </c>
       <c r="L21" t="n">
-        <v>328.7</v>
+        <v>328.39</v>
       </c>
       <c r="M21" t="n">
-        <v>331.8</v>
+        <v>331.49</v>
       </c>
       <c r="N21" t="n">
-        <v>322.49</v>
+        <v>322.18</v>
       </c>
       <c r="O21" t="n">
-        <v>344.53</v>
+        <v>344.22</v>
       </c>
       <c r="P21" t="n">
         <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>46.67</v>
+        <v>46.38</v>
       </c>
       <c r="R21" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.05</v>
+        <v>-3.14</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2819,25 +2819,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>937.5</v>
+        <v>937.05</v>
       </c>
       <c r="D22" t="n">
         <v>78</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.89</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="G22" t="n">
-        <v>5.62</v>
+        <v>5.57</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.18</v>
       </c>
       <c r="I22" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="J22" t="n">
         <v>23.14</v>
@@ -2846,28 +2846,28 @@
         <v>2.47</v>
       </c>
       <c r="L22" t="n">
-        <v>929.4</v>
+        <v>928.95</v>
       </c>
       <c r="M22" t="n">
-        <v>940.97</v>
+        <v>940.52</v>
       </c>
       <c r="N22" t="n">
-        <v>906.26</v>
+        <v>905.8099999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>988.41</v>
+        <v>987.96</v>
       </c>
       <c r="P22" t="n">
         <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>60.05</v>
+        <v>59.88</v>
       </c>
       <c r="R22" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.91</v>
+        <v>-3.96</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2928,22 +2928,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>400.75</v>
+        <v>400.96</v>
       </c>
       <c r="D23" t="n">
         <v>74</v>
       </c>
       <c r="E23" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.01</v>
+        <v>-0.96</v>
       </c>
       <c r="G23" t="n">
-        <v>11.8</v>
+        <v>11.86</v>
       </c>
       <c r="H23" t="n">
-        <v>-10.39</v>
+        <v>-10.27</v>
       </c>
       <c r="I23" t="n">
         <v>0.77</v>
@@ -2955,28 +2955,28 @@
         <v>4.65</v>
       </c>
       <c r="L23" t="n">
-        <v>394.23</v>
+        <v>394.44</v>
       </c>
       <c r="M23" t="n">
-        <v>403.55</v>
+        <v>403.76</v>
       </c>
       <c r="N23" t="n">
-        <v>375.59</v>
+        <v>375.8</v>
       </c>
       <c r="O23" t="n">
-        <v>441.75</v>
+        <v>441.96</v>
       </c>
       <c r="P23" t="n">
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>52.17</v>
+        <v>52.25</v>
       </c>
       <c r="R23" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.48</v>
+        <v>-5.43</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3037,13 +3037,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>180.51</v>
+        <v>180.52</v>
       </c>
       <c r="D24" t="n">
         <v>74</v>
       </c>
       <c r="E24" t="n">
-        <v>5.37</v>
+        <v>5.38</v>
       </c>
       <c r="F24" t="n">
         <v>-3.52</v>
@@ -3052,10 +3052,10 @@
         <v>1.58</v>
       </c>
       <c r="H24" t="n">
-        <v>-12.9</v>
+        <v>-12.83</v>
       </c>
       <c r="I24" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>7.55</v>
@@ -3064,7 +3064,7 @@
         <v>4.18</v>
       </c>
       <c r="L24" t="n">
-        <v>177.87</v>
+        <v>177.88</v>
       </c>
       <c r="M24" t="n">
         <v>181.65</v>
@@ -3079,10 +3079,10 @@
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>49.42</v>
+        <v>49.43</v>
       </c>
       <c r="R24" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="S24" t="n">
         <v>-5.56</v>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -3146,25 +3146,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>162.23</v>
+        <v>162.31</v>
       </c>
       <c r="D25" t="n">
         <v>96</v>
       </c>
       <c r="E25" t="n">
-        <v>8.43</v>
+        <v>8.49</v>
       </c>
       <c r="F25" t="n">
-        <v>10.09</v>
+        <v>10.15</v>
       </c>
       <c r="G25" t="n">
-        <v>8.34</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="I25" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>4.11</v>
@@ -3173,28 +3173,28 @@
         <v>2.53</v>
       </c>
       <c r="L25" t="n">
-        <v>160.79</v>
+        <v>160.87</v>
       </c>
       <c r="M25" t="n">
-        <v>162.85</v>
+        <v>162.93</v>
       </c>
       <c r="N25" t="n">
-        <v>156.68</v>
+        <v>156.76</v>
       </c>
       <c r="O25" t="n">
-        <v>171.27</v>
+        <v>171.35</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>63.07</v>
+        <v>63.16</v>
       </c>
       <c r="R25" t="n">
-        <v>7.23</v>
+        <v>7.28</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.12</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>XLE 9.61% · CL=F 12.07%</t>
+          <t>XLE 9.63% · CL=F 12.07%</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.61% · CL=F 12.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.63% · CL=F 12.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3259,25 +3259,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>61.26</v>
+        <v>61.28</v>
       </c>
       <c r="D26" t="n">
         <v>96</v>
       </c>
       <c r="E26" t="n">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="F26" t="n">
-        <v>9.640000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="G26" t="n">
-        <v>11.8</v>
+        <v>11.85</v>
       </c>
       <c r="H26" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="I26" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J26" t="n">
         <v>1.36</v>
@@ -3286,28 +3286,28 @@
         <v>2.22</v>
       </c>
       <c r="L26" t="n">
-        <v>60.78</v>
+        <v>60.81</v>
       </c>
       <c r="M26" t="n">
-        <v>61.46</v>
+        <v>61.49</v>
       </c>
       <c r="N26" t="n">
-        <v>59.42</v>
+        <v>59.45</v>
       </c>
       <c r="O26" t="n">
-        <v>64.23999999999999</v>
+        <v>64.27</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>59.82</v>
+        <v>59.93</v>
       </c>
       <c r="R26" t="n">
-        <v>5.47</v>
+        <v>5.52</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>XLE 9.61% · CL=F 12.07%</t>
+          <t>XLE 9.63% · CL=F 12.07%</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.61% · CL=F 12.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.63% · CL=F 12.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3372,25 +3372,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>49.74</v>
+        <v>49.78</v>
       </c>
       <c r="D27" t="n">
         <v>96</v>
       </c>
       <c r="E27" t="n">
-        <v>6.36</v>
+        <v>6.45</v>
       </c>
       <c r="F27" t="n">
-        <v>9.09</v>
+        <v>9.18</v>
       </c>
       <c r="G27" t="n">
-        <v>14.51</v>
+        <v>14.6</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.29</v>
+        <v>-0.13</v>
       </c>
       <c r="I27" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="J27" t="n">
         <v>1.72</v>
@@ -3399,28 +3399,28 @@
         <v>3.45</v>
       </c>
       <c r="L27" t="n">
-        <v>49.14</v>
+        <v>49.18</v>
       </c>
       <c r="M27" t="n">
-        <v>50</v>
+        <v>50.04</v>
       </c>
       <c r="N27" t="n">
-        <v>47.43</v>
+        <v>47.47</v>
       </c>
       <c r="O27" t="n">
-        <v>53.52</v>
+        <v>53.56</v>
       </c>
       <c r="P27" t="n">
         <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>44.52</v>
+        <v>44.7</v>
       </c>
       <c r="R27" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.24</v>
+        <v>-4.17</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>XLE 9.61% · CL=F 12.07%</t>
+          <t>XLE 9.63% · CL=F 12.07%</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.61% · CL=F 12.07%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.63% · CL=F 12.07%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3485,22 +3485,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>143.91</v>
+        <v>143.88</v>
       </c>
       <c r="D28" t="n">
         <v>96</v>
       </c>
       <c r="E28" t="n">
-        <v>7.29</v>
+        <v>7.27</v>
       </c>
       <c r="F28" t="n">
-        <v>8.67</v>
+        <v>8.65</v>
       </c>
       <c r="G28" t="n">
-        <v>18.57</v>
+        <v>18.55</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.71</v>
+        <v>-0.66</v>
       </c>
       <c r="I28" t="n">
         <v>0.47</v>
@@ -3512,28 +3512,28 @@
         <v>2.72</v>
       </c>
       <c r="L28" t="n">
-        <v>142.54</v>
+        <v>142.51</v>
       </c>
       <c r="M28" t="n">
-        <v>144.5</v>
+        <v>144.47</v>
       </c>
       <c r="N28" t="n">
-        <v>138.62</v>
+        <v>138.59</v>
       </c>
       <c r="O28" t="n">
-        <v>152.53</v>
+        <v>152.5</v>
       </c>
       <c r="P28" t="n">
         <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>57.68</v>
+        <v>57.64</v>
       </c>
       <c r="R28" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.46</v>
+        <v>-0.48</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>XLE 9.61% · CL=F 12.07%</t>
+          <t>XLE 9.63% · CL=F 12.07%</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.61% · CL=F 12.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.63% · CL=F 12.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3598,25 +3598,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>60.62</v>
+        <v>60.65</v>
       </c>
       <c r="D29" t="n">
         <v>96</v>
       </c>
       <c r="E29" t="n">
-        <v>7.72</v>
+        <v>7.78</v>
       </c>
       <c r="F29" t="n">
-        <v>7.61</v>
+        <v>7.67</v>
       </c>
       <c r="G29" t="n">
-        <v>16.16</v>
+        <v>16.23</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.77</v>
+        <v>-1.64</v>
       </c>
       <c r="I29" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="J29" t="n">
         <v>1.93</v>
@@ -3625,28 +3625,28 @@
         <v>3.18</v>
       </c>
       <c r="L29" t="n">
-        <v>59.94</v>
+        <v>59.98</v>
       </c>
       <c r="M29" t="n">
-        <v>60.9</v>
+        <v>60.94</v>
       </c>
       <c r="N29" t="n">
-        <v>58.01</v>
+        <v>58.05</v>
       </c>
       <c r="O29" t="n">
-        <v>64.84999999999999</v>
+        <v>64.89</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>49.61</v>
+        <v>49.71</v>
       </c>
       <c r="R29" t="n">
-        <v>5.05</v>
+        <v>5.11</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.29</v>
+        <v>-0.23</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>XLE 9.61% · CL=F 12.07%</t>
+          <t>XLE 9.63% · CL=F 12.07%</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.61% · CL=F 12.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.63% · CL=F 12.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3711,25 +3711,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>125.24</v>
+        <v>125.25</v>
       </c>
       <c r="D30" t="n">
         <v>85</v>
       </c>
       <c r="E30" t="n">
-        <v>6.25</v>
+        <v>6.26</v>
       </c>
       <c r="F30" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="G30" t="n">
-        <v>14.83</v>
+        <v>14.84</v>
       </c>
       <c r="H30" t="n">
-        <v>-4.47</v>
+        <v>-4.39</v>
       </c>
       <c r="I30" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="J30" t="n">
         <v>3.31</v>
@@ -3738,22 +3738,22 @@
         <v>2.64</v>
       </c>
       <c r="L30" t="n">
-        <v>124.08</v>
+        <v>124.09</v>
       </c>
       <c r="M30" t="n">
-        <v>125.74</v>
+        <v>125.75</v>
       </c>
       <c r="N30" t="n">
-        <v>120.78</v>
+        <v>120.79</v>
       </c>
       <c r="O30" t="n">
-        <v>132.52</v>
+        <v>132.53</v>
       </c>
       <c r="P30" t="n">
         <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>46.65</v>
+        <v>46.67</v>
       </c>
       <c r="R30" t="n">
         <v>3.59</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>XLE 9.61% · CL=F 12.07%</t>
+          <t>XLE 9.63% · CL=F 12.07%</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.61% · CL=F 12.07%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.63% · CL=F 12.07%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3824,22 +3824,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>225.07</v>
+        <v>224.37</v>
       </c>
       <c r="D31" t="n">
         <v>94</v>
       </c>
       <c r="E31" t="n">
-        <v>8.25</v>
+        <v>7.91</v>
       </c>
       <c r="F31" t="n">
-        <v>28.25</v>
+        <v>27.85</v>
       </c>
       <c r="G31" t="n">
-        <v>81.83</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>18.87</v>
+        <v>18.54</v>
       </c>
       <c r="I31" t="n">
         <v>0.6899999999999999</v>
@@ -3848,31 +3848,31 @@
         <v>16.39</v>
       </c>
       <c r="K31" t="n">
-        <v>7.28</v>
+        <v>7.3</v>
       </c>
       <c r="L31" t="n">
-        <v>219.33</v>
+        <v>218.63</v>
       </c>
       <c r="M31" t="n">
-        <v>227.53</v>
+        <v>226.82</v>
       </c>
       <c r="N31" t="n">
-        <v>202.94</v>
+        <v>202.24</v>
       </c>
       <c r="O31" t="n">
-        <v>261.13</v>
+        <v>260.42</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>58.55</v>
+        <v>58.34</v>
       </c>
       <c r="R31" t="n">
-        <v>5.44</v>
+        <v>5.12</v>
       </c>
       <c r="S31" t="n">
-        <v>-6.03</v>
+        <v>-6.32</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3928,7 +3928,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3937,55 +3937,55 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>179.02</v>
+        <v>418.15</v>
       </c>
       <c r="D32" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E32" t="n">
-        <v>8.83</v>
+        <v>-0.36</v>
       </c>
       <c r="F32" t="n">
-        <v>18.31</v>
+        <v>11.43</v>
       </c>
       <c r="G32" t="n">
-        <v>130.25</v>
+        <v>18.11</v>
       </c>
       <c r="H32" t="n">
-        <v>8.93</v>
+        <v>2.12</v>
       </c>
       <c r="I32" t="n">
-        <v>0.66</v>
+        <v>1.04</v>
       </c>
       <c r="J32" t="n">
-        <v>12</v>
+        <v>12.35</v>
       </c>
       <c r="K32" t="n">
-        <v>6.71</v>
+        <v>2.95</v>
       </c>
       <c r="L32" t="n">
-        <v>174.82</v>
+        <v>413.83</v>
       </c>
       <c r="M32" t="n">
-        <v>180.82</v>
+        <v>420</v>
       </c>
       <c r="N32" t="n">
-        <v>162.81</v>
+        <v>401.47</v>
       </c>
       <c r="O32" t="n">
-        <v>205.43</v>
+        <v>445.33</v>
       </c>
       <c r="P32" t="n">
         <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>62.51</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="R32" t="n">
-        <v>7.17</v>
+        <v>2.64</v>
       </c>
       <c r="S32" t="n">
-        <v>-6.83</v>
+        <v>-4.03</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4029,19 +4029,19 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Momentum 5D extendido; Algo extendida sobre MA20; Volatilidad alta</t>
+          <t>RSI algo alto; MACD sin confirmar</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4050,55 +4050,55 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>417.76</v>
+        <v>179.08</v>
       </c>
       <c r="D33" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.45</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>11.32</v>
+        <v>18.35</v>
       </c>
       <c r="G33" t="n">
-        <v>18</v>
+        <v>130.32</v>
       </c>
       <c r="H33" t="n">
-        <v>1.94</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>1.02</v>
+        <v>0.67</v>
       </c>
       <c r="J33" t="n">
-        <v>12.35</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>2.96</v>
+        <v>6.7</v>
       </c>
       <c r="L33" t="n">
-        <v>413.44</v>
+        <v>174.88</v>
       </c>
       <c r="M33" t="n">
-        <v>419.61</v>
+        <v>180.88</v>
       </c>
       <c r="N33" t="n">
-        <v>401.08</v>
+        <v>162.87</v>
       </c>
       <c r="O33" t="n">
-        <v>444.94</v>
+        <v>205.49</v>
       </c>
       <c r="P33" t="n">
         <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>65.67</v>
+        <v>62.54</v>
       </c>
       <c r="R33" t="n">
-        <v>2.55</v>
+        <v>7.21</v>
       </c>
       <c r="S33" t="n">
-        <v>-4.12</v>
+        <v>-6.8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>RSI algo alto; MACD sin confirmar</t>
+          <t>MACD sin confirmar; Volumen bajo; Momentum 5D extendido; Algo extendida sobre MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -4163,22 +4163,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>86.77</v>
+        <v>86.87</v>
       </c>
       <c r="D34" t="n">
         <v>90</v>
       </c>
       <c r="E34" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="F34" t="n">
-        <v>21.83</v>
+        <v>21.97</v>
       </c>
       <c r="G34" t="n">
-        <v>26.1</v>
+        <v>26.24</v>
       </c>
       <c r="H34" t="n">
-        <v>12.45</v>
+        <v>12.66</v>
       </c>
       <c r="I34" t="n">
         <v>0.57</v>
@@ -4187,31 +4187,31 @@
         <v>7.58</v>
       </c>
       <c r="K34" t="n">
-        <v>8.73</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>84.12</v>
+        <v>84.22</v>
       </c>
       <c r="M34" t="n">
-        <v>87.91</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>76.54000000000001</v>
+        <v>76.64</v>
       </c>
       <c r="O34" t="n">
-        <v>103.44</v>
+        <v>103.54</v>
       </c>
       <c r="P34" t="n">
         <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>64.12</v>
+        <v>64.23</v>
       </c>
       <c r="R34" t="n">
-        <v>6.09</v>
+        <v>6.2</v>
       </c>
       <c r="S34" t="n">
-        <v>-9.91</v>
+        <v>-9.81</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -4291,7 +4291,7 @@
         <v>7</v>
       </c>
       <c r="H35" t="n">
-        <v>-5.73</v>
+        <v>-5.66</v>
       </c>
       <c r="I35" t="n">
         <v>0.61</v>
@@ -4389,25 +4389,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>390.36</v>
+        <v>390.69</v>
       </c>
       <c r="D36" t="n">
         <v>88</v>
       </c>
       <c r="E36" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="F36" t="n">
-        <v>17.48</v>
+        <v>17.58</v>
       </c>
       <c r="G36" t="n">
-        <v>25.41</v>
+        <v>25.51</v>
       </c>
       <c r="H36" t="n">
-        <v>8.1</v>
+        <v>8.27</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>11.59</v>
@@ -4416,28 +4416,28 @@
         <v>2.97</v>
       </c>
       <c r="L36" t="n">
-        <v>386.31</v>
+        <v>386.63</v>
       </c>
       <c r="M36" t="n">
-        <v>392.1</v>
+        <v>392.43</v>
       </c>
       <c r="N36" t="n">
-        <v>374.72</v>
+        <v>375.05</v>
       </c>
       <c r="O36" t="n">
-        <v>415.86</v>
+        <v>416.18</v>
       </c>
       <c r="P36" t="n">
         <v>1.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>70.81</v>
+        <v>71.05</v>
       </c>
       <c r="R36" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="S36" t="n">
-        <v>-4.47</v>
+        <v>-4.39</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4493,64 +4493,64 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Ciberseguridad</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>392.2</v>
+        <v>86.33</v>
       </c>
       <c r="D37" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>13.35</v>
+        <v>11.19</v>
       </c>
       <c r="G37" t="n">
-        <v>39.99</v>
+        <v>24.2</v>
       </c>
       <c r="H37" t="n">
-        <v>3.97</v>
+        <v>1.88</v>
       </c>
       <c r="I37" t="n">
-        <v>0.39</v>
+        <v>0.78</v>
       </c>
       <c r="J37" t="n">
-        <v>8.9</v>
+        <v>3.74</v>
       </c>
       <c r="K37" t="n">
-        <v>2.27</v>
+        <v>4.33</v>
       </c>
       <c r="L37" t="n">
-        <v>389.09</v>
+        <v>85.02</v>
       </c>
       <c r="M37" t="n">
-        <v>393.54</v>
+        <v>86.89</v>
       </c>
       <c r="N37" t="n">
-        <v>380.2</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>411.78</v>
+        <v>94.55</v>
       </c>
       <c r="P37" t="n">
         <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>68.13</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="R37" t="n">
-        <v>4.53</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="S37" t="n">
-        <v>-2.96</v>
+        <v>-4.08</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4594,76 +4594,76 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; Fuerte vs QQQ</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>RSI algo alto; MACD sin confirmar; Volumen bajo</t>
+          <t>Tendencia larga débil; RSI algo alto; Momentum 5D extendido; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ciberseguridad</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>86.37</v>
+        <v>391.97</v>
       </c>
       <c r="D38" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E38" t="n">
-        <v>9.25</v>
+        <v>-1.12</v>
       </c>
       <c r="F38" t="n">
-        <v>11.24</v>
+        <v>13.28</v>
       </c>
       <c r="G38" t="n">
-        <v>24.26</v>
+        <v>39.91</v>
       </c>
       <c r="H38" t="n">
-        <v>1.86</v>
+        <v>3.97</v>
       </c>
       <c r="I38" t="n">
-        <v>0.77</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
-        <v>3.74</v>
+        <v>8.9</v>
       </c>
       <c r="K38" t="n">
-        <v>4.33</v>
+        <v>2.27</v>
       </c>
       <c r="L38" t="n">
-        <v>85.06</v>
+        <v>388.86</v>
       </c>
       <c r="M38" t="n">
-        <v>86.93000000000001</v>
+        <v>393.3</v>
       </c>
       <c r="N38" t="n">
-        <v>81.33</v>
+        <v>379.96</v>
       </c>
       <c r="O38" t="n">
-        <v>94.59</v>
+        <v>411.54</v>
       </c>
       <c r="P38" t="n">
         <v>1.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>67.86</v>
+        <v>68</v>
       </c>
       <c r="R38" t="n">
-        <v>9.19</v>
+        <v>4.47</v>
       </c>
       <c r="S38" t="n">
-        <v>-4.03</v>
+        <v>-3.01</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; MACD positivo; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; Fuerte vs QQQ</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI algo alto; Momentum 5D extendido; Algo extendida sobre MA20</t>
+          <t>RSI algo alto; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -4728,22 +4728,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>237.35</v>
+        <v>236.93</v>
       </c>
       <c r="D39" t="n">
         <v>82</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.67</v>
+        <v>-0.84</v>
       </c>
       <c r="F39" t="n">
-        <v>11.77</v>
+        <v>11.57</v>
       </c>
       <c r="G39" t="n">
-        <v>99.84</v>
+        <v>99.48</v>
       </c>
       <c r="H39" t="n">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="I39" t="n">
         <v>0.47</v>
@@ -4752,31 +4752,31 @@
         <v>14.38</v>
       </c>
       <c r="K39" t="n">
-        <v>6.06</v>
+        <v>6.07</v>
       </c>
       <c r="L39" t="n">
-        <v>232.32</v>
+        <v>231.9</v>
       </c>
       <c r="M39" t="n">
-        <v>239.51</v>
+        <v>239.09</v>
       </c>
       <c r="N39" t="n">
-        <v>217.94</v>
+        <v>217.52</v>
       </c>
       <c r="O39" t="n">
-        <v>268.98</v>
+        <v>268.56</v>
       </c>
       <c r="P39" t="n">
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>64.04000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="R39" t="n">
-        <v>4.51</v>
+        <v>4.33</v>
       </c>
       <c r="S39" t="n">
-        <v>-10.09</v>
+        <v>-10.25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -4841,25 +4841,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
       <c r="D40" t="n">
         <v>75</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.48</v>
+        <v>-3.57</v>
       </c>
       <c r="F40" t="n">
-        <v>12.88</v>
+        <v>12.76</v>
       </c>
       <c r="G40" t="n">
-        <v>6.13</v>
+        <v>6.03</v>
       </c>
       <c r="H40" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="J40" t="n">
         <v>0.77</v>
@@ -4868,28 +4868,28 @@
         <v>7.64</v>
       </c>
       <c r="L40" t="n">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
       <c r="M40" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
       <c r="N40" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
       <c r="O40" t="n">
-        <v>11.83</v>
+        <v>11.82</v>
       </c>
       <c r="P40" t="n">
         <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>61.46</v>
+        <v>61.37</v>
       </c>
       <c r="R40" t="n">
-        <v>4.41</v>
+        <v>4.31</v>
       </c>
       <c r="S40" t="n">
-        <v>-9.52</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4965,10 +4965,10 @@
         <v>17.89</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.56</v>
+        <v>-3.49</v>
       </c>
       <c r="I41" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="J41" t="n">
         <v>2.76</v>
@@ -5059,25 +5059,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>147.54</v>
+        <v>147.51</v>
       </c>
       <c r="D42" t="n">
         <v>75</v>
       </c>
       <c r="E42" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="F42" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="G42" t="n">
-        <v>-6.56</v>
+        <v>-6.57</v>
       </c>
       <c r="H42" t="n">
-        <v>-8.27</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="J42" t="n">
         <v>2.01</v>
@@ -5086,28 +5086,28 @@
         <v>1.36</v>
       </c>
       <c r="L42" t="n">
-        <v>146.84</v>
+        <v>146.81</v>
       </c>
       <c r="M42" t="n">
-        <v>147.84</v>
+        <v>147.81</v>
       </c>
       <c r="N42" t="n">
-        <v>144.82</v>
+        <v>144.79</v>
       </c>
       <c r="O42" t="n">
-        <v>151.97</v>
+        <v>151.94</v>
       </c>
       <c r="P42" t="n">
         <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>65.5</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="R42" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5168,22 +5168,22 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>412.8</v>
+        <v>412.02</v>
       </c>
       <c r="D43" t="n">
         <v>63</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.55</v>
+        <v>-1.74</v>
       </c>
       <c r="F43" t="n">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="G43" t="n">
-        <v>25.22</v>
+        <v>24.99</v>
       </c>
       <c r="H43" t="n">
-        <v>-6.74</v>
+        <v>-6.86</v>
       </c>
       <c r="I43" t="n">
         <v>0.64</v>
@@ -5192,31 +5192,31 @@
         <v>16.73</v>
       </c>
       <c r="K43" t="n">
-        <v>4.05</v>
+        <v>4.06</v>
       </c>
       <c r="L43" t="n">
-        <v>406.94</v>
+        <v>406.16</v>
       </c>
       <c r="M43" t="n">
-        <v>415.3</v>
+        <v>414.53</v>
       </c>
       <c r="N43" t="n">
-        <v>390.21</v>
+        <v>389.44</v>
       </c>
       <c r="O43" t="n">
-        <v>449.6</v>
+        <v>448.82</v>
       </c>
       <c r="P43" t="n">
         <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>52.89</v>
+        <v>52.57</v>
       </c>
       <c r="R43" t="n">
-        <v>-1.74</v>
+        <v>-1.92</v>
       </c>
       <c r="S43" t="n">
-        <v>-6.68</v>
+        <v>-6.86</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5277,22 +5277,22 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>408.64</v>
+        <v>408.58</v>
       </c>
       <c r="D44" t="n">
         <v>61</v>
       </c>
       <c r="E44" t="n">
-        <v>-5.23</v>
+        <v>-5.25</v>
       </c>
       <c r="F44" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="G44" t="n">
-        <v>9.390000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>-5.75</v>
+        <v>-5.7</v>
       </c>
       <c r="I44" t="n">
         <v>0.62</v>
@@ -5304,28 +5304,28 @@
         <v>4.91</v>
       </c>
       <c r="L44" t="n">
-        <v>401.62</v>
+        <v>401.55</v>
       </c>
       <c r="M44" t="n">
-        <v>411.66</v>
+        <v>411.59</v>
       </c>
       <c r="N44" t="n">
-        <v>381.54</v>
+        <v>381.47</v>
       </c>
       <c r="O44" t="n">
-        <v>452.82</v>
+        <v>452.75</v>
       </c>
       <c r="P44" t="n">
         <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>58.07</v>
+        <v>58.04</v>
       </c>
       <c r="R44" t="n">
-        <v>-1.11</v>
+        <v>-1.12</v>
       </c>
       <c r="S44" t="n">
-        <v>-8.880000000000001</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1465</v>
+        <v>1465.01</v>
       </c>
       <c r="D45" t="n">
         <v>61</v>
@@ -5401,10 +5401,10 @@
         <v>-1.2</v>
       </c>
       <c r="H45" t="n">
-        <v>-8.75</v>
+        <v>-8.68</v>
       </c>
       <c r="I45" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="J45" t="n">
         <v>67.13</v>
@@ -5413,16 +5413,16 @@
         <v>4.58</v>
       </c>
       <c r="L45" t="n">
-        <v>1441.5</v>
+        <v>1441.51</v>
       </c>
       <c r="M45" t="n">
-        <v>1475.07</v>
+        <v>1475.08</v>
       </c>
       <c r="N45" t="n">
-        <v>1374.37</v>
+        <v>1374.38</v>
       </c>
       <c r="O45" t="n">
-        <v>1612.69</v>
+        <v>1612.7</v>
       </c>
       <c r="P45" t="n">
         <v>1.63</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5495,55 +5495,55 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>405.04</v>
+        <v>404.35</v>
       </c>
       <c r="D46" t="n">
         <v>71</v>
       </c>
       <c r="E46" t="n">
-        <v>-6.56</v>
+        <v>-6.71</v>
       </c>
       <c r="F46" t="n">
-        <v>4.82</v>
+        <v>4.64</v>
       </c>
       <c r="G46" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="H46" t="n">
-        <v>-4.56</v>
+        <v>-4.67</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="J46" t="n">
         <v>18.51</v>
       </c>
       <c r="K46" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="L46" t="n">
-        <v>398.55</v>
+        <v>397.87</v>
       </c>
       <c r="M46" t="n">
-        <v>407.81</v>
+        <v>407.13</v>
       </c>
       <c r="N46" t="n">
-        <v>380.04</v>
+        <v>379.35</v>
       </c>
       <c r="O46" t="n">
-        <v>445.77</v>
+        <v>445.08</v>
       </c>
       <c r="P46" t="n">
         <v>1.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>61.34</v>
+        <v>61.05</v>
       </c>
       <c r="R46" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="S46" t="n">
-        <v>-10.67</v>
+        <v>-10.82</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -5604,25 +5604,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>863.55</v>
+        <v>864.59</v>
       </c>
       <c r="D47" t="n">
         <v>68</v>
       </c>
       <c r="E47" t="n">
-        <v>-5.33</v>
+        <v>-5.21</v>
       </c>
       <c r="F47" t="n">
-        <v>7.88</v>
+        <v>8.01</v>
       </c>
       <c r="G47" t="n">
-        <v>14.37</v>
+        <v>14.51</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="I47" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="J47" t="n">
         <v>34.12</v>
@@ -5631,28 +5631,28 @@
         <v>3.95</v>
       </c>
       <c r="L47" t="n">
-        <v>851.61</v>
+        <v>852.65</v>
       </c>
       <c r="M47" t="n">
-        <v>868.67</v>
+        <v>869.71</v>
       </c>
       <c r="N47" t="n">
-        <v>817.48</v>
+        <v>818.52</v>
       </c>
       <c r="O47" t="n">
-        <v>938.62</v>
+        <v>939.66</v>
       </c>
       <c r="P47" t="n">
         <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>58.66</v>
+        <v>58.82</v>
       </c>
       <c r="R47" t="n">
-        <v>-1.24</v>
+        <v>-1.13</v>
       </c>
       <c r="S47" t="n">
-        <v>-7.28</v>
+        <v>-7.17</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5713,22 +5713,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>183.44</v>
+        <v>183.2</v>
       </c>
       <c r="D48" t="n">
         <v>63</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.81</v>
+        <v>-1.94</v>
       </c>
       <c r="F48" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="G48" t="n">
-        <v>30.27</v>
+        <v>30.1</v>
       </c>
       <c r="H48" t="n">
-        <v>-8.130000000000001</v>
+        <v>-8.19</v>
       </c>
       <c r="I48" t="n">
         <v>0.42</v>
@@ -5737,31 +5737,31 @@
         <v>9.34</v>
       </c>
       <c r="K48" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="L48" t="n">
-        <v>180.17</v>
+        <v>179.93</v>
       </c>
       <c r="M48" t="n">
-        <v>184.84</v>
+        <v>184.6</v>
       </c>
       <c r="N48" t="n">
-        <v>170.83</v>
+        <v>170.59</v>
       </c>
       <c r="O48" t="n">
-        <v>203.98</v>
+        <v>203.74</v>
       </c>
       <c r="P48" t="n">
         <v>1.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>64.62</v>
+        <v>64.39</v>
       </c>
       <c r="R48" t="n">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="S48" t="n">
-        <v>-8.6</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -5822,22 +5822,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>177.41</v>
+        <v>177.46</v>
       </c>
       <c r="D49" t="n">
         <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="F49" t="n">
-        <v>-8.75</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>-11.07</v>
+        <v>-11.04</v>
       </c>
       <c r="H49" t="n">
-        <v>-18.13</v>
+        <v>-18.03</v>
       </c>
       <c r="I49" t="n">
         <v>0.86</v>
@@ -5846,31 +5846,31 @@
         <v>7.57</v>
       </c>
       <c r="K49" t="n">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
       <c r="L49" t="n">
-        <v>174.76</v>
+        <v>174.82</v>
       </c>
       <c r="M49" t="n">
-        <v>178.55</v>
+        <v>178.6</v>
       </c>
       <c r="N49" t="n">
-        <v>167.19</v>
+        <v>167.25</v>
       </c>
       <c r="O49" t="n">
-        <v>194.06</v>
+        <v>194.11</v>
       </c>
       <c r="P49" t="n">
         <v>1.63</v>
       </c>
       <c r="Q49" t="n">
-        <v>47.32</v>
+        <v>47.37</v>
       </c>
       <c r="R49" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="S49" t="n">
-        <v>-8.91</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -5931,22 +5931,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>111.86</v>
+        <v>112.23</v>
       </c>
       <c r="D50" t="n">
         <v>73</v>
       </c>
       <c r="E50" t="n">
-        <v>-7.25</v>
+        <v>-6.95</v>
       </c>
       <c r="F50" t="n">
-        <v>68.81999999999999</v>
+        <v>69.38</v>
       </c>
       <c r="G50" t="n">
-        <v>156.38</v>
+        <v>157.23</v>
       </c>
       <c r="H50" t="n">
-        <v>59.44</v>
+        <v>60.07</v>
       </c>
       <c r="I50" t="n">
         <v>0.67</v>
@@ -5955,31 +5955,31 @@
         <v>9.710000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>8.68</v>
+        <v>8.66</v>
       </c>
       <c r="L50" t="n">
-        <v>108.46</v>
+        <v>108.83</v>
       </c>
       <c r="M50" t="n">
-        <v>113.32</v>
+        <v>113.69</v>
       </c>
       <c r="N50" t="n">
-        <v>98.75</v>
+        <v>99.11</v>
       </c>
       <c r="O50" t="n">
-        <v>133.23</v>
+        <v>133.6</v>
       </c>
       <c r="P50" t="n">
         <v>1.63</v>
       </c>
       <c r="Q50" t="n">
-        <v>61.46</v>
+        <v>61.65</v>
       </c>
       <c r="R50" t="n">
-        <v>9.69</v>
+        <v>10.03</v>
       </c>
       <c r="S50" t="n">
-        <v>-15.74</v>
+        <v>-15.46</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6044,25 +6044,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>418.31</v>
+        <v>418.18</v>
       </c>
       <c r="D51" t="n">
         <v>66</v>
       </c>
       <c r="E51" t="n">
-        <v>-6.69</v>
+        <v>-6.72</v>
       </c>
       <c r="F51" t="n">
-        <v>47.04</v>
+        <v>46.99</v>
       </c>
       <c r="G51" t="n">
-        <v>112.77</v>
+        <v>112.71</v>
       </c>
       <c r="H51" t="n">
-        <v>37.66</v>
+        <v>37.68</v>
       </c>
       <c r="I51" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="J51" t="n">
         <v>29.02</v>
@@ -6071,28 +6071,28 @@
         <v>6.94</v>
       </c>
       <c r="L51" t="n">
-        <v>408.15</v>
+        <v>408.02</v>
       </c>
       <c r="M51" t="n">
-        <v>422.66</v>
+        <v>422.53</v>
       </c>
       <c r="N51" t="n">
-        <v>379.14</v>
+        <v>379.01</v>
       </c>
       <c r="O51" t="n">
-        <v>482.14</v>
+        <v>482.01</v>
       </c>
       <c r="P51" t="n">
         <v>1.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>67.31999999999999</v>
+        <v>67.28</v>
       </c>
       <c r="R51" t="n">
-        <v>8.449999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="S51" t="n">
-        <v>-10.85</v>
+        <v>-10.88</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>677.05</v>
+        <v>677.03</v>
       </c>
       <c r="D52" t="n">
         <v>70</v>
@@ -6172,7 +6172,7 @@
         <v>8.210000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>-4.78</v>
+        <v>-4.71</v>
       </c>
       <c r="I52" t="n">
         <v>0.62</v>
@@ -6184,25 +6184,25 @@
         <v>1.03</v>
       </c>
       <c r="L52" t="n">
-        <v>674.62</v>
+        <v>674.6</v>
       </c>
       <c r="M52" t="n">
-        <v>678.09</v>
+        <v>678.0700000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>667.66</v>
+        <v>667.64</v>
       </c>
       <c r="O52" t="n">
-        <v>692.34</v>
+        <v>692.3200000000001</v>
       </c>
       <c r="P52" t="n">
         <v>1.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>70.77</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="R52" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S52" t="n">
         <v>-1.75</v>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>736.42</v>
+        <v>736.41</v>
       </c>
       <c r="D53" t="n">
         <v>70</v>
@@ -6281,7 +6281,7 @@
         <v>8.210000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>-4.79</v>
+        <v>-4.72</v>
       </c>
       <c r="I53" t="n">
         <v>0.65</v>
@@ -6293,22 +6293,22 @@
         <v>1.03</v>
       </c>
       <c r="L53" t="n">
-        <v>733.76</v>
+        <v>733.75</v>
       </c>
       <c r="M53" t="n">
-        <v>737.5599999999999</v>
+        <v>737.55</v>
       </c>
       <c r="N53" t="n">
-        <v>726.1799999999999</v>
+        <v>726.17</v>
       </c>
       <c r="O53" t="n">
-        <v>753.11</v>
+        <v>753.1</v>
       </c>
       <c r="P53" t="n">
         <v>1.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>70.58</v>
+        <v>70.56</v>
       </c>
       <c r="R53" t="n">
         <v>1.31</v>
@@ -6375,55 +6375,55 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>476.57</v>
+        <v>477.59</v>
       </c>
       <c r="D54" t="n">
         <v>69</v>
       </c>
       <c r="E54" t="n">
-        <v>-2.88</v>
+        <v>-2.67</v>
       </c>
       <c r="F54" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="G54" t="n">
-        <v>25.21</v>
+        <v>25.48</v>
       </c>
       <c r="H54" t="n">
-        <v>-8.66</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J54" t="n">
         <v>31.35</v>
       </c>
       <c r="K54" t="n">
-        <v>6.58</v>
+        <v>6.56</v>
       </c>
       <c r="L54" t="n">
-        <v>465.59</v>
+        <v>466.62</v>
       </c>
       <c r="M54" t="n">
-        <v>481.27</v>
+        <v>482.29</v>
       </c>
       <c r="N54" t="n">
-        <v>434.25</v>
+        <v>435.27</v>
       </c>
       <c r="O54" t="n">
-        <v>545.53</v>
+        <v>546.55</v>
       </c>
       <c r="P54" t="n">
         <v>1.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>57.03</v>
+        <v>57.28</v>
       </c>
       <c r="R54" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="S54" t="n">
-        <v>-7.53</v>
+        <v>-7.33</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -6484,22 +6484,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>44.65</v>
+        <v>44.62</v>
       </c>
       <c r="D55" t="n">
         <v>62</v>
       </c>
       <c r="E55" t="n">
-        <v>-4.99</v>
+        <v>-5.07</v>
       </c>
       <c r="F55" t="n">
-        <v>13.28</v>
+        <v>13.18</v>
       </c>
       <c r="G55" t="n">
-        <v>16.81</v>
+        <v>16.71</v>
       </c>
       <c r="H55" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="I55" t="n">
         <v>0.34</v>
@@ -6511,28 +6511,28 @@
         <v>3.05</v>
       </c>
       <c r="L55" t="n">
-        <v>44.18</v>
+        <v>44.14</v>
       </c>
       <c r="M55" t="n">
-        <v>44.86</v>
+        <v>44.82</v>
       </c>
       <c r="N55" t="n">
-        <v>42.82</v>
+        <v>42.78</v>
       </c>
       <c r="O55" t="n">
-        <v>47.65</v>
+        <v>47.61</v>
       </c>
       <c r="P55" t="n">
         <v>1.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>71.90000000000001</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="R55" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S55" t="n">
-        <v>-6.56</v>
+        <v>-6.64</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6593,25 +6593,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>303.75</v>
+        <v>304.07</v>
       </c>
       <c r="D56" t="n">
         <v>81</v>
       </c>
       <c r="E56" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="F56" t="n">
-        <v>30.94</v>
+        <v>31.08</v>
       </c>
       <c r="G56" t="n">
-        <v>38.86</v>
+        <v>39</v>
       </c>
       <c r="H56" t="n">
-        <v>21.56</v>
+        <v>21.77</v>
       </c>
       <c r="I56" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="J56" t="n">
         <v>10.22</v>
@@ -6620,28 +6620,28 @@
         <v>3.36</v>
       </c>
       <c r="L56" t="n">
-        <v>300.17</v>
+        <v>300.49</v>
       </c>
       <c r="M56" t="n">
-        <v>305.28</v>
+        <v>305.6</v>
       </c>
       <c r="N56" t="n">
-        <v>289.96</v>
+        <v>290.28</v>
       </c>
       <c r="O56" t="n">
-        <v>326.23</v>
+        <v>326.55</v>
       </c>
       <c r="P56" t="n">
         <v>1.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>77.61</v>
+        <v>77.72</v>
       </c>
       <c r="R56" t="n">
-        <v>6.8</v>
+        <v>6.91</v>
       </c>
       <c r="S56" t="n">
-        <v>-2.11</v>
+        <v>-2</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -6706,55 +6706,55 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>717.52</v>
+        <v>717.8</v>
       </c>
       <c r="D57" t="n">
         <v>80</v>
       </c>
       <c r="E57" t="n">
-        <v>-6.4</v>
+        <v>-6.36</v>
       </c>
       <c r="F57" t="n">
-        <v>59.67</v>
+        <v>59.73</v>
       </c>
       <c r="G57" t="n">
-        <v>70.52</v>
+        <v>70.58</v>
       </c>
       <c r="H57" t="n">
-        <v>50.29</v>
+        <v>50.42</v>
       </c>
       <c r="I57" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="J57" t="n">
         <v>60.9</v>
       </c>
       <c r="K57" t="n">
-        <v>8.49</v>
+        <v>8.48</v>
       </c>
       <c r="L57" t="n">
-        <v>696.2</v>
+        <v>696.48</v>
       </c>
       <c r="M57" t="n">
-        <v>726.66</v>
+        <v>726.9400000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>635.3</v>
+        <v>635.58</v>
       </c>
       <c r="O57" t="n">
-        <v>851.51</v>
+        <v>851.79</v>
       </c>
       <c r="P57" t="n">
         <v>1.63</v>
       </c>
       <c r="Q57" t="n">
-        <v>68.31999999999999</v>
+        <v>68.34</v>
       </c>
       <c r="R57" t="n">
-        <v>13.76</v>
+        <v>13.8</v>
       </c>
       <c r="S57" t="n">
-        <v>-12.36</v>
+        <v>-12.32</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6815,22 +6815,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1014.31</v>
+        <v>1015.72</v>
       </c>
       <c r="D58" t="n">
         <v>93</v>
       </c>
       <c r="E58" t="n">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="F58" t="n">
-        <v>12.52</v>
+        <v>12.67</v>
       </c>
       <c r="G58" t="n">
-        <v>-4.02</v>
+        <v>-3.88</v>
       </c>
       <c r="H58" t="n">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="I58" t="n">
         <v>0.53</v>
@@ -6842,28 +6842,28 @@
         <v>3.37</v>
       </c>
       <c r="L58" t="n">
-        <v>1002.33</v>
+        <v>1003.75</v>
       </c>
       <c r="M58" t="n">
-        <v>1019.44</v>
+        <v>1020.86</v>
       </c>
       <c r="N58" t="n">
-        <v>968.11</v>
+        <v>969.53</v>
       </c>
       <c r="O58" t="n">
-        <v>1089.59</v>
+        <v>1091.01</v>
       </c>
       <c r="P58" t="n">
         <v>1.63</v>
       </c>
       <c r="Q58" t="n">
-        <v>77.7</v>
+        <v>77.8</v>
       </c>
       <c r="R58" t="n">
-        <v>6.54</v>
+        <v>6.68</v>
       </c>
       <c r="S58" t="n">
-        <v>-0.71</v>
+        <v>-0.57</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6928,25 +6928,25 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>298.39</v>
+        <v>298.21</v>
       </c>
       <c r="D59" t="n">
         <v>93</v>
       </c>
       <c r="E59" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="F59" t="n">
-        <v>12.21</v>
+        <v>12.14</v>
       </c>
       <c r="G59" t="n">
-        <v>12.2</v>
+        <v>12.14</v>
       </c>
       <c r="H59" t="n">
         <v>2.83</v>
       </c>
       <c r="I59" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J59" t="n">
         <v>6.68</v>
@@ -6955,28 +6955,28 @@
         <v>2.24</v>
       </c>
       <c r="L59" t="n">
-        <v>296.05</v>
+        <v>295.87</v>
       </c>
       <c r="M59" t="n">
-        <v>299.39</v>
+        <v>299.21</v>
       </c>
       <c r="N59" t="n">
-        <v>289.37</v>
+        <v>289.19</v>
       </c>
       <c r="O59" t="n">
-        <v>313.1</v>
+        <v>312.92</v>
       </c>
       <c r="P59" t="n">
         <v>1.63</v>
       </c>
       <c r="Q59" t="n">
-        <v>83.84</v>
+        <v>83.77</v>
       </c>
       <c r="R59" t="n">
-        <v>4.98</v>
+        <v>4.92</v>
       </c>
       <c r="S59" t="n">
-        <v>-1.59</v>
+        <v>-1.65</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -7041,25 +7041,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1088.59</v>
+        <v>1088.14</v>
       </c>
       <c r="D60" t="n">
         <v>87</v>
       </c>
       <c r="E60" t="n">
-        <v>6.53</v>
+        <v>6.48</v>
       </c>
       <c r="F60" t="n">
-        <v>8.390000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="G60" t="n">
-        <v>10.56</v>
+        <v>10.52</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.99</v>
+        <v>-0.97</v>
       </c>
       <c r="I60" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="J60" t="n">
         <v>21.81</v>
@@ -7068,28 +7068,28 @@
         <v>2</v>
       </c>
       <c r="L60" t="n">
-        <v>1080.96</v>
+        <v>1080.51</v>
       </c>
       <c r="M60" t="n">
-        <v>1091.86</v>
+        <v>1091.41</v>
       </c>
       <c r="N60" t="n">
-        <v>1059.15</v>
+        <v>1058.7</v>
       </c>
       <c r="O60" t="n">
-        <v>1136.57</v>
+        <v>1136.12</v>
       </c>
       <c r="P60" t="n">
         <v>1.63</v>
       </c>
       <c r="Q60" t="n">
-        <v>78.44</v>
+        <v>78.38</v>
       </c>
       <c r="R60" t="n">
-        <v>6.77</v>
+        <v>6.73</v>
       </c>
       <c r="S60" t="n">
-        <v>-0.72</v>
+        <v>-0.76</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7150,25 +7150,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>174.25</v>
+        <v>174.31</v>
       </c>
       <c r="D61" t="n">
         <v>71</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.54</v>
+        <v>-0.51</v>
       </c>
       <c r="F61" t="n">
-        <v>12.64</v>
+        <v>12.68</v>
       </c>
       <c r="G61" t="n">
-        <v>25.95</v>
+        <v>25.99</v>
       </c>
       <c r="H61" t="n">
-        <v>3.26</v>
+        <v>3.37</v>
       </c>
       <c r="I61" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="J61" t="n">
         <v>4.08</v>
@@ -7177,28 +7177,28 @@
         <v>2.34</v>
       </c>
       <c r="L61" t="n">
-        <v>172.82</v>
+        <v>172.88</v>
       </c>
       <c r="M61" t="n">
-        <v>174.86</v>
+        <v>174.92</v>
       </c>
       <c r="N61" t="n">
-        <v>168.74</v>
+        <v>168.8</v>
       </c>
       <c r="O61" t="n">
-        <v>183.23</v>
+        <v>183.29</v>
       </c>
       <c r="P61" t="n">
         <v>1.63</v>
       </c>
       <c r="Q61" t="n">
-        <v>73.90000000000001</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="R61" t="n">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
       <c r="S61" t="n">
-        <v>-3.31</v>
+        <v>-3.28</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -7259,55 +7259,55 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>126.79</v>
+        <v>127.14</v>
       </c>
       <c r="D62" t="n">
         <v>70</v>
       </c>
       <c r="E62" t="n">
-        <v>7.85</v>
+        <v>8.15</v>
       </c>
       <c r="F62" t="n">
-        <v>46.34</v>
+        <v>46.75</v>
       </c>
       <c r="G62" t="n">
-        <v>80.58</v>
+        <v>81.09</v>
       </c>
       <c r="H62" t="n">
-        <v>36.96</v>
+        <v>37.44</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="J62" t="n">
         <v>11.09</v>
       </c>
       <c r="K62" t="n">
-        <v>8.75</v>
+        <v>8.73</v>
       </c>
       <c r="L62" t="n">
-        <v>122.9</v>
+        <v>123.26</v>
       </c>
       <c r="M62" t="n">
-        <v>128.45</v>
+        <v>128.8</v>
       </c>
       <c r="N62" t="n">
-        <v>111.81</v>
+        <v>112.16</v>
       </c>
       <c r="O62" t="n">
-        <v>151.19</v>
+        <v>151.54</v>
       </c>
       <c r="P62" t="n">
         <v>1.63</v>
       </c>
       <c r="Q62" t="n">
-        <v>75.73</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="R62" t="n">
-        <v>29.66</v>
+        <v>30</v>
       </c>
       <c r="S62" t="n">
-        <v>-8.380000000000001</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7368,25 +7368,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>126.4</v>
+        <v>126.33</v>
       </c>
       <c r="D63" t="n">
         <v>67</v>
       </c>
       <c r="E63" t="n">
-        <v>11</v>
+        <v>10.95</v>
       </c>
       <c r="F63" t="n">
-        <v>48.25</v>
+        <v>48.18</v>
       </c>
       <c r="G63" t="n">
-        <v>67.2</v>
+        <v>67.11</v>
       </c>
       <c r="H63" t="n">
         <v>38.87</v>
       </c>
       <c r="I63" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>5.47</v>
@@ -7395,28 +7395,28 @@
         <v>4.33</v>
       </c>
       <c r="L63" t="n">
-        <v>124.49</v>
+        <v>124.42</v>
       </c>
       <c r="M63" t="n">
-        <v>127.22</v>
+        <v>127.16</v>
       </c>
       <c r="N63" t="n">
-        <v>119.02</v>
+        <v>118.95</v>
       </c>
       <c r="O63" t="n">
-        <v>138.43</v>
+        <v>138.36</v>
       </c>
       <c r="P63" t="n">
         <v>1.63</v>
       </c>
       <c r="Q63" t="n">
-        <v>92.65000000000001</v>
+        <v>92.53</v>
       </c>
       <c r="R63" t="n">
-        <v>25.27</v>
+        <v>25.21</v>
       </c>
       <c r="S63" t="n">
-        <v>-1.36</v>
+        <v>-1.41</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -7477,55 +7477,55 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>333</v>
+        <v>334.33</v>
       </c>
       <c r="D64" t="n">
         <v>66</v>
       </c>
       <c r="E64" t="n">
-        <v>7.87</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F64" t="n">
-        <v>27.38</v>
+        <v>27.89</v>
       </c>
       <c r="G64" t="n">
-        <v>9.050000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="H64" t="n">
-        <v>18</v>
+        <v>18.58</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J64" t="n">
         <v>18.41</v>
       </c>
       <c r="K64" t="n">
-        <v>5.53</v>
+        <v>5.51</v>
       </c>
       <c r="L64" t="n">
-        <v>326.56</v>
+        <v>327.89</v>
       </c>
       <c r="M64" t="n">
-        <v>335.76</v>
+        <v>337.09</v>
       </c>
       <c r="N64" t="n">
-        <v>308.15</v>
+        <v>309.48</v>
       </c>
       <c r="O64" t="n">
-        <v>373.5</v>
+        <v>374.83</v>
       </c>
       <c r="P64" t="n">
         <v>1.63</v>
       </c>
       <c r="Q64" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="R64" t="n">
-        <v>17.87</v>
+        <v>18.31</v>
       </c>
       <c r="S64" t="n">
-        <v>-4.64</v>
+        <v>-4.26</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -7586,25 +7586,25 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>211.69</v>
+        <v>211.73</v>
       </c>
       <c r="D65" t="n">
         <v>64</v>
       </c>
       <c r="E65" t="n">
-        <v>5.88</v>
+        <v>5.9</v>
       </c>
       <c r="F65" t="n">
-        <v>63.73</v>
+        <v>63.76</v>
       </c>
       <c r="G65" t="n">
-        <v>106.3</v>
+        <v>106.33</v>
       </c>
       <c r="H65" t="n">
-        <v>54.35</v>
+        <v>54.45</v>
       </c>
       <c r="I65" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="J65" t="n">
         <v>12.28</v>
@@ -7613,16 +7613,16 @@
         <v>5.8</v>
       </c>
       <c r="L65" t="n">
-        <v>207.39</v>
+        <v>207.43</v>
       </c>
       <c r="M65" t="n">
-        <v>213.53</v>
+        <v>213.57</v>
       </c>
       <c r="N65" t="n">
-        <v>195.11</v>
+        <v>195.15</v>
       </c>
       <c r="O65" t="n">
-        <v>238.71</v>
+        <v>238.75</v>
       </c>
       <c r="P65" t="n">
         <v>1.63</v>
@@ -7631,10 +7631,10 @@
         <v>90.08</v>
       </c>
       <c r="R65" t="n">
-        <v>27.36</v>
+        <v>27.38</v>
       </c>
       <c r="S65" t="n">
-        <v>-1.63</v>
+        <v>-1.61</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -7695,22 +7695,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>704.62</v>
+        <v>704.5700000000001</v>
       </c>
       <c r="D66" t="n">
         <v>63</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.37</v>
+        <v>-0.38</v>
       </c>
       <c r="F66" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="G66" t="n">
-        <v>17.31</v>
+        <v>17.3</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I66" t="n">
         <v>0.86</v>
@@ -7722,28 +7722,28 @@
         <v>1.6</v>
       </c>
       <c r="L66" t="n">
-        <v>700.67</v>
+        <v>700.62</v>
       </c>
       <c r="M66" t="n">
-        <v>706.3099999999999</v>
+        <v>706.26</v>
       </c>
       <c r="N66" t="n">
-        <v>689.38</v>
+        <v>689.33</v>
       </c>
       <c r="O66" t="n">
-        <v>729.45</v>
+        <v>729.4</v>
       </c>
       <c r="P66" t="n">
         <v>1.63</v>
       </c>
       <c r="Q66" t="n">
-        <v>74</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="R66" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="S66" t="n">
-        <v>-2.41</v>
+        <v>-2.42</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7804,25 +7804,25 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>102.64</v>
+        <v>102.79</v>
       </c>
       <c r="D67" t="n">
         <v>62</v>
       </c>
       <c r="E67" t="n">
-        <v>15.33</v>
+        <v>15.49</v>
       </c>
       <c r="F67" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="G67" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="H67" t="n">
-        <v>-6.88</v>
+        <v>-6.67</v>
       </c>
       <c r="I67" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="J67" t="n">
         <v>5.33</v>
@@ -7831,28 +7831,28 @@
         <v>5.19</v>
       </c>
       <c r="L67" t="n">
-        <v>100.78</v>
+        <v>100.92</v>
       </c>
       <c r="M67" t="n">
-        <v>103.44</v>
+        <v>103.58</v>
       </c>
       <c r="N67" t="n">
-        <v>95.45</v>
+        <v>95.59</v>
       </c>
       <c r="O67" t="n">
-        <v>114.38</v>
+        <v>114.52</v>
       </c>
       <c r="P67" t="n">
         <v>1.63</v>
       </c>
       <c r="Q67" t="n">
-        <v>69.06</v>
+        <v>69.33</v>
       </c>
       <c r="R67" t="n">
-        <v>11.31</v>
+        <v>11.45</v>
       </c>
       <c r="S67" t="n">
-        <v>-7.37</v>
+        <v>-7.24</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -7913,25 +7913,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>112.07</v>
+        <v>112.12</v>
       </c>
       <c r="D68" t="n">
         <v>60</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.2</v>
+        <v>-0.16</v>
       </c>
       <c r="F68" t="n">
-        <v>10.94</v>
+        <v>10.99</v>
       </c>
       <c r="G68" t="n">
-        <v>23.48</v>
+        <v>23.53</v>
       </c>
       <c r="H68" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="I68" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="J68" t="n">
         <v>2.44</v>
@@ -7940,28 +7940,28 @@
         <v>2.17</v>
       </c>
       <c r="L68" t="n">
-        <v>111.22</v>
+        <v>111.27</v>
       </c>
       <c r="M68" t="n">
-        <v>112.44</v>
+        <v>112.49</v>
       </c>
       <c r="N68" t="n">
-        <v>108.78</v>
+        <v>108.83</v>
       </c>
       <c r="O68" t="n">
-        <v>117.43</v>
+        <v>117.48</v>
       </c>
       <c r="P68" t="n">
         <v>1.63</v>
       </c>
       <c r="Q68" t="n">
-        <v>74.64</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="R68" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="S68" t="n">
-        <v>-3.07</v>
+        <v>-3.03</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -8022,55 +8022,55 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>247.11</v>
+        <v>246.6</v>
       </c>
       <c r="D69" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E69" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>-3.92</v>
+        <v>-4.12</v>
       </c>
       <c r="G69" t="n">
-        <v>10.89</v>
+        <v>10.67</v>
       </c>
       <c r="H69" t="n">
-        <v>-13.3</v>
+        <v>-13.43</v>
       </c>
       <c r="I69" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="J69" t="n">
         <v>7.99</v>
       </c>
       <c r="K69" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="L69" t="n">
-        <v>244.31</v>
+        <v>243.8</v>
       </c>
       <c r="M69" t="n">
-        <v>248.31</v>
+        <v>247.8</v>
       </c>
       <c r="N69" t="n">
-        <v>236.33</v>
+        <v>235.82</v>
       </c>
       <c r="O69" t="n">
-        <v>264.68</v>
+        <v>264.17</v>
       </c>
       <c r="P69" t="n">
         <v>1.63</v>
       </c>
       <c r="Q69" t="n">
-        <v>30.16</v>
+        <v>29.91</v>
       </c>
       <c r="R69" t="n">
-        <v>-3.06</v>
+        <v>-3.25</v>
       </c>
       <c r="S69" t="n">
-        <v>-10.08</v>
+        <v>-10.27</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>XLE 9.61% · CL=F 12.07%</t>
+          <t>XLE 9.63% · CL=F 12.07%</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -8097,11 +8097,7 @@
           <t>BAJO</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
@@ -8114,7 +8110,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.61% · CL=F 12.07%; Tendencia larga positiva; MACD mejorando; Momentum 5D sano</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.63% · CL=F 12.07%; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8135,22 +8131,22 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1751.64</v>
+        <v>1752.81</v>
       </c>
       <c r="D70" t="n">
         <v>33</v>
       </c>
       <c r="E70" t="n">
-        <v>-3.17</v>
+        <v>-3.11</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.76</v>
+        <v>-1.7</v>
       </c>
       <c r="G70" t="n">
-        <v>17.89</v>
+        <v>17.97</v>
       </c>
       <c r="H70" t="n">
-        <v>-11.14</v>
+        <v>-11.01</v>
       </c>
       <c r="I70" t="n">
         <v>0.48</v>
@@ -8159,31 +8155,31 @@
         <v>86.64</v>
       </c>
       <c r="K70" t="n">
-        <v>4.95</v>
+        <v>4.94</v>
       </c>
       <c r="L70" t="n">
-        <v>1721.32</v>
+        <v>1722.49</v>
       </c>
       <c r="M70" t="n">
-        <v>1764.64</v>
+        <v>1765.81</v>
       </c>
       <c r="N70" t="n">
-        <v>1634.68</v>
+        <v>1635.85</v>
       </c>
       <c r="O70" t="n">
-        <v>1942.24</v>
+        <v>1943.41</v>
       </c>
       <c r="P70" t="n">
         <v>1.63</v>
       </c>
       <c r="Q70" t="n">
-        <v>45.16</v>
+        <v>45.24</v>
       </c>
       <c r="R70" t="n">
-        <v>-3.03</v>
+        <v>-2.97</v>
       </c>
       <c r="S70" t="n">
-        <v>-9.56</v>
+        <v>-9.5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8202,7 +8198,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -8223,7 +8219,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -8244,55 +8240,55 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1476.12</v>
+        <v>1472.91</v>
       </c>
       <c r="D71" t="n">
         <v>33</v>
       </c>
       <c r="E71" t="n">
-        <v>-7.71</v>
+        <v>-7.92</v>
       </c>
       <c r="F71" t="n">
-        <v>-3.39</v>
+        <v>-3.6</v>
       </c>
       <c r="G71" t="n">
-        <v>24.29</v>
+        <v>24.02</v>
       </c>
       <c r="H71" t="n">
-        <v>-12.77</v>
+        <v>-12.91</v>
       </c>
       <c r="I71" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="J71" t="n">
         <v>79.84</v>
       </c>
       <c r="K71" t="n">
-        <v>5.41</v>
+        <v>5.42</v>
       </c>
       <c r="L71" t="n">
-        <v>1448.18</v>
+        <v>1444.97</v>
       </c>
       <c r="M71" t="n">
-        <v>1488.1</v>
+        <v>1484.89</v>
       </c>
       <c r="N71" t="n">
-        <v>1368.34</v>
+        <v>1365.13</v>
       </c>
       <c r="O71" t="n">
-        <v>1651.76</v>
+        <v>1648.55</v>
       </c>
       <c r="P71" t="n">
         <v>1.63</v>
       </c>
       <c r="Q71" t="n">
-        <v>46.13</v>
+        <v>45.91</v>
       </c>
       <c r="R71" t="n">
-        <v>-6.55</v>
+        <v>-6.74</v>
       </c>
       <c r="S71" t="n">
-        <v>-11.9</v>
+        <v>-12.09</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8311,7 +8307,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -8332,7 +8328,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8353,22 +8349,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>274.63</v>
+        <v>274.48</v>
       </c>
       <c r="D72" t="n">
         <v>58</v>
       </c>
       <c r="E72" t="n">
-        <v>-5.05</v>
+        <v>-5.1</v>
       </c>
       <c r="F72" t="n">
-        <v>6.29</v>
+        <v>6.24</v>
       </c>
       <c r="G72" t="n">
-        <v>13.49</v>
+        <v>13.43</v>
       </c>
       <c r="H72" t="n">
-        <v>-3.09</v>
+        <v>-3.07</v>
       </c>
       <c r="I72" t="n">
         <v>0.53</v>
@@ -8380,28 +8376,28 @@
         <v>5.29</v>
       </c>
       <c r="L72" t="n">
-        <v>269.55</v>
+        <v>269.4</v>
       </c>
       <c r="M72" t="n">
-        <v>276.81</v>
+        <v>276.66</v>
       </c>
       <c r="N72" t="n">
-        <v>255.02</v>
+        <v>254.87</v>
       </c>
       <c r="O72" t="n">
-        <v>306.59</v>
+        <v>306.44</v>
       </c>
       <c r="P72" t="n">
         <v>1.63</v>
       </c>
       <c r="Q72" t="n">
-        <v>61.54</v>
+        <v>61.46</v>
       </c>
       <c r="R72" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="S72" t="n">
-        <v>-9.06</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8462,22 +8458,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>88.69</v>
+        <v>88.61</v>
       </c>
       <c r="D73" t="n">
         <v>56</v>
       </c>
       <c r="E73" t="n">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="F73" t="n">
-        <v>-4.35</v>
+        <v>-4.43</v>
       </c>
       <c r="G73" t="n">
-        <v>-22.59</v>
+        <v>-22.66</v>
       </c>
       <c r="H73" t="n">
-        <v>-13.73</v>
+        <v>-13.74</v>
       </c>
       <c r="I73" t="n">
         <v>0.46</v>
@@ -8489,28 +8485,28 @@
         <v>2.41</v>
       </c>
       <c r="L73" t="n">
-        <v>87.94</v>
+        <v>87.86</v>
       </c>
       <c r="M73" t="n">
-        <v>89.01000000000001</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="N73" t="n">
-        <v>85.81</v>
+        <v>85.73</v>
       </c>
       <c r="O73" t="n">
-        <v>93.38</v>
+        <v>93.3</v>
       </c>
       <c r="P73" t="n">
         <v>1.63</v>
       </c>
       <c r="Q73" t="n">
-        <v>42.76</v>
+        <v>42.5</v>
       </c>
       <c r="R73" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="S73" t="n">
-        <v>-6.44</v>
+        <v>-6.52</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8571,22 +8567,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>419.1</v>
+        <v>419.27</v>
       </c>
       <c r="D74" t="n">
         <v>54</v>
       </c>
       <c r="E74" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.19</v>
+        <v>-1.15</v>
       </c>
       <c r="G74" t="n">
-        <v>9.01</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>-10.57</v>
+        <v>-10.46</v>
       </c>
       <c r="I74" t="n">
         <v>0.59</v>
@@ -8598,28 +8594,28 @@
         <v>2.86</v>
       </c>
       <c r="L74" t="n">
-        <v>414.9</v>
+        <v>415.07</v>
       </c>
       <c r="M74" t="n">
-        <v>420.89</v>
+        <v>421.07</v>
       </c>
       <c r="N74" t="n">
-        <v>402.91</v>
+        <v>403.08</v>
       </c>
       <c r="O74" t="n">
-        <v>445.47</v>
+        <v>445.65</v>
       </c>
       <c r="P74" t="n">
         <v>1.63</v>
       </c>
       <c r="Q74" t="n">
-        <v>46.38</v>
+        <v>46.49</v>
       </c>
       <c r="R74" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="S74" t="n">
-        <v>-3.37</v>
+        <v>-3.33</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8638,7 +8634,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -8680,22 +8676,22 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>223.95</v>
+        <v>223.85</v>
       </c>
       <c r="D75" t="n">
         <v>52</v>
       </c>
       <c r="E75" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="F75" t="n">
-        <v>-11.77</v>
+        <v>-11.81</v>
       </c>
       <c r="G75" t="n">
-        <v>1.01</v>
+        <v>0.96</v>
       </c>
       <c r="H75" t="n">
-        <v>-21.15</v>
+        <v>-21.12</v>
       </c>
       <c r="I75" t="n">
         <v>0.36</v>
@@ -8707,28 +8703,28 @@
         <v>2.48</v>
       </c>
       <c r="L75" t="n">
-        <v>222.01</v>
+        <v>221.9</v>
       </c>
       <c r="M75" t="n">
-        <v>224.78</v>
+        <v>224.68</v>
       </c>
       <c r="N75" t="n">
-        <v>216.45</v>
+        <v>216.35</v>
       </c>
       <c r="O75" t="n">
-        <v>236.17</v>
+        <v>236.06</v>
       </c>
       <c r="P75" t="n">
         <v>1.63</v>
       </c>
       <c r="Q75" t="n">
-        <v>48.21</v>
+        <v>48.08</v>
       </c>
       <c r="R75" t="n">
-        <v>-1.19</v>
+        <v>-1.24</v>
       </c>
       <c r="S75" t="n">
-        <v>-12.4</v>
+        <v>-12.44</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8747,7 +8743,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -8789,7 +8785,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>259.26</v>
+        <v>259.27</v>
       </c>
       <c r="D76" t="n">
         <v>46</v>
@@ -8804,7 +8800,7 @@
         <v>26.3</v>
       </c>
       <c r="H76" t="n">
-        <v>-5.64</v>
+        <v>-5.57</v>
       </c>
       <c r="I76" t="n">
         <v>0.6</v>
@@ -8816,22 +8812,22 @@
         <v>2.86</v>
       </c>
       <c r="L76" t="n">
-        <v>256.66</v>
+        <v>256.67</v>
       </c>
       <c r="M76" t="n">
-        <v>260.37</v>
+        <v>260.38</v>
       </c>
       <c r="N76" t="n">
         <v>249.24</v>
       </c>
       <c r="O76" t="n">
-        <v>275.59</v>
+        <v>275.6</v>
       </c>
       <c r="P76" t="n">
         <v>1.63</v>
       </c>
       <c r="Q76" t="n">
-        <v>45.36</v>
+        <v>45.37</v>
       </c>
       <c r="R76" t="n">
         <v>-2.47</v>
@@ -8856,7 +8852,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
@@ -8898,25 +8894,25 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>274.02</v>
+        <v>274.05</v>
       </c>
       <c r="D77" t="n">
         <v>44</v>
       </c>
       <c r="E77" t="n">
-        <v>-3.03</v>
+        <v>-3.02</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="G77" t="n">
-        <v>5.38</v>
+        <v>5.39</v>
       </c>
       <c r="H77" t="n">
-        <v>-9.56</v>
+        <v>-9.48</v>
       </c>
       <c r="I77" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="J77" t="n">
         <v>4.84</v>
@@ -8925,28 +8921,28 @@
         <v>1.77</v>
       </c>
       <c r="L77" t="n">
-        <v>272.33</v>
+        <v>272.36</v>
       </c>
       <c r="M77" t="n">
-        <v>274.75</v>
+        <v>274.78</v>
       </c>
       <c r="N77" t="n">
-        <v>267.49</v>
+        <v>267.52</v>
       </c>
       <c r="O77" t="n">
-        <v>284.66</v>
+        <v>284.69</v>
       </c>
       <c r="P77" t="n">
         <v>1.63</v>
       </c>
       <c r="Q77" t="n">
-        <v>52.41</v>
+        <v>52.45</v>
       </c>
       <c r="R77" t="n">
-        <v>-1.88</v>
+        <v>-1.87</v>
       </c>
       <c r="S77" t="n">
-        <v>-4.72</v>
+        <v>-4.7</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8998,68 +8994,68 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>501.45</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="D78" t="n">
         <v>43</v>
       </c>
       <c r="E78" t="n">
-        <v>0.33</v>
+        <v>1.48</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.94</v>
+        <v>-3.92</v>
       </c>
       <c r="G78" t="n">
-        <v>1.27</v>
+        <v>17.02</v>
       </c>
       <c r="H78" t="n">
-        <v>-11.32</v>
+        <v>-13.23</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="J78" t="n">
-        <v>12.54</v>
+        <v>2.49</v>
       </c>
       <c r="K78" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="L78" t="n">
-        <v>497.06</v>
+        <v>88.08</v>
       </c>
       <c r="M78" t="n">
-        <v>503.33</v>
+        <v>89.33</v>
       </c>
       <c r="N78" t="n">
-        <v>484.53</v>
+        <v>85.59</v>
       </c>
       <c r="O78" t="n">
-        <v>529.03</v>
+        <v>94.44</v>
       </c>
       <c r="P78" t="n">
         <v>1.63</v>
       </c>
       <c r="Q78" t="n">
-        <v>38.2</v>
+        <v>40.55</v>
       </c>
       <c r="R78" t="n">
-        <v>0.05</v>
+        <v>-0.95</v>
       </c>
       <c r="S78" t="n">
-        <v>-6.13</v>
+        <v>-6.07</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>BAJA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -9069,12 +9065,12 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
@@ -9095,12 +9091,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MACD positivo; MACD mejorando</t>
+          <t>Mercado NEUTRO +; MACD positivo; MACD mejorando; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Volumen bajo; Débil vs QQQ; Lejos del máximo 20D</t>
+          <t>Precio bajo MA20; Tendencia larga débil; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -9116,25 +9112,25 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1045.29</v>
+        <v>1046</v>
       </c>
       <c r="D79" t="n">
         <v>42</v>
       </c>
       <c r="E79" t="n">
-        <v>-4.32</v>
+        <v>-4.26</v>
       </c>
       <c r="F79" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="G79" t="n">
-        <v>-1.86</v>
+        <v>-1.79</v>
       </c>
       <c r="H79" t="n">
-        <v>-9.15</v>
+        <v>-9.01</v>
       </c>
       <c r="I79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="J79" t="n">
         <v>23.77</v>
@@ -9143,28 +9139,28 @@
         <v>2.27</v>
       </c>
       <c r="L79" t="n">
-        <v>1036.97</v>
+        <v>1037.68</v>
       </c>
       <c r="M79" t="n">
-        <v>1048.85</v>
+        <v>1049.57</v>
       </c>
       <c r="N79" t="n">
-        <v>1013.19</v>
+        <v>1013.91</v>
       </c>
       <c r="O79" t="n">
-        <v>1097.58</v>
+        <v>1098.3</v>
       </c>
       <c r="P79" t="n">
         <v>1.63</v>
       </c>
       <c r="Q79" t="n">
-        <v>51.61</v>
+        <v>51.81</v>
       </c>
       <c r="R79" t="n">
-        <v>-2.06</v>
+        <v>-2</v>
       </c>
       <c r="S79" t="n">
-        <v>-5.92</v>
+        <v>-5.86</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9225,22 +9221,22 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8.789999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="D80" t="n">
         <v>42</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="F80" t="n">
-        <v>-4.46</v>
+        <v>-4.51</v>
       </c>
       <c r="G80" t="n">
-        <v>-10.21</v>
+        <v>-10.27</v>
       </c>
       <c r="H80" t="n">
-        <v>-13.84</v>
+        <v>-13.82</v>
       </c>
       <c r="I80" t="n">
         <v>0.53</v>
@@ -9255,25 +9251,25 @@
         <v>8.630000000000001</v>
       </c>
       <c r="M80" t="n">
-        <v>8.859999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="N80" t="n">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="O80" t="n">
         <v>9.789999999999999</v>
       </c>
       <c r="P80" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q80" t="n">
-        <v>48.92</v>
+        <v>48.84</v>
       </c>
       <c r="R80" t="n">
-        <v>-2.87</v>
+        <v>-2.93</v>
       </c>
       <c r="S80" t="n">
-        <v>-11.03</v>
+        <v>-11.08</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9292,7 +9288,7 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
@@ -9325,64 +9321,64 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Consumo</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>88.79000000000001</v>
+        <v>282.48</v>
       </c>
       <c r="D81" t="n">
         <v>38</v>
       </c>
       <c r="E81" t="n">
-        <v>1.28</v>
+        <v>2.78</v>
       </c>
       <c r="F81" t="n">
-        <v>-4.1</v>
+        <v>-6.41</v>
       </c>
       <c r="G81" t="n">
-        <v>16.79</v>
+        <v>-15.1</v>
       </c>
       <c r="H81" t="n">
-        <v>-13.48</v>
+        <v>-15.72</v>
       </c>
       <c r="I81" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="J81" t="n">
-        <v>2.49</v>
+        <v>5.9</v>
       </c>
       <c r="K81" t="n">
-        <v>2.81</v>
+        <v>2.09</v>
       </c>
       <c r="L81" t="n">
-        <v>87.91</v>
+        <v>280.41</v>
       </c>
       <c r="M81" t="n">
-        <v>89.16</v>
+        <v>283.37</v>
       </c>
       <c r="N81" t="n">
-        <v>85.42</v>
+        <v>274.51</v>
       </c>
       <c r="O81" t="n">
-        <v>94.27</v>
+        <v>295.47</v>
       </c>
       <c r="P81" t="n">
         <v>1.63</v>
       </c>
       <c r="Q81" t="n">
-        <v>40.14</v>
+        <v>38.82</v>
       </c>
       <c r="R81" t="n">
-        <v>-1.13</v>
+        <v>-1.04</v>
       </c>
       <c r="S81" t="n">
-        <v>-6.25</v>
+        <v>-7.35</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9396,12 +9392,12 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
@@ -9434,64 +9430,64 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>282.65</v>
+        <v>74.61</v>
       </c>
       <c r="D82" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E82" t="n">
-        <v>2.84</v>
+        <v>-2.29</v>
       </c>
       <c r="F82" t="n">
-        <v>-6.36</v>
+        <v>-3.43</v>
       </c>
       <c r="G82" t="n">
-        <v>-15.04</v>
+        <v>5.5</v>
       </c>
       <c r="H82" t="n">
-        <v>-15.74</v>
+        <v>-12.74</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="J82" t="n">
-        <v>5.9</v>
+        <v>2.58</v>
       </c>
       <c r="K82" t="n">
-        <v>2.09</v>
+        <v>3.46</v>
       </c>
       <c r="L82" t="n">
-        <v>280.58</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="M82" t="n">
-        <v>283.54</v>
+        <v>75</v>
       </c>
       <c r="N82" t="n">
-        <v>274.68</v>
+        <v>71.12</v>
       </c>
       <c r="O82" t="n">
-        <v>295.64</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="P82" t="n">
         <v>1.63</v>
       </c>
       <c r="Q82" t="n">
-        <v>39.12</v>
+        <v>50.43</v>
       </c>
       <c r="R82" t="n">
-        <v>-0.99</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="S82" t="n">
-        <v>-7.29</v>
+        <v>-7.7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9505,12 +9501,12 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -9531,76 +9527,76 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; MACD positivo; MACD mejorando; Momentum 5D sano</t>
+          <t>Mercado NEUTRO +; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; Volumen bajo; Débil vs QQQ; Lejos del máximo 20D</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>ARKK</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Innovación</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>74.59999999999999</v>
+        <v>74.38</v>
       </c>
       <c r="D83" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E83" t="n">
-        <v>-2.3</v>
+        <v>-4.9</v>
       </c>
       <c r="F83" t="n">
-        <v>-3.44</v>
+        <v>-3.88</v>
       </c>
       <c r="G83" t="n">
-        <v>5.49</v>
+        <v>6.25</v>
       </c>
       <c r="H83" t="n">
-        <v>-12.82</v>
+        <v>-13.19</v>
       </c>
       <c r="I83" t="n">
-        <v>0.59</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="K83" t="n">
-        <v>3.46</v>
+        <v>3.27</v>
       </c>
       <c r="L83" t="n">
-        <v>73.7</v>
+        <v>73.52</v>
       </c>
       <c r="M83" t="n">
-        <v>74.98999999999999</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="N83" t="n">
-        <v>71.11</v>
+        <v>71.09</v>
       </c>
       <c r="O83" t="n">
-        <v>80.28</v>
+        <v>79.73</v>
       </c>
       <c r="P83" t="n">
         <v>1.63</v>
       </c>
       <c r="Q83" t="n">
-        <v>50.4</v>
+        <v>52.25</v>
       </c>
       <c r="R83" t="n">
-        <v>-0.82</v>
+        <v>-3.42</v>
       </c>
       <c r="S83" t="n">
-        <v>-7.71</v>
+        <v>-7.82</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9619,7 +9615,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
@@ -9645,75 +9641,75 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ETF Innovación</t>
+          <t>ETF Finanzas</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>74.48999999999999</v>
+        <v>51.44</v>
       </c>
       <c r="D84" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E84" t="n">
-        <v>-4.76</v>
+        <v>-0.26</v>
       </c>
       <c r="F84" t="n">
-        <v>-3.74</v>
+        <v>-1.63</v>
       </c>
       <c r="G84" t="n">
-        <v>6.41</v>
+        <v>1.93</v>
       </c>
       <c r="H84" t="n">
-        <v>-13.12</v>
+        <v>-10.94</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="J84" t="n">
-        <v>2.44</v>
+        <v>0.65</v>
       </c>
       <c r="K84" t="n">
-        <v>3.27</v>
+        <v>1.26</v>
       </c>
       <c r="L84" t="n">
-        <v>73.63</v>
+        <v>51.22</v>
       </c>
       <c r="M84" t="n">
-        <v>74.84999999999999</v>
+        <v>51.54</v>
       </c>
       <c r="N84" t="n">
-        <v>71.2</v>
+        <v>50.57</v>
       </c>
       <c r="O84" t="n">
-        <v>79.84</v>
+        <v>52.87</v>
       </c>
       <c r="P84" t="n">
         <v>1.63</v>
       </c>
       <c r="Q84" t="n">
-        <v>52.56</v>
+        <v>44.2</v>
       </c>
       <c r="R84" t="n">
-        <v>-3.28</v>
+        <v>-0.32</v>
       </c>
       <c r="S84" t="n">
-        <v>-7.68</v>
+        <v>-2.29</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>BAJA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9723,12 +9719,12 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
@@ -9749,80 +9745,80 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado NEUTRO +; MA20 sobre MA50; MACD mejorando</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Momentum negativo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ETF Finanzas</t>
+          <t>Finanzas</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>51.47</v>
+        <v>51.15</v>
       </c>
       <c r="D85" t="n">
         <v>32</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.21</v>
+        <v>0.72</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.59</v>
+        <v>-4.37</v>
       </c>
       <c r="G85" t="n">
-        <v>1.98</v>
+        <v>0.71</v>
       </c>
       <c r="H85" t="n">
-        <v>-10.97</v>
+        <v>-13.68</v>
       </c>
       <c r="I85" t="n">
-        <v>0.57</v>
+        <v>0.78</v>
       </c>
       <c r="J85" t="n">
-        <v>0.65</v>
+        <v>1.18</v>
       </c>
       <c r="K85" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="L85" t="n">
-        <v>51.24</v>
+        <v>50.73</v>
       </c>
       <c r="M85" t="n">
-        <v>51.57</v>
+        <v>51.32</v>
       </c>
       <c r="N85" t="n">
-        <v>50.6</v>
+        <v>49.55</v>
       </c>
       <c r="O85" t="n">
-        <v>52.89</v>
+        <v>53.74</v>
       </c>
       <c r="P85" t="n">
         <v>1.63</v>
       </c>
       <c r="Q85" t="n">
-        <v>44.47</v>
+        <v>40.3</v>
       </c>
       <c r="R85" t="n">
-        <v>-0.27</v>
+        <v>-1.46</v>
       </c>
       <c r="S85" t="n">
-        <v>-2.24</v>
+        <v>-5.64</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9863,71 +9859,71 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Débil vs QQQ; Lejos del máximo 20D</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Finanzas</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>51.15</v>
+        <v>559.96</v>
       </c>
       <c r="D86" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E86" t="n">
-        <v>0.74</v>
+        <v>-4.96</v>
       </c>
       <c r="F86" t="n">
-        <v>-4.35</v>
+        <v>-4.66</v>
       </c>
       <c r="G86" t="n">
-        <v>0.73</v>
+        <v>-13.18</v>
       </c>
       <c r="H86" t="n">
-        <v>-13.73</v>
+        <v>-13.97</v>
       </c>
       <c r="I86" t="n">
-        <v>0.78</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
-        <v>1.18</v>
+        <v>15.02</v>
       </c>
       <c r="K86" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="L86" t="n">
-        <v>50.74</v>
+        <v>554.7</v>
       </c>
       <c r="M86" t="n">
-        <v>51.33</v>
+        <v>562.21</v>
       </c>
       <c r="N86" t="n">
-        <v>49.56</v>
+        <v>539.6799999999999</v>
       </c>
       <c r="O86" t="n">
-        <v>53.75</v>
+        <v>592.99</v>
       </c>
       <c r="P86" t="n">
         <v>1.63</v>
       </c>
       <c r="Q86" t="n">
-        <v>40.37</v>
+        <v>49.97</v>
       </c>
       <c r="R86" t="n">
-        <v>-1.45</v>
+        <v>-2.73</v>
       </c>
       <c r="S86" t="n">
-        <v>-5.62</v>
+        <v>-5.89</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9967,76 +9963,76 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; MA20 sobre MA50; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Débil vs QQQ; Lejos del máximo 20D</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Redes / IA</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>560.1799999999999</v>
+        <v>140.03</v>
       </c>
       <c r="D87" t="n">
         <v>31</v>
       </c>
       <c r="E87" t="n">
-        <v>-4.92</v>
+        <v>-1.76</v>
       </c>
       <c r="F87" t="n">
-        <v>-4.62</v>
+        <v>-18.99</v>
       </c>
       <c r="G87" t="n">
-        <v>-13.14</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>-14</v>
+        <v>-28.3</v>
       </c>
       <c r="I87" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="J87" t="n">
-        <v>15.02</v>
+        <v>8.27</v>
       </c>
       <c r="K87" t="n">
-        <v>2.68</v>
+        <v>5.91</v>
       </c>
       <c r="L87" t="n">
-        <v>554.92</v>
+        <v>137.14</v>
       </c>
       <c r="M87" t="n">
-        <v>562.4299999999999</v>
+        <v>141.27</v>
       </c>
       <c r="N87" t="n">
-        <v>539.91</v>
+        <v>128.87</v>
       </c>
       <c r="O87" t="n">
-        <v>593.22</v>
+        <v>158.22</v>
       </c>
       <c r="P87" t="n">
         <v>1.63</v>
       </c>
       <c r="Q87" t="n">
-        <v>50.06</v>
+        <v>27.34</v>
       </c>
       <c r="R87" t="n">
-        <v>-2.7</v>
+        <v>-10.91</v>
       </c>
       <c r="S87" t="n">
-        <v>-5.85</v>
+        <v>-22.12</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10050,12 +10046,12 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
@@ -10076,76 +10072,76 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; RSI débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Redes / IA</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>140.04</v>
+        <v>501.07</v>
       </c>
       <c r="D88" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E88" t="n">
-        <v>-1.76</v>
+        <v>0.25</v>
       </c>
       <c r="F88" t="n">
-        <v>-18.99</v>
+        <v>-2.01</v>
       </c>
       <c r="G88" t="n">
-        <v>9.890000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="H88" t="n">
-        <v>-28.37</v>
+        <v>-11.32</v>
       </c>
       <c r="I88" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="J88" t="n">
-        <v>8.27</v>
+        <v>12.54</v>
       </c>
       <c r="K88" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="L88" t="n">
-        <v>137.14</v>
+        <v>496.68</v>
       </c>
       <c r="M88" t="n">
-        <v>141.28</v>
+        <v>502.95</v>
       </c>
       <c r="N88" t="n">
-        <v>128.87</v>
+        <v>484.15</v>
       </c>
       <c r="O88" t="n">
-        <v>158.23</v>
+        <v>528.65</v>
       </c>
       <c r="P88" t="n">
         <v>1.63</v>
       </c>
       <c r="Q88" t="n">
-        <v>27.34</v>
+        <v>38.06</v>
       </c>
       <c r="R88" t="n">
-        <v>-10.91</v>
+        <v>-0.02</v>
       </c>
       <c r="S88" t="n">
-        <v>-22.12</v>
+        <v>-6.2</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10159,12 +10155,12 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -10185,12 +10181,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
+          <t>Mercado NEUTRO +; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; RSI débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; Volumen bajo; Débil vs QQQ; Lejos del máximo 20D</t>
         </is>
       </c>
     </row>
@@ -10206,22 +10202,22 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>69.41</v>
+        <v>69.31</v>
       </c>
       <c r="D89" t="n">
         <v>29</v>
       </c>
       <c r="E89" t="n">
-        <v>-3.76</v>
+        <v>-3.89</v>
       </c>
       <c r="F89" t="n">
-        <v>-3.26</v>
+        <v>-3.4</v>
       </c>
       <c r="G89" t="n">
-        <v>36.77</v>
+        <v>36.57</v>
       </c>
       <c r="H89" t="n">
-        <v>-12.64</v>
+        <v>-12.71</v>
       </c>
       <c r="I89" t="n">
         <v>0.51</v>
@@ -10233,28 +10229,28 @@
         <v>3.76</v>
       </c>
       <c r="L89" t="n">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="M89" t="n">
-        <v>69.8</v>
+        <v>69.7</v>
       </c>
       <c r="N89" t="n">
-        <v>65.89</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="O89" t="n">
-        <v>75.15000000000001</v>
+        <v>75.05</v>
       </c>
       <c r="P89" t="n">
         <v>1.63</v>
       </c>
       <c r="Q89" t="n">
-        <v>49.86</v>
+        <v>49.6</v>
       </c>
       <c r="R89" t="n">
-        <v>-2.42</v>
+        <v>-2.55</v>
       </c>
       <c r="S89" t="n">
-        <v>-10.04</v>
+        <v>-10.17</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10315,22 +10311,22 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>75.20999999999999</v>
+        <v>75.08</v>
       </c>
       <c r="D90" t="n">
         <v>29</v>
       </c>
       <c r="E90" t="n">
-        <v>-3.9</v>
+        <v>-4.07</v>
       </c>
       <c r="F90" t="n">
-        <v>-12.98</v>
+        <v>-13.13</v>
       </c>
       <c r="G90" t="n">
-        <v>4.79</v>
+        <v>4.6</v>
       </c>
       <c r="H90" t="n">
-        <v>-22.36</v>
+        <v>-22.44</v>
       </c>
       <c r="I90" t="n">
         <v>0.5</v>
@@ -10339,31 +10335,31 @@
         <v>3.96</v>
       </c>
       <c r="K90" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
       <c r="L90" t="n">
-        <v>73.83</v>
+        <v>73.7</v>
       </c>
       <c r="M90" t="n">
-        <v>75.81</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N90" t="n">
-        <v>69.87</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="O90" t="n">
-        <v>83.92</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="P90" t="n">
         <v>1.63</v>
       </c>
       <c r="Q90" t="n">
-        <v>57.02</v>
+        <v>56.76</v>
       </c>
       <c r="R90" t="n">
-        <v>-4.33</v>
+        <v>-4.49</v>
       </c>
       <c r="S90" t="n">
-        <v>-16.55</v>
+        <v>-16.7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10424,22 +10420,22 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>298.38</v>
+        <v>298.14</v>
       </c>
       <c r="D91" t="n">
         <v>28</v>
       </c>
       <c r="E91" t="n">
-        <v>-2.13</v>
+        <v>-2.21</v>
       </c>
       <c r="F91" t="n">
-        <v>-4.67</v>
+        <v>-4.75</v>
       </c>
       <c r="G91" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="H91" t="n">
-        <v>-14.05</v>
+        <v>-14.06</v>
       </c>
       <c r="I91" t="n">
         <v>0.45</v>
@@ -10451,28 +10447,28 @@
         <v>2.03</v>
       </c>
       <c r="L91" t="n">
-        <v>296.26</v>
+        <v>296.02</v>
       </c>
       <c r="M91" t="n">
-        <v>299.28</v>
+        <v>299.05</v>
       </c>
       <c r="N91" t="n">
-        <v>290.21</v>
+        <v>289.97</v>
       </c>
       <c r="O91" t="n">
-        <v>311.69</v>
+        <v>311.45</v>
       </c>
       <c r="P91" t="n">
         <v>1.63</v>
       </c>
       <c r="Q91" t="n">
-        <v>38.89</v>
+        <v>38.7</v>
       </c>
       <c r="R91" t="n">
-        <v>-2.7</v>
+        <v>-2.78</v>
       </c>
       <c r="S91" t="n">
-        <v>-5.67</v>
+        <v>-5.74</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10533,25 +10529,25 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>25.65</v>
+        <v>25.64</v>
       </c>
       <c r="D92" t="n">
         <v>26</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.87</v>
+        <v>-0.89</v>
       </c>
       <c r="F92" t="n">
-        <v>-4.55</v>
+        <v>-4.57</v>
       </c>
       <c r="G92" t="n">
-        <v>-3.66</v>
+        <v>-3.68</v>
       </c>
       <c r="H92" t="n">
-        <v>-13.93</v>
+        <v>-13.88</v>
       </c>
       <c r="I92" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J92" t="n">
         <v>0.49</v>
@@ -10563,10 +10559,10 @@
         <v>25.47</v>
       </c>
       <c r="M92" t="n">
-        <v>25.72</v>
+        <v>25.71</v>
       </c>
       <c r="N92" t="n">
-        <v>24.98</v>
+        <v>24.97</v>
       </c>
       <c r="O92" t="n">
         <v>26.73</v>
@@ -10575,13 +10571,13 @@
         <v>1.63</v>
       </c>
       <c r="Q92" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="R92" t="n">
-        <v>-1.17</v>
+        <v>-1.19</v>
       </c>
       <c r="S92" t="n">
-        <v>-5.48</v>
+        <v>-5.5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10642,22 +10638,22 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>121.06</v>
+        <v>121.09</v>
       </c>
       <c r="D93" t="n">
         <v>22</v>
       </c>
       <c r="E93" t="n">
-        <v>-4.25</v>
+        <v>-4.23</v>
       </c>
       <c r="F93" t="n">
-        <v>-7.63</v>
+        <v>-7.61</v>
       </c>
       <c r="G93" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="H93" t="n">
-        <v>-17.01</v>
+        <v>-16.92</v>
       </c>
       <c r="I93" t="n">
         <v>0.57</v>
@@ -10669,28 +10665,28 @@
         <v>2.7</v>
       </c>
       <c r="L93" t="n">
-        <v>119.92</v>
+        <v>119.95</v>
       </c>
       <c r="M93" t="n">
-        <v>121.55</v>
+        <v>121.58</v>
       </c>
       <c r="N93" t="n">
-        <v>116.65</v>
+        <v>116.68</v>
       </c>
       <c r="O93" t="n">
-        <v>128.25</v>
+        <v>128.28</v>
       </c>
       <c r="P93" t="n">
         <v>1.63</v>
       </c>
       <c r="Q93" t="n">
-        <v>33.14</v>
+        <v>33.2</v>
       </c>
       <c r="R93" t="n">
-        <v>-4.15</v>
+        <v>-4.13</v>
       </c>
       <c r="S93" t="n">
-        <v>-8.25</v>
+        <v>-8.23</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10742,68 +10738,68 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>15.34</v>
+        <v>285.9</v>
       </c>
       <c r="D94" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E94" t="n">
-        <v>-3.52</v>
+        <v>-3.88</v>
       </c>
       <c r="F94" t="n">
-        <v>-18.53</v>
+        <v>-0.29</v>
       </c>
       <c r="G94" t="n">
-        <v>-15.81</v>
+        <v>-15.54</v>
       </c>
       <c r="H94" t="n">
-        <v>-27.91</v>
+        <v>-9.6</v>
       </c>
       <c r="I94" t="n">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="J94" t="n">
-        <v>0.7</v>
+        <v>9.07</v>
       </c>
       <c r="K94" t="n">
-        <v>4.54</v>
+        <v>3.17</v>
       </c>
       <c r="L94" t="n">
-        <v>15.1</v>
+        <v>282.73</v>
       </c>
       <c r="M94" t="n">
-        <v>15.44</v>
+        <v>287.26</v>
       </c>
       <c r="N94" t="n">
-        <v>14.4</v>
+        <v>273.66</v>
       </c>
       <c r="O94" t="n">
-        <v>16.87</v>
+        <v>305.85</v>
       </c>
       <c r="P94" t="n">
         <v>1.63</v>
       </c>
       <c r="Q94" t="n">
-        <v>48.22</v>
+        <v>51.51</v>
       </c>
       <c r="R94" t="n">
-        <v>-7.43</v>
+        <v>-1.2</v>
       </c>
       <c r="S94" t="n">
-        <v>-21.12</v>
+        <v>-7.77</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>BAJA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10839,7 +10835,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; RSI saludable; MACD mejorando</t>
+          <t>Mercado NEUTRO +; RSI saludable</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -10851,68 +10847,68 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>285.77</v>
+        <v>15.33</v>
       </c>
       <c r="D95" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E95" t="n">
-        <v>-3.93</v>
+        <v>-3.58</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.33</v>
+        <v>-18.59</v>
       </c>
       <c r="G95" t="n">
-        <v>-15.58</v>
+        <v>-15.86</v>
       </c>
       <c r="H95" t="n">
-        <v>-9.710000000000001</v>
+        <v>-27.9</v>
       </c>
       <c r="I95" t="n">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="J95" t="n">
-        <v>9.07</v>
+        <v>0.7</v>
       </c>
       <c r="K95" t="n">
-        <v>3.17</v>
+        <v>4.54</v>
       </c>
       <c r="L95" t="n">
-        <v>282.6</v>
+        <v>15.09</v>
       </c>
       <c r="M95" t="n">
-        <v>287.13</v>
+        <v>15.43</v>
       </c>
       <c r="N95" t="n">
-        <v>273.53</v>
+        <v>14.39</v>
       </c>
       <c r="O95" t="n">
-        <v>305.72</v>
+        <v>16.86</v>
       </c>
       <c r="P95" t="n">
         <v>1.63</v>
       </c>
       <c r="Q95" t="n">
-        <v>51.42</v>
+        <v>48.13</v>
       </c>
       <c r="R95" t="n">
-        <v>-1.25</v>
+        <v>-7.48</v>
       </c>
       <c r="S95" t="n">
-        <v>-7.82</v>
+        <v>-21.17</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10969,25 +10965,25 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>218.83</v>
+        <v>218.57</v>
       </c>
       <c r="D96" t="n">
         <v>15</v>
       </c>
       <c r="E96" t="n">
-        <v>-7.62</v>
+        <v>-7.73</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.15</v>
+        <v>-0.27</v>
       </c>
       <c r="G96" t="n">
-        <v>-5.04</v>
+        <v>-5.15</v>
       </c>
       <c r="H96" t="n">
-        <v>-9.529999999999999</v>
+        <v>-9.58</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="J96" t="n">
         <v>6.86</v>
@@ -10996,28 +10992,28 @@
         <v>3.14</v>
       </c>
       <c r="L96" t="n">
-        <v>216.43</v>
+        <v>216.17</v>
       </c>
       <c r="M96" t="n">
-        <v>219.86</v>
+        <v>219.6</v>
       </c>
       <c r="N96" t="n">
-        <v>209.57</v>
+        <v>209.31</v>
       </c>
       <c r="O96" t="n">
-        <v>233.93</v>
+        <v>233.67</v>
       </c>
       <c r="P96" t="n">
         <v>1.63</v>
       </c>
       <c r="Q96" t="n">
-        <v>45.34</v>
+        <v>45.13</v>
       </c>
       <c r="R96" t="n">
-        <v>-4.63</v>
+        <v>-4.74</v>
       </c>
       <c r="S96" t="n">
-        <v>-10.34</v>
+        <v>-10.45</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11078,55 +11074,55 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>135.5</v>
+        <v>135.43</v>
       </c>
       <c r="D97" t="n">
         <v>15</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.37</v>
+        <v>-0.42</v>
       </c>
       <c r="F97" t="n">
-        <v>-7.17</v>
+        <v>-7.22</v>
       </c>
       <c r="G97" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H97" t="n">
-        <v>-16.55</v>
+        <v>-16.53</v>
       </c>
       <c r="I97" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>5.62</v>
       </c>
       <c r="K97" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="L97" t="n">
-        <v>133.53</v>
+        <v>133.46</v>
       </c>
       <c r="M97" t="n">
-        <v>136.34</v>
+        <v>136.27</v>
       </c>
       <c r="N97" t="n">
-        <v>127.92</v>
+        <v>127.85</v>
       </c>
       <c r="O97" t="n">
-        <v>147.86</v>
+        <v>147.78</v>
       </c>
       <c r="P97" t="n">
         <v>1.63</v>
       </c>
       <c r="Q97" t="n">
-        <v>46.71</v>
+        <v>46.6</v>
       </c>
       <c r="R97" t="n">
-        <v>-2.33</v>
+        <v>-2.38</v>
       </c>
       <c r="S97" t="n">
-        <v>-11.25</v>
+        <v>-11.3</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11145,7 +11141,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
@@ -11187,7 +11183,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>452.66</v>
+        <v>452.64</v>
       </c>
       <c r="D98" t="n">
         <v>15</v>
@@ -11199,13 +11195,13 @@
         <v>-13.71</v>
       </c>
       <c r="G98" t="n">
-        <v>-12.26</v>
+        <v>-12.27</v>
       </c>
       <c r="H98" t="n">
-        <v>-23.09</v>
+        <v>-23.02</v>
       </c>
       <c r="I98" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="J98" t="n">
         <v>13.96</v>
@@ -11214,22 +11210,22 @@
         <v>3.08</v>
       </c>
       <c r="L98" t="n">
-        <v>447.77</v>
+        <v>447.75</v>
       </c>
       <c r="M98" t="n">
-        <v>454.75</v>
+        <v>454.73</v>
       </c>
       <c r="N98" t="n">
-        <v>433.81</v>
+        <v>433.79</v>
       </c>
       <c r="O98" t="n">
-        <v>483.37</v>
+        <v>483.35</v>
       </c>
       <c r="P98" t="n">
         <v>1.63</v>
       </c>
       <c r="Q98" t="n">
-        <v>43.77</v>
+        <v>43.76</v>
       </c>
       <c r="R98" t="n">
         <v>-2.49</v>
@@ -11296,22 +11292,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>602.0599999999999</v>
+        <v>602.25</v>
       </c>
       <c r="D99" t="n">
         <v>14</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.16</v>
+        <v>-0.12</v>
       </c>
       <c r="F99" t="n">
-        <v>-9.98</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="G99" t="n">
-        <v>-5.44</v>
+        <v>-5.41</v>
       </c>
       <c r="H99" t="n">
-        <v>-19.36</v>
+        <v>-19.27</v>
       </c>
       <c r="I99" t="n">
         <v>0.47</v>
@@ -11323,28 +11319,28 @@
         <v>2.89</v>
       </c>
       <c r="L99" t="n">
-        <v>595.97</v>
+        <v>596.16</v>
       </c>
       <c r="M99" t="n">
-        <v>604.67</v>
+        <v>604.86</v>
       </c>
       <c r="N99" t="n">
-        <v>578.5599999999999</v>
+        <v>578.75</v>
       </c>
       <c r="O99" t="n">
-        <v>640.35</v>
+        <v>640.54</v>
       </c>
       <c r="P99" t="n">
         <v>1.63</v>
       </c>
       <c r="Q99" t="n">
-        <v>24.83</v>
+        <v>24.87</v>
       </c>
       <c r="R99" t="n">
-        <v>-4.19</v>
+        <v>-4.16</v>
       </c>
       <c r="S99" t="n">
-        <v>-11.79</v>
+        <v>-11.76</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11363,7 +11359,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
@@ -11405,22 +11401,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>44.04</v>
+        <v>44.01</v>
       </c>
       <c r="D100" t="n">
         <v>13</v>
       </c>
       <c r="E100" t="n">
-        <v>-3.07</v>
+        <v>-3.14</v>
       </c>
       <c r="F100" t="n">
-        <v>-13.43</v>
+        <v>-13.49</v>
       </c>
       <c r="G100" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="H100" t="n">
-        <v>-22.81</v>
+        <v>-22.8</v>
       </c>
       <c r="I100" t="n">
         <v>0.58</v>
@@ -11432,28 +11428,28 @@
         <v>3.23</v>
       </c>
       <c r="L100" t="n">
-        <v>43.55</v>
+        <v>43.52</v>
       </c>
       <c r="M100" t="n">
-        <v>44.26</v>
+        <v>44.23</v>
       </c>
       <c r="N100" t="n">
-        <v>42.13</v>
+        <v>42.1</v>
       </c>
       <c r="O100" t="n">
-        <v>47.17</v>
+        <v>47.14</v>
       </c>
       <c r="P100" t="n">
         <v>1.63</v>
       </c>
       <c r="Q100" t="n">
-        <v>8.140000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="R100" t="n">
-        <v>-7.35</v>
+        <v>-7.41</v>
       </c>
       <c r="S100" t="n">
-        <v>-15.09</v>
+        <v>-15.14</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11514,22 +11510,22 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>74.83</v>
+        <v>74.78</v>
       </c>
       <c r="D101" t="n">
         <v>7</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.47</v>
+        <v>-0.53</v>
       </c>
       <c r="F101" t="n">
-        <v>-7.72</v>
+        <v>-7.78</v>
       </c>
       <c r="G101" t="n">
-        <v>-11.62</v>
+        <v>-11.68</v>
       </c>
       <c r="H101" t="n">
-        <v>-17.1</v>
+        <v>-17.09</v>
       </c>
       <c r="I101" t="n">
         <v>0.37</v>
@@ -11541,28 +11537,28 @@
         <v>2.57</v>
       </c>
       <c r="L101" t="n">
-        <v>74.16</v>
+        <v>74.11</v>
       </c>
       <c r="M101" t="n">
-        <v>75.12</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="N101" t="n">
-        <v>72.23999999999999</v>
+        <v>72.19</v>
       </c>
       <c r="O101" t="n">
-        <v>79.05</v>
+        <v>79</v>
       </c>
       <c r="P101" t="n">
         <v>1.63</v>
       </c>
       <c r="Q101" t="n">
-        <v>31.34</v>
+        <v>31.13</v>
       </c>
       <c r="R101" t="n">
-        <v>-3.73</v>
+        <v>-3.79</v>
       </c>
       <c r="S101" t="n">
-        <v>-8.949999999999999</v>
+        <v>-9.02</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11623,25 +11619,25 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>218.66</v>
+        <v>218.56</v>
       </c>
       <c r="D102" t="n">
         <v>7</v>
       </c>
       <c r="E102" t="n">
-        <v>-2.61</v>
+        <v>-2.65</v>
       </c>
       <c r="F102" t="n">
-        <v>-12.53</v>
+        <v>-12.57</v>
       </c>
       <c r="G102" t="n">
-        <v>-19.92</v>
+        <v>-19.96</v>
       </c>
       <c r="H102" t="n">
-        <v>-21.91</v>
+        <v>-21.88</v>
       </c>
       <c r="I102" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="J102" t="n">
         <v>5.88</v>
@@ -11650,28 +11646,28 @@
         <v>2.69</v>
       </c>
       <c r="L102" t="n">
-        <v>216.61</v>
+        <v>216.5</v>
       </c>
       <c r="M102" t="n">
-        <v>219.55</v>
+        <v>219.44</v>
       </c>
       <c r="N102" t="n">
-        <v>210.73</v>
+        <v>210.62</v>
       </c>
       <c r="O102" t="n">
-        <v>231.6</v>
+        <v>231.49</v>
       </c>
       <c r="P102" t="n">
         <v>1.63</v>
       </c>
       <c r="Q102" t="n">
-        <v>35.82</v>
+        <v>35.7</v>
       </c>
       <c r="R102" t="n">
-        <v>-5.27</v>
+        <v>-5.32</v>
       </c>
       <c r="S102" t="n">
-        <v>-13.24</v>
+        <v>-13.28</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11732,25 +11728,25 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>301</v>
+        <v>300.75</v>
       </c>
       <c r="D103" t="n">
         <v>4</v>
       </c>
       <c r="E103" t="n">
-        <v>-3.05</v>
+        <v>-3.13</v>
       </c>
       <c r="F103" t="n">
-        <v>-12.48</v>
+        <v>-12.55</v>
       </c>
       <c r="G103" t="n">
-        <v>-19.62</v>
+        <v>-19.69</v>
       </c>
       <c r="H103" t="n">
         <v>-21.86</v>
       </c>
       <c r="I103" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="J103" t="n">
         <v>8.08</v>
@@ -11759,28 +11755,28 @@
         <v>2.69</v>
       </c>
       <c r="L103" t="n">
-        <v>298.17</v>
+        <v>297.92</v>
       </c>
       <c r="M103" t="n">
-        <v>302.21</v>
+        <v>301.96</v>
       </c>
       <c r="N103" t="n">
-        <v>290.09</v>
+        <v>289.84</v>
       </c>
       <c r="O103" t="n">
-        <v>318.78</v>
+        <v>318.53</v>
       </c>
       <c r="P103" t="n">
         <v>1.63</v>
       </c>
       <c r="Q103" t="n">
-        <v>33.38</v>
+        <v>33.13</v>
       </c>
       <c r="R103" t="n">
-        <v>-5.5</v>
+        <v>-5.58</v>
       </c>
       <c r="S103" t="n">
-        <v>-12.81</v>
+        <v>-12.89</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11841,55 +11837,55 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>8.470000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="D104" t="n">
         <v>56</v>
       </c>
       <c r="E104" t="n">
-        <v>5.09</v>
+        <v>4.92</v>
       </c>
       <c r="F104" t="n">
-        <v>7.9</v>
+        <v>7.73</v>
       </c>
       <c r="G104" t="n">
-        <v>8.17</v>
+        <v>8.01</v>
       </c>
       <c r="H104" t="n">
-        <v>-1.48</v>
+        <v>-1.58</v>
       </c>
       <c r="I104" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="J104" t="n">
         <v>0.66</v>
       </c>
       <c r="K104" t="n">
-        <v>7.75</v>
+        <v>7.76</v>
       </c>
       <c r="L104" t="n">
-        <v>8.24</v>
+        <v>8.23</v>
       </c>
       <c r="M104" t="n">
-        <v>8.57</v>
+        <v>8.56</v>
       </c>
       <c r="N104" t="n">
-        <v>7.58</v>
+        <v>7.57</v>
       </c>
       <c r="O104" t="n">
-        <v>9.91</v>
+        <v>9.9</v>
       </c>
       <c r="P104" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q104" t="n">
-        <v>57.48</v>
+        <v>57.37</v>
       </c>
       <c r="R104" t="n">
-        <v>-0.85</v>
+        <v>-0.99</v>
       </c>
       <c r="S104" t="n">
-        <v>-15.68</v>
+        <v>-15.81</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11908,7 +11904,7 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
@@ -11950,22 +11946,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>30.81</v>
+        <v>30.8</v>
       </c>
       <c r="D105" t="n">
         <v>53</v>
       </c>
       <c r="E105" t="n">
-        <v>-6.05</v>
+        <v>-6.08</v>
       </c>
       <c r="F105" t="n">
-        <v>8.35</v>
+        <v>8.32</v>
       </c>
       <c r="G105" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="H105" t="n">
-        <v>-1.03</v>
+        <v>-0.99</v>
       </c>
       <c r="I105" t="n">
         <v>0.4</v>
@@ -11977,28 +11973,28 @@
         <v>7.55</v>
       </c>
       <c r="L105" t="n">
-        <v>29.99</v>
+        <v>29.98</v>
       </c>
       <c r="M105" t="n">
-        <v>31.15</v>
+        <v>31.14</v>
       </c>
       <c r="N105" t="n">
-        <v>27.67</v>
+        <v>27.66</v>
       </c>
       <c r="O105" t="n">
-        <v>35.92</v>
+        <v>35.91</v>
       </c>
       <c r="P105" t="n">
         <v>1.63</v>
       </c>
       <c r="Q105" t="n">
-        <v>62.09</v>
+        <v>62.05</v>
       </c>
       <c r="R105" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="S105" t="n">
-        <v>-15.3</v>
+        <v>-15.33</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12017,7 +12013,7 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
@@ -12059,25 +12055,25 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>126.84</v>
+        <v>126.93</v>
       </c>
       <c r="D106" t="n">
         <v>43</v>
       </c>
       <c r="E106" t="n">
-        <v>9.029999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="F106" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="G106" t="n">
-        <v>-18.02</v>
+        <v>-17.97</v>
       </c>
       <c r="H106" t="n">
-        <v>-18.83</v>
+        <v>-18.7</v>
       </c>
       <c r="I106" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="J106" t="n">
         <v>6.04</v>
@@ -12086,28 +12082,28 @@
         <v>4.76</v>
       </c>
       <c r="L106" t="n">
-        <v>124.72</v>
+        <v>124.82</v>
       </c>
       <c r="M106" t="n">
-        <v>127.75</v>
+        <v>127.84</v>
       </c>
       <c r="N106" t="n">
-        <v>118.68</v>
+        <v>118.77</v>
       </c>
       <c r="O106" t="n">
-        <v>140.13</v>
+        <v>140.22</v>
       </c>
       <c r="P106" t="n">
         <v>1.63</v>
       </c>
       <c r="Q106" t="n">
-        <v>37.64</v>
+        <v>37.71</v>
       </c>
       <c r="R106" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="S106" t="n">
-        <v>-10.82</v>
+        <v>-10.76</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12126,7 +12122,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
@@ -12168,55 +12164,55 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>6.03</v>
+        <v>6.01</v>
       </c>
       <c r="D107" t="n">
         <v>38</v>
       </c>
       <c r="E107" t="n">
-        <v>-5.71</v>
+        <v>-5.95</v>
       </c>
       <c r="F107" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="G107" t="n">
-        <v>-13.43</v>
+        <v>-13.65</v>
       </c>
       <c r="H107" t="n">
-        <v>-7.95</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="J107" t="n">
         <v>0.41</v>
       </c>
       <c r="K107" t="n">
-        <v>6.83</v>
+        <v>6.85</v>
       </c>
       <c r="L107" t="n">
-        <v>5.88</v>
+        <v>5.87</v>
       </c>
       <c r="M107" t="n">
-        <v>6.09</v>
+        <v>6.07</v>
       </c>
       <c r="N107" t="n">
-        <v>5.47</v>
+        <v>5.45</v>
       </c>
       <c r="O107" t="n">
-        <v>6.93</v>
+        <v>6.92</v>
       </c>
       <c r="P107" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q107" t="n">
-        <v>58.91</v>
+        <v>58.65</v>
       </c>
       <c r="R107" t="n">
-        <v>-0.51</v>
+        <v>-0.74</v>
       </c>
       <c r="S107" t="n">
-        <v>-10.74</v>
+        <v>-10.96</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12277,22 +12273,22 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>202.37</v>
+        <v>202.43</v>
       </c>
       <c r="D108" t="n">
         <v>37</v>
       </c>
       <c r="E108" t="n">
-        <v>8.34</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F108" t="n">
-        <v>-2.55</v>
+        <v>-2.52</v>
       </c>
       <c r="G108" t="n">
-        <v>26.33</v>
+        <v>26.37</v>
       </c>
       <c r="H108" t="n">
-        <v>-11.93</v>
+        <v>-11.83</v>
       </c>
       <c r="I108" t="n">
         <v>0.46</v>
@@ -12304,28 +12300,28 @@
         <v>7.56</v>
       </c>
       <c r="L108" t="n">
-        <v>197.01</v>
+        <v>197.08</v>
       </c>
       <c r="M108" t="n">
-        <v>204.67</v>
+        <v>204.73</v>
       </c>
       <c r="N108" t="n">
-        <v>181.71</v>
+        <v>181.78</v>
       </c>
       <c r="O108" t="n">
-        <v>236.04</v>
+        <v>236.1</v>
       </c>
       <c r="P108" t="n">
         <v>1.63</v>
       </c>
       <c r="Q108" t="n">
-        <v>46.78</v>
+        <v>46.8</v>
       </c>
       <c r="R108" t="n">
-        <v>-4.08</v>
+        <v>-4.05</v>
       </c>
       <c r="S108" t="n">
-        <v>-21.83</v>
+        <v>-21.8</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12344,7 +12340,7 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
@@ -12386,55 +12382,55 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>155.03</v>
+        <v>155.45</v>
       </c>
       <c r="D109" t="n">
         <v>35</v>
       </c>
       <c r="E109" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="F109" t="n">
-        <v>-1.14</v>
+        <v>-0.88</v>
       </c>
       <c r="G109" t="n">
-        <v>8.82</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="H109" t="n">
-        <v>-10.52</v>
+        <v>-10.19</v>
       </c>
       <c r="I109" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="J109" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="K109" t="n">
-        <v>6.26</v>
+        <v>6.24</v>
       </c>
       <c r="L109" t="n">
-        <v>151.63</v>
+        <v>152.05</v>
       </c>
       <c r="M109" t="n">
-        <v>156.49</v>
+        <v>156.9</v>
       </c>
       <c r="N109" t="n">
-        <v>141.93</v>
+        <v>142.34</v>
       </c>
       <c r="O109" t="n">
-        <v>176.38</v>
+        <v>176.8</v>
       </c>
       <c r="P109" t="n">
         <v>1.63</v>
       </c>
       <c r="Q109" t="n">
-        <v>55.83</v>
+        <v>56.2</v>
       </c>
       <c r="R109" t="n">
-        <v>-1.98</v>
+        <v>-1.73</v>
       </c>
       <c r="S109" t="n">
-        <v>-12.48</v>
+        <v>-12.24</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12453,7 +12449,7 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
@@ -12495,55 +12491,55 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>28.47</v>
+        <v>28.48</v>
       </c>
       <c r="D110" t="n">
         <v>31</v>
       </c>
       <c r="E110" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="F110" t="n">
-        <v>-14.25</v>
+        <v>-14.22</v>
       </c>
       <c r="G110" t="n">
-        <v>4.44</v>
+        <v>4.48</v>
       </c>
       <c r="H110" t="n">
-        <v>-23.63</v>
+        <v>-23.53</v>
       </c>
       <c r="I110" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="J110" t="n">
         <v>1.86</v>
       </c>
       <c r="K110" t="n">
-        <v>6.54</v>
+        <v>6.55</v>
       </c>
       <c r="L110" t="n">
-        <v>27.82</v>
+        <v>27.83</v>
       </c>
       <c r="M110" t="n">
-        <v>28.75</v>
+        <v>28.76</v>
       </c>
       <c r="N110" t="n">
         <v>25.96</v>
       </c>
       <c r="O110" t="n">
-        <v>32.57</v>
+        <v>32.58</v>
       </c>
       <c r="P110" t="n">
         <v>1.63</v>
       </c>
       <c r="Q110" t="n">
-        <v>42.63</v>
+        <v>42.67</v>
       </c>
       <c r="R110" t="n">
-        <v>-6.79</v>
+        <v>-6.76</v>
       </c>
       <c r="S110" t="n">
-        <v>-19.1</v>
+        <v>-19.07</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12562,7 +12558,7 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
@@ -12619,7 +12615,7 @@
         <v>-10.01</v>
       </c>
       <c r="H111" t="n">
-        <v>-15.63</v>
+        <v>-15.56</v>
       </c>
       <c r="I111" t="n">
         <v>0.58</v>
@@ -12671,7 +12667,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -12713,22 +12709,22 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>102.15</v>
+        <v>102.25</v>
       </c>
       <c r="D112" t="n">
         <v>6</v>
       </c>
       <c r="E112" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="F112" t="n">
-        <v>-22.1</v>
+        <v>-22.03</v>
       </c>
       <c r="G112" t="n">
-        <v>-12.9</v>
+        <v>-12.82</v>
       </c>
       <c r="H112" t="n">
-        <v>-31.48</v>
+        <v>-31.34</v>
       </c>
       <c r="I112" t="n">
         <v>0.54</v>
@@ -12737,31 +12733,31 @@
         <v>6.4</v>
       </c>
       <c r="K112" t="n">
-        <v>6.27</v>
+        <v>6.26</v>
       </c>
       <c r="L112" t="n">
-        <v>99.91</v>
+        <v>100</v>
       </c>
       <c r="M112" t="n">
-        <v>103.12</v>
+        <v>103.21</v>
       </c>
       <c r="N112" t="n">
-        <v>93.51000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O112" t="n">
-        <v>116.24</v>
+        <v>116.33</v>
       </c>
       <c r="P112" t="n">
         <v>1.63</v>
       </c>
       <c r="Q112" t="n">
-        <v>33.74</v>
+        <v>33.8</v>
       </c>
       <c r="R112" t="n">
-        <v>-9.640000000000001</v>
+        <v>-9.57</v>
       </c>
       <c r="S112" t="n">
-        <v>-23.63</v>
+        <v>-23.57</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12780,7 +12776,7 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
@@ -12822,55 +12818,55 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>12.46</v>
+        <v>12.38</v>
       </c>
       <c r="D113" t="n">
         <v>52</v>
       </c>
       <c r="E113" t="n">
-        <v>-2.04</v>
+        <v>-2.71</v>
       </c>
       <c r="F113" t="n">
-        <v>10.95</v>
+        <v>10.2</v>
       </c>
       <c r="G113" t="n">
-        <v>58.12</v>
+        <v>57.04</v>
       </c>
       <c r="H113" t="n">
-        <v>1.57</v>
+        <v>0.89</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="J113" t="n">
         <v>1.03</v>
       </c>
       <c r="K113" t="n">
-        <v>8.279999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="L113" t="n">
-        <v>12.1</v>
+        <v>12.01</v>
       </c>
       <c r="M113" t="n">
-        <v>12.61</v>
+        <v>12.53</v>
       </c>
       <c r="N113" t="n">
-        <v>11.07</v>
+        <v>10.98</v>
       </c>
       <c r="O113" t="n">
-        <v>14.73</v>
+        <v>14.64</v>
       </c>
       <c r="P113" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q113" t="n">
-        <v>62.39</v>
+        <v>61.93</v>
       </c>
       <c r="R113" t="n">
-        <v>2.32</v>
+        <v>1.66</v>
       </c>
       <c r="S113" t="n">
-        <v>-9.710000000000001</v>
+        <v>-10.33</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12889,7 +12885,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>BTC-USD 1.45% · ETH-USD -6.02%</t>
+          <t>BTC-USD 1.26% · ETH-USD -6.29%</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -12915,7 +12911,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.45% · ETH-USD -6.02%; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Volatilidad alta</t>
+          <t>Sector no acompaña: BTC-USD 1.26% · ETH-USD -6.29%; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -12931,22 +12927,22 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>166.89</v>
+        <v>166.47</v>
       </c>
       <c r="D114" t="n">
         <v>21</v>
       </c>
       <c r="E114" t="n">
-        <v>-9.51</v>
+        <v>-9.73</v>
       </c>
       <c r="F114" t="n">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="G114" t="n">
-        <v>34.9</v>
+        <v>34.56</v>
       </c>
       <c r="H114" t="n">
-        <v>-7.6</v>
+        <v>-7.79</v>
       </c>
       <c r="I114" t="n">
         <v>0.39</v>
@@ -12955,31 +12951,31 @@
         <v>11.53</v>
       </c>
       <c r="K114" t="n">
-        <v>6.91</v>
+        <v>6.93</v>
       </c>
       <c r="L114" t="n">
-        <v>162.85</v>
+        <v>162.43</v>
       </c>
       <c r="M114" t="n">
-        <v>168.62</v>
+        <v>168.2</v>
       </c>
       <c r="N114" t="n">
-        <v>151.32</v>
+        <v>150.9</v>
       </c>
       <c r="O114" t="n">
-        <v>192.26</v>
+        <v>191.84</v>
       </c>
       <c r="P114" t="n">
         <v>1.63</v>
       </c>
       <c r="Q114" t="n">
-        <v>54.38</v>
+        <v>54.17</v>
       </c>
       <c r="R114" t="n">
-        <v>-5.71</v>
+        <v>-5.93</v>
       </c>
       <c r="S114" t="n">
-        <v>-15.28</v>
+        <v>-15.5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12998,7 +12994,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>BTC-USD 1.45% · ETH-USD -6.02%</t>
+          <t>BTC-USD 1.26% · ETH-USD -6.29%</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -13024,7 +13020,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.45% · ETH-USD -6.02%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Sector no acompaña: BTC-USD 1.26% · ETH-USD -6.29%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -13040,55 +13036,55 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>195.16</v>
+        <v>194.4</v>
       </c>
       <c r="D115" t="n">
         <v>12</v>
       </c>
       <c r="E115" t="n">
-        <v>-6.01</v>
+        <v>-6.38</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.4</v>
+        <v>-0.79</v>
       </c>
       <c r="G115" t="n">
-        <v>21.79</v>
+        <v>21.32</v>
       </c>
       <c r="H115" t="n">
-        <v>-9.779999999999999</v>
+        <v>-10.1</v>
       </c>
       <c r="I115" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>14.26</v>
       </c>
       <c r="K115" t="n">
-        <v>7.31</v>
+        <v>7.34</v>
       </c>
       <c r="L115" t="n">
-        <v>190.17</v>
+        <v>189.41</v>
       </c>
       <c r="M115" t="n">
-        <v>197.3</v>
+        <v>196.54</v>
       </c>
       <c r="N115" t="n">
-        <v>175.91</v>
+        <v>175.15</v>
       </c>
       <c r="O115" t="n">
-        <v>226.54</v>
+        <v>225.78</v>
       </c>
       <c r="P115" t="n">
         <v>1.63</v>
       </c>
       <c r="Q115" t="n">
-        <v>56.18</v>
+        <v>55.87</v>
       </c>
       <c r="R115" t="n">
-        <v>-1.59</v>
+        <v>-1.96</v>
       </c>
       <c r="S115" t="n">
-        <v>-12.23</v>
+        <v>-12.57</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13107,7 +13103,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>BTC-USD 1.45% · ETH-USD -6.02%</t>
+          <t>BTC-USD 1.26% · ETH-USD -6.29%</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
@@ -13133,7 +13129,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.45% · ETH-USD -6.02%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Sector no acompaña: BTC-USD 1.26% · ETH-USD -6.29%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -13149,22 +13145,22 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>198.86</v>
+        <v>198.65</v>
       </c>
       <c r="D116" t="n">
         <v>53</v>
       </c>
       <c r="E116" t="n">
-        <v>-5.44</v>
+        <v>-5.54</v>
       </c>
       <c r="F116" t="n">
-        <v>46.7</v>
+        <v>46.54</v>
       </c>
       <c r="G116" t="n">
-        <v>42.54</v>
+        <v>42.39</v>
       </c>
       <c r="H116" t="n">
-        <v>37.32</v>
+        <v>37.23</v>
       </c>
       <c r="I116" t="n">
         <v>0.42</v>
@@ -13173,31 +13169,31 @@
         <v>19.75</v>
       </c>
       <c r="K116" t="n">
-        <v>9.93</v>
+        <v>9.94</v>
       </c>
       <c r="L116" t="n">
-        <v>191.95</v>
+        <v>191.74</v>
       </c>
       <c r="M116" t="n">
-        <v>201.82</v>
+        <v>201.61</v>
       </c>
       <c r="N116" t="n">
-        <v>172.19</v>
+        <v>171.98</v>
       </c>
       <c r="O116" t="n">
-        <v>242.32</v>
+        <v>242.11</v>
       </c>
       <c r="P116" t="n">
         <v>1.63</v>
       </c>
       <c r="Q116" t="n">
-        <v>63.79</v>
+        <v>63.7</v>
       </c>
       <c r="R116" t="n">
-        <v>8.49</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S116" t="n">
-        <v>-19.78</v>
+        <v>-19.87</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13216,7 +13212,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>SOXX 19.33% · QQQ 9.38%</t>
+          <t>SOXX 19.14% · QQQ 9.31%</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -13237,7 +13233,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.33% · QQQ 9.38%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.14% · QQQ 9.31%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -13258,25 +13254,25 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>175.78</v>
+        <v>175.75</v>
       </c>
       <c r="D117" t="n">
         <v>59</v>
       </c>
       <c r="E117" t="n">
-        <v>20.26</v>
+        <v>20.24</v>
       </c>
       <c r="F117" t="n">
-        <v>25.91</v>
+        <v>25.89</v>
       </c>
       <c r="G117" t="n">
-        <v>22.68</v>
+        <v>22.66</v>
       </c>
       <c r="H117" t="n">
-        <v>16.53</v>
+        <v>16.58</v>
       </c>
       <c r="I117" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="J117" t="n">
         <v>9.06</v>
@@ -13285,28 +13281,28 @@
         <v>5.16</v>
       </c>
       <c r="L117" t="n">
-        <v>172.61</v>
+        <v>172.58</v>
       </c>
       <c r="M117" t="n">
-        <v>177.14</v>
+        <v>177.11</v>
       </c>
       <c r="N117" t="n">
-        <v>163.55</v>
+        <v>163.52</v>
       </c>
       <c r="O117" t="n">
-        <v>195.72</v>
+        <v>195.69</v>
       </c>
       <c r="P117" t="n">
         <v>1.63</v>
       </c>
       <c r="Q117" t="n">
-        <v>79.69</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="R117" t="n">
-        <v>20.13</v>
+        <v>20.11</v>
       </c>
       <c r="S117" t="n">
-        <v>-3.93</v>
+        <v>-3.95</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13325,7 +13321,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -13367,25 +13363,25 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>242.48</v>
+        <v>242.38</v>
       </c>
       <c r="D118" t="n">
         <v>56</v>
       </c>
       <c r="E118" t="n">
-        <v>12.47</v>
+        <v>12.42</v>
       </c>
       <c r="F118" t="n">
-        <v>38.59</v>
+        <v>38.53</v>
       </c>
       <c r="G118" t="n">
-        <v>68.23</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="H118" t="n">
-        <v>29.21</v>
+        <v>29.22</v>
       </c>
       <c r="I118" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="J118" t="n">
         <v>10.3</v>
@@ -13394,28 +13390,28 @@
         <v>4.25</v>
       </c>
       <c r="L118" t="n">
-        <v>238.88</v>
+        <v>238.77</v>
       </c>
       <c r="M118" t="n">
-        <v>244.02</v>
+        <v>243.92</v>
       </c>
       <c r="N118" t="n">
-        <v>228.58</v>
+        <v>228.47</v>
       </c>
       <c r="O118" t="n">
-        <v>265.14</v>
+        <v>265.03</v>
       </c>
       <c r="P118" t="n">
         <v>1.63</v>
       </c>
       <c r="Q118" t="n">
-        <v>89.43000000000001</v>
+        <v>89.31</v>
       </c>
       <c r="R118" t="n">
-        <v>20.53</v>
+        <v>20.48</v>
       </c>
       <c r="S118" t="n">
-        <v>-2.56</v>
+        <v>-2.6</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13434,7 +13430,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -13476,25 +13472,25 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>620.41</v>
+        <v>620.15</v>
       </c>
       <c r="D119" t="n">
         <v>56</v>
       </c>
       <c r="E119" t="n">
-        <v>13.59</v>
+        <v>13.54</v>
       </c>
       <c r="F119" t="n">
-        <v>37.99</v>
+        <v>37.93</v>
       </c>
       <c r="G119" t="n">
-        <v>77.09</v>
+        <v>77.02</v>
       </c>
       <c r="H119" t="n">
-        <v>28.61</v>
+        <v>28.62</v>
       </c>
       <c r="I119" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>24.91</v>
@@ -13503,28 +13499,28 @@
         <v>4.02</v>
       </c>
       <c r="L119" t="n">
-        <v>611.6900000000001</v>
+        <v>611.4299999999999</v>
       </c>
       <c r="M119" t="n">
-        <v>624.15</v>
+        <v>623.89</v>
       </c>
       <c r="N119" t="n">
-        <v>586.78</v>
+        <v>586.52</v>
       </c>
       <c r="O119" t="n">
-        <v>675.21</v>
+        <v>674.95</v>
       </c>
       <c r="P119" t="n">
         <v>1.63</v>
       </c>
       <c r="Q119" t="n">
-        <v>92.39</v>
+        <v>92.38</v>
       </c>
       <c r="R119" t="n">
-        <v>22.43</v>
+        <v>22.38</v>
       </c>
       <c r="S119" t="n">
-        <v>-2.18</v>
+        <v>-2.22</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13543,7 +13539,7 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
@@ -13585,55 +13581,55 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>170.95</v>
+        <v>171.53</v>
       </c>
       <c r="D120" t="n">
         <v>53</v>
       </c>
       <c r="E120" t="n">
-        <v>12.48</v>
+        <v>12.86</v>
       </c>
       <c r="F120" t="n">
-        <v>13.33</v>
+        <v>13.72</v>
       </c>
       <c r="G120" t="n">
-        <v>8.470000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="H120" t="n">
-        <v>3.95</v>
+        <v>4.41</v>
       </c>
       <c r="I120" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="J120" t="n">
         <v>8.83</v>
       </c>
       <c r="K120" t="n">
-        <v>5.17</v>
+        <v>5.15</v>
       </c>
       <c r="L120" t="n">
-        <v>167.85</v>
+        <v>168.44</v>
       </c>
       <c r="M120" t="n">
-        <v>172.27</v>
+        <v>172.85</v>
       </c>
       <c r="N120" t="n">
-        <v>159.02</v>
+        <v>159.61</v>
       </c>
       <c r="O120" t="n">
-        <v>190.38</v>
+        <v>190.96</v>
       </c>
       <c r="P120" t="n">
         <v>1.63</v>
       </c>
       <c r="Q120" t="n">
-        <v>76.62</v>
+        <v>76.87</v>
       </c>
       <c r="R120" t="n">
-        <v>14.77</v>
+        <v>15.14</v>
       </c>
       <c r="S120" t="n">
-        <v>-3.41</v>
+        <v>-3.08</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13652,7 +13648,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -13694,22 +13690,22 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>49</v>
+        <v>48.88</v>
       </c>
       <c r="D121" t="n">
         <v>42</v>
       </c>
       <c r="E121" t="n">
-        <v>-12.3</v>
+        <v>-12.5</v>
       </c>
       <c r="F121" t="n">
-        <v>5.88</v>
+        <v>5.63</v>
       </c>
       <c r="G121" t="n">
-        <v>59.19</v>
+        <v>58.82</v>
       </c>
       <c r="H121" t="n">
-        <v>-3.5</v>
+        <v>-3.68</v>
       </c>
       <c r="I121" t="n">
         <v>0.5</v>
@@ -13718,31 +13714,31 @@
         <v>4.94</v>
       </c>
       <c r="K121" t="n">
-        <v>10.09</v>
+        <v>10.12</v>
       </c>
       <c r="L121" t="n">
-        <v>47.27</v>
+        <v>47.15</v>
       </c>
       <c r="M121" t="n">
-        <v>49.74</v>
+        <v>49.63</v>
       </c>
       <c r="N121" t="n">
-        <v>42.32</v>
+        <v>42.21</v>
       </c>
       <c r="O121" t="n">
-        <v>59.88</v>
+        <v>59.76</v>
       </c>
       <c r="P121" t="n">
         <v>1.63</v>
       </c>
       <c r="Q121" t="n">
-        <v>59.12</v>
+        <v>58.94</v>
       </c>
       <c r="R121" t="n">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="S121" t="n">
-        <v>-17.16</v>
+        <v>-17.35</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13761,7 +13757,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -13803,55 +13799,55 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>18.52</v>
+        <v>18.5</v>
       </c>
       <c r="D122" t="n">
         <v>15</v>
       </c>
       <c r="E122" t="n">
-        <v>-17.11</v>
+        <v>-17.21</v>
       </c>
       <c r="F122" t="n">
-        <v>-9.01</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="G122" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="H122" t="n">
-        <v>-18.39</v>
+        <v>-18.43</v>
       </c>
       <c r="I122" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="J122" t="n">
         <v>1.95</v>
       </c>
       <c r="K122" t="n">
-        <v>10.51</v>
+        <v>10.53</v>
       </c>
       <c r="L122" t="n">
-        <v>17.84</v>
+        <v>17.82</v>
       </c>
       <c r="M122" t="n">
-        <v>18.82</v>
+        <v>18.8</v>
       </c>
       <c r="N122" t="n">
-        <v>15.9</v>
+        <v>15.87</v>
       </c>
       <c r="O122" t="n">
-        <v>22.81</v>
+        <v>22.79</v>
       </c>
       <c r="P122" t="n">
         <v>1.63</v>
       </c>
       <c r="Q122" t="n">
-        <v>50.78</v>
+        <v>50.72</v>
       </c>
       <c r="R122" t="n">
-        <v>-10.45</v>
+        <v>-10.54</v>
       </c>
       <c r="S122" t="n">
-        <v>-25.24</v>
+        <v>-25.33</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13870,7 +13866,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -13912,22 +13908,22 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>16.35</v>
+        <v>16.3</v>
       </c>
       <c r="D123" t="n">
         <v>15</v>
       </c>
       <c r="E123" t="n">
-        <v>-14.26</v>
+        <v>-14.54</v>
       </c>
       <c r="F123" t="n">
-        <v>-10.41</v>
+        <v>-10.7</v>
       </c>
       <c r="G123" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="H123" t="n">
-        <v>-19.79</v>
+        <v>-20.01</v>
       </c>
       <c r="I123" t="n">
         <v>0.5600000000000001</v>
@@ -13936,31 +13932,31 @@
         <v>1.69</v>
       </c>
       <c r="K123" t="n">
-        <v>10.33</v>
+        <v>10.36</v>
       </c>
       <c r="L123" t="n">
-        <v>15.76</v>
+        <v>15.71</v>
       </c>
       <c r="M123" t="n">
-        <v>16.6</v>
+        <v>16.55</v>
       </c>
       <c r="N123" t="n">
-        <v>14.07</v>
+        <v>14.02</v>
       </c>
       <c r="O123" t="n">
-        <v>20.07</v>
+        <v>20.01</v>
       </c>
       <c r="P123" t="n">
         <v>1.63</v>
       </c>
       <c r="Q123" t="n">
-        <v>50.98</v>
+        <v>50.78</v>
       </c>
       <c r="R123" t="n">
-        <v>-8.56</v>
+        <v>-8.84</v>
       </c>
       <c r="S123" t="n">
-        <v>-22.22</v>
+        <v>-22.47</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13979,7 +13975,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -14021,25 +14017,25 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>208.27</v>
+        <v>208.35</v>
       </c>
       <c r="D124" t="n">
         <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>15.98</v>
+        <v>16.02</v>
       </c>
       <c r="F124" t="n">
-        <v>-9.630000000000001</v>
+        <v>-9.59</v>
       </c>
       <c r="G124" t="n">
-        <v>-4.18</v>
+        <v>-4.15</v>
       </c>
       <c r="H124" t="n">
-        <v>-19.01</v>
+        <v>-18.9</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J124" t="n">
         <v>19.19</v>
@@ -14048,28 +14044,28 @@
         <v>9.210000000000001</v>
       </c>
       <c r="L124" t="n">
-        <v>201.55</v>
+        <v>201.63</v>
       </c>
       <c r="M124" t="n">
-        <v>211.15</v>
+        <v>211.23</v>
       </c>
       <c r="N124" t="n">
-        <v>182.36</v>
+        <v>182.44</v>
       </c>
       <c r="O124" t="n">
-        <v>250.49</v>
+        <v>250.57</v>
       </c>
       <c r="P124" t="n">
         <v>1.63</v>
       </c>
       <c r="Q124" t="n">
-        <v>43.52</v>
+        <v>43.54</v>
       </c>
       <c r="R124" t="n">
-        <v>-3.78</v>
+        <v>-3.74</v>
       </c>
       <c r="S124" t="n">
-        <v>-18.33</v>
+        <v>-18.29</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14088,7 +14084,7 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>QQQ 9.38% · ARKK -3.71% · SPY 4.61%</t>
+          <t>QQQ 9.31% · ARKK -3.87% · SPY 4.56%</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
@@ -14130,55 +14126,55 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>22.97</v>
+        <v>22.89</v>
       </c>
       <c r="D125" t="n">
         <v>53</v>
       </c>
       <c r="E125" t="n">
-        <v>-6.28</v>
+        <v>-6.61</v>
       </c>
       <c r="F125" t="n">
-        <v>31.94</v>
+        <v>31.48</v>
       </c>
       <c r="G125" t="n">
-        <v>46.77</v>
+        <v>46.26</v>
       </c>
       <c r="H125" t="n">
-        <v>22.56</v>
+        <v>22.17</v>
       </c>
       <c r="I125" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="J125" t="n">
         <v>1.63</v>
       </c>
       <c r="K125" t="n">
-        <v>7.09</v>
+        <v>7.11</v>
       </c>
       <c r="L125" t="n">
-        <v>22.4</v>
+        <v>22.32</v>
       </c>
       <c r="M125" t="n">
-        <v>23.21</v>
+        <v>23.13</v>
       </c>
       <c r="N125" t="n">
-        <v>20.77</v>
+        <v>20.69</v>
       </c>
       <c r="O125" t="n">
-        <v>26.55</v>
+        <v>26.47</v>
       </c>
       <c r="P125" t="n">
         <v>1.63</v>
       </c>
       <c r="Q125" t="n">
-        <v>77.72</v>
+        <v>77.23</v>
       </c>
       <c r="R125" t="n">
-        <v>8.91</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S125" t="n">
-        <v>-11.18</v>
+        <v>-11.48</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14197,7 +14193,7 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>BTC-USD 1.45% · ETH-USD -6.02%</t>
+          <t>BTC-USD 1.26% · ETH-USD -6.29%</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
@@ -14223,7 +14219,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.45% · ETH-USD -6.02%; RSI sobrecomprado; Volumen bajo; Momentum negativo; Algo extendida sobre MA20</t>
+          <t>Sector no acompaña: BTC-USD 1.26% · ETH-USD -6.29%; RSI sobrecomprado; Volumen bajo; Momentum negativo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -575,25 +575,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43.06</v>
+        <v>43.02</v>
       </c>
       <c r="D2" t="n">
         <v>96</v>
       </c>
       <c r="E2" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="F2" t="n">
-        <v>12.86</v>
+        <v>12.77</v>
       </c>
       <c r="G2" t="n">
-        <v>22.77</v>
+        <v>22.67</v>
       </c>
       <c r="H2" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="I2" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="J2" t="n">
         <v>1.15</v>
@@ -602,28 +602,28 @@
         <v>2.67</v>
       </c>
       <c r="L2" t="n">
-        <v>42.65</v>
+        <v>42.62</v>
       </c>
       <c r="M2" t="n">
-        <v>43.23</v>
+        <v>43.19</v>
       </c>
       <c r="N2" t="n">
-        <v>41.5</v>
+        <v>41.47</v>
       </c>
       <c r="O2" t="n">
-        <v>45.58</v>
+        <v>45.55</v>
       </c>
       <c r="P2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>56.48</v>
+        <v>56.32</v>
       </c>
       <c r="R2" t="n">
-        <v>4.92</v>
+        <v>4.84</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.73</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>XLE 9.71% · CL=F 13.44%</t>
+          <t>XLE 9.67% · CL=F 13.23%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.71% · CL=F 13.44%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.67% · CL=F 13.23%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>207.89</v>
+        <v>207.82</v>
       </c>
       <c r="D3" t="n">
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>5.49</v>
+        <v>5.46</v>
       </c>
       <c r="F3" t="n">
-        <v>10.13</v>
+        <v>10.1</v>
       </c>
       <c r="G3" t="n">
-        <v>20.98</v>
+        <v>20.94</v>
       </c>
       <c r="H3" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="I3" t="n">
         <v>0.37</v>
@@ -715,28 +715,28 @@
         <v>3.08</v>
       </c>
       <c r="L3" t="n">
-        <v>205.65</v>
+        <v>205.58</v>
       </c>
       <c r="M3" t="n">
-        <v>208.85</v>
+        <v>208.78</v>
       </c>
       <c r="N3" t="n">
-        <v>199.24</v>
+        <v>199.17</v>
       </c>
       <c r="O3" t="n">
-        <v>221.99</v>
+        <v>221.92</v>
       </c>
       <c r="P3" t="n">
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>53.46</v>
+        <v>53.4</v>
       </c>
       <c r="R3" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.55</v>
+        <v>-2.59</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>XLE 9.71% · CL=F 13.44%</t>
+          <t>XLE 9.67% · CL=F 13.23%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.71% · CL=F 13.44%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.67% · CL=F 13.23%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -801,25 +801,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>57</v>
+        <v>56.97</v>
       </c>
       <c r="D4" t="n">
         <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="F4" t="n">
-        <v>8.02</v>
+        <v>7.97</v>
       </c>
       <c r="G4" t="n">
-        <v>11.24</v>
+        <v>11.19</v>
       </c>
       <c r="H4" t="n">
         <v>-1.22</v>
       </c>
       <c r="I4" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="J4" t="n">
         <v>1.46</v>
@@ -828,28 +828,28 @@
         <v>2.56</v>
       </c>
       <c r="L4" t="n">
-        <v>56.49</v>
+        <v>56.46</v>
       </c>
       <c r="M4" t="n">
-        <v>57.22</v>
+        <v>57.19</v>
       </c>
       <c r="N4" t="n">
-        <v>55.03</v>
+        <v>55</v>
       </c>
       <c r="O4" t="n">
-        <v>60.21</v>
+        <v>60.19</v>
       </c>
       <c r="P4" t="n">
         <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>55.68</v>
+        <v>55.56</v>
       </c>
       <c r="R4" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.02</v>
+        <v>-1.07</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>XLE 9.71% · CL=F 13.44%</t>
+          <t>XLE 9.67% · CL=F 13.23%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.71% · CL=F 13.44%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.67% · CL=F 13.23%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -914,25 +914,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>197.08</v>
+        <v>197.05</v>
       </c>
       <c r="D5" t="n">
         <v>96</v>
       </c>
       <c r="E5" t="n">
-        <v>5.99</v>
+        <v>5.97</v>
       </c>
       <c r="F5" t="n">
-        <v>5.97</v>
+        <v>5.95</v>
       </c>
       <c r="G5" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.27</v>
+        <v>-3.24</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="J5" t="n">
         <v>4.43</v>
@@ -941,28 +941,28 @@
         <v>2.25</v>
       </c>
       <c r="L5" t="n">
-        <v>195.53</v>
+        <v>195.5</v>
       </c>
       <c r="M5" t="n">
-        <v>197.75</v>
+        <v>197.72</v>
       </c>
       <c r="N5" t="n">
-        <v>191.09</v>
+        <v>191.06</v>
       </c>
       <c r="O5" t="n">
-        <v>206.83</v>
+        <v>206.8</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>57.53</v>
+        <v>57.49</v>
       </c>
       <c r="R5" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>XLE 9.71% · CL=F 13.44%</t>
+          <t>XLE 9.67% · CL=F 13.23%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.71% · CL=F 13.44%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.67% · CL=F 13.23%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1027,22 +1027,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>107.03</v>
+        <v>106.86</v>
       </c>
       <c r="D6" t="n">
         <v>96</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="F6" t="n">
-        <v>23.15</v>
+        <v>22.96</v>
       </c>
       <c r="G6" t="n">
-        <v>54.07</v>
+        <v>53.83</v>
       </c>
       <c r="H6" t="n">
-        <v>13.91</v>
+        <v>13.77</v>
       </c>
       <c r="I6" t="n">
         <v>0.45</v>
@@ -1051,31 +1051,31 @@
         <v>6.26</v>
       </c>
       <c r="K6" t="n">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="L6" t="n">
-        <v>104.84</v>
+        <v>104.67</v>
       </c>
       <c r="M6" t="n">
-        <v>107.97</v>
+        <v>107.8</v>
       </c>
       <c r="N6" t="n">
-        <v>98.58</v>
+        <v>98.41</v>
       </c>
       <c r="O6" t="n">
-        <v>120.81</v>
+        <v>120.64</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>58.27</v>
+        <v>58.07</v>
       </c>
       <c r="R6" t="n">
-        <v>3.49</v>
+        <v>3.33</v>
       </c>
       <c r="S6" t="n">
-        <v>-10.13</v>
+        <v>-10.27</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>547.28</v>
+        <v>547.5700000000001</v>
       </c>
       <c r="D7" t="n">
         <v>96</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.49</v>
+        <v>-2.44</v>
       </c>
       <c r="F7" t="n">
-        <v>17.78</v>
+        <v>17.84</v>
       </c>
       <c r="G7" t="n">
-        <v>32.55</v>
+        <v>32.62</v>
       </c>
       <c r="H7" t="n">
-        <v>8.539999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="I7" t="n">
         <v>0.97</v>
@@ -1167,28 +1167,28 @@
         <v>3.62</v>
       </c>
       <c r="L7" t="n">
-        <v>540.35</v>
+        <v>540.63</v>
       </c>
       <c r="M7" t="n">
-        <v>550.26</v>
+        <v>550.54</v>
       </c>
       <c r="N7" t="n">
-        <v>520.53</v>
+        <v>520.8099999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>590.89</v>
+        <v>591.1799999999999</v>
       </c>
       <c r="P7" t="n">
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>64.23</v>
+        <v>64.3</v>
       </c>
       <c r="R7" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.83</v>
+        <v>-5.78</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1253,22 +1253,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>222.65</v>
+        <v>222.45</v>
       </c>
       <c r="D8" t="n">
         <v>96</v>
       </c>
       <c r="E8" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F8" t="n">
-        <v>11.39</v>
+        <v>11.29</v>
       </c>
       <c r="G8" t="n">
-        <v>16.24</v>
+        <v>16.14</v>
       </c>
       <c r="H8" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="I8" t="n">
         <v>0.59</v>
@@ -1277,31 +1277,31 @@
         <v>8.51</v>
       </c>
       <c r="K8" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="L8" t="n">
-        <v>219.67</v>
+        <v>219.47</v>
       </c>
       <c r="M8" t="n">
-        <v>223.93</v>
+        <v>223.72</v>
       </c>
       <c r="N8" t="n">
-        <v>211.16</v>
+        <v>210.95</v>
       </c>
       <c r="O8" t="n">
-        <v>241.38</v>
+        <v>241.17</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>60.18</v>
+        <v>60.06</v>
       </c>
       <c r="R8" t="n">
-        <v>4.8</v>
+        <v>4.71</v>
       </c>
       <c r="S8" t="n">
-        <v>-5.87</v>
+        <v>-5.96</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1366,22 +1366,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>296.28</v>
+        <v>296.21</v>
       </c>
       <c r="D9" t="n">
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="F9" t="n">
-        <v>31.97</v>
+        <v>31.94</v>
       </c>
       <c r="G9" t="n">
-        <v>28.84</v>
+        <v>28.81</v>
       </c>
       <c r="H9" t="n">
-        <v>22.73</v>
+        <v>22.75</v>
       </c>
       <c r="I9" t="n">
         <v>0.31</v>
@@ -1393,28 +1393,28 @@
         <v>3.88</v>
       </c>
       <c r="L9" t="n">
-        <v>292.26</v>
+        <v>292.19</v>
       </c>
       <c r="M9" t="n">
-        <v>298</v>
+        <v>297.93</v>
       </c>
       <c r="N9" t="n">
-        <v>280.77</v>
+        <v>280.7</v>
       </c>
       <c r="O9" t="n">
-        <v>321.55</v>
+        <v>321.48</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>54.39</v>
+        <v>54.35</v>
       </c>
       <c r="R9" t="n">
-        <v>5.81</v>
+        <v>5.79</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.37</v>
+        <v>-3.4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>499.98</v>
+        <v>500.22</v>
       </c>
       <c r="D10" t="n">
         <v>91</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1</v>
+        <v>-3.06</v>
       </c>
       <c r="F10" t="n">
-        <v>18.84</v>
+        <v>18.9</v>
       </c>
       <c r="G10" t="n">
-        <v>40.21</v>
+        <v>40.27</v>
       </c>
       <c r="H10" t="n">
-        <v>9.6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>1.26</v>
@@ -1506,28 +1506,28 @@
         <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>492.62</v>
+        <v>492.86</v>
       </c>
       <c r="M10" t="n">
-        <v>503.13</v>
+        <v>503.37</v>
       </c>
       <c r="N10" t="n">
-        <v>471.61</v>
+        <v>471.85</v>
       </c>
       <c r="O10" t="n">
-        <v>546.21</v>
+        <v>546.45</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>63.28</v>
+        <v>63.32</v>
       </c>
       <c r="R10" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.33</v>
+        <v>-6.28</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1592,22 +1592,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>92.69</v>
+        <v>92.61</v>
       </c>
       <c r="D11" t="n">
         <v>74</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.13</v>
+        <v>-5.21</v>
       </c>
       <c r="F11" t="n">
-        <v>14.53</v>
+        <v>14.43</v>
       </c>
       <c r="G11" t="n">
-        <v>21.01</v>
+        <v>20.9</v>
       </c>
       <c r="H11" t="n">
-        <v>5.29</v>
+        <v>5.24</v>
       </c>
       <c r="I11" t="n">
         <v>0.29</v>
@@ -1619,28 +1619,28 @@
         <v>4.5</v>
       </c>
       <c r="L11" t="n">
-        <v>91.23</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>93.31999999999999</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>87.06</v>
+        <v>86.98</v>
       </c>
       <c r="O11" t="n">
-        <v>101.86</v>
+        <v>101.78</v>
       </c>
       <c r="P11" t="n">
         <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>55.33</v>
+        <v>55.14</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.28</v>
+        <v>-1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>-12.48</v>
+        <v>-12.56</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1705,22 +1705,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>395.08</v>
+        <v>394.84</v>
       </c>
       <c r="D12" t="n">
         <v>74</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.55</v>
+        <v>-0.61</v>
       </c>
       <c r="F12" t="n">
-        <v>7.34</v>
+        <v>7.27</v>
       </c>
       <c r="G12" t="n">
-        <v>7.07</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9</v>
+        <v>-1.92</v>
       </c>
       <c r="I12" t="n">
         <v>0.71</v>
@@ -1732,28 +1732,28 @@
         <v>3.98</v>
       </c>
       <c r="L12" t="n">
-        <v>389.58</v>
+        <v>389.34</v>
       </c>
       <c r="M12" t="n">
-        <v>397.44</v>
+        <v>397.2</v>
       </c>
       <c r="N12" t="n">
-        <v>373.86</v>
+        <v>373.62</v>
       </c>
       <c r="O12" t="n">
-        <v>429.67</v>
+        <v>429.42</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>50.6</v>
+        <v>50.48</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.4</v>
+        <v>-1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.37</v>
+        <v>-6.43</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1814,22 +1814,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>106.73</v>
+        <v>106.7</v>
       </c>
       <c r="D13" t="n">
         <v>96</v>
       </c>
       <c r="E13" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="F13" t="n">
-        <v>9.77</v>
+        <v>9.74</v>
       </c>
       <c r="G13" t="n">
-        <v>13.27</v>
+        <v>13.24</v>
       </c>
       <c r="H13" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="I13" t="n">
         <v>0.33</v>
@@ -1841,28 +1841,28 @@
         <v>2.32</v>
       </c>
       <c r="L13" t="n">
-        <v>105.86</v>
+        <v>105.83</v>
       </c>
       <c r="M13" t="n">
-        <v>107.1</v>
+        <v>107.07</v>
       </c>
       <c r="N13" t="n">
-        <v>103.38</v>
+        <v>103.35</v>
       </c>
       <c r="O13" t="n">
-        <v>112.19</v>
+        <v>112.16</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>59.12</v>
+        <v>58.99</v>
       </c>
       <c r="R13" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4</v>
+        <v>-1.43</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1927,25 +1927,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>254.6</v>
+        <v>254.47</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
       </c>
       <c r="E14" t="n">
-        <v>5.72</v>
+        <v>5.66</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="G14" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="H14" t="n">
         <v>-6.24</v>
       </c>
       <c r="I14" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>9.41</v>
@@ -1954,28 +1954,28 @@
         <v>3.7</v>
       </c>
       <c r="L14" t="n">
-        <v>251.3</v>
+        <v>251.18</v>
       </c>
       <c r="M14" t="n">
-        <v>256.01</v>
+        <v>255.88</v>
       </c>
       <c r="N14" t="n">
-        <v>241.89</v>
+        <v>241.77</v>
       </c>
       <c r="O14" t="n">
-        <v>275.3</v>
+        <v>275.17</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>58.49</v>
+        <v>58.38</v>
       </c>
       <c r="R14" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.96</v>
+        <v>-4.01</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2040,22 +2040,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>114.4</v>
+        <v>114.39</v>
       </c>
       <c r="D15" t="n">
         <v>96</v>
       </c>
       <c r="E15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="F15" t="n">
         <v>1.63</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.92</v>
+        <v>-6.93</v>
       </c>
       <c r="H15" t="n">
-        <v>-7.61</v>
+        <v>-7.56</v>
       </c>
       <c r="I15" t="n">
         <v>0.42</v>
@@ -2067,28 +2067,28 @@
         <v>2.29</v>
       </c>
       <c r="L15" t="n">
-        <v>113.48</v>
+        <v>113.47</v>
       </c>
       <c r="M15" t="n">
-        <v>114.79</v>
+        <v>114.78</v>
       </c>
       <c r="N15" t="n">
-        <v>110.87</v>
+        <v>110.86</v>
       </c>
       <c r="O15" t="n">
-        <v>120.16</v>
+        <v>120.15</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>60.99</v>
+        <v>60.97</v>
       </c>
       <c r="R15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>229.2</v>
+        <v>229.19</v>
       </c>
       <c r="D16" t="n">
         <v>93</v>
@@ -2168,7 +2168,7 @@
         <v>-6.28</v>
       </c>
       <c r="H16" t="n">
-        <v>-7.9</v>
+        <v>-7.85</v>
       </c>
       <c r="I16" t="n">
         <v>0.6</v>
@@ -2180,13 +2180,13 @@
         <v>1.66</v>
       </c>
       <c r="L16" t="n">
-        <v>227.87</v>
+        <v>227.86</v>
       </c>
       <c r="M16" t="n">
         <v>229.76</v>
       </c>
       <c r="N16" t="n">
-        <v>224.07</v>
+        <v>224.06</v>
       </c>
       <c r="O16" t="n">
         <v>237.55</v>
@@ -2195,7 +2195,7 @@
         <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>53.1</v>
+        <v>53.09</v>
       </c>
       <c r="R16" t="n">
         <v>1.15</v>
@@ -2266,25 +2266,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>213.1</v>
+        <v>213.82</v>
       </c>
       <c r="D17" t="n">
         <v>82</v>
       </c>
       <c r="E17" t="n">
-        <v>2.52</v>
+        <v>2.87</v>
       </c>
       <c r="F17" t="n">
-        <v>3.89</v>
+        <v>4.24</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.37</v>
+        <v>-6.05</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.35</v>
+        <v>-4.95</v>
       </c>
       <c r="I17" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="J17" t="n">
         <v>5.32</v>
@@ -2293,28 +2293,28 @@
         <v>2.49</v>
       </c>
       <c r="L17" t="n">
-        <v>211.23</v>
+        <v>211.96</v>
       </c>
       <c r="M17" t="n">
-        <v>213.89</v>
+        <v>214.62</v>
       </c>
       <c r="N17" t="n">
-        <v>205.92</v>
+        <v>206.64</v>
       </c>
       <c r="O17" t="n">
-        <v>224.79</v>
+        <v>225.51</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.31</v>
+        <v>64.06</v>
       </c>
       <c r="R17" t="n">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.25</v>
+        <v>-0.92</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2379,22 +2379,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>92.40000000000001</v>
+        <v>92.44</v>
       </c>
       <c r="D18" t="n">
         <v>82</v>
       </c>
       <c r="E18" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="F18" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H18" t="n">
-        <v>-8.41</v>
+        <v>-8.32</v>
       </c>
       <c r="I18" t="n">
         <v>0.52</v>
@@ -2406,28 +2406,28 @@
         <v>2.38</v>
       </c>
       <c r="L18" t="n">
-        <v>91.63</v>
+        <v>91.67</v>
       </c>
       <c r="M18" t="n">
-        <v>92.73999999999999</v>
+        <v>92.77</v>
       </c>
       <c r="N18" t="n">
-        <v>89.43000000000001</v>
+        <v>89.47</v>
       </c>
       <c r="O18" t="n">
-        <v>97.25</v>
+        <v>97.28</v>
       </c>
       <c r="P18" t="n">
         <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>55.68</v>
+        <v>55.79</v>
       </c>
       <c r="R18" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1</v>
+        <v>-1.06</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2492,25 +2492,25 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>495.38</v>
+        <v>495.2</v>
       </c>
       <c r="D19" t="n">
         <v>81</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.45</v>
+        <v>-0.49</v>
       </c>
       <c r="F19" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="G19" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="H19" t="n">
-        <v>-8.369999999999999</v>
+        <v>-8.35</v>
       </c>
       <c r="I19" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="J19" t="n">
         <v>5.11</v>
@@ -2519,28 +2519,28 @@
         <v>1.03</v>
       </c>
       <c r="L19" t="n">
-        <v>493.59</v>
+        <v>493.41</v>
       </c>
       <c r="M19" t="n">
-        <v>496.15</v>
+        <v>495.97</v>
       </c>
       <c r="N19" t="n">
-        <v>488.48</v>
+        <v>488.3</v>
       </c>
       <c r="O19" t="n">
-        <v>506.63</v>
+        <v>506.45</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.21</v>
+        <v>57.97</v>
       </c>
       <c r="R19" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3</v>
+        <v>-1.33</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2601,22 +2601,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>330.69</v>
+        <v>330.67</v>
       </c>
       <c r="D20" t="n">
         <v>80</v>
       </c>
       <c r="E20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="F20" t="n">
-        <v>6.92</v>
+        <v>6.91</v>
       </c>
       <c r="G20" t="n">
-        <v>8.109999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.32</v>
+        <v>-2.28</v>
       </c>
       <c r="I20" t="n">
         <v>0.62</v>
@@ -2628,28 +2628,28 @@
         <v>1.88</v>
       </c>
       <c r="L20" t="n">
-        <v>328.52</v>
+        <v>328.5</v>
       </c>
       <c r="M20" t="n">
-        <v>331.62</v>
+        <v>331.6</v>
       </c>
       <c r="N20" t="n">
-        <v>322.31</v>
+        <v>322.29</v>
       </c>
       <c r="O20" t="n">
-        <v>344.35</v>
+        <v>344.33</v>
       </c>
       <c r="P20" t="n">
         <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>46.5</v>
+        <v>46.48</v>
       </c>
       <c r="R20" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="S20" t="n">
-        <v>-3.1</v>
+        <v>-3.11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2710,25 +2710,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>191.44</v>
+        <v>191.48</v>
       </c>
       <c r="D21" t="n">
         <v>78</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="F21" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G21" t="n">
-        <v>15.39</v>
+        <v>15.41</v>
       </c>
       <c r="H21" t="n">
-        <v>-7.57</v>
+        <v>-7.5</v>
       </c>
       <c r="I21" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="J21" t="n">
         <v>4.27</v>
@@ -2737,28 +2737,28 @@
         <v>2.23</v>
       </c>
       <c r="L21" t="n">
-        <v>189.95</v>
+        <v>189.99</v>
       </c>
       <c r="M21" t="n">
-        <v>192.08</v>
+        <v>192.12</v>
       </c>
       <c r="N21" t="n">
-        <v>185.68</v>
+        <v>185.72</v>
       </c>
       <c r="O21" t="n">
-        <v>200.83</v>
+        <v>200.87</v>
       </c>
       <c r="P21" t="n">
         <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>59.78</v>
+        <v>59.87</v>
       </c>
       <c r="R21" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.07</v>
+        <v>-3.05</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2819,25 +2819,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>933.8200000000001</v>
+        <v>934.03</v>
       </c>
       <c r="D22" t="n">
         <v>78</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.28</v>
+        <v>-1.25</v>
       </c>
       <c r="F22" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>5.2</v>
+        <v>5.23</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="J22" t="n">
         <v>23.14</v>
@@ -2846,28 +2846,28 @@
         <v>2.48</v>
       </c>
       <c r="L22" t="n">
-        <v>925.72</v>
+        <v>925.9299999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>937.29</v>
+        <v>937.5</v>
       </c>
       <c r="N22" t="n">
-        <v>902.58</v>
+        <v>902.79</v>
       </c>
       <c r="O22" t="n">
-        <v>984.73</v>
+        <v>984.9400000000001</v>
       </c>
       <c r="P22" t="n">
         <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>58.69</v>
+        <v>58.76</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.29</v>
+        <v>-4.27</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2928,55 +2928,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>402.16</v>
+        <v>401.91</v>
       </c>
       <c r="D23" t="n">
         <v>74</v>
       </c>
       <c r="E23" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.66</v>
+        <v>-0.73</v>
       </c>
       <c r="G23" t="n">
-        <v>12.2</v>
+        <v>12.13</v>
       </c>
       <c r="H23" t="n">
-        <v>-9.9</v>
+        <v>-9.92</v>
       </c>
       <c r="I23" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>18.64</v>
       </c>
       <c r="K23" t="n">
-        <v>4.63</v>
+        <v>4.64</v>
       </c>
       <c r="L23" t="n">
-        <v>395.64</v>
+        <v>395.39</v>
       </c>
       <c r="M23" t="n">
-        <v>404.96</v>
+        <v>404.71</v>
       </c>
       <c r="N23" t="n">
-        <v>377</v>
+        <v>376.75</v>
       </c>
       <c r="O23" t="n">
-        <v>443.16</v>
+        <v>442.91</v>
       </c>
       <c r="P23" t="n">
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>52.74</v>
+        <v>52.64</v>
       </c>
       <c r="R23" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.15</v>
+        <v>-5.21</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3037,22 +3037,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>180.97</v>
+        <v>180.69</v>
       </c>
       <c r="D24" t="n">
         <v>74</v>
       </c>
       <c r="E24" t="n">
-        <v>5.64</v>
+        <v>5.48</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.28</v>
+        <v>-3.43</v>
       </c>
       <c r="G24" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="H24" t="n">
-        <v>-12.52</v>
+        <v>-12.62</v>
       </c>
       <c r="I24" t="n">
         <v>0.96</v>
@@ -3061,31 +3061,31 @@
         <v>7.55</v>
       </c>
       <c r="K24" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="L24" t="n">
-        <v>178.33</v>
+        <v>178.05</v>
       </c>
       <c r="M24" t="n">
-        <v>182.1</v>
+        <v>181.82</v>
       </c>
       <c r="N24" t="n">
-        <v>170.78</v>
+        <v>170.5</v>
       </c>
       <c r="O24" t="n">
-        <v>197.57</v>
+        <v>197.29</v>
       </c>
       <c r="P24" t="n">
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>49.8</v>
+        <v>49.57</v>
       </c>
       <c r="R24" t="n">
-        <v>1.03</v>
+        <v>0.89</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.33</v>
+        <v>-5.47</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -3146,25 +3146,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>162.59</v>
+        <v>162.65</v>
       </c>
       <c r="D25" t="n">
         <v>96</v>
       </c>
       <c r="E25" t="n">
-        <v>8.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>10.33</v>
+        <v>10.38</v>
       </c>
       <c r="G25" t="n">
-        <v>8.58</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="I25" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>4.13</v>
@@ -3173,28 +3173,28 @@
         <v>2.54</v>
       </c>
       <c r="L25" t="n">
-        <v>161.14</v>
+        <v>161.2</v>
       </c>
       <c r="M25" t="n">
-        <v>163.2</v>
+        <v>163.27</v>
       </c>
       <c r="N25" t="n">
-        <v>157.01</v>
+        <v>157.07</v>
       </c>
       <c r="O25" t="n">
-        <v>171.67</v>
+        <v>171.74</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>63.47</v>
+        <v>63.54</v>
       </c>
       <c r="R25" t="n">
-        <v>7.45</v>
+        <v>7.49</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>XLE 9.71% · CL=F 13.44%</t>
+          <t>XLE 9.67% · CL=F 13.23%</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.71% · CL=F 13.44%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.67% · CL=F 13.23%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3268,13 +3268,13 @@
         <v>6.44</v>
       </c>
       <c r="F26" t="n">
-        <v>9.67</v>
+        <v>9.68</v>
       </c>
       <c r="G26" t="n">
-        <v>11.83</v>
+        <v>11.84</v>
       </c>
       <c r="H26" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="I26" t="n">
         <v>0.61</v>
@@ -3295,19 +3295,19 @@
         <v>59.44</v>
       </c>
       <c r="O26" t="n">
-        <v>64.27</v>
+        <v>64.28</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>59.89</v>
+        <v>59.91</v>
       </c>
       <c r="R26" t="n">
-        <v>5.5</v>
+        <v>5.51</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>XLE 9.71% · CL=F 13.44%</t>
+          <t>XLE 9.67% · CL=F 13.23%</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.71% · CL=F 13.44%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.67% · CL=F 13.23%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3372,25 +3372,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>49.84</v>
+        <v>49.8</v>
       </c>
       <c r="D27" t="n">
         <v>96</v>
       </c>
       <c r="E27" t="n">
-        <v>6.56</v>
+        <v>6.48</v>
       </c>
       <c r="F27" t="n">
-        <v>9.300000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>14.72</v>
+        <v>14.63</v>
       </c>
       <c r="H27" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I27" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="J27" t="n">
         <v>1.72</v>
@@ -3399,28 +3399,28 @@
         <v>3.45</v>
       </c>
       <c r="L27" t="n">
-        <v>49.24</v>
+        <v>49.2</v>
       </c>
       <c r="M27" t="n">
-        <v>50.1</v>
+        <v>50.06</v>
       </c>
       <c r="N27" t="n">
-        <v>47.52</v>
+        <v>47.48</v>
       </c>
       <c r="O27" t="n">
-        <v>53.62</v>
+        <v>53.58</v>
       </c>
       <c r="P27" t="n">
         <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>44.95</v>
+        <v>44.77</v>
       </c>
       <c r="R27" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.06</v>
+        <v>-4.14</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>XLE 9.71% · CL=F 13.44%</t>
+          <t>XLE 9.67% · CL=F 13.23%</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.71% · CL=F 13.44%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.67% · CL=F 13.23%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3485,22 +3485,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>144.16</v>
+        <v>144.15</v>
       </c>
       <c r="D28" t="n">
         <v>96</v>
       </c>
       <c r="E28" t="n">
-        <v>7.48</v>
+        <v>7.47</v>
       </c>
       <c r="F28" t="n">
-        <v>8.859999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="G28" t="n">
-        <v>18.78</v>
+        <v>18.77</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.38</v>
+        <v>-0.34</v>
       </c>
       <c r="I28" t="n">
         <v>0.49</v>
@@ -3512,28 +3512,28 @@
         <v>2.72</v>
       </c>
       <c r="L28" t="n">
-        <v>142.79</v>
+        <v>142.78</v>
       </c>
       <c r="M28" t="n">
-        <v>144.75</v>
+        <v>144.74</v>
       </c>
       <c r="N28" t="n">
-        <v>138.87</v>
+        <v>138.86</v>
       </c>
       <c r="O28" t="n">
-        <v>152.78</v>
+        <v>152.77</v>
       </c>
       <c r="P28" t="n">
         <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>58.02</v>
+        <v>58</v>
       </c>
       <c r="R28" t="n">
-        <v>5.56</v>
+        <v>5.55</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>XLE 9.71% · CL=F 13.44%</t>
+          <t>XLE 9.67% · CL=F 13.23%</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.71% · CL=F 13.44%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.67% · CL=F 13.23%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3598,22 +3598,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>125.38</v>
+        <v>125.3</v>
       </c>
       <c r="D29" t="n">
         <v>85</v>
       </c>
       <c r="E29" t="n">
-        <v>6.37</v>
+        <v>6.3</v>
       </c>
       <c r="F29" t="n">
-        <v>5.03</v>
+        <v>4.97</v>
       </c>
       <c r="G29" t="n">
-        <v>14.95</v>
+        <v>14.88</v>
       </c>
       <c r="H29" t="n">
-        <v>-4.21</v>
+        <v>-4.22</v>
       </c>
       <c r="I29" t="n">
         <v>0.39</v>
@@ -3625,28 +3625,28 @@
         <v>2.64</v>
       </c>
       <c r="L29" t="n">
-        <v>124.22</v>
+        <v>124.14</v>
       </c>
       <c r="M29" t="n">
-        <v>125.88</v>
+        <v>125.8</v>
       </c>
       <c r="N29" t="n">
-        <v>120.92</v>
+        <v>120.84</v>
       </c>
       <c r="O29" t="n">
-        <v>132.66</v>
+        <v>132.58</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>46.89</v>
+        <v>46.76</v>
       </c>
       <c r="R29" t="n">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.53</v>
+        <v>-1.6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>XLE 9.71% · CL=F 13.44%</t>
+          <t>XLE 9.67% · CL=F 13.23%</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.71% · CL=F 13.44%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.67% · CL=F 13.23%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3711,25 +3711,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>60.78</v>
+        <v>60.79</v>
       </c>
       <c r="D30" t="n">
         <v>96</v>
       </c>
       <c r="E30" t="n">
-        <v>8.02</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>7.91</v>
+        <v>7.92</v>
       </c>
       <c r="G30" t="n">
-        <v>16.49</v>
+        <v>16.5</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.33</v>
+        <v>-1.27</v>
       </c>
       <c r="I30" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="J30" t="n">
         <v>1.93</v>
@@ -3744,19 +3744,19 @@
         <v>61.08</v>
       </c>
       <c r="N30" t="n">
-        <v>58.17</v>
+        <v>58.18</v>
       </c>
       <c r="O30" t="n">
-        <v>65.04000000000001</v>
+        <v>65.05</v>
       </c>
       <c r="P30" t="n">
         <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.07</v>
+        <v>50.08</v>
       </c>
       <c r="R30" t="n">
-        <v>5.33</v>
+        <v>5.34</v>
       </c>
       <c r="S30" t="n">
         <v>-0.02</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>XLE 9.71% · CL=F 13.44%</t>
+          <t>XLE 9.67% · CL=F 13.23%</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.71% · CL=F 13.44%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.67% · CL=F 13.23%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3824,22 +3824,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>223.76</v>
+        <v>224.01</v>
       </c>
       <c r="D31" t="n">
         <v>94</v>
       </c>
       <c r="E31" t="n">
-        <v>7.62</v>
+        <v>7.74</v>
       </c>
       <c r="F31" t="n">
-        <v>27.5</v>
+        <v>27.65</v>
       </c>
       <c r="G31" t="n">
-        <v>80.77</v>
+        <v>80.97</v>
       </c>
       <c r="H31" t="n">
-        <v>18.26</v>
+        <v>18.46</v>
       </c>
       <c r="I31" t="n">
         <v>0.71</v>
@@ -3851,28 +3851,28 @@
         <v>7.32</v>
       </c>
       <c r="L31" t="n">
-        <v>218.02</v>
+        <v>218.27</v>
       </c>
       <c r="M31" t="n">
-        <v>226.21</v>
+        <v>226.46</v>
       </c>
       <c r="N31" t="n">
-        <v>201.63</v>
+        <v>201.88</v>
       </c>
       <c r="O31" t="n">
-        <v>259.81</v>
+        <v>260.06</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>58.15</v>
+        <v>58.23</v>
       </c>
       <c r="R31" t="n">
-        <v>4.85</v>
+        <v>4.96</v>
       </c>
       <c r="S31" t="n">
-        <v>-6.57</v>
+        <v>-6.47</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3937,22 +3937,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>178.48</v>
+        <v>178.05</v>
       </c>
       <c r="D32" t="n">
         <v>94</v>
       </c>
       <c r="E32" t="n">
-        <v>8.5</v>
+        <v>8.24</v>
       </c>
       <c r="F32" t="n">
-        <v>17.95</v>
+        <v>17.68</v>
       </c>
       <c r="G32" t="n">
-        <v>129.55</v>
+        <v>129.01</v>
       </c>
       <c r="H32" t="n">
-        <v>8.710000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="I32" t="n">
         <v>0.6899999999999999</v>
@@ -3961,31 +3961,31 @@
         <v>12</v>
       </c>
       <c r="K32" t="n">
-        <v>6.73</v>
+        <v>6.74</v>
       </c>
       <c r="L32" t="n">
-        <v>174.28</v>
+        <v>173.85</v>
       </c>
       <c r="M32" t="n">
-        <v>180.28</v>
+        <v>179.86</v>
       </c>
       <c r="N32" t="n">
-        <v>162.27</v>
+        <v>161.85</v>
       </c>
       <c r="O32" t="n">
-        <v>204.89</v>
+        <v>204.46</v>
       </c>
       <c r="P32" t="n">
         <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>62.29</v>
+        <v>62.11</v>
       </c>
       <c r="R32" t="n">
-        <v>6.87</v>
+        <v>6.63</v>
       </c>
       <c r="S32" t="n">
-        <v>-7.12</v>
+        <v>-7.34</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4050,25 +4050,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>417.23</v>
+        <v>417.49</v>
       </c>
       <c r="D33" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.58</v>
+        <v>-0.51</v>
       </c>
       <c r="F33" t="n">
-        <v>11.18</v>
+        <v>11.25</v>
       </c>
       <c r="G33" t="n">
-        <v>17.85</v>
+        <v>17.92</v>
       </c>
       <c r="H33" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="I33" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="J33" t="n">
         <v>12.35</v>
@@ -4077,28 +4077,28 @@
         <v>2.96</v>
       </c>
       <c r="L33" t="n">
-        <v>412.91</v>
+        <v>413.17</v>
       </c>
       <c r="M33" t="n">
-        <v>419.08</v>
+        <v>419.35</v>
       </c>
       <c r="N33" t="n">
-        <v>400.55</v>
+        <v>400.82</v>
       </c>
       <c r="O33" t="n">
-        <v>444.41</v>
+        <v>444.67</v>
       </c>
       <c r="P33" t="n">
         <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>65.29000000000001</v>
+        <v>65.48</v>
       </c>
       <c r="R33" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="S33" t="n">
-        <v>-4.24</v>
+        <v>-4.18</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4163,19 +4163,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>86.81999999999999</v>
+        <v>86.78</v>
       </c>
       <c r="D34" t="n">
         <v>90</v>
       </c>
       <c r="E34" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="F34" t="n">
-        <v>21.9</v>
+        <v>21.85</v>
       </c>
       <c r="G34" t="n">
-        <v>26.17</v>
+        <v>26.12</v>
       </c>
       <c r="H34" t="n">
         <v>12.66</v>
@@ -4190,28 +4190,28 @@
         <v>8.73</v>
       </c>
       <c r="L34" t="n">
-        <v>84.17</v>
+        <v>84.13</v>
       </c>
       <c r="M34" t="n">
-        <v>87.95999999999999</v>
+        <v>87.92</v>
       </c>
       <c r="N34" t="n">
-        <v>76.59</v>
+        <v>76.55</v>
       </c>
       <c r="O34" t="n">
-        <v>103.49</v>
+        <v>103.45</v>
       </c>
       <c r="P34" t="n">
         <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>64.18000000000001</v>
+        <v>64.14</v>
       </c>
       <c r="R34" t="n">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="S34" t="n">
-        <v>-9.859999999999999</v>
+        <v>-9.9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -4276,22 +4276,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>134.21</v>
+        <v>134.13</v>
       </c>
       <c r="D35" t="n">
         <v>96</v>
       </c>
       <c r="E35" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="F35" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="G35" t="n">
-        <v>7.1</v>
+        <v>7.04</v>
       </c>
       <c r="H35" t="n">
-        <v>-5.49</v>
+        <v>-5.5</v>
       </c>
       <c r="I35" t="n">
         <v>0.63</v>
@@ -4303,28 +4303,28 @@
         <v>1.99</v>
       </c>
       <c r="L35" t="n">
-        <v>133.28</v>
+        <v>133.2</v>
       </c>
       <c r="M35" t="n">
-        <v>134.61</v>
+        <v>134.53</v>
       </c>
       <c r="N35" t="n">
-        <v>130.61</v>
+        <v>130.53</v>
       </c>
       <c r="O35" t="n">
-        <v>140.08</v>
+        <v>140</v>
       </c>
       <c r="P35" t="n">
         <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>67.18000000000001</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="R35" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.7</v>
+        <v>-0.76</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4380,64 +4380,64 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ciberseguridad</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>86.42</v>
+        <v>389.68</v>
       </c>
       <c r="D36" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E36" t="n">
-        <v>9.31</v>
+        <v>0.6</v>
       </c>
       <c r="F36" t="n">
-        <v>11.31</v>
+        <v>17.27</v>
       </c>
       <c r="G36" t="n">
-        <v>24.33</v>
+        <v>25.19</v>
       </c>
       <c r="H36" t="n">
-        <v>2.07</v>
+        <v>8.08</v>
       </c>
       <c r="I36" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="J36" t="n">
-        <v>3.74</v>
+        <v>11.59</v>
       </c>
       <c r="K36" t="n">
-        <v>4.32</v>
+        <v>2.97</v>
       </c>
       <c r="L36" t="n">
-        <v>85.11</v>
+        <v>385.62</v>
       </c>
       <c r="M36" t="n">
-        <v>86.98</v>
+        <v>391.42</v>
       </c>
       <c r="N36" t="n">
-        <v>81.38</v>
+        <v>374.04</v>
       </c>
       <c r="O36" t="n">
-        <v>94.64</v>
+        <v>415.17</v>
       </c>
       <c r="P36" t="n">
         <v>1.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>67.97</v>
+        <v>70.31</v>
       </c>
       <c r="R36" t="n">
-        <v>9.25</v>
+        <v>2.89</v>
       </c>
       <c r="S36" t="n">
-        <v>-3.98</v>
+        <v>-4.63</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4481,76 +4481,76 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; MACD positivo; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; Fuerte vs QQQ</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI algo alto; Momentum 5D extendido; Algo extendida sobre MA20</t>
+          <t>RSI algo alto; MACD sin confirmar</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Ciberseguridad</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>390.13</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E37" t="n">
-        <v>0.72</v>
+        <v>9.18</v>
       </c>
       <c r="F37" t="n">
-        <v>17.41</v>
+        <v>11.18</v>
       </c>
       <c r="G37" t="n">
-        <v>25.33</v>
+        <v>24.18</v>
       </c>
       <c r="H37" t="n">
-        <v>8.17</v>
+        <v>1.99</v>
       </c>
       <c r="I37" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
-        <v>11.59</v>
+        <v>3.74</v>
       </c>
       <c r="K37" t="n">
-        <v>2.97</v>
+        <v>4.33</v>
       </c>
       <c r="L37" t="n">
-        <v>386.07</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>391.87</v>
+        <v>86.88</v>
       </c>
       <c r="N37" t="n">
-        <v>374.49</v>
+        <v>81.28</v>
       </c>
       <c r="O37" t="n">
-        <v>415.62</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="P37" t="n">
         <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>70.64</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="R37" t="n">
-        <v>3</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="S37" t="n">
-        <v>-4.52</v>
+        <v>-4.09</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; Fuerte vs QQQ</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>RSI algo alto; MACD sin confirmar</t>
+          <t>Tendencia larga débil; RSI algo alto; Momentum 5D extendido; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
@@ -4615,22 +4615,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>391.76</v>
+        <v>391.45</v>
       </c>
       <c r="D38" t="n">
         <v>84</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.17</v>
+        <v>-1.25</v>
       </c>
       <c r="F38" t="n">
-        <v>13.22</v>
+        <v>13.13</v>
       </c>
       <c r="G38" t="n">
-        <v>39.83</v>
+        <v>39.72</v>
       </c>
       <c r="H38" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="I38" t="n">
         <v>0.42</v>
@@ -4642,28 +4642,28 @@
         <v>2.27</v>
       </c>
       <c r="L38" t="n">
-        <v>388.65</v>
+        <v>388.34</v>
       </c>
       <c r="M38" t="n">
-        <v>393.09</v>
+        <v>392.78</v>
       </c>
       <c r="N38" t="n">
-        <v>379.75</v>
+        <v>379.44</v>
       </c>
       <c r="O38" t="n">
-        <v>411.33</v>
+        <v>411.02</v>
       </c>
       <c r="P38" t="n">
         <v>1.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>67.89</v>
+        <v>67.72</v>
       </c>
       <c r="R38" t="n">
-        <v>4.42</v>
+        <v>4.34</v>
       </c>
       <c r="S38" t="n">
-        <v>-3.07</v>
+        <v>-3.14</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4728,22 +4728,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>236.65</v>
+        <v>236.37</v>
       </c>
       <c r="D39" t="n">
         <v>82</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.96</v>
+        <v>-1.08</v>
       </c>
       <c r="F39" t="n">
-        <v>11.44</v>
+        <v>11.31</v>
       </c>
       <c r="G39" t="n">
-        <v>99.25</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="I39" t="n">
         <v>0.49</v>
@@ -4755,28 +4755,28 @@
         <v>6.08</v>
       </c>
       <c r="L39" t="n">
-        <v>231.62</v>
+        <v>231.34</v>
       </c>
       <c r="M39" t="n">
-        <v>238.81</v>
+        <v>238.53</v>
       </c>
       <c r="N39" t="n">
-        <v>217.24</v>
+        <v>216.96</v>
       </c>
       <c r="O39" t="n">
-        <v>268.28</v>
+        <v>268</v>
       </c>
       <c r="P39" t="n">
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>63.64</v>
+        <v>63.49</v>
       </c>
       <c r="R39" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="S39" t="n">
-        <v>-10.36</v>
+        <v>-10.46</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -4841,55 +4841,55 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10.1</v>
+        <v>10.05</v>
       </c>
       <c r="D40" t="n">
         <v>75</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.67</v>
+        <v>-4.19</v>
       </c>
       <c r="F40" t="n">
-        <v>12.65</v>
+        <v>12.04</v>
       </c>
       <c r="G40" t="n">
-        <v>5.92</v>
+        <v>5.35</v>
       </c>
       <c r="H40" t="n">
-        <v>3.41</v>
+        <v>2.85</v>
       </c>
       <c r="I40" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="J40" t="n">
         <v>0.77</v>
       </c>
       <c r="K40" t="n">
-        <v>7.65</v>
+        <v>7.69</v>
       </c>
       <c r="L40" t="n">
-        <v>9.83</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>10.22</v>
+        <v>10.17</v>
       </c>
       <c r="N40" t="n">
-        <v>9.06</v>
+        <v>9.01</v>
       </c>
       <c r="O40" t="n">
-        <v>11.81</v>
+        <v>11.75</v>
       </c>
       <c r="P40" t="n">
         <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>61.27</v>
+        <v>60.73</v>
       </c>
       <c r="R40" t="n">
-        <v>4.22</v>
+        <v>3.68</v>
       </c>
       <c r="S40" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.19</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4950,25 +4950,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>84.06</v>
+        <v>84.14</v>
       </c>
       <c r="D41" t="n">
         <v>75</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.63</v>
+        <v>-0.53</v>
       </c>
       <c r="F41" t="n">
-        <v>5.58</v>
+        <v>5.68</v>
       </c>
       <c r="G41" t="n">
-        <v>17.63</v>
+        <v>17.75</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.66</v>
+        <v>-3.51</v>
       </c>
       <c r="I41" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="J41" t="n">
         <v>2.76</v>
@@ -4977,28 +4977,28 @@
         <v>3.29</v>
       </c>
       <c r="L41" t="n">
-        <v>83.09</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>84.47</v>
+        <v>84.56</v>
       </c>
       <c r="N41" t="n">
-        <v>80.33</v>
+        <v>80.41</v>
       </c>
       <c r="O41" t="n">
-        <v>90.14</v>
+        <v>90.23</v>
       </c>
       <c r="P41" t="n">
         <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>65.41</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="R41" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="S41" t="n">
-        <v>-4.95</v>
+        <v>-4.86</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5059,55 +5059,55 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>147.38</v>
+        <v>147.42</v>
       </c>
       <c r="D42" t="n">
         <v>75</v>
       </c>
       <c r="E42" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="G42" t="n">
-        <v>-6.66</v>
+        <v>-6.63</v>
       </c>
       <c r="H42" t="n">
-        <v>-8.24</v>
+        <v>-8.16</v>
       </c>
       <c r="I42" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="J42" t="n">
         <v>2.01</v>
       </c>
       <c r="K42" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="L42" t="n">
-        <v>146.68</v>
+        <v>146.72</v>
       </c>
       <c r="M42" t="n">
-        <v>147.68</v>
+        <v>147.72</v>
       </c>
       <c r="N42" t="n">
-        <v>144.66</v>
+        <v>144.7</v>
       </c>
       <c r="O42" t="n">
-        <v>151.81</v>
+        <v>151.85</v>
       </c>
       <c r="P42" t="n">
         <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>65.13</v>
+        <v>65.23</v>
       </c>
       <c r="R42" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.46</v>
+        <v>-0.44</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5168,55 +5168,55 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>412.05</v>
+        <v>411.31</v>
       </c>
       <c r="D43" t="n">
         <v>63</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.73</v>
+        <v>-1.91</v>
       </c>
       <c r="F43" t="n">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="G43" t="n">
-        <v>25</v>
+        <v>24.77</v>
       </c>
       <c r="H43" t="n">
-        <v>-6.78</v>
+        <v>-6.92</v>
       </c>
       <c r="I43" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="J43" t="n">
         <v>16.73</v>
       </c>
       <c r="K43" t="n">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
       <c r="L43" t="n">
-        <v>406.19</v>
+        <v>405.45</v>
       </c>
       <c r="M43" t="n">
-        <v>414.56</v>
+        <v>413.82</v>
       </c>
       <c r="N43" t="n">
-        <v>389.47</v>
+        <v>388.73</v>
       </c>
       <c r="O43" t="n">
-        <v>448.85</v>
+        <v>448.11</v>
       </c>
       <c r="P43" t="n">
         <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>52.58</v>
+        <v>52.28</v>
       </c>
       <c r="R43" t="n">
-        <v>-1.91</v>
+        <v>-2.08</v>
       </c>
       <c r="S43" t="n">
-        <v>-6.85</v>
+        <v>-7.02</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5277,25 +5277,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>408</v>
+        <v>408.22</v>
       </c>
       <c r="D44" t="n">
         <v>61</v>
       </c>
       <c r="E44" t="n">
-        <v>-5.38</v>
+        <v>-5.33</v>
       </c>
       <c r="F44" t="n">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="G44" t="n">
-        <v>9.220000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>-5.77</v>
+        <v>-5.67</v>
       </c>
       <c r="I44" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="J44" t="n">
         <v>20.08</v>
@@ -5304,28 +5304,28 @@
         <v>4.92</v>
       </c>
       <c r="L44" t="n">
-        <v>400.97</v>
+        <v>401.19</v>
       </c>
       <c r="M44" t="n">
-        <v>411.01</v>
+        <v>411.23</v>
       </c>
       <c r="N44" t="n">
-        <v>380.89</v>
+        <v>381.11</v>
       </c>
       <c r="O44" t="n">
-        <v>452.17</v>
+        <v>452.39</v>
       </c>
       <c r="P44" t="n">
         <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>57.84</v>
+        <v>57.91</v>
       </c>
       <c r="R44" t="n">
-        <v>-1.25</v>
+        <v>-1.2</v>
       </c>
       <c r="S44" t="n">
-        <v>-9.02</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5386,22 +5386,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1461.64</v>
+        <v>1462.71</v>
       </c>
       <c r="D45" t="n">
         <v>61</v>
       </c>
       <c r="E45" t="n">
-        <v>-3.9</v>
+        <v>-3.83</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.42</v>
+        <v>-1.35</v>
       </c>
       <c r="H45" t="n">
-        <v>-8.84</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="I45" t="n">
         <v>0.65</v>
@@ -5413,28 +5413,28 @@
         <v>4.59</v>
       </c>
       <c r="L45" t="n">
-        <v>1438.14</v>
+        <v>1439.21</v>
       </c>
       <c r="M45" t="n">
-        <v>1471.71</v>
+        <v>1472.78</v>
       </c>
       <c r="N45" t="n">
-        <v>1371.01</v>
+        <v>1372.08</v>
       </c>
       <c r="O45" t="n">
-        <v>1609.33</v>
+        <v>1610.4</v>
       </c>
       <c r="P45" t="n">
         <v>1.63</v>
       </c>
       <c r="Q45" t="n">
-        <v>55.47</v>
+        <v>55.57</v>
       </c>
       <c r="R45" t="n">
-        <v>-1.1</v>
+        <v>-1.03</v>
       </c>
       <c r="S45" t="n">
-        <v>-8.85</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5495,55 +5495,55 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>404.42</v>
+        <v>404.94</v>
       </c>
       <c r="D46" t="n">
         <v>71</v>
       </c>
       <c r="E46" t="n">
-        <v>-6.7</v>
+        <v>-6.58</v>
       </c>
       <c r="F46" t="n">
-        <v>4.66</v>
+        <v>4.79</v>
       </c>
       <c r="G46" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="H46" t="n">
-        <v>-4.58</v>
+        <v>-4.4</v>
       </c>
       <c r="I46" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="J46" t="n">
         <v>18.51</v>
       </c>
       <c r="K46" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="L46" t="n">
-        <v>397.94</v>
+        <v>398.46</v>
       </c>
       <c r="M46" t="n">
-        <v>407.2</v>
+        <v>407.72</v>
       </c>
       <c r="N46" t="n">
-        <v>379.42</v>
+        <v>379.94</v>
       </c>
       <c r="O46" t="n">
-        <v>445.15</v>
+        <v>445.67</v>
       </c>
       <c r="P46" t="n">
         <v>1.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>61.08</v>
+        <v>61.3</v>
       </c>
       <c r="R46" t="n">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="S46" t="n">
-        <v>-10.8</v>
+        <v>-10.69</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -5604,25 +5604,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>863.67</v>
+        <v>864.15</v>
       </c>
       <c r="D47" t="n">
         <v>68</v>
       </c>
       <c r="E47" t="n">
-        <v>-5.31</v>
+        <v>-5.26</v>
       </c>
       <c r="F47" t="n">
-        <v>7.9</v>
+        <v>7.96</v>
       </c>
       <c r="G47" t="n">
-        <v>14.39</v>
+        <v>14.45</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.34</v>
+        <v>-1.23</v>
       </c>
       <c r="I47" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="J47" t="n">
         <v>34.12</v>
@@ -5631,28 +5631,28 @@
         <v>3.95</v>
       </c>
       <c r="L47" t="n">
-        <v>851.73</v>
+        <v>852.21</v>
       </c>
       <c r="M47" t="n">
-        <v>868.79</v>
+        <v>869.27</v>
       </c>
       <c r="N47" t="n">
-        <v>817.6</v>
+        <v>818.08</v>
       </c>
       <c r="O47" t="n">
-        <v>938.74</v>
+        <v>939.22</v>
       </c>
       <c r="P47" t="n">
         <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>58.68</v>
+        <v>58.76</v>
       </c>
       <c r="R47" t="n">
-        <v>-1.23</v>
+        <v>-1.18</v>
       </c>
       <c r="S47" t="n">
-        <v>-7.27</v>
+        <v>-7.22</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5713,22 +5713,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>182.64</v>
+        <v>182.91</v>
       </c>
       <c r="D48" t="n">
         <v>63</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.24</v>
+        <v>-2.1</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="G48" t="n">
-        <v>29.7</v>
+        <v>29.89</v>
       </c>
       <c r="H48" t="n">
-        <v>-8.43</v>
+        <v>-8.23</v>
       </c>
       <c r="I48" t="n">
         <v>0.43</v>
@@ -5740,28 +5740,28 @@
         <v>5.11</v>
       </c>
       <c r="L48" t="n">
-        <v>179.37</v>
+        <v>179.64</v>
       </c>
       <c r="M48" t="n">
-        <v>184.04</v>
+        <v>184.31</v>
       </c>
       <c r="N48" t="n">
-        <v>170.03</v>
+        <v>170.3</v>
       </c>
       <c r="O48" t="n">
-        <v>203.18</v>
+        <v>203.45</v>
       </c>
       <c r="P48" t="n">
         <v>1.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>63.86</v>
+        <v>64.11</v>
       </c>
       <c r="R48" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="S48" t="n">
-        <v>-9</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -5822,25 +5822,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>177.33</v>
+        <v>177.16</v>
       </c>
       <c r="D49" t="n">
         <v>60</v>
       </c>
       <c r="E49" t="n">
-        <v>4.45</v>
+        <v>4.36</v>
       </c>
       <c r="F49" t="n">
-        <v>-8.789999999999999</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>-11.11</v>
+        <v>-11.19</v>
       </c>
       <c r="H49" t="n">
-        <v>-18.03</v>
+        <v>-18.07</v>
       </c>
       <c r="I49" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="J49" t="n">
         <v>7.57</v>
@@ -5849,28 +5849,28 @@
         <v>4.27</v>
       </c>
       <c r="L49" t="n">
-        <v>174.68</v>
+        <v>174.52</v>
       </c>
       <c r="M49" t="n">
-        <v>178.47</v>
+        <v>178.3</v>
       </c>
       <c r="N49" t="n">
-        <v>167.11</v>
+        <v>166.95</v>
       </c>
       <c r="O49" t="n">
-        <v>193.98</v>
+        <v>193.81</v>
       </c>
       <c r="P49" t="n">
         <v>1.63</v>
       </c>
       <c r="Q49" t="n">
-        <v>47.25</v>
+        <v>47.1</v>
       </c>
       <c r="R49" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="S49" t="n">
-        <v>-8.949999999999999</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -5931,55 +5931,55 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>111.65</v>
+        <v>111.56</v>
       </c>
       <c r="D50" t="n">
         <v>73</v>
       </c>
       <c r="E50" t="n">
-        <v>-7.42</v>
+        <v>-7.5</v>
       </c>
       <c r="F50" t="n">
-        <v>68.51000000000001</v>
+        <v>68.37</v>
       </c>
       <c r="G50" t="n">
-        <v>155.91</v>
+        <v>155.7</v>
       </c>
       <c r="H50" t="n">
-        <v>59.27</v>
+        <v>59.18</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>9.710000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>8.699999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>108.26</v>
+        <v>108.16</v>
       </c>
       <c r="M50" t="n">
-        <v>113.11</v>
+        <v>113.02</v>
       </c>
       <c r="N50" t="n">
-        <v>98.54000000000001</v>
+        <v>98.45</v>
       </c>
       <c r="O50" t="n">
-        <v>133.02</v>
+        <v>132.93</v>
       </c>
       <c r="P50" t="n">
         <v>1.63</v>
       </c>
       <c r="Q50" t="n">
-        <v>61.35</v>
+        <v>61.3</v>
       </c>
       <c r="R50" t="n">
-        <v>9.5</v>
+        <v>9.42</v>
       </c>
       <c r="S50" t="n">
-        <v>-15.89</v>
+        <v>-15.96</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6044,22 +6044,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>417.5</v>
+        <v>417.01</v>
       </c>
       <c r="D51" t="n">
         <v>66</v>
       </c>
       <c r="E51" t="n">
-        <v>-6.87</v>
+        <v>-6.98</v>
       </c>
       <c r="F51" t="n">
-        <v>46.75</v>
+        <v>46.58</v>
       </c>
       <c r="G51" t="n">
-        <v>112.36</v>
+        <v>112.11</v>
       </c>
       <c r="H51" t="n">
-        <v>37.51</v>
+        <v>37.39</v>
       </c>
       <c r="I51" t="n">
         <v>0.65</v>
@@ -6068,31 +6068,31 @@
         <v>29.02</v>
       </c>
       <c r="K51" t="n">
-        <v>6.95</v>
+        <v>6.96</v>
       </c>
       <c r="L51" t="n">
-        <v>407.34</v>
+        <v>406.85</v>
       </c>
       <c r="M51" t="n">
-        <v>421.85</v>
+        <v>421.36</v>
       </c>
       <c r="N51" t="n">
-        <v>378.33</v>
+        <v>377.83</v>
       </c>
       <c r="O51" t="n">
-        <v>481.33</v>
+        <v>480.84</v>
       </c>
       <c r="P51" t="n">
         <v>1.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>67.09</v>
+        <v>66.95</v>
       </c>
       <c r="R51" t="n">
-        <v>8.25</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="S51" t="n">
-        <v>-11.02</v>
+        <v>-11.13</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6157,25 +6157,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>676.29</v>
+        <v>676.25</v>
       </c>
       <c r="D52" t="n">
         <v>70</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.35</v>
+        <v>-0.36</v>
       </c>
       <c r="F52" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
       <c r="G52" t="n">
         <v>8.09</v>
       </c>
       <c r="H52" t="n">
-        <v>-4.75</v>
+        <v>-4.71</v>
       </c>
       <c r="I52" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="J52" t="n">
         <v>6.95</v>
@@ -6184,25 +6184,25 @@
         <v>1.03</v>
       </c>
       <c r="L52" t="n">
-        <v>673.86</v>
+        <v>673.8200000000001</v>
       </c>
       <c r="M52" t="n">
-        <v>677.33</v>
+        <v>677.29</v>
       </c>
       <c r="N52" t="n">
-        <v>666.9</v>
+        <v>666.86</v>
       </c>
       <c r="O52" t="n">
-        <v>691.58</v>
+        <v>691.54</v>
       </c>
       <c r="P52" t="n">
         <v>1.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>69.8</v>
+        <v>69.75</v>
       </c>
       <c r="R52" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S52" t="n">
         <v>-1.86</v>
@@ -6266,22 +6266,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>735.5700000000001</v>
+        <v>735.55</v>
       </c>
       <c r="D53" t="n">
         <v>70</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.35</v>
+        <v>-0.36</v>
       </c>
       <c r="F53" t="n">
         <v>4.47</v>
       </c>
       <c r="G53" t="n">
-        <v>8.09</v>
+        <v>8.08</v>
       </c>
       <c r="H53" t="n">
-        <v>-4.77</v>
+        <v>-4.72</v>
       </c>
       <c r="I53" t="n">
         <v>0.6899999999999999</v>
@@ -6293,28 +6293,28 @@
         <v>1.03</v>
       </c>
       <c r="L53" t="n">
-        <v>732.91</v>
+        <v>732.89</v>
       </c>
       <c r="M53" t="n">
-        <v>736.71</v>
+        <v>736.6900000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>725.33</v>
+        <v>725.3099999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>752.26</v>
+        <v>752.24</v>
       </c>
       <c r="P53" t="n">
         <v>1.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>69.59999999999999</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="R53" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S53" t="n">
-        <v>-1.86</v>
+        <v>-1.87</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6375,22 +6375,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>478.1</v>
+        <v>476.77</v>
       </c>
       <c r="D54" t="n">
         <v>69</v>
       </c>
       <c r="E54" t="n">
-        <v>-2.57</v>
+        <v>-2.84</v>
       </c>
       <c r="F54" t="n">
-        <v>1.04</v>
+        <v>0.76</v>
       </c>
       <c r="G54" t="n">
-        <v>25.61</v>
+        <v>25.26</v>
       </c>
       <c r="H54" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.43</v>
       </c>
       <c r="I54" t="n">
         <v>0.47</v>
@@ -6399,31 +6399,31 @@
         <v>31.35</v>
       </c>
       <c r="K54" t="n">
-        <v>6.56</v>
+        <v>6.57</v>
       </c>
       <c r="L54" t="n">
-        <v>467.13</v>
+        <v>465.8</v>
       </c>
       <c r="M54" t="n">
-        <v>482.8</v>
+        <v>481.48</v>
       </c>
       <c r="N54" t="n">
-        <v>435.78</v>
+        <v>434.46</v>
       </c>
       <c r="O54" t="n">
-        <v>547.0599999999999</v>
+        <v>545.74</v>
       </c>
       <c r="P54" t="n">
         <v>1.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>57.41</v>
+        <v>57.09</v>
       </c>
       <c r="R54" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="S54" t="n">
-        <v>-7.24</v>
+        <v>-7.49</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -6484,22 +6484,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>44.65</v>
+        <v>44.61</v>
       </c>
       <c r="D55" t="n">
         <v>62</v>
       </c>
       <c r="E55" t="n">
-        <v>-5.01</v>
+        <v>-5.09</v>
       </c>
       <c r="F55" t="n">
-        <v>13.25</v>
+        <v>13.17</v>
       </c>
       <c r="G55" t="n">
-        <v>16.79</v>
+        <v>16.69</v>
       </c>
       <c r="H55" t="n">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="I55" t="n">
         <v>0.35</v>
@@ -6511,28 +6511,28 @@
         <v>3.05</v>
       </c>
       <c r="L55" t="n">
-        <v>44.17</v>
+        <v>44.13</v>
       </c>
       <c r="M55" t="n">
-        <v>44.85</v>
+        <v>44.81</v>
       </c>
       <c r="N55" t="n">
-        <v>42.81</v>
+        <v>42.77</v>
       </c>
       <c r="O55" t="n">
-        <v>47.64</v>
+        <v>47.61</v>
       </c>
       <c r="P55" t="n">
         <v>1.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>71.87</v>
+        <v>71.77</v>
       </c>
       <c r="R55" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="S55" t="n">
-        <v>-6.58</v>
+        <v>-6.65</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6593,22 +6593,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>303.67</v>
+        <v>303.57</v>
       </c>
       <c r="D56" t="n">
         <v>81</v>
       </c>
       <c r="E56" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="F56" t="n">
-        <v>30.91</v>
+        <v>30.87</v>
       </c>
       <c r="G56" t="n">
-        <v>38.82</v>
+        <v>38.78</v>
       </c>
       <c r="H56" t="n">
-        <v>21.67</v>
+        <v>21.68</v>
       </c>
       <c r="I56" t="n">
         <v>0.47</v>
@@ -6617,31 +6617,31 @@
         <v>10.22</v>
       </c>
       <c r="K56" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="L56" t="n">
-        <v>300.09</v>
+        <v>299.99</v>
       </c>
       <c r="M56" t="n">
-        <v>305.2</v>
+        <v>305.1</v>
       </c>
       <c r="N56" t="n">
-        <v>289.88</v>
+        <v>289.78</v>
       </c>
       <c r="O56" t="n">
-        <v>326.15</v>
+        <v>326.05</v>
       </c>
       <c r="P56" t="n">
         <v>1.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>77.59</v>
+        <v>77.55</v>
       </c>
       <c r="R56" t="n">
-        <v>6.78</v>
+        <v>6.74</v>
       </c>
       <c r="S56" t="n">
-        <v>-2.13</v>
+        <v>-2.17</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -6706,22 +6706,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>710.99</v>
+        <v>710.54</v>
       </c>
       <c r="D57" t="n">
         <v>80</v>
       </c>
       <c r="E57" t="n">
-        <v>-7.25</v>
+        <v>-7.31</v>
       </c>
       <c r="F57" t="n">
-        <v>58.21</v>
+        <v>58.12</v>
       </c>
       <c r="G57" t="n">
-        <v>68.95999999999999</v>
+        <v>68.86</v>
       </c>
       <c r="H57" t="n">
-        <v>48.97</v>
+        <v>48.93</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
@@ -6733,28 +6733,28 @@
         <v>8.57</v>
       </c>
       <c r="L57" t="n">
-        <v>689.67</v>
+        <v>689.22</v>
       </c>
       <c r="M57" t="n">
-        <v>720.12</v>
+        <v>719.6799999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>628.76</v>
+        <v>628.3200000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>844.97</v>
+        <v>844.53</v>
       </c>
       <c r="P57" t="n">
         <v>1.63</v>
       </c>
       <c r="Q57" t="n">
-        <v>67.94</v>
+        <v>67.91</v>
       </c>
       <c r="R57" t="n">
-        <v>12.78</v>
+        <v>12.72</v>
       </c>
       <c r="S57" t="n">
-        <v>-13.15</v>
+        <v>-13.21</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1016.46</v>
+        <v>1016.45</v>
       </c>
       <c r="D58" t="n">
         <v>93</v>
@@ -6824,16 +6824,16 @@
         <v>2.86</v>
       </c>
       <c r="F58" t="n">
-        <v>12.76</v>
+        <v>12.75</v>
       </c>
       <c r="G58" t="n">
         <v>-3.81</v>
       </c>
       <c r="H58" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="I58" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="J58" t="n">
         <v>34.22</v>
@@ -6842,16 +6842,16 @@
         <v>3.37</v>
       </c>
       <c r="L58" t="n">
-        <v>1004.48</v>
+        <v>1004.47</v>
       </c>
       <c r="M58" t="n">
-        <v>1021.59</v>
+        <v>1021.58</v>
       </c>
       <c r="N58" t="n">
-        <v>970.26</v>
+        <v>970.25</v>
       </c>
       <c r="O58" t="n">
-        <v>1091.74</v>
+        <v>1091.73</v>
       </c>
       <c r="P58" t="n">
         <v>1.63</v>
@@ -6919,64 +6919,64 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Consumo</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>297.82</v>
+        <v>1089.2</v>
       </c>
       <c r="D59" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E59" t="n">
-        <v>1.02</v>
+        <v>6.59</v>
       </c>
       <c r="F59" t="n">
-        <v>11.99</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>11.99</v>
+        <v>10.62</v>
       </c>
       <c r="H59" t="n">
-        <v>2.75</v>
+        <v>-0.74</v>
       </c>
       <c r="I59" t="n">
-        <v>0.46</v>
+        <v>0.77</v>
       </c>
       <c r="J59" t="n">
-        <v>6.68</v>
+        <v>21.81</v>
       </c>
       <c r="K59" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="L59" t="n">
-        <v>295.48</v>
+        <v>1081.57</v>
       </c>
       <c r="M59" t="n">
-        <v>298.82</v>
+        <v>1092.47</v>
       </c>
       <c r="N59" t="n">
-        <v>288.8</v>
+        <v>1059.76</v>
       </c>
       <c r="O59" t="n">
-        <v>312.53</v>
+        <v>1137.18</v>
       </c>
       <c r="P59" t="n">
         <v>1.63</v>
       </c>
       <c r="Q59" t="n">
-        <v>83.59</v>
+        <v>78.53</v>
       </c>
       <c r="R59" t="n">
-        <v>4.79</v>
+        <v>6.83</v>
       </c>
       <c r="S59" t="n">
-        <v>-1.77</v>
+        <v>-0.67</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -7003,11 +7003,7 @@
           <t>ALTO</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -7025,71 +7021,71 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo</t>
+          <t>RSI sobrecomprado; Momentum 5D extendido</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1089.73</v>
+        <v>297.7</v>
       </c>
       <c r="D60" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E60" t="n">
-        <v>6.64</v>
+        <v>0.99</v>
       </c>
       <c r="F60" t="n">
-        <v>8.5</v>
+        <v>11.95</v>
       </c>
       <c r="G60" t="n">
-        <v>10.68</v>
+        <v>11.95</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.74</v>
+        <v>2.76</v>
       </c>
       <c r="I60" t="n">
-        <v>0.76</v>
+        <v>0.46</v>
       </c>
       <c r="J60" t="n">
-        <v>21.81</v>
+        <v>6.68</v>
       </c>
       <c r="K60" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L60" t="n">
-        <v>1082.1</v>
+        <v>295.37</v>
       </c>
       <c r="M60" t="n">
-        <v>1093.01</v>
+        <v>298.71</v>
       </c>
       <c r="N60" t="n">
-        <v>1060.29</v>
+        <v>288.68</v>
       </c>
       <c r="O60" t="n">
-        <v>1137.72</v>
+        <v>312.41</v>
       </c>
       <c r="P60" t="n">
         <v>1.63</v>
       </c>
       <c r="Q60" t="n">
-        <v>78.59999999999999</v>
+        <v>83.36</v>
       </c>
       <c r="R60" t="n">
-        <v>6.88</v>
+        <v>4.75</v>
       </c>
       <c r="S60" t="n">
-        <v>-0.62</v>
+        <v>-1.81</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7103,12 +7099,12 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -7134,7 +7130,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Momentum 5D extendido</t>
+          <t>RSI sobrecomprado; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -7150,25 +7146,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>173.91</v>
+        <v>173.92</v>
       </c>
       <c r="D61" t="n">
         <v>71</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.74</v>
+        <v>-0.73</v>
       </c>
       <c r="F61" t="n">
-        <v>12.42</v>
+        <v>12.43</v>
       </c>
       <c r="G61" t="n">
-        <v>25.7</v>
+        <v>25.71</v>
       </c>
       <c r="H61" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="I61" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>4.08</v>
@@ -7177,22 +7173,22 @@
         <v>2.35</v>
       </c>
       <c r="L61" t="n">
-        <v>172.48</v>
+        <v>172.49</v>
       </c>
       <c r="M61" t="n">
-        <v>174.52</v>
+        <v>174.53</v>
       </c>
       <c r="N61" t="n">
-        <v>168.4</v>
+        <v>168.41</v>
       </c>
       <c r="O61" t="n">
-        <v>182.89</v>
+        <v>182.9</v>
       </c>
       <c r="P61" t="n">
         <v>1.63</v>
       </c>
       <c r="Q61" t="n">
-        <v>73.11</v>
+        <v>73.13</v>
       </c>
       <c r="R61" t="n">
         <v>3.83</v>
@@ -7217,7 +7213,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -7259,55 +7255,55 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>126.8</v>
+        <v>126.23</v>
       </c>
       <c r="D62" t="n">
         <v>70</v>
       </c>
       <c r="E62" t="n">
-        <v>7.86</v>
+        <v>7.37</v>
       </c>
       <c r="F62" t="n">
-        <v>46.35</v>
+        <v>45.69</v>
       </c>
       <c r="G62" t="n">
-        <v>80.59</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>37.11</v>
+        <v>36.5</v>
       </c>
       <c r="I62" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="J62" t="n">
         <v>11.09</v>
       </c>
       <c r="K62" t="n">
-        <v>8.75</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>122.91</v>
+        <v>122.35</v>
       </c>
       <c r="M62" t="n">
-        <v>128.46</v>
+        <v>127.89</v>
       </c>
       <c r="N62" t="n">
-        <v>111.82</v>
+        <v>111.25</v>
       </c>
       <c r="O62" t="n">
-        <v>151.2</v>
+        <v>150.63</v>
       </c>
       <c r="P62" t="n">
         <v>1.63</v>
       </c>
       <c r="Q62" t="n">
-        <v>75.73999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="R62" t="n">
-        <v>29.67</v>
+        <v>29.13</v>
       </c>
       <c r="S62" t="n">
-        <v>-8.369999999999999</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7368,25 +7364,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>334.93</v>
+        <v>334.91</v>
       </c>
       <c r="D63" t="n">
         <v>70</v>
       </c>
       <c r="E63" t="n">
-        <v>8.49</v>
+        <v>8.48</v>
       </c>
       <c r="F63" t="n">
         <v>28.11</v>
       </c>
       <c r="G63" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
       <c r="H63" t="n">
-        <v>18.87</v>
+        <v>18.92</v>
       </c>
       <c r="I63" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="J63" t="n">
         <v>18.41</v>
@@ -7395,16 +7391,16 @@
         <v>5.5</v>
       </c>
       <c r="L63" t="n">
-        <v>328.49</v>
+        <v>328.47</v>
       </c>
       <c r="M63" t="n">
-        <v>337.69</v>
+        <v>337.67</v>
       </c>
       <c r="N63" t="n">
-        <v>310.08</v>
+        <v>310.06</v>
       </c>
       <c r="O63" t="n">
-        <v>375.43</v>
+        <v>375.41</v>
       </c>
       <c r="P63" t="n">
         <v>1.63</v>
@@ -7413,7 +7409,7 @@
         <v>83.18000000000001</v>
       </c>
       <c r="R63" t="n">
-        <v>18.51</v>
+        <v>18.5</v>
       </c>
       <c r="S63" t="n">
         <v>-4.09</v>
@@ -7435,7 +7431,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -7477,55 +7473,55 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>126.38</v>
+        <v>126.48</v>
       </c>
       <c r="D64" t="n">
         <v>67</v>
       </c>
       <c r="E64" t="n">
-        <v>10.98</v>
+        <v>11.07</v>
       </c>
       <c r="F64" t="n">
-        <v>48.22</v>
+        <v>48.35</v>
       </c>
       <c r="G64" t="n">
-        <v>67.16</v>
+        <v>67.3</v>
       </c>
       <c r="H64" t="n">
-        <v>38.98</v>
+        <v>39.16</v>
       </c>
       <c r="I64" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="J64" t="n">
         <v>5.47</v>
       </c>
       <c r="K64" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="L64" t="n">
-        <v>124.46</v>
+        <v>124.57</v>
       </c>
       <c r="M64" t="n">
-        <v>127.2</v>
+        <v>127.3</v>
       </c>
       <c r="N64" t="n">
-        <v>118.99</v>
+        <v>119.1</v>
       </c>
       <c r="O64" t="n">
-        <v>138.4</v>
+        <v>138.51</v>
       </c>
       <c r="P64" t="n">
         <v>1.63</v>
       </c>
       <c r="Q64" t="n">
-        <v>92.59999999999999</v>
+        <v>92.81</v>
       </c>
       <c r="R64" t="n">
-        <v>25.25</v>
+        <v>25.35</v>
       </c>
       <c r="S64" t="n">
-        <v>-1.38</v>
+        <v>-1.3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7544,7 +7540,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -7586,22 +7582,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>703.5599999999999</v>
+        <v>703.48</v>
       </c>
       <c r="D65" t="n">
         <v>63</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="F65" t="n">
-        <v>9.19</v>
+        <v>9.18</v>
       </c>
       <c r="G65" t="n">
-        <v>17.13</v>
+        <v>17.12</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="I65" t="n">
         <v>0.89</v>
@@ -7613,28 +7609,28 @@
         <v>1.6</v>
       </c>
       <c r="L65" t="n">
-        <v>699.61</v>
+        <v>699.53</v>
       </c>
       <c r="M65" t="n">
-        <v>705.25</v>
+        <v>705.1799999999999</v>
       </c>
       <c r="N65" t="n">
-        <v>688.3200000000001</v>
+        <v>688.25</v>
       </c>
       <c r="O65" t="n">
-        <v>728.39</v>
+        <v>728.3200000000001</v>
       </c>
       <c r="P65" t="n">
         <v>1.63</v>
       </c>
       <c r="Q65" t="n">
-        <v>73.13</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="R65" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="S65" t="n">
-        <v>-2.56</v>
+        <v>-2.57</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7695,22 +7691,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>103.21</v>
+        <v>103.14</v>
       </c>
       <c r="D66" t="n">
         <v>62</v>
       </c>
       <c r="E66" t="n">
-        <v>15.97</v>
+        <v>15.89</v>
       </c>
       <c r="F66" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="H66" t="n">
-        <v>-6.17</v>
+        <v>-6.19</v>
       </c>
       <c r="I66" t="n">
         <v>1.49</v>
@@ -7722,28 +7718,28 @@
         <v>5.17</v>
       </c>
       <c r="L66" t="n">
-        <v>101.34</v>
+        <v>101.27</v>
       </c>
       <c r="M66" t="n">
-        <v>104.01</v>
+        <v>103.94</v>
       </c>
       <c r="N66" t="n">
-        <v>96.01000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="O66" t="n">
-        <v>114.94</v>
+        <v>114.87</v>
       </c>
       <c r="P66" t="n">
         <v>1.63</v>
       </c>
       <c r="Q66" t="n">
-        <v>70.16</v>
+        <v>70.02</v>
       </c>
       <c r="R66" t="n">
-        <v>11.89</v>
+        <v>11.82</v>
       </c>
       <c r="S66" t="n">
-        <v>-6.86</v>
+        <v>-6.92</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7762,7 +7758,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -7804,22 +7800,22 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>111.88</v>
+        <v>111.86</v>
       </c>
       <c r="D67" t="n">
         <v>60</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.37</v>
+        <v>-0.39</v>
       </c>
       <c r="F67" t="n">
-        <v>10.75</v>
+        <v>10.73</v>
       </c>
       <c r="G67" t="n">
-        <v>23.27</v>
+        <v>23.25</v>
       </c>
       <c r="H67" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="I67" t="n">
         <v>0.6</v>
@@ -7831,28 +7827,28 @@
         <v>2.18</v>
       </c>
       <c r="L67" t="n">
-        <v>111.03</v>
+        <v>111.01</v>
       </c>
       <c r="M67" t="n">
-        <v>112.25</v>
+        <v>112.23</v>
       </c>
       <c r="N67" t="n">
-        <v>108.59</v>
+        <v>108.57</v>
       </c>
       <c r="O67" t="n">
-        <v>117.24</v>
+        <v>117.22</v>
       </c>
       <c r="P67" t="n">
         <v>1.63</v>
       </c>
       <c r="Q67" t="n">
-        <v>73.87</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="R67" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="S67" t="n">
-        <v>-3.23</v>
+        <v>-3.25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7871,7 +7867,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -7913,25 +7909,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>246.85</v>
+        <v>246.32</v>
       </c>
       <c r="D68" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E68" t="n">
-        <v>1.04</v>
+        <v>0.82</v>
       </c>
       <c r="F68" t="n">
-        <v>-4.02</v>
+        <v>-4.22</v>
       </c>
       <c r="G68" t="n">
-        <v>10.78</v>
+        <v>10.54</v>
       </c>
       <c r="H68" t="n">
-        <v>-13.26</v>
+        <v>-13.41</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="J68" t="n">
         <v>7.99</v>
@@ -7940,28 +7936,28 @@
         <v>3.24</v>
       </c>
       <c r="L68" t="n">
-        <v>244.05</v>
+        <v>243.52</v>
       </c>
       <c r="M68" t="n">
-        <v>248.05</v>
+        <v>247.52</v>
       </c>
       <c r="N68" t="n">
-        <v>236.07</v>
+        <v>235.54</v>
       </c>
       <c r="O68" t="n">
-        <v>264.42</v>
+        <v>263.89</v>
       </c>
       <c r="P68" t="n">
         <v>1.63</v>
       </c>
       <c r="Q68" t="n">
-        <v>30.03</v>
+        <v>29.78</v>
       </c>
       <c r="R68" t="n">
-        <v>-3.16</v>
+        <v>-3.36</v>
       </c>
       <c r="S68" t="n">
-        <v>-10.18</v>
+        <v>-10.37</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7980,7 +7976,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>XLE 9.71% · CL=F 13.44%</t>
+          <t>XLE 9.67% · CL=F 13.23%</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -7988,11 +7984,7 @@
           <t>BAJO</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
@@ -8005,7 +7997,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.71% · CL=F 13.44%; Tendencia larga positiva; MACD mejorando; Momentum 5D sano</t>
+          <t>Mercado NEUTRO +; Sector acompaña: XLE 9.67% · CL=F 13.23%; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8026,25 +8018,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1751.04</v>
+        <v>1751.51</v>
       </c>
       <c r="D69" t="n">
         <v>33</v>
       </c>
       <c r="E69" t="n">
-        <v>-3.21</v>
+        <v>-3.18</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.8</v>
+        <v>-1.77</v>
       </c>
       <c r="G69" t="n">
-        <v>17.85</v>
+        <v>17.89</v>
       </c>
       <c r="H69" t="n">
-        <v>-11.04</v>
+        <v>-10.96</v>
       </c>
       <c r="I69" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>86.64</v>
@@ -8053,28 +8045,28 @@
         <v>4.95</v>
       </c>
       <c r="L69" t="n">
-        <v>1720.72</v>
+        <v>1721.18</v>
       </c>
       <c r="M69" t="n">
-        <v>1764.04</v>
+        <v>1764.5</v>
       </c>
       <c r="N69" t="n">
-        <v>1634.08</v>
+        <v>1634.54</v>
       </c>
       <c r="O69" t="n">
-        <v>1941.64</v>
+        <v>1942.11</v>
       </c>
       <c r="P69" t="n">
         <v>1.63</v>
       </c>
       <c r="Q69" t="n">
-        <v>45.11</v>
+        <v>45.15</v>
       </c>
       <c r="R69" t="n">
-        <v>-3.07</v>
+        <v>-3.04</v>
       </c>
       <c r="S69" t="n">
-        <v>-9.6</v>
+        <v>-9.57</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8093,7 +8085,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -8114,7 +8106,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8135,22 +8127,22 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1472.82</v>
+        <v>1475.75</v>
       </c>
       <c r="D70" t="n">
         <v>33</v>
       </c>
       <c r="E70" t="n">
-        <v>-7.92</v>
+        <v>-7.74</v>
       </c>
       <c r="F70" t="n">
-        <v>-3.61</v>
+        <v>-3.42</v>
       </c>
       <c r="G70" t="n">
-        <v>24.01</v>
+        <v>24.25</v>
       </c>
       <c r="H70" t="n">
-        <v>-12.85</v>
+        <v>-12.61</v>
       </c>
       <c r="I70" t="n">
         <v>0.57</v>
@@ -8159,31 +8151,31 @@
         <v>79.84</v>
       </c>
       <c r="K70" t="n">
-        <v>5.42</v>
+        <v>5.41</v>
       </c>
       <c r="L70" t="n">
-        <v>1444.88</v>
+        <v>1447.81</v>
       </c>
       <c r="M70" t="n">
-        <v>1484.8</v>
+        <v>1487.73</v>
       </c>
       <c r="N70" t="n">
-        <v>1365.04</v>
+        <v>1367.97</v>
       </c>
       <c r="O70" t="n">
-        <v>1648.46</v>
+        <v>1651.39</v>
       </c>
       <c r="P70" t="n">
         <v>1.63</v>
       </c>
       <c r="Q70" t="n">
-        <v>45.9</v>
+        <v>46.11</v>
       </c>
       <c r="R70" t="n">
-        <v>-6.75</v>
+        <v>-6.57</v>
       </c>
       <c r="S70" t="n">
-        <v>-12.09</v>
+        <v>-11.92</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8202,7 +8194,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -8223,7 +8215,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -8244,25 +8236,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>273.62</v>
+        <v>273.68</v>
       </c>
       <c r="D71" t="n">
         <v>58</v>
       </c>
       <c r="E71" t="n">
-        <v>-5.4</v>
+        <v>-5.38</v>
       </c>
       <c r="F71" t="n">
-        <v>5.9</v>
+        <v>5.93</v>
       </c>
       <c r="G71" t="n">
-        <v>13.08</v>
+        <v>13.1</v>
       </c>
       <c r="H71" t="n">
-        <v>-3.34</v>
+        <v>-3.26</v>
       </c>
       <c r="I71" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="J71" t="n">
         <v>14.53</v>
@@ -8271,28 +8263,28 @@
         <v>5.31</v>
       </c>
       <c r="L71" t="n">
-        <v>268.54</v>
+        <v>268.6</v>
       </c>
       <c r="M71" t="n">
-        <v>275.8</v>
+        <v>275.86</v>
       </c>
       <c r="N71" t="n">
-        <v>254.01</v>
+        <v>254.07</v>
       </c>
       <c r="O71" t="n">
-        <v>305.58</v>
+        <v>305.64</v>
       </c>
       <c r="P71" t="n">
         <v>1.63</v>
       </c>
       <c r="Q71" t="n">
-        <v>60.99</v>
+        <v>61.02</v>
       </c>
       <c r="R71" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="S71" t="n">
-        <v>-9.4</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8353,22 +8345,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>88.65000000000001</v>
+        <v>88.61</v>
       </c>
       <c r="D72" t="n">
         <v>56</v>
       </c>
       <c r="E72" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="F72" t="n">
-        <v>-4.39</v>
+        <v>-4.43</v>
       </c>
       <c r="G72" t="n">
-        <v>-22.62</v>
+        <v>-22.66</v>
       </c>
       <c r="H72" t="n">
-        <v>-13.63</v>
+        <v>-13.62</v>
       </c>
       <c r="I72" t="n">
         <v>0.48</v>
@@ -8380,28 +8372,28 @@
         <v>2.41</v>
       </c>
       <c r="L72" t="n">
-        <v>87.90000000000001</v>
+        <v>87.86</v>
       </c>
       <c r="M72" t="n">
-        <v>88.97</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="N72" t="n">
-        <v>85.77</v>
+        <v>85.73</v>
       </c>
       <c r="O72" t="n">
-        <v>93.34</v>
+        <v>93.3</v>
       </c>
       <c r="P72" t="n">
         <v>1.63</v>
       </c>
       <c r="Q72" t="n">
-        <v>42.63</v>
+        <v>42.5</v>
       </c>
       <c r="R72" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="S72" t="n">
-        <v>-6.48</v>
+        <v>-6.52</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8462,22 +8454,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>419.36</v>
+        <v>419.12</v>
       </c>
       <c r="D73" t="n">
         <v>54</v>
       </c>
       <c r="E73" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.13</v>
+        <v>-1.19</v>
       </c>
       <c r="G73" t="n">
-        <v>9.07</v>
+        <v>9.01</v>
       </c>
       <c r="H73" t="n">
-        <v>-10.37</v>
+        <v>-10.38</v>
       </c>
       <c r="I73" t="n">
         <v>0.62</v>
@@ -8489,28 +8481,28 @@
         <v>2.86</v>
       </c>
       <c r="L73" t="n">
-        <v>415.16</v>
+        <v>414.92</v>
       </c>
       <c r="M73" t="n">
-        <v>421.16</v>
+        <v>420.92</v>
       </c>
       <c r="N73" t="n">
-        <v>403.17</v>
+        <v>402.93</v>
       </c>
       <c r="O73" t="n">
-        <v>445.74</v>
+        <v>445.5</v>
       </c>
       <c r="P73" t="n">
         <v>1.63</v>
       </c>
       <c r="Q73" t="n">
-        <v>46.55</v>
+        <v>46.4</v>
       </c>
       <c r="R73" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="S73" t="n">
-        <v>-3.31</v>
+        <v>-3.36</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8529,7 +8521,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -8571,25 +8563,25 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>224.07</v>
+        <v>224.04</v>
       </c>
       <c r="D74" t="n">
         <v>52</v>
       </c>
       <c r="E74" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="F74" t="n">
-        <v>-11.72</v>
+        <v>-11.73</v>
       </c>
       <c r="G74" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H74" t="n">
-        <v>-20.96</v>
+        <v>-20.92</v>
       </c>
       <c r="I74" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="J74" t="n">
         <v>5.55</v>
@@ -8598,28 +8590,28 @@
         <v>2.48</v>
       </c>
       <c r="L74" t="n">
-        <v>222.13</v>
+        <v>222.1</v>
       </c>
       <c r="M74" t="n">
-        <v>224.9</v>
+        <v>224.87</v>
       </c>
       <c r="N74" t="n">
-        <v>216.57</v>
+        <v>216.54</v>
       </c>
       <c r="O74" t="n">
-        <v>236.29</v>
+        <v>236.26</v>
       </c>
       <c r="P74" t="n">
         <v>1.63</v>
       </c>
       <c r="Q74" t="n">
-        <v>48.36</v>
+        <v>48.32</v>
       </c>
       <c r="R74" t="n">
-        <v>-1.14</v>
+        <v>-1.15</v>
       </c>
       <c r="S74" t="n">
-        <v>-12.36</v>
+        <v>-12.37</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8638,7 +8630,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -8680,22 +8672,22 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>259.2</v>
+        <v>259.22</v>
       </c>
       <c r="D75" t="n">
         <v>46</v>
       </c>
       <c r="E75" t="n">
-        <v>-2.49</v>
+        <v>-2.48</v>
       </c>
       <c r="F75" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="G75" t="n">
-        <v>26.27</v>
+        <v>26.28</v>
       </c>
       <c r="H75" t="n">
-        <v>-5.52</v>
+        <v>-5.46</v>
       </c>
       <c r="I75" t="n">
         <v>0.62</v>
@@ -8707,28 +8699,28 @@
         <v>2.86</v>
       </c>
       <c r="L75" t="n">
-        <v>256.6</v>
+        <v>256.62</v>
       </c>
       <c r="M75" t="n">
-        <v>260.31</v>
+        <v>260.33</v>
       </c>
       <c r="N75" t="n">
-        <v>249.17</v>
+        <v>249.2</v>
       </c>
       <c r="O75" t="n">
-        <v>275.53</v>
+        <v>275.55</v>
       </c>
       <c r="P75" t="n">
         <v>1.63</v>
       </c>
       <c r="Q75" t="n">
-        <v>45.29</v>
+        <v>45.32</v>
       </c>
       <c r="R75" t="n">
-        <v>-2.49</v>
+        <v>-2.48</v>
       </c>
       <c r="S75" t="n">
-        <v>-6.95</v>
+        <v>-6.94</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8747,7 +8739,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -8789,25 +8781,25 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>273.81</v>
+        <v>273.64</v>
       </c>
       <c r="D76" t="n">
         <v>44</v>
       </c>
       <c r="E76" t="n">
-        <v>-3.1</v>
+        <v>-3.16</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.26</v>
+        <v>-0.32</v>
       </c>
       <c r="G76" t="n">
-        <v>5.3</v>
+        <v>5.24</v>
       </c>
       <c r="H76" t="n">
-        <v>-9.5</v>
+        <v>-9.51</v>
       </c>
       <c r="I76" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="J76" t="n">
         <v>4.84</v>
@@ -8816,28 +8808,28 @@
         <v>1.77</v>
       </c>
       <c r="L76" t="n">
-        <v>272.12</v>
+        <v>271.95</v>
       </c>
       <c r="M76" t="n">
-        <v>274.54</v>
+        <v>274.37</v>
       </c>
       <c r="N76" t="n">
-        <v>267.28</v>
+        <v>267.11</v>
       </c>
       <c r="O76" t="n">
-        <v>284.45</v>
+        <v>284.28</v>
       </c>
       <c r="P76" t="n">
         <v>1.63</v>
       </c>
       <c r="Q76" t="n">
-        <v>52.14</v>
+        <v>51.92</v>
       </c>
       <c r="R76" t="n">
-        <v>-1.95</v>
+        <v>-2.01</v>
       </c>
       <c r="S76" t="n">
-        <v>-4.79</v>
+        <v>-4.85</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8898,22 +8890,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>88.95999999999999</v>
+        <v>88.94</v>
       </c>
       <c r="D77" t="n">
         <v>43</v>
       </c>
       <c r="E77" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="F77" t="n">
-        <v>-3.91</v>
+        <v>-3.93</v>
       </c>
       <c r="G77" t="n">
-        <v>17.02</v>
+        <v>17</v>
       </c>
       <c r="H77" t="n">
-        <v>-13.15</v>
+        <v>-13.12</v>
       </c>
       <c r="I77" t="n">
         <v>0.6899999999999999</v>
@@ -8925,28 +8917,28 @@
         <v>2.8</v>
       </c>
       <c r="L77" t="n">
-        <v>88.09</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="M77" t="n">
-        <v>89.33</v>
+        <v>89.31</v>
       </c>
       <c r="N77" t="n">
-        <v>85.59</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="O77" t="n">
-        <v>94.44</v>
+        <v>94.42</v>
       </c>
       <c r="P77" t="n">
         <v>1.63</v>
       </c>
       <c r="Q77" t="n">
-        <v>40.56</v>
+        <v>40.51</v>
       </c>
       <c r="R77" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.96</v>
       </c>
       <c r="S77" t="n">
-        <v>-6.06</v>
+        <v>-6.08</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8965,7 +8957,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
@@ -9007,25 +8999,25 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1044.9</v>
+        <v>1045.67</v>
       </c>
       <c r="D78" t="n">
         <v>42</v>
       </c>
       <c r="E78" t="n">
-        <v>-4.36</v>
+        <v>-4.29</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="G78" t="n">
-        <v>-1.89</v>
+        <v>-1.82</v>
       </c>
       <c r="H78" t="n">
-        <v>-9.039999999999999</v>
+        <v>-8.92</v>
       </c>
       <c r="I78" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="J78" t="n">
         <v>23.77</v>
@@ -9034,28 +9026,28 @@
         <v>2.27</v>
       </c>
       <c r="L78" t="n">
-        <v>1036.58</v>
+        <v>1037.35</v>
       </c>
       <c r="M78" t="n">
-        <v>1048.47</v>
+        <v>1049.24</v>
       </c>
       <c r="N78" t="n">
-        <v>1012.81</v>
+        <v>1013.58</v>
       </c>
       <c r="O78" t="n">
-        <v>1097.2</v>
+        <v>1097.97</v>
       </c>
       <c r="P78" t="n">
         <v>1.63</v>
       </c>
       <c r="Q78" t="n">
-        <v>51.5</v>
+        <v>51.72</v>
       </c>
       <c r="R78" t="n">
-        <v>-2.1</v>
+        <v>-2.03</v>
       </c>
       <c r="S78" t="n">
-        <v>-5.96</v>
+        <v>-5.89</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9107,64 +9099,64 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Consumo</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8.800000000000001</v>
+        <v>282.23</v>
       </c>
       <c r="D79" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E79" t="n">
-        <v>0.06</v>
+        <v>2.69</v>
       </c>
       <c r="F79" t="n">
-        <v>-4.4</v>
+        <v>-6.5</v>
       </c>
       <c r="G79" t="n">
-        <v>-10.16</v>
+        <v>-15.17</v>
       </c>
       <c r="H79" t="n">
-        <v>-13.64</v>
+        <v>-15.69</v>
       </c>
       <c r="I79" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="J79" t="n">
-        <v>0.46</v>
+        <v>5.9</v>
       </c>
       <c r="K79" t="n">
-        <v>5.18</v>
+        <v>2.09</v>
       </c>
       <c r="L79" t="n">
-        <v>8.640000000000001</v>
+        <v>280.16</v>
       </c>
       <c r="M79" t="n">
-        <v>8.859999999999999</v>
+        <v>283.12</v>
       </c>
       <c r="N79" t="n">
-        <v>8.18</v>
+        <v>274.26</v>
       </c>
       <c r="O79" t="n">
-        <v>9.800000000000001</v>
+        <v>295.22</v>
       </c>
       <c r="P79" t="n">
         <v>1.63</v>
       </c>
       <c r="Q79" t="n">
-        <v>49</v>
+        <v>38.53</v>
       </c>
       <c r="R79" t="n">
-        <v>-2.82</v>
+        <v>-1.13</v>
       </c>
       <c r="S79" t="n">
-        <v>-10.98</v>
+        <v>-7.43</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9178,12 +9170,12 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -9204,76 +9196,76 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; MA20 sobre MA50; RSI saludable; MACD mejorando</t>
+          <t>Mercado NEUTRO +; MACD positivo; MACD mejorando; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; Volumen bajo; Débil vs QQQ; Lejos del máximo 20D</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>282.47</v>
+        <v>74.56</v>
       </c>
       <c r="D80" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E80" t="n">
-        <v>2.78</v>
+        <v>-2.36</v>
       </c>
       <c r="F80" t="n">
-        <v>-6.42</v>
+        <v>-3.49</v>
       </c>
       <c r="G80" t="n">
-        <v>-15.1</v>
+        <v>5.43</v>
       </c>
       <c r="H80" t="n">
-        <v>-15.66</v>
+        <v>-12.68</v>
       </c>
       <c r="I80" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="J80" t="n">
-        <v>5.9</v>
+        <v>2.58</v>
       </c>
       <c r="K80" t="n">
-        <v>2.09</v>
+        <v>3.46</v>
       </c>
       <c r="L80" t="n">
-        <v>280.4</v>
+        <v>73.66</v>
       </c>
       <c r="M80" t="n">
-        <v>283.36</v>
+        <v>74.95</v>
       </c>
       <c r="N80" t="n">
-        <v>274.5</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="O80" t="n">
-        <v>295.46</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="P80" t="n">
         <v>1.63</v>
       </c>
       <c r="Q80" t="n">
-        <v>38.8</v>
+        <v>50.28</v>
       </c>
       <c r="R80" t="n">
-        <v>-1.05</v>
+        <v>-0.87</v>
       </c>
       <c r="S80" t="n">
-        <v>-7.35</v>
+        <v>-7.76</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9287,12 +9279,12 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
@@ -9313,76 +9305,76 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; MACD positivo; MACD mejorando; Momentum 5D sano</t>
+          <t>Mercado NEUTRO +; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; Volumen bajo; Débil vs QQQ; Lejos del máximo 20D</t>
+          <t>Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>74.55</v>
+        <v>8.77</v>
       </c>
       <c r="D81" t="n">
         <v>36</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.37</v>
+        <v>-0.17</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.51</v>
+        <v>-4.62</v>
       </c>
       <c r="G81" t="n">
-        <v>5.42</v>
+        <v>-10.37</v>
       </c>
       <c r="H81" t="n">
-        <v>-12.75</v>
+        <v>-13.81</v>
       </c>
       <c r="I81" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="J81" t="n">
-        <v>2.58</v>
+        <v>0.46</v>
       </c>
       <c r="K81" t="n">
-        <v>3.46</v>
+        <v>5.19</v>
       </c>
       <c r="L81" t="n">
-        <v>73.65000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="M81" t="n">
-        <v>74.94</v>
+        <v>8.84</v>
       </c>
       <c r="N81" t="n">
-        <v>71.06</v>
+        <v>8.16</v>
       </c>
       <c r="O81" t="n">
-        <v>80.23</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="P81" t="n">
         <v>1.63</v>
       </c>
       <c r="Q81" t="n">
-        <v>50.25</v>
+        <v>48.68</v>
       </c>
       <c r="R81" t="n">
-        <v>-0.89</v>
+        <v>-3.03</v>
       </c>
       <c r="S81" t="n">
-        <v>-7.77</v>
+        <v>-11.18</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9401,7 +9393,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
@@ -9443,25 +9435,25 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>74.29000000000001</v>
+        <v>74.19</v>
       </c>
       <c r="D82" t="n">
         <v>33</v>
       </c>
       <c r="E82" t="n">
-        <v>-5.01</v>
+        <v>-5.13</v>
       </c>
       <c r="F82" t="n">
-        <v>-3.99</v>
+        <v>-4.12</v>
       </c>
       <c r="G82" t="n">
-        <v>6.13</v>
+        <v>5.99</v>
       </c>
       <c r="H82" t="n">
-        <v>-13.23</v>
+        <v>-13.31</v>
       </c>
       <c r="I82" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="J82" t="n">
         <v>2.44</v>
@@ -9470,28 +9462,28 @@
         <v>3.28</v>
       </c>
       <c r="L82" t="n">
-        <v>73.44</v>
+        <v>73.34</v>
       </c>
       <c r="M82" t="n">
-        <v>74.66</v>
+        <v>74.56</v>
       </c>
       <c r="N82" t="n">
-        <v>71</v>
+        <v>70.91</v>
       </c>
       <c r="O82" t="n">
-        <v>79.65000000000001</v>
+        <v>79.55</v>
       </c>
       <c r="P82" t="n">
         <v>1.63</v>
       </c>
       <c r="Q82" t="n">
-        <v>52.02</v>
+        <v>51.76</v>
       </c>
       <c r="R82" t="n">
-        <v>-3.52</v>
+        <v>-3.64</v>
       </c>
       <c r="S82" t="n">
-        <v>-7.93</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9510,7 +9502,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -9552,25 +9544,25 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>51.41</v>
+        <v>51.4</v>
       </c>
       <c r="D83" t="n">
         <v>32</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.33</v>
+        <v>-0.36</v>
       </c>
       <c r="F83" t="n">
-        <v>-1.7</v>
+        <v>-1.73</v>
       </c>
       <c r="G83" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="H83" t="n">
-        <v>-10.94</v>
+        <v>-10.92</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="J83" t="n">
         <v>0.65</v>
@@ -9579,28 +9571,28 @@
         <v>1.26</v>
       </c>
       <c r="L83" t="n">
-        <v>51.18</v>
+        <v>51.17</v>
       </c>
       <c r="M83" t="n">
-        <v>51.51</v>
+        <v>51.49</v>
       </c>
       <c r="N83" t="n">
-        <v>50.54</v>
+        <v>50.52</v>
       </c>
       <c r="O83" t="n">
-        <v>52.83</v>
+        <v>52.82</v>
       </c>
       <c r="P83" t="n">
         <v>1.63</v>
       </c>
       <c r="Q83" t="n">
-        <v>43.83</v>
+        <v>43.67</v>
       </c>
       <c r="R83" t="n">
-        <v>-0.38</v>
+        <v>-0.41</v>
       </c>
       <c r="S83" t="n">
-        <v>-2.36</v>
+        <v>-2.38</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9661,25 +9653,25 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>51.06</v>
+        <v>51.02</v>
       </c>
       <c r="D84" t="n">
         <v>32</v>
       </c>
       <c r="E84" t="n">
-        <v>0.54</v>
+        <v>0.47</v>
       </c>
       <c r="F84" t="n">
-        <v>-4.53</v>
+        <v>-4.6</v>
       </c>
       <c r="G84" t="n">
-        <v>0.54</v>
+        <v>0.47</v>
       </c>
       <c r="H84" t="n">
-        <v>-13.77</v>
+        <v>-13.79</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J84" t="n">
         <v>1.18</v>
@@ -9688,28 +9680,28 @@
         <v>2.31</v>
       </c>
       <c r="L84" t="n">
-        <v>50.64</v>
+        <v>50.61</v>
       </c>
       <c r="M84" t="n">
-        <v>51.23</v>
+        <v>51.2</v>
       </c>
       <c r="N84" t="n">
-        <v>49.46</v>
+        <v>49.43</v>
       </c>
       <c r="O84" t="n">
-        <v>53.65</v>
+        <v>53.61</v>
       </c>
       <c r="P84" t="n">
         <v>1.63</v>
       </c>
       <c r="Q84" t="n">
-        <v>39.7</v>
+        <v>39.46</v>
       </c>
       <c r="R84" t="n">
-        <v>-1.63</v>
+        <v>-1.69</v>
       </c>
       <c r="S84" t="n">
-        <v>-5.8</v>
+        <v>-5.87</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9770,22 +9762,22 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>559.74</v>
+        <v>559.54</v>
       </c>
       <c r="D85" t="n">
         <v>31</v>
       </c>
       <c r="E85" t="n">
-        <v>-5</v>
+        <v>-5.03</v>
       </c>
       <c r="F85" t="n">
-        <v>-4.69</v>
+        <v>-4.73</v>
       </c>
       <c r="G85" t="n">
-        <v>-13.21</v>
+        <v>-13.24</v>
       </c>
       <c r="H85" t="n">
-        <v>-13.93</v>
+        <v>-13.92</v>
       </c>
       <c r="I85" t="n">
         <v>0.52</v>
@@ -9797,28 +9789,28 @@
         <v>2.68</v>
       </c>
       <c r="L85" t="n">
-        <v>554.48</v>
+        <v>554.28</v>
       </c>
       <c r="M85" t="n">
-        <v>561.99</v>
+        <v>561.79</v>
       </c>
       <c r="N85" t="n">
-        <v>539.47</v>
+        <v>539.27</v>
       </c>
       <c r="O85" t="n">
-        <v>592.78</v>
+        <v>592.58</v>
       </c>
       <c r="P85" t="n">
         <v>1.63</v>
       </c>
       <c r="Q85" t="n">
-        <v>49.89</v>
+        <v>49.81</v>
       </c>
       <c r="R85" t="n">
-        <v>-2.77</v>
+        <v>-2.8</v>
       </c>
       <c r="S85" t="n">
-        <v>-5.92</v>
+        <v>-5.95</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9879,25 +9871,25 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>139.85</v>
+        <v>139.96</v>
       </c>
       <c r="D86" t="n">
         <v>31</v>
       </c>
       <c r="E86" t="n">
-        <v>-1.89</v>
+        <v>-1.81</v>
       </c>
       <c r="F86" t="n">
-        <v>-19.1</v>
+        <v>-19.04</v>
       </c>
       <c r="G86" t="n">
-        <v>9.75</v>
+        <v>9.83</v>
       </c>
       <c r="H86" t="n">
-        <v>-28.34</v>
+        <v>-28.23</v>
       </c>
       <c r="I86" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J86" t="n">
         <v>8.27</v>
@@ -9906,28 +9898,28 @@
         <v>5.91</v>
       </c>
       <c r="L86" t="n">
-        <v>136.96</v>
+        <v>137.06</v>
       </c>
       <c r="M86" t="n">
-        <v>141.09</v>
+        <v>141.2</v>
       </c>
       <c r="N86" t="n">
-        <v>128.69</v>
+        <v>128.79</v>
       </c>
       <c r="O86" t="n">
-        <v>158.04</v>
+        <v>158.15</v>
       </c>
       <c r="P86" t="n">
         <v>1.63</v>
       </c>
       <c r="Q86" t="n">
-        <v>27.26</v>
+        <v>27.31</v>
       </c>
       <c r="R86" t="n">
-        <v>-11.02</v>
+        <v>-10.96</v>
       </c>
       <c r="S86" t="n">
-        <v>-22.22</v>
+        <v>-22.16</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9946,7 +9938,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
@@ -9988,22 +9980,22 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>69.39</v>
+        <v>69.36</v>
       </c>
       <c r="D87" t="n">
         <v>29</v>
       </c>
       <c r="E87" t="n">
-        <v>-3.79</v>
+        <v>-3.83</v>
       </c>
       <c r="F87" t="n">
-        <v>-3.29</v>
+        <v>-3.33</v>
       </c>
       <c r="G87" t="n">
-        <v>36.73</v>
+        <v>36.67</v>
       </c>
       <c r="H87" t="n">
-        <v>-12.53</v>
+        <v>-12.52</v>
       </c>
       <c r="I87" t="n">
         <v>0.53</v>
@@ -10015,28 +10007,28 @@
         <v>3.76</v>
       </c>
       <c r="L87" t="n">
-        <v>68.48</v>
+        <v>68.45</v>
       </c>
       <c r="M87" t="n">
-        <v>69.78</v>
+        <v>69.75</v>
       </c>
       <c r="N87" t="n">
-        <v>65.87</v>
+        <v>65.84</v>
       </c>
       <c r="O87" t="n">
-        <v>75.13</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="P87" t="n">
         <v>1.63</v>
       </c>
       <c r="Q87" t="n">
-        <v>49.81</v>
+        <v>49.73</v>
       </c>
       <c r="R87" t="n">
-        <v>-2.45</v>
+        <v>-2.49</v>
       </c>
       <c r="S87" t="n">
-        <v>-10.07</v>
+        <v>-10.11</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10097,22 +10089,22 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>74.73</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="D88" t="n">
         <v>29</v>
       </c>
       <c r="E88" t="n">
-        <v>-4.52</v>
+        <v>-4.45</v>
       </c>
       <c r="F88" t="n">
-        <v>-13.54</v>
+        <v>-13.47</v>
       </c>
       <c r="G88" t="n">
-        <v>4.11</v>
+        <v>4.19</v>
       </c>
       <c r="H88" t="n">
-        <v>-22.78</v>
+        <v>-22.66</v>
       </c>
       <c r="I88" t="n">
         <v>0.52</v>
@@ -10124,28 +10116,28 @@
         <v>5.29</v>
       </c>
       <c r="L88" t="n">
-        <v>73.34999999999999</v>
+        <v>73.41</v>
       </c>
       <c r="M88" t="n">
-        <v>75.31999999999999</v>
+        <v>75.38</v>
       </c>
       <c r="N88" t="n">
-        <v>69.39</v>
+        <v>69.45</v>
       </c>
       <c r="O88" t="n">
-        <v>83.43000000000001</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="P88" t="n">
         <v>1.63</v>
       </c>
       <c r="Q88" t="n">
-        <v>56.07</v>
+        <v>56.18</v>
       </c>
       <c r="R88" t="n">
-        <v>-4.92</v>
+        <v>-4.85</v>
       </c>
       <c r="S88" t="n">
-        <v>-17.09</v>
+        <v>-17.02</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10206,22 +10198,22 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>297.67</v>
+        <v>297.69</v>
       </c>
       <c r="D89" t="n">
         <v>28</v>
       </c>
       <c r="E89" t="n">
-        <v>-2.37</v>
+        <v>-2.36</v>
       </c>
       <c r="F89" t="n">
-        <v>-4.9</v>
+        <v>-4.89</v>
       </c>
       <c r="G89" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H89" t="n">
-        <v>-14.14</v>
+        <v>-14.08</v>
       </c>
       <c r="I89" t="n">
         <v>0.47</v>
@@ -10233,28 +10225,28 @@
         <v>2.03</v>
       </c>
       <c r="L89" t="n">
-        <v>295.55</v>
+        <v>295.57</v>
       </c>
       <c r="M89" t="n">
-        <v>298.57</v>
+        <v>298.6</v>
       </c>
       <c r="N89" t="n">
-        <v>289.5</v>
+        <v>289.52</v>
       </c>
       <c r="O89" t="n">
-        <v>310.98</v>
+        <v>311</v>
       </c>
       <c r="P89" t="n">
         <v>1.63</v>
       </c>
       <c r="Q89" t="n">
-        <v>38.33</v>
+        <v>38.35</v>
       </c>
       <c r="R89" t="n">
         <v>-2.92</v>
       </c>
       <c r="S89" t="n">
-        <v>-5.89</v>
+        <v>-5.88</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10321,19 +10313,19 @@
         <v>26</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.89</v>
+        <v>-0.91</v>
       </c>
       <c r="F90" t="n">
-        <v>-4.57</v>
+        <v>-4.58</v>
       </c>
       <c r="G90" t="n">
-        <v>-3.68</v>
+        <v>-3.7</v>
       </c>
       <c r="H90" t="n">
-        <v>-13.81</v>
+        <v>-13.77</v>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="J90" t="n">
         <v>0.49</v>
@@ -10342,7 +10334,7 @@
         <v>1.93</v>
       </c>
       <c r="L90" t="n">
-        <v>25.47</v>
+        <v>25.46</v>
       </c>
       <c r="M90" t="n">
         <v>25.71</v>
@@ -10351,19 +10343,19 @@
         <v>24.97</v>
       </c>
       <c r="O90" t="n">
-        <v>26.73</v>
+        <v>26.72</v>
       </c>
       <c r="P90" t="n">
         <v>1.63</v>
       </c>
       <c r="Q90" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="R90" t="n">
-        <v>-1.19</v>
+        <v>-1.21</v>
       </c>
       <c r="S90" t="n">
-        <v>-5.5</v>
+        <v>-5.52</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10424,22 +10416,22 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>500.62</v>
+        <v>500.47</v>
       </c>
       <c r="D91" t="n">
         <v>22</v>
       </c>
       <c r="E91" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F91" t="n">
-        <v>-2.1</v>
+        <v>-2.13</v>
       </c>
       <c r="G91" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="H91" t="n">
-        <v>-11.34</v>
+        <v>-11.32</v>
       </c>
       <c r="I91" t="n">
         <v>0.42</v>
@@ -10451,28 +10443,28 @@
         <v>2.5</v>
       </c>
       <c r="L91" t="n">
-        <v>496.23</v>
+        <v>496.08</v>
       </c>
       <c r="M91" t="n">
-        <v>502.5</v>
+        <v>502.35</v>
       </c>
       <c r="N91" t="n">
-        <v>483.7</v>
+        <v>483.55</v>
       </c>
       <c r="O91" t="n">
-        <v>528.2</v>
+        <v>528.05</v>
       </c>
       <c r="P91" t="n">
         <v>1.63</v>
       </c>
       <c r="Q91" t="n">
-        <v>37.89</v>
+        <v>37.84</v>
       </c>
       <c r="R91" t="n">
-        <v>-0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="S91" t="n">
-        <v>-6.29</v>
+        <v>-6.32</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10533,25 +10525,25 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>120.91</v>
+        <v>120.82</v>
       </c>
       <c r="D92" t="n">
         <v>22</v>
       </c>
       <c r="E92" t="n">
-        <v>-4.37</v>
+        <v>-4.44</v>
       </c>
       <c r="F92" t="n">
-        <v>-7.74</v>
+        <v>-7.81</v>
       </c>
       <c r="G92" t="n">
-        <v>9.69</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="H92" t="n">
-        <v>-16.98</v>
+        <v>-17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J92" t="n">
         <v>3.27</v>
@@ -10560,28 +10552,28 @@
         <v>2.7</v>
       </c>
       <c r="L92" t="n">
-        <v>119.77</v>
+        <v>119.68</v>
       </c>
       <c r="M92" t="n">
-        <v>121.4</v>
+        <v>121.31</v>
       </c>
       <c r="N92" t="n">
-        <v>116.5</v>
+        <v>116.41</v>
       </c>
       <c r="O92" t="n">
-        <v>128.1</v>
+        <v>128.01</v>
       </c>
       <c r="P92" t="n">
         <v>1.63</v>
       </c>
       <c r="Q92" t="n">
-        <v>32.86</v>
+        <v>32.7</v>
       </c>
       <c r="R92" t="n">
-        <v>-4.26</v>
+        <v>-4.33</v>
       </c>
       <c r="S92" t="n">
-        <v>-8.369999999999999</v>
+        <v>-8.44</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10642,22 +10634,22 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>44.1</v>
+        <v>44.11</v>
       </c>
       <c r="D93" t="n">
         <v>20</v>
       </c>
       <c r="E93" t="n">
-        <v>-2.96</v>
+        <v>-2.93</v>
       </c>
       <c r="F93" t="n">
-        <v>-13.34</v>
+        <v>-13.31</v>
       </c>
       <c r="G93" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="H93" t="n">
-        <v>-22.58</v>
+        <v>-22.5</v>
       </c>
       <c r="I93" t="n">
         <v>0.61</v>
@@ -10669,28 +10661,28 @@
         <v>3.22</v>
       </c>
       <c r="L93" t="n">
-        <v>43.6</v>
+        <v>43.61</v>
       </c>
       <c r="M93" t="n">
-        <v>44.31</v>
+        <v>44.32</v>
       </c>
       <c r="N93" t="n">
-        <v>42.18</v>
+        <v>42.19</v>
       </c>
       <c r="O93" t="n">
-        <v>47.22</v>
+        <v>47.24</v>
       </c>
       <c r="P93" t="n">
         <v>1.63</v>
       </c>
       <c r="Q93" t="n">
-        <v>8.19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R93" t="n">
-        <v>-7.25</v>
+        <v>-7.22</v>
       </c>
       <c r="S93" t="n">
-        <v>-14.99</v>
+        <v>-14.96</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10757,19 +10749,19 @@
         <v>20</v>
       </c>
       <c r="E94" t="n">
-        <v>-3.65</v>
+        <v>-3.63</v>
       </c>
       <c r="F94" t="n">
-        <v>-18.64</v>
+        <v>-18.62</v>
       </c>
       <c r="G94" t="n">
-        <v>-15.92</v>
+        <v>-15.9</v>
       </c>
       <c r="H94" t="n">
-        <v>-27.88</v>
+        <v>-27.81</v>
       </c>
       <c r="I94" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="J94" t="n">
         <v>0.7</v>
@@ -10781,7 +10773,7 @@
         <v>15.08</v>
       </c>
       <c r="M94" t="n">
-        <v>15.42</v>
+        <v>15.43</v>
       </c>
       <c r="N94" t="n">
         <v>14.38</v>
@@ -10790,16 +10782,16 @@
         <v>16.85</v>
       </c>
       <c r="P94" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q94" t="n">
-        <v>48.04</v>
+        <v>48.07</v>
       </c>
       <c r="R94" t="n">
-        <v>-7.54</v>
+        <v>-7.52</v>
       </c>
       <c r="S94" t="n">
-        <v>-21.23</v>
+        <v>-21.21</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10860,25 +10852,25 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>452.01</v>
+        <v>451.73</v>
       </c>
       <c r="D95" t="n">
         <v>19</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.59</v>
+        <v>-1.65</v>
       </c>
       <c r="F95" t="n">
-        <v>-13.83</v>
+        <v>-13.89</v>
       </c>
       <c r="G95" t="n">
-        <v>-12.39</v>
+        <v>-12.44</v>
       </c>
       <c r="H95" t="n">
-        <v>-23.07</v>
+        <v>-23.08</v>
       </c>
       <c r="I95" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="J95" t="n">
         <v>13.96</v>
@@ -10887,28 +10879,28 @@
         <v>3.09</v>
       </c>
       <c r="L95" t="n">
-        <v>447.12</v>
+        <v>446.84</v>
       </c>
       <c r="M95" t="n">
-        <v>454.1</v>
+        <v>453.82</v>
       </c>
       <c r="N95" t="n">
-        <v>433.16</v>
+        <v>432.88</v>
       </c>
       <c r="O95" t="n">
-        <v>482.72</v>
+        <v>482.44</v>
       </c>
       <c r="P95" t="n">
         <v>1.63</v>
       </c>
       <c r="Q95" t="n">
-        <v>43.43</v>
+        <v>43.28</v>
       </c>
       <c r="R95" t="n">
-        <v>-2.62</v>
+        <v>-2.68</v>
       </c>
       <c r="S95" t="n">
-        <v>-14.71</v>
+        <v>-14.77</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10969,25 +10961,25 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>285.26</v>
+        <v>285.2</v>
       </c>
       <c r="D96" t="n">
         <v>16</v>
       </c>
       <c r="E96" t="n">
-        <v>-4.1</v>
+        <v>-4.12</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="G96" t="n">
-        <v>-15.73</v>
+        <v>-15.74</v>
       </c>
       <c r="H96" t="n">
-        <v>-9.75</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="J96" t="n">
         <v>9.07</v>
@@ -10996,28 +10988,28 @@
         <v>3.18</v>
       </c>
       <c r="L96" t="n">
-        <v>282.09</v>
+        <v>282.03</v>
       </c>
       <c r="M96" t="n">
-        <v>286.62</v>
+        <v>286.56</v>
       </c>
       <c r="N96" t="n">
-        <v>273.02</v>
+        <v>272.97</v>
       </c>
       <c r="O96" t="n">
-        <v>305.21</v>
+        <v>305.15</v>
       </c>
       <c r="P96" t="n">
         <v>1.63</v>
       </c>
       <c r="Q96" t="n">
-        <v>51.09</v>
+        <v>51.05</v>
       </c>
       <c r="R96" t="n">
-        <v>-1.41</v>
+        <v>-1.43</v>
       </c>
       <c r="S96" t="n">
-        <v>-7.98</v>
+        <v>-8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11078,55 +11070,55 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>217.48</v>
+        <v>217.21</v>
       </c>
       <c r="D97" t="n">
         <v>15</v>
       </c>
       <c r="E97" t="n">
-        <v>-8.19</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.77</v>
+        <v>-0.89</v>
       </c>
       <c r="G97" t="n">
-        <v>-5.63</v>
+        <v>-5.74</v>
       </c>
       <c r="H97" t="n">
-        <v>-10.01</v>
+        <v>-10.08</v>
       </c>
       <c r="I97" t="n">
         <v>0.34</v>
       </c>
       <c r="J97" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="K97" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="L97" t="n">
-        <v>215.06</v>
+        <v>214.79</v>
       </c>
       <c r="M97" t="n">
-        <v>218.51</v>
+        <v>218.24</v>
       </c>
       <c r="N97" t="n">
-        <v>208.17</v>
+        <v>207.88</v>
       </c>
       <c r="O97" t="n">
-        <v>232.63</v>
+        <v>232.39</v>
       </c>
       <c r="P97" t="n">
         <v>1.63</v>
       </c>
       <c r="Q97" t="n">
-        <v>44.28</v>
+        <v>44.07</v>
       </c>
       <c r="R97" t="n">
-        <v>-5.2</v>
+        <v>-5.31</v>
       </c>
       <c r="S97" t="n">
-        <v>-10.9</v>
+        <v>-11.01</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11187,22 +11179,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>135.37</v>
+        <v>135.24</v>
       </c>
       <c r="D98" t="n">
         <v>15</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.46</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F98" t="n">
-        <v>-7.26</v>
+        <v>-7.35</v>
       </c>
       <c r="G98" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="H98" t="n">
-        <v>-16.5</v>
+        <v>-16.54</v>
       </c>
       <c r="I98" t="n">
         <v>0.51</v>
@@ -11214,28 +11206,28 @@
         <v>4.15</v>
       </c>
       <c r="L98" t="n">
-        <v>133.4</v>
+        <v>133.27</v>
       </c>
       <c r="M98" t="n">
-        <v>136.21</v>
+        <v>136.08</v>
       </c>
       <c r="N98" t="n">
-        <v>127.79</v>
+        <v>127.66</v>
       </c>
       <c r="O98" t="n">
-        <v>147.73</v>
+        <v>147.6</v>
       </c>
       <c r="P98" t="n">
         <v>1.63</v>
       </c>
       <c r="Q98" t="n">
-        <v>46.52</v>
+        <v>46.34</v>
       </c>
       <c r="R98" t="n">
-        <v>-2.42</v>
+        <v>-2.51</v>
       </c>
       <c r="S98" t="n">
-        <v>-11.34</v>
+        <v>-11.42</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11254,7 +11246,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
@@ -11296,25 +11288,25 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>602.21</v>
+        <v>602.0700000000001</v>
       </c>
       <c r="D99" t="n">
         <v>14</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.13</v>
+        <v>-0.16</v>
       </c>
       <c r="F99" t="n">
-        <v>-9.960000000000001</v>
+        <v>-9.98</v>
       </c>
       <c r="G99" t="n">
-        <v>-5.42</v>
+        <v>-5.44</v>
       </c>
       <c r="H99" t="n">
-        <v>-19.2</v>
+        <v>-19.17</v>
       </c>
       <c r="I99" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="J99" t="n">
         <v>17.4</v>
@@ -11323,28 +11315,28 @@
         <v>2.89</v>
       </c>
       <c r="L99" t="n">
-        <v>596.11</v>
+        <v>595.97</v>
       </c>
       <c r="M99" t="n">
-        <v>604.8200000000001</v>
+        <v>604.6799999999999</v>
       </c>
       <c r="N99" t="n">
-        <v>578.71</v>
+        <v>578.5700000000001</v>
       </c>
       <c r="O99" t="n">
-        <v>640.49</v>
+        <v>640.35</v>
       </c>
       <c r="P99" t="n">
         <v>1.63</v>
       </c>
       <c r="Q99" t="n">
-        <v>24.86</v>
+        <v>24.83</v>
       </c>
       <c r="R99" t="n">
-        <v>-4.17</v>
+        <v>-4.19</v>
       </c>
       <c r="S99" t="n">
-        <v>-11.76</v>
+        <v>-11.79</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11363,7 +11355,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
@@ -11396,64 +11388,64 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Finanzas</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>301.32</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="D100" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E100" t="n">
-        <v>-2.94</v>
+        <v>-0.53</v>
       </c>
       <c r="F100" t="n">
-        <v>-12.39</v>
+        <v>-7.77</v>
       </c>
       <c r="G100" t="n">
-        <v>-19.54</v>
+        <v>-11.67</v>
       </c>
       <c r="H100" t="n">
-        <v>-21.63</v>
+        <v>-16.96</v>
       </c>
       <c r="I100" t="n">
-        <v>1.26</v>
+        <v>0.39</v>
       </c>
       <c r="J100" t="n">
-        <v>8.08</v>
+        <v>1.92</v>
       </c>
       <c r="K100" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="L100" t="n">
-        <v>298.49</v>
+        <v>74.11</v>
       </c>
       <c r="M100" t="n">
-        <v>302.53</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="N100" t="n">
-        <v>290.41</v>
+        <v>72.19</v>
       </c>
       <c r="O100" t="n">
-        <v>319.1</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="P100" t="n">
         <v>1.63</v>
       </c>
       <c r="Q100" t="n">
-        <v>33.71</v>
+        <v>31.15</v>
       </c>
       <c r="R100" t="n">
-        <v>-5.41</v>
+        <v>-3.79</v>
       </c>
       <c r="S100" t="n">
-        <v>-12.72</v>
+        <v>-9.01</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11498,71 +11490,71 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Finanzas</t>
+          <t>Consumo</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>74.81</v>
+        <v>218.58</v>
       </c>
       <c r="D101" t="n">
         <v>7</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.49</v>
+        <v>-2.65</v>
       </c>
       <c r="F101" t="n">
-        <v>-7.74</v>
+        <v>-12.56</v>
       </c>
       <c r="G101" t="n">
-        <v>-11.64</v>
+        <v>-19.95</v>
       </c>
       <c r="H101" t="n">
-        <v>-16.98</v>
+        <v>-21.75</v>
       </c>
       <c r="I101" t="n">
-        <v>0.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J101" t="n">
-        <v>1.92</v>
+        <v>5.88</v>
       </c>
       <c r="K101" t="n">
-        <v>2.57</v>
+        <v>2.69</v>
       </c>
       <c r="L101" t="n">
-        <v>74.14</v>
+        <v>216.52</v>
       </c>
       <c r="M101" t="n">
-        <v>75.09999999999999</v>
+        <v>219.46</v>
       </c>
       <c r="N101" t="n">
-        <v>72.22</v>
+        <v>210.64</v>
       </c>
       <c r="O101" t="n">
-        <v>79.03</v>
+        <v>231.51</v>
       </c>
       <c r="P101" t="n">
         <v>1.63</v>
       </c>
       <c r="Q101" t="n">
-        <v>31.25</v>
+        <v>35.72</v>
       </c>
       <c r="R101" t="n">
-        <v>-3.76</v>
+        <v>-5.31</v>
       </c>
       <c r="S101" t="n">
-        <v>-8.98</v>
+        <v>-13.27</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11614,7 +11606,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11623,55 +11615,55 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>218.82</v>
+        <v>300.96</v>
       </c>
       <c r="D102" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E102" t="n">
-        <v>-2.54</v>
+        <v>-3.06</v>
       </c>
       <c r="F102" t="n">
-        <v>-12.47</v>
+        <v>-12.49</v>
       </c>
       <c r="G102" t="n">
-        <v>-19.86</v>
+        <v>-19.63</v>
       </c>
       <c r="H102" t="n">
-        <v>-21.71</v>
+        <v>-21.68</v>
       </c>
       <c r="I102" t="n">
-        <v>0.68</v>
+        <v>1.27</v>
       </c>
       <c r="J102" t="n">
-        <v>5.88</v>
+        <v>8.08</v>
       </c>
       <c r="K102" t="n">
         <v>2.69</v>
       </c>
       <c r="L102" t="n">
-        <v>216.77</v>
+        <v>298.13</v>
       </c>
       <c r="M102" t="n">
-        <v>219.71</v>
+        <v>302.17</v>
       </c>
       <c r="N102" t="n">
-        <v>210.89</v>
+        <v>290.05</v>
       </c>
       <c r="O102" t="n">
-        <v>231.76</v>
+        <v>318.74</v>
       </c>
       <c r="P102" t="n">
         <v>1.63</v>
       </c>
       <c r="Q102" t="n">
-        <v>36.02</v>
+        <v>33.34</v>
       </c>
       <c r="R102" t="n">
-        <v>-5.21</v>
+        <v>-5.51</v>
       </c>
       <c r="S102" t="n">
-        <v>-13.17</v>
+        <v>-12.83</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11716,7 +11708,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Precio bajo MA20; Tendencia larga débil; RSI débil; MACD sin confirmar; Momentum negativo</t>
         </is>
       </c>
     </row>
@@ -11732,55 +11724,55 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>8.470000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="D103" t="n">
         <v>56</v>
       </c>
       <c r="E103" t="n">
-        <v>5.09</v>
+        <v>5.33</v>
       </c>
       <c r="F103" t="n">
-        <v>7.9</v>
+        <v>8.15</v>
       </c>
       <c r="G103" t="n">
-        <v>8.17</v>
+        <v>8.43</v>
       </c>
       <c r="H103" t="n">
-        <v>-1.34</v>
+        <v>-1.04</v>
       </c>
       <c r="I103" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0.66</v>
       </c>
       <c r="K103" t="n">
-        <v>7.76</v>
+        <v>7.77</v>
       </c>
       <c r="L103" t="n">
-        <v>8.24</v>
+        <v>8.26</v>
       </c>
       <c r="M103" t="n">
-        <v>8.57</v>
+        <v>8.59</v>
       </c>
       <c r="N103" t="n">
-        <v>7.58</v>
+        <v>7.6</v>
       </c>
       <c r="O103" t="n">
-        <v>9.92</v>
+        <v>9.94</v>
       </c>
       <c r="P103" t="n">
         <v>1.63</v>
       </c>
       <c r="Q103" t="n">
-        <v>57.48</v>
+        <v>57.65</v>
       </c>
       <c r="R103" t="n">
-        <v>-0.85</v>
+        <v>-0.63</v>
       </c>
       <c r="S103" t="n">
-        <v>-15.68</v>
+        <v>-15.48</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11799,7 +11791,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
@@ -11841,22 +11833,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>30.95</v>
+        <v>30.98</v>
       </c>
       <c r="D104" t="n">
         <v>53</v>
       </c>
       <c r="E104" t="n">
-        <v>-5.61</v>
+        <v>-5.54</v>
       </c>
       <c r="F104" t="n">
-        <v>8.859999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G104" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.38</v>
+        <v>-0.24</v>
       </c>
       <c r="I104" t="n">
         <v>0.42</v>
@@ -11868,28 +11860,28 @@
         <v>7.51</v>
       </c>
       <c r="L104" t="n">
-        <v>30.14</v>
+        <v>30.16</v>
       </c>
       <c r="M104" t="n">
-        <v>31.3</v>
+        <v>31.32</v>
       </c>
       <c r="N104" t="n">
-        <v>27.81</v>
+        <v>27.84</v>
       </c>
       <c r="O104" t="n">
-        <v>36.07</v>
+        <v>36.09</v>
       </c>
       <c r="P104" t="n">
         <v>1.63</v>
       </c>
       <c r="Q104" t="n">
-        <v>62.44</v>
+        <v>62.49</v>
       </c>
       <c r="R104" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S104" t="n">
-        <v>-14.9</v>
+        <v>-14.83</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11908,7 +11900,7 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
@@ -11950,25 +11942,25 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>126.74</v>
+        <v>126.71</v>
       </c>
       <c r="D105" t="n">
         <v>43</v>
       </c>
       <c r="E105" t="n">
-        <v>8.94</v>
+        <v>8.91</v>
       </c>
       <c r="F105" t="n">
-        <v>-9.529999999999999</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="G105" t="n">
-        <v>-18.09</v>
+        <v>-18.11</v>
       </c>
       <c r="H105" t="n">
-        <v>-18.77</v>
+        <v>-18.74</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="J105" t="n">
         <v>6.04</v>
@@ -11977,28 +11969,28 @@
         <v>4.77</v>
       </c>
       <c r="L105" t="n">
-        <v>124.62</v>
+        <v>124.59</v>
       </c>
       <c r="M105" t="n">
-        <v>127.64</v>
+        <v>127.61</v>
       </c>
       <c r="N105" t="n">
-        <v>118.58</v>
+        <v>118.55</v>
       </c>
       <c r="O105" t="n">
-        <v>140.03</v>
+        <v>140</v>
       </c>
       <c r="P105" t="n">
         <v>1.63</v>
       </c>
       <c r="Q105" t="n">
-        <v>37.57</v>
+        <v>37.55</v>
       </c>
       <c r="R105" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S105" t="n">
-        <v>-10.89</v>
+        <v>-10.92</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12017,7 +12009,7 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
@@ -12059,55 +12051,55 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6.03</v>
+        <v>5.99</v>
       </c>
       <c r="D106" t="n">
         <v>38</v>
       </c>
       <c r="E106" t="n">
-        <v>-5.71</v>
+        <v>-6.26</v>
       </c>
       <c r="F106" t="n">
-        <v>1.43</v>
+        <v>0.84</v>
       </c>
       <c r="G106" t="n">
-        <v>-13.43</v>
+        <v>-13.94</v>
       </c>
       <c r="H106" t="n">
-        <v>-7.81</v>
+        <v>-8.35</v>
       </c>
       <c r="I106" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="J106" t="n">
         <v>0.41</v>
       </c>
       <c r="K106" t="n">
-        <v>6.83</v>
+        <v>6.87</v>
       </c>
       <c r="L106" t="n">
-        <v>5.88</v>
+        <v>5.85</v>
       </c>
       <c r="M106" t="n">
-        <v>6.09</v>
+        <v>6.05</v>
       </c>
       <c r="N106" t="n">
-        <v>5.47</v>
+        <v>5.43</v>
       </c>
       <c r="O106" t="n">
-        <v>6.93</v>
+        <v>6.9</v>
       </c>
       <c r="P106" t="n">
         <v>1.63</v>
       </c>
       <c r="Q106" t="n">
-        <v>58.91</v>
+        <v>58.3</v>
       </c>
       <c r="R106" t="n">
-        <v>-0.51</v>
+        <v>-1.06</v>
       </c>
       <c r="S106" t="n">
-        <v>-10.74</v>
+        <v>-11.26</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12168,55 +12160,55 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>202.73</v>
+        <v>202.85</v>
       </c>
       <c r="D107" t="n">
         <v>37</v>
       </c>
       <c r="E107" t="n">
-        <v>8.529999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="F107" t="n">
-        <v>-2.38</v>
+        <v>-2.32</v>
       </c>
       <c r="G107" t="n">
-        <v>26.56</v>
+        <v>26.63</v>
       </c>
       <c r="H107" t="n">
-        <v>-11.62</v>
+        <v>-11.51</v>
       </c>
       <c r="I107" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="J107" t="n">
         <v>15.3</v>
       </c>
       <c r="K107" t="n">
-        <v>7.55</v>
+        <v>7.54</v>
       </c>
       <c r="L107" t="n">
-        <v>197.37</v>
+        <v>197.5</v>
       </c>
       <c r="M107" t="n">
-        <v>205.03</v>
+        <v>205.15</v>
       </c>
       <c r="N107" t="n">
-        <v>182.07</v>
+        <v>182.2</v>
       </c>
       <c r="O107" t="n">
-        <v>236.4</v>
+        <v>236.52</v>
       </c>
       <c r="P107" t="n">
         <v>1.63</v>
       </c>
       <c r="Q107" t="n">
-        <v>46.9</v>
+        <v>46.95</v>
       </c>
       <c r="R107" t="n">
-        <v>-3.92</v>
+        <v>-3.86</v>
       </c>
       <c r="S107" t="n">
-        <v>-21.69</v>
+        <v>-21.64</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12235,7 +12227,7 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
@@ -12277,22 +12269,22 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>156.28</v>
+        <v>156.08</v>
       </c>
       <c r="D108" t="n">
         <v>35</v>
       </c>
       <c r="E108" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.34</v>
+        <v>-0.47</v>
       </c>
       <c r="G108" t="n">
-        <v>9.699999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="H108" t="n">
-        <v>-9.58</v>
+        <v>-9.66</v>
       </c>
       <c r="I108" t="n">
         <v>0.38</v>
@@ -12301,31 +12293,31 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K108" t="n">
-        <v>6.21</v>
+        <v>6.22</v>
       </c>
       <c r="L108" t="n">
-        <v>152.88</v>
+        <v>152.68</v>
       </c>
       <c r="M108" t="n">
-        <v>157.74</v>
+        <v>157.54</v>
       </c>
       <c r="N108" t="n">
-        <v>143.18</v>
+        <v>142.98</v>
       </c>
       <c r="O108" t="n">
-        <v>177.63</v>
+        <v>177.43</v>
       </c>
       <c r="P108" t="n">
         <v>1.63</v>
       </c>
       <c r="Q108" t="n">
-        <v>56.97</v>
+        <v>56.78</v>
       </c>
       <c r="R108" t="n">
-        <v>-1.23</v>
+        <v>-1.35</v>
       </c>
       <c r="S108" t="n">
-        <v>-11.77</v>
+        <v>-11.88</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12344,7 +12336,7 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
@@ -12386,55 +12378,55 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>28.34</v>
+        <v>28.41</v>
       </c>
       <c r="D109" t="n">
         <v>31</v>
       </c>
       <c r="E109" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="F109" t="n">
-        <v>-14.64</v>
+        <v>-14.43</v>
       </c>
       <c r="G109" t="n">
-        <v>3.96</v>
+        <v>4.22</v>
       </c>
       <c r="H109" t="n">
-        <v>-23.88</v>
+        <v>-23.62</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="J109" t="n">
         <v>1.86</v>
       </c>
       <c r="K109" t="n">
-        <v>6.58</v>
+        <v>6.56</v>
       </c>
       <c r="L109" t="n">
-        <v>27.69</v>
+        <v>27.76</v>
       </c>
       <c r="M109" t="n">
-        <v>28.62</v>
+        <v>28.69</v>
       </c>
       <c r="N109" t="n">
-        <v>25.82</v>
+        <v>25.89</v>
       </c>
       <c r="O109" t="n">
-        <v>32.44</v>
+        <v>32.51</v>
       </c>
       <c r="P109" t="n">
         <v>1.63</v>
       </c>
       <c r="Q109" t="n">
-        <v>42.07</v>
+        <v>42.37</v>
       </c>
       <c r="R109" t="n">
-        <v>-7.2</v>
+        <v>-6.98</v>
       </c>
       <c r="S109" t="n">
-        <v>-19.47</v>
+        <v>-19.27</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12453,7 +12445,7 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
@@ -12495,55 +12487,55 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>21.77</v>
+        <v>21.74</v>
       </c>
       <c r="D110" t="n">
         <v>6</v>
       </c>
       <c r="E110" t="n">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="F110" t="n">
-        <v>-6.16</v>
+        <v>-6.31</v>
       </c>
       <c r="G110" t="n">
-        <v>-9.93</v>
+        <v>-10.07</v>
       </c>
       <c r="H110" t="n">
-        <v>-15.4</v>
+        <v>-15.5</v>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="J110" t="n">
         <v>1.36</v>
       </c>
       <c r="K110" t="n">
-        <v>6.23</v>
+        <v>6.24</v>
       </c>
       <c r="L110" t="n">
-        <v>21.3</v>
+        <v>21.26</v>
       </c>
       <c r="M110" t="n">
-        <v>21.97</v>
+        <v>21.94</v>
       </c>
       <c r="N110" t="n">
-        <v>19.94</v>
+        <v>19.9</v>
       </c>
       <c r="O110" t="n">
-        <v>24.75</v>
+        <v>24.72</v>
       </c>
       <c r="P110" t="n">
         <v>1.63</v>
       </c>
       <c r="Q110" t="n">
-        <v>34.95</v>
+        <v>34.81</v>
       </c>
       <c r="R110" t="n">
-        <v>-4.68</v>
+        <v>-4.82</v>
       </c>
       <c r="S110" t="n">
-        <v>-12.46</v>
+        <v>-12.61</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12562,7 +12554,7 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
@@ -12604,55 +12596,55 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>102.24</v>
+        <v>101.96</v>
       </c>
       <c r="D111" t="n">
         <v>6</v>
       </c>
       <c r="E111" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="F111" t="n">
-        <v>-22.03</v>
+        <v>-22.25</v>
       </c>
       <c r="G111" t="n">
-        <v>-12.82</v>
+        <v>-13.06</v>
       </c>
       <c r="H111" t="n">
-        <v>-31.27</v>
+        <v>-31.44</v>
       </c>
       <c r="I111" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="J111" t="n">
         <v>6.4</v>
       </c>
       <c r="K111" t="n">
-        <v>6.26</v>
+        <v>6.28</v>
       </c>
       <c r="L111" t="n">
-        <v>100</v>
+        <v>99.72</v>
       </c>
       <c r="M111" t="n">
-        <v>103.2</v>
+        <v>102.92</v>
       </c>
       <c r="N111" t="n">
-        <v>93.59999999999999</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="O111" t="n">
-        <v>116.33</v>
+        <v>116.05</v>
       </c>
       <c r="P111" t="n">
         <v>1.63</v>
       </c>
       <c r="Q111" t="n">
-        <v>33.79</v>
+        <v>33.63</v>
       </c>
       <c r="R111" t="n">
-        <v>-9.57</v>
+        <v>-9.81</v>
       </c>
       <c r="S111" t="n">
-        <v>-23.57</v>
+        <v>-23.78</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12671,7 +12663,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -12713,55 +12705,55 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>12.34</v>
+        <v>12.32</v>
       </c>
       <c r="D112" t="n">
         <v>45</v>
       </c>
       <c r="E112" t="n">
-        <v>-3.03</v>
+        <v>-3.14</v>
       </c>
       <c r="F112" t="n">
-        <v>9.84</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="G112" t="n">
-        <v>56.54</v>
+        <v>56.35</v>
       </c>
       <c r="H112" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I112" t="n">
         <v>0.6</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0.59</v>
       </c>
       <c r="J112" t="n">
         <v>1.03</v>
       </c>
       <c r="K112" t="n">
-        <v>8.359999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L112" t="n">
-        <v>11.97</v>
+        <v>11.96</v>
       </c>
       <c r="M112" t="n">
-        <v>12.49</v>
+        <v>12.47</v>
       </c>
       <c r="N112" t="n">
-        <v>10.94</v>
+        <v>10.93</v>
       </c>
       <c r="O112" t="n">
-        <v>14.6</v>
+        <v>14.59</v>
       </c>
       <c r="P112" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q112" t="n">
-        <v>61.71</v>
+        <v>61.63</v>
       </c>
       <c r="R112" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="S112" t="n">
-        <v>-10.62</v>
+        <v>-10.72</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12780,7 +12772,7 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>BTC-USD 1.27% · ETH-USD -6.22%</t>
+          <t>BTC-USD 1.28% · ETH-USD -6.22%</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
@@ -12806,7 +12798,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.27% · ETH-USD -6.22%; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
+          <t>Sector no acompaña: BTC-USD 1.28% · ETH-USD -6.22%; Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>
@@ -12822,55 +12814,55 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>165.94</v>
+        <v>165.5</v>
       </c>
       <c r="D113" t="n">
         <v>21</v>
       </c>
       <c r="E113" t="n">
-        <v>-10.02</v>
+        <v>-10.26</v>
       </c>
       <c r="F113" t="n">
-        <v>1.2</v>
+        <v>0.93</v>
       </c>
       <c r="G113" t="n">
-        <v>34.14</v>
+        <v>33.78</v>
       </c>
       <c r="H113" t="n">
-        <v>-8.039999999999999</v>
+        <v>-8.26</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="J113" t="n">
         <v>11.53</v>
       </c>
       <c r="K113" t="n">
-        <v>6.95</v>
+        <v>6.97</v>
       </c>
       <c r="L113" t="n">
-        <v>161.9</v>
+        <v>161.47</v>
       </c>
       <c r="M113" t="n">
-        <v>167.67</v>
+        <v>167.23</v>
       </c>
       <c r="N113" t="n">
-        <v>150.37</v>
+        <v>149.93</v>
       </c>
       <c r="O113" t="n">
-        <v>191.31</v>
+        <v>190.87</v>
       </c>
       <c r="P113" t="n">
         <v>1.63</v>
       </c>
       <c r="Q113" t="n">
-        <v>53.88</v>
+        <v>53.65</v>
       </c>
       <c r="R113" t="n">
-        <v>-6.22</v>
+        <v>-6.46</v>
       </c>
       <c r="S113" t="n">
-        <v>-15.77</v>
+        <v>-15.99</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12889,7 +12881,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>BTC-USD 1.27% · ETH-USD -6.22%</t>
+          <t>BTC-USD 1.28% · ETH-USD -6.22%</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -12915,7 +12907,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.27% · ETH-USD -6.22%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Sector no acompaña: BTC-USD 1.28% · ETH-USD -6.22%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -12931,25 +12923,25 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>194</v>
+        <v>194.13</v>
       </c>
       <c r="D114" t="n">
         <v>12</v>
       </c>
       <c r="E114" t="n">
-        <v>-6.57</v>
+        <v>-6.51</v>
       </c>
       <c r="F114" t="n">
-        <v>-1</v>
+        <v>-0.93</v>
       </c>
       <c r="G114" t="n">
-        <v>21.07</v>
+        <v>21.15</v>
       </c>
       <c r="H114" t="n">
-        <v>-10.24</v>
+        <v>-10.12</v>
       </c>
       <c r="I114" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="J114" t="n">
         <v>14.26</v>
@@ -12958,28 +12950,28 @@
         <v>7.35</v>
       </c>
       <c r="L114" t="n">
-        <v>189.01</v>
+        <v>189.14</v>
       </c>
       <c r="M114" t="n">
-        <v>196.14</v>
+        <v>196.27</v>
       </c>
       <c r="N114" t="n">
-        <v>174.75</v>
+        <v>174.88</v>
       </c>
       <c r="O114" t="n">
-        <v>225.38</v>
+        <v>225.51</v>
       </c>
       <c r="P114" t="n">
         <v>1.63</v>
       </c>
       <c r="Q114" t="n">
-        <v>55.71</v>
+        <v>55.76</v>
       </c>
       <c r="R114" t="n">
-        <v>-2.15</v>
+        <v>-2.09</v>
       </c>
       <c r="S114" t="n">
-        <v>-12.75</v>
+        <v>-12.69</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12998,7 +12990,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>BTC-USD 1.27% · ETH-USD -6.22%</t>
+          <t>BTC-USD 1.28% · ETH-USD -6.22%</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -13024,7 +13016,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.27% · ETH-USD -6.22%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Sector no acompaña: BTC-USD 1.28% · ETH-USD -6.22%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -13040,55 +13032,55 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>199.51</v>
+        <v>199.28</v>
       </c>
       <c r="D115" t="n">
         <v>53</v>
       </c>
       <c r="E115" t="n">
-        <v>-5.14</v>
+        <v>-5.24</v>
       </c>
       <c r="F115" t="n">
-        <v>47.17</v>
+        <v>47.01</v>
       </c>
       <c r="G115" t="n">
-        <v>43</v>
+        <v>42.84</v>
       </c>
       <c r="H115" t="n">
-        <v>37.93</v>
+        <v>37.82</v>
       </c>
       <c r="I115" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J115" t="n">
         <v>19.75</v>
       </c>
       <c r="K115" t="n">
-        <v>9.9</v>
+        <v>9.91</v>
       </c>
       <c r="L115" t="n">
-        <v>192.59</v>
+        <v>192.37</v>
       </c>
       <c r="M115" t="n">
-        <v>202.47</v>
+        <v>202.24</v>
       </c>
       <c r="N115" t="n">
-        <v>172.84</v>
+        <v>172.61</v>
       </c>
       <c r="O115" t="n">
-        <v>242.97</v>
+        <v>242.74</v>
       </c>
       <c r="P115" t="n">
         <v>1.63</v>
       </c>
       <c r="Q115" t="n">
-        <v>64.05</v>
+        <v>63.96</v>
       </c>
       <c r="R115" t="n">
-        <v>8.82</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="S115" t="n">
-        <v>-19.52</v>
+        <v>-19.61</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13107,7 +13099,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>SOXX 18.95% · QQQ 9.24%</t>
+          <t>SOXX 18.88% · QQQ 9.19%</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
@@ -13128,7 +13120,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.95% · QQQ 9.24%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 18.88% · QQQ 9.19%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -13149,55 +13141,55 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>212.71</v>
+        <v>212.44</v>
       </c>
       <c r="D116" t="n">
         <v>59</v>
       </c>
       <c r="E116" t="n">
-        <v>6.39</v>
+        <v>6.25</v>
       </c>
       <c r="F116" t="n">
-        <v>64.53</v>
+        <v>64.31</v>
       </c>
       <c r="G116" t="n">
-        <v>107.29</v>
+        <v>107.03</v>
       </c>
       <c r="H116" t="n">
-        <v>55.29</v>
+        <v>55.12</v>
       </c>
       <c r="I116" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="J116" t="n">
         <v>12.28</v>
       </c>
       <c r="K116" t="n">
-        <v>5.77</v>
+        <v>5.78</v>
       </c>
       <c r="L116" t="n">
-        <v>208.42</v>
+        <v>208.14</v>
       </c>
       <c r="M116" t="n">
-        <v>214.56</v>
+        <v>214.28</v>
       </c>
       <c r="N116" t="n">
-        <v>196.13</v>
+        <v>195.86</v>
       </c>
       <c r="O116" t="n">
-        <v>239.74</v>
+        <v>239.46</v>
       </c>
       <c r="P116" t="n">
         <v>1.63</v>
       </c>
       <c r="Q116" t="n">
-        <v>90.18000000000001</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="R116" t="n">
-        <v>27.94</v>
+        <v>27.78</v>
       </c>
       <c r="S116" t="n">
-        <v>-1.15</v>
+        <v>-1.28</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13216,7 +13208,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -13258,25 +13250,25 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>176.29</v>
+        <v>176.22</v>
       </c>
       <c r="D117" t="n">
         <v>59</v>
       </c>
       <c r="E117" t="n">
-        <v>20.61</v>
+        <v>20.56</v>
       </c>
       <c r="F117" t="n">
-        <v>26.27</v>
+        <v>26.22</v>
       </c>
       <c r="G117" t="n">
-        <v>23.04</v>
+        <v>22.99</v>
       </c>
       <c r="H117" t="n">
         <v>17.03</v>
       </c>
       <c r="I117" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="J117" t="n">
         <v>9.06</v>
@@ -13285,28 +13277,28 @@
         <v>5.14</v>
       </c>
       <c r="L117" t="n">
-        <v>173.12</v>
+        <v>173.05</v>
       </c>
       <c r="M117" t="n">
-        <v>177.65</v>
+        <v>177.58</v>
       </c>
       <c r="N117" t="n">
-        <v>164.06</v>
+        <v>163.99</v>
       </c>
       <c r="O117" t="n">
-        <v>196.23</v>
+        <v>196.16</v>
       </c>
       <c r="P117" t="n">
         <v>1.63</v>
       </c>
       <c r="Q117" t="n">
-        <v>79.84</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="R117" t="n">
-        <v>20.46</v>
+        <v>20.41</v>
       </c>
       <c r="S117" t="n">
-        <v>-3.65</v>
+        <v>-3.69</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13325,7 +13317,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -13367,22 +13359,22 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>242.49</v>
+        <v>242.69</v>
       </c>
       <c r="D118" t="n">
         <v>56</v>
       </c>
       <c r="E118" t="n">
-        <v>12.47</v>
+        <v>12.56</v>
       </c>
       <c r="F118" t="n">
-        <v>38.59</v>
+        <v>38.71</v>
       </c>
       <c r="G118" t="n">
-        <v>68.23</v>
+        <v>68.37</v>
       </c>
       <c r="H118" t="n">
-        <v>29.35</v>
+        <v>29.52</v>
       </c>
       <c r="I118" t="n">
         <v>0.99</v>
@@ -13391,31 +13383,31 @@
         <v>10.3</v>
       </c>
       <c r="K118" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="L118" t="n">
-        <v>238.88</v>
+        <v>239.09</v>
       </c>
       <c r="M118" t="n">
-        <v>244.03</v>
+        <v>244.23</v>
       </c>
       <c r="N118" t="n">
-        <v>228.58</v>
+        <v>228.79</v>
       </c>
       <c r="O118" t="n">
-        <v>265.14</v>
+        <v>265.35</v>
       </c>
       <c r="P118" t="n">
         <v>1.63</v>
       </c>
       <c r="Q118" t="n">
-        <v>89.43000000000001</v>
+        <v>89.67</v>
       </c>
       <c r="R118" t="n">
-        <v>20.53</v>
+        <v>20.63</v>
       </c>
       <c r="S118" t="n">
-        <v>-2.56</v>
+        <v>-2.48</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13434,7 +13426,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -13476,22 +13468,22 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>620.59</v>
+        <v>620.1900000000001</v>
       </c>
       <c r="D119" t="n">
         <v>56</v>
       </c>
       <c r="E119" t="n">
-        <v>13.62</v>
+        <v>13.55</v>
       </c>
       <c r="F119" t="n">
-        <v>38.03</v>
+        <v>37.94</v>
       </c>
       <c r="G119" t="n">
-        <v>77.14</v>
+        <v>77.03</v>
       </c>
       <c r="H119" t="n">
-        <v>28.79</v>
+        <v>28.75</v>
       </c>
       <c r="I119" t="n">
         <v>1.12</v>
@@ -13500,31 +13492,31 @@
         <v>24.91</v>
       </c>
       <c r="K119" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="L119" t="n">
-        <v>611.87</v>
+        <v>611.47</v>
       </c>
       <c r="M119" t="n">
-        <v>624.33</v>
+        <v>623.9299999999999</v>
       </c>
       <c r="N119" t="n">
-        <v>586.96</v>
+        <v>586.5599999999999</v>
       </c>
       <c r="O119" t="n">
-        <v>675.39</v>
+        <v>674.99</v>
       </c>
       <c r="P119" t="n">
         <v>1.63</v>
       </c>
       <c r="Q119" t="n">
-        <v>92.39</v>
+        <v>92.38</v>
       </c>
       <c r="R119" t="n">
-        <v>22.46</v>
+        <v>22.39</v>
       </c>
       <c r="S119" t="n">
-        <v>-2.15</v>
+        <v>-2.22</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13543,7 +13535,7 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
@@ -13585,55 +13577,55 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>172.07</v>
+        <v>171.59</v>
       </c>
       <c r="D120" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E120" t="n">
-        <v>13.22</v>
+        <v>12.9</v>
       </c>
       <c r="F120" t="n">
-        <v>14.07</v>
+        <v>13.76</v>
       </c>
       <c r="G120" t="n">
-        <v>9.18</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H120" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="I120" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="J120" t="n">
         <v>8.83</v>
       </c>
       <c r="K120" t="n">
-        <v>5.13</v>
+        <v>5.15</v>
       </c>
       <c r="L120" t="n">
-        <v>168.98</v>
+        <v>168.5</v>
       </c>
       <c r="M120" t="n">
-        <v>173.39</v>
+        <v>172.91</v>
       </c>
       <c r="N120" t="n">
-        <v>160.15</v>
+        <v>159.67</v>
       </c>
       <c r="O120" t="n">
-        <v>191.5</v>
+        <v>191.02</v>
       </c>
       <c r="P120" t="n">
         <v>1.63</v>
       </c>
       <c r="Q120" t="n">
-        <v>77.09</v>
+        <v>76.89</v>
       </c>
       <c r="R120" t="n">
-        <v>15.48</v>
+        <v>15.18</v>
       </c>
       <c r="S120" t="n">
-        <v>-2.77</v>
+        <v>-3.05</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13652,7 +13644,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -13694,55 +13686,55 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>48.94</v>
+        <v>48.81</v>
       </c>
       <c r="D121" t="n">
         <v>42</v>
       </c>
       <c r="E121" t="n">
-        <v>-12.4</v>
+        <v>-12.63</v>
       </c>
       <c r="F121" t="n">
-        <v>5.75</v>
+        <v>5.48</v>
       </c>
       <c r="G121" t="n">
-        <v>59</v>
+        <v>58.59</v>
       </c>
       <c r="H121" t="n">
-        <v>-3.49</v>
+        <v>-3.71</v>
       </c>
       <c r="I121" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="J121" t="n">
         <v>4.94</v>
       </c>
       <c r="K121" t="n">
-        <v>10.1</v>
+        <v>10.13</v>
       </c>
       <c r="L121" t="n">
-        <v>47.21</v>
+        <v>47.08</v>
       </c>
       <c r="M121" t="n">
-        <v>49.68</v>
+        <v>49.56</v>
       </c>
       <c r="N121" t="n">
-        <v>42.26</v>
+        <v>42.14</v>
       </c>
       <c r="O121" t="n">
-        <v>59.82</v>
+        <v>59.69</v>
       </c>
       <c r="P121" t="n">
         <v>1.63</v>
       </c>
       <c r="Q121" t="n">
-        <v>59.03</v>
+        <v>58.83</v>
       </c>
       <c r="R121" t="n">
-        <v>0.6</v>
+        <v>0.36</v>
       </c>
       <c r="S121" t="n">
-        <v>-17.26</v>
+        <v>-17.47</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13761,7 +13753,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -13803,22 +13795,22 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>18.48</v>
+        <v>18.4</v>
       </c>
       <c r="D122" t="n">
         <v>15</v>
       </c>
       <c r="E122" t="n">
-        <v>-17.34</v>
+        <v>-17.7</v>
       </c>
       <c r="F122" t="n">
-        <v>-9.26</v>
+        <v>-9.65</v>
       </c>
       <c r="G122" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="H122" t="n">
-        <v>-18.5</v>
+        <v>-18.84</v>
       </c>
       <c r="I122" t="n">
         <v>0.6</v>
@@ -13827,31 +13819,31 @@
         <v>1.95</v>
       </c>
       <c r="K122" t="n">
-        <v>10.54</v>
+        <v>10.59</v>
       </c>
       <c r="L122" t="n">
-        <v>17.79</v>
+        <v>17.71</v>
       </c>
       <c r="M122" t="n">
-        <v>18.77</v>
+        <v>18.69</v>
       </c>
       <c r="N122" t="n">
-        <v>15.85</v>
+        <v>15.77</v>
       </c>
       <c r="O122" t="n">
-        <v>22.76</v>
+        <v>22.68</v>
       </c>
       <c r="P122" t="n">
         <v>1.63</v>
       </c>
       <c r="Q122" t="n">
-        <v>50.63</v>
+        <v>50.38</v>
       </c>
       <c r="R122" t="n">
-        <v>-10.68</v>
+        <v>-11.05</v>
       </c>
       <c r="S122" t="n">
-        <v>-25.44</v>
+        <v>-25.77</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13870,7 +13862,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -13912,22 +13904,22 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>16.31</v>
+        <v>16.26</v>
       </c>
       <c r="D123" t="n">
         <v>15</v>
       </c>
       <c r="E123" t="n">
-        <v>-14.5</v>
+        <v>-14.74</v>
       </c>
       <c r="F123" t="n">
-        <v>-10.66</v>
+        <v>-10.9</v>
       </c>
       <c r="G123" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="H123" t="n">
-        <v>-19.9</v>
+        <v>-20.09</v>
       </c>
       <c r="I123" t="n">
         <v>0.58</v>
@@ -13936,31 +13928,31 @@
         <v>1.69</v>
       </c>
       <c r="K123" t="n">
-        <v>10.36</v>
+        <v>10.39</v>
       </c>
       <c r="L123" t="n">
-        <v>15.71</v>
+        <v>15.67</v>
       </c>
       <c r="M123" t="n">
-        <v>16.56</v>
+        <v>16.51</v>
       </c>
       <c r="N123" t="n">
-        <v>14.03</v>
+        <v>13.98</v>
       </c>
       <c r="O123" t="n">
-        <v>20.02</v>
+        <v>19.98</v>
       </c>
       <c r="P123" t="n">
         <v>1.63</v>
       </c>
       <c r="Q123" t="n">
-        <v>50.81</v>
+        <v>50.65</v>
       </c>
       <c r="R123" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="S123" t="n">
-        <v>-22.43</v>
+        <v>-22.65</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13979,7 +13971,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -14021,22 +14013,22 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>208.87</v>
+        <v>208.4</v>
       </c>
       <c r="D124" t="n">
         <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>16.31</v>
+        <v>16.05</v>
       </c>
       <c r="F124" t="n">
-        <v>-9.369999999999999</v>
+        <v>-9.57</v>
       </c>
       <c r="G124" t="n">
-        <v>-3.91</v>
+        <v>-4.12</v>
       </c>
       <c r="H124" t="n">
-        <v>-18.61</v>
+        <v>-18.76</v>
       </c>
       <c r="I124" t="n">
         <v>0.83</v>
@@ -14045,31 +14037,31 @@
         <v>19.19</v>
       </c>
       <c r="K124" t="n">
-        <v>9.19</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L124" t="n">
-        <v>202.15</v>
+        <v>201.68</v>
       </c>
       <c r="M124" t="n">
-        <v>211.74</v>
+        <v>211.28</v>
       </c>
       <c r="N124" t="n">
-        <v>182.96</v>
+        <v>182.49</v>
       </c>
       <c r="O124" t="n">
-        <v>251.09</v>
+        <v>250.62</v>
       </c>
       <c r="P124" t="n">
         <v>1.63</v>
       </c>
       <c r="Q124" t="n">
-        <v>43.73</v>
+        <v>43.56</v>
       </c>
       <c r="R124" t="n">
-        <v>-3.52</v>
+        <v>-3.72</v>
       </c>
       <c r="S124" t="n">
-        <v>-18.09</v>
+        <v>-18.27</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14088,7 +14080,7 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>QQQ 9.24% · ARKK -3.93% · SPY 4.5%</t>
+          <t>QQQ 9.19% · ARKK -4.01% · SPY 4.49%</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
@@ -14130,22 +14122,22 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>22.73</v>
+        <v>22.6</v>
       </c>
       <c r="D125" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E125" t="n">
-        <v>-7.27</v>
+        <v>-7.79</v>
       </c>
       <c r="F125" t="n">
-        <v>30.54</v>
+        <v>29.81</v>
       </c>
       <c r="G125" t="n">
-        <v>45.22</v>
+        <v>44.41</v>
       </c>
       <c r="H125" t="n">
-        <v>21.3</v>
+        <v>20.62</v>
       </c>
       <c r="I125" t="n">
         <v>0.54</v>
@@ -14154,31 +14146,31 @@
         <v>1.63</v>
       </c>
       <c r="K125" t="n">
-        <v>7.16</v>
+        <v>7.2</v>
       </c>
       <c r="L125" t="n">
-        <v>22.16</v>
+        <v>22.03</v>
       </c>
       <c r="M125" t="n">
-        <v>22.97</v>
+        <v>22.84</v>
       </c>
       <c r="N125" t="n">
-        <v>20.53</v>
+        <v>20.4</v>
       </c>
       <c r="O125" t="n">
-        <v>26.31</v>
+        <v>26.18</v>
       </c>
       <c r="P125" t="n">
         <v>1.63</v>
       </c>
       <c r="Q125" t="n">
-        <v>76.25</v>
+        <v>75.5</v>
       </c>
       <c r="R125" t="n">
-        <v>7.82</v>
+        <v>7.25</v>
       </c>
       <c r="S125" t="n">
-        <v>-12.11</v>
+        <v>-12.61</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14197,7 +14189,7 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>BTC-USD 1.27% · ETH-USD -6.22%</t>
+          <t>BTC-USD 1.28% · ETH-USD -6.22%</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
@@ -14218,12 +14210,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; Fuerte vs QQQ</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.27% · ETH-USD -6.22%; RSI sobrecomprado; Volumen bajo; Momentum negativo; Algo extendida sobre MA20</t>
+          <t>Sector no acompaña: BTC-USD 1.28% · ETH-USD -6.22%; RSI sobrecomprado; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -575,25 +575,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>499.48</v>
+        <v>499.33</v>
       </c>
       <c r="D2" t="n">
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="G2" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.49</v>
+        <v>-7.48</v>
       </c>
       <c r="I2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="J2" t="n">
         <v>5.02</v>
@@ -602,28 +602,28 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>497.72</v>
+        <v>497.57</v>
       </c>
       <c r="M2" t="n">
-        <v>500.23</v>
+        <v>500.08</v>
       </c>
       <c r="N2" t="n">
-        <v>492.71</v>
+        <v>492.56</v>
       </c>
       <c r="O2" t="n">
-        <v>510.52</v>
+        <v>510.37</v>
       </c>
       <c r="P2" t="n">
         <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>53.75</v>
+        <v>53.58</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.48</v>
+        <v>-0.51</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -684,40 +684,40 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42.2</v>
+        <v>42.17</v>
       </c>
       <c r="D3" t="n">
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="F3" t="n">
-        <v>7.9</v>
+        <v>7.82</v>
       </c>
       <c r="G3" t="n">
-        <v>18.48</v>
+        <v>18.4</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6</v>
+        <v>-0.64</v>
       </c>
       <c r="I3" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="J3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="K3" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="L3" t="n">
-        <v>41.79</v>
+        <v>41.76</v>
       </c>
       <c r="M3" t="n">
-        <v>42.37</v>
+        <v>42.35</v>
       </c>
       <c r="N3" t="n">
-        <v>40.63</v>
+        <v>40.58</v>
       </c>
       <c r="O3" t="n">
         <v>44.76</v>
@@ -726,13 +726,13 @@
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>49.49</v>
+        <v>49.34</v>
       </c>
       <c r="R3" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.19</v>
+        <v>-3.26</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>XLE 6.01% · CL=F 4.96%</t>
+          <t>XLE 5.61% · CL=F 5.07%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 6.01% · CL=F 4.96%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.61% · CL=F 5.07%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -797,55 +797,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>157.53</v>
+        <v>157.3</v>
       </c>
       <c r="D4" t="n">
         <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>4.64</v>
+        <v>4.49</v>
       </c>
       <c r="F4" t="n">
-        <v>6.09</v>
+        <v>5.93</v>
       </c>
       <c r="G4" t="n">
-        <v>6.26</v>
+        <v>6.11</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.41</v>
+        <v>-2.53</v>
       </c>
       <c r="I4" t="n">
         <v>0.59</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="K4" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="L4" t="n">
-        <v>156.02</v>
+        <v>155.79</v>
       </c>
       <c r="M4" t="n">
-        <v>158.18</v>
+        <v>157.95</v>
       </c>
       <c r="N4" t="n">
-        <v>151.72</v>
+        <v>151.46</v>
       </c>
       <c r="O4" t="n">
-        <v>167</v>
+        <v>166.83</v>
       </c>
       <c r="P4" t="n">
         <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="R4" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.76</v>
+        <v>-3.89</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>XLE 6.01% · CL=F 4.96%</t>
+          <t>XLE 5.61% · CL=F 5.07%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 6.01% · CL=F 4.96%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.61% · CL=F 5.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -910,55 +910,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>59.78</v>
+        <v>59.75</v>
       </c>
       <c r="D5" t="n">
         <v>96</v>
       </c>
       <c r="E5" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="F5" t="n">
-        <v>5.74</v>
+        <v>5.68</v>
       </c>
       <c r="G5" t="n">
-        <v>9.210000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.76</v>
+        <v>-2.78</v>
       </c>
       <c r="I5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="J5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="L5" t="n">
-        <v>59.3</v>
+        <v>59.27</v>
       </c>
       <c r="M5" t="n">
-        <v>59.99</v>
+        <v>59.96</v>
       </c>
       <c r="N5" t="n">
-        <v>57.93</v>
+        <v>57.89</v>
       </c>
       <c r="O5" t="n">
-        <v>62.81</v>
+        <v>62.79</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>50.55</v>
+        <v>50.41</v>
       </c>
       <c r="R5" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.1</v>
+        <v>-3.16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>XLE 6.01% · CL=F 4.96%</t>
+          <t>XLE 5.61% · CL=F 5.07%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 6.01% · CL=F 4.96%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.61% · CL=F 5.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1019,55 +1019,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>140.55</v>
+        <v>140.47</v>
       </c>
       <c r="D6" t="n">
         <v>96</v>
       </c>
       <c r="E6" t="n">
-        <v>4.16</v>
+        <v>4.11</v>
       </c>
       <c r="F6" t="n">
-        <v>5.67</v>
+        <v>5.61</v>
       </c>
       <c r="G6" t="n">
-        <v>14.5</v>
+        <v>14.44</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.83</v>
+        <v>-2.85</v>
       </c>
       <c r="I6" t="n">
         <v>0.48</v>
       </c>
       <c r="J6" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="L6" t="n">
-        <v>139.17</v>
+        <v>139.09</v>
       </c>
       <c r="M6" t="n">
-        <v>141.14</v>
+        <v>141.06</v>
       </c>
       <c r="N6" t="n">
-        <v>135.23</v>
+        <v>135.13</v>
       </c>
       <c r="O6" t="n">
-        <v>149.22</v>
+        <v>149.17</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>49.97</v>
+        <v>49.85</v>
       </c>
       <c r="R6" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.54</v>
+        <v>-3.59</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>XLE 6.01% · CL=F 4.96%</t>
+          <t>XLE 5.61% · CL=F 5.07%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 6.01% · CL=F 4.96%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.61% · CL=F 5.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1132,55 +1132,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>203.21</v>
+        <v>203.1</v>
       </c>
       <c r="D7" t="n">
         <v>96</v>
       </c>
       <c r="E7" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="F7" t="n">
-        <v>5.4</v>
+        <v>5.34</v>
       </c>
       <c r="G7" t="n">
-        <v>19.15</v>
+        <v>19.08</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.1</v>
+        <v>-3.12</v>
       </c>
       <c r="I7" t="n">
         <v>0.31</v>
       </c>
       <c r="J7" t="n">
-        <v>6.53</v>
+        <v>6.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="L7" t="n">
-        <v>200.93</v>
+        <v>200.81</v>
       </c>
       <c r="M7" t="n">
-        <v>204.19</v>
+        <v>204.09</v>
       </c>
       <c r="N7" t="n">
-        <v>194.4</v>
+        <v>194.26</v>
       </c>
       <c r="O7" t="n">
-        <v>217.58</v>
+        <v>217.52</v>
       </c>
       <c r="P7" t="n">
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>48.88</v>
+        <v>48.79</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.74</v>
+        <v>-4.8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>XLE 6.01% · CL=F 4.96%</t>
+          <t>XLE 5.61% · CL=F 5.07%</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 6.01% · CL=F 4.96%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.61% · CL=F 5.07%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1245,25 +1245,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>56.82</v>
+        <v>56.76</v>
       </c>
       <c r="D8" t="n">
         <v>96</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="F8" t="n">
-        <v>4.54</v>
+        <v>4.43</v>
       </c>
       <c r="G8" t="n">
-        <v>9.59</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.96</v>
+        <v>-4.03</v>
       </c>
       <c r="I8" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="J8" t="n">
         <v>1.41</v>
@@ -1272,28 +1272,28 @@
         <v>2.48</v>
       </c>
       <c r="L8" t="n">
-        <v>56.33</v>
+        <v>56.27</v>
       </c>
       <c r="M8" t="n">
-        <v>57.03</v>
+        <v>56.97</v>
       </c>
       <c r="N8" t="n">
-        <v>54.92</v>
+        <v>54.86</v>
       </c>
       <c r="O8" t="n">
-        <v>59.92</v>
+        <v>59.86</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>49.72</v>
+        <v>49.43</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.53</v>
+        <v>-1.63</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>XLE 6.01% · CL=F 4.96%</t>
+          <t>XLE 5.61% · CL=F 5.07%</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 6.01% · CL=F 4.96%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.61% · CL=F 5.07%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1358,22 +1358,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>515.84</v>
+        <v>516.39</v>
       </c>
       <c r="D9" t="n">
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.36</v>
+        <v>-2.25</v>
       </c>
       <c r="F9" t="n">
-        <v>19.47</v>
+        <v>19.6</v>
       </c>
       <c r="G9" t="n">
-        <v>42.57</v>
+        <v>42.72</v>
       </c>
       <c r="H9" t="n">
-        <v>10.97</v>
+        <v>11.14</v>
       </c>
       <c r="I9" t="n">
         <v>0.65</v>
@@ -1385,28 +1385,28 @@
         <v>4.21</v>
       </c>
       <c r="L9" t="n">
-        <v>508.24</v>
+        <v>508.79</v>
       </c>
       <c r="M9" t="n">
-        <v>519.1</v>
+        <v>519.65</v>
       </c>
       <c r="N9" t="n">
-        <v>486.52</v>
+        <v>487.07</v>
       </c>
       <c r="O9" t="n">
-        <v>563.62</v>
+        <v>564.17</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>64.12</v>
+        <v>64.22</v>
       </c>
       <c r="R9" t="n">
-        <v>5.68</v>
+        <v>5.79</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.35</v>
+        <v>-3.25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1471,55 +1471,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>192.43</v>
+        <v>192.3</v>
       </c>
       <c r="D10" t="n">
         <v>91</v>
       </c>
       <c r="E10" t="n">
-        <v>4.4</v>
+        <v>4.34</v>
       </c>
       <c r="F10" t="n">
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="G10" t="n">
-        <v>4.77</v>
+        <v>4.71</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.28</v>
+        <v>-4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="J10" t="n">
-        <v>4.52</v>
+        <v>4.54</v>
       </c>
       <c r="K10" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="L10" t="n">
-        <v>190.84</v>
+        <v>190.71</v>
       </c>
       <c r="M10" t="n">
-        <v>193.1</v>
+        <v>192.99</v>
       </c>
       <c r="N10" t="n">
-        <v>186.32</v>
+        <v>186.17</v>
       </c>
       <c r="O10" t="n">
-        <v>202.38</v>
+        <v>202.3</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>51.15</v>
+        <v>50.99</v>
       </c>
       <c r="R10" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.24</v>
+        <v>-3.3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>XLE 6.01% · CL=F 4.96%</t>
+          <t>XLE 5.61% · CL=F 5.07%</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 6.01% · CL=F 4.96%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.61% · CL=F 5.07%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>110.17</v>
+        <v>110.34</v>
       </c>
       <c r="D11" t="n">
         <v>83</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.79</v>
+        <v>-4.64</v>
       </c>
       <c r="F11" t="n">
-        <v>23.8</v>
+        <v>23.99</v>
       </c>
       <c r="G11" t="n">
-        <v>57.32</v>
+        <v>57.56</v>
       </c>
       <c r="H11" t="n">
-        <v>15.3</v>
+        <v>15.53</v>
       </c>
       <c r="I11" t="n">
         <v>0.26</v>
@@ -1608,31 +1608,31 @@
         <v>6.38</v>
       </c>
       <c r="K11" t="n">
-        <v>5.79</v>
+        <v>5.78</v>
       </c>
       <c r="L11" t="n">
-        <v>107.94</v>
+        <v>108.11</v>
       </c>
       <c r="M11" t="n">
-        <v>111.13</v>
+        <v>111.3</v>
       </c>
       <c r="N11" t="n">
-        <v>101.56</v>
+        <v>101.73</v>
       </c>
       <c r="O11" t="n">
-        <v>124.2</v>
+        <v>124.37</v>
       </c>
       <c r="P11" t="n">
         <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>58.89</v>
+        <v>59.03</v>
       </c>
       <c r="R11" t="n">
-        <v>5.49</v>
+        <v>5.65</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.5</v>
+        <v>-7.36</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1697,25 +1697,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1538.17</v>
+        <v>1539.05</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.74</v>
+        <v>-2.69</v>
       </c>
       <c r="F12" t="n">
-        <v>6.78</v>
+        <v>6.84</v>
       </c>
       <c r="G12" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.72</v>
+        <v>-1.62</v>
       </c>
       <c r="I12" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="J12" t="n">
         <v>70.26000000000001</v>
@@ -1724,28 +1724,28 @@
         <v>4.57</v>
       </c>
       <c r="L12" t="n">
-        <v>1513.58</v>
+        <v>1514.46</v>
       </c>
       <c r="M12" t="n">
-        <v>1548.71</v>
+        <v>1549.59</v>
       </c>
       <c r="N12" t="n">
-        <v>1443.32</v>
+        <v>1444.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1692.74</v>
+        <v>1693.62</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>57.59</v>
+        <v>57.65</v>
       </c>
       <c r="R12" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.07</v>
+        <v>-4.02</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1801,64 +1801,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>59.07</v>
+        <v>401.58</v>
       </c>
       <c r="D13" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E13" t="n">
-        <v>5.14</v>
+        <v>0.44</v>
       </c>
       <c r="F13" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="G13" t="n">
-        <v>14.24</v>
+        <v>4.4</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.96</v>
+        <v>-4.81</v>
       </c>
       <c r="I13" t="n">
-        <v>0.63</v>
+        <v>0.45</v>
       </c>
       <c r="J13" t="n">
-        <v>1.97</v>
+        <v>15.59</v>
       </c>
       <c r="K13" t="n">
-        <v>3.33</v>
+        <v>3.88</v>
       </c>
       <c r="L13" t="n">
-        <v>58.38</v>
+        <v>396.12</v>
       </c>
       <c r="M13" t="n">
-        <v>59.36</v>
+        <v>403.91</v>
       </c>
       <c r="N13" t="n">
-        <v>56.41</v>
+        <v>380.53</v>
       </c>
       <c r="O13" t="n">
-        <v>63.39</v>
+        <v>435.87</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>46.25</v>
+        <v>52.41</v>
       </c>
       <c r="R13" t="n">
-        <v>2.19</v>
+        <v>0.08</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.48</v>
+        <v>-4.83</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>XLE 6.01% · CL=F 4.96%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1902,19 +1902,19 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 6.01% · CL=F 4.96%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Volumen bajo; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1923,55 +1923,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>48.57</v>
+        <v>58.96</v>
       </c>
       <c r="D14" t="n">
         <v>77</v>
       </c>
       <c r="E14" t="n">
-        <v>3.56</v>
+        <v>4.95</v>
       </c>
       <c r="F14" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="G14" t="n">
-        <v>12.81</v>
+        <v>14.03</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.42</v>
+        <v>-5.11</v>
       </c>
       <c r="I14" t="n">
-        <v>0.47</v>
+        <v>0.65</v>
       </c>
       <c r="J14" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="K14" t="n">
-        <v>3.53</v>
+        <v>3.36</v>
       </c>
       <c r="L14" t="n">
-        <v>47.97</v>
+        <v>58.27</v>
       </c>
       <c r="M14" t="n">
-        <v>48.83</v>
+        <v>59.26</v>
       </c>
       <c r="N14" t="n">
-        <v>46.26</v>
+        <v>56.29</v>
       </c>
       <c r="O14" t="n">
-        <v>52.34</v>
+        <v>63.32</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>39.2</v>
+        <v>46</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.02</v>
+        <v>2.01</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.51</v>
+        <v>-3.66</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>XLE 6.01% · CL=F 4.96%</t>
+          <t>XLE 5.61% · CL=F 5.07%</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2015,19 +2015,19 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 6.01% · CL=F 4.96%; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.61% · CL=F 5.07%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Volumen bajo; Débil vs QQQ</t>
+          <t>Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2036,55 +2036,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>122.07</v>
+        <v>48.49</v>
       </c>
       <c r="D15" t="n">
         <v>77</v>
       </c>
       <c r="E15" t="n">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="F15" t="n">
-        <v>0.31</v>
+        <v>2.92</v>
       </c>
       <c r="G15" t="n">
-        <v>11.2</v>
+        <v>12.63</v>
       </c>
       <c r="H15" t="n">
-        <v>-8.19</v>
+        <v>-5.54</v>
       </c>
       <c r="I15" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="J15" t="n">
-        <v>3.27</v>
+        <v>1.72</v>
       </c>
       <c r="K15" t="n">
-        <v>2.68</v>
+        <v>3.56</v>
       </c>
       <c r="L15" t="n">
-        <v>120.93</v>
+        <v>47.89</v>
       </c>
       <c r="M15" t="n">
-        <v>122.56</v>
+        <v>48.75</v>
       </c>
       <c r="N15" t="n">
-        <v>117.66</v>
+        <v>46.17</v>
       </c>
       <c r="O15" t="n">
-        <v>129.26</v>
+        <v>52.29</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>45.56</v>
+        <v>38.97</v>
       </c>
       <c r="R15" t="n">
-        <v>0.95</v>
+        <v>-0.17</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.13</v>
+        <v>-6.65</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>XLE 6.01% · CL=F 4.96%</t>
+          <t>XLE 5.61% · CL=F 5.07%</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2128,76 +2128,76 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 6.01% · CL=F 4.96%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.61% · CL=F 5.07%; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>93.29000000000001</v>
+        <v>121.97</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.53</v>
+        <v>3.89</v>
       </c>
       <c r="F16" t="n">
-        <v>13.11</v>
+        <v>0.23</v>
       </c>
       <c r="G16" t="n">
-        <v>22.87</v>
+        <v>11.11</v>
       </c>
       <c r="H16" t="n">
-        <v>4.61</v>
+        <v>-8.23</v>
       </c>
       <c r="I16" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
-        <v>4.07</v>
+        <v>3.29</v>
       </c>
       <c r="K16" t="n">
-        <v>4.36</v>
+        <v>2.7</v>
       </c>
       <c r="L16" t="n">
-        <v>91.87</v>
+        <v>120.82</v>
       </c>
       <c r="M16" t="n">
-        <v>93.91</v>
+        <v>122.46</v>
       </c>
       <c r="N16" t="n">
-        <v>87.8</v>
+        <v>117.53</v>
       </c>
       <c r="O16" t="n">
-        <v>102.25</v>
+        <v>129.21</v>
       </c>
       <c r="P16" t="n">
         <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>50.83</v>
+        <v>45.41</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.16</v>
+        <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-11.91</v>
+        <v>-4.21</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>XLE 5.61% · CL=F 5.07%</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2241,76 +2241,76 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.61% · CL=F 5.07%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
+          <t>Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1807.48</v>
+        <v>93.36</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.16</v>
+        <v>-3.46</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.13</v>
+        <v>13.19</v>
       </c>
       <c r="G17" t="n">
-        <v>20.12</v>
+        <v>22.96</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.630000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="I17" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="J17" t="n">
-        <v>81.3</v>
+        <v>4.07</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="L17" t="n">
-        <v>1779.02</v>
+        <v>91.94</v>
       </c>
       <c r="M17" t="n">
-        <v>1819.68</v>
+        <v>93.97</v>
       </c>
       <c r="N17" t="n">
-        <v>1697.72</v>
+        <v>87.86</v>
       </c>
       <c r="O17" t="n">
-        <v>1986.34</v>
+        <v>102.32</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>54.53</v>
+        <v>50.96</v>
       </c>
       <c r="R17" t="n">
-        <v>0.09</v>
+        <v>-1.09</v>
       </c>
       <c r="S17" t="n">
-        <v>-6.68</v>
+        <v>-11.85</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2337,7 +2337,11 @@
           <t>BAJO</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -2350,19 +2354,19 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2371,55 +2375,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>421.77</v>
+        <v>1806.88</v>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.4</v>
+        <v>-2.19</v>
       </c>
       <c r="F18" t="n">
-        <v>4.53</v>
+        <v>-0.16</v>
       </c>
       <c r="G18" t="n">
-        <v>11.6</v>
+        <v>20.08</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.97</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="J18" t="n">
-        <v>20.58</v>
+        <v>81.3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.88</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>414.57</v>
+        <v>1778.42</v>
       </c>
       <c r="M18" t="n">
-        <v>424.86</v>
+        <v>1819.07</v>
       </c>
       <c r="N18" t="n">
-        <v>393.99</v>
+        <v>1697.12</v>
       </c>
       <c r="O18" t="n">
-        <v>467.04</v>
+        <v>1985.74</v>
       </c>
       <c r="P18" t="n">
         <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>58.21</v>
+        <v>54.49</v>
       </c>
       <c r="R18" t="n">
-        <v>1.87</v>
+        <v>0.06</v>
       </c>
       <c r="S18" t="n">
-        <v>-5.95</v>
+        <v>-6.71</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2438,7 +2442,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2459,76 +2463,76 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>401.23</v>
+        <v>421.82</v>
       </c>
       <c r="D19" t="n">
         <v>74</v>
       </c>
       <c r="E19" t="n">
-        <v>0.36</v>
+        <v>-3.39</v>
       </c>
       <c r="F19" t="n">
-        <v>3.56</v>
+        <v>4.55</v>
       </c>
       <c r="G19" t="n">
-        <v>4.31</v>
+        <v>11.61</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.94</v>
+        <v>-3.91</v>
       </c>
       <c r="I19" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="J19" t="n">
-        <v>15.59</v>
+        <v>20.58</v>
       </c>
       <c r="K19" t="n">
-        <v>3.89</v>
+        <v>4.88</v>
       </c>
       <c r="L19" t="n">
-        <v>395.77</v>
+        <v>414.62</v>
       </c>
       <c r="M19" t="n">
-        <v>403.57</v>
+        <v>424.91</v>
       </c>
       <c r="N19" t="n">
-        <v>380.18</v>
+        <v>394.04</v>
       </c>
       <c r="O19" t="n">
-        <v>435.53</v>
+        <v>467.09</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>52.26</v>
+        <v>58.22</v>
       </c>
       <c r="R19" t="n">
-        <v>-0</v>
+        <v>1.88</v>
       </c>
       <c r="S19" t="n">
-        <v>-4.92</v>
+        <v>-5.94</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2547,7 +2551,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2568,12 +2572,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -2589,25 +2593,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>107.36</v>
+        <v>107.26</v>
       </c>
       <c r="D20" t="n">
         <v>96</v>
       </c>
       <c r="E20" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="F20" t="n">
-        <v>8.51</v>
+        <v>8.41</v>
       </c>
       <c r="G20" t="n">
-        <v>11.89</v>
+        <v>11.8</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="I20" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="J20" t="n">
         <v>2.48</v>
@@ -2616,28 +2620,28 @@
         <v>2.31</v>
       </c>
       <c r="L20" t="n">
-        <v>106.49</v>
+        <v>106.4</v>
       </c>
       <c r="M20" t="n">
-        <v>107.73</v>
+        <v>107.64</v>
       </c>
       <c r="N20" t="n">
-        <v>104.02</v>
+        <v>103.92</v>
       </c>
       <c r="O20" t="n">
-        <v>112.81</v>
+        <v>112.71</v>
       </c>
       <c r="P20" t="n">
         <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>62</v>
+        <v>61.66</v>
       </c>
       <c r="R20" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.82</v>
+        <v>-0.91</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2666,7 +2670,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2702,22 +2706,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>331.48</v>
+        <v>331.43</v>
       </c>
       <c r="D21" t="n">
         <v>96</v>
       </c>
       <c r="E21" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="F21" t="n">
-        <v>6.71</v>
+        <v>6.69</v>
       </c>
       <c r="G21" t="n">
-        <v>8.119999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.79</v>
+        <v>-1.77</v>
       </c>
       <c r="I21" t="n">
         <v>0.45</v>
@@ -2729,28 +2733,28 @@
         <v>1.84</v>
       </c>
       <c r="L21" t="n">
-        <v>329.34</v>
+        <v>329.3</v>
       </c>
       <c r="M21" t="n">
-        <v>332.39</v>
+        <v>332.34</v>
       </c>
       <c r="N21" t="n">
-        <v>323.25</v>
+        <v>323.21</v>
       </c>
       <c r="O21" t="n">
-        <v>344.87</v>
+        <v>344.83</v>
       </c>
       <c r="P21" t="n">
         <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>52.47</v>
+        <v>52.42</v>
       </c>
       <c r="R21" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.87</v>
+        <v>-2.88</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2815,22 +2819,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>972.91</v>
+        <v>972.3099999999999</v>
       </c>
       <c r="D22" t="n">
         <v>96</v>
       </c>
       <c r="E22" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="F22" t="n">
-        <v>4.07</v>
+        <v>4.01</v>
       </c>
       <c r="G22" t="n">
-        <v>8.4</v>
+        <v>8.33</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.43</v>
+        <v>-4.45</v>
       </c>
       <c r="I22" t="n">
         <v>0.93</v>
@@ -2842,28 +2846,28 @@
         <v>2.56</v>
       </c>
       <c r="L22" t="n">
-        <v>964.21</v>
+        <v>963.61</v>
       </c>
       <c r="M22" t="n">
-        <v>976.64</v>
+        <v>976.04</v>
       </c>
       <c r="N22" t="n">
-        <v>939.34</v>
+        <v>938.74</v>
       </c>
       <c r="O22" t="n">
-        <v>1027.61</v>
+        <v>1027.01</v>
       </c>
       <c r="P22" t="n">
         <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>62.7</v>
+        <v>62.58</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.29</v>
+        <v>-0.35</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2912,7 +2916,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Débil vs QQQ</t>
+          <t>MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -2928,25 +2932,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>197.24</v>
+        <v>196.91</v>
       </c>
       <c r="D23" t="n">
         <v>95</v>
       </c>
       <c r="E23" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="F23" t="n">
-        <v>3.79</v>
+        <v>3.62</v>
       </c>
       <c r="G23" t="n">
-        <v>17.48</v>
+        <v>17.29</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.71</v>
+        <v>-4.84</v>
       </c>
       <c r="I23" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="J23" t="n">
         <v>4.45</v>
@@ -2955,28 +2959,28 @@
         <v>2.26</v>
       </c>
       <c r="L23" t="n">
-        <v>195.68</v>
+        <v>195.36</v>
       </c>
       <c r="M23" t="n">
-        <v>197.91</v>
+        <v>197.58</v>
       </c>
       <c r="N23" t="n">
-        <v>191.23</v>
+        <v>190.91</v>
       </c>
       <c r="O23" t="n">
-        <v>207.03</v>
+        <v>206.7</v>
       </c>
       <c r="P23" t="n">
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>60.26</v>
+        <v>59.86</v>
       </c>
       <c r="R23" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.34</v>
+        <v>-0.51</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3041,22 +3045,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>298.25</v>
+        <v>298.62</v>
       </c>
       <c r="D24" t="n">
         <v>85</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="F24" t="n">
-        <v>7.95</v>
+        <v>8.08</v>
       </c>
       <c r="G24" t="n">
-        <v>-13.59</v>
+        <v>-13.48</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.55</v>
+        <v>-0.38</v>
       </c>
       <c r="I24" t="n">
         <v>0.55</v>
@@ -3065,31 +3069,31 @@
         <v>9.57</v>
       </c>
       <c r="K24" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="L24" t="n">
-        <v>294.9</v>
+        <v>295.27</v>
       </c>
       <c r="M24" t="n">
-        <v>299.69</v>
+        <v>300.06</v>
       </c>
       <c r="N24" t="n">
-        <v>285.33</v>
+        <v>285.7</v>
       </c>
       <c r="O24" t="n">
-        <v>319.3</v>
+        <v>319.68</v>
       </c>
       <c r="P24" t="n">
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>54.93</v>
+        <v>55.13</v>
       </c>
       <c r="R24" t="n">
-        <v>2.68</v>
+        <v>2.81</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.79</v>
+        <v>-3.67</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3154,25 +3158,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>384.79</v>
+        <v>385.25</v>
       </c>
       <c r="D25" t="n">
         <v>84</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.43</v>
+        <v>-4.31</v>
       </c>
       <c r="F25" t="n">
-        <v>13.4</v>
+        <v>13.54</v>
       </c>
       <c r="G25" t="n">
-        <v>23.85</v>
+        <v>24</v>
       </c>
       <c r="H25" t="n">
-        <v>4.9</v>
+        <v>5.08</v>
       </c>
       <c r="I25" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="J25" t="n">
         <v>9.81</v>
@@ -3181,28 +3185,28 @@
         <v>2.55</v>
       </c>
       <c r="L25" t="n">
-        <v>381.36</v>
+        <v>381.82</v>
       </c>
       <c r="M25" t="n">
-        <v>386.26</v>
+        <v>386.72</v>
       </c>
       <c r="N25" t="n">
-        <v>371.55</v>
+        <v>372.01</v>
       </c>
       <c r="O25" t="n">
-        <v>406.37</v>
+        <v>406.83</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>49.99</v>
+        <v>50.33</v>
       </c>
       <c r="R25" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.83</v>
+        <v>-5.72</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3221,7 +3225,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3267,19 +3271,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>212.62</v>
+        <v>212.52</v>
       </c>
       <c r="D26" t="n">
         <v>82</v>
       </c>
       <c r="E26" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="F26" t="n">
-        <v>6.04</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.15</v>
+        <v>-6.2</v>
       </c>
       <c r="H26" t="n">
         <v>-2.46</v>
@@ -3294,28 +3298,28 @@
         <v>2.23</v>
       </c>
       <c r="L26" t="n">
-        <v>210.96</v>
+        <v>210.86</v>
       </c>
       <c r="M26" t="n">
-        <v>213.33</v>
+        <v>213.23</v>
       </c>
       <c r="N26" t="n">
-        <v>206.21</v>
+        <v>206.11</v>
       </c>
       <c r="O26" t="n">
-        <v>223.06</v>
+        <v>222.96</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>52.24</v>
+        <v>52.06</v>
       </c>
       <c r="R26" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.47</v>
+        <v>-1.52</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3380,55 +3384,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>131.87</v>
+        <v>131.51</v>
       </c>
       <c r="D27" t="n">
         <v>96</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="F27" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="G27" t="n">
-        <v>4.45</v>
+        <v>4.17</v>
       </c>
       <c r="H27" t="n">
-        <v>-6.85</v>
+        <v>-7.09</v>
       </c>
       <c r="I27" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="J27" t="n">
         <v>2.59</v>
       </c>
       <c r="K27" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="L27" t="n">
-        <v>130.96</v>
+        <v>130.61</v>
       </c>
       <c r="M27" t="n">
-        <v>132.26</v>
+        <v>131.9</v>
       </c>
       <c r="N27" t="n">
-        <v>128.38</v>
+        <v>128.02</v>
       </c>
       <c r="O27" t="n">
-        <v>137.56</v>
+        <v>137.21</v>
       </c>
       <c r="P27" t="n">
         <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>50.56</v>
+        <v>49.53</v>
       </c>
       <c r="R27" t="n">
-        <v>1.03</v>
+        <v>0.77</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.43</v>
+        <v>-2.7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3489,25 +3493,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>288.02</v>
+        <v>287.9</v>
       </c>
       <c r="D28" t="n">
         <v>90</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.51</v>
+        <v>-2.55</v>
       </c>
       <c r="F28" t="n">
-        <v>8.460000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="G28" t="n">
-        <v>18.06</v>
+        <v>18.01</v>
       </c>
       <c r="H28" t="n">
         <v>-0.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="J28" t="n">
         <v>15.26</v>
@@ -3516,28 +3520,28 @@
         <v>5.3</v>
       </c>
       <c r="L28" t="n">
-        <v>282.68</v>
+        <v>282.56</v>
       </c>
       <c r="M28" t="n">
-        <v>290.31</v>
+        <v>290.19</v>
       </c>
       <c r="N28" t="n">
-        <v>267.41</v>
+        <v>267.29</v>
       </c>
       <c r="O28" t="n">
-        <v>321.6</v>
+        <v>321.48</v>
       </c>
       <c r="P28" t="n">
         <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>62.68</v>
+        <v>62.65</v>
       </c>
       <c r="R28" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="S28" t="n">
-        <v>-4.63</v>
+        <v>-4.67</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3598,22 +3602,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>113.39</v>
+        <v>113.32</v>
       </c>
       <c r="D29" t="n">
         <v>89</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="F29" t="n">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="G29" t="n">
-        <v>-7.83</v>
+        <v>-7.88</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.06</v>
+        <v>-8.07</v>
       </c>
       <c r="I29" t="n">
         <v>0.42</v>
@@ -3625,28 +3629,28 @@
         <v>2.21</v>
       </c>
       <c r="L29" t="n">
-        <v>112.51</v>
+        <v>112.45</v>
       </c>
       <c r="M29" t="n">
-        <v>113.77</v>
+        <v>113.7</v>
       </c>
       <c r="N29" t="n">
-        <v>110.01</v>
+        <v>109.95</v>
       </c>
       <c r="O29" t="n">
-        <v>118.89</v>
+        <v>118.83</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>64.41</v>
+        <v>64.12</v>
       </c>
       <c r="R29" t="n">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.49</v>
+        <v>-1.54</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3707,22 +3711,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>230.07</v>
+        <v>229.95</v>
       </c>
       <c r="D30" t="n">
         <v>85</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.15</v>
+        <v>-0.2</v>
       </c>
       <c r="F30" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="G30" t="n">
-        <v>-6.58</v>
+        <v>-6.63</v>
       </c>
       <c r="H30" t="n">
-        <v>-6.74</v>
+        <v>-6.76</v>
       </c>
       <c r="I30" t="n">
         <v>0.28</v>
@@ -3734,28 +3738,28 @@
         <v>1.62</v>
       </c>
       <c r="L30" t="n">
-        <v>228.77</v>
+        <v>228.65</v>
       </c>
       <c r="M30" t="n">
-        <v>230.63</v>
+        <v>230.51</v>
       </c>
       <c r="N30" t="n">
-        <v>225.04</v>
+        <v>224.92</v>
       </c>
       <c r="O30" t="n">
-        <v>238.27</v>
+        <v>238.14</v>
       </c>
       <c r="P30" t="n">
         <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.39</v>
+        <v>50.18</v>
       </c>
       <c r="R30" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.89</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3816,55 +3820,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>84.43000000000001</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="D31" t="n">
         <v>84</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.82</v>
+        <v>-0.74</v>
       </c>
       <c r="F31" t="n">
-        <v>8.08</v>
+        <v>8.17</v>
       </c>
       <c r="G31" t="n">
-        <v>17.51</v>
+        <v>17.6</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.42</v>
+        <v>-0.29</v>
       </c>
       <c r="I31" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="J31" t="n">
         <v>2.67</v>
       </c>
       <c r="K31" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="L31" t="n">
-        <v>83.48999999999999</v>
+        <v>83.55</v>
       </c>
       <c r="M31" t="n">
-        <v>84.83</v>
+        <v>84.89</v>
       </c>
       <c r="N31" t="n">
-        <v>80.81999999999999</v>
+        <v>80.88</v>
       </c>
       <c r="O31" t="n">
-        <v>90.31</v>
+        <v>90.37</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>61.25</v>
+        <v>61.37</v>
       </c>
       <c r="R31" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S31" t="n">
-        <v>-4.54</v>
+        <v>-4.47</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3925,25 +3929,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>382.62</v>
+        <v>382.92</v>
       </c>
       <c r="D32" t="n">
         <v>77</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.62</v>
+        <v>-4.55</v>
       </c>
       <c r="F32" t="n">
-        <v>8.23</v>
+        <v>8.32</v>
       </c>
       <c r="G32" t="n">
-        <v>40.76</v>
+        <v>40.86</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.27</v>
+        <v>-0.14</v>
       </c>
       <c r="I32" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="J32" t="n">
         <v>9.1</v>
@@ -3952,28 +3956,28 @@
         <v>2.38</v>
       </c>
       <c r="L32" t="n">
-        <v>379.44</v>
+        <v>379.74</v>
       </c>
       <c r="M32" t="n">
-        <v>383.99</v>
+        <v>384.29</v>
       </c>
       <c r="N32" t="n">
-        <v>370.34</v>
+        <v>370.64</v>
       </c>
       <c r="O32" t="n">
-        <v>402.64</v>
+        <v>402.93</v>
       </c>
       <c r="P32" t="n">
         <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>59.15</v>
+        <v>59.41</v>
       </c>
       <c r="R32" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="S32" t="n">
-        <v>-5.33</v>
+        <v>-5.25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4025,64 +4029,64 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ETF Russell</t>
+          <t>ETF Salud</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>278.96</v>
+        <v>146.87</v>
       </c>
       <c r="D33" t="n">
         <v>74</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.31</v>
+        <v>0.11</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9</v>
+        <v>0.33</v>
       </c>
       <c r="G33" t="n">
-        <v>6.13</v>
+        <v>-6.59</v>
       </c>
       <c r="H33" t="n">
-        <v>-7.6</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J33" t="n">
-        <v>4.89</v>
+        <v>1.89</v>
       </c>
       <c r="K33" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="L33" t="n">
-        <v>277.25</v>
+        <v>146.2</v>
       </c>
       <c r="M33" t="n">
-        <v>279.7</v>
+        <v>147.15</v>
       </c>
       <c r="N33" t="n">
-        <v>272.36</v>
+        <v>144.32</v>
       </c>
       <c r="O33" t="n">
-        <v>289.73</v>
+        <v>151.02</v>
       </c>
       <c r="P33" t="n">
         <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>51.2</v>
+        <v>53.57</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.13</v>
+        <v>1.2</v>
       </c>
       <c r="S33" t="n">
-        <v>-3</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4122,76 +4126,76 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; MA20 sobre MA50; Tendencia larga positiva; RSI saludable; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; RSI saludable; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Débil vs QQQ</t>
+          <t>Tendencia larga débil; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ETF Salud</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>146.89</v>
+        <v>308.07</v>
       </c>
       <c r="D34" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="E34" t="n">
-        <v>0.12</v>
+        <v>3.24</v>
       </c>
       <c r="F34" t="n">
-        <v>0.35</v>
+        <v>36.46</v>
       </c>
       <c r="G34" t="n">
-        <v>-6.57</v>
+        <v>31.98</v>
       </c>
       <c r="H34" t="n">
-        <v>-8.15</v>
+        <v>28</v>
       </c>
       <c r="I34" t="n">
-        <v>0.84</v>
+        <v>0.33</v>
       </c>
       <c r="J34" t="n">
-        <v>1.89</v>
+        <v>11.46</v>
       </c>
       <c r="K34" t="n">
-        <v>1.29</v>
+        <v>3.72</v>
       </c>
       <c r="L34" t="n">
-        <v>146.23</v>
+        <v>304.05</v>
       </c>
       <c r="M34" t="n">
-        <v>147.17</v>
+        <v>309.78</v>
       </c>
       <c r="N34" t="n">
-        <v>144.34</v>
+        <v>292.59</v>
       </c>
       <c r="O34" t="n">
-        <v>151.04</v>
+        <v>333.28</v>
       </c>
       <c r="P34" t="n">
         <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>53.68</v>
+        <v>58.28</v>
       </c>
       <c r="R34" t="n">
-        <v>1.21</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.8</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4205,20 +4209,24 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO +</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
       <c r="Z34" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -4231,19 +4239,19 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; RSI saludable; MACD positivo; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4252,55 +4260,55 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>307.35</v>
+        <v>185.07</v>
       </c>
       <c r="D35" t="n">
         <v>96</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>36.15</v>
+        <v>17.64</v>
       </c>
       <c r="G35" t="n">
-        <v>31.67</v>
+        <v>136.21</v>
       </c>
       <c r="H35" t="n">
-        <v>27.65</v>
+        <v>9.18</v>
       </c>
       <c r="I35" t="n">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="J35" t="n">
-        <v>11.42</v>
+        <v>12.56</v>
       </c>
       <c r="K35" t="n">
-        <v>3.72</v>
+        <v>6.79</v>
       </c>
       <c r="L35" t="n">
-        <v>303.35</v>
+        <v>180.67</v>
       </c>
       <c r="M35" t="n">
-        <v>309.06</v>
+        <v>186.95</v>
       </c>
       <c r="N35" t="n">
-        <v>291.93</v>
+        <v>168.11</v>
       </c>
       <c r="O35" t="n">
-        <v>332.47</v>
+        <v>212.71</v>
       </c>
       <c r="P35" t="n">
         <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>57.93</v>
+        <v>61.43</v>
       </c>
       <c r="R35" t="n">
-        <v>8.23</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.11</v>
+        <v>-4.27</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4319,7 +4327,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4344,76 +4352,76 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Algo extendida sobre MA20</t>
+          <t>MACD sin confirmar; Algo extendida sobre MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>184.94</v>
+        <v>224.36</v>
       </c>
       <c r="D36" t="n">
         <v>96</v>
       </c>
       <c r="E36" t="n">
-        <v>3.93</v>
+        <v>-0.65</v>
       </c>
       <c r="F36" t="n">
-        <v>17.56</v>
+        <v>10.8</v>
       </c>
       <c r="G36" t="n">
-        <v>136.04</v>
+        <v>16.35</v>
       </c>
       <c r="H36" t="n">
-        <v>9.06</v>
+        <v>2.34</v>
       </c>
       <c r="I36" t="n">
-        <v>0.83</v>
+        <v>0.57</v>
       </c>
       <c r="J36" t="n">
-        <v>12.56</v>
+        <v>8.09</v>
       </c>
       <c r="K36" t="n">
-        <v>6.79</v>
+        <v>3.6</v>
       </c>
       <c r="L36" t="n">
-        <v>180.54</v>
+        <v>221.53</v>
       </c>
       <c r="M36" t="n">
-        <v>186.82</v>
+        <v>225.57</v>
       </c>
       <c r="N36" t="n">
-        <v>167.98</v>
+        <v>213.44</v>
       </c>
       <c r="O36" t="n">
-        <v>212.58</v>
+        <v>242.15</v>
       </c>
       <c r="P36" t="n">
         <v>1.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>61.37</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="R36" t="n">
-        <v>9.9</v>
+        <v>5.11</v>
       </c>
       <c r="S36" t="n">
-        <v>-4.33</v>
+        <v>-5.15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4432,7 +4440,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4457,76 +4465,76 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Algo extendida sobre MA20; Volatilidad alta</t>
+          <t>RSI algo alto; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>224.41</v>
+        <v>300.54</v>
       </c>
       <c r="D37" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.63</v>
+        <v>-1.89</v>
       </c>
       <c r="F37" t="n">
-        <v>10.82</v>
+        <v>27.83</v>
       </c>
       <c r="G37" t="n">
-        <v>16.37</v>
+        <v>41.58</v>
       </c>
       <c r="H37" t="n">
-        <v>2.32</v>
+        <v>19.37</v>
       </c>
       <c r="I37" t="n">
-        <v>0.57</v>
+        <v>0.37</v>
       </c>
       <c r="J37" t="n">
-        <v>8.09</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="L37" t="n">
-        <v>221.58</v>
+        <v>297.18</v>
       </c>
       <c r="M37" t="n">
-        <v>225.62</v>
+        <v>301.98</v>
       </c>
       <c r="N37" t="n">
-        <v>213.49</v>
+        <v>287.57</v>
       </c>
       <c r="O37" t="n">
-        <v>242.2</v>
+        <v>321.68</v>
       </c>
       <c r="P37" t="n">
         <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>70.26000000000001</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="R37" t="n">
-        <v>5.14</v>
+        <v>4.5</v>
       </c>
       <c r="S37" t="n">
-        <v>-5.13</v>
+        <v>-3.14</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4545,7 +4553,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4570,76 +4578,76 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>RSI algo alto; Volumen bajo</t>
+          <t>RSI algo alto; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>300.42</v>
+        <v>560.97</v>
       </c>
       <c r="D38" t="n">
         <v>87</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.93</v>
+        <v>-2.01</v>
       </c>
       <c r="F38" t="n">
-        <v>27.78</v>
+        <v>17.65</v>
       </c>
       <c r="G38" t="n">
-        <v>41.53</v>
+        <v>33.83</v>
       </c>
       <c r="H38" t="n">
-        <v>19.28</v>
+        <v>9.19</v>
       </c>
       <c r="I38" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
-        <v>9.609999999999999</v>
+        <v>20.4</v>
       </c>
       <c r="K38" t="n">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="L38" t="n">
-        <v>297.06</v>
+        <v>553.84</v>
       </c>
       <c r="M38" t="n">
-        <v>301.87</v>
+        <v>564.03</v>
       </c>
       <c r="N38" t="n">
-        <v>287.45</v>
+        <v>533.4400000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>321.56</v>
+        <v>605.84</v>
       </c>
       <c r="P38" t="n">
         <v>1.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>69.36</v>
+        <v>65.2</v>
       </c>
       <c r="R38" t="n">
-        <v>4.46</v>
+        <v>5.02</v>
       </c>
       <c r="S38" t="n">
-        <v>-3.18</v>
+        <v>-3.47</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4658,7 +4666,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -4683,7 +4691,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4695,64 +4703,64 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>560.49</v>
+        <v>33.76</v>
       </c>
       <c r="D39" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.09</v>
+        <v>5.52</v>
       </c>
       <c r="F39" t="n">
-        <v>17.55</v>
+        <v>15.71</v>
       </c>
       <c r="G39" t="n">
-        <v>33.72</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>9.050000000000001</v>
+        <v>7.25</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
-        <v>20.4</v>
+        <v>2.47</v>
       </c>
       <c r="K39" t="n">
-        <v>3.64</v>
+        <v>7.33</v>
       </c>
       <c r="L39" t="n">
-        <v>553.35</v>
+        <v>32.9</v>
       </c>
       <c r="M39" t="n">
-        <v>563.55</v>
+        <v>34.14</v>
       </c>
       <c r="N39" t="n">
-        <v>532.96</v>
+        <v>30.43</v>
       </c>
       <c r="O39" t="n">
-        <v>605.36</v>
+        <v>39.21</v>
       </c>
       <c r="P39" t="n">
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>65.09999999999999</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="R39" t="n">
-        <v>4.93</v>
+        <v>10.94</v>
       </c>
       <c r="S39" t="n">
-        <v>-3.56</v>
+        <v>-7.16</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4766,12 +4774,12 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>NEUTRO +</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -4796,76 +4804,76 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>RSI algo alto; MACD sin confirmar; Volumen bajo</t>
+          <t>Tendencia larga débil; RSI algo alto; Volumen bajo; Algo extendida sobre MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Consumo</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>33.81</v>
+        <v>1079.69</v>
       </c>
       <c r="D40" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E40" t="n">
-        <v>5.66</v>
+        <v>4.51</v>
       </c>
       <c r="F40" t="n">
-        <v>15.87</v>
+        <v>7.73</v>
       </c>
       <c r="G40" t="n">
-        <v>8.609999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>7.37</v>
+        <v>-0.73</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="J40" t="n">
-        <v>2.47</v>
+        <v>21.76</v>
       </c>
       <c r="K40" t="n">
-        <v>7.31</v>
+        <v>2.02</v>
       </c>
       <c r="L40" t="n">
-        <v>32.95</v>
+        <v>1072.07</v>
       </c>
       <c r="M40" t="n">
-        <v>34.18</v>
+        <v>1082.95</v>
       </c>
       <c r="N40" t="n">
-        <v>30.47</v>
+        <v>1050.31</v>
       </c>
       <c r="O40" t="n">
-        <v>39.25</v>
+        <v>1127.56</v>
       </c>
       <c r="P40" t="n">
         <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>65.29000000000001</v>
+        <v>70.17</v>
       </c>
       <c r="R40" t="n">
-        <v>11.09</v>
+        <v>5.47</v>
       </c>
       <c r="S40" t="n">
-        <v>-7.04</v>
+        <v>-1.53</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4879,12 +4887,12 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -4894,7 +4902,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -4909,76 +4917,76 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; MACD positivo; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI algo alto; Volumen bajo; Algo extendida sobre MA20; Volatilidad alta</t>
+          <t>RSI algo alto; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1081.28</v>
+        <v>1009.32</v>
       </c>
       <c r="D41" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E41" t="n">
-        <v>4.67</v>
+        <v>-0.46</v>
       </c>
       <c r="F41" t="n">
-        <v>7.89</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>8.449999999999999</v>
+        <v>-2.98</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.61</v>
+        <v>1.26</v>
       </c>
       <c r="I41" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="J41" t="n">
-        <v>21.76</v>
+        <v>29.94</v>
       </c>
       <c r="K41" t="n">
-        <v>2.01</v>
+        <v>2.97</v>
       </c>
       <c r="L41" t="n">
-        <v>1073.66</v>
+        <v>998.84</v>
       </c>
       <c r="M41" t="n">
-        <v>1084.54</v>
+        <v>1013.81</v>
       </c>
       <c r="N41" t="n">
-        <v>1051.9</v>
+        <v>968.9</v>
       </c>
       <c r="O41" t="n">
-        <v>1129.15</v>
+        <v>1075.2</v>
       </c>
       <c r="P41" t="n">
         <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>70.86</v>
+        <v>66.38</v>
       </c>
       <c r="R41" t="n">
-        <v>5.61</v>
+        <v>5.48</v>
       </c>
       <c r="S41" t="n">
-        <v>-1.39</v>
+        <v>-2.74</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5034,64 +5042,64 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1008.77</v>
+        <v>245.9</v>
       </c>
       <c r="D42" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.52</v>
+        <v>0.83</v>
       </c>
       <c r="F42" t="n">
-        <v>9.66</v>
+        <v>14.56</v>
       </c>
       <c r="G42" t="n">
-        <v>-3.04</v>
+        <v>105.93</v>
       </c>
       <c r="H42" t="n">
-        <v>1.16</v>
+        <v>6.1</v>
       </c>
       <c r="I42" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="J42" t="n">
-        <v>29.94</v>
+        <v>14.58</v>
       </c>
       <c r="K42" t="n">
-        <v>2.97</v>
+        <v>5.93</v>
       </c>
       <c r="L42" t="n">
-        <v>998.29</v>
+        <v>240.8</v>
       </c>
       <c r="M42" t="n">
-        <v>1013.26</v>
+        <v>248.09</v>
       </c>
       <c r="N42" t="n">
-        <v>968.34</v>
+        <v>226.22</v>
       </c>
       <c r="O42" t="n">
-        <v>1074.64</v>
+        <v>277.99</v>
       </c>
       <c r="P42" t="n">
         <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>66.22</v>
+        <v>65.11</v>
       </c>
       <c r="R42" t="n">
-        <v>5.43</v>
+        <v>7.59</v>
       </c>
       <c r="S42" t="n">
-        <v>-2.79</v>
+        <v>-6.85</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5105,12 +5113,12 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -5118,11 +5126,7 @@
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -5135,19 +5139,19 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>RSI algo alto; Volumen bajo</t>
+          <t>RSI algo alto; MACD sin confirmar; Volumen bajo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5156,55 +5160,55 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>245.87</v>
+        <v>251.56</v>
       </c>
       <c r="D43" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E43" t="n">
-        <v>0.82</v>
+        <v>6.56</v>
       </c>
       <c r="F43" t="n">
-        <v>14.54</v>
+        <v>-1.71</v>
       </c>
       <c r="G43" t="n">
-        <v>105.9</v>
+        <v>-1.41</v>
       </c>
       <c r="H43" t="n">
-        <v>6.04</v>
+        <v>-10.17</v>
       </c>
       <c r="I43" t="n">
-        <v>0.44</v>
+        <v>0.58</v>
       </c>
       <c r="J43" t="n">
-        <v>14.58</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>5.93</v>
+        <v>3.69</v>
       </c>
       <c r="L43" t="n">
-        <v>240.77</v>
+        <v>248.31</v>
       </c>
       <c r="M43" t="n">
-        <v>248.06</v>
+        <v>252.95</v>
       </c>
       <c r="N43" t="n">
-        <v>226.18</v>
+        <v>239.01</v>
       </c>
       <c r="O43" t="n">
-        <v>277.96</v>
+        <v>272.01</v>
       </c>
       <c r="P43" t="n">
         <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>65.09999999999999</v>
+        <v>54.17</v>
       </c>
       <c r="R43" t="n">
-        <v>7.57</v>
+        <v>1.71</v>
       </c>
       <c r="S43" t="n">
-        <v>-6.86</v>
+        <v>-5.1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5223,7 +5227,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -5244,76 +5248,76 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>RSI algo alto; MACD sin confirmar; Volumen bajo; Algo extendida sobre MA20</t>
+          <t>Tendencia larga débil; Volumen bajo; Momentum 5D extendido; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>JOBY</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Movilidad aérea</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>251.54</v>
+        <v>10.3</v>
       </c>
       <c r="D44" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E44" t="n">
-        <v>6.55</v>
+        <v>-6.92</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.72</v>
+        <v>12.64</v>
       </c>
       <c r="G44" t="n">
-        <v>-1.42</v>
+        <v>5.92</v>
       </c>
       <c r="H44" t="n">
-        <v>-10.22</v>
+        <v>4.18</v>
       </c>
       <c r="I44" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="J44" t="n">
-        <v>9.289999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="K44" t="n">
-        <v>3.69</v>
+        <v>7.55</v>
       </c>
       <c r="L44" t="n">
-        <v>248.29</v>
+        <v>10.02</v>
       </c>
       <c r="M44" t="n">
-        <v>252.93</v>
+        <v>10.41</v>
       </c>
       <c r="N44" t="n">
-        <v>238.99</v>
+        <v>9.25</v>
       </c>
       <c r="O44" t="n">
-        <v>271.99</v>
+        <v>12</v>
       </c>
       <c r="P44" t="n">
         <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>54.16</v>
+        <v>58.99</v>
       </c>
       <c r="R44" t="n">
-        <v>1.71</v>
+        <v>5.6</v>
       </c>
       <c r="S44" t="n">
-        <v>-5.11</v>
+        <v>-8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5327,12 +5331,12 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -5358,71 +5362,71 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Volumen bajo; Momentum 5D extendido; Débil vs QQQ</t>
+          <t>Tendencia larga débil; Volumen bajo; Momentum negativo; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JOBY</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Movilidad aérea</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10.29</v>
+        <v>263.47</v>
       </c>
       <c r="D45" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E45" t="n">
-        <v>-6.96</v>
+        <v>-2.47</v>
       </c>
       <c r="F45" t="n">
-        <v>12.58</v>
+        <v>3.18</v>
       </c>
       <c r="G45" t="n">
-        <v>5.86</v>
+        <v>26.33</v>
       </c>
       <c r="H45" t="n">
-        <v>4.08</v>
+        <v>-5.28</v>
       </c>
       <c r="I45" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="J45" t="n">
-        <v>0.78</v>
+        <v>6.6</v>
       </c>
       <c r="K45" t="n">
-        <v>7.55</v>
+        <v>2.51</v>
       </c>
       <c r="L45" t="n">
-        <v>10.02</v>
+        <v>261.16</v>
       </c>
       <c r="M45" t="n">
-        <v>10.41</v>
+        <v>264.46</v>
       </c>
       <c r="N45" t="n">
-        <v>9.24</v>
+        <v>254.56</v>
       </c>
       <c r="O45" t="n">
-        <v>12</v>
+        <v>278</v>
       </c>
       <c r="P45" t="n">
         <v>1.63</v>
       </c>
       <c r="Q45" t="n">
-        <v>58.96</v>
+        <v>48.14</v>
       </c>
       <c r="R45" t="n">
-        <v>5.55</v>
+        <v>-1.04</v>
       </c>
       <c r="S45" t="n">
-        <v>-8.039999999999999</v>
+        <v>-5.42</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5436,102 +5440,102 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
+          <t>Mercado NEUTRO +; MA20 sobre MA50; Tendencia larga positiva; RSI saludable; MACD mejorando</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Volumen bajo; Momentum negativo; Volatilidad alta</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Russell</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>263.48</v>
+        <v>278.85</v>
       </c>
       <c r="D46" t="n">
         <v>71</v>
       </c>
       <c r="E46" t="n">
-        <v>-2.46</v>
+        <v>-1.35</v>
       </c>
       <c r="F46" t="n">
-        <v>3.18</v>
+        <v>0.86</v>
       </c>
       <c r="G46" t="n">
-        <v>26.33</v>
+        <v>6.08</v>
       </c>
       <c r="H46" t="n">
-        <v>-5.32</v>
+        <v>-7.6</v>
       </c>
       <c r="I46" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
-        <v>6.6</v>
+        <v>4.89</v>
       </c>
       <c r="K46" t="n">
-        <v>2.51</v>
+        <v>1.75</v>
       </c>
       <c r="L46" t="n">
-        <v>261.17</v>
+        <v>277.14</v>
       </c>
       <c r="M46" t="n">
-        <v>264.47</v>
+        <v>279.58</v>
       </c>
       <c r="N46" t="n">
-        <v>254.57</v>
+        <v>272.24</v>
       </c>
       <c r="O46" t="n">
-        <v>278.01</v>
+        <v>289.61</v>
       </c>
       <c r="P46" t="n">
         <v>1.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>48.15</v>
+        <v>51.07</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.03</v>
+        <v>-0.17</v>
       </c>
       <c r="S46" t="n">
-        <v>-5.41</v>
+        <v>-3.04</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5545,12 +5549,12 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -5576,7 +5580,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -5592,22 +5596,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>420.56</v>
+        <v>420.61</v>
       </c>
       <c r="D47" t="n">
         <v>71</v>
       </c>
       <c r="E47" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.86</v>
+        <v>-2.84</v>
       </c>
       <c r="G47" t="n">
-        <v>8.109999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>-11.36</v>
+        <v>-11.3</v>
       </c>
       <c r="I47" t="n">
         <v>0.44</v>
@@ -5619,28 +5623,28 @@
         <v>2.58</v>
       </c>
       <c r="L47" t="n">
-        <v>416.76</v>
+        <v>416.82</v>
       </c>
       <c r="M47" t="n">
-        <v>422.19</v>
+        <v>422.24</v>
       </c>
       <c r="N47" t="n">
-        <v>405.91</v>
+        <v>405.97</v>
       </c>
       <c r="O47" t="n">
-        <v>444.43</v>
+        <v>444.48</v>
       </c>
       <c r="P47" t="n">
         <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>60.26</v>
+        <v>60.3</v>
       </c>
       <c r="R47" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="S47" t="n">
-        <v>-2.81</v>
+        <v>-2.79</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5659,7 +5663,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -5701,22 +5705,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>71.7</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="D48" t="n">
         <v>68</v>
       </c>
       <c r="E48" t="n">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.1</v>
+        <v>-1.28</v>
       </c>
       <c r="G48" t="n">
-        <v>40.59</v>
+        <v>40.33</v>
       </c>
       <c r="H48" t="n">
-        <v>-9.6</v>
+        <v>-9.74</v>
       </c>
       <c r="I48" t="n">
         <v>0.6</v>
@@ -5725,31 +5729,31 @@
         <v>2.75</v>
       </c>
       <c r="K48" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="L48" t="n">
-        <v>70.73999999999999</v>
+        <v>70.61</v>
       </c>
       <c r="M48" t="n">
-        <v>72.11</v>
+        <v>71.98</v>
       </c>
       <c r="N48" t="n">
-        <v>67.98999999999999</v>
+        <v>67.86</v>
       </c>
       <c r="O48" t="n">
-        <v>77.73999999999999</v>
+        <v>77.61</v>
       </c>
       <c r="P48" t="n">
         <v>1.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>52.96</v>
+        <v>52.65</v>
       </c>
       <c r="R48" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="S48" t="n">
-        <v>-7.08</v>
+        <v>-7.24</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5810,55 +5814,55 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>414.21</v>
+        <v>412.88</v>
       </c>
       <c r="D49" t="n">
         <v>62</v>
       </c>
       <c r="E49" t="n">
-        <v>-6.98</v>
+        <v>-7.27</v>
       </c>
       <c r="F49" t="n">
-        <v>6.89</v>
+        <v>6.55</v>
       </c>
       <c r="G49" t="n">
-        <v>1.18</v>
+        <v>0.85</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.61</v>
+        <v>-1.91</v>
       </c>
       <c r="I49" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>18.12</v>
       </c>
       <c r="K49" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="L49" t="n">
-        <v>407.87</v>
+        <v>406.54</v>
       </c>
       <c r="M49" t="n">
-        <v>416.93</v>
+        <v>415.6</v>
       </c>
       <c r="N49" t="n">
-        <v>389.75</v>
+        <v>388.42</v>
       </c>
       <c r="O49" t="n">
-        <v>454.07</v>
+        <v>452.74</v>
       </c>
       <c r="P49" t="n">
         <v>1.63</v>
       </c>
       <c r="Q49" t="n">
-        <v>61.29</v>
+        <v>60.93</v>
       </c>
       <c r="R49" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="S49" t="n">
-        <v>-8.640000000000001</v>
+        <v>-8.94</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5877,7 +5881,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -5919,22 +5923,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>85.98999999999999</v>
+        <v>85.88</v>
       </c>
       <c r="D50" t="n">
         <v>63</v>
       </c>
       <c r="E50" t="n">
-        <v>6.66</v>
+        <v>6.52</v>
       </c>
       <c r="F50" t="n">
-        <v>16.19</v>
+        <v>16.04</v>
       </c>
       <c r="G50" t="n">
-        <v>20.81</v>
+        <v>20.65</v>
       </c>
       <c r="H50" t="n">
-        <v>7.69</v>
+        <v>7.58</v>
       </c>
       <c r="I50" t="n">
         <v>0.27</v>
@@ -5943,31 +5947,31 @@
         <v>7.61</v>
       </c>
       <c r="K50" t="n">
-        <v>8.85</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>83.33</v>
+        <v>83.22</v>
       </c>
       <c r="M50" t="n">
-        <v>87.13</v>
+        <v>87.02</v>
       </c>
       <c r="N50" t="n">
-        <v>75.72</v>
+        <v>75.61</v>
       </c>
       <c r="O50" t="n">
-        <v>102.73</v>
+        <v>102.62</v>
       </c>
       <c r="P50" t="n">
         <v>1.63</v>
       </c>
       <c r="Q50" t="n">
-        <v>65.40000000000001</v>
+        <v>65.27</v>
       </c>
       <c r="R50" t="n">
-        <v>4.38</v>
+        <v>4.25</v>
       </c>
       <c r="S50" t="n">
-        <v>-10.72</v>
+        <v>-10.84</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5986,7 +5990,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -6032,22 +6036,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>739.76</v>
+        <v>739.72</v>
       </c>
       <c r="D51" t="n">
         <v>70</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="F51" t="n">
         <v>4.01</v>
       </c>
       <c r="G51" t="n">
-        <v>7.92</v>
+        <v>7.91</v>
       </c>
       <c r="H51" t="n">
-        <v>-4.49</v>
+        <v>-4.45</v>
       </c>
       <c r="I51" t="n">
         <v>0.54</v>
@@ -6059,28 +6063,28 @@
         <v>1.01</v>
       </c>
       <c r="L51" t="n">
-        <v>737.13</v>
+        <v>737.09</v>
       </c>
       <c r="M51" t="n">
-        <v>740.88</v>
+        <v>740.85</v>
       </c>
       <c r="N51" t="n">
-        <v>729.63</v>
+        <v>729.59</v>
       </c>
       <c r="O51" t="n">
-        <v>756.26</v>
+        <v>756.23</v>
       </c>
       <c r="P51" t="n">
         <v>1.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>67.01000000000001</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="R51" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S51" t="n">
-        <v>-1.3</v>
+        <v>-1.31</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6141,7 +6145,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>680.1</v>
+        <v>680.08</v>
       </c>
       <c r="D52" t="n">
         <v>70</v>
@@ -6150,16 +6154,16 @@
         <v>-0.34</v>
       </c>
       <c r="F52" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="G52" t="n">
         <v>7.91</v>
       </c>
       <c r="H52" t="n">
-        <v>-4.49</v>
+        <v>-4.46</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="J52" t="n">
         <v>6.87</v>
@@ -6168,22 +6172,22 @@
         <v>1.01</v>
       </c>
       <c r="L52" t="n">
-        <v>677.7</v>
+        <v>677.67</v>
       </c>
       <c r="M52" t="n">
-        <v>681.13</v>
+        <v>681.1</v>
       </c>
       <c r="N52" t="n">
-        <v>670.83</v>
+        <v>670.8099999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>695.2</v>
+        <v>695.1799999999999</v>
       </c>
       <c r="P52" t="n">
         <v>1.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>67.26000000000001</v>
+        <v>67.25</v>
       </c>
       <c r="R52" t="n">
         <v>1.59</v>
@@ -6250,22 +6254,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9.279999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="D53" t="n">
         <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>7.26</v>
+        <v>7.05</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.19</v>
+        <v>-1.39</v>
       </c>
       <c r="G53" t="n">
-        <v>-8.32</v>
+        <v>-8.5</v>
       </c>
       <c r="H53" t="n">
-        <v>-9.69</v>
+        <v>-9.85</v>
       </c>
       <c r="I53" t="n">
         <v>0.6899999999999999</v>
@@ -6274,31 +6278,31 @@
         <v>0.48</v>
       </c>
       <c r="K53" t="n">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="L53" t="n">
-        <v>9.109999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="M53" t="n">
-        <v>9.35</v>
+        <v>9.33</v>
       </c>
       <c r="N53" t="n">
-        <v>8.630000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>10.34</v>
+        <v>10.32</v>
       </c>
       <c r="P53" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>56.07</v>
+        <v>55.86</v>
       </c>
       <c r="R53" t="n">
-        <v>2.56</v>
+        <v>2.37</v>
       </c>
       <c r="S53" t="n">
-        <v>-6.09</v>
+        <v>-6.28</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6317,7 +6321,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -6359,22 +6363,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>44.94</v>
+        <v>44.93</v>
       </c>
       <c r="D54" t="n">
         <v>62</v>
       </c>
       <c r="E54" t="n">
-        <v>-4.56</v>
+        <v>-4.57</v>
       </c>
       <c r="F54" t="n">
-        <v>14.78</v>
+        <v>14.76</v>
       </c>
       <c r="G54" t="n">
-        <v>20.71</v>
+        <v>20.7</v>
       </c>
       <c r="H54" t="n">
-        <v>6.28</v>
+        <v>6.3</v>
       </c>
       <c r="I54" t="n">
         <v>0.35</v>
@@ -6389,25 +6393,25 @@
         <v>44.5</v>
       </c>
       <c r="M54" t="n">
-        <v>45.12</v>
+        <v>45.11</v>
       </c>
       <c r="N54" t="n">
         <v>43.27</v>
       </c>
       <c r="O54" t="n">
-        <v>47.65</v>
+        <v>47.64</v>
       </c>
       <c r="P54" t="n">
         <v>1.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>66.33</v>
+        <v>66.31</v>
       </c>
       <c r="R54" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S54" t="n">
-        <v>-5.97</v>
+        <v>-5.98</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6468,22 +6472,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>207.9</v>
+        <v>207.68</v>
       </c>
       <c r="D55" t="n">
         <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>7.93</v>
+        <v>7.82</v>
       </c>
       <c r="F55" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="G55" t="n">
-        <v>26.92</v>
+        <v>26.78</v>
       </c>
       <c r="H55" t="n">
-        <v>-8.34</v>
+        <v>-8.4</v>
       </c>
       <c r="I55" t="n">
         <v>0.37</v>
@@ -6492,31 +6496,31 @@
         <v>15.04</v>
       </c>
       <c r="K55" t="n">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="L55" t="n">
-        <v>202.64</v>
+        <v>202.42</v>
       </c>
       <c r="M55" t="n">
-        <v>210.16</v>
+        <v>209.94</v>
       </c>
       <c r="N55" t="n">
-        <v>187.6</v>
+        <v>187.38</v>
       </c>
       <c r="O55" t="n">
-        <v>240.98</v>
+        <v>240.76</v>
       </c>
       <c r="P55" t="n">
         <v>1.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>50.99</v>
+        <v>50.92</v>
       </c>
       <c r="R55" t="n">
-        <v>-1.57</v>
+        <v>-1.67</v>
       </c>
       <c r="S55" t="n">
-        <v>-19.69</v>
+        <v>-19.78</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6535,7 +6539,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -6577,55 +6581,55 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>13.37</v>
+        <v>13.35</v>
       </c>
       <c r="D56" t="n">
         <v>72</v>
       </c>
       <c r="E56" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="F56" t="n">
-        <v>12.92</v>
+        <v>12.8</v>
       </c>
       <c r="G56" t="n">
-        <v>66.09</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>4.42</v>
+        <v>4.34</v>
       </c>
       <c r="I56" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>7.5</v>
+        <v>7.51</v>
       </c>
       <c r="L56" t="n">
-        <v>13.02</v>
+        <v>13</v>
       </c>
       <c r="M56" t="n">
-        <v>13.52</v>
+        <v>13.51</v>
       </c>
       <c r="N56" t="n">
-        <v>12.02</v>
+        <v>12</v>
       </c>
       <c r="O56" t="n">
-        <v>15.58</v>
+        <v>15.56</v>
       </c>
       <c r="P56" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>60.36</v>
+        <v>60.27</v>
       </c>
       <c r="R56" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="S56" t="n">
-        <v>-3.12</v>
+        <v>-3.22</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6644,7 +6648,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>BTC-USD 1.64% · ETH-USD -5.09%</t>
+          <t>BTC-USD 1.53% · ETH-USD -5.24%</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -6674,7 +6678,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.64% · ETH-USD -5.09%; Tendencia larga débil; MACD sin confirmar; Algo extendida sobre MA20; Volatilidad alta</t>
+          <t>Sector no acompaña: BTC-USD 1.53% · ETH-USD -5.24%; Tendencia larga débil; MACD sin confirmar; Algo extendida sobre MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -6690,22 +6694,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>253.3</v>
+        <v>253.84</v>
       </c>
       <c r="D57" t="n">
         <v>95</v>
       </c>
       <c r="E57" t="n">
-        <v>14.51</v>
+        <v>14.75</v>
       </c>
       <c r="F57" t="n">
-        <v>28.86</v>
+        <v>29.13</v>
       </c>
       <c r="G57" t="n">
-        <v>97.67</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>20.36</v>
+        <v>20.67</v>
       </c>
       <c r="I57" t="n">
         <v>1.2</v>
@@ -6714,31 +6718,31 @@
         <v>17.9</v>
       </c>
       <c r="K57" t="n">
-        <v>7.07</v>
+        <v>7.05</v>
       </c>
       <c r="L57" t="n">
-        <v>247.04</v>
+        <v>247.57</v>
       </c>
       <c r="M57" t="n">
-        <v>255.98</v>
+        <v>256.52</v>
       </c>
       <c r="N57" t="n">
-        <v>229.14</v>
+        <v>229.68</v>
       </c>
       <c r="O57" t="n">
-        <v>292.68</v>
+        <v>293.22</v>
       </c>
       <c r="P57" t="n">
         <v>1.63</v>
       </c>
       <c r="Q57" t="n">
-        <v>63.75</v>
+        <v>63.88</v>
       </c>
       <c r="R57" t="n">
-        <v>17.16</v>
+        <v>17.39</v>
       </c>
       <c r="S57" t="n">
-        <v>-2.37</v>
+        <v>-2.16</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6757,7 +6761,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6782,7 +6786,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6803,22 +6807,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>117.5</v>
+        <v>117.86</v>
       </c>
       <c r="D58" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E58" t="n">
-        <v>-2.32</v>
+        <v>-2.02</v>
       </c>
       <c r="F58" t="n">
-        <v>80.03</v>
+        <v>80.58</v>
       </c>
       <c r="G58" t="n">
-        <v>154.78</v>
+        <v>155.56</v>
       </c>
       <c r="H58" t="n">
-        <v>71.53</v>
+        <v>72.12</v>
       </c>
       <c r="I58" t="n">
         <v>0.75</v>
@@ -6827,31 +6831,31 @@
         <v>10.24</v>
       </c>
       <c r="K58" t="n">
-        <v>8.720000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="L58" t="n">
-        <v>113.92</v>
+        <v>114.28</v>
       </c>
       <c r="M58" t="n">
-        <v>119.04</v>
+        <v>119.4</v>
       </c>
       <c r="N58" t="n">
-        <v>103.68</v>
+        <v>104.04</v>
       </c>
       <c r="O58" t="n">
-        <v>140.04</v>
+        <v>140.4</v>
       </c>
       <c r="P58" t="n">
         <v>1.63</v>
       </c>
       <c r="Q58" t="n">
-        <v>64.39</v>
+        <v>64.55</v>
       </c>
       <c r="R58" t="n">
-        <v>12.41</v>
+        <v>12.73</v>
       </c>
       <c r="S58" t="n">
-        <v>-11.48</v>
+        <v>-11.21</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6870,7 +6874,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -6878,7 +6882,11 @@
           <t>ALTO</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="Z58" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -6891,12 +6899,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Muy alejada de MA20; Volatilidad alta</t>
+          <t>MACD sin confirmar; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -6912,22 +6920,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>444.27</v>
+        <v>444.08</v>
       </c>
       <c r="D59" t="n">
         <v>68</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.28</v>
+        <v>-0.32</v>
       </c>
       <c r="F59" t="n">
-        <v>46.4</v>
+        <v>46.34</v>
       </c>
       <c r="G59" t="n">
-        <v>107.76</v>
+        <v>107.67</v>
       </c>
       <c r="H59" t="n">
-        <v>37.9</v>
+        <v>37.88</v>
       </c>
       <c r="I59" t="n">
         <v>0.52</v>
@@ -6939,28 +6947,28 @@
         <v>6.73</v>
       </c>
       <c r="L59" t="n">
-        <v>433.81</v>
+        <v>433.62</v>
       </c>
       <c r="M59" t="n">
-        <v>448.75</v>
+        <v>448.56</v>
       </c>
       <c r="N59" t="n">
-        <v>403.91</v>
+        <v>403.72</v>
       </c>
       <c r="O59" t="n">
-        <v>510.04</v>
+        <v>509.85</v>
       </c>
       <c r="P59" t="n">
         <v>1.63</v>
       </c>
       <c r="Q59" t="n">
-        <v>67.84999999999999</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="R59" t="n">
-        <v>13.18</v>
+        <v>13.13</v>
       </c>
       <c r="S59" t="n">
-        <v>-5.32</v>
+        <v>-5.36</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6979,7 +6987,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -7000,7 +7008,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7021,55 +7029,55 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>726.89</v>
+        <v>728.9</v>
       </c>
       <c r="D60" t="n">
         <v>61</v>
       </c>
       <c r="E60" t="n">
-        <v>-9.550000000000001</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>49.11</v>
+        <v>49.52</v>
       </c>
       <c r="G60" t="n">
-        <v>73.97</v>
+        <v>74.45</v>
       </c>
       <c r="H60" t="n">
-        <v>40.61</v>
+        <v>41.06</v>
       </c>
       <c r="I60" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>61.19</v>
       </c>
       <c r="K60" t="n">
-        <v>8.42</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>705.47</v>
+        <v>707.48</v>
       </c>
       <c r="M60" t="n">
-        <v>736.0700000000001</v>
+        <v>738.08</v>
       </c>
       <c r="N60" t="n">
-        <v>644.28</v>
+        <v>646.29</v>
       </c>
       <c r="O60" t="n">
-        <v>861.51</v>
+        <v>863.52</v>
       </c>
       <c r="P60" t="n">
         <v>1.63</v>
       </c>
       <c r="Q60" t="n">
-        <v>69.02</v>
+        <v>69.13</v>
       </c>
       <c r="R60" t="n">
-        <v>13.27</v>
+        <v>13.56</v>
       </c>
       <c r="S60" t="n">
-        <v>-11.21</v>
+        <v>-10.97</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7088,7 +7096,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -7109,7 +7117,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7145,10 +7153,10 @@
         <v>71.17</v>
       </c>
       <c r="H61" t="n">
-        <v>39.36</v>
+        <v>39.4</v>
       </c>
       <c r="I61" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="J61" t="n">
         <v>5.49</v>
@@ -7197,7 +7205,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -7239,7 +7247,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>300.99</v>
+        <v>301</v>
       </c>
       <c r="D62" t="n">
         <v>78</v>
@@ -7251,13 +7259,13 @@
         <v>10.29</v>
       </c>
       <c r="G62" t="n">
-        <v>10.7</v>
+        <v>10.71</v>
       </c>
       <c r="H62" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="I62" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J62" t="n">
         <v>6.43</v>
@@ -7266,16 +7274,16 @@
         <v>2.14</v>
       </c>
       <c r="L62" t="n">
-        <v>298.74</v>
+        <v>298.75</v>
       </c>
       <c r="M62" t="n">
-        <v>301.95</v>
+        <v>301.96</v>
       </c>
       <c r="N62" t="n">
-        <v>292.31</v>
+        <v>292.32</v>
       </c>
       <c r="O62" t="n">
-        <v>315.14</v>
+        <v>315.15</v>
       </c>
       <c r="P62" t="n">
         <v>1.63</v>
@@ -7306,7 +7314,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -7348,25 +7356,25 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>213.27</v>
+        <v>213.05</v>
       </c>
       <c r="D63" t="n">
         <v>76</v>
       </c>
       <c r="E63" t="n">
-        <v>3.88</v>
+        <v>3.77</v>
       </c>
       <c r="F63" t="n">
-        <v>61.4</v>
+        <v>61.23</v>
       </c>
       <c r="G63" t="n">
-        <v>104.22</v>
+        <v>104.01</v>
       </c>
       <c r="H63" t="n">
-        <v>52.9</v>
+        <v>52.77</v>
       </c>
       <c r="I63" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="J63" t="n">
         <v>12.32</v>
@@ -7375,28 +7383,28 @@
         <v>5.78</v>
       </c>
       <c r="L63" t="n">
-        <v>208.96</v>
+        <v>208.74</v>
       </c>
       <c r="M63" t="n">
-        <v>215.12</v>
+        <v>214.9</v>
       </c>
       <c r="N63" t="n">
-        <v>196.63</v>
+        <v>196.41</v>
       </c>
       <c r="O63" t="n">
-        <v>240.38</v>
+        <v>240.16</v>
       </c>
       <c r="P63" t="n">
         <v>1.63</v>
       </c>
       <c r="Q63" t="n">
-        <v>90.34</v>
+        <v>90.14</v>
       </c>
       <c r="R63" t="n">
-        <v>25.13</v>
+        <v>25</v>
       </c>
       <c r="S63" t="n">
-        <v>-3.21</v>
+        <v>-3.31</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7415,7 +7423,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -7448,64 +7456,64 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>ETF Tecnología</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>131.39</v>
+        <v>176.44</v>
       </c>
       <c r="D64" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E64" t="n">
-        <v>5.83</v>
+        <v>-0.23</v>
       </c>
       <c r="F64" t="n">
-        <v>45.92</v>
+        <v>11.61</v>
       </c>
       <c r="G64" t="n">
-        <v>87.78</v>
+        <v>25.9</v>
       </c>
       <c r="H64" t="n">
-        <v>37.42</v>
+        <v>3.15</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="J64" t="n">
-        <v>11.33</v>
+        <v>4.16</v>
       </c>
       <c r="K64" t="n">
-        <v>8.630000000000001</v>
+        <v>2.36</v>
       </c>
       <c r="L64" t="n">
-        <v>127.42</v>
+        <v>174.98</v>
       </c>
       <c r="M64" t="n">
-        <v>133.09</v>
+        <v>177.06</v>
       </c>
       <c r="N64" t="n">
-        <v>116.09</v>
+        <v>170.83</v>
       </c>
       <c r="O64" t="n">
-        <v>156.32</v>
+        <v>185.59</v>
       </c>
       <c r="P64" t="n">
         <v>1.63</v>
       </c>
       <c r="Q64" t="n">
-        <v>75.79000000000001</v>
+        <v>73.86</v>
       </c>
       <c r="R64" t="n">
-        <v>31.55</v>
+        <v>4.79</v>
       </c>
       <c r="S64" t="n">
-        <v>-5.05</v>
+        <v>-2.1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7519,12 +7527,12 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -7545,76 +7553,76 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; Fuerte vs QQQ</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; Volumen bajo; Muy alejada de MA20; Volatilidad alta</t>
+          <t>RSI sobrecomprado; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ETF Tecnología</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>176.33</v>
+        <v>132</v>
       </c>
       <c r="D65" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.29</v>
+        <v>6.32</v>
       </c>
       <c r="F65" t="n">
-        <v>11.54</v>
+        <v>46.6</v>
       </c>
       <c r="G65" t="n">
-        <v>25.82</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>3.04</v>
+        <v>38.14</v>
       </c>
       <c r="I65" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
-        <v>4.16</v>
+        <v>11.33</v>
       </c>
       <c r="K65" t="n">
-        <v>2.36</v>
+        <v>8.59</v>
       </c>
       <c r="L65" t="n">
-        <v>174.87</v>
+        <v>128.03</v>
       </c>
       <c r="M65" t="n">
-        <v>176.95</v>
+        <v>133.7</v>
       </c>
       <c r="N65" t="n">
-        <v>170.72</v>
+        <v>116.7</v>
       </c>
       <c r="O65" t="n">
-        <v>185.48</v>
+        <v>156.93</v>
       </c>
       <c r="P65" t="n">
         <v>1.63</v>
       </c>
       <c r="Q65" t="n">
-        <v>73.78</v>
+        <v>75.94</v>
       </c>
       <c r="R65" t="n">
-        <v>4.72</v>
+        <v>32.12</v>
       </c>
       <c r="S65" t="n">
-        <v>-2.16</v>
+        <v>-4.61</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7628,12 +7636,12 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -7654,12 +7662,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; Fuerte vs QQQ</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>RSI sobrecomprado; MACD sin confirmar; Volumen bajo</t>
+          <t>RSI sobrecomprado; Volumen bajo; Momentum 5D extendido; Muy alejada de MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -7675,25 +7683,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>246.91</v>
+        <v>246.84</v>
       </c>
       <c r="D66" t="n">
         <v>63</v>
       </c>
       <c r="E66" t="n">
-        <v>8.390000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>36.26</v>
+        <v>36.22</v>
       </c>
       <c r="G66" t="n">
-        <v>74.29000000000001</v>
+        <v>74.23</v>
       </c>
       <c r="H66" t="n">
         <v>27.76</v>
       </c>
       <c r="I66" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="J66" t="n">
         <v>10.83</v>
@@ -7702,28 +7710,28 @@
         <v>4.39</v>
       </c>
       <c r="L66" t="n">
-        <v>243.12</v>
+        <v>243.04</v>
       </c>
       <c r="M66" t="n">
-        <v>248.53</v>
+        <v>248.46</v>
       </c>
       <c r="N66" t="n">
-        <v>232.29</v>
+        <v>232.21</v>
       </c>
       <c r="O66" t="n">
-        <v>270.74</v>
+        <v>270.67</v>
       </c>
       <c r="P66" t="n">
         <v>1.63</v>
       </c>
       <c r="Q66" t="n">
-        <v>90.14</v>
+        <v>90.13</v>
       </c>
       <c r="R66" t="n">
-        <v>20.83</v>
+        <v>20.8</v>
       </c>
       <c r="S66" t="n">
-        <v>-1.24</v>
+        <v>-1.27</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7742,7 +7750,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -7784,25 +7792,25 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>87.40000000000001</v>
+        <v>87.38</v>
       </c>
       <c r="D67" t="n">
         <v>63</v>
       </c>
       <c r="E67" t="n">
-        <v>11.77</v>
+        <v>11.73</v>
       </c>
       <c r="F67" t="n">
-        <v>11.06</v>
+        <v>11.02</v>
       </c>
       <c r="G67" t="n">
-        <v>22.86</v>
+        <v>22.82</v>
       </c>
       <c r="H67" t="n">
         <v>2.56</v>
       </c>
       <c r="I67" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>3.81</v>
@@ -7811,28 +7819,28 @@
         <v>4.36</v>
       </c>
       <c r="L67" t="n">
-        <v>86.06999999999999</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="M67" t="n">
-        <v>87.98</v>
+        <v>87.95</v>
       </c>
       <c r="N67" t="n">
-        <v>82.26000000000001</v>
+        <v>82.23</v>
       </c>
       <c r="O67" t="n">
-        <v>95.79000000000001</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="P67" t="n">
         <v>1.63</v>
       </c>
       <c r="Q67" t="n">
-        <v>74.17</v>
+        <v>74.14</v>
       </c>
       <c r="R67" t="n">
-        <v>9.94</v>
+        <v>9.9</v>
       </c>
       <c r="S67" t="n">
-        <v>-2.88</v>
+        <v>-2.92</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7851,7 +7859,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -7893,25 +7901,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>113.43</v>
+        <v>113.48</v>
       </c>
       <c r="D68" t="n">
         <v>63</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F68" t="n">
-        <v>10.1</v>
+        <v>10.14</v>
       </c>
       <c r="G68" t="n">
-        <v>23.21</v>
+        <v>23.25</v>
       </c>
       <c r="H68" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="I68" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>2.47</v>
@@ -7920,28 +7928,28 @@
         <v>2.18</v>
       </c>
       <c r="L68" t="n">
-        <v>112.57</v>
+        <v>112.61</v>
       </c>
       <c r="M68" t="n">
-        <v>113.81</v>
+        <v>113.85</v>
       </c>
       <c r="N68" t="n">
-        <v>110.1</v>
+        <v>110.14</v>
       </c>
       <c r="O68" t="n">
-        <v>118.87</v>
+        <v>118.91</v>
       </c>
       <c r="P68" t="n">
         <v>1.63</v>
       </c>
       <c r="Q68" t="n">
-        <v>74.95</v>
+        <v>75</v>
       </c>
       <c r="R68" t="n">
-        <v>4.44</v>
+        <v>4.48</v>
       </c>
       <c r="S68" t="n">
-        <v>-1.89</v>
+        <v>-1.85</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7960,7 +7968,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -8002,25 +8010,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>642.09</v>
+        <v>641.84</v>
       </c>
       <c r="D69" t="n">
         <v>62</v>
       </c>
       <c r="E69" t="n">
-        <v>14.14</v>
+        <v>14.09</v>
       </c>
       <c r="F69" t="n">
-        <v>37.59</v>
+        <v>37.53</v>
       </c>
       <c r="G69" t="n">
-        <v>83.31999999999999</v>
+        <v>83.25</v>
       </c>
       <c r="H69" t="n">
-        <v>29.09</v>
+        <v>29.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="J69" t="n">
         <v>25.82</v>
@@ -8029,28 +8037,28 @@
         <v>4.02</v>
       </c>
       <c r="L69" t="n">
-        <v>633.05</v>
+        <v>632.8</v>
       </c>
       <c r="M69" t="n">
-        <v>645.96</v>
+        <v>645.71</v>
       </c>
       <c r="N69" t="n">
-        <v>607.23</v>
+        <v>606.98</v>
       </c>
       <c r="O69" t="n">
-        <v>698.9</v>
+        <v>698.65</v>
       </c>
       <c r="P69" t="n">
         <v>1.63</v>
       </c>
       <c r="Q69" t="n">
-        <v>95.20999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="R69" t="n">
-        <v>24.59</v>
+        <v>24.55</v>
       </c>
       <c r="S69" t="n">
-        <v>-0.71</v>
+        <v>-0.74</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8069,7 +8077,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -8111,25 +8119,25 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>390.4</v>
+        <v>390.36</v>
       </c>
       <c r="D70" t="n">
         <v>46</v>
       </c>
       <c r="E70" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G70" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>-6.14</v>
+        <v>-6.12</v>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="J70" t="n">
         <v>13.58</v>
@@ -8138,28 +8146,28 @@
         <v>3.48</v>
       </c>
       <c r="L70" t="n">
-        <v>385.65</v>
+        <v>385.61</v>
       </c>
       <c r="M70" t="n">
-        <v>392.44</v>
+        <v>392.4</v>
       </c>
       <c r="N70" t="n">
-        <v>372.08</v>
+        <v>372.03</v>
       </c>
       <c r="O70" t="n">
-        <v>420.27</v>
+        <v>420.23</v>
       </c>
       <c r="P70" t="n">
         <v>1.63</v>
       </c>
       <c r="Q70" t="n">
-        <v>44.36</v>
+        <v>44.34</v>
       </c>
       <c r="R70" t="n">
-        <v>-4.23</v>
+        <v>-4.25</v>
       </c>
       <c r="S70" t="n">
-        <v>-10.4</v>
+        <v>-10.41</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8178,7 +8186,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -8203,7 +8211,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -8224,55 +8232,55 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>243.37</v>
+        <v>243.25</v>
       </c>
       <c r="D71" t="n">
         <v>33</v>
       </c>
       <c r="E71" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="F71" t="n">
-        <v>-5.26</v>
+        <v>-5.31</v>
       </c>
       <c r="G71" t="n">
-        <v>10.4</v>
+        <v>10.34</v>
       </c>
       <c r="H71" t="n">
-        <v>-13.76</v>
+        <v>-13.77</v>
       </c>
       <c r="I71" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="J71" t="n">
-        <v>8</v>
+        <v>8.01</v>
       </c>
       <c r="K71" t="n">
         <v>3.29</v>
       </c>
       <c r="L71" t="n">
-        <v>240.57</v>
+        <v>240.45</v>
       </c>
       <c r="M71" t="n">
-        <v>244.57</v>
+        <v>244.45</v>
       </c>
       <c r="N71" t="n">
-        <v>232.58</v>
+        <v>232.44</v>
       </c>
       <c r="O71" t="n">
-        <v>260.96</v>
+        <v>260.86</v>
       </c>
       <c r="P71" t="n">
         <v>1.63</v>
       </c>
       <c r="Q71" t="n">
-        <v>25.34</v>
+        <v>25.29</v>
       </c>
       <c r="R71" t="n">
-        <v>-4.27</v>
+        <v>-4.31</v>
       </c>
       <c r="S71" t="n">
-        <v>-11.44</v>
+        <v>-11.49</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8291,7 +8299,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>XLE 6.01% · CL=F 4.96%</t>
+          <t>XLE 5.61% · CL=F 5.07%</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -8316,7 +8324,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 6.01% · CL=F 4.96%; Tendencia larga positiva; MACD mejorando; Momentum 5D sano</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.61% · CL=F 5.07%; Tendencia larga positiva; MACD mejorando; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8337,55 +8345,55 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>417.62</v>
+        <v>418.14</v>
       </c>
       <c r="D72" t="n">
         <v>59</v>
       </c>
       <c r="E72" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.19</v>
+        <v>-1.07</v>
       </c>
       <c r="G72" t="n">
-        <v>28.57</v>
+        <v>28.73</v>
       </c>
       <c r="H72" t="n">
-        <v>-9.69</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J72" t="n">
         <v>16.66</v>
       </c>
       <c r="K72" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="L72" t="n">
-        <v>411.79</v>
+        <v>412.31</v>
       </c>
       <c r="M72" t="n">
-        <v>420.12</v>
+        <v>420.64</v>
       </c>
       <c r="N72" t="n">
-        <v>395.14</v>
+        <v>395.66</v>
       </c>
       <c r="O72" t="n">
-        <v>454.26</v>
+        <v>454.78</v>
       </c>
       <c r="P72" t="n">
         <v>1.63</v>
       </c>
       <c r="Q72" t="n">
-        <v>50.08</v>
+        <v>50.29</v>
       </c>
       <c r="R72" t="n">
-        <v>-0.52</v>
+        <v>-0.4</v>
       </c>
       <c r="S72" t="n">
-        <v>-5.59</v>
+        <v>-5.48</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8404,7 +8412,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -8425,7 +8433,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -8446,22 +8454,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1534.18</v>
+        <v>1535.35</v>
       </c>
       <c r="D73" t="n">
         <v>53</v>
       </c>
       <c r="E73" t="n">
-        <v>-7.04</v>
+        <v>-6.97</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="G73" t="n">
-        <v>26.66</v>
+        <v>26.76</v>
       </c>
       <c r="H73" t="n">
-        <v>-7.7</v>
+        <v>-7.59</v>
       </c>
       <c r="I73" t="n">
         <v>0.36</v>
@@ -8470,31 +8478,31 @@
         <v>78.53</v>
       </c>
       <c r="K73" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="L73" t="n">
-        <v>1506.7</v>
+        <v>1507.87</v>
       </c>
       <c r="M73" t="n">
-        <v>1545.96</v>
+        <v>1547.13</v>
       </c>
       <c r="N73" t="n">
-        <v>1428.17</v>
+        <v>1429.34</v>
       </c>
       <c r="O73" t="n">
-        <v>1706.94</v>
+        <v>1708.11</v>
       </c>
       <c r="P73" t="n">
         <v>1.63</v>
       </c>
       <c r="Q73" t="n">
-        <v>43.76</v>
+        <v>43.86</v>
       </c>
       <c r="R73" t="n">
-        <v>-2.88</v>
+        <v>-2.81</v>
       </c>
       <c r="S73" t="n">
-        <v>-8.43</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8513,7 +8521,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -8534,7 +8542,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -8555,25 +8563,25 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>51.63</v>
+        <v>51.61</v>
       </c>
       <c r="D74" t="n">
         <v>57</v>
       </c>
       <c r="E74" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.1</v>
+        <v>-1.15</v>
       </c>
       <c r="G74" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="H74" t="n">
-        <v>-9.6</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="J74" t="n">
         <v>0.65</v>
@@ -8582,28 +8590,28 @@
         <v>1.26</v>
       </c>
       <c r="L74" t="n">
-        <v>51.41</v>
+        <v>51.38</v>
       </c>
       <c r="M74" t="n">
-        <v>51.73</v>
+        <v>51.71</v>
       </c>
       <c r="N74" t="n">
-        <v>50.76</v>
+        <v>50.73</v>
       </c>
       <c r="O74" t="n">
-        <v>53.07</v>
+        <v>53.04</v>
       </c>
       <c r="P74" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q74" t="n">
-        <v>44.81</v>
+        <v>44.51</v>
       </c>
       <c r="R74" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="S74" t="n">
-        <v>-1.85</v>
+        <v>-1.9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8664,22 +8672,22 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>88.36</v>
+        <v>88.33</v>
       </c>
       <c r="D75" t="n">
         <v>56</v>
       </c>
       <c r="E75" t="n">
-        <v>5.41</v>
+        <v>5.37</v>
       </c>
       <c r="F75" t="n">
-        <v>-3.64</v>
+        <v>-3.67</v>
       </c>
       <c r="G75" t="n">
-        <v>-22.4</v>
+        <v>-22.42</v>
       </c>
       <c r="H75" t="n">
-        <v>-12.14</v>
+        <v>-12.13</v>
       </c>
       <c r="I75" t="n">
         <v>0.29</v>
@@ -8691,28 +8699,28 @@
         <v>2.46</v>
       </c>
       <c r="L75" t="n">
-        <v>87.61</v>
+        <v>87.58</v>
       </c>
       <c r="M75" t="n">
-        <v>88.69</v>
+        <v>88.66</v>
       </c>
       <c r="N75" t="n">
-        <v>85.44</v>
+        <v>85.41</v>
       </c>
       <c r="O75" t="n">
-        <v>93.14</v>
+        <v>93.11</v>
       </c>
       <c r="P75" t="n">
         <v>1.63</v>
       </c>
       <c r="Q75" t="n">
-        <v>43.36</v>
+        <v>43.29</v>
       </c>
       <c r="R75" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="S75" t="n">
-        <v>-6.78</v>
+        <v>-6.81</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8773,22 +8781,22 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>871.47</v>
+        <v>871.51</v>
       </c>
       <c r="D76" t="n">
         <v>50</v>
       </c>
       <c r="E76" t="n">
-        <v>-3.42</v>
+        <v>-3.41</v>
       </c>
       <c r="F76" t="n">
         <v>7.74</v>
       </c>
       <c r="G76" t="n">
-        <v>13.65</v>
+        <v>13.66</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.76</v>
+        <v>-0.72</v>
       </c>
       <c r="I76" t="n">
         <v>0.5</v>
@@ -8800,22 +8808,22 @@
         <v>3.37</v>
       </c>
       <c r="L76" t="n">
-        <v>861.1799999999999</v>
+        <v>861.22</v>
       </c>
       <c r="M76" t="n">
-        <v>875.88</v>
+        <v>875.92</v>
       </c>
       <c r="N76" t="n">
-        <v>831.79</v>
+        <v>831.83</v>
       </c>
       <c r="O76" t="n">
-        <v>936.14</v>
+        <v>936.1799999999999</v>
       </c>
       <c r="P76" t="n">
         <v>1.63</v>
       </c>
       <c r="Q76" t="n">
-        <v>46.17</v>
+        <v>46.18</v>
       </c>
       <c r="R76" t="n">
         <v>-0.67</v>
@@ -8882,25 +8890,25 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>385.03</v>
+        <v>385.06</v>
       </c>
       <c r="D77" t="n">
         <v>50</v>
       </c>
       <c r="E77" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="F77" t="n">
-        <v>-5.79</v>
+        <v>-5.78</v>
       </c>
       <c r="G77" t="n">
-        <v>7.67</v>
+        <v>7.68</v>
       </c>
       <c r="H77" t="n">
-        <v>-14.29</v>
+        <v>-14.24</v>
       </c>
       <c r="I77" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="J77" t="n">
         <v>19.25</v>
@@ -8909,28 +8917,28 @@
         <v>5</v>
       </c>
       <c r="L77" t="n">
-        <v>378.29</v>
+        <v>378.32</v>
       </c>
       <c r="M77" t="n">
-        <v>387.92</v>
+        <v>387.95</v>
       </c>
       <c r="N77" t="n">
-        <v>359.04</v>
+        <v>359.07</v>
       </c>
       <c r="O77" t="n">
-        <v>427.38</v>
+        <v>427.41</v>
       </c>
       <c r="P77" t="n">
         <v>1.63</v>
       </c>
       <c r="Q77" t="n">
-        <v>48.76</v>
+        <v>48.77</v>
       </c>
       <c r="R77" t="n">
-        <v>-2.04</v>
+        <v>-2.03</v>
       </c>
       <c r="S77" t="n">
-        <v>-9.19</v>
+        <v>-9.18</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8949,7 +8957,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
@@ -8991,25 +8999,25 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>124.93</v>
+        <v>124.94</v>
       </c>
       <c r="D78" t="n">
         <v>48</v>
       </c>
       <c r="E78" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="F78" t="n">
         <v>-3.24</v>
       </c>
       <c r="G78" t="n">
-        <v>14.57</v>
+        <v>14.58</v>
       </c>
       <c r="H78" t="n">
-        <v>-11.74</v>
+        <v>-11.7</v>
       </c>
       <c r="I78" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="J78" t="n">
         <v>3.49</v>
@@ -9018,28 +9026,28 @@
         <v>2.8</v>
       </c>
       <c r="L78" t="n">
-        <v>123.71</v>
+        <v>123.72</v>
       </c>
       <c r="M78" t="n">
-        <v>125.45</v>
+        <v>125.46</v>
       </c>
       <c r="N78" t="n">
-        <v>120.21</v>
+        <v>120.22</v>
       </c>
       <c r="O78" t="n">
-        <v>132.62</v>
+        <v>132.63</v>
       </c>
       <c r="P78" t="n">
         <v>1.63</v>
       </c>
       <c r="Q78" t="n">
-        <v>44.75</v>
+        <v>44.78</v>
       </c>
       <c r="R78" t="n">
-        <v>-0.88</v>
+        <v>-0.87</v>
       </c>
       <c r="S78" t="n">
-        <v>-5.32</v>
+        <v>-5.31</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9100,22 +9108,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>223.24</v>
+        <v>223.37</v>
       </c>
       <c r="D79" t="n">
         <v>43</v>
       </c>
       <c r="E79" t="n">
-        <v>4.01</v>
+        <v>4.06</v>
       </c>
       <c r="F79" t="n">
-        <v>-10.71</v>
+        <v>-10.66</v>
       </c>
       <c r="G79" t="n">
-        <v>-1.93</v>
+        <v>-1.88</v>
       </c>
       <c r="H79" t="n">
-        <v>-19.21</v>
+        <v>-19.12</v>
       </c>
       <c r="I79" t="n">
         <v>0.27</v>
@@ -9127,28 +9135,28 @@
         <v>2.49</v>
       </c>
       <c r="L79" t="n">
-        <v>221.29</v>
+        <v>221.42</v>
       </c>
       <c r="M79" t="n">
-        <v>224.07</v>
+        <v>224.2</v>
       </c>
       <c r="N79" t="n">
-        <v>215.73</v>
+        <v>215.86</v>
       </c>
       <c r="O79" t="n">
-        <v>235.47</v>
+        <v>235.6</v>
       </c>
       <c r="P79" t="n">
         <v>1.63</v>
       </c>
       <c r="Q79" t="n">
-        <v>42.01</v>
+        <v>42.2</v>
       </c>
       <c r="R79" t="n">
-        <v>-0.88</v>
+        <v>-0.83</v>
       </c>
       <c r="S79" t="n">
-        <v>-4.69</v>
+        <v>-4.64</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9167,7 +9175,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -9209,22 +9217,22 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>90.59999999999999</v>
+        <v>90.58</v>
       </c>
       <c r="D80" t="n">
         <v>42</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.63</v>
+        <v>-0.65</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.86</v>
+        <v>-0.88</v>
       </c>
       <c r="G80" t="n">
-        <v>-2.36</v>
+        <v>-2.38</v>
       </c>
       <c r="H80" t="n">
-        <v>-9.359999999999999</v>
+        <v>-9.34</v>
       </c>
       <c r="I80" t="n">
         <v>0.46</v>
@@ -9236,28 +9244,28 @@
         <v>2.41</v>
       </c>
       <c r="L80" t="n">
-        <v>89.83</v>
+        <v>89.81</v>
       </c>
       <c r="M80" t="n">
-        <v>90.92</v>
+        <v>90.91</v>
       </c>
       <c r="N80" t="n">
-        <v>87.64</v>
+        <v>87.63</v>
       </c>
       <c r="O80" t="n">
-        <v>95.41</v>
+        <v>95.39</v>
       </c>
       <c r="P80" t="n">
         <v>1.63</v>
       </c>
       <c r="Q80" t="n">
-        <v>47.63</v>
+        <v>47.58</v>
       </c>
       <c r="R80" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="S80" t="n">
-        <v>-3.03</v>
+        <v>-3.05</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9318,22 +9326,22 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>74.87</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="D81" t="n">
         <v>42</v>
       </c>
       <c r="E81" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.01</v>
       </c>
       <c r="G81" t="n">
-        <v>4.89</v>
+        <v>4.82</v>
       </c>
       <c r="H81" t="n">
-        <v>-9.44</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="I81" t="n">
         <v>0.42</v>
@@ -9342,31 +9350,31 @@
         <v>2.61</v>
       </c>
       <c r="K81" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="L81" t="n">
-        <v>73.95999999999999</v>
+        <v>73.91</v>
       </c>
       <c r="M81" t="n">
-        <v>75.26000000000001</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="N81" t="n">
-        <v>71.34999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="O81" t="n">
-        <v>80.61</v>
+        <v>80.56</v>
       </c>
       <c r="P81" t="n">
         <v>1.63</v>
       </c>
       <c r="Q81" t="n">
-        <v>50.75</v>
+        <v>50.61</v>
       </c>
       <c r="R81" t="n">
-        <v>-0.38</v>
+        <v>-0.45</v>
       </c>
       <c r="S81" t="n">
-        <v>-7.37</v>
+        <v>-7.44</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9385,7 +9393,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
@@ -9427,19 +9435,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>75.95999999999999</v>
+        <v>75.92</v>
       </c>
       <c r="D82" t="n">
         <v>42</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.04</v>
+        <v>-1.08</v>
       </c>
       <c r="F82" t="n">
-        <v>-14.11</v>
+        <v>-14.15</v>
       </c>
       <c r="G82" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H82" t="n">
         <v>-22.61</v>
@@ -9454,28 +9462,28 @@
         <v>5.16</v>
       </c>
       <c r="L82" t="n">
-        <v>74.58</v>
+        <v>74.55</v>
       </c>
       <c r="M82" t="n">
-        <v>76.54000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="N82" t="n">
-        <v>70.66</v>
+        <v>70.63</v>
       </c>
       <c r="O82" t="n">
-        <v>84.58</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="P82" t="n">
         <v>1.63</v>
       </c>
       <c r="Q82" t="n">
-        <v>55.15</v>
+        <v>55.1</v>
       </c>
       <c r="R82" t="n">
-        <v>-2.55</v>
+        <v>-2.59</v>
       </c>
       <c r="S82" t="n">
-        <v>-13.3</v>
+        <v>-13.34</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9536,22 +9544,22 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>497.79</v>
+        <v>498.04</v>
       </c>
       <c r="D83" t="n">
         <v>38</v>
       </c>
       <c r="E83" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="F83" t="n">
-        <v>-2.42</v>
+        <v>-2.38</v>
       </c>
       <c r="G83" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H83" t="n">
-        <v>-10.92</v>
+        <v>-10.84</v>
       </c>
       <c r="I83" t="n">
         <v>0.54</v>
@@ -9563,28 +9571,28 @@
         <v>2.28</v>
       </c>
       <c r="L83" t="n">
-        <v>493.82</v>
+        <v>494.07</v>
       </c>
       <c r="M83" t="n">
-        <v>499.49</v>
+        <v>499.74</v>
       </c>
       <c r="N83" t="n">
-        <v>482.49</v>
+        <v>482.74</v>
       </c>
       <c r="O83" t="n">
-        <v>522.72</v>
+        <v>522.97</v>
       </c>
       <c r="P83" t="n">
         <v>1.63</v>
       </c>
       <c r="Q83" t="n">
-        <v>46.88</v>
+        <v>47.02</v>
       </c>
       <c r="R83" t="n">
-        <v>-0.54</v>
+        <v>-0.49</v>
       </c>
       <c r="S83" t="n">
-        <v>-6.82</v>
+        <v>-6.77</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9645,55 +9653,55 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>75.69</v>
+        <v>75.63</v>
       </c>
       <c r="D84" t="n">
         <v>35</v>
       </c>
       <c r="E84" t="n">
-        <v>-3.02</v>
+        <v>-3.1</v>
       </c>
       <c r="F84" t="n">
-        <v>-4.55</v>
+        <v>-4.63</v>
       </c>
       <c r="G84" t="n">
-        <v>5.02</v>
+        <v>4.94</v>
       </c>
       <c r="H84" t="n">
-        <v>-13.05</v>
+        <v>-13.09</v>
       </c>
       <c r="I84" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="J84" t="n">
         <v>2.4</v>
       </c>
       <c r="K84" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="L84" t="n">
-        <v>74.84999999999999</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="M84" t="n">
-        <v>76.05</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="N84" t="n">
-        <v>72.45</v>
+        <v>72.39</v>
       </c>
       <c r="O84" t="n">
-        <v>80.98</v>
+        <v>80.92</v>
       </c>
       <c r="P84" t="n">
         <v>1.63</v>
       </c>
       <c r="Q84" t="n">
-        <v>49.6</v>
+        <v>49.44</v>
       </c>
       <c r="R84" t="n">
-        <v>-1.44</v>
+        <v>-1.52</v>
       </c>
       <c r="S84" t="n">
-        <v>-6.19</v>
+        <v>-6.27</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9712,7 +9720,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
@@ -9754,22 +9762,22 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>140.45</v>
+        <v>140.42</v>
       </c>
       <c r="D85" t="n">
         <v>31</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.17</v>
+        <v>-0.19</v>
       </c>
       <c r="F85" t="n">
-        <v>-20.98</v>
+        <v>-20.99</v>
       </c>
       <c r="G85" t="n">
-        <v>9.07</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>-29.48</v>
+        <v>-29.45</v>
       </c>
       <c r="I85" t="n">
         <v>0.37</v>
@@ -9778,31 +9786,31 @@
         <v>8.07</v>
       </c>
       <c r="K85" t="n">
-        <v>5.74</v>
+        <v>5.75</v>
       </c>
       <c r="L85" t="n">
-        <v>137.63</v>
+        <v>137.6</v>
       </c>
       <c r="M85" t="n">
-        <v>141.66</v>
+        <v>141.63</v>
       </c>
       <c r="N85" t="n">
-        <v>129.56</v>
+        <v>129.53</v>
       </c>
       <c r="O85" t="n">
-        <v>158.2</v>
+        <v>158.17</v>
       </c>
       <c r="P85" t="n">
         <v>1.63</v>
       </c>
       <c r="Q85" t="n">
-        <v>22.55</v>
+        <v>22.54</v>
       </c>
       <c r="R85" t="n">
-        <v>-9.619999999999999</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="S85" t="n">
-        <v>-21.89</v>
+        <v>-21.9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9821,7 +9829,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
@@ -9863,22 +9871,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>565.38</v>
+        <v>564.9299999999999</v>
       </c>
       <c r="D86" t="n">
         <v>30</v>
       </c>
       <c r="E86" t="n">
-        <v>-2.63</v>
+        <v>-2.71</v>
       </c>
       <c r="F86" t="n">
-        <v>-2.52</v>
+        <v>-2.6</v>
       </c>
       <c r="G86" t="n">
-        <v>-12.03</v>
+        <v>-12.1</v>
       </c>
       <c r="H86" t="n">
-        <v>-11.02</v>
+        <v>-11.06</v>
       </c>
       <c r="I86" t="n">
         <v>0.6</v>
@@ -9890,28 +9898,28 @@
         <v>2.44</v>
       </c>
       <c r="L86" t="n">
-        <v>560.55</v>
+        <v>560.1</v>
       </c>
       <c r="M86" t="n">
-        <v>567.45</v>
+        <v>567</v>
       </c>
       <c r="N86" t="n">
-        <v>546.75</v>
+        <v>546.3</v>
       </c>
       <c r="O86" t="n">
-        <v>595.74</v>
+        <v>595.29</v>
       </c>
       <c r="P86" t="n">
         <v>1.63</v>
       </c>
       <c r="Q86" t="n">
-        <v>38.57</v>
+        <v>38.31</v>
       </c>
       <c r="R86" t="n">
-        <v>-1.65</v>
+        <v>-1.73</v>
       </c>
       <c r="S86" t="n">
-        <v>-4.97</v>
+        <v>-5.05</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9972,25 +9980,25 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>280.52</v>
+        <v>280.36</v>
       </c>
       <c r="D87" t="n">
         <v>30</v>
       </c>
       <c r="E87" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="F87" t="n">
-        <v>-6.52</v>
+        <v>-6.57</v>
       </c>
       <c r="G87" t="n">
-        <v>-15.3</v>
+        <v>-15.35</v>
       </c>
       <c r="H87" t="n">
-        <v>-15.02</v>
+        <v>-15.03</v>
       </c>
       <c r="I87" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="J87" t="n">
         <v>5.91</v>
@@ -9999,28 +10007,28 @@
         <v>2.11</v>
       </c>
       <c r="L87" t="n">
-        <v>278.45</v>
+        <v>278.29</v>
       </c>
       <c r="M87" t="n">
-        <v>281.41</v>
+        <v>281.25</v>
       </c>
       <c r="N87" t="n">
-        <v>272.54</v>
+        <v>272.38</v>
       </c>
       <c r="O87" t="n">
-        <v>293.52</v>
+        <v>293.36</v>
       </c>
       <c r="P87" t="n">
         <v>1.63</v>
       </c>
       <c r="Q87" t="n">
-        <v>29.84</v>
+        <v>29.69</v>
       </c>
       <c r="R87" t="n">
-        <v>-1.36</v>
+        <v>-1.42</v>
       </c>
       <c r="S87" t="n">
-        <v>-7.99</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10081,7 +10089,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>301.69</v>
+        <v>301.7</v>
       </c>
       <c r="D88" t="n">
         <v>28</v>
@@ -10096,10 +10104,10 @@
         <v>2</v>
       </c>
       <c r="H88" t="n">
-        <v>-12.12</v>
+        <v>-12.08</v>
       </c>
       <c r="I88" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="J88" t="n">
         <v>6.29</v>
@@ -10108,25 +10116,25 @@
         <v>2.09</v>
       </c>
       <c r="L88" t="n">
-        <v>299.49</v>
+        <v>299.5</v>
       </c>
       <c r="M88" t="n">
-        <v>302.63</v>
+        <v>302.64</v>
       </c>
       <c r="N88" t="n">
-        <v>293.2</v>
+        <v>293.21</v>
       </c>
       <c r="O88" t="n">
-        <v>315.53</v>
+        <v>315.54</v>
       </c>
       <c r="P88" t="n">
         <v>1.63</v>
       </c>
       <c r="Q88" t="n">
-        <v>39.24</v>
+        <v>39.25</v>
       </c>
       <c r="R88" t="n">
-        <v>-1.4</v>
+        <v>-1.39</v>
       </c>
       <c r="S88" t="n">
         <v>-4.62</v>
@@ -10205,7 +10213,7 @@
         <v>2.05</v>
       </c>
       <c r="H89" t="n">
-        <v>-12.2</v>
+        <v>-12.16</v>
       </c>
       <c r="I89" t="n">
         <v>0.71</v>
@@ -10299,25 +10307,25 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>605.49</v>
+        <v>604.84</v>
       </c>
       <c r="D90" t="n">
         <v>28</v>
       </c>
       <c r="E90" t="n">
-        <v>-1.81</v>
+        <v>-1.91</v>
       </c>
       <c r="F90" t="n">
-        <v>-10.26</v>
+        <v>-10.36</v>
       </c>
       <c r="G90" t="n">
-        <v>-5.21</v>
+        <v>-5.31</v>
       </c>
       <c r="H90" t="n">
-        <v>-18.76</v>
+        <v>-18.82</v>
       </c>
       <c r="I90" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="J90" t="n">
         <v>13.2</v>
@@ -10326,28 +10334,28 @@
         <v>2.18</v>
       </c>
       <c r="L90" t="n">
-        <v>600.88</v>
+        <v>600.22</v>
       </c>
       <c r="M90" t="n">
-        <v>607.47</v>
+        <v>606.8200000000001</v>
       </c>
       <c r="N90" t="n">
-        <v>587.6799999999999</v>
+        <v>587.03</v>
       </c>
       <c r="O90" t="n">
-        <v>634.53</v>
+        <v>633.87</v>
       </c>
       <c r="P90" t="n">
         <v>1.63</v>
       </c>
       <c r="Q90" t="n">
-        <v>45.91</v>
+        <v>45.45</v>
       </c>
       <c r="R90" t="n">
-        <v>-3.11</v>
+        <v>-3.21</v>
       </c>
       <c r="S90" t="n">
-        <v>-11.28</v>
+        <v>-11.38</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10366,7 +10374,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
@@ -10408,25 +10416,25 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>25.88</v>
+        <v>25.84</v>
       </c>
       <c r="D91" t="n">
         <v>26</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.31</v>
+        <v>-0.44</v>
       </c>
       <c r="F91" t="n">
-        <v>-1.84</v>
+        <v>-1.97</v>
       </c>
       <c r="G91" t="n">
-        <v>-3.07</v>
+        <v>-3.2</v>
       </c>
       <c r="H91" t="n">
-        <v>-10.34</v>
+        <v>-10.43</v>
       </c>
       <c r="I91" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0.48</v>
@@ -10435,28 +10443,28 @@
         <v>1.84</v>
       </c>
       <c r="L91" t="n">
-        <v>25.71</v>
+        <v>25.68</v>
       </c>
       <c r="M91" t="n">
-        <v>25.95</v>
+        <v>25.92</v>
       </c>
       <c r="N91" t="n">
-        <v>25.24</v>
+        <v>25.2</v>
       </c>
       <c r="O91" t="n">
-        <v>26.93</v>
+        <v>26.89</v>
       </c>
       <c r="P91" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q91" t="n">
-        <v>42.27</v>
+        <v>41.45</v>
       </c>
       <c r="R91" t="n">
-        <v>-0.18</v>
+        <v>-0.31</v>
       </c>
       <c r="S91" t="n">
-        <v>-4.61</v>
+        <v>-4.74</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10517,22 +10525,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>135.99</v>
+        <v>135.76</v>
       </c>
       <c r="D92" t="n">
         <v>23</v>
       </c>
       <c r="E92" t="n">
-        <v>4.57</v>
+        <v>4.39</v>
       </c>
       <c r="F92" t="n">
-        <v>-10.9</v>
+        <v>-11.05</v>
       </c>
       <c r="G92" t="n">
-        <v>5.55</v>
+        <v>5.37</v>
       </c>
       <c r="H92" t="n">
-        <v>-19.4</v>
+        <v>-19.51</v>
       </c>
       <c r="I92" t="n">
         <v>0.42</v>
@@ -10541,31 +10549,31 @@
         <v>5.67</v>
       </c>
       <c r="K92" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="L92" t="n">
-        <v>134</v>
+        <v>133.77</v>
       </c>
       <c r="M92" t="n">
-        <v>136.84</v>
+        <v>136.61</v>
       </c>
       <c r="N92" t="n">
-        <v>128.33</v>
+        <v>128.1</v>
       </c>
       <c r="O92" t="n">
-        <v>148.47</v>
+        <v>148.24</v>
       </c>
       <c r="P92" t="n">
         <v>1.63</v>
       </c>
       <c r="Q92" t="n">
-        <v>45.77</v>
+        <v>45.43</v>
       </c>
       <c r="R92" t="n">
-        <v>-1.38</v>
+        <v>-1.53</v>
       </c>
       <c r="S92" t="n">
-        <v>-9.51</v>
+        <v>-9.67</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10584,7 +10592,7 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
@@ -10626,55 +10634,55 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>15.7</v>
+        <v>15.65</v>
       </c>
       <c r="D93" t="n">
         <v>23</v>
       </c>
       <c r="E93" t="n">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="F93" t="n">
-        <v>-17.6</v>
+        <v>-17.86</v>
       </c>
       <c r="G93" t="n">
-        <v>-15.84</v>
+        <v>-16.1</v>
       </c>
       <c r="H93" t="n">
-        <v>-26.1</v>
+        <v>-26.32</v>
       </c>
       <c r="I93" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="J93" t="n">
         <v>0.68</v>
       </c>
       <c r="K93" t="n">
-        <v>4.36</v>
+        <v>4.37</v>
       </c>
       <c r="L93" t="n">
-        <v>15.47</v>
+        <v>15.42</v>
       </c>
       <c r="M93" t="n">
-        <v>15.81</v>
+        <v>15.76</v>
       </c>
       <c r="N93" t="n">
-        <v>14.78</v>
+        <v>14.73</v>
       </c>
       <c r="O93" t="n">
-        <v>17.21</v>
+        <v>17.16</v>
       </c>
       <c r="P93" t="n">
         <v>1.63</v>
       </c>
       <c r="Q93" t="n">
-        <v>46.21</v>
+        <v>45.68</v>
       </c>
       <c r="R93" t="n">
-        <v>-4.22</v>
+        <v>-4.51</v>
       </c>
       <c r="S93" t="n">
-        <v>-18.08</v>
+        <v>-18.34</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10735,55 +10743,55 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>88.27</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="D94" t="n">
         <v>22</v>
       </c>
       <c r="E94" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="F94" t="n">
-        <v>-5.33</v>
+        <v>-5.45</v>
       </c>
       <c r="G94" t="n">
-        <v>13.11</v>
+        <v>12.96</v>
       </c>
       <c r="H94" t="n">
-        <v>-13.83</v>
+        <v>-13.91</v>
       </c>
       <c r="I94" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="J94" t="n">
         <v>2.38</v>
       </c>
       <c r="K94" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="L94" t="n">
-        <v>87.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="M94" t="n">
-        <v>88.63</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="N94" t="n">
-        <v>85.06</v>
+        <v>84.94</v>
       </c>
       <c r="O94" t="n">
-        <v>93.5</v>
+        <v>93.39</v>
       </c>
       <c r="P94" t="n">
         <v>1.63</v>
       </c>
       <c r="Q94" t="n">
-        <v>33.25</v>
+        <v>33.01</v>
       </c>
       <c r="R94" t="n">
-        <v>-1.46</v>
+        <v>-1.58</v>
       </c>
       <c r="S94" t="n">
-        <v>-6.79</v>
+        <v>-6.91</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10802,7 +10810,7 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
@@ -10844,22 +10852,22 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>222.32</v>
+        <v>222.09</v>
       </c>
       <c r="D95" t="n">
         <v>21</v>
       </c>
       <c r="E95" t="n">
-        <v>-7.6</v>
+        <v>-7.69</v>
       </c>
       <c r="F95" t="n">
-        <v>-3.87</v>
+        <v>-3.97</v>
       </c>
       <c r="G95" t="n">
-        <v>-4.74</v>
+        <v>-4.84</v>
       </c>
       <c r="H95" t="n">
-        <v>-12.37</v>
+        <v>-12.43</v>
       </c>
       <c r="I95" t="n">
         <v>0.62</v>
@@ -10871,28 +10879,28 @@
         <v>3.29</v>
       </c>
       <c r="L95" t="n">
-        <v>219.76</v>
+        <v>219.53</v>
       </c>
       <c r="M95" t="n">
-        <v>223.42</v>
+        <v>223.19</v>
       </c>
       <c r="N95" t="n">
-        <v>212.45</v>
+        <v>212.22</v>
       </c>
       <c r="O95" t="n">
-        <v>238.41</v>
+        <v>238.18</v>
       </c>
       <c r="P95" t="n">
         <v>1.63</v>
       </c>
       <c r="Q95" t="n">
-        <v>44.66</v>
+        <v>44.46</v>
       </c>
       <c r="R95" t="n">
-        <v>-2.84</v>
+        <v>-2.94</v>
       </c>
       <c r="S95" t="n">
-        <v>-8.91</v>
+        <v>-9.01</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10953,25 +10961,25 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>44.23</v>
+        <v>44.22</v>
       </c>
       <c r="D96" t="n">
         <v>20</v>
       </c>
       <c r="E96" t="n">
-        <v>-2.21</v>
+        <v>-2.23</v>
       </c>
       <c r="F96" t="n">
-        <v>-13.65</v>
+        <v>-13.67</v>
       </c>
       <c r="G96" t="n">
-        <v>-5.65</v>
+        <v>-5.67</v>
       </c>
       <c r="H96" t="n">
-        <v>-22.15</v>
+        <v>-22.13</v>
       </c>
       <c r="I96" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="J96" t="n">
         <v>1.41</v>
@@ -10980,28 +10988,28 @@
         <v>3.2</v>
       </c>
       <c r="L96" t="n">
-        <v>43.73</v>
+        <v>43.72</v>
       </c>
       <c r="M96" t="n">
-        <v>44.44</v>
+        <v>44.43</v>
       </c>
       <c r="N96" t="n">
-        <v>42.32</v>
+        <v>42.31</v>
       </c>
       <c r="O96" t="n">
-        <v>47.34</v>
+        <v>47.33</v>
       </c>
       <c r="P96" t="n">
         <v>1.63</v>
       </c>
       <c r="Q96" t="n">
-        <v>13.29</v>
+        <v>13.18</v>
       </c>
       <c r="R96" t="n">
-        <v>-6.25</v>
+        <v>-6.27</v>
       </c>
       <c r="S96" t="n">
-        <v>-14.73</v>
+        <v>-14.75</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11062,22 +11070,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1045.94</v>
+        <v>1045.37</v>
       </c>
       <c r="D97" t="n">
         <v>15</v>
       </c>
       <c r="E97" t="n">
-        <v>-4.4</v>
+        <v>-4.45</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.56</v>
+        <v>-1.61</v>
       </c>
       <c r="G97" t="n">
-        <v>-2.71</v>
+        <v>-2.76</v>
       </c>
       <c r="H97" t="n">
-        <v>-10.06</v>
+        <v>-10.07</v>
       </c>
       <c r="I97" t="n">
         <v>0.6</v>
@@ -11089,28 +11097,28 @@
         <v>2.2</v>
       </c>
       <c r="L97" t="n">
-        <v>1037.88</v>
+        <v>1037.31</v>
       </c>
       <c r="M97" t="n">
-        <v>1049.4</v>
+        <v>1048.83</v>
       </c>
       <c r="N97" t="n">
-        <v>1014.84</v>
+        <v>1014.27</v>
       </c>
       <c r="O97" t="n">
-        <v>1096.63</v>
+        <v>1096.06</v>
       </c>
       <c r="P97" t="n">
         <v>1.63</v>
       </c>
       <c r="Q97" t="n">
-        <v>44.41</v>
+        <v>44.23</v>
       </c>
       <c r="R97" t="n">
-        <v>-1.89</v>
+        <v>-1.94</v>
       </c>
       <c r="S97" t="n">
-        <v>-5.86</v>
+        <v>-5.91</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11171,25 +11179,25 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>75.58</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="D98" t="n">
         <v>15</v>
       </c>
       <c r="E98" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="F98" t="n">
-        <v>-5.67</v>
+        <v>-5.69</v>
       </c>
       <c r="G98" t="n">
-        <v>-10.12</v>
+        <v>-10.14</v>
       </c>
       <c r="H98" t="n">
-        <v>-14.17</v>
+        <v>-14.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="J98" t="n">
         <v>1.9</v>
@@ -11198,28 +11206,28 @@
         <v>2.51</v>
       </c>
       <c r="L98" t="n">
-        <v>74.92</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="M98" t="n">
-        <v>75.86</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="N98" t="n">
-        <v>73.02</v>
+        <v>73</v>
       </c>
       <c r="O98" t="n">
-        <v>79.76000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="P98" t="n">
         <v>1.63</v>
       </c>
       <c r="Q98" t="n">
-        <v>31.48</v>
+        <v>31.41</v>
       </c>
       <c r="R98" t="n">
-        <v>-2.46</v>
+        <v>-2.48</v>
       </c>
       <c r="S98" t="n">
-        <v>-8.039999999999999</v>
+        <v>-8.06</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11280,25 +11288,25 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>309.17</v>
+        <v>308.95</v>
       </c>
       <c r="D99" t="n">
         <v>15</v>
       </c>
       <c r="E99" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="F99" t="n">
-        <v>-8.93</v>
+        <v>-9</v>
       </c>
       <c r="G99" t="n">
-        <v>-19.05</v>
+        <v>-19.11</v>
       </c>
       <c r="H99" t="n">
-        <v>-17.43</v>
+        <v>-17.46</v>
       </c>
       <c r="I99" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="J99" t="n">
         <v>8.43</v>
@@ -11307,28 +11315,28 @@
         <v>2.73</v>
       </c>
       <c r="L99" t="n">
-        <v>306.22</v>
+        <v>306.01</v>
       </c>
       <c r="M99" t="n">
-        <v>310.43</v>
+        <v>310.22</v>
       </c>
       <c r="N99" t="n">
-        <v>297.8</v>
+        <v>297.58</v>
       </c>
       <c r="O99" t="n">
-        <v>327.71</v>
+        <v>327.49</v>
       </c>
       <c r="P99" t="n">
         <v>1.63</v>
       </c>
       <c r="Q99" t="n">
-        <v>35.53</v>
+        <v>35.32</v>
       </c>
       <c r="R99" t="n">
-        <v>-2.49</v>
+        <v>-2.56</v>
       </c>
       <c r="S99" t="n">
-        <v>-9.289999999999999</v>
+        <v>-9.35</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11389,25 +11397,25 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>219.96</v>
+        <v>219.81</v>
       </c>
       <c r="D100" t="n">
         <v>11</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.22</v>
+        <v>-0.29</v>
       </c>
       <c r="F100" t="n">
-        <v>-10.29</v>
+        <v>-10.35</v>
       </c>
       <c r="G100" t="n">
-        <v>-20.67</v>
+        <v>-20.72</v>
       </c>
       <c r="H100" t="n">
-        <v>-18.79</v>
+        <v>-18.81</v>
       </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="J100" t="n">
         <v>6.37</v>
@@ -11416,28 +11424,28 @@
         <v>2.9</v>
       </c>
       <c r="L100" t="n">
-        <v>217.73</v>
+        <v>217.58</v>
       </c>
       <c r="M100" t="n">
-        <v>220.92</v>
+        <v>220.77</v>
       </c>
       <c r="N100" t="n">
-        <v>211.36</v>
+        <v>211.21</v>
       </c>
       <c r="O100" t="n">
-        <v>233.98</v>
+        <v>233.83</v>
       </c>
       <c r="P100" t="n">
         <v>1.63</v>
       </c>
       <c r="Q100" t="n">
-        <v>30.52</v>
+        <v>30.3</v>
       </c>
       <c r="R100" t="n">
-        <v>-4.18</v>
+        <v>-4.25</v>
       </c>
       <c r="S100" t="n">
-        <v>-11.17</v>
+        <v>-11.23</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11498,55 +11506,55 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>447</v>
+        <v>447.72</v>
       </c>
       <c r="D101" t="n">
         <v>7</v>
       </c>
       <c r="E101" t="n">
-        <v>0.22</v>
+        <v>0.38</v>
       </c>
       <c r="F101" t="n">
-        <v>-13.03</v>
+        <v>-12.89</v>
       </c>
       <c r="G101" t="n">
-        <v>-13.22</v>
+        <v>-13.08</v>
       </c>
       <c r="H101" t="n">
-        <v>-21.53</v>
+        <v>-21.35</v>
       </c>
       <c r="I101" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="J101" t="n">
         <v>13.57</v>
       </c>
       <c r="K101" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="L101" t="n">
-        <v>442.25</v>
+        <v>442.97</v>
       </c>
       <c r="M101" t="n">
-        <v>449.04</v>
+        <v>449.76</v>
       </c>
       <c r="N101" t="n">
-        <v>428.68</v>
+        <v>429.4</v>
       </c>
       <c r="O101" t="n">
-        <v>476.86</v>
+        <v>477.58</v>
       </c>
       <c r="P101" t="n">
         <v>1.63</v>
       </c>
       <c r="Q101" t="n">
-        <v>32.7</v>
+        <v>32.96</v>
       </c>
       <c r="R101" t="n">
-        <v>-2.95</v>
+        <v>-2.81</v>
       </c>
       <c r="S101" t="n">
-        <v>-7.23</v>
+        <v>-7.08</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11607,22 +11615,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>202.13</v>
+        <v>202.4</v>
       </c>
       <c r="D102" t="n">
         <v>58</v>
       </c>
       <c r="E102" t="n">
-        <v>-5.18</v>
+        <v>-5.05</v>
       </c>
       <c r="F102" t="n">
-        <v>48.55</v>
+        <v>48.75</v>
       </c>
       <c r="G102" t="n">
-        <v>40.51</v>
+        <v>40.7</v>
       </c>
       <c r="H102" t="n">
-        <v>40.05</v>
+        <v>40.29</v>
       </c>
       <c r="I102" t="n">
         <v>0.35</v>
@@ -11631,31 +11639,31 @@
         <v>18.19</v>
       </c>
       <c r="K102" t="n">
-        <v>9</v>
+        <v>8.99</v>
       </c>
       <c r="L102" t="n">
-        <v>195.76</v>
+        <v>196.03</v>
       </c>
       <c r="M102" t="n">
-        <v>204.86</v>
+        <v>205.13</v>
       </c>
       <c r="N102" t="n">
-        <v>177.57</v>
+        <v>177.84</v>
       </c>
       <c r="O102" t="n">
-        <v>242.15</v>
+        <v>242.42</v>
       </c>
       <c r="P102" t="n">
         <v>1.63</v>
       </c>
       <c r="Q102" t="n">
-        <v>57.96</v>
+        <v>58.04</v>
       </c>
       <c r="R102" t="n">
-        <v>8.42</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S102" t="n">
-        <v>-18.46</v>
+        <v>-18.35</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11674,7 +11682,7 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>SOXX 19.49% · QQQ 8.5%</t>
+          <t>SOXX 19.54% · QQQ 8.46%</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
@@ -11699,7 +11707,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.49% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.46%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -11720,25 +11728,25 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>480.29</v>
+        <v>480</v>
       </c>
       <c r="D103" t="n">
         <v>53</v>
       </c>
       <c r="E103" t="n">
-        <v>5.9</v>
+        <v>5.84</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.71</v>
+        <v>-0.77</v>
       </c>
       <c r="G103" t="n">
-        <v>22.14</v>
+        <v>22.07</v>
       </c>
       <c r="H103" t="n">
-        <v>-9.210000000000001</v>
+        <v>-9.23</v>
       </c>
       <c r="I103" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="J103" t="n">
         <v>31.74</v>
@@ -11747,28 +11755,28 @@
         <v>6.61</v>
       </c>
       <c r="L103" t="n">
-        <v>469.18</v>
+        <v>468.89</v>
       </c>
       <c r="M103" t="n">
-        <v>485.05</v>
+        <v>484.76</v>
       </c>
       <c r="N103" t="n">
-        <v>437.45</v>
+        <v>437.16</v>
       </c>
       <c r="O103" t="n">
-        <v>550.11</v>
+        <v>549.8200000000001</v>
       </c>
       <c r="P103" t="n">
         <v>1.63</v>
       </c>
       <c r="Q103" t="n">
-        <v>57.2</v>
+        <v>57.15</v>
       </c>
       <c r="R103" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="S103" t="n">
-        <v>-6.81</v>
+        <v>-6.87</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11787,7 +11795,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
@@ -11829,22 +11837,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>178.46</v>
+        <v>178.15</v>
       </c>
       <c r="D104" t="n">
         <v>52</v>
       </c>
       <c r="E104" t="n">
-        <v>7.61</v>
+        <v>7.42</v>
       </c>
       <c r="F104" t="n">
-        <v>-5.97</v>
+        <v>-6.14</v>
       </c>
       <c r="G104" t="n">
-        <v>-3.51</v>
+        <v>-3.68</v>
       </c>
       <c r="H104" t="n">
-        <v>-14.47</v>
+        <v>-14.6</v>
       </c>
       <c r="I104" t="n">
         <v>0.54</v>
@@ -11853,31 +11861,31 @@
         <v>7.39</v>
       </c>
       <c r="K104" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="L104" t="n">
-        <v>175.87</v>
+        <v>175.56</v>
       </c>
       <c r="M104" t="n">
-        <v>179.57</v>
+        <v>179.26</v>
       </c>
       <c r="N104" t="n">
-        <v>168.48</v>
+        <v>168.17</v>
       </c>
       <c r="O104" t="n">
-        <v>194.73</v>
+        <v>194.42</v>
       </c>
       <c r="P104" t="n">
         <v>1.63</v>
       </c>
       <c r="Q104" t="n">
-        <v>51.71</v>
+        <v>51.42</v>
       </c>
       <c r="R104" t="n">
-        <v>-0.01</v>
+        <v>-0.17</v>
       </c>
       <c r="S104" t="n">
-        <v>-6.23</v>
+        <v>-6.39</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11896,7 +11904,7 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
@@ -11938,22 +11946,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>184.93</v>
+        <v>184.95</v>
       </c>
       <c r="D105" t="n">
         <v>47</v>
       </c>
       <c r="E105" t="n">
-        <v>-2.55</v>
+        <v>-2.53</v>
       </c>
       <c r="F105" t="n">
-        <v>-1.37</v>
+        <v>-1.36</v>
       </c>
       <c r="G105" t="n">
-        <v>26.99</v>
+        <v>27</v>
       </c>
       <c r="H105" t="n">
-        <v>-9.869999999999999</v>
+        <v>-9.82</v>
       </c>
       <c r="I105" t="n">
         <v>0.38</v>
@@ -11965,16 +11973,16 @@
         <v>5.13</v>
       </c>
       <c r="L105" t="n">
-        <v>181.61</v>
+        <v>181.63</v>
       </c>
       <c r="M105" t="n">
-        <v>186.35</v>
+        <v>186.37</v>
       </c>
       <c r="N105" t="n">
-        <v>172.13</v>
+        <v>172.15</v>
       </c>
       <c r="O105" t="n">
-        <v>205.79</v>
+        <v>205.81</v>
       </c>
       <c r="P105" t="n">
         <v>1.63</v>
@@ -11983,10 +11991,10 @@
         <v>66.8</v>
       </c>
       <c r="R105" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S105" t="n">
-        <v>-7.86</v>
+        <v>-7.85</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12005,7 +12013,7 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
@@ -12047,55 +12055,55 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8.470000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="D106" t="n">
         <v>42</v>
       </c>
       <c r="E106" t="n">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
       <c r="F106" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="G106" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="H106" t="n">
-        <v>-5.46</v>
+        <v>-5.54</v>
       </c>
       <c r="I106" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="J106" t="n">
         <v>0.65</v>
       </c>
       <c r="K106" t="n">
-        <v>7.72</v>
+        <v>7.73</v>
       </c>
       <c r="L106" t="n">
-        <v>8.24</v>
+        <v>8.23</v>
       </c>
       <c r="M106" t="n">
-        <v>8.57</v>
+        <v>8.56</v>
       </c>
       <c r="N106" t="n">
-        <v>7.59</v>
+        <v>7.58</v>
       </c>
       <c r="O106" t="n">
-        <v>9.91</v>
+        <v>9.9</v>
       </c>
       <c r="P106" t="n">
         <v>1.64</v>
       </c>
       <c r="Q106" t="n">
-        <v>55.28</v>
+        <v>55.19</v>
       </c>
       <c r="R106" t="n">
-        <v>-0.98</v>
+        <v>-1.09</v>
       </c>
       <c r="S106" t="n">
-        <v>-15.68</v>
+        <v>-15.78</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12114,7 +12122,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
@@ -12156,55 +12164,55 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>146.44</v>
+        <v>145.73</v>
       </c>
       <c r="D107" t="n">
         <v>24</v>
       </c>
       <c r="E107" t="n">
-        <v>-4.98</v>
+        <v>-5.44</v>
       </c>
       <c r="F107" t="n">
-        <v>-10.88</v>
+        <v>-11.31</v>
       </c>
       <c r="G107" t="n">
-        <v>3.07</v>
+        <v>2.57</v>
       </c>
       <c r="H107" t="n">
-        <v>-19.38</v>
+        <v>-19.77</v>
       </c>
       <c r="I107" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>10</v>
       </c>
       <c r="K107" t="n">
-        <v>6.83</v>
+        <v>6.87</v>
       </c>
       <c r="L107" t="n">
-        <v>142.94</v>
+        <v>142.23</v>
       </c>
       <c r="M107" t="n">
-        <v>147.94</v>
+        <v>147.23</v>
       </c>
       <c r="N107" t="n">
-        <v>132.93</v>
+        <v>132.22</v>
       </c>
       <c r="O107" t="n">
-        <v>168.45</v>
+        <v>167.74</v>
       </c>
       <c r="P107" t="n">
         <v>1.63</v>
       </c>
       <c r="Q107" t="n">
-        <v>49.44</v>
+        <v>48.95</v>
       </c>
       <c r="R107" t="n">
-        <v>-6.88</v>
+        <v>-7.32</v>
       </c>
       <c r="S107" t="n">
-        <v>-17.33</v>
+        <v>-17.73</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12223,7 +12231,7 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
@@ -12280,10 +12288,10 @@
         <v>3.2</v>
       </c>
       <c r="H108" t="n">
-        <v>-24.91</v>
+        <v>-24.87</v>
       </c>
       <c r="I108" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J108" t="n">
         <v>1.92</v>
@@ -12332,7 +12340,7 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
@@ -12374,55 +12382,55 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5.91</v>
+        <v>5.89</v>
       </c>
       <c r="D109" t="n">
         <v>20</v>
       </c>
       <c r="E109" t="n">
-        <v>-9.43</v>
+        <v>-9.59</v>
       </c>
       <c r="F109" t="n">
-        <v>-2.56</v>
+        <v>-2.72</v>
       </c>
       <c r="G109" t="n">
-        <v>-17.87</v>
+        <v>-18.01</v>
       </c>
       <c r="H109" t="n">
-        <v>-11.06</v>
+        <v>-11.18</v>
       </c>
       <c r="I109" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="J109" t="n">
         <v>0.41</v>
       </c>
       <c r="K109" t="n">
-        <v>7.03</v>
+        <v>7.04</v>
       </c>
       <c r="L109" t="n">
-        <v>5.76</v>
+        <v>5.75</v>
       </c>
       <c r="M109" t="n">
-        <v>5.97</v>
+        <v>5.96</v>
       </c>
       <c r="N109" t="n">
-        <v>5.34</v>
+        <v>5.33</v>
       </c>
       <c r="O109" t="n">
-        <v>6.82</v>
+        <v>6.81</v>
       </c>
       <c r="P109" t="n">
         <v>1.62</v>
       </c>
       <c r="Q109" t="n">
-        <v>53.83</v>
+        <v>53.58</v>
       </c>
       <c r="R109" t="n">
-        <v>-2.27</v>
+        <v>-2.43</v>
       </c>
       <c r="S109" t="n">
-        <v>-12.52</v>
+        <v>-12.67</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12483,55 +12491,55 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>20.91</v>
+        <v>20.88</v>
       </c>
       <c r="D110" t="n">
         <v>6</v>
       </c>
       <c r="E110" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="F110" t="n">
-        <v>-11.25</v>
+        <v>-11.38</v>
       </c>
       <c r="G110" t="n">
-        <v>-16.16</v>
+        <v>-16.28</v>
       </c>
       <c r="H110" t="n">
-        <v>-19.75</v>
+        <v>-19.84</v>
       </c>
       <c r="I110" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="J110" t="n">
         <v>1.36</v>
       </c>
       <c r="K110" t="n">
-        <v>6.5</v>
+        <v>6.51</v>
       </c>
       <c r="L110" t="n">
-        <v>20.43</v>
+        <v>20.4</v>
       </c>
       <c r="M110" t="n">
-        <v>21.11</v>
+        <v>21.08</v>
       </c>
       <c r="N110" t="n">
-        <v>19.08</v>
+        <v>19.05</v>
       </c>
       <c r="O110" t="n">
-        <v>23.9</v>
+        <v>23.87</v>
       </c>
       <c r="P110" t="n">
         <v>1.63</v>
       </c>
       <c r="Q110" t="n">
-        <v>34.63</v>
+        <v>34.51</v>
       </c>
       <c r="R110" t="n">
-        <v>-7.78</v>
+        <v>-7.91</v>
       </c>
       <c r="S110" t="n">
-        <v>-15.92</v>
+        <v>-16.04</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12550,7 +12558,7 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
@@ -12592,22 +12600,22 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>104.67</v>
+        <v>104.58</v>
       </c>
       <c r="D111" t="n">
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>9.710000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="F111" t="n">
-        <v>-20.68</v>
+        <v>-20.74</v>
       </c>
       <c r="G111" t="n">
-        <v>-10.49</v>
+        <v>-10.56</v>
       </c>
       <c r="H111" t="n">
-        <v>-29.18</v>
+        <v>-29.2</v>
       </c>
       <c r="I111" t="n">
         <v>0.32</v>
@@ -12619,28 +12627,28 @@
         <v>6.21</v>
       </c>
       <c r="L111" t="n">
-        <v>102.39</v>
+        <v>102.31</v>
       </c>
       <c r="M111" t="n">
-        <v>105.64</v>
+        <v>105.56</v>
       </c>
       <c r="N111" t="n">
-        <v>95.89</v>
+        <v>95.81</v>
       </c>
       <c r="O111" t="n">
-        <v>118.96</v>
+        <v>118.88</v>
       </c>
       <c r="P111" t="n">
         <v>1.63</v>
       </c>
       <c r="Q111" t="n">
-        <v>37.02</v>
+        <v>36.94</v>
       </c>
       <c r="R111" t="n">
-        <v>-6.24</v>
+        <v>-6.31</v>
       </c>
       <c r="S111" t="n">
-        <v>-19.67</v>
+        <v>-19.74</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12659,7 +12667,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -12701,25 +12709,25 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>195.28</v>
+        <v>195.25</v>
       </c>
       <c r="D112" t="n">
         <v>12</v>
       </c>
       <c r="E112" t="n">
-        <v>-3.23</v>
+        <v>-3.25</v>
       </c>
       <c r="F112" t="n">
-        <v>-5.31</v>
+        <v>-5.33</v>
       </c>
       <c r="G112" t="n">
-        <v>20.52</v>
+        <v>20.5</v>
       </c>
       <c r="H112" t="n">
-        <v>-13.81</v>
+        <v>-13.79</v>
       </c>
       <c r="I112" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="J112" t="n">
         <v>14.04</v>
@@ -12728,28 +12736,28 @@
         <v>7.19</v>
       </c>
       <c r="L112" t="n">
-        <v>190.37</v>
+        <v>190.34</v>
       </c>
       <c r="M112" t="n">
-        <v>197.39</v>
+        <v>197.36</v>
       </c>
       <c r="N112" t="n">
-        <v>176.33</v>
+        <v>176.3</v>
       </c>
       <c r="O112" t="n">
-        <v>226.16</v>
+        <v>226.13</v>
       </c>
       <c r="P112" t="n">
         <v>1.63</v>
       </c>
       <c r="Q112" t="n">
-        <v>53.66</v>
+        <v>53.64</v>
       </c>
       <c r="R112" t="n">
-        <v>-1.22</v>
+        <v>-1.23</v>
       </c>
       <c r="S112" t="n">
-        <v>-12.17</v>
+        <v>-12.19</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12768,7 +12776,7 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>BTC-USD 1.64% · ETH-USD -5.09%</t>
+          <t>BTC-USD 1.53% · ETH-USD -5.24%</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
@@ -12794,7 +12802,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.64% · ETH-USD -5.09%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Sector no acompaña: BTC-USD 1.53% · ETH-USD -5.24%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -12810,22 +12818,22 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>168.56</v>
+        <v>168.28</v>
       </c>
       <c r="D113" t="n">
         <v>12</v>
       </c>
       <c r="E113" t="n">
-        <v>-5.32</v>
+        <v>-5.48</v>
       </c>
       <c r="F113" t="n">
-        <v>-6.02</v>
+        <v>-6.18</v>
       </c>
       <c r="G113" t="n">
-        <v>35.27</v>
+        <v>35.05</v>
       </c>
       <c r="H113" t="n">
-        <v>-14.52</v>
+        <v>-14.64</v>
       </c>
       <c r="I113" t="n">
         <v>0.36</v>
@@ -12834,31 +12842,31 @@
         <v>11.34</v>
       </c>
       <c r="K113" t="n">
-        <v>6.73</v>
+        <v>6.74</v>
       </c>
       <c r="L113" t="n">
-        <v>164.59</v>
+        <v>164.31</v>
       </c>
       <c r="M113" t="n">
-        <v>170.26</v>
+        <v>169.98</v>
       </c>
       <c r="N113" t="n">
-        <v>153.25</v>
+        <v>152.97</v>
       </c>
       <c r="O113" t="n">
-        <v>193.5</v>
+        <v>193.22</v>
       </c>
       <c r="P113" t="n">
         <v>1.63</v>
       </c>
       <c r="Q113" t="n">
-        <v>51.59</v>
+        <v>51.45</v>
       </c>
       <c r="R113" t="n">
-        <v>-4.41</v>
+        <v>-4.56</v>
       </c>
       <c r="S113" t="n">
-        <v>-14.44</v>
+        <v>-14.58</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12877,7 +12885,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>BTC-USD 1.64% · ETH-USD -5.09%</t>
+          <t>BTC-USD 1.53% · ETH-USD -5.24%</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -12903,7 +12911,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.64% · ETH-USD -5.09%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Sector no acompaña: BTC-USD 1.53% · ETH-USD -5.24%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -12919,25 +12927,25 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>710.47</v>
+        <v>710.65</v>
       </c>
       <c r="D114" t="n">
         <v>59</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.59</v>
+        <v>-0.57</v>
       </c>
       <c r="F114" t="n">
-        <v>8.449999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="G114" t="n">
-        <v>17.03</v>
+        <v>17.05</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="I114" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>11.31</v>
@@ -12946,28 +12954,28 @@
         <v>1.59</v>
       </c>
       <c r="L114" t="n">
-        <v>706.51</v>
+        <v>706.6900000000001</v>
       </c>
       <c r="M114" t="n">
-        <v>712.17</v>
+        <v>712.34</v>
       </c>
       <c r="N114" t="n">
-        <v>695.21</v>
+        <v>695.38</v>
       </c>
       <c r="O114" t="n">
-        <v>735.34</v>
+        <v>735.52</v>
       </c>
       <c r="P114" t="n">
         <v>1.63</v>
       </c>
       <c r="Q114" t="n">
-        <v>72.36</v>
+        <v>72.41</v>
       </c>
       <c r="R114" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="S114" t="n">
-        <v>-1.6</v>
+        <v>-1.58</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13028,25 +13036,25 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>180.08</v>
+        <v>180.05</v>
       </c>
       <c r="D115" t="n">
         <v>57</v>
       </c>
       <c r="E115" t="n">
-        <v>12.8</v>
+        <v>12.79</v>
       </c>
       <c r="F115" t="n">
-        <v>-5.27</v>
+        <v>-5.29</v>
       </c>
       <c r="G115" t="n">
-        <v>-7.69</v>
+        <v>-7.7</v>
       </c>
       <c r="H115" t="n">
-        <v>-13.77</v>
+        <v>-13.75</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="J115" t="n">
         <v>7.84</v>
@@ -13055,28 +13063,28 @@
         <v>4.35</v>
       </c>
       <c r="L115" t="n">
-        <v>177.34</v>
+        <v>177.31</v>
       </c>
       <c r="M115" t="n">
-        <v>181.26</v>
+        <v>181.23</v>
       </c>
       <c r="N115" t="n">
-        <v>169.5</v>
+        <v>169.47</v>
       </c>
       <c r="O115" t="n">
-        <v>197.32</v>
+        <v>197.29</v>
       </c>
       <c r="P115" t="n">
         <v>1.63</v>
       </c>
       <c r="Q115" t="n">
-        <v>51.23</v>
+        <v>51.21</v>
       </c>
       <c r="R115" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="S115" t="n">
-        <v>-2.55</v>
+        <v>-2.57</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13095,7 +13103,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
@@ -13137,22 +13145,22 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>328.34</v>
+        <v>328</v>
       </c>
       <c r="D116" t="n">
         <v>56</v>
       </c>
       <c r="E116" t="n">
-        <v>8.359999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="F116" t="n">
-        <v>21.81</v>
+        <v>21.69</v>
       </c>
       <c r="G116" t="n">
-        <v>5.07</v>
+        <v>4.96</v>
       </c>
       <c r="H116" t="n">
-        <v>13.31</v>
+        <v>13.23</v>
       </c>
       <c r="I116" t="n">
         <v>0.47</v>
@@ -13164,28 +13172,28 @@
         <v>5.58</v>
       </c>
       <c r="L116" t="n">
-        <v>321.93</v>
+        <v>321.59</v>
       </c>
       <c r="M116" t="n">
-        <v>331.09</v>
+        <v>330.75</v>
       </c>
       <c r="N116" t="n">
-        <v>303.61</v>
+        <v>303.27</v>
       </c>
       <c r="O116" t="n">
-        <v>368.64</v>
+        <v>368.3</v>
       </c>
       <c r="P116" t="n">
         <v>1.63</v>
       </c>
       <c r="Q116" t="n">
-        <v>83.95999999999999</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="R116" t="n">
-        <v>14.98</v>
+        <v>14.87</v>
       </c>
       <c r="S116" t="n">
-        <v>-5.98</v>
+        <v>-6.07</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13204,7 +13212,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -13246,25 +13254,25 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>173.59</v>
+        <v>173.49</v>
       </c>
       <c r="D117" t="n">
         <v>49</v>
       </c>
       <c r="E117" t="n">
-        <v>13.88</v>
+        <v>13.82</v>
       </c>
       <c r="F117" t="n">
-        <v>21.68</v>
+        <v>21.61</v>
       </c>
       <c r="G117" t="n">
-        <v>16.22</v>
+        <v>16.16</v>
       </c>
       <c r="H117" t="n">
-        <v>13.18</v>
+        <v>13.15</v>
       </c>
       <c r="I117" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="J117" t="n">
         <v>9.08</v>
@@ -13273,28 +13281,28 @@
         <v>5.23</v>
       </c>
       <c r="L117" t="n">
-        <v>170.41</v>
+        <v>170.31</v>
       </c>
       <c r="M117" t="n">
-        <v>174.95</v>
+        <v>174.85</v>
       </c>
       <c r="N117" t="n">
-        <v>161.33</v>
+        <v>161.23</v>
       </c>
       <c r="O117" t="n">
-        <v>193.56</v>
+        <v>193.46</v>
       </c>
       <c r="P117" t="n">
         <v>1.63</v>
       </c>
       <c r="Q117" t="n">
-        <v>82.40000000000001</v>
+        <v>82.28</v>
       </c>
       <c r="R117" t="n">
-        <v>17.41</v>
+        <v>17.35</v>
       </c>
       <c r="S117" t="n">
-        <v>-5.13</v>
+        <v>-5.18</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13313,7 +13321,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -13355,22 +13363,22 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>52.02</v>
+        <v>51.97</v>
       </c>
       <c r="D118" t="n">
         <v>48</v>
       </c>
       <c r="E118" t="n">
-        <v>-5.86</v>
+        <v>-5.95</v>
       </c>
       <c r="F118" t="n">
-        <v>9.84</v>
+        <v>9.73</v>
       </c>
       <c r="G118" t="n">
-        <v>64.52</v>
+        <v>64.36</v>
       </c>
       <c r="H118" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="I118" t="n">
         <v>0.46</v>
@@ -13379,31 +13387,31 @@
         <v>4.96</v>
       </c>
       <c r="K118" t="n">
-        <v>9.539999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L118" t="n">
-        <v>50.28</v>
+        <v>50.23</v>
       </c>
       <c r="M118" t="n">
-        <v>52.76</v>
+        <v>52.71</v>
       </c>
       <c r="N118" t="n">
-        <v>45.32</v>
+        <v>45.27</v>
       </c>
       <c r="O118" t="n">
-        <v>62.93</v>
+        <v>62.88</v>
       </c>
       <c r="P118" t="n">
         <v>1.63</v>
       </c>
       <c r="Q118" t="n">
-        <v>58.87</v>
+        <v>58.82</v>
       </c>
       <c r="R118" t="n">
-        <v>6.48</v>
+        <v>6.38</v>
       </c>
       <c r="S118" t="n">
-        <v>-12.05</v>
+        <v>-12.14</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13422,7 +13430,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -13464,22 +13472,22 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>165.42</v>
+        <v>165.06</v>
       </c>
       <c r="D119" t="n">
         <v>45</v>
       </c>
       <c r="E119" t="n">
-        <v>8.56</v>
+        <v>8.33</v>
       </c>
       <c r="F119" t="n">
-        <v>6.33</v>
+        <v>6.1</v>
       </c>
       <c r="G119" t="n">
-        <v>2.71</v>
+        <v>2.48</v>
       </c>
       <c r="H119" t="n">
-        <v>-2.17</v>
+        <v>-2.36</v>
       </c>
       <c r="I119" t="n">
         <v>0.41</v>
@@ -13488,31 +13496,31 @@
         <v>8.69</v>
       </c>
       <c r="K119" t="n">
-        <v>5.25</v>
+        <v>5.27</v>
       </c>
       <c r="L119" t="n">
-        <v>162.38</v>
+        <v>162.02</v>
       </c>
       <c r="M119" t="n">
-        <v>166.72</v>
+        <v>166.36</v>
       </c>
       <c r="N119" t="n">
-        <v>153.69</v>
+        <v>153.33</v>
       </c>
       <c r="O119" t="n">
-        <v>184.54</v>
+        <v>184.18</v>
       </c>
       <c r="P119" t="n">
         <v>1.63</v>
       </c>
       <c r="Q119" t="n">
-        <v>76.90000000000001</v>
+        <v>76.39</v>
       </c>
       <c r="R119" t="n">
-        <v>10.75</v>
+        <v>10.52</v>
       </c>
       <c r="S119" t="n">
-        <v>-6.53</v>
+        <v>-6.74</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13531,7 +13539,7 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
@@ -13573,55 +13581,55 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>102.97</v>
+        <v>102.79</v>
       </c>
       <c r="D120" t="n">
         <v>42</v>
       </c>
       <c r="E120" t="n">
-        <v>18.29</v>
+        <v>18.09</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.09</v>
+        <v>-0.27</v>
       </c>
       <c r="G120" t="n">
-        <v>0.47</v>
+        <v>0.3</v>
       </c>
       <c r="H120" t="n">
-        <v>-8.59</v>
+        <v>-8.73</v>
       </c>
       <c r="I120" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="J120" t="n">
         <v>5.52</v>
       </c>
       <c r="K120" t="n">
-        <v>5.36</v>
+        <v>5.37</v>
       </c>
       <c r="L120" t="n">
-        <v>101.04</v>
+        <v>100.86</v>
       </c>
       <c r="M120" t="n">
-        <v>103.8</v>
+        <v>103.62</v>
       </c>
       <c r="N120" t="n">
-        <v>95.52</v>
+        <v>95.34</v>
       </c>
       <c r="O120" t="n">
-        <v>115.12</v>
+        <v>114.94</v>
       </c>
       <c r="P120" t="n">
         <v>1.63</v>
       </c>
       <c r="Q120" t="n">
-        <v>69.56999999999999</v>
+        <v>69.42</v>
       </c>
       <c r="R120" t="n">
-        <v>11.72</v>
+        <v>11.54</v>
       </c>
       <c r="S120" t="n">
-        <v>-7.09</v>
+        <v>-7.25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13640,7 +13648,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -13682,22 +13690,22 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>127.2</v>
+        <v>127.12</v>
       </c>
       <c r="D121" t="n">
         <v>30</v>
       </c>
       <c r="E121" t="n">
-        <v>10.45</v>
+        <v>10.38</v>
       </c>
       <c r="F121" t="n">
-        <v>-10.22</v>
+        <v>-10.28</v>
       </c>
       <c r="G121" t="n">
-        <v>-16.56</v>
+        <v>-16.61</v>
       </c>
       <c r="H121" t="n">
-        <v>-18.72</v>
+        <v>-18.74</v>
       </c>
       <c r="I121" t="n">
         <v>0.23</v>
@@ -13709,28 +13717,28 @@
         <v>3.48</v>
       </c>
       <c r="L121" t="n">
-        <v>125.65</v>
+        <v>125.57</v>
       </c>
       <c r="M121" t="n">
-        <v>127.86</v>
+        <v>127.78</v>
       </c>
       <c r="N121" t="n">
-        <v>121.23</v>
+        <v>121.15</v>
       </c>
       <c r="O121" t="n">
-        <v>136.94</v>
+        <v>136.86</v>
       </c>
       <c r="P121" t="n">
         <v>1.63</v>
       </c>
       <c r="Q121" t="n">
-        <v>76.62</v>
+        <v>76.55</v>
       </c>
       <c r="R121" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="S121" t="n">
-        <v>-10.08</v>
+        <v>-10.14</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13749,7 +13757,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -13791,22 +13799,22 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>16.91</v>
+        <v>16.92</v>
       </c>
       <c r="D122" t="n">
         <v>15</v>
       </c>
       <c r="E122" t="n">
-        <v>-8.17</v>
+        <v>-8.15</v>
       </c>
       <c r="F122" t="n">
-        <v>-8</v>
+        <v>-7.97</v>
       </c>
       <c r="G122" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="H122" t="n">
-        <v>-16.5</v>
+        <v>-16.43</v>
       </c>
       <c r="I122" t="n">
         <v>0.63</v>
@@ -13818,28 +13826,28 @@
         <v>9.890000000000001</v>
       </c>
       <c r="L122" t="n">
-        <v>16.32</v>
+        <v>16.33</v>
       </c>
       <c r="M122" t="n">
-        <v>17.16</v>
+        <v>17.17</v>
       </c>
       <c r="N122" t="n">
-        <v>14.65</v>
+        <v>14.66</v>
       </c>
       <c r="O122" t="n">
-        <v>20.59</v>
+        <v>20.6</v>
       </c>
       <c r="P122" t="n">
         <v>1.63</v>
       </c>
       <c r="Q122" t="n">
-        <v>48.04</v>
+        <v>48.06</v>
       </c>
       <c r="R122" t="n">
-        <v>-4.93</v>
+        <v>-4.91</v>
       </c>
       <c r="S122" t="n">
-        <v>-19.55</v>
+        <v>-19.53</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13858,7 +13866,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -13900,25 +13908,25 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>19.13</v>
+        <v>19.14</v>
       </c>
       <c r="D123" t="n">
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>-10.79</v>
+        <v>-10.75</v>
       </c>
       <c r="F123" t="n">
-        <v>-9.949999999999999</v>
+        <v>-9.91</v>
       </c>
       <c r="G123" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="H123" t="n">
-        <v>-18.45</v>
+        <v>-18.37</v>
       </c>
       <c r="I123" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J123" t="n">
         <v>1.88</v>
@@ -13927,28 +13935,28 @@
         <v>9.83</v>
       </c>
       <c r="L123" t="n">
-        <v>18.47</v>
+        <v>18.48</v>
       </c>
       <c r="M123" t="n">
-        <v>19.41</v>
+        <v>19.42</v>
       </c>
       <c r="N123" t="n">
-        <v>16.59</v>
+        <v>16.6</v>
       </c>
       <c r="O123" t="n">
-        <v>23.26</v>
+        <v>23.27</v>
       </c>
       <c r="P123" t="n">
         <v>1.63</v>
       </c>
       <c r="Q123" t="n">
-        <v>46.3</v>
+        <v>46.33</v>
       </c>
       <c r="R123" t="n">
-        <v>-6.99</v>
+        <v>-6.95</v>
       </c>
       <c r="S123" t="n">
-        <v>-22.81</v>
+        <v>-22.78</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13967,7 +13975,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -14009,22 +14017,22 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>206.51</v>
+        <v>205.39</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>15.37</v>
+        <v>14.74</v>
       </c>
       <c r="F124" t="n">
-        <v>-11.27</v>
+        <v>-11.76</v>
       </c>
       <c r="G124" t="n">
-        <v>-11.22</v>
+        <v>-11.7</v>
       </c>
       <c r="H124" t="n">
-        <v>-19.77</v>
+        <v>-20.22</v>
       </c>
       <c r="I124" t="n">
         <v>0.3</v>
@@ -14033,35 +14041,35 @@
         <v>19.18</v>
       </c>
       <c r="K124" t="n">
-        <v>9.289999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="L124" t="n">
-        <v>199.8</v>
+        <v>198.68</v>
       </c>
       <c r="M124" t="n">
-        <v>209.39</v>
+        <v>208.27</v>
       </c>
       <c r="N124" t="n">
-        <v>180.61</v>
+        <v>179.49</v>
       </c>
       <c r="O124" t="n">
-        <v>248.71</v>
+        <v>247.59</v>
       </c>
       <c r="P124" t="n">
         <v>1.63</v>
       </c>
       <c r="Q124" t="n">
-        <v>44.66</v>
+        <v>44.31</v>
       </c>
       <c r="R124" t="n">
-        <v>-4.01</v>
+        <v>-4.5</v>
       </c>
       <c r="S124" t="n">
-        <v>-19.02</v>
+        <v>-19.45</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -14076,7 +14084,7 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>QQQ 8.5% · ARKK -4.5% · SPY 4.05%</t>
+          <t>QQQ 8.46% · ARKK -4.55% · SPY 4.02%</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
@@ -14118,22 +14126,22 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>24</v>
+        <v>23.94</v>
       </c>
       <c r="D125" t="n">
         <v>33</v>
       </c>
       <c r="E125" t="n">
-        <v>-3.67</v>
+        <v>-3.91</v>
       </c>
       <c r="F125" t="n">
-        <v>29.9</v>
+        <v>29.57</v>
       </c>
       <c r="G125" t="n">
-        <v>45.48</v>
+        <v>45.12</v>
       </c>
       <c r="H125" t="n">
-        <v>21.4</v>
+        <v>21.11</v>
       </c>
       <c r="I125" t="n">
         <v>0.46</v>
@@ -14142,31 +14150,31 @@
         <v>1.65</v>
       </c>
       <c r="K125" t="n">
-        <v>6.86</v>
+        <v>6.87</v>
       </c>
       <c r="L125" t="n">
-        <v>23.43</v>
+        <v>23.37</v>
       </c>
       <c r="M125" t="n">
-        <v>24.25</v>
+        <v>24.19</v>
       </c>
       <c r="N125" t="n">
-        <v>21.78</v>
+        <v>21.72</v>
       </c>
       <c r="O125" t="n">
-        <v>27.63</v>
+        <v>27.57</v>
       </c>
       <c r="P125" t="n">
         <v>1.63</v>
       </c>
       <c r="Q125" t="n">
-        <v>75.95</v>
+        <v>75.84</v>
       </c>
       <c r="R125" t="n">
-        <v>12.43</v>
+        <v>12.17</v>
       </c>
       <c r="S125" t="n">
-        <v>-7.17</v>
+        <v>-7.41</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14185,7 +14193,7 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>BTC-USD 1.64% · ETH-USD -5.09%</t>
+          <t>BTC-USD 1.53% · ETH-USD -5.24%</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
@@ -14211,7 +14219,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.64% · ETH-USD -5.09%; RSI sobrecomprado; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
+          <t>Sector no acompaña: BTC-USD 1.53% · ETH-USD -5.24%; RSI sobrecomprado; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -575,22 +575,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>499.46</v>
+        <v>499.66</v>
       </c>
       <c r="D2" t="n">
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.54</v>
+        <v>-7.49</v>
       </c>
       <c r="I2" t="n">
         <v>1.18</v>
@@ -602,28 +602,28 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>497.7</v>
+        <v>497.9</v>
       </c>
       <c r="M2" t="n">
-        <v>500.21</v>
+        <v>500.41</v>
       </c>
       <c r="N2" t="n">
-        <v>492.69</v>
+        <v>492.89</v>
       </c>
       <c r="O2" t="n">
-        <v>510.5</v>
+        <v>510.7</v>
       </c>
       <c r="P2" t="n">
         <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>53.72</v>
+        <v>53.95</v>
       </c>
       <c r="R2" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.48</v>
+        <v>-0.44</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -684,55 +684,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42.28</v>
+        <v>42.19</v>
       </c>
       <c r="D3" t="n">
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="F3" t="n">
-        <v>8.119999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="G3" t="n">
-        <v>18.72</v>
+        <v>18.47</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.43</v>
+        <v>-0.65</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J3" t="n">
         <v>1.18</v>
       </c>
       <c r="K3" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="L3" t="n">
-        <v>41.87</v>
+        <v>41.78</v>
       </c>
       <c r="M3" t="n">
-        <v>42.46</v>
+        <v>42.37</v>
       </c>
       <c r="N3" t="n">
-        <v>40.7</v>
+        <v>40.61</v>
       </c>
       <c r="O3" t="n">
-        <v>44.87</v>
+        <v>44.78</v>
       </c>
       <c r="P3" t="n">
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>49.92</v>
+        <v>49.47</v>
       </c>
       <c r="R3" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.99</v>
+        <v>-3.2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>XLE 5.77% · CL=F 5.65%</t>
+          <t>XLE 5.63% · CL=F 5.62%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.77% · CL=F 5.65%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>157.53</v>
+        <v>157.34</v>
       </c>
       <c r="D4" t="n">
         <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>4.64</v>
+        <v>4.51</v>
       </c>
       <c r="F4" t="n">
-        <v>6.09</v>
+        <v>5.96</v>
       </c>
       <c r="G4" t="n">
-        <v>6.26</v>
+        <v>6.13</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.46</v>
+        <v>-2.58</v>
       </c>
       <c r="I4" t="n">
         <v>0.61</v>
@@ -824,28 +824,28 @@
         <v>2.75</v>
       </c>
       <c r="L4" t="n">
-        <v>156.02</v>
+        <v>155.83</v>
       </c>
       <c r="M4" t="n">
-        <v>158.18</v>
+        <v>157.99</v>
       </c>
       <c r="N4" t="n">
-        <v>151.69</v>
+        <v>151.5</v>
       </c>
       <c r="O4" t="n">
-        <v>167.05</v>
+        <v>166.86</v>
       </c>
       <c r="P4" t="n">
         <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>55.59</v>
+        <v>55.32</v>
       </c>
       <c r="R4" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.76</v>
+        <v>-3.87</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>XLE 5.77% · CL=F 5.65%</t>
+          <t>XLE 5.63% · CL=F 5.62%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.77% · CL=F 5.65%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>59.81</v>
+        <v>59.75</v>
       </c>
       <c r="D5" t="n">
         <v>96</v>
       </c>
       <c r="E5" t="n">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="F5" t="n">
-        <v>5.78</v>
+        <v>5.68</v>
       </c>
       <c r="G5" t="n">
-        <v>9.26</v>
+        <v>9.15</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.77</v>
+        <v>-2.86</v>
       </c>
       <c r="I5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="J5" t="n">
         <v>1.38</v>
@@ -937,28 +937,28 @@
         <v>2.31</v>
       </c>
       <c r="L5" t="n">
-        <v>59.33</v>
+        <v>59.27</v>
       </c>
       <c r="M5" t="n">
-        <v>60.02</v>
+        <v>59.96</v>
       </c>
       <c r="N5" t="n">
-        <v>57.95</v>
+        <v>57.89</v>
       </c>
       <c r="O5" t="n">
-        <v>62.85</v>
+        <v>62.79</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>50.65</v>
+        <v>50.41</v>
       </c>
       <c r="R5" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.06</v>
+        <v>-3.16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>XLE 5.77% · CL=F 5.65%</t>
+          <t>XLE 5.63% · CL=F 5.62%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.77% · CL=F 5.65%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1019,55 +1019,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>140.61</v>
+        <v>140.4</v>
       </c>
       <c r="D6" t="n">
         <v>96</v>
       </c>
       <c r="E6" t="n">
-        <v>4.21</v>
+        <v>4.05</v>
       </c>
       <c r="F6" t="n">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
       <c r="G6" t="n">
-        <v>14.55</v>
+        <v>14.38</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.84</v>
+        <v>-2.98</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="K6" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="L6" t="n">
-        <v>139.23</v>
+        <v>139.01</v>
       </c>
       <c r="M6" t="n">
-        <v>141.2</v>
+        <v>140.99</v>
       </c>
       <c r="N6" t="n">
-        <v>135.27</v>
+        <v>135.05</v>
       </c>
       <c r="O6" t="n">
-        <v>149.31</v>
+        <v>149.12</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>50.06</v>
+        <v>49.75</v>
       </c>
       <c r="R6" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.49</v>
+        <v>-3.64</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>XLE 5.77% · CL=F 5.65%</t>
+          <t>XLE 5.63% · CL=F 5.62%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.77% · CL=F 5.65%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1132,22 +1132,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>203.75</v>
+        <v>203.02</v>
       </c>
       <c r="D7" t="n">
         <v>96</v>
       </c>
       <c r="E7" t="n">
-        <v>1.87</v>
+        <v>1.51</v>
       </c>
       <c r="F7" t="n">
-        <v>5.67</v>
+        <v>5.3</v>
       </c>
       <c r="G7" t="n">
-        <v>19.46</v>
+        <v>19.03</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.88</v>
+        <v>-3.24</v>
       </c>
       <c r="I7" t="n">
         <v>0.33</v>
@@ -1156,31 +1156,31 @@
         <v>6.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="L7" t="n">
-        <v>201.46</v>
+        <v>200.73</v>
       </c>
       <c r="M7" t="n">
-        <v>204.73</v>
+        <v>204</v>
       </c>
       <c r="N7" t="n">
-        <v>194.9</v>
+        <v>194.17</v>
       </c>
       <c r="O7" t="n">
-        <v>218.17</v>
+        <v>217.44</v>
       </c>
       <c r="P7" t="n">
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>49.34</v>
+        <v>48.71</v>
       </c>
       <c r="R7" t="n">
-        <v>1.89</v>
+        <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.49</v>
+        <v>-4.84</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>XLE 5.77% · CL=F 5.65%</t>
+          <t>XLE 5.63% · CL=F 5.62%</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.77% · CL=F 5.65%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Volumen bajo</t>
+          <t>Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -1245,22 +1245,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57.07</v>
+        <v>56.89</v>
       </c>
       <c r="D8" t="n">
         <v>96</v>
       </c>
       <c r="E8" t="n">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="G8" t="n">
-        <v>10.07</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.55</v>
+        <v>-3.87</v>
       </c>
       <c r="I8" t="n">
         <v>0.51</v>
@@ -1269,31 +1269,31 @@
         <v>1.41</v>
       </c>
       <c r="K8" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="L8" t="n">
-        <v>56.58</v>
+        <v>56.4</v>
       </c>
       <c r="M8" t="n">
-        <v>57.28</v>
+        <v>57.1</v>
       </c>
       <c r="N8" t="n">
-        <v>55.17</v>
+        <v>54.99</v>
       </c>
       <c r="O8" t="n">
-        <v>60.17</v>
+        <v>59.99</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>50.88</v>
+        <v>50.05</v>
       </c>
       <c r="R8" t="n">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.09</v>
+        <v>-1.4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>XLE 5.77% · CL=F 5.65%</t>
+          <t>XLE 5.63% · CL=F 5.62%</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.77% · CL=F 5.65%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1358,25 +1358,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>516.9</v>
+        <v>516.71</v>
       </c>
       <c r="D9" t="n">
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.16</v>
+        <v>-2.19</v>
       </c>
       <c r="F9" t="n">
-        <v>19.72</v>
+        <v>19.67</v>
       </c>
       <c r="G9" t="n">
-        <v>42.86</v>
+        <v>42.81</v>
       </c>
       <c r="H9" t="n">
-        <v>11.17</v>
+        <v>11.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="J9" t="n">
         <v>21.72</v>
@@ -1385,28 +1385,28 @@
         <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>509.3</v>
+        <v>509.1</v>
       </c>
       <c r="M9" t="n">
-        <v>520.16</v>
+        <v>519.96</v>
       </c>
       <c r="N9" t="n">
-        <v>487.58</v>
+        <v>487.38</v>
       </c>
       <c r="O9" t="n">
-        <v>564.6799999999999</v>
+        <v>564.49</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>64.31</v>
+        <v>64.28</v>
       </c>
       <c r="R9" t="n">
-        <v>5.89</v>
+        <v>5.85</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.16</v>
+        <v>-3.19</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1471,25 +1471,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>192.67</v>
+        <v>192.43</v>
       </c>
       <c r="D10" t="n">
         <v>91</v>
       </c>
       <c r="E10" t="n">
-        <v>4.53</v>
+        <v>4.4</v>
       </c>
       <c r="F10" t="n">
-        <v>4.36</v>
+        <v>4.23</v>
       </c>
       <c r="G10" t="n">
-        <v>4.91</v>
+        <v>4.78</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.19</v>
+        <v>-4.31</v>
       </c>
       <c r="I10" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="J10" t="n">
         <v>4.54</v>
@@ -1498,28 +1498,28 @@
         <v>2.36</v>
       </c>
       <c r="L10" t="n">
-        <v>191.08</v>
+        <v>190.84</v>
       </c>
       <c r="M10" t="n">
-        <v>193.35</v>
+        <v>193.11</v>
       </c>
       <c r="N10" t="n">
-        <v>186.54</v>
+        <v>186.3</v>
       </c>
       <c r="O10" t="n">
-        <v>202.66</v>
+        <v>202.42</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>51.49</v>
+        <v>51.16</v>
       </c>
       <c r="R10" t="n">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.12</v>
+        <v>-3.24</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>XLE 5.77% · CL=F 5.65%</t>
+          <t>XLE 5.63% · CL=F 5.62%</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.77% · CL=F 5.65%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>109.83</v>
+        <v>109.64</v>
       </c>
       <c r="D11" t="n">
         <v>83</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.08</v>
+        <v>-5.25</v>
       </c>
       <c r="F11" t="n">
-        <v>23.42</v>
+        <v>23.2</v>
       </c>
       <c r="G11" t="n">
-        <v>56.83</v>
+        <v>56.55</v>
       </c>
       <c r="H11" t="n">
-        <v>14.87</v>
+        <v>14.66</v>
       </c>
       <c r="I11" t="n">
         <v>0.27</v>
@@ -1608,31 +1608,31 @@
         <v>6.38</v>
       </c>
       <c r="K11" t="n">
-        <v>5.81</v>
+        <v>5.82</v>
       </c>
       <c r="L11" t="n">
-        <v>107.6</v>
+        <v>107.4</v>
       </c>
       <c r="M11" t="n">
-        <v>110.79</v>
+        <v>110.59</v>
       </c>
       <c r="N11" t="n">
-        <v>101.22</v>
+        <v>101.02</v>
       </c>
       <c r="O11" t="n">
-        <v>123.86</v>
+        <v>123.67</v>
       </c>
       <c r="P11" t="n">
         <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>58.63</v>
+        <v>58.47</v>
       </c>
       <c r="R11" t="n">
-        <v>5.18</v>
+        <v>5.01</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.78</v>
+        <v>-7.95</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1542.94</v>
+        <v>1543.06</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -1706,13 +1706,13 @@
         <v>-2.44</v>
       </c>
       <c r="F12" t="n">
-        <v>7.11</v>
+        <v>7.12</v>
       </c>
       <c r="G12" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.44</v>
+        <v>-1.42</v>
       </c>
       <c r="I12" t="n">
         <v>0.73</v>
@@ -1724,28 +1724,28 @@
         <v>4.55</v>
       </c>
       <c r="L12" t="n">
-        <v>1518.34</v>
+        <v>1518.47</v>
       </c>
       <c r="M12" t="n">
-        <v>1553.47</v>
+        <v>1553.6</v>
       </c>
       <c r="N12" t="n">
-        <v>1448.08</v>
+        <v>1448.21</v>
       </c>
       <c r="O12" t="n">
-        <v>1697.51</v>
+        <v>1697.64</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>57.9</v>
+        <v>57.91</v>
       </c>
       <c r="R12" t="n">
-        <v>4.05</v>
+        <v>4.06</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.78</v>
+        <v>-3.77</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1810,19 +1810,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>401.87</v>
+        <v>401.81</v>
       </c>
       <c r="D13" t="n">
         <v>87</v>
       </c>
       <c r="E13" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="F13" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="G13" t="n">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="H13" t="n">
         <v>-4.83</v>
@@ -1837,28 +1837,28 @@
         <v>3.88</v>
       </c>
       <c r="L13" t="n">
-        <v>396.41</v>
+        <v>396.35</v>
       </c>
       <c r="M13" t="n">
-        <v>404.21</v>
+        <v>404.15</v>
       </c>
       <c r="N13" t="n">
-        <v>380.82</v>
+        <v>380.76</v>
       </c>
       <c r="O13" t="n">
-        <v>436.17</v>
+        <v>436.11</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>52.53</v>
+        <v>52.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.76</v>
+        <v>-4.78</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1923,55 +1923,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1814.03</v>
+        <v>1812.31</v>
       </c>
       <c r="D14" t="n">
         <v>87</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="F14" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="G14" t="n">
-        <v>20.55</v>
+        <v>20.44</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.31</v>
+        <v>-8.4</v>
       </c>
       <c r="I14" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="J14" t="n">
         <v>81.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.48</v>
+        <v>4.49</v>
       </c>
       <c r="L14" t="n">
-        <v>1785.57</v>
+        <v>1783.85</v>
       </c>
       <c r="M14" t="n">
-        <v>1826.22</v>
+        <v>1824.51</v>
       </c>
       <c r="N14" t="n">
-        <v>1704.27</v>
+        <v>1702.55</v>
       </c>
       <c r="O14" t="n">
-        <v>1992.89</v>
+        <v>1991.17</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>54.98</v>
+        <v>54.87</v>
       </c>
       <c r="R14" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.34</v>
+        <v>-6.43</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2036,55 +2036,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>59.06</v>
+        <v>58.96</v>
       </c>
       <c r="D15" t="n">
         <v>77</v>
       </c>
       <c r="E15" t="n">
-        <v>5.13</v>
+        <v>4.95</v>
       </c>
       <c r="F15" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="G15" t="n">
-        <v>14.23</v>
+        <v>14.03</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.03</v>
+        <v>-5.19</v>
       </c>
       <c r="I15" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="J15" t="n">
         <v>1.98</v>
       </c>
       <c r="K15" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="L15" t="n">
-        <v>58.37</v>
+        <v>58.27</v>
       </c>
       <c r="M15" t="n">
-        <v>59.36</v>
+        <v>59.26</v>
       </c>
       <c r="N15" t="n">
-        <v>56.39</v>
+        <v>56.29</v>
       </c>
       <c r="O15" t="n">
-        <v>63.42</v>
+        <v>63.32</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>46.23</v>
+        <v>46</v>
       </c>
       <c r="R15" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.49</v>
+        <v>-3.66</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>XLE 5.77% · CL=F 5.65%</t>
+          <t>XLE 5.63% · CL=F 5.62%</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.77% · CL=F 5.65%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2149,55 +2149,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>48.54</v>
+        <v>48.43</v>
       </c>
       <c r="D16" t="n">
         <v>77</v>
       </c>
       <c r="E16" t="n">
-        <v>3.49</v>
+        <v>3.26</v>
       </c>
       <c r="F16" t="n">
-        <v>3.01</v>
+        <v>2.78</v>
       </c>
       <c r="G16" t="n">
-        <v>12.73</v>
+        <v>12.48</v>
       </c>
       <c r="H16" t="n">
-        <v>-5.54</v>
+        <v>-5.76</v>
       </c>
       <c r="I16" t="n">
         <v>0.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="K16" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="L16" t="n">
-        <v>47.93</v>
+        <v>47.83</v>
       </c>
       <c r="M16" t="n">
-        <v>48.79</v>
+        <v>48.69</v>
       </c>
       <c r="N16" t="n">
-        <v>46.21</v>
+        <v>46.1</v>
       </c>
       <c r="O16" t="n">
-        <v>52.33</v>
+        <v>52.23</v>
       </c>
       <c r="P16" t="n">
         <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>39.09</v>
+        <v>38.78</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.09</v>
+        <v>-0.3</v>
       </c>
       <c r="S16" t="n">
-        <v>-6.57</v>
+        <v>-6.78</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>XLE 5.77% · CL=F 5.65%</t>
+          <t>XLE 5.63% · CL=F 5.62%</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.77% · CL=F 5.65%; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>122.11</v>
+        <v>121.95</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
       </c>
       <c r="E17" t="n">
-        <v>4.01</v>
+        <v>3.88</v>
       </c>
       <c r="F17" t="n">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="G17" t="n">
-        <v>11.24</v>
+        <v>11.09</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.210000000000001</v>
+        <v>-8.33</v>
       </c>
       <c r="I17" t="n">
         <v>0.42</v>
@@ -2289,28 +2289,28 @@
         <v>2.7</v>
       </c>
       <c r="L17" t="n">
-        <v>120.96</v>
+        <v>120.8</v>
       </c>
       <c r="M17" t="n">
-        <v>122.6</v>
+        <v>122.44</v>
       </c>
       <c r="N17" t="n">
-        <v>117.67</v>
+        <v>117.51</v>
       </c>
       <c r="O17" t="n">
-        <v>129.35</v>
+        <v>129.19</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>45.61</v>
+        <v>45.38</v>
       </c>
       <c r="R17" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.1</v>
+        <v>-4.23</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>XLE 5.77% · CL=F 5.65%</t>
+          <t>XLE 5.63% · CL=F 5.62%</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.77% · CL=F 5.65%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2375,55 +2375,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>93.64</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="D18" t="n">
         <v>74</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.18</v>
+        <v>-3.39</v>
       </c>
       <c r="F18" t="n">
-        <v>13.53</v>
+        <v>13.28</v>
       </c>
       <c r="G18" t="n">
-        <v>23.32</v>
+        <v>23.05</v>
       </c>
       <c r="H18" t="n">
-        <v>4.98</v>
+        <v>4.74</v>
       </c>
       <c r="I18" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>4.07</v>
       </c>
       <c r="K18" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="L18" t="n">
-        <v>92.20999999999999</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>94.25</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>88.14</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>102.6</v>
+        <v>102.39</v>
       </c>
       <c r="P18" t="n">
         <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>51.54</v>
+        <v>51.11</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.02</v>
       </c>
       <c r="S18" t="n">
-        <v>-11.59</v>
+        <v>-11.78</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2488,55 +2488,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>423.66</v>
+        <v>422.45</v>
       </c>
       <c r="D19" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.97</v>
+        <v>-3.24</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="G19" t="n">
-        <v>12.1</v>
+        <v>11.78</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.55</v>
+        <v>-3.84</v>
       </c>
       <c r="I19" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="J19" t="n">
         <v>20.58</v>
       </c>
       <c r="K19" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="L19" t="n">
-        <v>416.46</v>
+        <v>415.24</v>
       </c>
       <c r="M19" t="n">
-        <v>426.75</v>
+        <v>425.53</v>
       </c>
       <c r="N19" t="n">
-        <v>395.88</v>
+        <v>394.67</v>
       </c>
       <c r="O19" t="n">
-        <v>468.93</v>
+        <v>467.72</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.68</v>
+        <v>58.38</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="S19" t="n">
-        <v>-5.53</v>
+        <v>-5.8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2576,76 +2576,76 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo; Momentum negativo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Finanzas</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>975.77</v>
+        <v>331.05</v>
       </c>
       <c r="D20" t="n">
         <v>96</v>
       </c>
       <c r="E20" t="n">
-        <v>2.13</v>
+        <v>3.35</v>
       </c>
       <c r="F20" t="n">
-        <v>4.38</v>
+        <v>6.57</v>
       </c>
       <c r="G20" t="n">
-        <v>8.720000000000001</v>
+        <v>7.98</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.17</v>
+        <v>-1.97</v>
       </c>
       <c r="I20" t="n">
-        <v>0.97</v>
+        <v>0.47</v>
       </c>
       <c r="J20" t="n">
-        <v>24.93</v>
+        <v>6.09</v>
       </c>
       <c r="K20" t="n">
-        <v>2.56</v>
+        <v>1.84</v>
       </c>
       <c r="L20" t="n">
-        <v>967.04</v>
+        <v>328.92</v>
       </c>
       <c r="M20" t="n">
-        <v>979.51</v>
+        <v>331.97</v>
       </c>
       <c r="N20" t="n">
-        <v>942.11</v>
+        <v>322.83</v>
       </c>
       <c r="O20" t="n">
-        <v>1030.62</v>
+        <v>344.45</v>
       </c>
       <c r="P20" t="n">
         <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>63.24</v>
+        <v>52.04</v>
       </c>
       <c r="R20" t="n">
-        <v>4.29</v>
+        <v>2.79</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1</v>
+        <v>-2.99</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2689,76 +2689,76 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Débil vs QQQ</t>
+          <t>Tendencia larga débil; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Finanzas</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>106.58</v>
+        <v>975.7</v>
       </c>
       <c r="D21" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E21" t="n">
-        <v>1.19</v>
+        <v>2.12</v>
       </c>
       <c r="F21" t="n">
-        <v>7.73</v>
+        <v>4.37</v>
       </c>
       <c r="G21" t="n">
-        <v>11.09</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.82</v>
+        <v>-4.17</v>
       </c>
       <c r="I21" t="n">
-        <v>0.49</v>
+        <v>0.98</v>
       </c>
       <c r="J21" t="n">
-        <v>2.48</v>
+        <v>24.93</v>
       </c>
       <c r="K21" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="L21" t="n">
-        <v>105.72</v>
+        <v>966.97</v>
       </c>
       <c r="M21" t="n">
-        <v>106.96</v>
+        <v>979.4400000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>103.24</v>
+        <v>942.03</v>
       </c>
       <c r="O21" t="n">
-        <v>112.03</v>
+        <v>1030.55</v>
       </c>
       <c r="P21" t="n">
         <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>59.12</v>
+        <v>63.22</v>
       </c>
       <c r="R21" t="n">
-        <v>2.63</v>
+        <v>4.29</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.53</v>
+        <v>-0.1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2807,71 +2807,71 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo</t>
+          <t>Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Finanzas</t>
+          <t>Consumo</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>197.29</v>
+        <v>106.64</v>
       </c>
       <c r="D22" t="n">
         <v>95</v>
       </c>
       <c r="E22" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="F22" t="n">
-        <v>3.82</v>
+        <v>7.79</v>
       </c>
       <c r="G22" t="n">
-        <v>17.51</v>
+        <v>11.15</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.73</v>
+        <v>-0.75</v>
       </c>
       <c r="I22" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
-        <v>4.45</v>
+        <v>2.48</v>
       </c>
       <c r="K22" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="L22" t="n">
-        <v>195.73</v>
+        <v>105.78</v>
       </c>
       <c r="M22" t="n">
-        <v>197.96</v>
+        <v>107.02</v>
       </c>
       <c r="N22" t="n">
-        <v>191.28</v>
+        <v>103.3</v>
       </c>
       <c r="O22" t="n">
-        <v>207.08</v>
+        <v>112.09</v>
       </c>
       <c r="P22" t="n">
         <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>60.32</v>
+        <v>59.36</v>
       </c>
       <c r="R22" t="n">
-        <v>3.37</v>
+        <v>2.69</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.32</v>
+        <v>-1.48</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2920,71 +2920,71 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Finanzas</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>330.74</v>
+        <v>197.4</v>
       </c>
       <c r="D23" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E23" t="n">
-        <v>3.26</v>
+        <v>1.84</v>
       </c>
       <c r="F23" t="n">
-        <v>6.47</v>
+        <v>3.88</v>
       </c>
       <c r="G23" t="n">
-        <v>7.88</v>
+        <v>17.58</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.08</v>
+        <v>-4.66</v>
       </c>
       <c r="I23" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="J23" t="n">
-        <v>6.09</v>
+        <v>4.45</v>
       </c>
       <c r="K23" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="L23" t="n">
-        <v>328.61</v>
+        <v>195.84</v>
       </c>
       <c r="M23" t="n">
-        <v>331.66</v>
+        <v>198.06</v>
       </c>
       <c r="N23" t="n">
-        <v>322.52</v>
+        <v>191.39</v>
       </c>
       <c r="O23" t="n">
-        <v>344.14</v>
+        <v>207.18</v>
       </c>
       <c r="P23" t="n">
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>51.71</v>
+        <v>60.45</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.09</v>
+        <v>-0.27</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3028,76 +3028,76 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Volumen bajo</t>
+          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>288.94</v>
+        <v>298.39</v>
       </c>
       <c r="D24" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2</v>
+        <v>1.25</v>
       </c>
       <c r="F24" t="n">
-        <v>8.81</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>18.44</v>
+        <v>-13.54</v>
       </c>
       <c r="H24" t="n">
-        <v>0.26</v>
+        <v>-0.54</v>
       </c>
       <c r="I24" t="n">
-        <v>0.48</v>
+        <v>0.57</v>
       </c>
       <c r="J24" t="n">
-        <v>15.26</v>
+        <v>9.57</v>
       </c>
       <c r="K24" t="n">
-        <v>5.28</v>
+        <v>3.21</v>
       </c>
       <c r="L24" t="n">
-        <v>283.6</v>
+        <v>295.04</v>
       </c>
       <c r="M24" t="n">
-        <v>291.23</v>
+        <v>299.83</v>
       </c>
       <c r="N24" t="n">
-        <v>268.33</v>
+        <v>285.47</v>
       </c>
       <c r="O24" t="n">
-        <v>322.52</v>
+        <v>319.44</v>
       </c>
       <c r="P24" t="n">
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>62.97</v>
+        <v>55</v>
       </c>
       <c r="R24" t="n">
-        <v>4.74</v>
+        <v>2.73</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.32</v>
+        <v>-3.75</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3141,76 +3141,76 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; RSI saludable; MACD positivo; MACD mejorando</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo</t>
+          <t>Tendencia larga débil; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>298.27</v>
+        <v>386.83</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E25" t="n">
-        <v>1.21</v>
+        <v>-3.92</v>
       </c>
       <c r="F25" t="n">
-        <v>7.96</v>
+        <v>14</v>
       </c>
       <c r="G25" t="n">
-        <v>-13.58</v>
+        <v>24.51</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.59</v>
+        <v>5.46</v>
       </c>
       <c r="I25" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="J25" t="n">
-        <v>9.57</v>
+        <v>9.81</v>
       </c>
       <c r="K25" t="n">
-        <v>3.21</v>
+        <v>2.54</v>
       </c>
       <c r="L25" t="n">
-        <v>294.92</v>
+        <v>383.4</v>
       </c>
       <c r="M25" t="n">
-        <v>299.71</v>
+        <v>388.3</v>
       </c>
       <c r="N25" t="n">
-        <v>285.35</v>
+        <v>373.59</v>
       </c>
       <c r="O25" t="n">
-        <v>319.32</v>
+        <v>408.41</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>54.94</v>
+        <v>51.54</v>
       </c>
       <c r="R25" t="n">
-        <v>2.69</v>
+        <v>1.53</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.78</v>
+        <v>-5.33</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3254,76 +3254,76 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; RSI saludable; MACD positivo; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Volumen bajo</t>
+          <t>MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>387.02</v>
+        <v>212.6</v>
       </c>
       <c r="D26" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.87</v>
+        <v>1.97</v>
       </c>
       <c r="F26" t="n">
-        <v>14.06</v>
+        <v>6.03</v>
       </c>
       <c r="G26" t="n">
-        <v>24.57</v>
+        <v>-6.16</v>
       </c>
       <c r="H26" t="n">
-        <v>5.51</v>
+        <v>-2.51</v>
       </c>
       <c r="I26" t="n">
-        <v>0.58</v>
+        <v>0.32</v>
       </c>
       <c r="J26" t="n">
-        <v>9.81</v>
+        <v>4.74</v>
       </c>
       <c r="K26" t="n">
-        <v>2.53</v>
+        <v>2.23</v>
       </c>
       <c r="L26" t="n">
-        <v>383.59</v>
+        <v>210.94</v>
       </c>
       <c r="M26" t="n">
-        <v>388.49</v>
+        <v>213.31</v>
       </c>
       <c r="N26" t="n">
-        <v>373.78</v>
+        <v>206.19</v>
       </c>
       <c r="O26" t="n">
-        <v>408.6</v>
+        <v>223.04</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>51.69</v>
+        <v>52.21</v>
       </c>
       <c r="R26" t="n">
-        <v>1.57</v>
+        <v>3.3</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.28</v>
+        <v>-1.48</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3367,76 +3367,76 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; RSI saludable; MACD positivo; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Momentum negativo</t>
+          <t>Tendencia larga débil; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Consumo</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>212.54</v>
+        <v>131.5</v>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="E27" t="n">
-        <v>1.94</v>
+        <v>0.02</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>1.36</v>
       </c>
       <c r="G27" t="n">
-        <v>-6.19</v>
+        <v>4.16</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.55</v>
+        <v>-7.18</v>
       </c>
       <c r="I27" t="n">
-        <v>0.31</v>
+        <v>0.83</v>
       </c>
       <c r="J27" t="n">
-        <v>4.74</v>
+        <v>2.59</v>
       </c>
       <c r="K27" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="L27" t="n">
-        <v>210.87</v>
+        <v>130.59</v>
       </c>
       <c r="M27" t="n">
-        <v>213.25</v>
+        <v>131.89</v>
       </c>
       <c r="N27" t="n">
-        <v>206.13</v>
+        <v>128.01</v>
       </c>
       <c r="O27" t="n">
-        <v>222.97</v>
+        <v>137.19</v>
       </c>
       <c r="P27" t="n">
         <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>52.09</v>
+        <v>49.49</v>
       </c>
       <c r="R27" t="n">
-        <v>3.27</v>
+        <v>0.76</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.51</v>
+        <v>-2.71</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3463,11 +3463,7 @@
           <t>BAJO</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -3480,76 +3476,76 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; RSI saludable; MACD positivo; Momentum 5D sano</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Volumen bajo</t>
+          <t>Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>131.54</v>
+        <v>288.02</v>
       </c>
       <c r="D28" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E28" t="n">
-        <v>0.05</v>
+        <v>-2.51</v>
       </c>
       <c r="F28" t="n">
-        <v>1.39</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>4.19</v>
+        <v>18.06</v>
       </c>
       <c r="H28" t="n">
-        <v>-7.16</v>
+        <v>-0.08</v>
       </c>
       <c r="I28" t="n">
-        <v>0.82</v>
+        <v>0.48</v>
       </c>
       <c r="J28" t="n">
-        <v>2.59</v>
+        <v>15.26</v>
       </c>
       <c r="K28" t="n">
-        <v>1.97</v>
+        <v>5.3</v>
       </c>
       <c r="L28" t="n">
-        <v>130.63</v>
+        <v>282.67</v>
       </c>
       <c r="M28" t="n">
-        <v>131.93</v>
+        <v>290.3</v>
       </c>
       <c r="N28" t="n">
-        <v>128.05</v>
+        <v>267.41</v>
       </c>
       <c r="O28" t="n">
-        <v>137.23</v>
+        <v>321.59</v>
       </c>
       <c r="P28" t="n">
         <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>49.6</v>
+        <v>62.68</v>
       </c>
       <c r="R28" t="n">
-        <v>0.79</v>
+        <v>4.42</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.68</v>
+        <v>-4.63</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3594,7 +3590,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Débil vs QQQ</t>
+          <t>MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -3610,19 +3606,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>113.25</v>
+        <v>113.24</v>
       </c>
       <c r="D29" t="n">
         <v>89</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="F29" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="G29" t="n">
-        <v>-7.94</v>
+        <v>-7.95</v>
       </c>
       <c r="H29" t="n">
         <v>-8.23</v>
@@ -3637,28 +3633,28 @@
         <v>2.21</v>
       </c>
       <c r="L29" t="n">
-        <v>112.37</v>
+        <v>112.36</v>
       </c>
       <c r="M29" t="n">
-        <v>113.63</v>
+        <v>113.62</v>
       </c>
       <c r="N29" t="n">
-        <v>109.87</v>
+        <v>109.86</v>
       </c>
       <c r="O29" t="n">
-        <v>118.75</v>
+        <v>118.74</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>63.8</v>
+        <v>63.75</v>
       </c>
       <c r="R29" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.61</v>
+        <v>-1.62</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3719,22 +3715,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>230.11</v>
+        <v>230.13</v>
       </c>
       <c r="D30" t="n">
         <v>85</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="F30" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G30" t="n">
-        <v>-6.57</v>
+        <v>-6.56</v>
       </c>
       <c r="H30" t="n">
-        <v>-6.78</v>
+        <v>-6.76</v>
       </c>
       <c r="I30" t="n">
         <v>0.29</v>
@@ -3746,28 +3742,28 @@
         <v>1.62</v>
       </c>
       <c r="L30" t="n">
-        <v>228.81</v>
+        <v>228.83</v>
       </c>
       <c r="M30" t="n">
-        <v>230.67</v>
+        <v>230.69</v>
       </c>
       <c r="N30" t="n">
-        <v>225.08</v>
+        <v>225.11</v>
       </c>
       <c r="O30" t="n">
-        <v>238.31</v>
+        <v>238.33</v>
       </c>
       <c r="P30" t="n">
         <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.46</v>
+        <v>50.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.87</v>
+        <v>-0.86</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3828,55 +3824,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>84.14</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="D31" t="n">
         <v>84</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.15</v>
+        <v>-0.78</v>
       </c>
       <c r="F31" t="n">
-        <v>7.72</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>17.12</v>
+        <v>17.56</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.83</v>
+        <v>-0.41</v>
       </c>
       <c r="I31" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="J31" t="n">
         <v>2.67</v>
       </c>
       <c r="K31" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="L31" t="n">
-        <v>83.2</v>
+        <v>83.52</v>
       </c>
       <c r="M31" t="n">
-        <v>84.54000000000001</v>
+        <v>84.86</v>
       </c>
       <c r="N31" t="n">
-        <v>80.53</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>90.02</v>
+        <v>90.34</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>60.74</v>
+        <v>61.31</v>
       </c>
       <c r="R31" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="S31" t="n">
-        <v>-4.86</v>
+        <v>-4.5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3937,25 +3933,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>383.18</v>
+        <v>383.61</v>
       </c>
       <c r="D32" t="n">
         <v>77</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.48</v>
+        <v>-4.37</v>
       </c>
       <c r="F32" t="n">
-        <v>8.390000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="G32" t="n">
-        <v>40.96</v>
+        <v>41.12</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.16</v>
+        <v>-0.03</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="J32" t="n">
         <v>9.1</v>
@@ -3964,28 +3960,28 @@
         <v>2.37</v>
       </c>
       <c r="L32" t="n">
-        <v>380</v>
+        <v>380.43</v>
       </c>
       <c r="M32" t="n">
-        <v>384.54</v>
+        <v>384.97</v>
       </c>
       <c r="N32" t="n">
-        <v>370.9</v>
+        <v>371.33</v>
       </c>
       <c r="O32" t="n">
-        <v>403.19</v>
+        <v>403.62</v>
       </c>
       <c r="P32" t="n">
         <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>59.65</v>
+        <v>60.04</v>
       </c>
       <c r="R32" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="S32" t="n">
-        <v>-5.19</v>
+        <v>-5.08</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4046,22 +4042,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>279.26</v>
+        <v>279.21</v>
       </c>
       <c r="D33" t="n">
         <v>74</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.21</v>
+        <v>-1.22</v>
       </c>
       <c r="F33" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="G33" t="n">
-        <v>6.24</v>
+        <v>6.22</v>
       </c>
       <c r="H33" t="n">
-        <v>-7.54</v>
+        <v>-7.55</v>
       </c>
       <c r="I33" t="n">
         <v>0.83</v>
@@ -4073,28 +4069,28 @@
         <v>1.75</v>
       </c>
       <c r="L33" t="n">
-        <v>277.55</v>
+        <v>277.5</v>
       </c>
       <c r="M33" t="n">
-        <v>279.99</v>
+        <v>279.95</v>
       </c>
       <c r="N33" t="n">
-        <v>272.65</v>
+        <v>272.61</v>
       </c>
       <c r="O33" t="n">
-        <v>290.02</v>
+        <v>289.98</v>
       </c>
       <c r="P33" t="n">
         <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>51.55</v>
+        <v>51.5</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="S33" t="n">
-        <v>-2.89</v>
+        <v>-2.91</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4155,22 +4151,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>146.79</v>
+        <v>146.83</v>
       </c>
       <c r="D34" t="n">
         <v>74</v>
       </c>
       <c r="E34" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="F34" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="G34" t="n">
-        <v>-6.63</v>
+        <v>-6.61</v>
       </c>
       <c r="H34" t="n">
-        <v>-8.27</v>
+        <v>-8.23</v>
       </c>
       <c r="I34" t="n">
         <v>0.87</v>
@@ -4182,28 +4178,28 @@
         <v>1.29</v>
       </c>
       <c r="L34" t="n">
-        <v>146.13</v>
+        <v>146.17</v>
       </c>
       <c r="M34" t="n">
-        <v>147.08</v>
+        <v>147.11</v>
       </c>
       <c r="N34" t="n">
-        <v>144.25</v>
+        <v>144.28</v>
       </c>
       <c r="O34" t="n">
-        <v>150.95</v>
+        <v>150.98</v>
       </c>
       <c r="P34" t="n">
         <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>53.27</v>
+        <v>53.42</v>
       </c>
       <c r="R34" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.86</v>
+        <v>-0.84</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4264,22 +4260,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>306.98</v>
+        <v>306.47</v>
       </c>
       <c r="D35" t="n">
         <v>96</v>
       </c>
       <c r="E35" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="F35" t="n">
-        <v>35.98</v>
+        <v>35.76</v>
       </c>
       <c r="G35" t="n">
-        <v>31.51</v>
+        <v>31.3</v>
       </c>
       <c r="H35" t="n">
-        <v>27.43</v>
+        <v>27.22</v>
       </c>
       <c r="I35" t="n">
         <v>0.36</v>
@@ -4288,31 +4284,31 @@
         <v>11.48</v>
       </c>
       <c r="K35" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="L35" t="n">
-        <v>302.96</v>
+        <v>302.45</v>
       </c>
       <c r="M35" t="n">
-        <v>308.7</v>
+        <v>308.19</v>
       </c>
       <c r="N35" t="n">
-        <v>291.48</v>
+        <v>290.97</v>
       </c>
       <c r="O35" t="n">
-        <v>332.24</v>
+        <v>331.73</v>
       </c>
       <c r="P35" t="n">
         <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>57.75</v>
+        <v>57.5</v>
       </c>
       <c r="R35" t="n">
-        <v>8.1</v>
+        <v>7.93</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.5</v>
+        <v>-0.67</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4331,7 +4327,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4356,7 +4352,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4377,55 +4373,55 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>184.87</v>
+        <v>184.46</v>
       </c>
       <c r="D36" t="n">
         <v>96</v>
       </c>
       <c r="E36" t="n">
-        <v>3.89</v>
+        <v>3.66</v>
       </c>
       <c r="F36" t="n">
-        <v>17.51</v>
+        <v>17.25</v>
       </c>
       <c r="G36" t="n">
-        <v>135.95</v>
+        <v>135.43</v>
       </c>
       <c r="H36" t="n">
-        <v>8.960000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="J36" t="n">
         <v>12.56</v>
       </c>
       <c r="K36" t="n">
-        <v>6.79</v>
+        <v>6.81</v>
       </c>
       <c r="L36" t="n">
-        <v>180.47</v>
+        <v>180.07</v>
       </c>
       <c r="M36" t="n">
-        <v>186.75</v>
+        <v>186.35</v>
       </c>
       <c r="N36" t="n">
-        <v>167.91</v>
+        <v>167.51</v>
       </c>
       <c r="O36" t="n">
-        <v>212.51</v>
+        <v>212.1</v>
       </c>
       <c r="P36" t="n">
         <v>1.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>61.34</v>
+        <v>61.16</v>
       </c>
       <c r="R36" t="n">
-        <v>9.859999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="S36" t="n">
-        <v>-4.37</v>
+        <v>-4.58</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4444,7 +4440,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4469,7 +4465,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4490,22 +4486,22 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>224.75</v>
+        <v>224.37</v>
       </c>
       <c r="D37" t="n">
         <v>96</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.48</v>
+        <v>-0.65</v>
       </c>
       <c r="F37" t="n">
-        <v>10.99</v>
+        <v>10.8</v>
       </c>
       <c r="G37" t="n">
-        <v>16.55</v>
+        <v>16.35</v>
       </c>
       <c r="H37" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="I37" t="n">
         <v>0.59</v>
@@ -4517,28 +4513,28 @@
         <v>3.6</v>
       </c>
       <c r="L37" t="n">
-        <v>221.92</v>
+        <v>221.54</v>
       </c>
       <c r="M37" t="n">
-        <v>225.96</v>
+        <v>225.58</v>
       </c>
       <c r="N37" t="n">
-        <v>213.83</v>
+        <v>213.45</v>
       </c>
       <c r="O37" t="n">
-        <v>242.54</v>
+        <v>242.16</v>
       </c>
       <c r="P37" t="n">
         <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>70.43000000000001</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="R37" t="n">
-        <v>5.29</v>
+        <v>5.12</v>
       </c>
       <c r="S37" t="n">
-        <v>-4.98</v>
+        <v>-5.15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4557,7 +4553,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4582,7 +4578,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4603,22 +4599,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>300.66</v>
+        <v>300.36</v>
       </c>
       <c r="D38" t="n">
         <v>87</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.85</v>
+        <v>-1.95</v>
       </c>
       <c r="F38" t="n">
-        <v>27.88</v>
+        <v>27.75</v>
       </c>
       <c r="G38" t="n">
-        <v>41.64</v>
+        <v>41.5</v>
       </c>
       <c r="H38" t="n">
-        <v>19.33</v>
+        <v>19.21</v>
       </c>
       <c r="I38" t="n">
         <v>0.38</v>
@@ -4630,28 +4626,28 @@
         <v>3.2</v>
       </c>
       <c r="L38" t="n">
-        <v>297.3</v>
+        <v>297</v>
       </c>
       <c r="M38" t="n">
-        <v>302.1</v>
+        <v>301.8</v>
       </c>
       <c r="N38" t="n">
-        <v>287.69</v>
+        <v>287.39</v>
       </c>
       <c r="O38" t="n">
-        <v>321.8</v>
+        <v>321.5</v>
       </c>
       <c r="P38" t="n">
         <v>1.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>69.66</v>
+        <v>69.27</v>
       </c>
       <c r="R38" t="n">
-        <v>4.54</v>
+        <v>4.44</v>
       </c>
       <c r="S38" t="n">
-        <v>-3.1</v>
+        <v>-3.2</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4670,7 +4666,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -4695,7 +4691,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4716,25 +4712,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>561.5599999999999</v>
+        <v>561.35</v>
       </c>
       <c r="D39" t="n">
         <v>87</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.9</v>
+        <v>-1.94</v>
       </c>
       <c r="F39" t="n">
-        <v>17.77</v>
+        <v>17.73</v>
       </c>
       <c r="G39" t="n">
-        <v>33.97</v>
+        <v>33.92</v>
       </c>
       <c r="H39" t="n">
-        <v>9.220000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="I39" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="J39" t="n">
         <v>20.4</v>
@@ -4743,28 +4739,28 @@
         <v>3.63</v>
       </c>
       <c r="L39" t="n">
-        <v>554.42</v>
+        <v>554.21</v>
       </c>
       <c r="M39" t="n">
-        <v>564.62</v>
+        <v>564.41</v>
       </c>
       <c r="N39" t="n">
-        <v>534.03</v>
+        <v>533.8200000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>606.4299999999999</v>
+        <v>606.22</v>
       </c>
       <c r="P39" t="n">
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>65.31</v>
+        <v>65.27</v>
       </c>
       <c r="R39" t="n">
-        <v>5.12</v>
+        <v>5.08</v>
       </c>
       <c r="S39" t="n">
-        <v>-3.37</v>
+        <v>-3.41</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4783,7 +4779,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -4808,7 +4804,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4820,64 +4816,64 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Consumo</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>246.38</v>
+        <v>1079.79</v>
       </c>
       <c r="D40" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E40" t="n">
-        <v>1.03</v>
+        <v>4.52</v>
       </c>
       <c r="F40" t="n">
-        <v>14.78</v>
+        <v>7.74</v>
       </c>
       <c r="G40" t="n">
-        <v>106.33</v>
+        <v>8.31</v>
       </c>
       <c r="H40" t="n">
-        <v>6.23</v>
+        <v>-0.8</v>
       </c>
       <c r="I40" t="n">
         <v>0.47</v>
       </c>
       <c r="J40" t="n">
-        <v>14.62</v>
+        <v>21.76</v>
       </c>
       <c r="K40" t="n">
-        <v>5.93</v>
+        <v>2.02</v>
       </c>
       <c r="L40" t="n">
-        <v>241.26</v>
+        <v>1072.17</v>
       </c>
       <c r="M40" t="n">
-        <v>248.57</v>
+        <v>1083.05</v>
       </c>
       <c r="N40" t="n">
-        <v>226.65</v>
+        <v>1050.41</v>
       </c>
       <c r="O40" t="n">
-        <v>278.54</v>
+        <v>1127.66</v>
       </c>
       <c r="P40" t="n">
         <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>65.23999999999999</v>
+        <v>70.22</v>
       </c>
       <c r="R40" t="n">
-        <v>7.78</v>
+        <v>5.48</v>
       </c>
       <c r="S40" t="n">
-        <v>-6.67</v>
+        <v>-1.52</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4891,12 +4887,12 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -4906,7 +4902,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -4921,76 +4917,76 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>RSI algo alto; MACD sin confirmar; Volumen bajo; Algo extendida sobre MA20</t>
+          <t>RSI algo alto; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>33.77</v>
+        <v>1007.25</v>
       </c>
       <c r="D41" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E41" t="n">
-        <v>5.53</v>
+        <v>-0.67</v>
       </c>
       <c r="F41" t="n">
-        <v>15.73</v>
+        <v>9.5</v>
       </c>
       <c r="G41" t="n">
-        <v>8.48</v>
+        <v>-3.18</v>
       </c>
       <c r="H41" t="n">
-        <v>7.18</v>
+        <v>0.96</v>
       </c>
       <c r="I41" t="n">
-        <v>0.73</v>
+        <v>0.43</v>
       </c>
       <c r="J41" t="n">
-        <v>2.48</v>
+        <v>29.94</v>
       </c>
       <c r="K41" t="n">
-        <v>7.35</v>
+        <v>2.97</v>
       </c>
       <c r="L41" t="n">
-        <v>32.9</v>
+        <v>996.77</v>
       </c>
       <c r="M41" t="n">
-        <v>34.14</v>
+        <v>1011.74</v>
       </c>
       <c r="N41" t="n">
-        <v>30.42</v>
+        <v>966.83</v>
       </c>
       <c r="O41" t="n">
-        <v>39.23</v>
+        <v>1073.13</v>
       </c>
       <c r="P41" t="n">
         <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>65.22</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="R41" t="n">
-        <v>10.96</v>
+        <v>5.28</v>
       </c>
       <c r="S41" t="n">
-        <v>-7.15</v>
+        <v>-2.94</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5004,12 +5000,12 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -5019,7 +5015,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -5034,76 +5030,76 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; MACD positivo; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI algo alto; Volumen bajo; Algo extendida sobre MA20; Volatilidad alta</t>
+          <t>RSI algo alto; Volumen bajo</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Consumo</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1080.86</v>
+        <v>245.77</v>
       </c>
       <c r="D42" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E42" t="n">
-        <v>4.63</v>
+        <v>0.78</v>
       </c>
       <c r="F42" t="n">
-        <v>7.84</v>
+        <v>14.5</v>
       </c>
       <c r="G42" t="n">
-        <v>8.41</v>
+        <v>105.82</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.71</v>
+        <v>5.96</v>
       </c>
       <c r="I42" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="J42" t="n">
-        <v>21.76</v>
+        <v>14.62</v>
       </c>
       <c r="K42" t="n">
-        <v>2.01</v>
+        <v>5.95</v>
       </c>
       <c r="L42" t="n">
-        <v>1073.24</v>
+        <v>240.65</v>
       </c>
       <c r="M42" t="n">
-        <v>1084.12</v>
+        <v>247.96</v>
       </c>
       <c r="N42" t="n">
-        <v>1051.48</v>
+        <v>226.04</v>
       </c>
       <c r="O42" t="n">
-        <v>1128.73</v>
+        <v>277.93</v>
       </c>
       <c r="P42" t="n">
         <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>70.68000000000001</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="R42" t="n">
-        <v>5.57</v>
+        <v>7.53</v>
       </c>
       <c r="S42" t="n">
-        <v>-1.43</v>
+        <v>-6.9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5117,12 +5113,12 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -5130,11 +5126,7 @@
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -5147,76 +5139,76 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>RSI algo alto; Volumen bajo</t>
+          <t>RSI algo alto; MACD sin confirmar; Volumen bajo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>JOBY</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Movilidad aérea</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1008.33</v>
+        <v>10.3</v>
       </c>
       <c r="D43" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-6.87</v>
       </c>
       <c r="F43" t="n">
-        <v>9.609999999999999</v>
+        <v>12.69</v>
       </c>
       <c r="G43" t="n">
-        <v>-3.08</v>
+        <v>5.97</v>
       </c>
       <c r="H43" t="n">
-        <v>1.06</v>
+        <v>4.15</v>
       </c>
       <c r="I43" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
-        <v>29.94</v>
+        <v>0.78</v>
       </c>
       <c r="K43" t="n">
-        <v>2.97</v>
+        <v>7.54</v>
       </c>
       <c r="L43" t="n">
-        <v>997.85</v>
+        <v>10.03</v>
       </c>
       <c r="M43" t="n">
-        <v>1012.82</v>
+        <v>10.42</v>
       </c>
       <c r="N43" t="n">
-        <v>967.91</v>
+        <v>9.25</v>
       </c>
       <c r="O43" t="n">
-        <v>1074.21</v>
+        <v>12.01</v>
       </c>
       <c r="P43" t="n">
         <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>66.09999999999999</v>
+        <v>59.02</v>
       </c>
       <c r="R43" t="n">
-        <v>5.38</v>
+        <v>5.65</v>
       </c>
       <c r="S43" t="n">
-        <v>-2.83</v>
+        <v>-7.95</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5243,11 +5235,7 @@
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -5260,76 +5248,76 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>RSI algo alto; Volumen bajo</t>
+          <t>Tendencia larga débil; Volumen bajo; Momentum negativo; Volatilidad alta</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JOBY</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Movilidad aérea</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10.3</v>
+        <v>263.76</v>
       </c>
       <c r="D44" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E44" t="n">
-        <v>-6.92</v>
+        <v>-2.36</v>
       </c>
       <c r="F44" t="n">
-        <v>12.64</v>
+        <v>3.29</v>
       </c>
       <c r="G44" t="n">
-        <v>5.92</v>
+        <v>26.47</v>
       </c>
       <c r="H44" t="n">
-        <v>4.09</v>
+        <v>-5.25</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="J44" t="n">
-        <v>0.78</v>
+        <v>6.6</v>
       </c>
       <c r="K44" t="n">
-        <v>7.55</v>
+        <v>2.5</v>
       </c>
       <c r="L44" t="n">
-        <v>10.02</v>
+        <v>261.45</v>
       </c>
       <c r="M44" t="n">
-        <v>10.41</v>
+        <v>264.75</v>
       </c>
       <c r="N44" t="n">
-        <v>9.25</v>
+        <v>254.85</v>
       </c>
       <c r="O44" t="n">
-        <v>12</v>
+        <v>278.29</v>
       </c>
       <c r="P44" t="n">
         <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>58.99</v>
+        <v>48.49</v>
       </c>
       <c r="R44" t="n">
-        <v>5.6</v>
+        <v>-0.93</v>
       </c>
       <c r="S44" t="n">
-        <v>-8</v>
+        <v>-5.31</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5343,45 +5331,45 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD positivo</t>
+          <t>Mercado NEUTRO +; MA20 sobre MA50; Tendencia larga positiva; RSI saludable; MACD mejorando</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; Volumen bajo; Momentum negativo; Volatilidad alta</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5390,55 +5378,55 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>263.6</v>
+        <v>419.77</v>
       </c>
       <c r="D45" t="n">
         <v>71</v>
       </c>
       <c r="E45" t="n">
-        <v>-2.42</v>
+        <v>3.59</v>
       </c>
       <c r="F45" t="n">
-        <v>3.23</v>
+        <v>-3.04</v>
       </c>
       <c r="G45" t="n">
-        <v>26.39</v>
+        <v>7.91</v>
       </c>
       <c r="H45" t="n">
-        <v>-5.32</v>
+        <v>-11.58</v>
       </c>
       <c r="I45" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="J45" t="n">
-        <v>6.6</v>
+        <v>10.85</v>
       </c>
       <c r="K45" t="n">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="L45" t="n">
-        <v>261.29</v>
+        <v>415.97</v>
       </c>
       <c r="M45" t="n">
-        <v>264.59</v>
+        <v>421.4</v>
       </c>
       <c r="N45" t="n">
-        <v>254.69</v>
+        <v>405.12</v>
       </c>
       <c r="O45" t="n">
-        <v>278.13</v>
+        <v>443.64</v>
       </c>
       <c r="P45" t="n">
         <v>1.63</v>
       </c>
       <c r="Q45" t="n">
-        <v>48.3</v>
+        <v>59.75</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.99</v>
+        <v>0.74</v>
       </c>
       <c r="S45" t="n">
-        <v>-5.37</v>
+        <v>-2.99</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5457,7 +5445,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5478,76 +5466,76 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; MA20 sobre MA50; Tendencia larga positiva; RSI saludable; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD mejorando</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>418.93</v>
+        <v>71.62</v>
       </c>
       <c r="D46" t="n">
         <v>68</v>
       </c>
       <c r="E46" t="n">
-        <v>3.39</v>
+        <v>2.64</v>
       </c>
       <c r="F46" t="n">
-        <v>-3.23</v>
+        <v>-1.21</v>
       </c>
       <c r="G46" t="n">
-        <v>7.69</v>
+        <v>40.43</v>
       </c>
       <c r="H46" t="n">
-        <v>-11.78</v>
+        <v>-9.75</v>
       </c>
       <c r="I46" t="n">
-        <v>0.46</v>
+        <v>0.64</v>
       </c>
       <c r="J46" t="n">
-        <v>10.85</v>
+        <v>2.75</v>
       </c>
       <c r="K46" t="n">
-        <v>2.59</v>
+        <v>3.84</v>
       </c>
       <c r="L46" t="n">
-        <v>415.13</v>
+        <v>70.66</v>
       </c>
       <c r="M46" t="n">
-        <v>420.56</v>
+        <v>72.03</v>
       </c>
       <c r="N46" t="n">
-        <v>404.28</v>
+        <v>67.91</v>
       </c>
       <c r="O46" t="n">
-        <v>442.8</v>
+        <v>77.66</v>
       </c>
       <c r="P46" t="n">
         <v>1.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>59.2</v>
+        <v>52.77</v>
       </c>
       <c r="R46" t="n">
-        <v>0.55</v>
+        <v>0.77</v>
       </c>
       <c r="S46" t="n">
-        <v>-3.18</v>
+        <v>-7.18</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5561,12 +5549,12 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>NEUTRO</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>SPY/QQQ</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -5599,68 +5587,68 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>71.52</v>
+        <v>413.08</v>
       </c>
       <c r="D47" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E47" t="n">
-        <v>2.49</v>
+        <v>-7.23</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.35</v>
+        <v>6.6</v>
       </c>
       <c r="G47" t="n">
-        <v>40.24</v>
+        <v>0.9</v>
       </c>
       <c r="H47" t="n">
-        <v>-9.9</v>
+        <v>-1.94</v>
       </c>
       <c r="I47" t="n">
-        <v>0.63</v>
+        <v>0.51</v>
       </c>
       <c r="J47" t="n">
-        <v>2.75</v>
+        <v>18.12</v>
       </c>
       <c r="K47" t="n">
-        <v>3.84</v>
+        <v>4.39</v>
       </c>
       <c r="L47" t="n">
-        <v>70.56</v>
+        <v>406.74</v>
       </c>
       <c r="M47" t="n">
-        <v>71.93000000000001</v>
+        <v>415.8</v>
       </c>
       <c r="N47" t="n">
-        <v>67.81</v>
+        <v>388.62</v>
       </c>
       <c r="O47" t="n">
-        <v>77.56</v>
+        <v>452.94</v>
       </c>
       <c r="P47" t="n">
         <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>52.53</v>
+        <v>60.98</v>
       </c>
       <c r="R47" t="n">
-        <v>0.63</v>
+        <v>2.16</v>
       </c>
       <c r="S47" t="n">
-        <v>-7.31</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>BAJA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5670,12 +5658,12 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>NEUTRO</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>SPY/QQQ</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -5696,76 +5684,76 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; RSI saludable; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ; Lejos del máximo 20D</t>
+          <t>Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>412.68</v>
+        <v>33.75</v>
       </c>
       <c r="D48" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E48" t="n">
-        <v>-7.32</v>
+        <v>5.47</v>
       </c>
       <c r="F48" t="n">
-        <v>6.5</v>
+        <v>15.66</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8100000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="H48" t="n">
-        <v>-2.05</v>
+        <v>7.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.51</v>
+        <v>0.73</v>
       </c>
       <c r="J48" t="n">
-        <v>18.12</v>
+        <v>2.48</v>
       </c>
       <c r="K48" t="n">
-        <v>4.39</v>
+        <v>7.36</v>
       </c>
       <c r="L48" t="n">
-        <v>406.34</v>
+        <v>32.88</v>
       </c>
       <c r="M48" t="n">
-        <v>415.4</v>
+        <v>34.12</v>
       </c>
       <c r="N48" t="n">
-        <v>388.22</v>
+        <v>30.4</v>
       </c>
       <c r="O48" t="n">
-        <v>452.54</v>
+        <v>39.21</v>
       </c>
       <c r="P48" t="n">
         <v>1.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>60.88</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="R48" t="n">
-        <v>2.06</v>
+        <v>10.9</v>
       </c>
       <c r="S48" t="n">
-        <v>-8.98</v>
+        <v>-7.2</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5784,15 +5772,19 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="Z48" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -5805,12 +5797,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado NEUTRO +; Precio sobre MA20; MA20 sobre MA50; MACD mejorando; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
+          <t>Tendencia larga débil; RSI algo alto; MACD sin confirmar; Volumen bajo; Algo extendida sobre MA20</t>
         </is>
       </c>
     </row>
@@ -5826,55 +5818,55 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>85.83</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="D49" t="n">
         <v>63</v>
       </c>
       <c r="E49" t="n">
-        <v>6.46</v>
+        <v>6.76</v>
       </c>
       <c r="F49" t="n">
-        <v>15.97</v>
+        <v>16.3</v>
       </c>
       <c r="G49" t="n">
-        <v>20.58</v>
+        <v>20.92</v>
       </c>
       <c r="H49" t="n">
-        <v>7.42</v>
+        <v>7.76</v>
       </c>
       <c r="I49" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="J49" t="n">
         <v>7.61</v>
       </c>
       <c r="K49" t="n">
-        <v>8.869999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="L49" t="n">
-        <v>83.17</v>
+        <v>83.41</v>
       </c>
       <c r="M49" t="n">
-        <v>86.97</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>75.56</v>
+        <v>75.8</v>
       </c>
       <c r="O49" t="n">
-        <v>102.57</v>
+        <v>102.81</v>
       </c>
       <c r="P49" t="n">
         <v>1.63</v>
       </c>
       <c r="Q49" t="n">
-        <v>65.20999999999999</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="R49" t="n">
-        <v>4.2</v>
+        <v>4.47</v>
       </c>
       <c r="S49" t="n">
-        <v>-10.89</v>
+        <v>-10.64</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5893,7 +5885,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -5939,25 +5931,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>250.49</v>
+        <v>250.55</v>
       </c>
       <c r="D50" t="n">
         <v>72</v>
       </c>
       <c r="E50" t="n">
-        <v>6.11</v>
+        <v>6.13</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.13</v>
+        <v>-2.11</v>
       </c>
       <c r="G50" t="n">
-        <v>-1.84</v>
+        <v>-1.81</v>
       </c>
       <c r="H50" t="n">
-        <v>-10.68</v>
+        <v>-10.65</v>
       </c>
       <c r="I50" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>9.289999999999999</v>
@@ -5966,28 +5958,28 @@
         <v>3.71</v>
       </c>
       <c r="L50" t="n">
-        <v>247.23</v>
+        <v>247.3</v>
       </c>
       <c r="M50" t="n">
-        <v>251.88</v>
+        <v>251.94</v>
       </c>
       <c r="N50" t="n">
-        <v>237.94</v>
+        <v>238</v>
       </c>
       <c r="O50" t="n">
-        <v>270.93</v>
+        <v>271</v>
       </c>
       <c r="P50" t="n">
         <v>1.63</v>
       </c>
       <c r="Q50" t="n">
-        <v>53.3</v>
+        <v>53.35</v>
       </c>
       <c r="R50" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S50" t="n">
-        <v>-5.51</v>
+        <v>-5.48</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6006,7 +5998,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -6048,22 +6040,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>739.9299999999999</v>
+        <v>740.21</v>
       </c>
       <c r="D51" t="n">
         <v>70</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="F51" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="G51" t="n">
-        <v>7.94</v>
+        <v>7.98</v>
       </c>
       <c r="H51" t="n">
-        <v>-4.51</v>
+        <v>-4.46</v>
       </c>
       <c r="I51" t="n">
         <v>0.57</v>
@@ -6075,28 +6067,28 @@
         <v>1.01</v>
       </c>
       <c r="L51" t="n">
-        <v>737.3</v>
+        <v>737.58</v>
       </c>
       <c r="M51" t="n">
-        <v>741.0599999999999</v>
+        <v>741.34</v>
       </c>
       <c r="N51" t="n">
-        <v>729.8</v>
+        <v>730.08</v>
       </c>
       <c r="O51" t="n">
-        <v>756.4400000000001</v>
+        <v>756.72</v>
       </c>
       <c r="P51" t="n">
         <v>1.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>67.11</v>
+        <v>67.25</v>
       </c>
       <c r="R51" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S51" t="n">
-        <v>-1.28</v>
+        <v>-1.24</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6157,25 +6149,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>680.24</v>
+        <v>680.5700000000001</v>
       </c>
       <c r="D52" t="n">
         <v>70</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.32</v>
+        <v>-0.27</v>
       </c>
       <c r="F52" t="n">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="G52" t="n">
-        <v>7.94</v>
+        <v>7.99</v>
       </c>
       <c r="H52" t="n">
-        <v>-4.52</v>
+        <v>-4.46</v>
       </c>
       <c r="I52" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="J52" t="n">
         <v>6.87</v>
@@ -6184,28 +6176,28 @@
         <v>1.01</v>
       </c>
       <c r="L52" t="n">
-        <v>677.84</v>
+        <v>678.17</v>
       </c>
       <c r="M52" t="n">
-        <v>681.27</v>
+        <v>681.6</v>
       </c>
       <c r="N52" t="n">
-        <v>670.97</v>
+        <v>671.3</v>
       </c>
       <c r="O52" t="n">
-        <v>695.34</v>
+        <v>695.67</v>
       </c>
       <c r="P52" t="n">
         <v>1.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>67.34</v>
+        <v>67.53</v>
       </c>
       <c r="R52" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="S52" t="n">
-        <v>-1.29</v>
+        <v>-1.24</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6272,19 +6264,19 @@
         <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>7.17</v>
+        <v>7.23</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.28</v>
+        <v>-1.22</v>
       </c>
       <c r="G53" t="n">
-        <v>-8.4</v>
+        <v>-8.35</v>
       </c>
       <c r="H53" t="n">
-        <v>-9.83</v>
+        <v>-9.76</v>
       </c>
       <c r="I53" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="J53" t="n">
         <v>0.48</v>
@@ -6293,28 +6285,28 @@
         <v>5.21</v>
       </c>
       <c r="L53" t="n">
-        <v>9.1</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>9.34</v>
+        <v>9.35</v>
       </c>
       <c r="N53" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>10.33</v>
+        <v>10.34</v>
       </c>
       <c r="P53" t="n">
         <v>1.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>55.98</v>
+        <v>56.04</v>
       </c>
       <c r="R53" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="S53" t="n">
-        <v>-6.17</v>
+        <v>-6.12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6333,7 +6325,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -6375,25 +6367,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>44.99</v>
+        <v>45</v>
       </c>
       <c r="D54" t="n">
         <v>62</v>
       </c>
       <c r="E54" t="n">
-        <v>-4.44</v>
+        <v>-4.42</v>
       </c>
       <c r="F54" t="n">
-        <v>14.91</v>
+        <v>14.94</v>
       </c>
       <c r="G54" t="n">
-        <v>20.85</v>
+        <v>20.89</v>
       </c>
       <c r="H54" t="n">
-        <v>6.36</v>
+        <v>6.4</v>
       </c>
       <c r="I54" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="J54" t="n">
         <v>1.23</v>
@@ -6402,28 +6394,28 @@
         <v>2.74</v>
       </c>
       <c r="L54" t="n">
-        <v>44.56</v>
+        <v>44.57</v>
       </c>
       <c r="M54" t="n">
-        <v>45.17</v>
+        <v>45.19</v>
       </c>
       <c r="N54" t="n">
-        <v>43.32</v>
+        <v>43.33</v>
       </c>
       <c r="O54" t="n">
-        <v>47.7</v>
+        <v>47.71</v>
       </c>
       <c r="P54" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q54" t="n">
-        <v>66.54000000000001</v>
+        <v>66.59</v>
       </c>
       <c r="R54" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S54" t="n">
-        <v>-5.86</v>
+        <v>-5.84</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6484,22 +6476,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>207.67</v>
+        <v>207.86</v>
       </c>
       <c r="D55" t="n">
         <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>7.81</v>
+        <v>7.91</v>
       </c>
       <c r="F55" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="G55" t="n">
-        <v>26.77</v>
+        <v>26.89</v>
       </c>
       <c r="H55" t="n">
-        <v>-8.5</v>
+        <v>-8.4</v>
       </c>
       <c r="I55" t="n">
         <v>0.39</v>
@@ -6508,31 +6500,31 @@
         <v>15.04</v>
       </c>
       <c r="K55" t="n">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="L55" t="n">
-        <v>202.4</v>
+        <v>202.6</v>
       </c>
       <c r="M55" t="n">
-        <v>209.92</v>
+        <v>210.12</v>
       </c>
       <c r="N55" t="n">
-        <v>187.37</v>
+        <v>187.56</v>
       </c>
       <c r="O55" t="n">
-        <v>240.75</v>
+        <v>240.94</v>
       </c>
       <c r="P55" t="n">
         <v>1.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>50.92</v>
+        <v>50.98</v>
       </c>
       <c r="R55" t="n">
-        <v>-1.67</v>
+        <v>-1.58</v>
       </c>
       <c r="S55" t="n">
-        <v>-19.78</v>
+        <v>-19.71</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6551,7 +6543,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -6593,55 +6585,55 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>13.42</v>
+        <v>13.36</v>
       </c>
       <c r="D56" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E56" t="n">
-        <v>5.25</v>
+        <v>4.82</v>
       </c>
       <c r="F56" t="n">
-        <v>13.34</v>
+        <v>12.88</v>
       </c>
       <c r="G56" t="n">
-        <v>66.70999999999999</v>
+        <v>66.02</v>
       </c>
       <c r="H56" t="n">
-        <v>4.79</v>
+        <v>4.34</v>
       </c>
       <c r="I56" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>7.47</v>
+        <v>7.5</v>
       </c>
       <c r="L56" t="n">
-        <v>13.07</v>
+        <v>13.01</v>
       </c>
       <c r="M56" t="n">
-        <v>13.57</v>
+        <v>13.52</v>
       </c>
       <c r="N56" t="n">
-        <v>12.07</v>
+        <v>12.01</v>
       </c>
       <c r="O56" t="n">
-        <v>15.63</v>
+        <v>15.57</v>
       </c>
       <c r="P56" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>60.66</v>
+        <v>60.33</v>
       </c>
       <c r="R56" t="n">
-        <v>9.51</v>
+        <v>9.08</v>
       </c>
       <c r="S56" t="n">
-        <v>-2.75</v>
+        <v>-3.15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6660,7 +6652,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>BTC-USD 1.48% · ETH-USD -5.3%</t>
+          <t>BTC-USD 1.43% · ETH-USD -5.34%</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -6690,7 +6682,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.48% · ETH-USD -5.3%; Tendencia larga débil; MACD sin confirmar; Algo extendida sobre MA20; Volatilidad alta</t>
+          <t>Sector no acompaña: BTC-USD 1.43% · ETH-USD -5.34%; Tendencia larga débil; MACD sin confirmar; Algo extendida sobre MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -6706,22 +6698,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>253.78</v>
+        <v>253.35</v>
       </c>
       <c r="D57" t="n">
         <v>95</v>
       </c>
       <c r="E57" t="n">
-        <v>14.72</v>
+        <v>14.53</v>
       </c>
       <c r="F57" t="n">
-        <v>29.1</v>
+        <v>28.88</v>
       </c>
       <c r="G57" t="n">
-        <v>98.05</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>20.55</v>
+        <v>20.34</v>
       </c>
       <c r="I57" t="n">
         <v>1.23</v>
@@ -6730,31 +6722,31 @@
         <v>17.9</v>
       </c>
       <c r="K57" t="n">
-        <v>7.05</v>
+        <v>7.07</v>
       </c>
       <c r="L57" t="n">
-        <v>247.52</v>
+        <v>247.08</v>
       </c>
       <c r="M57" t="n">
-        <v>256.46</v>
+        <v>256.03</v>
       </c>
       <c r="N57" t="n">
-        <v>229.62</v>
+        <v>229.18</v>
       </c>
       <c r="O57" t="n">
-        <v>293.16</v>
+        <v>292.72</v>
       </c>
       <c r="P57" t="n">
         <v>1.63</v>
       </c>
       <c r="Q57" t="n">
-        <v>63.86</v>
+        <v>63.76</v>
       </c>
       <c r="R57" t="n">
-        <v>17.37</v>
+        <v>17.18</v>
       </c>
       <c r="S57" t="n">
-        <v>-2.18</v>
+        <v>-2.35</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6773,7 +6765,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6798,7 +6790,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6819,55 +6811,55 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>117.99</v>
+        <v>117.69</v>
       </c>
       <c r="D58" t="n">
         <v>85</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.91</v>
+        <v>-2.16</v>
       </c>
       <c r="F58" t="n">
-        <v>80.77</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>155.83</v>
+        <v>155.19</v>
       </c>
       <c r="H58" t="n">
-        <v>72.22</v>
+        <v>71.78</v>
       </c>
       <c r="I58" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="J58" t="n">
         <v>10.24</v>
       </c>
       <c r="K58" t="n">
-        <v>8.68</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>114.41</v>
+        <v>114.11</v>
       </c>
       <c r="M58" t="n">
-        <v>119.53</v>
+        <v>119.23</v>
       </c>
       <c r="N58" t="n">
-        <v>104.16</v>
+        <v>103.87</v>
       </c>
       <c r="O58" t="n">
-        <v>140.52</v>
+        <v>140.23</v>
       </c>
       <c r="P58" t="n">
         <v>1.63</v>
       </c>
       <c r="Q58" t="n">
-        <v>64.59999999999999</v>
+        <v>64.47</v>
       </c>
       <c r="R58" t="n">
-        <v>12.85</v>
+        <v>12.58</v>
       </c>
       <c r="S58" t="n">
-        <v>-11.12</v>
+        <v>-11.34</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6886,7 +6878,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -6911,7 +6903,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -6932,55 +6924,55 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>445.88</v>
+        <v>444.71</v>
       </c>
       <c r="D59" t="n">
         <v>68</v>
       </c>
       <c r="E59" t="n">
-        <v>0.09</v>
+        <v>-0.18</v>
       </c>
       <c r="F59" t="n">
-        <v>46.93</v>
+        <v>46.55</v>
       </c>
       <c r="G59" t="n">
-        <v>108.51</v>
+        <v>107.97</v>
       </c>
       <c r="H59" t="n">
-        <v>38.38</v>
+        <v>38.01</v>
       </c>
       <c r="I59" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="J59" t="n">
         <v>29.9</v>
       </c>
       <c r="K59" t="n">
-        <v>6.71</v>
+        <v>6.72</v>
       </c>
       <c r="L59" t="n">
-        <v>435.42</v>
+        <v>434.25</v>
       </c>
       <c r="M59" t="n">
-        <v>450.36</v>
+        <v>449.2</v>
       </c>
       <c r="N59" t="n">
-        <v>405.52</v>
+        <v>404.35</v>
       </c>
       <c r="O59" t="n">
-        <v>511.65</v>
+        <v>510.49</v>
       </c>
       <c r="P59" t="n">
         <v>1.63</v>
       </c>
       <c r="Q59" t="n">
-        <v>68.05</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="R59" t="n">
-        <v>13.57</v>
+        <v>13.29</v>
       </c>
       <c r="S59" t="n">
-        <v>-4.97</v>
+        <v>-5.22</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6999,7 +6991,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -7020,7 +7012,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7041,25 +7033,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>728.84</v>
+        <v>728.05</v>
       </c>
       <c r="D60" t="n">
         <v>61</v>
       </c>
       <c r="E60" t="n">
-        <v>-9.31</v>
+        <v>-9.4</v>
       </c>
       <c r="F60" t="n">
-        <v>49.51</v>
+        <v>49.35</v>
       </c>
       <c r="G60" t="n">
-        <v>74.43000000000001</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>40.96</v>
+        <v>40.81</v>
       </c>
       <c r="I60" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="J60" t="n">
         <v>61.19</v>
@@ -7068,28 +7060,28 @@
         <v>8.4</v>
       </c>
       <c r="L60" t="n">
-        <v>707.42</v>
+        <v>706.63</v>
       </c>
       <c r="M60" t="n">
-        <v>738.02</v>
+        <v>737.23</v>
       </c>
       <c r="N60" t="n">
-        <v>646.23</v>
+        <v>645.4400000000001</v>
       </c>
       <c r="O60" t="n">
-        <v>863.46</v>
+        <v>862.67</v>
       </c>
       <c r="P60" t="n">
         <v>1.63</v>
       </c>
       <c r="Q60" t="n">
-        <v>69.13</v>
+        <v>69.09</v>
       </c>
       <c r="R60" t="n">
-        <v>13.55</v>
+        <v>13.44</v>
       </c>
       <c r="S60" t="n">
-        <v>-10.97</v>
+        <v>-11.07</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7108,7 +7100,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -7129,7 +7121,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7150,22 +7142,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>128.81</v>
+        <v>128.77</v>
       </c>
       <c r="D61" t="n">
         <v>78</v>
       </c>
       <c r="E61" t="n">
-        <v>9.449999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="F61" t="n">
-        <v>47.9</v>
+        <v>47.86</v>
       </c>
       <c r="G61" t="n">
-        <v>71.22</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>39.35</v>
+        <v>39.32</v>
       </c>
       <c r="I61" t="n">
         <v>0.44</v>
@@ -7174,19 +7166,19 @@
         <v>5.49</v>
       </c>
       <c r="K61" t="n">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
       <c r="L61" t="n">
-        <v>126.89</v>
+        <v>126.85</v>
       </c>
       <c r="M61" t="n">
-        <v>129.63</v>
+        <v>129.6</v>
       </c>
       <c r="N61" t="n">
-        <v>121.39</v>
+        <v>121.36</v>
       </c>
       <c r="O61" t="n">
-        <v>140.9</v>
+        <v>140.86</v>
       </c>
       <c r="P61" t="n">
         <v>1.63</v>
@@ -7195,10 +7187,10 @@
         <v>96.7</v>
       </c>
       <c r="R61" t="n">
-        <v>25</v>
+        <v>24.97</v>
       </c>
       <c r="S61" t="n">
-        <v>-0.38</v>
+        <v>-0.41</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7217,7 +7209,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -7259,22 +7251,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>301.21</v>
+        <v>301.27</v>
       </c>
       <c r="D62" t="n">
         <v>78</v>
       </c>
       <c r="E62" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="F62" t="n">
-        <v>10.37</v>
+        <v>10.39</v>
       </c>
       <c r="G62" t="n">
-        <v>10.78</v>
+        <v>10.8</v>
       </c>
       <c r="H62" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="I62" t="n">
         <v>0.41</v>
@@ -7286,28 +7278,28 @@
         <v>2.13</v>
       </c>
       <c r="L62" t="n">
-        <v>298.96</v>
+        <v>299.01</v>
       </c>
       <c r="M62" t="n">
-        <v>302.17</v>
+        <v>302.23</v>
       </c>
       <c r="N62" t="n">
-        <v>292.53</v>
+        <v>292.59</v>
       </c>
       <c r="O62" t="n">
-        <v>315.36</v>
+        <v>315.41</v>
       </c>
       <c r="P62" t="n">
         <v>1.63</v>
       </c>
       <c r="Q62" t="n">
-        <v>84.45</v>
+        <v>84.47</v>
       </c>
       <c r="R62" t="n">
-        <v>5.44</v>
+        <v>5.46</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.66</v>
+        <v>-0.64</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7326,7 +7318,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -7368,55 +7360,55 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>212.81</v>
+        <v>212.61</v>
       </c>
       <c r="D63" t="n">
         <v>76</v>
       </c>
       <c r="E63" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="F63" t="n">
-        <v>61.05</v>
+        <v>60.9</v>
       </c>
       <c r="G63" t="n">
-        <v>103.78</v>
+        <v>103.59</v>
       </c>
       <c r="H63" t="n">
-        <v>52.5</v>
+        <v>52.36</v>
       </c>
       <c r="I63" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J63" t="n">
         <v>12.32</v>
       </c>
       <c r="K63" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="L63" t="n">
-        <v>208.5</v>
+        <v>208.3</v>
       </c>
       <c r="M63" t="n">
-        <v>214.66</v>
+        <v>214.46</v>
       </c>
       <c r="N63" t="n">
-        <v>196.17</v>
+        <v>195.97</v>
       </c>
       <c r="O63" t="n">
-        <v>239.92</v>
+        <v>239.72</v>
       </c>
       <c r="P63" t="n">
         <v>1.63</v>
       </c>
       <c r="Q63" t="n">
-        <v>89.93000000000001</v>
+        <v>89.75</v>
       </c>
       <c r="R63" t="n">
-        <v>24.87</v>
+        <v>24.76</v>
       </c>
       <c r="S63" t="n">
-        <v>-3.42</v>
+        <v>-3.51</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7435,7 +7427,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -7477,22 +7469,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>176.46</v>
+        <v>176.52</v>
       </c>
       <c r="D64" t="n">
         <v>70</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="F64" t="n">
-        <v>11.62</v>
+        <v>11.66</v>
       </c>
       <c r="G64" t="n">
-        <v>25.91</v>
+        <v>25.95</v>
       </c>
       <c r="H64" t="n">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
       <c r="I64" t="n">
         <v>0.68</v>
@@ -7504,28 +7496,28 @@
         <v>2.36</v>
       </c>
       <c r="L64" t="n">
-        <v>175</v>
+        <v>175.06</v>
       </c>
       <c r="M64" t="n">
-        <v>177.08</v>
+        <v>177.14</v>
       </c>
       <c r="N64" t="n">
-        <v>170.85</v>
+        <v>170.91</v>
       </c>
       <c r="O64" t="n">
-        <v>185.61</v>
+        <v>185.67</v>
       </c>
       <c r="P64" t="n">
         <v>1.63</v>
       </c>
       <c r="Q64" t="n">
-        <v>73.87</v>
+        <v>73.92</v>
       </c>
       <c r="R64" t="n">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="S64" t="n">
-        <v>-2.09</v>
+        <v>-2.05</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7544,7 +7536,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -7586,55 +7578,55 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>133.76</v>
+        <v>134.22</v>
       </c>
       <c r="D65" t="n">
         <v>66</v>
       </c>
       <c r="E65" t="n">
-        <v>7.74</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>48.56</v>
+        <v>49.07</v>
       </c>
       <c r="G65" t="n">
-        <v>91.17</v>
+        <v>91.83</v>
       </c>
       <c r="H65" t="n">
-        <v>40.01</v>
+        <v>40.53</v>
       </c>
       <c r="I65" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="J65" t="n">
-        <v>11.33</v>
+        <v>11.34</v>
       </c>
       <c r="K65" t="n">
-        <v>8.470000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>129.79</v>
+        <v>130.25</v>
       </c>
       <c r="M65" t="n">
-        <v>135.46</v>
+        <v>135.92</v>
       </c>
       <c r="N65" t="n">
-        <v>118.46</v>
+        <v>118.91</v>
       </c>
       <c r="O65" t="n">
-        <v>158.69</v>
+        <v>159.17</v>
       </c>
       <c r="P65" t="n">
         <v>1.63</v>
       </c>
       <c r="Q65" t="n">
-        <v>76.38</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="R65" t="n">
-        <v>33.77</v>
+        <v>34.2</v>
       </c>
       <c r="S65" t="n">
-        <v>-3.34</v>
+        <v>-3.01</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7695,55 +7687,55 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>246.83</v>
+        <v>247.25</v>
       </c>
       <c r="D66" t="n">
         <v>63</v>
       </c>
       <c r="E66" t="n">
-        <v>8.359999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>36.22</v>
+        <v>36.45</v>
       </c>
       <c r="G66" t="n">
-        <v>74.23</v>
+        <v>74.53</v>
       </c>
       <c r="H66" t="n">
-        <v>27.67</v>
+        <v>27.91</v>
       </c>
       <c r="I66" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="J66" t="n">
         <v>10.83</v>
       </c>
       <c r="K66" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="L66" t="n">
-        <v>243.04</v>
+        <v>243.46</v>
       </c>
       <c r="M66" t="n">
-        <v>248.45</v>
+        <v>248.87</v>
       </c>
       <c r="N66" t="n">
-        <v>232.21</v>
+        <v>232.63</v>
       </c>
       <c r="O66" t="n">
-        <v>270.66</v>
+        <v>271.08</v>
       </c>
       <c r="P66" t="n">
         <v>1.63</v>
       </c>
       <c r="Q66" t="n">
-        <v>90.13</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="R66" t="n">
-        <v>20.79</v>
+        <v>20.99</v>
       </c>
       <c r="S66" t="n">
-        <v>-1.27</v>
+        <v>-1.1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7762,7 +7754,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -7804,55 +7796,55 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>87.65000000000001</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="D67" t="n">
         <v>63</v>
       </c>
       <c r="E67" t="n">
-        <v>12.08</v>
+        <v>12.31</v>
       </c>
       <c r="F67" t="n">
-        <v>11.37</v>
+        <v>11.59</v>
       </c>
       <c r="G67" t="n">
-        <v>23.21</v>
+        <v>23.45</v>
       </c>
       <c r="H67" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="I67" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J67" t="n">
         <v>3.85</v>
       </c>
       <c r="K67" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="L67" t="n">
-        <v>86.3</v>
+        <v>86.48</v>
       </c>
       <c r="M67" t="n">
-        <v>88.23</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="N67" t="n">
-        <v>82.45999999999999</v>
+        <v>82.63</v>
       </c>
       <c r="O67" t="n">
-        <v>96.11</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="P67" t="n">
         <v>1.63</v>
       </c>
       <c r="Q67" t="n">
-        <v>74.39</v>
+        <v>74.55</v>
       </c>
       <c r="R67" t="n">
-        <v>10.23</v>
+        <v>10.44</v>
       </c>
       <c r="S67" t="n">
-        <v>-2.61</v>
+        <v>-2.42</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7871,7 +7863,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -7913,55 +7905,55 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>113.5</v>
+        <v>113.53</v>
       </c>
       <c r="D68" t="n">
         <v>63</v>
       </c>
       <c r="E68" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F68" t="n">
-        <v>10.16</v>
+        <v>10.19</v>
       </c>
       <c r="G68" t="n">
-        <v>23.27</v>
+        <v>23.32</v>
       </c>
       <c r="H68" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="I68" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="J68" t="n">
         <v>2.47</v>
       </c>
       <c r="K68" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="L68" t="n">
-        <v>112.63</v>
+        <v>112.67</v>
       </c>
       <c r="M68" t="n">
-        <v>113.87</v>
+        <v>113.9</v>
       </c>
       <c r="N68" t="n">
-        <v>110.16</v>
+        <v>110.2</v>
       </c>
       <c r="O68" t="n">
-        <v>118.93</v>
+        <v>118.96</v>
       </c>
       <c r="P68" t="n">
         <v>1.63</v>
       </c>
       <c r="Q68" t="n">
-        <v>75.02</v>
+        <v>75.06</v>
       </c>
       <c r="R68" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="S68" t="n">
-        <v>-1.84</v>
+        <v>-1.81</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7980,7 +7972,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -8022,55 +8014,55 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>643.05</v>
+        <v>643.47</v>
       </c>
       <c r="D69" t="n">
         <v>62</v>
       </c>
       <c r="E69" t="n">
-        <v>14.31</v>
+        <v>14.38</v>
       </c>
       <c r="F69" t="n">
-        <v>37.79</v>
+        <v>37.88</v>
       </c>
       <c r="G69" t="n">
-        <v>83.59999999999999</v>
+        <v>83.72</v>
       </c>
       <c r="H69" t="n">
-        <v>29.24</v>
+        <v>29.34</v>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="J69" t="n">
         <v>25.82</v>
       </c>
       <c r="K69" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="L69" t="n">
-        <v>634.01</v>
+        <v>634.4299999999999</v>
       </c>
       <c r="M69" t="n">
-        <v>646.92</v>
+        <v>647.34</v>
       </c>
       <c r="N69" t="n">
-        <v>608.1900000000001</v>
+        <v>608.61</v>
       </c>
       <c r="O69" t="n">
-        <v>699.86</v>
+        <v>700.28</v>
       </c>
       <c r="P69" t="n">
         <v>1.63</v>
       </c>
       <c r="Q69" t="n">
-        <v>95.23</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="R69" t="n">
-        <v>24.77</v>
+        <v>24.84</v>
       </c>
       <c r="S69" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.49</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8089,7 +8081,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -8131,55 +8123,55 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>390.92</v>
+        <v>389.99</v>
       </c>
       <c r="D70" t="n">
         <v>46</v>
       </c>
       <c r="E70" t="n">
-        <v>-9.59</v>
+        <v>-9.81</v>
       </c>
       <c r="F70" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="G70" t="n">
-        <v>10.12</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H70" t="n">
-        <v>-6.06</v>
+        <v>-6.29</v>
       </c>
       <c r="I70" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="J70" t="n">
         <v>13.58</v>
       </c>
       <c r="K70" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="L70" t="n">
-        <v>386.16</v>
+        <v>385.24</v>
       </c>
       <c r="M70" t="n">
-        <v>392.95</v>
+        <v>392.03</v>
       </c>
       <c r="N70" t="n">
-        <v>372.59</v>
+        <v>371.66</v>
       </c>
       <c r="O70" t="n">
-        <v>420.78</v>
+        <v>419.86</v>
       </c>
       <c r="P70" t="n">
         <v>1.63</v>
       </c>
       <c r="Q70" t="n">
-        <v>44.58</v>
+        <v>44.19</v>
       </c>
       <c r="R70" t="n">
-        <v>-4.12</v>
+        <v>-4.33</v>
       </c>
       <c r="S70" t="n">
-        <v>-10.28</v>
+        <v>-10.5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8198,7 +8190,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -8223,7 +8215,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -8244,22 +8236,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>243.36</v>
+        <v>243.13</v>
       </c>
       <c r="D71" t="n">
         <v>33</v>
       </c>
       <c r="E71" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="F71" t="n">
-        <v>-5.26</v>
+        <v>-5.35</v>
       </c>
       <c r="G71" t="n">
-        <v>10.39</v>
+        <v>10.29</v>
       </c>
       <c r="H71" t="n">
-        <v>-13.81</v>
+        <v>-13.89</v>
       </c>
       <c r="I71" t="n">
         <v>0.5</v>
@@ -8271,28 +8263,28 @@
         <v>3.3</v>
       </c>
       <c r="L71" t="n">
-        <v>240.55</v>
+        <v>240.32</v>
       </c>
       <c r="M71" t="n">
-        <v>244.57</v>
+        <v>244.33</v>
       </c>
       <c r="N71" t="n">
-        <v>232.53</v>
+        <v>232.3</v>
       </c>
       <c r="O71" t="n">
-        <v>261.01</v>
+        <v>260.78</v>
       </c>
       <c r="P71" t="n">
         <v>1.63</v>
       </c>
       <c r="Q71" t="n">
-        <v>25.34</v>
+        <v>25.24</v>
       </c>
       <c r="R71" t="n">
-        <v>-4.27</v>
+        <v>-4.36</v>
       </c>
       <c r="S71" t="n">
-        <v>-11.44</v>
+        <v>-11.53</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8311,7 +8303,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>XLE 5.77% · CL=F 5.65%</t>
+          <t>XLE 5.63% · CL=F 5.62%</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -8336,7 +8328,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.77% · CL=F 5.65%; Tendencia larga positiva; MACD mejorando; Momentum 5D sano</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Tendencia larga positiva; MACD mejorando; Momentum 5D sano</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8357,22 +8349,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>418.57</v>
+        <v>418.55</v>
       </c>
       <c r="D72" t="n">
         <v>59</v>
       </c>
       <c r="E72" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="F72" t="n">
         <v>-0.97</v>
       </c>
       <c r="G72" t="n">
-        <v>28.87</v>
+        <v>28.86</v>
       </c>
       <c r="H72" t="n">
-        <v>-9.52</v>
+        <v>-9.51</v>
       </c>
       <c r="I72" t="n">
         <v>0.48</v>
@@ -8384,22 +8376,22 @@
         <v>3.98</v>
       </c>
       <c r="L72" t="n">
-        <v>412.74</v>
+        <v>412.72</v>
       </c>
       <c r="M72" t="n">
-        <v>421.07</v>
+        <v>421.05</v>
       </c>
       <c r="N72" t="n">
-        <v>396.09</v>
+        <v>396.07</v>
       </c>
       <c r="O72" t="n">
-        <v>455.21</v>
+        <v>455.19</v>
       </c>
       <c r="P72" t="n">
         <v>1.63</v>
       </c>
       <c r="Q72" t="n">
-        <v>50.46</v>
+        <v>50.45</v>
       </c>
       <c r="R72" t="n">
         <v>-0.3</v>
@@ -8424,7 +8416,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -8445,7 +8437,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -8466,55 +8458,55 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1541.25</v>
+        <v>1540.01</v>
       </c>
       <c r="D73" t="n">
         <v>53</v>
       </c>
       <c r="E73" t="n">
-        <v>-6.61</v>
+        <v>-6.69</v>
       </c>
       <c r="F73" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="G73" t="n">
-        <v>27.25</v>
+        <v>27.14</v>
       </c>
       <c r="H73" t="n">
-        <v>-7.29</v>
+        <v>-7.36</v>
       </c>
       <c r="I73" t="n">
         <v>0.38</v>
       </c>
       <c r="J73" t="n">
-        <v>78.79000000000001</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
       <c r="L73" t="n">
-        <v>1513.68</v>
+        <v>1512.41</v>
       </c>
       <c r="M73" t="n">
-        <v>1553.07</v>
+        <v>1551.84</v>
       </c>
       <c r="N73" t="n">
-        <v>1434.89</v>
+        <v>1433.56</v>
       </c>
       <c r="O73" t="n">
-        <v>1714.58</v>
+        <v>1713.48</v>
       </c>
       <c r="P73" t="n">
         <v>1.63</v>
       </c>
       <c r="Q73" t="n">
-        <v>44.37</v>
+        <v>44.26</v>
       </c>
       <c r="R73" t="n">
-        <v>-2.46</v>
+        <v>-2.53</v>
       </c>
       <c r="S73" t="n">
-        <v>-8.01</v>
+        <v>-8.08</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8533,7 +8525,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -8554,7 +8546,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; MA20 sobre MA50; Tendencia larga positiva; MACD mejorando</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -8575,22 +8567,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>51.6</v>
+        <v>51.64</v>
       </c>
       <c r="D74" t="n">
         <v>57</v>
       </c>
       <c r="E74" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.16</v>
+        <v>-1.09</v>
       </c>
       <c r="G74" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="H74" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="I74" t="n">
         <v>0.78</v>
@@ -8602,28 +8594,28 @@
         <v>1.26</v>
       </c>
       <c r="L74" t="n">
-        <v>51.38</v>
+        <v>51.41</v>
       </c>
       <c r="M74" t="n">
-        <v>51.7</v>
+        <v>51.74</v>
       </c>
       <c r="N74" t="n">
-        <v>50.73</v>
+        <v>50.76</v>
       </c>
       <c r="O74" t="n">
-        <v>53.04</v>
+        <v>53.07</v>
       </c>
       <c r="P74" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q74" t="n">
-        <v>44.46</v>
+        <v>44.86</v>
       </c>
       <c r="R74" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="S74" t="n">
-        <v>-1.91</v>
+        <v>-1.84</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8684,22 +8676,22 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>88.3</v>
+        <v>88.47</v>
       </c>
       <c r="D75" t="n">
         <v>56</v>
       </c>
       <c r="E75" t="n">
-        <v>5.33</v>
+        <v>5.54</v>
       </c>
       <c r="F75" t="n">
-        <v>-3.71</v>
+        <v>-3.52</v>
       </c>
       <c r="G75" t="n">
-        <v>-22.45</v>
+        <v>-22.3</v>
       </c>
       <c r="H75" t="n">
-        <v>-12.26</v>
+        <v>-12.06</v>
       </c>
       <c r="I75" t="n">
         <v>0.31</v>
@@ -8708,31 +8700,31 @@
         <v>2.17</v>
       </c>
       <c r="K75" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="L75" t="n">
-        <v>87.54000000000001</v>
+        <v>87.72</v>
       </c>
       <c r="M75" t="n">
-        <v>88.63</v>
+        <v>88.8</v>
       </c>
       <c r="N75" t="n">
-        <v>85.37</v>
+        <v>85.55</v>
       </c>
       <c r="O75" t="n">
-        <v>93.06999999999999</v>
+        <v>93.25</v>
       </c>
       <c r="P75" t="n">
         <v>1.63</v>
       </c>
       <c r="Q75" t="n">
-        <v>43.21</v>
+        <v>43.62</v>
       </c>
       <c r="R75" t="n">
-        <v>0.38</v>
+        <v>0.57</v>
       </c>
       <c r="S75" t="n">
-        <v>-6.85</v>
+        <v>-6.66</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8793,22 +8785,22 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>874.05</v>
+        <v>872.92</v>
       </c>
       <c r="D76" t="n">
         <v>50</v>
       </c>
       <c r="E76" t="n">
-        <v>-3.13</v>
+        <v>-3.26</v>
       </c>
       <c r="F76" t="n">
-        <v>8.06</v>
+        <v>7.92</v>
       </c>
       <c r="G76" t="n">
-        <v>13.99</v>
+        <v>13.84</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.49</v>
+        <v>-0.62</v>
       </c>
       <c r="I76" t="n">
         <v>0.52</v>
@@ -8817,31 +8809,31 @@
         <v>29.39</v>
       </c>
       <c r="K76" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="L76" t="n">
-        <v>863.76</v>
+        <v>862.63</v>
       </c>
       <c r="M76" t="n">
-        <v>878.46</v>
+        <v>877.33</v>
       </c>
       <c r="N76" t="n">
-        <v>834.37</v>
+        <v>833.24</v>
       </c>
       <c r="O76" t="n">
-        <v>938.72</v>
+        <v>937.59</v>
       </c>
       <c r="P76" t="n">
         <v>1.63</v>
       </c>
       <c r="Q76" t="n">
-        <v>46.74</v>
+        <v>46.49</v>
       </c>
       <c r="R76" t="n">
-        <v>-0.39</v>
+        <v>-0.51</v>
       </c>
       <c r="S76" t="n">
-        <v>-6.15</v>
+        <v>-6.27</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8902,25 +8894,25 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>384.04</v>
+        <v>384.19</v>
       </c>
       <c r="D77" t="n">
         <v>50</v>
       </c>
       <c r="E77" t="n">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="F77" t="n">
-        <v>-6.03</v>
+        <v>-5.99</v>
       </c>
       <c r="G77" t="n">
-        <v>7.39</v>
+        <v>7.43</v>
       </c>
       <c r="H77" t="n">
-        <v>-14.58</v>
+        <v>-14.53</v>
       </c>
       <c r="I77" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="J77" t="n">
         <v>19.25</v>
@@ -8929,28 +8921,28 @@
         <v>5.01</v>
       </c>
       <c r="L77" t="n">
-        <v>377.3</v>
+        <v>377.45</v>
       </c>
       <c r="M77" t="n">
-        <v>386.92</v>
+        <v>387.08</v>
       </c>
       <c r="N77" t="n">
-        <v>358.04</v>
+        <v>358.2</v>
       </c>
       <c r="O77" t="n">
-        <v>426.39</v>
+        <v>426.54</v>
       </c>
       <c r="P77" t="n">
         <v>1.63</v>
       </c>
       <c r="Q77" t="n">
-        <v>48.41</v>
+        <v>48.47</v>
       </c>
       <c r="R77" t="n">
-        <v>-2.28</v>
+        <v>-2.24</v>
       </c>
       <c r="S77" t="n">
-        <v>-9.42</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8969,7 +8961,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
@@ -9011,19 +9003,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>124.99</v>
+        <v>124.97</v>
       </c>
       <c r="D78" t="n">
         <v>48</v>
       </c>
       <c r="E78" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="F78" t="n">
-        <v>-3.2</v>
+        <v>-3.21</v>
       </c>
       <c r="G78" t="n">
-        <v>14.62</v>
+        <v>14.6</v>
       </c>
       <c r="H78" t="n">
         <v>-11.75</v>
@@ -9038,28 +9030,28 @@
         <v>2.8</v>
       </c>
       <c r="L78" t="n">
-        <v>123.76</v>
+        <v>123.74</v>
       </c>
       <c r="M78" t="n">
-        <v>125.52</v>
+        <v>125.5</v>
       </c>
       <c r="N78" t="n">
-        <v>120.26</v>
+        <v>120.24</v>
       </c>
       <c r="O78" t="n">
-        <v>132.7</v>
+        <v>132.68</v>
       </c>
       <c r="P78" t="n">
         <v>1.63</v>
       </c>
       <c r="Q78" t="n">
-        <v>44.9</v>
+        <v>44.85</v>
       </c>
       <c r="R78" t="n">
-        <v>-0.83</v>
+        <v>-0.85</v>
       </c>
       <c r="S78" t="n">
-        <v>-5.27</v>
+        <v>-5.29</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9120,25 +9112,25 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>222.9</v>
+        <v>223.13</v>
       </c>
       <c r="D79" t="n">
         <v>43</v>
       </c>
       <c r="E79" t="n">
-        <v>3.85</v>
+        <v>3.96</v>
       </c>
       <c r="F79" t="n">
-        <v>-10.85</v>
+        <v>-10.76</v>
       </c>
       <c r="G79" t="n">
-        <v>-2.08</v>
+        <v>-1.98</v>
       </c>
       <c r="H79" t="n">
-        <v>-19.4</v>
+        <v>-19.3</v>
       </c>
       <c r="I79" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="J79" t="n">
         <v>5.56</v>
@@ -9147,28 +9139,28 @@
         <v>2.49</v>
       </c>
       <c r="L79" t="n">
-        <v>220.95</v>
+        <v>221.18</v>
       </c>
       <c r="M79" t="n">
-        <v>223.73</v>
+        <v>223.96</v>
       </c>
       <c r="N79" t="n">
-        <v>215.39</v>
+        <v>215.62</v>
       </c>
       <c r="O79" t="n">
-        <v>235.13</v>
+        <v>235.36</v>
       </c>
       <c r="P79" t="n">
         <v>1.63</v>
       </c>
       <c r="Q79" t="n">
-        <v>41.48</v>
+        <v>41.84</v>
       </c>
       <c r="R79" t="n">
-        <v>-1.03</v>
+        <v>-0.93</v>
       </c>
       <c r="S79" t="n">
-        <v>-4.84</v>
+        <v>-4.74</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9187,7 +9179,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -9229,22 +9221,22 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>74.68000000000001</v>
+        <v>74.73</v>
       </c>
       <c r="D80" t="n">
         <v>42</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.19</v>
+        <v>-1.12</v>
       </c>
       <c r="G80" t="n">
-        <v>4.62</v>
+        <v>4.7</v>
       </c>
       <c r="H80" t="n">
-        <v>-9.74</v>
+        <v>-9.66</v>
       </c>
       <c r="I80" t="n">
         <v>0.43</v>
@@ -9256,28 +9248,28 @@
         <v>3.49</v>
       </c>
       <c r="L80" t="n">
-        <v>73.77</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="M80" t="n">
-        <v>75.06999999999999</v>
+        <v>75.12</v>
       </c>
       <c r="N80" t="n">
-        <v>71.16</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="O80" t="n">
-        <v>80.42</v>
+        <v>80.47</v>
       </c>
       <c r="P80" t="n">
         <v>1.63</v>
       </c>
       <c r="Q80" t="n">
-        <v>50.2</v>
+        <v>50.36</v>
       </c>
       <c r="R80" t="n">
-        <v>-0.62</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="S80" t="n">
-        <v>-7.61</v>
+        <v>-7.54</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9296,7 +9288,7 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
@@ -9338,22 +9330,22 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>75.78</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="D81" t="n">
         <v>42</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.91</v>
+        <v>-2.93</v>
       </c>
       <c r="F81" t="n">
-        <v>-4.44</v>
+        <v>-4.46</v>
       </c>
       <c r="G81" t="n">
-        <v>5.15</v>
+        <v>5.13</v>
       </c>
       <c r="H81" t="n">
-        <v>-12.99</v>
+        <v>-13</v>
       </c>
       <c r="I81" t="n">
         <v>0.7</v>
@@ -9365,28 +9357,28 @@
         <v>3.17</v>
       </c>
       <c r="L81" t="n">
-        <v>74.94</v>
+        <v>74.92</v>
       </c>
       <c r="M81" t="n">
-        <v>76.14</v>
+        <v>76.13</v>
       </c>
       <c r="N81" t="n">
-        <v>72.54000000000001</v>
+        <v>72.52</v>
       </c>
       <c r="O81" t="n">
-        <v>81.06999999999999</v>
+        <v>81.05</v>
       </c>
       <c r="P81" t="n">
         <v>1.63</v>
       </c>
       <c r="Q81" t="n">
-        <v>49.84</v>
+        <v>49.8</v>
       </c>
       <c r="R81" t="n">
-        <v>-1.33</v>
+        <v>-1.35</v>
       </c>
       <c r="S81" t="n">
-        <v>-6.08</v>
+        <v>-6.1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9405,7 +9397,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
@@ -9447,55 +9439,55 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>76.11</v>
+        <v>76.17</v>
       </c>
       <c r="D82" t="n">
         <v>42</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.83</v>
+        <v>-0.76</v>
       </c>
       <c r="F82" t="n">
-        <v>-13.93</v>
+        <v>-13.86</v>
       </c>
       <c r="G82" t="n">
-        <v>3.71</v>
+        <v>3.79</v>
       </c>
       <c r="H82" t="n">
-        <v>-22.48</v>
+        <v>-22.4</v>
       </c>
       <c r="I82" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J82" t="n">
         <v>3.92</v>
       </c>
       <c r="K82" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="L82" t="n">
-        <v>74.73999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="M82" t="n">
-        <v>76.7</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="N82" t="n">
-        <v>70.81999999999999</v>
+        <v>70.88</v>
       </c>
       <c r="O82" t="n">
-        <v>84.73</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="P82" t="n">
         <v>1.63</v>
       </c>
       <c r="Q82" t="n">
-        <v>55.38</v>
+        <v>55.47</v>
       </c>
       <c r="R82" t="n">
-        <v>-2.36</v>
+        <v>-2.29</v>
       </c>
       <c r="S82" t="n">
-        <v>-13.13</v>
+        <v>-13.06</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9556,22 +9548,22 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>497.2</v>
+        <v>497.59</v>
       </c>
       <c r="D83" t="n">
         <v>38</v>
       </c>
       <c r="E83" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="F83" t="n">
-        <v>-2.54</v>
+        <v>-2.46</v>
       </c>
       <c r="G83" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="H83" t="n">
-        <v>-11.09</v>
+        <v>-11</v>
       </c>
       <c r="I83" t="n">
         <v>0.5600000000000001</v>
@@ -9583,28 +9575,28 @@
         <v>2.28</v>
       </c>
       <c r="L83" t="n">
-        <v>493.23</v>
+        <v>493.62</v>
       </c>
       <c r="M83" t="n">
-        <v>498.9</v>
+        <v>499.29</v>
       </c>
       <c r="N83" t="n">
-        <v>481.9</v>
+        <v>482.29</v>
       </c>
       <c r="O83" t="n">
-        <v>522.13</v>
+        <v>522.52</v>
       </c>
       <c r="P83" t="n">
         <v>1.63</v>
       </c>
       <c r="Q83" t="n">
-        <v>46.54</v>
+        <v>46.76</v>
       </c>
       <c r="R83" t="n">
-        <v>-0.65</v>
+        <v>-0.58</v>
       </c>
       <c r="S83" t="n">
-        <v>-6.93</v>
+        <v>-6.85</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9665,55 +9657,55 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>140.46</v>
+        <v>140.3</v>
       </c>
       <c r="D84" t="n">
         <v>31</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.17</v>
+        <v>-0.28</v>
       </c>
       <c r="F84" t="n">
-        <v>-20.97</v>
+        <v>-21.06</v>
       </c>
       <c r="G84" t="n">
-        <v>9.07</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>-29.52</v>
+        <v>-29.6</v>
       </c>
       <c r="I84" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J84" t="n">
         <v>8.07</v>
       </c>
       <c r="K84" t="n">
-        <v>5.74</v>
+        <v>5.75</v>
       </c>
       <c r="L84" t="n">
-        <v>137.63</v>
+        <v>137.48</v>
       </c>
       <c r="M84" t="n">
-        <v>141.67</v>
+        <v>141.51</v>
       </c>
       <c r="N84" t="n">
-        <v>129.56</v>
+        <v>129.41</v>
       </c>
       <c r="O84" t="n">
-        <v>158.21</v>
+        <v>158.05</v>
       </c>
       <c r="P84" t="n">
         <v>1.63</v>
       </c>
       <c r="Q84" t="n">
-        <v>22.55</v>
+        <v>22.49</v>
       </c>
       <c r="R84" t="n">
-        <v>-9.609999999999999</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="S84" t="n">
-        <v>-21.88</v>
+        <v>-21.97</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9732,7 +9724,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
@@ -9774,25 +9766,25 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>565.59</v>
+        <v>565.92</v>
       </c>
       <c r="D85" t="n">
         <v>30</v>
       </c>
       <c r="E85" t="n">
-        <v>-2.59</v>
+        <v>-2.54</v>
       </c>
       <c r="F85" t="n">
-        <v>-2.48</v>
+        <v>-2.43</v>
       </c>
       <c r="G85" t="n">
-        <v>-11.99</v>
+        <v>-11.94</v>
       </c>
       <c r="H85" t="n">
-        <v>-11.03</v>
+        <v>-10.97</v>
       </c>
       <c r="I85" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="J85" t="n">
         <v>13.8</v>
@@ -9801,28 +9793,28 @@
         <v>2.44</v>
       </c>
       <c r="L85" t="n">
-        <v>560.76</v>
+        <v>561.1</v>
       </c>
       <c r="M85" t="n">
-        <v>567.66</v>
+        <v>567.99</v>
       </c>
       <c r="N85" t="n">
-        <v>546.96</v>
+        <v>547.3</v>
       </c>
       <c r="O85" t="n">
-        <v>595.95</v>
+        <v>596.28</v>
       </c>
       <c r="P85" t="n">
         <v>1.63</v>
       </c>
       <c r="Q85" t="n">
-        <v>38.69</v>
+        <v>38.88</v>
       </c>
       <c r="R85" t="n">
-        <v>-1.62</v>
+        <v>-1.56</v>
       </c>
       <c r="S85" t="n">
-        <v>-4.94</v>
+        <v>-4.88</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9883,22 +9875,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>280.06</v>
+        <v>280.16</v>
       </c>
       <c r="D86" t="n">
         <v>30</v>
       </c>
       <c r="E86" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="F86" t="n">
-        <v>-6.67</v>
+        <v>-6.64</v>
       </c>
       <c r="G86" t="n">
-        <v>-15.44</v>
+        <v>-15.41</v>
       </c>
       <c r="H86" t="n">
-        <v>-15.22</v>
+        <v>-15.18</v>
       </c>
       <c r="I86" t="n">
         <v>0.49</v>
@@ -9910,28 +9902,28 @@
         <v>2.11</v>
       </c>
       <c r="L86" t="n">
-        <v>277.99</v>
+        <v>278.09</v>
       </c>
       <c r="M86" t="n">
-        <v>280.95</v>
+        <v>281.05</v>
       </c>
       <c r="N86" t="n">
-        <v>272.08</v>
+        <v>272.18</v>
       </c>
       <c r="O86" t="n">
-        <v>293.06</v>
+        <v>293.16</v>
       </c>
       <c r="P86" t="n">
         <v>1.63</v>
       </c>
       <c r="Q86" t="n">
-        <v>29.42</v>
+        <v>29.51</v>
       </c>
       <c r="R86" t="n">
-        <v>-1.52</v>
+        <v>-1.48</v>
       </c>
       <c r="S86" t="n">
-        <v>-8.140000000000001</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9992,25 +9984,25 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>90.3</v>
+        <v>90.33</v>
       </c>
       <c r="D87" t="n">
         <v>29</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.95</v>
+        <v>-0.92</v>
       </c>
       <c r="F87" t="n">
-        <v>-1.18</v>
+        <v>-1.15</v>
       </c>
       <c r="G87" t="n">
-        <v>-2.68</v>
+        <v>-2.64</v>
       </c>
       <c r="H87" t="n">
-        <v>-9.73</v>
+        <v>-9.69</v>
       </c>
       <c r="I87" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>2.19</v>
@@ -10019,28 +10011,28 @@
         <v>2.42</v>
       </c>
       <c r="L87" t="n">
-        <v>89.53</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="M87" t="n">
-        <v>90.63</v>
+        <v>90.66</v>
       </c>
       <c r="N87" t="n">
-        <v>87.34999999999999</v>
+        <v>87.38</v>
       </c>
       <c r="O87" t="n">
-        <v>95.11</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="P87" t="n">
         <v>1.63</v>
       </c>
       <c r="Q87" t="n">
-        <v>46.72</v>
+        <v>46.82</v>
       </c>
       <c r="R87" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="S87" t="n">
-        <v>-3.35</v>
+        <v>-3.31</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10101,7 +10093,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>302.02</v>
+        <v>302.03</v>
       </c>
       <c r="D88" t="n">
         <v>28</v>
@@ -10116,7 +10108,7 @@
         <v>2.11</v>
       </c>
       <c r="H88" t="n">
-        <v>-12.06</v>
+        <v>-12.05</v>
       </c>
       <c r="I88" t="n">
         <v>0.55</v>
@@ -10128,22 +10120,22 @@
         <v>2.08</v>
       </c>
       <c r="L88" t="n">
-        <v>299.82</v>
+        <v>299.83</v>
       </c>
       <c r="M88" t="n">
-        <v>302.96</v>
+        <v>302.97</v>
       </c>
       <c r="N88" t="n">
-        <v>293.52</v>
+        <v>293.53</v>
       </c>
       <c r="O88" t="n">
-        <v>315.87</v>
+        <v>315.88</v>
       </c>
       <c r="P88" t="n">
         <v>1.63</v>
       </c>
       <c r="Q88" t="n">
-        <v>39.61</v>
+        <v>39.62</v>
       </c>
       <c r="R88" t="n">
         <v>-1.29</v>
@@ -10210,22 +10202,22 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>51.22</v>
+        <v>51.24</v>
       </c>
       <c r="D89" t="n">
         <v>28</v>
       </c>
       <c r="E89" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="F89" t="n">
-        <v>-3.58</v>
+        <v>-3.53</v>
       </c>
       <c r="G89" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="H89" t="n">
-        <v>-12.13</v>
+        <v>-12.07</v>
       </c>
       <c r="I89" t="n">
         <v>0.73</v>
@@ -10237,28 +10229,28 @@
         <v>2.24</v>
       </c>
       <c r="L89" t="n">
-        <v>50.82</v>
+        <v>50.84</v>
       </c>
       <c r="M89" t="n">
-        <v>51.39</v>
+        <v>51.42</v>
       </c>
       <c r="N89" t="n">
-        <v>49.67</v>
+        <v>49.7</v>
       </c>
       <c r="O89" t="n">
-        <v>53.74</v>
+        <v>53.77</v>
       </c>
       <c r="P89" t="n">
         <v>1.63</v>
       </c>
       <c r="Q89" t="n">
-        <v>36.73</v>
+        <v>36.92</v>
       </c>
       <c r="R89" t="n">
-        <v>-1.1</v>
+        <v>-1.05</v>
       </c>
       <c r="S89" t="n">
-        <v>-5.5</v>
+        <v>-5.45</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10319,25 +10311,25 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>604.72</v>
+        <v>604.84</v>
       </c>
       <c r="D90" t="n">
         <v>28</v>
       </c>
       <c r="E90" t="n">
-        <v>-1.93</v>
+        <v>-1.91</v>
       </c>
       <c r="F90" t="n">
-        <v>-10.37</v>
+        <v>-10.36</v>
       </c>
       <c r="G90" t="n">
-        <v>-5.33</v>
+        <v>-5.31</v>
       </c>
       <c r="H90" t="n">
-        <v>-18.92</v>
+        <v>-18.9</v>
       </c>
       <c r="I90" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J90" t="n">
         <v>13.2</v>
@@ -10346,28 +10338,28 @@
         <v>2.18</v>
       </c>
       <c r="L90" t="n">
-        <v>600.1</v>
+        <v>600.22</v>
       </c>
       <c r="M90" t="n">
-        <v>606.7</v>
+        <v>606.8099999999999</v>
       </c>
       <c r="N90" t="n">
-        <v>586.91</v>
+        <v>587.02</v>
       </c>
       <c r="O90" t="n">
-        <v>633.75</v>
+        <v>633.87</v>
       </c>
       <c r="P90" t="n">
         <v>1.63</v>
       </c>
       <c r="Q90" t="n">
-        <v>45.37</v>
+        <v>45.45</v>
       </c>
       <c r="R90" t="n">
-        <v>-3.23</v>
+        <v>-3.21</v>
       </c>
       <c r="S90" t="n">
-        <v>-11.4</v>
+        <v>-11.38</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10386,7 +10378,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
@@ -10428,25 +10420,25 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>25.79</v>
+        <v>25.8</v>
       </c>
       <c r="D91" t="n">
         <v>26</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="F91" t="n">
-        <v>-2.18</v>
+        <v>-2.14</v>
       </c>
       <c r="G91" t="n">
-        <v>-3.41</v>
+        <v>-3.37</v>
       </c>
       <c r="H91" t="n">
-        <v>-10.73</v>
+        <v>-10.68</v>
       </c>
       <c r="I91" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="J91" t="n">
         <v>0.48</v>
@@ -10455,28 +10447,28 @@
         <v>1.84</v>
       </c>
       <c r="L91" t="n">
-        <v>25.62</v>
+        <v>25.63</v>
       </c>
       <c r="M91" t="n">
-        <v>25.86</v>
+        <v>25.87</v>
       </c>
       <c r="N91" t="n">
-        <v>25.15</v>
+        <v>25.16</v>
       </c>
       <c r="O91" t="n">
-        <v>26.84</v>
+        <v>26.85</v>
       </c>
       <c r="P91" t="n">
         <v>1.64</v>
       </c>
       <c r="Q91" t="n">
-        <v>40.11</v>
+        <v>40.36</v>
       </c>
       <c r="R91" t="n">
-        <v>-0.51</v>
+        <v>-0.47</v>
       </c>
       <c r="S91" t="n">
-        <v>-4.95</v>
+        <v>-4.91</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10537,22 +10529,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>135.67</v>
+        <v>135.8</v>
       </c>
       <c r="D92" t="n">
         <v>23</v>
       </c>
       <c r="E92" t="n">
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="F92" t="n">
-        <v>-11.11</v>
+        <v>-11.02</v>
       </c>
       <c r="G92" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H92" t="n">
-        <v>-19.66</v>
+        <v>-19.56</v>
       </c>
       <c r="I92" t="n">
         <v>0.43</v>
@@ -10564,28 +10556,28 @@
         <v>4.18</v>
       </c>
       <c r="L92" t="n">
-        <v>133.68</v>
+        <v>133.81</v>
       </c>
       <c r="M92" t="n">
-        <v>136.52</v>
+        <v>136.65</v>
       </c>
       <c r="N92" t="n">
-        <v>128.01</v>
+        <v>128.14</v>
       </c>
       <c r="O92" t="n">
-        <v>148.15</v>
+        <v>148.28</v>
       </c>
       <c r="P92" t="n">
         <v>1.63</v>
       </c>
       <c r="Q92" t="n">
-        <v>45.29</v>
+        <v>45.49</v>
       </c>
       <c r="R92" t="n">
-        <v>-1.6</v>
+        <v>-1.51</v>
       </c>
       <c r="S92" t="n">
-        <v>-9.73</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10604,7 +10596,7 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
@@ -10646,22 +10638,22 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>15.66</v>
+        <v>15.67</v>
       </c>
       <c r="D93" t="n">
         <v>23</v>
       </c>
       <c r="E93" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="F93" t="n">
-        <v>-17.85</v>
+        <v>-17.79</v>
       </c>
       <c r="G93" t="n">
-        <v>-16.09</v>
+        <v>-16.02</v>
       </c>
       <c r="H93" t="n">
-        <v>-26.4</v>
+        <v>-26.33</v>
       </c>
       <c r="I93" t="n">
         <v>0.48</v>
@@ -10673,28 +10665,28 @@
         <v>4.37</v>
       </c>
       <c r="L93" t="n">
-        <v>15.42</v>
+        <v>15.43</v>
       </c>
       <c r="M93" t="n">
-        <v>15.76</v>
+        <v>15.77</v>
       </c>
       <c r="N93" t="n">
-        <v>14.73</v>
+        <v>14.75</v>
       </c>
       <c r="O93" t="n">
-        <v>17.16</v>
+        <v>17.18</v>
       </c>
       <c r="P93" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q93" t="n">
-        <v>45.72</v>
+        <v>45.84</v>
       </c>
       <c r="R93" t="n">
-        <v>-4.5</v>
+        <v>-4.43</v>
       </c>
       <c r="S93" t="n">
-        <v>-18.32</v>
+        <v>-18.26</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10755,22 +10747,22 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>88.14</v>
+        <v>88.22</v>
       </c>
       <c r="D94" t="n">
         <v>22</v>
       </c>
       <c r="E94" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="F94" t="n">
-        <v>-5.47</v>
+        <v>-5.39</v>
       </c>
       <c r="G94" t="n">
-        <v>12.94</v>
+        <v>13.04</v>
       </c>
       <c r="H94" t="n">
-        <v>-14.02</v>
+        <v>-13.93</v>
       </c>
       <c r="I94" t="n">
         <v>0.38</v>
@@ -10782,28 +10774,28 @@
         <v>2.7</v>
       </c>
       <c r="L94" t="n">
-        <v>87.31</v>
+        <v>87.38</v>
       </c>
       <c r="M94" t="n">
-        <v>88.5</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="N94" t="n">
-        <v>84.93000000000001</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="O94" t="n">
-        <v>93.37</v>
+        <v>93.45</v>
       </c>
       <c r="P94" t="n">
         <v>1.63</v>
       </c>
       <c r="Q94" t="n">
-        <v>32.98</v>
+        <v>33.14</v>
       </c>
       <c r="R94" t="n">
-        <v>-1.59</v>
+        <v>-1.51</v>
       </c>
       <c r="S94" t="n">
-        <v>-6.93</v>
+        <v>-6.85</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10822,7 +10814,7 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
@@ -10864,22 +10856,22 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>221.65</v>
+        <v>221.93</v>
       </c>
       <c r="D95" t="n">
         <v>21</v>
       </c>
       <c r="E95" t="n">
-        <v>-7.88</v>
+        <v>-7.76</v>
       </c>
       <c r="F95" t="n">
-        <v>-4.16</v>
+        <v>-4.04</v>
       </c>
       <c r="G95" t="n">
-        <v>-5.03</v>
+        <v>-4.91</v>
       </c>
       <c r="H95" t="n">
-        <v>-12.71</v>
+        <v>-12.58</v>
       </c>
       <c r="I95" t="n">
         <v>0.64</v>
@@ -10888,31 +10880,31 @@
         <v>7.31</v>
       </c>
       <c r="K95" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="L95" t="n">
-        <v>219.09</v>
+        <v>219.37</v>
       </c>
       <c r="M95" t="n">
-        <v>222.75</v>
+        <v>223.03</v>
       </c>
       <c r="N95" t="n">
-        <v>211.78</v>
+        <v>212.06</v>
       </c>
       <c r="O95" t="n">
-        <v>237.74</v>
+        <v>238.02</v>
       </c>
       <c r="P95" t="n">
         <v>1.63</v>
       </c>
       <c r="Q95" t="n">
-        <v>44.07</v>
+        <v>44.32</v>
       </c>
       <c r="R95" t="n">
-        <v>-3.12</v>
+        <v>-3</v>
       </c>
       <c r="S95" t="n">
-        <v>-9.19</v>
+        <v>-9.07</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10973,25 +10965,25 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>44.19</v>
+        <v>44.26</v>
       </c>
       <c r="D96" t="n">
         <v>20</v>
       </c>
       <c r="E96" t="n">
-        <v>-2.29</v>
+        <v>-2.13</v>
       </c>
       <c r="F96" t="n">
-        <v>-13.72</v>
+        <v>-13.58</v>
       </c>
       <c r="G96" t="n">
-        <v>-5.72</v>
+        <v>-5.57</v>
       </c>
       <c r="H96" t="n">
-        <v>-22.27</v>
+        <v>-22.12</v>
       </c>
       <c r="I96" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J96" t="n">
         <v>1.42</v>
@@ -11000,28 +10992,28 @@
         <v>3.21</v>
       </c>
       <c r="L96" t="n">
-        <v>43.7</v>
+        <v>43.77</v>
       </c>
       <c r="M96" t="n">
-        <v>44.41</v>
+        <v>44.48</v>
       </c>
       <c r="N96" t="n">
-        <v>42.28</v>
+        <v>42.35</v>
       </c>
       <c r="O96" t="n">
-        <v>47.32</v>
+        <v>47.39</v>
       </c>
       <c r="P96" t="n">
         <v>1.63</v>
       </c>
       <c r="Q96" t="n">
-        <v>12.91</v>
+        <v>13.67</v>
       </c>
       <c r="R96" t="n">
-        <v>-6.32</v>
+        <v>-6.18</v>
       </c>
       <c r="S96" t="n">
-        <v>-14.8</v>
+        <v>-14.66</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11082,25 +11074,25 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1044.26</v>
+        <v>1044.01</v>
       </c>
       <c r="D97" t="n">
         <v>15</v>
       </c>
       <c r="E97" t="n">
-        <v>-4.56</v>
+        <v>-4.58</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.71</v>
+        <v>-1.74</v>
       </c>
       <c r="G97" t="n">
-        <v>-2.87</v>
+        <v>-2.89</v>
       </c>
       <c r="H97" t="n">
-        <v>-10.26</v>
+        <v>-10.28</v>
       </c>
       <c r="I97" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="J97" t="n">
         <v>23.04</v>
@@ -11109,28 +11101,28 @@
         <v>2.21</v>
       </c>
       <c r="L97" t="n">
-        <v>1036.2</v>
+        <v>1035.94</v>
       </c>
       <c r="M97" t="n">
-        <v>1047.72</v>
+        <v>1047.46</v>
       </c>
       <c r="N97" t="n">
-        <v>1013.16</v>
+        <v>1012.9</v>
       </c>
       <c r="O97" t="n">
-        <v>1094.95</v>
+        <v>1094.69</v>
       </c>
       <c r="P97" t="n">
         <v>1.63</v>
       </c>
       <c r="Q97" t="n">
-        <v>43.87</v>
+        <v>43.79</v>
       </c>
       <c r="R97" t="n">
-        <v>-2.04</v>
+        <v>-2.06</v>
       </c>
       <c r="S97" t="n">
-        <v>-6.01</v>
+        <v>-6.04</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11191,22 +11183,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>75.68000000000001</v>
+        <v>75.69</v>
       </c>
       <c r="D98" t="n">
         <v>15</v>
       </c>
       <c r="E98" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="F98" t="n">
-        <v>-5.54</v>
+        <v>-5.53</v>
       </c>
       <c r="G98" t="n">
-        <v>-10</v>
+        <v>-9.99</v>
       </c>
       <c r="H98" t="n">
-        <v>-14.09</v>
+        <v>-14.07</v>
       </c>
       <c r="I98" t="n">
         <v>0.48</v>
@@ -11218,28 +11210,28 @@
         <v>2.51</v>
       </c>
       <c r="L98" t="n">
-        <v>75.02</v>
+        <v>75.03</v>
       </c>
       <c r="M98" t="n">
-        <v>75.95999999999999</v>
+        <v>75.97</v>
       </c>
       <c r="N98" t="n">
-        <v>73.12</v>
+        <v>73.13</v>
       </c>
       <c r="O98" t="n">
-        <v>79.86</v>
+        <v>79.87</v>
       </c>
       <c r="P98" t="n">
         <v>1.63</v>
       </c>
       <c r="Q98" t="n">
-        <v>31.88</v>
+        <v>31.93</v>
       </c>
       <c r="R98" t="n">
-        <v>-2.34</v>
+        <v>-2.33</v>
       </c>
       <c r="S98" t="n">
-        <v>-7.92</v>
+        <v>-7.91</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11300,55 +11292,55 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>308.68</v>
+        <v>309.27</v>
       </c>
       <c r="D99" t="n">
         <v>15</v>
       </c>
       <c r="E99" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="F99" t="n">
-        <v>-9.08</v>
+        <v>-8.9</v>
       </c>
       <c r="G99" t="n">
-        <v>-19.18</v>
+        <v>-19.02</v>
       </c>
       <c r="H99" t="n">
-        <v>-17.63</v>
+        <v>-17.44</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>8.43</v>
       </c>
       <c r="K99" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="L99" t="n">
-        <v>305.74</v>
+        <v>306.33</v>
       </c>
       <c r="M99" t="n">
-        <v>309.95</v>
+        <v>310.54</v>
       </c>
       <c r="N99" t="n">
-        <v>297.31</v>
+        <v>297.9</v>
       </c>
       <c r="O99" t="n">
-        <v>327.22</v>
+        <v>327.81</v>
       </c>
       <c r="P99" t="n">
         <v>1.63</v>
       </c>
       <c r="Q99" t="n">
-        <v>35.06</v>
+        <v>35.63</v>
       </c>
       <c r="R99" t="n">
-        <v>-2.64</v>
+        <v>-2.46</v>
       </c>
       <c r="S99" t="n">
-        <v>-9.43</v>
+        <v>-9.26</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11409,55 +11401,55 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>219.17</v>
+        <v>219.61</v>
       </c>
       <c r="D100" t="n">
         <v>11</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.58</v>
+        <v>-0.38</v>
       </c>
       <c r="F100" t="n">
-        <v>-10.61</v>
+        <v>-10.43</v>
       </c>
       <c r="G100" t="n">
-        <v>-20.95</v>
+        <v>-20.79</v>
       </c>
       <c r="H100" t="n">
-        <v>-19.16</v>
+        <v>-18.97</v>
       </c>
       <c r="I100" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="J100" t="n">
         <v>6.37</v>
       </c>
       <c r="K100" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="L100" t="n">
-        <v>216.94</v>
+        <v>217.38</v>
       </c>
       <c r="M100" t="n">
-        <v>220.13</v>
+        <v>220.57</v>
       </c>
       <c r="N100" t="n">
-        <v>210.57</v>
+        <v>211.01</v>
       </c>
       <c r="O100" t="n">
-        <v>233.19</v>
+        <v>233.63</v>
       </c>
       <c r="P100" t="n">
         <v>1.63</v>
       </c>
       <c r="Q100" t="n">
-        <v>29.37</v>
+        <v>30.01</v>
       </c>
       <c r="R100" t="n">
-        <v>-4.51</v>
+        <v>-4.33</v>
       </c>
       <c r="S100" t="n">
-        <v>-11.49</v>
+        <v>-11.31</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11518,55 +11510,55 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>446.86</v>
+        <v>447.3</v>
       </c>
       <c r="D101" t="n">
         <v>7</v>
       </c>
       <c r="E101" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="F101" t="n">
-        <v>-13.06</v>
+        <v>-12.97</v>
       </c>
       <c r="G101" t="n">
-        <v>-13.25</v>
+        <v>-13.16</v>
       </c>
       <c r="H101" t="n">
-        <v>-21.61</v>
+        <v>-21.51</v>
       </c>
       <c r="I101" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J101" t="n">
         <v>13.57</v>
       </c>
       <c r="K101" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="L101" t="n">
-        <v>442.11</v>
+        <v>442.55</v>
       </c>
       <c r="M101" t="n">
-        <v>448.9</v>
+        <v>449.34</v>
       </c>
       <c r="N101" t="n">
-        <v>428.54</v>
+        <v>428.98</v>
       </c>
       <c r="O101" t="n">
-        <v>476.72</v>
+        <v>477.16</v>
       </c>
       <c r="P101" t="n">
         <v>1.63</v>
       </c>
       <c r="Q101" t="n">
-        <v>32.65</v>
+        <v>32.81</v>
       </c>
       <c r="R101" t="n">
-        <v>-2.98</v>
+        <v>-2.89</v>
       </c>
       <c r="S101" t="n">
-        <v>-7.26</v>
+        <v>-7.17</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11627,22 +11619,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>202.74</v>
+        <v>202.64</v>
       </c>
       <c r="D102" t="n">
         <v>58</v>
       </c>
       <c r="E102" t="n">
-        <v>-4.89</v>
+        <v>-4.94</v>
       </c>
       <c r="F102" t="n">
-        <v>49</v>
+        <v>48.92</v>
       </c>
       <c r="G102" t="n">
-        <v>40.93</v>
+        <v>40.86</v>
       </c>
       <c r="H102" t="n">
-        <v>40.45</v>
+        <v>40.38</v>
       </c>
       <c r="I102" t="n">
         <v>0.37</v>
@@ -11651,31 +11643,31 @@
         <v>18.21</v>
       </c>
       <c r="K102" t="n">
-        <v>8.98</v>
+        <v>8.99</v>
       </c>
       <c r="L102" t="n">
-        <v>196.37</v>
+        <v>196.26</v>
       </c>
       <c r="M102" t="n">
-        <v>205.47</v>
+        <v>205.37</v>
       </c>
       <c r="N102" t="n">
-        <v>178.15</v>
+        <v>178.05</v>
       </c>
       <c r="O102" t="n">
-        <v>242.81</v>
+        <v>242.71</v>
       </c>
       <c r="P102" t="n">
         <v>1.63</v>
       </c>
       <c r="Q102" t="n">
-        <v>58.14</v>
+        <v>58.11</v>
       </c>
       <c r="R102" t="n">
-        <v>8.73</v>
+        <v>8.68</v>
       </c>
       <c r="S102" t="n">
-        <v>-18.22</v>
+        <v>-18.26</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11694,7 +11686,7 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>SOXX 19.81% · QQQ 8.55%</t>
+          <t>SOXX 19.64% · QQQ 8.54%</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
@@ -11719,7 +11711,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.81% · QQQ 8.55%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; RSI saludable</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -11740,19 +11732,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>479.38</v>
+        <v>479.3</v>
       </c>
       <c r="D103" t="n">
         <v>53</v>
       </c>
       <c r="E103" t="n">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.9</v>
+        <v>-0.91</v>
       </c>
       <c r="G103" t="n">
-        <v>21.91</v>
+        <v>21.89</v>
       </c>
       <c r="H103" t="n">
         <v>-9.449999999999999</v>
@@ -11767,28 +11759,28 @@
         <v>6.62</v>
       </c>
       <c r="L103" t="n">
-        <v>468.27</v>
+        <v>468.2</v>
       </c>
       <c r="M103" t="n">
-        <v>484.14</v>
+        <v>484.07</v>
       </c>
       <c r="N103" t="n">
-        <v>436.54</v>
+        <v>436.46</v>
       </c>
       <c r="O103" t="n">
-        <v>549.2</v>
+        <v>549.12</v>
       </c>
       <c r="P103" t="n">
         <v>1.63</v>
       </c>
       <c r="Q103" t="n">
-        <v>57.04</v>
+        <v>57.02</v>
       </c>
       <c r="R103" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S103" t="n">
-        <v>-6.99</v>
+        <v>-7</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11807,7 +11799,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
@@ -11849,25 +11841,25 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>177.54</v>
+        <v>177.6</v>
       </c>
       <c r="D104" t="n">
         <v>52</v>
       </c>
       <c r="E104" t="n">
-        <v>7.05</v>
+        <v>7.09</v>
       </c>
       <c r="F104" t="n">
-        <v>-6.46</v>
+        <v>-6.43</v>
       </c>
       <c r="G104" t="n">
-        <v>-4.01</v>
+        <v>-3.98</v>
       </c>
       <c r="H104" t="n">
-        <v>-15.01</v>
+        <v>-14.97</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="J104" t="n">
         <v>7.39</v>
@@ -11876,28 +11868,28 @@
         <v>4.16</v>
       </c>
       <c r="L104" t="n">
-        <v>174.95</v>
+        <v>175.01</v>
       </c>
       <c r="M104" t="n">
-        <v>178.64</v>
+        <v>178.71</v>
       </c>
       <c r="N104" t="n">
-        <v>167.55</v>
+        <v>167.62</v>
       </c>
       <c r="O104" t="n">
-        <v>193.8</v>
+        <v>193.87</v>
       </c>
       <c r="P104" t="n">
         <v>1.63</v>
       </c>
       <c r="Q104" t="n">
-        <v>50.87</v>
+        <v>50.93</v>
       </c>
       <c r="R104" t="n">
-        <v>-0.5</v>
+        <v>-0.46</v>
       </c>
       <c r="S104" t="n">
-        <v>-6.71</v>
+        <v>-6.68</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11916,7 +11908,7 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
@@ -11958,22 +11950,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>185.2</v>
+        <v>184.9</v>
       </c>
       <c r="D105" t="n">
         <v>47</v>
       </c>
       <c r="E105" t="n">
-        <v>-2.4</v>
+        <v>-2.56</v>
       </c>
       <c r="F105" t="n">
-        <v>-1.23</v>
+        <v>-1.39</v>
       </c>
       <c r="G105" t="n">
-        <v>27.17</v>
+        <v>26.96</v>
       </c>
       <c r="H105" t="n">
-        <v>-9.779999999999999</v>
+        <v>-9.93</v>
       </c>
       <c r="I105" t="n">
         <v>0.39</v>
@@ -11982,31 +11974,31 @@
         <v>9.48</v>
       </c>
       <c r="K105" t="n">
-        <v>5.12</v>
+        <v>5.13</v>
       </c>
       <c r="L105" t="n">
-        <v>181.88</v>
+        <v>181.58</v>
       </c>
       <c r="M105" t="n">
-        <v>186.62</v>
+        <v>186.32</v>
       </c>
       <c r="N105" t="n">
-        <v>172.4</v>
+        <v>172.1</v>
       </c>
       <c r="O105" t="n">
-        <v>206.06</v>
+        <v>205.75</v>
       </c>
       <c r="P105" t="n">
         <v>1.63</v>
       </c>
       <c r="Q105" t="n">
-        <v>66.92</v>
+        <v>66.78</v>
       </c>
       <c r="R105" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="S105" t="n">
-        <v>-7.73</v>
+        <v>-7.88</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12025,7 +12017,7 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
@@ -12067,55 +12059,55 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8.470000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="D106" t="n">
         <v>42</v>
       </c>
       <c r="E106" t="n">
-        <v>0.59</v>
+        <v>0.89</v>
       </c>
       <c r="F106" t="n">
-        <v>3.04</v>
+        <v>3.35</v>
       </c>
       <c r="G106" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="H106" t="n">
-        <v>-5.51</v>
+        <v>-5.19</v>
       </c>
       <c r="I106" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J106" t="n">
         <v>0.65</v>
       </c>
       <c r="K106" t="n">
-        <v>7.72</v>
+        <v>7.69</v>
       </c>
       <c r="L106" t="n">
-        <v>8.24</v>
+        <v>8.27</v>
       </c>
       <c r="M106" t="n">
-        <v>8.57</v>
+        <v>8.59</v>
       </c>
       <c r="N106" t="n">
-        <v>7.59</v>
+        <v>7.61</v>
       </c>
       <c r="O106" t="n">
-        <v>9.91</v>
+        <v>9.93</v>
       </c>
       <c r="P106" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q106" t="n">
-        <v>55.28</v>
+        <v>55.51</v>
       </c>
       <c r="R106" t="n">
-        <v>-0.98</v>
+        <v>-0.7</v>
       </c>
       <c r="S106" t="n">
-        <v>-15.68</v>
+        <v>-15.43</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12134,7 +12126,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
@@ -12182,49 +12174,49 @@
         <v>24</v>
       </c>
       <c r="E107" t="n">
-        <v>-9.43</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="F107" t="n">
-        <v>-2.56</v>
+        <v>-2.39</v>
       </c>
       <c r="G107" t="n">
-        <v>-17.87</v>
+        <v>-17.73</v>
       </c>
       <c r="H107" t="n">
-        <v>-11.11</v>
+        <v>-10.93</v>
       </c>
       <c r="I107" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="J107" t="n">
         <v>0.41</v>
       </c>
       <c r="K107" t="n">
-        <v>7.03</v>
+        <v>7.02</v>
       </c>
       <c r="L107" t="n">
-        <v>5.76</v>
+        <v>5.77</v>
       </c>
       <c r="M107" t="n">
-        <v>5.97</v>
+        <v>5.98</v>
       </c>
       <c r="N107" t="n">
-        <v>5.34</v>
+        <v>5.35</v>
       </c>
       <c r="O107" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="P107" t="n">
         <v>1.62</v>
       </c>
       <c r="Q107" t="n">
-        <v>53.83</v>
+        <v>54.06</v>
       </c>
       <c r="R107" t="n">
-        <v>-2.27</v>
+        <v>-2.11</v>
       </c>
       <c r="S107" t="n">
-        <v>-12.52</v>
+        <v>-12.37</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12285,55 +12277,55 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>144.91</v>
+        <v>145.72</v>
       </c>
       <c r="D108" t="n">
         <v>24</v>
       </c>
       <c r="E108" t="n">
-        <v>-5.97</v>
+        <v>-5.45</v>
       </c>
       <c r="F108" t="n">
-        <v>-11.8</v>
+        <v>-11.31</v>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="H108" t="n">
-        <v>-20.35</v>
+        <v>-19.85</v>
       </c>
       <c r="I108" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="J108" t="n">
         <v>10</v>
       </c>
       <c r="K108" t="n">
-        <v>6.9</v>
+        <v>6.87</v>
       </c>
       <c r="L108" t="n">
-        <v>141.41</v>
+        <v>142.22</v>
       </c>
       <c r="M108" t="n">
-        <v>146.42</v>
+        <v>147.22</v>
       </c>
       <c r="N108" t="n">
-        <v>131.41</v>
+        <v>132.21</v>
       </c>
       <c r="O108" t="n">
-        <v>166.93</v>
+        <v>167.73</v>
       </c>
       <c r="P108" t="n">
         <v>1.63</v>
       </c>
       <c r="Q108" t="n">
-        <v>48.39</v>
+        <v>48.94</v>
       </c>
       <c r="R108" t="n">
-        <v>-7.81</v>
+        <v>-7.32</v>
       </c>
       <c r="S108" t="n">
-        <v>-18.19</v>
+        <v>-17.73</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12352,7 +12344,7 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
@@ -12394,22 +12386,22 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>29.02</v>
+        <v>29.04</v>
       </c>
       <c r="D109" t="n">
         <v>22</v>
       </c>
       <c r="E109" t="n">
-        <v>7.52</v>
+        <v>7.6</v>
       </c>
       <c r="F109" t="n">
-        <v>-16.47</v>
+        <v>-16.41</v>
       </c>
       <c r="G109" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="H109" t="n">
-        <v>-25.02</v>
+        <v>-24.95</v>
       </c>
       <c r="I109" t="n">
         <v>0.64</v>
@@ -12421,28 +12413,28 @@
         <v>6.61</v>
       </c>
       <c r="L109" t="n">
-        <v>28.35</v>
+        <v>28.37</v>
       </c>
       <c r="M109" t="n">
-        <v>29.31</v>
+        <v>29.33</v>
       </c>
       <c r="N109" t="n">
-        <v>26.43</v>
+        <v>26.45</v>
       </c>
       <c r="O109" t="n">
-        <v>33.24</v>
+        <v>33.26</v>
       </c>
       <c r="P109" t="n">
         <v>1.63</v>
       </c>
       <c r="Q109" t="n">
-        <v>40.21</v>
+        <v>40.31</v>
       </c>
       <c r="R109" t="n">
-        <v>-4.03</v>
+        <v>-3.97</v>
       </c>
       <c r="S109" t="n">
-        <v>-15.54</v>
+        <v>-15.48</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12461,7 +12453,7 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
@@ -12503,55 +12495,55 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>20.86</v>
+        <v>20.89</v>
       </c>
       <c r="D110" t="n">
         <v>6</v>
       </c>
       <c r="E110" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="F110" t="n">
-        <v>-11.46</v>
+        <v>-11.33</v>
       </c>
       <c r="G110" t="n">
-        <v>-16.36</v>
+        <v>-16.24</v>
       </c>
       <c r="H110" t="n">
-        <v>-20.01</v>
+        <v>-19.87</v>
       </c>
       <c r="I110" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>1.36</v>
       </c>
       <c r="K110" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="L110" t="n">
-        <v>20.38</v>
+        <v>20.41</v>
       </c>
       <c r="M110" t="n">
-        <v>21.06</v>
+        <v>21.09</v>
       </c>
       <c r="N110" t="n">
-        <v>19.03</v>
+        <v>19.06</v>
       </c>
       <c r="O110" t="n">
-        <v>23.85</v>
+        <v>23.88</v>
       </c>
       <c r="P110" t="n">
         <v>1.63</v>
       </c>
       <c r="Q110" t="n">
-        <v>34.44</v>
+        <v>34.55</v>
       </c>
       <c r="R110" t="n">
-        <v>-7.99</v>
+        <v>-7.87</v>
       </c>
       <c r="S110" t="n">
-        <v>-16.12</v>
+        <v>-16</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12570,7 +12562,7 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
@@ -12612,22 +12604,22 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>104.38</v>
+        <v>104.46</v>
       </c>
       <c r="D111" t="n">
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>9.41</v>
+        <v>9.5</v>
       </c>
       <c r="F111" t="n">
-        <v>-20.9</v>
+        <v>-20.84</v>
       </c>
       <c r="G111" t="n">
-        <v>-10.73</v>
+        <v>-10.66</v>
       </c>
       <c r="H111" t="n">
-        <v>-29.45</v>
+        <v>-29.38</v>
       </c>
       <c r="I111" t="n">
         <v>0.34</v>
@@ -12636,31 +12628,31 @@
         <v>6.5</v>
       </c>
       <c r="K111" t="n">
-        <v>6.23</v>
+        <v>6.22</v>
       </c>
       <c r="L111" t="n">
-        <v>102.1</v>
+        <v>102.18</v>
       </c>
       <c r="M111" t="n">
-        <v>105.36</v>
+        <v>105.44</v>
       </c>
       <c r="N111" t="n">
-        <v>95.59999999999999</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="O111" t="n">
-        <v>118.68</v>
+        <v>118.76</v>
       </c>
       <c r="P111" t="n">
         <v>1.63</v>
       </c>
       <c r="Q111" t="n">
-        <v>36.74</v>
+        <v>36.82</v>
       </c>
       <c r="R111" t="n">
-        <v>-6.49</v>
+        <v>-6.42</v>
       </c>
       <c r="S111" t="n">
-        <v>-19.89</v>
+        <v>-19.83</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12679,7 +12671,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -12721,22 +12713,22 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>196.11</v>
+        <v>195.9</v>
       </c>
       <c r="D112" t="n">
         <v>24</v>
       </c>
       <c r="E112" t="n">
-        <v>-2.82</v>
+        <v>-2.92</v>
       </c>
       <c r="F112" t="n">
-        <v>-4.91</v>
+        <v>-5.01</v>
       </c>
       <c r="G112" t="n">
-        <v>21.03</v>
+        <v>20.91</v>
       </c>
       <c r="H112" t="n">
-        <v>-13.46</v>
+        <v>-13.55</v>
       </c>
       <c r="I112" t="n">
         <v>0.47</v>
@@ -12745,31 +12737,31 @@
         <v>14.06</v>
       </c>
       <c r="K112" t="n">
-        <v>7.17</v>
+        <v>7.18</v>
       </c>
       <c r="L112" t="n">
-        <v>191.19</v>
+        <v>190.98</v>
       </c>
       <c r="M112" t="n">
-        <v>198.22</v>
+        <v>198.01</v>
       </c>
       <c r="N112" t="n">
-        <v>177.12</v>
+        <v>176.92</v>
       </c>
       <c r="O112" t="n">
-        <v>227.05</v>
+        <v>226.85</v>
       </c>
       <c r="P112" t="n">
         <v>1.63</v>
       </c>
       <c r="Q112" t="n">
-        <v>54.03</v>
+        <v>53.94</v>
       </c>
       <c r="R112" t="n">
-        <v>-0.82</v>
+        <v>-0.92</v>
       </c>
       <c r="S112" t="n">
-        <v>-11.8</v>
+        <v>-11.89</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12788,7 +12780,7 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>BTC-USD 1.48% · ETH-USD -5.3%</t>
+          <t>BTC-USD 1.43% · ETH-USD -5.34%</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
@@ -12814,7 +12806,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.48% · ETH-USD -5.3%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Sector no acompaña: BTC-USD 1.43% · ETH-USD -5.34%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -12830,22 +12822,22 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>168.72</v>
+        <v>168.15</v>
       </c>
       <c r="D113" t="n">
         <v>12</v>
       </c>
       <c r="E113" t="n">
-        <v>-5.23</v>
+        <v>-5.55</v>
       </c>
       <c r="F113" t="n">
-        <v>-5.93</v>
+        <v>-6.25</v>
       </c>
       <c r="G113" t="n">
-        <v>35.4</v>
+        <v>34.94</v>
       </c>
       <c r="H113" t="n">
-        <v>-14.48</v>
+        <v>-14.79</v>
       </c>
       <c r="I113" t="n">
         <v>0.37</v>
@@ -12854,31 +12846,31 @@
         <v>11.34</v>
       </c>
       <c r="K113" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
       <c r="L113" t="n">
-        <v>164.75</v>
+        <v>164.18</v>
       </c>
       <c r="M113" t="n">
-        <v>170.42</v>
+        <v>169.85</v>
       </c>
       <c r="N113" t="n">
-        <v>153.41</v>
+        <v>152.84</v>
       </c>
       <c r="O113" t="n">
-        <v>193.67</v>
+        <v>193.1</v>
       </c>
       <c r="P113" t="n">
         <v>1.63</v>
       </c>
       <c r="Q113" t="n">
-        <v>51.67</v>
+        <v>51.39</v>
       </c>
       <c r="R113" t="n">
-        <v>-4.32</v>
+        <v>-4.63</v>
       </c>
       <c r="S113" t="n">
-        <v>-14.36</v>
+        <v>-14.64</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12897,7 +12889,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>BTC-USD 1.48% · ETH-USD -5.3%</t>
+          <t>BTC-USD 1.43% · ETH-USD -5.34%</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -12923,7 +12915,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.48% · ETH-USD -5.3%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
+          <t>Sector no acompaña: BTC-USD 1.43% · ETH-USD -5.34%; Precio bajo MA20; Tendencia larga débil; MACD sin confirmar; Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -12939,25 +12931,25 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>710.85</v>
+        <v>711.11</v>
       </c>
       <c r="D114" t="n">
         <v>59</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.54</v>
+        <v>-0.5</v>
       </c>
       <c r="F114" t="n">
-        <v>8.51</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G114" t="n">
-        <v>17.09</v>
+        <v>17.13</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I114" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J114" t="n">
         <v>11.31</v>
@@ -12966,28 +12958,28 @@
         <v>1.59</v>
       </c>
       <c r="L114" t="n">
-        <v>706.89</v>
+        <v>707.15</v>
       </c>
       <c r="M114" t="n">
-        <v>712.55</v>
+        <v>712.8099999999999</v>
       </c>
       <c r="N114" t="n">
-        <v>695.59</v>
+        <v>695.85</v>
       </c>
       <c r="O114" t="n">
-        <v>735.72</v>
+        <v>735.98</v>
       </c>
       <c r="P114" t="n">
         <v>1.63</v>
       </c>
       <c r="Q114" t="n">
-        <v>72.47</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="R114" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="S114" t="n">
-        <v>-1.55</v>
+        <v>-1.51</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13048,22 +13040,22 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>179.37</v>
+        <v>179.57</v>
       </c>
       <c r="D115" t="n">
         <v>57</v>
       </c>
       <c r="E115" t="n">
-        <v>12.36</v>
+        <v>12.49</v>
       </c>
       <c r="F115" t="n">
-        <v>-5.64</v>
+        <v>-5.54</v>
       </c>
       <c r="G115" t="n">
-        <v>-8.050000000000001</v>
+        <v>-7.95</v>
       </c>
       <c r="H115" t="n">
-        <v>-14.19</v>
+        <v>-14.08</v>
       </c>
       <c r="I115" t="n">
         <v>0.42</v>
@@ -13075,28 +13067,28 @@
         <v>4.37</v>
       </c>
       <c r="L115" t="n">
-        <v>176.63</v>
+        <v>176.83</v>
       </c>
       <c r="M115" t="n">
-        <v>180.55</v>
+        <v>180.75</v>
       </c>
       <c r="N115" t="n">
-        <v>168.79</v>
+        <v>168.99</v>
       </c>
       <c r="O115" t="n">
-        <v>196.62</v>
+        <v>196.82</v>
       </c>
       <c r="P115" t="n">
         <v>1.63</v>
       </c>
       <c r="Q115" t="n">
-        <v>50.6</v>
+        <v>50.79</v>
       </c>
       <c r="R115" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="S115" t="n">
-        <v>-2.93</v>
+        <v>-2.82</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13115,7 +13107,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
@@ -13157,55 +13149,55 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>326.27</v>
+        <v>326.23</v>
       </c>
       <c r="D116" t="n">
         <v>56</v>
       </c>
       <c r="E116" t="n">
-        <v>7.68</v>
+        <v>7.67</v>
       </c>
       <c r="F116" t="n">
-        <v>21.05</v>
+        <v>21.03</v>
       </c>
       <c r="G116" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="H116" t="n">
-        <v>12.5</v>
+        <v>12.49</v>
       </c>
       <c r="I116" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>18.32</v>
       </c>
       <c r="K116" t="n">
-        <v>5.61</v>
+        <v>5.62</v>
       </c>
       <c r="L116" t="n">
-        <v>319.86</v>
+        <v>319.81</v>
       </c>
       <c r="M116" t="n">
-        <v>329.02</v>
+        <v>328.97</v>
       </c>
       <c r="N116" t="n">
-        <v>301.55</v>
+        <v>301.5</v>
       </c>
       <c r="O116" t="n">
-        <v>366.57</v>
+        <v>366.52</v>
       </c>
       <c r="P116" t="n">
         <v>1.63</v>
       </c>
       <c r="Q116" t="n">
-        <v>82.47</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="R116" t="n">
-        <v>14.3</v>
+        <v>14.29</v>
       </c>
       <c r="S116" t="n">
-        <v>-6.57</v>
+        <v>-6.58</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13224,7 +13216,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -13281,10 +13273,10 @@
         <v>66.45</v>
       </c>
       <c r="H117" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="I117" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="J117" t="n">
         <v>4.98</v>
@@ -13333,7 +13325,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -13375,25 +13367,25 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>173.95</v>
+        <v>173.87</v>
       </c>
       <c r="D118" t="n">
         <v>49</v>
       </c>
       <c r="E118" t="n">
-        <v>14.12</v>
+        <v>14.07</v>
       </c>
       <c r="F118" t="n">
-        <v>21.94</v>
+        <v>21.88</v>
       </c>
       <c r="G118" t="n">
-        <v>16.47</v>
+        <v>16.41</v>
       </c>
       <c r="H118" t="n">
-        <v>13.39</v>
+        <v>13.34</v>
       </c>
       <c r="I118" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="J118" t="n">
         <v>9.08</v>
@@ -13402,28 +13394,28 @@
         <v>5.22</v>
       </c>
       <c r="L118" t="n">
-        <v>170.78</v>
+        <v>170.69</v>
       </c>
       <c r="M118" t="n">
-        <v>175.31</v>
+        <v>175.23</v>
       </c>
       <c r="N118" t="n">
-        <v>161.7</v>
+        <v>161.61</v>
       </c>
       <c r="O118" t="n">
-        <v>193.93</v>
+        <v>193.84</v>
       </c>
       <c r="P118" t="n">
         <v>1.63</v>
       </c>
       <c r="Q118" t="n">
-        <v>82.86</v>
+        <v>82.75</v>
       </c>
       <c r="R118" t="n">
-        <v>17.64</v>
+        <v>17.59</v>
       </c>
       <c r="S118" t="n">
-        <v>-4.93</v>
+        <v>-4.97</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13442,7 +13434,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -13484,25 +13476,25 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>164.59</v>
+        <v>164.48</v>
       </c>
       <c r="D119" t="n">
         <v>45</v>
       </c>
       <c r="E119" t="n">
-        <v>8.02</v>
+        <v>7.95</v>
       </c>
       <c r="F119" t="n">
-        <v>5.8</v>
+        <v>5.73</v>
       </c>
       <c r="G119" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="H119" t="n">
-        <v>-2.75</v>
+        <v>-2.81</v>
       </c>
       <c r="I119" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J119" t="n">
         <v>8.69</v>
@@ -13511,28 +13503,28 @@
         <v>5.28</v>
       </c>
       <c r="L119" t="n">
-        <v>161.55</v>
+        <v>161.44</v>
       </c>
       <c r="M119" t="n">
-        <v>165.89</v>
+        <v>165.78</v>
       </c>
       <c r="N119" t="n">
-        <v>152.86</v>
+        <v>152.75</v>
       </c>
       <c r="O119" t="n">
-        <v>183.71</v>
+        <v>183.6</v>
       </c>
       <c r="P119" t="n">
         <v>1.63</v>
       </c>
       <c r="Q119" t="n">
-        <v>75.73</v>
+        <v>75.58</v>
       </c>
       <c r="R119" t="n">
-        <v>10.22</v>
+        <v>10.15</v>
       </c>
       <c r="S119" t="n">
-        <v>-7</v>
+        <v>-7.06</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13551,7 +13543,7 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
@@ -13593,55 +13585,55 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>102.14</v>
+        <v>101.92</v>
       </c>
       <c r="D120" t="n">
         <v>42</v>
       </c>
       <c r="E120" t="n">
-        <v>17.33</v>
+        <v>17.08</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.9</v>
+        <v>-1.12</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.34</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="H120" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.66</v>
       </c>
       <c r="I120" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="J120" t="n">
         <v>5.52</v>
       </c>
       <c r="K120" t="n">
-        <v>5.41</v>
+        <v>5.42</v>
       </c>
       <c r="L120" t="n">
-        <v>100.21</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="M120" t="n">
-        <v>102.97</v>
+        <v>102.75</v>
       </c>
       <c r="N120" t="n">
-        <v>94.69</v>
+        <v>94.47</v>
       </c>
       <c r="O120" t="n">
-        <v>114.29</v>
+        <v>114.07</v>
       </c>
       <c r="P120" t="n">
         <v>1.63</v>
       </c>
       <c r="Q120" t="n">
-        <v>68.88</v>
+        <v>68.69</v>
       </c>
       <c r="R120" t="n">
-        <v>10.87</v>
+        <v>10.64</v>
       </c>
       <c r="S120" t="n">
-        <v>-7.84</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13660,7 +13652,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -13702,22 +13694,22 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>126.68</v>
+        <v>126.82</v>
       </c>
       <c r="D121" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E121" t="n">
-        <v>9.99</v>
+        <v>10.12</v>
       </c>
       <c r="F121" t="n">
-        <v>-10.59</v>
+        <v>-10.49</v>
       </c>
       <c r="G121" t="n">
-        <v>-16.9</v>
+        <v>-16.81</v>
       </c>
       <c r="H121" t="n">
-        <v>-19.14</v>
+        <v>-19.03</v>
       </c>
       <c r="I121" t="n">
         <v>0.24</v>
@@ -13729,28 +13721,28 @@
         <v>3.49</v>
       </c>
       <c r="L121" t="n">
-        <v>125.13</v>
+        <v>125.27</v>
       </c>
       <c r="M121" t="n">
-        <v>127.34</v>
+        <v>127.48</v>
       </c>
       <c r="N121" t="n">
-        <v>120.7</v>
+        <v>120.85</v>
       </c>
       <c r="O121" t="n">
-        <v>136.41</v>
+        <v>136.56</v>
       </c>
       <c r="P121" t="n">
         <v>1.63</v>
       </c>
       <c r="Q121" t="n">
-        <v>76.17</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="R121" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="S121" t="n">
-        <v>-10.45</v>
+        <v>-10.35</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13769,7 +13761,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -13795,7 +13787,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; RSI sobrecomprado; Volumen bajo; Momentum 5D extendido; Débil vs QQQ</t>
+          <t>Tendencia larga débil; RSI sobrecomprado; Volumen bajo; Subida muy extendida 5D; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -13817,19 +13809,19 @@
         <v>15</v>
       </c>
       <c r="E122" t="n">
-        <v>-7.66</v>
+        <v>-7.71</v>
       </c>
       <c r="F122" t="n">
-        <v>-7.48</v>
+        <v>-7.54</v>
       </c>
       <c r="G122" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="H122" t="n">
-        <v>-16.03</v>
+        <v>-16.08</v>
       </c>
       <c r="I122" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="J122" t="n">
         <v>1.67</v>
@@ -13838,28 +13830,28 @@
         <v>9.84</v>
       </c>
       <c r="L122" t="n">
-        <v>16.42</v>
+        <v>16.41</v>
       </c>
       <c r="M122" t="n">
-        <v>17.26</v>
+        <v>17.25</v>
       </c>
       <c r="N122" t="n">
-        <v>14.75</v>
+        <v>14.74</v>
       </c>
       <c r="O122" t="n">
-        <v>20.69</v>
+        <v>20.68</v>
       </c>
       <c r="P122" t="n">
         <v>1.63</v>
       </c>
       <c r="Q122" t="n">
-        <v>48.4</v>
+        <v>48.36</v>
       </c>
       <c r="R122" t="n">
-        <v>-4.42</v>
+        <v>-4.48</v>
       </c>
       <c r="S122" t="n">
-        <v>-19.1</v>
+        <v>-19.15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13878,7 +13870,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -13920,55 +13912,55 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>19.32</v>
+        <v>19.29</v>
       </c>
       <c r="D123" t="n">
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>-9.91</v>
+        <v>-10.03</v>
       </c>
       <c r="F123" t="n">
-        <v>-9.06</v>
+        <v>-9.18</v>
       </c>
       <c r="G123" t="n">
-        <v>3.51</v>
+        <v>3.38</v>
       </c>
       <c r="H123" t="n">
-        <v>-17.61</v>
+        <v>-17.72</v>
       </c>
       <c r="I123" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J123" t="n">
         <v>1.88</v>
       </c>
       <c r="K123" t="n">
-        <v>9.74</v>
+        <v>9.75</v>
       </c>
       <c r="L123" t="n">
-        <v>18.66</v>
+        <v>18.63</v>
       </c>
       <c r="M123" t="n">
-        <v>19.6</v>
+        <v>19.57</v>
       </c>
       <c r="N123" t="n">
-        <v>16.78</v>
+        <v>16.75</v>
       </c>
       <c r="O123" t="n">
-        <v>23.45</v>
+        <v>23.43</v>
       </c>
       <c r="P123" t="n">
         <v>1.63</v>
       </c>
       <c r="Q123" t="n">
-        <v>46.94</v>
+        <v>46.86</v>
       </c>
       <c r="R123" t="n">
-        <v>-6.12</v>
+        <v>-6.23</v>
       </c>
       <c r="S123" t="n">
-        <v>-22.05</v>
+        <v>-22.15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13987,7 +13979,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -14029,22 +14021,22 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>204.38</v>
+        <v>204.4</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>14.18</v>
+        <v>14.19</v>
       </c>
       <c r="F124" t="n">
-        <v>-12.19</v>
+        <v>-12.18</v>
       </c>
       <c r="G124" t="n">
-        <v>-12.13</v>
+        <v>-12.12</v>
       </c>
       <c r="H124" t="n">
-        <v>-20.74</v>
+        <v>-20.72</v>
       </c>
       <c r="I124" t="n">
         <v>0.31</v>
@@ -14053,31 +14045,31 @@
         <v>19.18</v>
       </c>
       <c r="K124" t="n">
-        <v>9.390000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L124" t="n">
-        <v>197.67</v>
+        <v>197.69</v>
       </c>
       <c r="M124" t="n">
-        <v>207.26</v>
+        <v>207.28</v>
       </c>
       <c r="N124" t="n">
-        <v>178.49</v>
+        <v>178.5</v>
       </c>
       <c r="O124" t="n">
-        <v>246.58</v>
+        <v>246.6</v>
       </c>
       <c r="P124" t="n">
         <v>1.63</v>
       </c>
       <c r="Q124" t="n">
-        <v>44</v>
+        <v>44.01</v>
       </c>
       <c r="R124" t="n">
-        <v>-4.95</v>
+        <v>-4.94</v>
       </c>
       <c r="S124" t="n">
-        <v>-19.85</v>
+        <v>-19.84</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14096,7 +14088,7 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>QQQ 8.55% · ARKK -4.39% · SPY 4.04%</t>
+          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
@@ -14138,22 +14130,22 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>24.11</v>
+        <v>24.04</v>
       </c>
       <c r="D125" t="n">
         <v>33</v>
       </c>
       <c r="E125" t="n">
-        <v>-3.25</v>
+        <v>-3.53</v>
       </c>
       <c r="F125" t="n">
-        <v>30.47</v>
+        <v>30.09</v>
       </c>
       <c r="G125" t="n">
-        <v>46.12</v>
+        <v>45.7</v>
       </c>
       <c r="H125" t="n">
-        <v>21.92</v>
+        <v>21.55</v>
       </c>
       <c r="I125" t="n">
         <v>0.48</v>
@@ -14162,31 +14154,31 @@
         <v>1.65</v>
       </c>
       <c r="K125" t="n">
-        <v>6.83</v>
+        <v>6.85</v>
       </c>
       <c r="L125" t="n">
-        <v>23.53</v>
+        <v>23.46</v>
       </c>
       <c r="M125" t="n">
-        <v>24.36</v>
+        <v>24.29</v>
       </c>
       <c r="N125" t="n">
-        <v>21.89</v>
+        <v>21.82</v>
       </c>
       <c r="O125" t="n">
-        <v>27.73</v>
+        <v>27.66</v>
       </c>
       <c r="P125" t="n">
         <v>1.63</v>
       </c>
       <c r="Q125" t="n">
-        <v>76.14</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="R125" t="n">
-        <v>12.89</v>
+        <v>12.59</v>
       </c>
       <c r="S125" t="n">
-        <v>-6.77</v>
+        <v>-7.04</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14205,7 +14197,7 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>BTC-USD 1.48% · ETH-USD -5.3%</t>
+          <t>BTC-USD 1.43% · ETH-USD -5.34%</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
@@ -14231,7 +14223,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.48% · ETH-USD -5.3%; RSI sobrecomprado; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
+          <t>Sector no acompaña: BTC-USD 1.43% · ETH-USD -5.34%; RSI sobrecomprado; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -575,25 +575,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>499.66</v>
+        <v>499.59</v>
       </c>
       <c r="D2" t="n">
         <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="F2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="G2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.49</v>
+        <v>-7.47</v>
       </c>
       <c r="I2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="J2" t="n">
         <v>5.02</v>
@@ -602,28 +602,28 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>497.9</v>
+        <v>497.83</v>
       </c>
       <c r="M2" t="n">
-        <v>500.41</v>
+        <v>500.34</v>
       </c>
       <c r="N2" t="n">
-        <v>492.89</v>
+        <v>492.82</v>
       </c>
       <c r="O2" t="n">
-        <v>510.7</v>
+        <v>510.63</v>
       </c>
       <c r="P2" t="n">
         <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>53.95</v>
+        <v>53.87</v>
       </c>
       <c r="R2" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -684,55 +684,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42.19</v>
+        <v>42.32</v>
       </c>
       <c r="D3" t="n">
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>2.86</v>
+        <v>3.17</v>
       </c>
       <c r="F3" t="n">
-        <v>7.89</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>18.47</v>
+        <v>18.82</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.65</v>
+        <v>-0.29</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="J3" t="n">
         <v>1.18</v>
       </c>
       <c r="K3" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="L3" t="n">
-        <v>41.78</v>
+        <v>41.91</v>
       </c>
       <c r="M3" t="n">
-        <v>42.37</v>
+        <v>42.5</v>
       </c>
       <c r="N3" t="n">
-        <v>40.61</v>
+        <v>40.73</v>
       </c>
       <c r="O3" t="n">
-        <v>44.78</v>
+        <v>44.91</v>
       </c>
       <c r="P3" t="n">
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>49.47</v>
+        <v>50.1</v>
       </c>
       <c r="R3" t="n">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.2</v>
+        <v>-2.91</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>XLE 5.63% · CL=F 5.62%</t>
+          <t>XLE 5.79% · CL=F 5.84%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.79% · CL=F 5.84%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -797,55 +797,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>157.34</v>
+        <v>157.77</v>
       </c>
       <c r="D4" t="n">
         <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>4.51</v>
+        <v>4.8</v>
       </c>
       <c r="F4" t="n">
-        <v>5.96</v>
+        <v>6.25</v>
       </c>
       <c r="G4" t="n">
-        <v>6.13</v>
+        <v>6.42</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.58</v>
+        <v>-2.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J4" t="n">
         <v>4.33</v>
       </c>
       <c r="K4" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="L4" t="n">
-        <v>155.83</v>
+        <v>156.26</v>
       </c>
       <c r="M4" t="n">
-        <v>157.99</v>
+        <v>158.42</v>
       </c>
       <c r="N4" t="n">
-        <v>151.5</v>
+        <v>151.93</v>
       </c>
       <c r="O4" t="n">
-        <v>166.86</v>
+        <v>167.3</v>
       </c>
       <c r="P4" t="n">
         <v>1.63</v>
       </c>
       <c r="Q4" t="n">
-        <v>55.32</v>
+        <v>55.95</v>
       </c>
       <c r="R4" t="n">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.87</v>
+        <v>-3.61</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>XLE 5.63% · CL=F 5.62%</t>
+          <t>XLE 5.79% · CL=F 5.84%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.79% · CL=F 5.84%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>59.75</v>
+        <v>59.87</v>
       </c>
       <c r="D5" t="n">
         <v>96</v>
       </c>
       <c r="E5" t="n">
-        <v>3.68</v>
+        <v>3.88</v>
       </c>
       <c r="F5" t="n">
-        <v>5.68</v>
+        <v>5.88</v>
       </c>
       <c r="G5" t="n">
-        <v>9.15</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.86</v>
+        <v>-2.62</v>
       </c>
       <c r="I5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="J5" t="n">
         <v>1.38</v>
@@ -937,28 +937,28 @@
         <v>2.31</v>
       </c>
       <c r="L5" t="n">
-        <v>59.27</v>
+        <v>59.38</v>
       </c>
       <c r="M5" t="n">
-        <v>59.96</v>
+        <v>60.07</v>
       </c>
       <c r="N5" t="n">
-        <v>57.89</v>
+        <v>58</v>
       </c>
       <c r="O5" t="n">
-        <v>62.79</v>
+        <v>62.9</v>
       </c>
       <c r="P5" t="n">
         <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>50.41</v>
+        <v>50.88</v>
       </c>
       <c r="R5" t="n">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.16</v>
+        <v>-2.97</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>XLE 5.63% · CL=F 5.62%</t>
+          <t>XLE 5.79% · CL=F 5.84%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.79% · CL=F 5.84%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1019,22 +1019,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>140.4</v>
+        <v>140.82</v>
       </c>
       <c r="D6" t="n">
         <v>96</v>
       </c>
       <c r="E6" t="n">
-        <v>4.05</v>
+        <v>4.37</v>
       </c>
       <c r="F6" t="n">
-        <v>5.56</v>
+        <v>5.88</v>
       </c>
       <c r="G6" t="n">
-        <v>14.38</v>
+        <v>14.73</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.98</v>
+        <v>-2.62</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -1043,31 +1043,31 @@
         <v>3.96</v>
       </c>
       <c r="K6" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="L6" t="n">
-        <v>139.01</v>
+        <v>139.44</v>
       </c>
       <c r="M6" t="n">
-        <v>140.99</v>
+        <v>141.42</v>
       </c>
       <c r="N6" t="n">
-        <v>135.05</v>
+        <v>135.48</v>
       </c>
       <c r="O6" t="n">
-        <v>149.12</v>
+        <v>149.54</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>49.75</v>
+        <v>50.38</v>
       </c>
       <c r="R6" t="n">
-        <v>2.52</v>
+        <v>2.81</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.64</v>
+        <v>-3.35</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>XLE 5.63% · CL=F 5.62%</t>
+          <t>XLE 5.79% · CL=F 5.84%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.79% · CL=F 5.84%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1132,22 +1132,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>203.02</v>
+        <v>203.45</v>
       </c>
       <c r="D7" t="n">
         <v>96</v>
       </c>
       <c r="E7" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="F7" t="n">
-        <v>5.3</v>
+        <v>5.52</v>
       </c>
       <c r="G7" t="n">
-        <v>19.03</v>
+        <v>19.29</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.24</v>
+        <v>-2.98</v>
       </c>
       <c r="I7" t="n">
         <v>0.33</v>
@@ -1156,31 +1156,31 @@
         <v>6.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="L7" t="n">
-        <v>200.73</v>
+        <v>201.16</v>
       </c>
       <c r="M7" t="n">
-        <v>204</v>
+        <v>204.43</v>
       </c>
       <c r="N7" t="n">
-        <v>194.17</v>
+        <v>194.6</v>
       </c>
       <c r="O7" t="n">
-        <v>217.44</v>
+        <v>217.87</v>
       </c>
       <c r="P7" t="n">
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>48.71</v>
+        <v>49.08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.84</v>
+        <v>-4.63</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>XLE 5.63% · CL=F 5.62%</t>
+          <t>XLE 5.79% · CL=F 5.84%</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.79% · CL=F 5.84%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Volumen bajo; Débil vs QQQ</t>
+          <t>Volumen bajo</t>
         </is>
       </c>
     </row>
@@ -1245,55 +1245,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>56.89</v>
+        <v>57.01</v>
       </c>
       <c r="D8" t="n">
         <v>96</v>
       </c>
       <c r="E8" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="F8" t="n">
-        <v>4.67</v>
+        <v>4.89</v>
       </c>
       <c r="G8" t="n">
-        <v>9.720000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.87</v>
+        <v>-3.61</v>
       </c>
       <c r="I8" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="J8" t="n">
         <v>1.41</v>
       </c>
       <c r="K8" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="L8" t="n">
-        <v>56.4</v>
+        <v>56.51</v>
       </c>
       <c r="M8" t="n">
-        <v>57.1</v>
+        <v>57.22</v>
       </c>
       <c r="N8" t="n">
-        <v>54.99</v>
+        <v>55.1</v>
       </c>
       <c r="O8" t="n">
-        <v>59.99</v>
+        <v>60.11</v>
       </c>
       <c r="P8" t="n">
         <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>50.05</v>
+        <v>50.58</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4</v>
+        <v>-1.2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>XLE 5.63% · CL=F 5.62%</t>
+          <t>XLE 5.79% · CL=F 5.84%</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.79% · CL=F 5.84%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1358,55 +1358,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>516.71</v>
+        <v>515.99</v>
       </c>
       <c r="D9" t="n">
         <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.19</v>
+        <v>-2.33</v>
       </c>
       <c r="F9" t="n">
-        <v>19.67</v>
+        <v>19.51</v>
       </c>
       <c r="G9" t="n">
-        <v>42.81</v>
+        <v>42.61</v>
       </c>
       <c r="H9" t="n">
-        <v>11.13</v>
+        <v>11.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>21.72</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="L9" t="n">
-        <v>509.1</v>
+        <v>508.39</v>
       </c>
       <c r="M9" t="n">
-        <v>519.96</v>
+        <v>519.25</v>
       </c>
       <c r="N9" t="n">
-        <v>487.38</v>
+        <v>486.67</v>
       </c>
       <c r="O9" t="n">
-        <v>564.49</v>
+        <v>563.77</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>64.28</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>5.85</v>
+        <v>5.71</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.19</v>
+        <v>-3.33</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SOXX 19.64% · QQQ 8.54%</t>
+          <t>SOXX 19.54% · QQQ 8.5%</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1471,22 +1471,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>192.43</v>
+        <v>192.8</v>
       </c>
       <c r="D10" t="n">
         <v>91</v>
       </c>
       <c r="E10" t="n">
-        <v>4.4</v>
+        <v>4.61</v>
       </c>
       <c r="F10" t="n">
-        <v>4.23</v>
+        <v>4.43</v>
       </c>
       <c r="G10" t="n">
-        <v>4.78</v>
+        <v>4.98</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.31</v>
+        <v>-4.07</v>
       </c>
       <c r="I10" t="n">
         <v>0.65</v>
@@ -1498,28 +1498,28 @@
         <v>2.36</v>
       </c>
       <c r="L10" t="n">
-        <v>190.84</v>
+        <v>191.21</v>
       </c>
       <c r="M10" t="n">
-        <v>193.11</v>
+        <v>193.48</v>
       </c>
       <c r="N10" t="n">
-        <v>186.3</v>
+        <v>186.67</v>
       </c>
       <c r="O10" t="n">
-        <v>202.42</v>
+        <v>202.79</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>51.16</v>
+        <v>51.67</v>
       </c>
       <c r="R10" t="n">
-        <v>2.74</v>
+        <v>2.93</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.24</v>
+        <v>-3.05</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>XLE 5.63% · CL=F 5.62%</t>
+          <t>XLE 5.79% · CL=F 5.84%</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.79% · CL=F 5.84%; Precio sobre MA20; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>109.64</v>
+        <v>109.37</v>
       </c>
       <c r="D11" t="n">
         <v>83</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.25</v>
+        <v>-5.48</v>
       </c>
       <c r="F11" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="G11" t="n">
-        <v>56.55</v>
+        <v>56.18</v>
       </c>
       <c r="H11" t="n">
-        <v>14.66</v>
+        <v>14.4</v>
       </c>
       <c r="I11" t="n">
         <v>0.27</v>
@@ -1608,31 +1608,31 @@
         <v>6.38</v>
       </c>
       <c r="K11" t="n">
-        <v>5.82</v>
+        <v>5.83</v>
       </c>
       <c r="L11" t="n">
-        <v>107.4</v>
+        <v>107.14</v>
       </c>
       <c r="M11" t="n">
-        <v>110.59</v>
+        <v>110.33</v>
       </c>
       <c r="N11" t="n">
-        <v>101.02</v>
+        <v>100.76</v>
       </c>
       <c r="O11" t="n">
-        <v>123.67</v>
+        <v>123.4</v>
       </c>
       <c r="P11" t="n">
         <v>1.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>58.47</v>
+        <v>58.26</v>
       </c>
       <c r="R11" t="n">
-        <v>5.01</v>
+        <v>4.77</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.95</v>
+        <v>-8.17</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>SOXX 19.64% · QQQ 8.54%</t>
+          <t>SOXX 19.54% · QQQ 8.5%</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1697,55 +1697,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1543.06</v>
+        <v>1540.27</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.44</v>
+        <v>-2.61</v>
       </c>
       <c r="F12" t="n">
-        <v>7.12</v>
+        <v>6.92</v>
       </c>
       <c r="G12" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.42</v>
+        <v>-1.58</v>
       </c>
       <c r="I12" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="J12" t="n">
         <v>70.26000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>4.55</v>
+        <v>4.56</v>
       </c>
       <c r="L12" t="n">
-        <v>1518.47</v>
+        <v>1515.67</v>
       </c>
       <c r="M12" t="n">
-        <v>1553.6</v>
+        <v>1550.8</v>
       </c>
       <c r="N12" t="n">
-        <v>1448.21</v>
+        <v>1445.41</v>
       </c>
       <c r="O12" t="n">
-        <v>1697.64</v>
+        <v>1694.84</v>
       </c>
       <c r="P12" t="n">
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>57.91</v>
+        <v>57.73</v>
       </c>
       <c r="R12" t="n">
-        <v>4.06</v>
+        <v>3.88</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.77</v>
+        <v>-3.94</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>SOXX 19.64% · QQQ 8.54%</t>
+          <t>SOXX 19.54% · QQQ 8.5%</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1810,25 +1810,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>401.81</v>
+        <v>401.36</v>
       </c>
       <c r="D13" t="n">
         <v>87</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="F13" t="n">
-        <v>3.71</v>
+        <v>3.59</v>
       </c>
       <c r="G13" t="n">
-        <v>4.46</v>
+        <v>4.34</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.83</v>
+        <v>-4.91</v>
       </c>
       <c r="I13" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="J13" t="n">
         <v>15.59</v>
@@ -1837,28 +1837,28 @@
         <v>3.88</v>
       </c>
       <c r="L13" t="n">
-        <v>396.35</v>
+        <v>395.9</v>
       </c>
       <c r="M13" t="n">
-        <v>404.15</v>
+        <v>403.7</v>
       </c>
       <c r="N13" t="n">
-        <v>380.76</v>
+        <v>380.31</v>
       </c>
       <c r="O13" t="n">
-        <v>436.11</v>
+        <v>435.66</v>
       </c>
       <c r="P13" t="n">
         <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>52.5</v>
+        <v>52.32</v>
       </c>
       <c r="R13" t="n">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.78</v>
+        <v>-4.88</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>SOXX 19.64% · QQQ 8.54%</t>
+          <t>SOXX 19.54% · QQQ 8.5%</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1914,64 +1914,64 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1812.31</v>
+        <v>59.13</v>
       </c>
       <c r="D14" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.9</v>
+        <v>5.25</v>
       </c>
       <c r="F14" t="n">
-        <v>0.14</v>
+        <v>3.65</v>
       </c>
       <c r="G14" t="n">
-        <v>20.44</v>
+        <v>14.36</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.4</v>
+        <v>-4.85</v>
       </c>
       <c r="I14" t="n">
-        <v>0.36</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>81.3</v>
+        <v>1.98</v>
       </c>
       <c r="K14" t="n">
-        <v>4.49</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
-        <v>1783.85</v>
+        <v>58.44</v>
       </c>
       <c r="M14" t="n">
-        <v>1824.51</v>
+        <v>59.43</v>
       </c>
       <c r="N14" t="n">
-        <v>1702.55</v>
+        <v>56.46</v>
       </c>
       <c r="O14" t="n">
-        <v>1991.17</v>
+        <v>63.49</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>54.87</v>
+        <v>46.39</v>
       </c>
       <c r="R14" t="n">
-        <v>0.35</v>
+        <v>2.29</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.43</v>
+        <v>-3.38</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>SOXX 19.64% · QQQ 8.54%</t>
+          <t>XLE 5.79% · CL=F 5.84%</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2015,19 +2015,19 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.79% · CL=F 5.84%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2036,55 +2036,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>58.96</v>
+        <v>48.53</v>
       </c>
       <c r="D15" t="n">
         <v>77</v>
       </c>
       <c r="E15" t="n">
-        <v>4.95</v>
+        <v>3.48</v>
       </c>
       <c r="F15" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="G15" t="n">
-        <v>14.03</v>
+        <v>12.72</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.19</v>
+        <v>-5.51</v>
       </c>
       <c r="I15" t="n">
-        <v>0.68</v>
+        <v>0.51</v>
       </c>
       <c r="J15" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="K15" t="n">
-        <v>3.36</v>
+        <v>3.56</v>
       </c>
       <c r="L15" t="n">
-        <v>58.27</v>
+        <v>47.93</v>
       </c>
       <c r="M15" t="n">
-        <v>59.26</v>
+        <v>48.79</v>
       </c>
       <c r="N15" t="n">
-        <v>56.29</v>
+        <v>46.2</v>
       </c>
       <c r="O15" t="n">
-        <v>63.32</v>
+        <v>52.33</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>46</v>
+        <v>39.08</v>
       </c>
       <c r="R15" t="n">
-        <v>2.01</v>
+        <v>-0.1</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.66</v>
+        <v>-6.58</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>XLE 5.63% · CL=F 5.62%</t>
+          <t>XLE 5.79% · CL=F 5.84%</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2128,19 +2128,19 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.79% · CL=F 5.84%; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2149,55 +2149,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>48.43</v>
+        <v>122.31</v>
       </c>
       <c r="D16" t="n">
         <v>77</v>
       </c>
       <c r="E16" t="n">
-        <v>3.26</v>
+        <v>4.18</v>
       </c>
       <c r="F16" t="n">
-        <v>2.78</v>
+        <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>12.48</v>
+        <v>11.42</v>
       </c>
       <c r="H16" t="n">
-        <v>-5.76</v>
+        <v>-8</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="J16" t="n">
-        <v>1.73</v>
+        <v>3.29</v>
       </c>
       <c r="K16" t="n">
-        <v>3.57</v>
+        <v>2.69</v>
       </c>
       <c r="L16" t="n">
-        <v>47.83</v>
+        <v>121.16</v>
       </c>
       <c r="M16" t="n">
-        <v>48.69</v>
+        <v>122.8</v>
       </c>
       <c r="N16" t="n">
-        <v>46.1</v>
+        <v>117.87</v>
       </c>
       <c r="O16" t="n">
-        <v>52.23</v>
+        <v>129.55</v>
       </c>
       <c r="P16" t="n">
         <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>38.78</v>
+        <v>45.91</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.3</v>
+        <v>1.14</v>
       </c>
       <c r="S16" t="n">
-        <v>-6.78</v>
+        <v>-3.95</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>XLE 5.63% · CL=F 5.62%</t>
+          <t>XLE 5.79% · CL=F 5.84%</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2241,76 +2241,76 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; MA20 sobre MA50; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.79% · CL=F 5.84%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; Volumen bajo; Débil vs QQQ</t>
+          <t>Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>121.95</v>
+        <v>93.2</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E17" t="n">
-        <v>3.88</v>
+        <v>-3.63</v>
       </c>
       <c r="F17" t="n">
-        <v>0.21</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>11.09</v>
+        <v>22.74</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.33</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="J17" t="n">
-        <v>3.29</v>
+        <v>4.07</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>4.37</v>
       </c>
       <c r="L17" t="n">
-        <v>120.8</v>
+        <v>91.77</v>
       </c>
       <c r="M17" t="n">
-        <v>122.44</v>
+        <v>93.81</v>
       </c>
       <c r="N17" t="n">
-        <v>117.51</v>
+        <v>87.7</v>
       </c>
       <c r="O17" t="n">
-        <v>129.19</v>
+        <v>102.16</v>
       </c>
       <c r="P17" t="n">
         <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>45.38</v>
+        <v>50.63</v>
       </c>
       <c r="R17" t="n">
-        <v>0.86</v>
+        <v>-1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.23</v>
+        <v>-12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>XLE 5.63% · CL=F 5.62%</t>
+          <t>SOXX 19.54% · QQQ 8.5%</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2354,76 +2354,76 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: XLE 5.63% · CL=F 5.62%; Precio sobre MA20; Tendencia larga positiva; MACD positivo</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.5%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Volumen bajo; Débil vs QQQ</t>
+          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>93.43000000000001</v>
+        <v>1809.01</v>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.39</v>
+        <v>-2.08</v>
       </c>
       <c r="F18" t="n">
-        <v>13.28</v>
+        <v>-0.04</v>
       </c>
       <c r="G18" t="n">
-        <v>23.05</v>
+        <v>20.22</v>
       </c>
       <c r="H18" t="n">
-        <v>4.74</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="J18" t="n">
-        <v>4.07</v>
+        <v>81.3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.36</v>
+        <v>4.49</v>
       </c>
       <c r="L18" t="n">
-        <v>92.01000000000001</v>
+        <v>1780.55</v>
       </c>
       <c r="M18" t="n">
-        <v>94.04000000000001</v>
+        <v>1821.21</v>
       </c>
       <c r="N18" t="n">
-        <v>87.93000000000001</v>
+        <v>1699.25</v>
       </c>
       <c r="O18" t="n">
-        <v>102.39</v>
+        <v>1987.87</v>
       </c>
       <c r="P18" t="n">
         <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>51.11</v>
+        <v>54.64</v>
       </c>
       <c r="R18" t="n">
-        <v>-1.02</v>
+        <v>0.17</v>
       </c>
       <c r="S18" t="n">
-        <v>-11.78</v>
+        <v>-6.6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>SOXX 19.64% · QQQ 8.54%</t>
+          <t>SOXX 19.54% · QQQ 8.5%</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2450,11 +2450,7 @@
           <t>BAJO</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -2467,12 +2463,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; MA20 sobre MA50; Tendencia larga positiva; RSI saludable</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Precio bajo MA20; MACD sin confirmar; Volumen bajo; Momentum negativo</t>
+          <t>MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2484,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>422.45</v>
+        <v>422.1</v>
       </c>
       <c r="D19" t="n">
         <v>74</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.24</v>
+        <v>-3.32</v>
       </c>
       <c r="F19" t="n">
-        <v>4.7</v>
+        <v>4.61</v>
       </c>
       <c r="G19" t="n">
-        <v>11.78</v>
+        <v>11.69</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.84</v>
+        <v>-3.89</v>
       </c>
       <c r="I19" t="n">
         <v>0.49</v>
@@ -2512,31 +2508,31 @@
         <v>20.58</v>
       </c>
       <c r="K19" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
       <c r="L19" t="n">
-        <v>415.24</v>
+        <v>414.89</v>
       </c>
       <c r="M19" t="n">
-        <v>425.53</v>
+        <v>425.18</v>
       </c>
       <c r="N19" t="n">
-        <v>394.67</v>
+        <v>394.31</v>
       </c>
       <c r="O19" t="n">
-        <v>467.72</v>
+        <v>467.37</v>
       </c>
       <c r="P19" t="n">
         <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.38</v>
+        <v>58.29</v>
       </c>
       <c r="R19" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="S19" t="n">
-        <v>-5.8</v>
+        <v>-5.88</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2555,7 +2551,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>SOXX 19.64% · QQQ 8.54%</t>
+          <t>SOXX 19.54% · QQQ 8.5%</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2576,7 +2572,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2597,25 +2593,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>331.05</v>
+        <v>331.14</v>
       </c>
       <c r="D20" t="n">
         <v>96</v>
       </c>
       <c r="E20" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="F20" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
       <c r="G20" t="n">
-        <v>7.98</v>
+        <v>8.01</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.97</v>
+        <v>-1.9</v>
       </c>
       <c r="I20" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="J20" t="n">
         <v>6.09</v>
@@ -2624,28 +2620,28 @@
         <v>1.84</v>
       </c>
       <c r="L20" t="n">
-        <v>328.92</v>
+        <v>329.01</v>
       </c>
       <c r="M20" t="n">
-        <v>331.97</v>
+        <v>332.06</v>
       </c>
       <c r="N20" t="n">
-        <v>322.83</v>
+        <v>322.92</v>
       </c>
       <c r="O20" t="n">
-        <v>344.45</v>
+        <v>344.54</v>
       </c>
       <c r="P20" t="n">
         <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>52.04</v>
+        <v>52.13</v>
       </c>
       <c r="R20" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.99</v>
+        <v>-2.97</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2710,25 +2706,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>975.7</v>
+        <v>974.48</v>
       </c>
       <c r="D21" t="n">
         <v>96</v>
       </c>
       <c r="E21" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="F21" t="n">
-        <v>4.37</v>
+        <v>4.24</v>
       </c>
       <c r="G21" t="n">
-        <v>8.710000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.17</v>
+        <v>-4.26</v>
       </c>
       <c r="I21" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="J21" t="n">
         <v>24.93</v>
@@ -2737,28 +2733,28 @@
         <v>2.56</v>
       </c>
       <c r="L21" t="n">
-        <v>966.97</v>
+        <v>965.75</v>
       </c>
       <c r="M21" t="n">
-        <v>979.4400000000001</v>
+        <v>978.22</v>
       </c>
       <c r="N21" t="n">
-        <v>942.03</v>
+        <v>940.8200000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>1030.55</v>
+        <v>1029.33</v>
       </c>
       <c r="P21" t="n">
         <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>63.22</v>
+        <v>63</v>
       </c>
       <c r="R21" t="n">
-        <v>4.29</v>
+        <v>4.16</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1</v>
+        <v>-0.23</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2823,25 +2819,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>106.64</v>
+        <v>106.57</v>
       </c>
       <c r="D22" t="n">
         <v>95</v>
       </c>
       <c r="E22" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="F22" t="n">
-        <v>7.79</v>
+        <v>7.71</v>
       </c>
       <c r="G22" t="n">
-        <v>11.15</v>
+        <v>11.07</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.75</v>
+        <v>-0.79</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="J22" t="n">
         <v>2.48</v>
@@ -2850,28 +2846,28 @@
         <v>2.32</v>
       </c>
       <c r="L22" t="n">
-        <v>105.78</v>
+        <v>105.7</v>
       </c>
       <c r="M22" t="n">
-        <v>107.02</v>
+        <v>106.94</v>
       </c>
       <c r="N22" t="n">
-        <v>103.3</v>
+        <v>103.23</v>
       </c>
       <c r="O22" t="n">
-        <v>112.09</v>
+        <v>112.02</v>
       </c>
       <c r="P22" t="n">
         <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>59.36</v>
+        <v>59.06</v>
       </c>
       <c r="R22" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.48</v>
+        <v>-1.55</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2936,55 +2932,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>197.4</v>
+        <v>197.15</v>
       </c>
       <c r="D23" t="n">
         <v>95</v>
       </c>
       <c r="E23" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="F23" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="G23" t="n">
-        <v>17.58</v>
+        <v>17.43</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.66</v>
+        <v>-4.75</v>
       </c>
       <c r="I23" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="J23" t="n">
         <v>4.45</v>
       </c>
       <c r="K23" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="L23" t="n">
-        <v>195.84</v>
+        <v>195.6</v>
       </c>
       <c r="M23" t="n">
-        <v>198.06</v>
+        <v>197.82</v>
       </c>
       <c r="N23" t="n">
-        <v>191.39</v>
+        <v>191.15</v>
       </c>
       <c r="O23" t="n">
-        <v>207.18</v>
+        <v>206.94</v>
       </c>
       <c r="P23" t="n">
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>60.45</v>
+        <v>60.15</v>
       </c>
       <c r="R23" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.27</v>
+        <v>-0.39</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3049,25 +3045,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>298.39</v>
+        <v>297.99</v>
       </c>
       <c r="D24" t="n">
         <v>85</v>
       </c>
       <c r="E24" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>7.85</v>
       </c>
       <c r="G24" t="n">
-        <v>-13.54</v>
+        <v>-13.66</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.54</v>
+        <v>-0.65</v>
       </c>
       <c r="I24" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="J24" t="n">
         <v>9.57</v>
@@ -3076,28 +3072,28 @@
         <v>3.21</v>
       </c>
       <c r="L24" t="n">
-        <v>295.04</v>
+        <v>294.64</v>
       </c>
       <c r="M24" t="n">
-        <v>299.83</v>
+        <v>299.42</v>
       </c>
       <c r="N24" t="n">
-        <v>285.47</v>
+        <v>285.07</v>
       </c>
       <c r="O24" t="n">
-        <v>319.44</v>
+        <v>319.04</v>
       </c>
       <c r="P24" t="n">
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>55</v>
+        <v>54.79</v>
       </c>
       <c r="R24" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.75</v>
+        <v>-3.87</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3162,22 +3158,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>386.83</v>
+        <v>387.1</v>
       </c>
       <c r="D25" t="n">
         <v>84</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.92</v>
+        <v>-3.85</v>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>14.08</v>
       </c>
       <c r="G25" t="n">
-        <v>24.51</v>
+        <v>24.6</v>
       </c>
       <c r="H25" t="n">
-        <v>5.46</v>
+        <v>5.58</v>
       </c>
       <c r="I25" t="n">
         <v>0.59</v>
@@ -3186,31 +3182,31 @@
         <v>9.81</v>
       </c>
       <c r="K25" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="L25" t="n">
-        <v>383.4</v>
+        <v>383.67</v>
       </c>
       <c r="M25" t="n">
-        <v>388.3</v>
+        <v>388.57</v>
       </c>
       <c r="N25" t="n">
-        <v>373.59</v>
+        <v>373.86</v>
       </c>
       <c r="O25" t="n">
-        <v>408.41</v>
+        <v>408.68</v>
       </c>
       <c r="P25" t="n">
         <v>1.63</v>
       </c>
       <c r="Q25" t="n">
-        <v>51.54</v>
+        <v>51.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.33</v>
+        <v>-5.26</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3229,7 +3225,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
+          <t>QQQ 8.5% · ARKK -4.51% · SPY 4.05%</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3275,25 +3271,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>212.6</v>
+        <v>212.4</v>
       </c>
       <c r="D26" t="n">
         <v>82</v>
       </c>
       <c r="E26" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="F26" t="n">
-        <v>6.03</v>
+        <v>5.94</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.16</v>
+        <v>-6.25</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.51</v>
+        <v>-2.56</v>
       </c>
       <c r="I26" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="J26" t="n">
         <v>4.74</v>
@@ -3302,28 +3298,28 @@
         <v>2.23</v>
       </c>
       <c r="L26" t="n">
-        <v>210.94</v>
+        <v>210.74</v>
       </c>
       <c r="M26" t="n">
-        <v>213.31</v>
+        <v>213.11</v>
       </c>
       <c r="N26" t="n">
-        <v>206.19</v>
+        <v>206</v>
       </c>
       <c r="O26" t="n">
-        <v>223.04</v>
+        <v>222.84</v>
       </c>
       <c r="P26" t="n">
         <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>52.21</v>
+        <v>51.86</v>
       </c>
       <c r="R26" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.48</v>
+        <v>-1.57</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3388,25 +3384,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>131.5</v>
+        <v>131.46</v>
       </c>
       <c r="D27" t="n">
         <v>96</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02</v>
+        <v>-0</v>
       </c>
       <c r="F27" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="G27" t="n">
-        <v>4.16</v>
+        <v>4.13</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.18</v>
+        <v>-7.16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="J27" t="n">
         <v>2.59</v>
@@ -3415,28 +3411,28 @@
         <v>1.97</v>
       </c>
       <c r="L27" t="n">
-        <v>130.59</v>
+        <v>130.56</v>
       </c>
       <c r="M27" t="n">
-        <v>131.89</v>
+        <v>131.85</v>
       </c>
       <c r="N27" t="n">
-        <v>128.01</v>
+        <v>127.97</v>
       </c>
       <c r="O27" t="n">
-        <v>137.19</v>
+        <v>137.16</v>
       </c>
       <c r="P27" t="n">
         <v>1.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>49.49</v>
+        <v>49.39</v>
       </c>
       <c r="R27" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.71</v>
+        <v>-2.73</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3497,22 +3493,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>288.02</v>
+        <v>287.76</v>
       </c>
       <c r="D28" t="n">
         <v>90</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.51</v>
+        <v>-2.6</v>
       </c>
       <c r="F28" t="n">
-        <v>8.460000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>18.06</v>
+        <v>17.95</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="I28" t="n">
         <v>0.48</v>
@@ -3524,28 +3520,28 @@
         <v>5.3</v>
       </c>
       <c r="L28" t="n">
-        <v>282.67</v>
+        <v>282.42</v>
       </c>
       <c r="M28" t="n">
-        <v>290.3</v>
+        <v>290.05</v>
       </c>
       <c r="N28" t="n">
-        <v>267.41</v>
+        <v>267.15</v>
       </c>
       <c r="O28" t="n">
-        <v>321.59</v>
+        <v>321.34</v>
       </c>
       <c r="P28" t="n">
         <v>1.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>62.68</v>
+        <v>62.6</v>
       </c>
       <c r="R28" t="n">
-        <v>4.42</v>
+        <v>4.33</v>
       </c>
       <c r="S28" t="n">
-        <v>-4.63</v>
+        <v>-4.72</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3606,25 +3602,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>113.24</v>
+        <v>113.29</v>
       </c>
       <c r="D29" t="n">
         <v>89</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="F29" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="G29" t="n">
-        <v>-7.95</v>
+        <v>-7.91</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.23</v>
+        <v>-8.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J29" t="n">
         <v>2.5</v>
@@ -3633,28 +3629,28 @@
         <v>2.21</v>
       </c>
       <c r="L29" t="n">
-        <v>112.36</v>
+        <v>112.41</v>
       </c>
       <c r="M29" t="n">
-        <v>113.62</v>
+        <v>113.67</v>
       </c>
       <c r="N29" t="n">
-        <v>109.86</v>
+        <v>109.91</v>
       </c>
       <c r="O29" t="n">
-        <v>118.74</v>
+        <v>118.79</v>
       </c>
       <c r="P29" t="n">
         <v>1.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>63.75</v>
+        <v>63.97</v>
       </c>
       <c r="R29" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.62</v>
+        <v>-1.57</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3715,7 +3711,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>230.13</v>
+        <v>230.15</v>
       </c>
       <c r="D30" t="n">
         <v>85</v>
@@ -3724,16 +3720,16 @@
         <v>-0.12</v>
       </c>
       <c r="F30" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G30" t="n">
-        <v>-6.56</v>
+        <v>-6.55</v>
       </c>
       <c r="H30" t="n">
-        <v>-6.76</v>
+        <v>-6.71</v>
       </c>
       <c r="I30" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="J30" t="n">
         <v>3.73</v>
@@ -3742,22 +3738,22 @@
         <v>1.62</v>
       </c>
       <c r="L30" t="n">
-        <v>228.83</v>
+        <v>228.85</v>
       </c>
       <c r="M30" t="n">
-        <v>230.69</v>
+        <v>230.71</v>
       </c>
       <c r="N30" t="n">
-        <v>225.11</v>
+        <v>225.12</v>
       </c>
       <c r="O30" t="n">
-        <v>238.33</v>
+        <v>238.34</v>
       </c>
       <c r="P30" t="n">
         <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.5</v>
+        <v>50.53</v>
       </c>
       <c r="R30" t="n">
         <v>1.46</v>
@@ -3824,25 +3820,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>84.45999999999999</v>
+        <v>84.38</v>
       </c>
       <c r="D31" t="n">
         <v>84</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.78</v>
+        <v>-0.87</v>
       </c>
       <c r="F31" t="n">
-        <v>8.130000000000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>17.56</v>
+        <v>17.45</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.41</v>
+        <v>-0.47</v>
       </c>
       <c r="I31" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="J31" t="n">
         <v>2.67</v>
@@ -3851,28 +3847,28 @@
         <v>3.17</v>
       </c>
       <c r="L31" t="n">
-        <v>83.52</v>
+        <v>83.44</v>
       </c>
       <c r="M31" t="n">
-        <v>84.86</v>
+        <v>84.78</v>
       </c>
       <c r="N31" t="n">
-        <v>80.84999999999999</v>
+        <v>80.77</v>
       </c>
       <c r="O31" t="n">
-        <v>90.34</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="P31" t="n">
         <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>61.31</v>
+        <v>61.17</v>
       </c>
       <c r="R31" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="S31" t="n">
-        <v>-4.5</v>
+        <v>-4.59</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3933,22 +3929,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>383.61</v>
+        <v>384.02</v>
       </c>
       <c r="D32" t="n">
         <v>77</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.37</v>
+        <v>-4.27</v>
       </c>
       <c r="F32" t="n">
-        <v>8.51</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>41.12</v>
+        <v>41.27</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.03</v>
+        <v>0.13</v>
       </c>
       <c r="I32" t="n">
         <v>0.57</v>
@@ -3960,28 +3956,28 @@
         <v>2.37</v>
       </c>
       <c r="L32" t="n">
-        <v>380.43</v>
+        <v>380.84</v>
       </c>
       <c r="M32" t="n">
-        <v>384.97</v>
+        <v>385.38</v>
       </c>
       <c r="N32" t="n">
-        <v>371.33</v>
+        <v>371.74</v>
       </c>
       <c r="O32" t="n">
-        <v>403.62</v>
+        <v>404.03</v>
       </c>
       <c r="P32" t="n">
         <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>60.04</v>
+        <v>60.42</v>
       </c>
       <c r="R32" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="S32" t="n">
-        <v>-5.08</v>
+        <v>-4.98</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4042,25 +4038,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>279.21</v>
+        <v>279.02</v>
       </c>
       <c r="D33" t="n">
         <v>74</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.22</v>
+        <v>-1.29</v>
       </c>
       <c r="F33" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="G33" t="n">
-        <v>6.22</v>
+        <v>6.14</v>
       </c>
       <c r="H33" t="n">
-        <v>-7.55</v>
+        <v>-7.58</v>
       </c>
       <c r="I33" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="J33" t="n">
         <v>4.89</v>
@@ -4069,28 +4065,28 @@
         <v>1.75</v>
       </c>
       <c r="L33" t="n">
-        <v>277.5</v>
+        <v>277.3</v>
       </c>
       <c r="M33" t="n">
-        <v>279.95</v>
+        <v>279.75</v>
       </c>
       <c r="N33" t="n">
-        <v>272.61</v>
+        <v>272.41</v>
       </c>
       <c r="O33" t="n">
-        <v>289.98</v>
+        <v>289.78</v>
       </c>
       <c r="P33" t="n">
         <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>51.5</v>
+        <v>51.26</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="S33" t="n">
-        <v>-2.91</v>
+        <v>-2.98</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4151,25 +4147,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>146.83</v>
+        <v>146.88</v>
       </c>
       <c r="D34" t="n">
         <v>74</v>
       </c>
       <c r="E34" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="F34" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="G34" t="n">
-        <v>-6.61</v>
+        <v>-6.58</v>
       </c>
       <c r="H34" t="n">
-        <v>-8.23</v>
+        <v>-8.16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="J34" t="n">
         <v>1.89</v>
@@ -4178,28 +4174,28 @@
         <v>1.29</v>
       </c>
       <c r="L34" t="n">
-        <v>146.17</v>
+        <v>146.21</v>
       </c>
       <c r="M34" t="n">
-        <v>147.11</v>
+        <v>147.16</v>
       </c>
       <c r="N34" t="n">
-        <v>144.28</v>
+        <v>144.33</v>
       </c>
       <c r="O34" t="n">
-        <v>150.98</v>
+        <v>151.03</v>
       </c>
       <c r="P34" t="n">
         <v>1.63</v>
       </c>
       <c r="Q34" t="n">
-        <v>53.42</v>
+        <v>53.62</v>
       </c>
       <c r="R34" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.84</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4260,25 +4256,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>306.47</v>
+        <v>305.74</v>
       </c>
       <c r="D35" t="n">
         <v>96</v>
       </c>
       <c r="E35" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="F35" t="n">
-        <v>35.76</v>
+        <v>35.44</v>
       </c>
       <c r="G35" t="n">
-        <v>31.3</v>
+        <v>30.99</v>
       </c>
       <c r="H35" t="n">
-        <v>27.22</v>
+        <v>26.94</v>
       </c>
       <c r="I35" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="J35" t="n">
         <v>11.48</v>
@@ -4287,28 +4283,28 @@
         <v>3.75</v>
       </c>
       <c r="L35" t="n">
-        <v>302.45</v>
+        <v>301.73</v>
       </c>
       <c r="M35" t="n">
-        <v>308.19</v>
+        <v>307.47</v>
       </c>
       <c r="N35" t="n">
-        <v>290.97</v>
+        <v>290.25</v>
       </c>
       <c r="O35" t="n">
-        <v>331.73</v>
+        <v>331</v>
       </c>
       <c r="P35" t="n">
         <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>57.5</v>
+        <v>57.14</v>
       </c>
       <c r="R35" t="n">
-        <v>7.93</v>
+        <v>7.69</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.67</v>
+        <v>-0.9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4327,7 +4323,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>SOXX 19.64% · QQQ 8.54%</t>
+          <t>SOXX 19.54% · QQQ 8.5%</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4352,7 +4348,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4373,19 +4369,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>184.46</v>
+        <v>184.4</v>
       </c>
       <c r="D36" t="n">
         <v>96</v>
       </c>
       <c r="E36" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="F36" t="n">
-        <v>17.25</v>
+        <v>17.21</v>
       </c>
       <c r="G36" t="n">
-        <v>135.43</v>
+        <v>135.35</v>
       </c>
       <c r="H36" t="n">
         <v>8.710000000000001</v>
@@ -4400,28 +4396,28 @@
         <v>6.81</v>
       </c>
       <c r="L36" t="n">
-        <v>180.07</v>
+        <v>180</v>
       </c>
       <c r="M36" t="n">
-        <v>186.35</v>
+        <v>186.28</v>
       </c>
       <c r="N36" t="n">
-        <v>167.51</v>
+        <v>167.44</v>
       </c>
       <c r="O36" t="n">
-        <v>212.1</v>
+        <v>212.03</v>
       </c>
       <c r="P36" t="n">
         <v>1.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>61.16</v>
+        <v>61.13</v>
       </c>
       <c r="R36" t="n">
-        <v>9.630000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="S36" t="n">
-        <v>-4.58</v>
+        <v>-4.62</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4440,7 +4436,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>SOXX 19.64% · QQQ 8.54%</t>
+          <t>SOXX 19.54% · QQQ 8.5%</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4465,7 +4461,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4486,7 +4482,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>224.37</v>
+        <v>224.36</v>
       </c>
       <c r="D37" t="n">
         <v>96</v>
@@ -4495,16 +4491,16 @@
         <v>-0.65</v>
       </c>
       <c r="F37" t="n">
-        <v>10.8</v>
+        <v>10.79</v>
       </c>
       <c r="G37" t="n">
-        <v>16.35</v>
+        <v>16.34</v>
       </c>
       <c r="H37" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="I37" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>8.09</v>
@@ -4513,25 +4509,25 @@
         <v>3.6</v>
       </c>
       <c r="L37" t="n">
-        <v>221.54</v>
+        <v>221.53</v>
       </c>
       <c r="M37" t="n">
-        <v>225.58</v>
+        <v>225.57</v>
       </c>
       <c r="N37" t="n">
-        <v>213.45</v>
+        <v>213.44</v>
       </c>
       <c r="O37" t="n">
-        <v>242.16</v>
+        <v>242.14</v>
       </c>
       <c r="P37" t="n">
         <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>70.23999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="R37" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="S37" t="n">
         <v>-5.15</v>
@@ -4553,7 +4549,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>SOXX 19.64% · QQQ 8.54%</t>
+          <t>SOXX 19.54% · QQQ 8.5%</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4578,7 +4574,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4599,55 +4595,55 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>300.36</v>
+        <v>299.74</v>
       </c>
       <c r="D38" t="n">
         <v>87</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.95</v>
+        <v>-2.15</v>
       </c>
       <c r="F38" t="n">
-        <v>27.75</v>
+        <v>27.49</v>
       </c>
       <c r="G38" t="n">
-        <v>41.5</v>
+        <v>41.21</v>
       </c>
       <c r="H38" t="n">
-        <v>19.21</v>
+        <v>18.99</v>
       </c>
       <c r="I38" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J38" t="n">
         <v>9.609999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="L38" t="n">
-        <v>297</v>
+        <v>296.38</v>
       </c>
       <c r="M38" t="n">
-        <v>301.8</v>
+        <v>301.19</v>
       </c>
       <c r="N38" t="n">
-        <v>287.39</v>
+        <v>286.77</v>
       </c>
       <c r="O38" t="n">
-        <v>321.5</v>
+        <v>320.88</v>
       </c>
       <c r="P38" t="n">
         <v>1.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>69.27</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="R38" t="n">
-        <v>4.44</v>
+        <v>4.24</v>
       </c>
       <c r="S38" t="n">
-        <v>-3.2</v>
+        <v>-3.4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4666,7 +4662,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>SOXX 19.64% · QQQ 8.54%</t>
+          <t>SOXX 19.54% · QQQ 8.5%</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -4691,7 +4687,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4712,22 +4708,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>561.35</v>
+        <v>560.78</v>
       </c>
       <c r="D39" t="n">
         <v>87</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.94</v>
+        <v>-2.04</v>
       </c>
       <c r="F39" t="n">
-        <v>17.73</v>
+        <v>17.61</v>
       </c>
       <c r="G39" t="n">
-        <v>33.92</v>
+        <v>33.79</v>
       </c>
       <c r="H39" t="n">
-        <v>9.19</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="I39" t="n">
         <v>0.53</v>
@@ -4736,31 +4732,31 @@
         <v>20.4</v>
       </c>
       <c r="K39" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="L39" t="n">
-        <v>554.21</v>
+        <v>553.64</v>
       </c>
       <c r="M39" t="n">
-        <v>564.41</v>
+        <v>563.84</v>
       </c>
       <c r="N39" t="n">
-        <v>533.8200000000001</v>
+        <v>533.25</v>
       </c>
       <c r="O39" t="n">
-        <v>606.22</v>
+        <v>605.65</v>
       </c>
       <c r="P39" t="n">
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>65.27</v>
+        <v>65.16</v>
       </c>
       <c r="R39" t="n">
-        <v>5.08</v>
+        <v>4.98</v>
       </c>
       <c r="S39" t="n">
-        <v>-3.41</v>
+        <v>-3.51</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4779,7 +4775,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>SOXX 19.64% · QQQ 8.54%</t>
+          <t>SOXX 19.54% · QQQ 8.5%</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -4804,7 +4800,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4825,55 +4821,55 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1079.79</v>
+        <v>1079.92</v>
       </c>
       <c r="D40" t="n">
         <v>96</v>
       </c>
       <c r="E40" t="n">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
       <c r="F40" t="n">
-        <v>7.74</v>
+        <v>7.75</v>
       </c>
       <c r="G40" t="n">
-        <v>8.31</v>
+        <v>8.32</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="I40" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="J40" t="n">
         <v>21.76</v>
       </c>
       <c r="K40" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="L40" t="n">
-        <v>1072.17</v>
+        <v>1072.3</v>
       </c>
       <c r="M40" t="n">
-        <v>1083.05</v>
+        <v>1083.18</v>
       </c>
       <c r="N40" t="n">
-        <v>1050.41</v>
+        <v>1050.54</v>
       </c>
       <c r="O40" t="n">
-        <v>1127.66</v>
+        <v>1127.79</v>
       </c>
       <c r="P40" t="n">
         <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>70.22</v>
+        <v>70.27</v>
       </c>
       <c r="R40" t="n">
-        <v>5.48</v>
+        <v>5.49</v>
       </c>
       <c r="S40" t="n">
-        <v>-1.52</v>
+        <v>-1.51</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4938,22 +4934,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1007.25</v>
+        <v>1007.46</v>
       </c>
       <c r="D41" t="n">
         <v>95</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.67</v>
+        <v>-0.65</v>
       </c>
       <c r="F41" t="n">
-        <v>9.5</v>
+        <v>9.52</v>
       </c>
       <c r="G41" t="n">
-        <v>-3.18</v>
+        <v>-3.16</v>
       </c>
       <c r="H41" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="I41" t="n">
         <v>0.43</v>
@@ -4965,28 +4961,28 @@
         <v>2.97</v>
       </c>
       <c r="L41" t="n">
-        <v>996.77</v>
+        <v>996.98</v>
       </c>
       <c r="M41" t="n">
-        <v>1011.74</v>
+        <v>1011.95</v>
       </c>
       <c r="N41" t="n">
-        <v>966.83</v>
+        <v>967.04</v>
       </c>
       <c r="O41" t="n">
-        <v>1073.13</v>
+        <v>1073.34</v>
       </c>
       <c r="P41" t="n">
         <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>65.79000000000001</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="R41" t="n">
-        <v>5.28</v>
+        <v>5.3</v>
       </c>
       <c r="S41" t="n">
-        <v>-2.94</v>
+        <v>-2.92</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5051,22 +5047,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>245.77</v>
+        <v>245.6</v>
       </c>
       <c r="D42" t="n">
         <v>81</v>
       </c>
       <c r="E42" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="F42" t="n">
-        <v>14.5</v>
+        <v>14.42</v>
       </c>
       <c r="G42" t="n">
-        <v>105.82</v>
+        <v>105.68</v>
       </c>
       <c r="H42" t="n">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="I42" t="n">
         <v>0.47</v>
@@ -5078,28 +5074,28 @@
         <v>5.95</v>
       </c>
       <c r="L42" t="n">
-        <v>240.65</v>
+        <v>240.48</v>
       </c>
       <c r="M42" t="n">
-        <v>247.96</v>
+        <v>247.79</v>
       </c>
       <c r="N42" t="n">
-        <v>226.04</v>
+        <v>225.87</v>
       </c>
       <c r="O42" t="n">
-        <v>277.93</v>
+        <v>277.76</v>
       </c>
       <c r="P42" t="n">
         <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>65.06999999999999</v>
+        <v>65.02</v>
       </c>
       <c r="R42" t="n">
-        <v>7.53</v>
+        <v>7.46</v>
       </c>
       <c r="S42" t="n">
-        <v>-6.9</v>
+        <v>-6.97</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5118,7 +5114,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
+          <t>QQQ 8.5% · ARKK -4.51% · SPY 4.05%</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -5160,22 +5156,22 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10.3</v>
+        <v>10.27</v>
       </c>
       <c r="D43" t="n">
         <v>75</v>
       </c>
       <c r="E43" t="n">
-        <v>-6.87</v>
+        <v>-7.19</v>
       </c>
       <c r="F43" t="n">
-        <v>12.69</v>
+        <v>12.31</v>
       </c>
       <c r="G43" t="n">
-        <v>5.97</v>
+        <v>5.61</v>
       </c>
       <c r="H43" t="n">
-        <v>4.15</v>
+        <v>3.81</v>
       </c>
       <c r="I43" t="n">
         <v>0.5</v>
@@ -5184,31 +5180,31 @@
         <v>0.78</v>
       </c>
       <c r="K43" t="n">
-        <v>7.54</v>
+        <v>7.57</v>
       </c>
       <c r="L43" t="n">
-        <v>10.03</v>
+        <v>9.99</v>
       </c>
       <c r="M43" t="n">
-        <v>10.42</v>
+        <v>10.38</v>
       </c>
       <c r="N43" t="n">
-        <v>9.25</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>12.01</v>
+        <v>11.97</v>
       </c>
       <c r="P43" t="n">
         <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>59.02</v>
+        <v>58.79</v>
       </c>
       <c r="R43" t="n">
-        <v>5.65</v>
+        <v>5.31</v>
       </c>
       <c r="S43" t="n">
-        <v>-7.95</v>
+        <v>-8.27</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5269,22 +5265,22 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>263.76</v>
+        <v>263.74</v>
       </c>
       <c r="D44" t="n">
         <v>71</v>
       </c>
       <c r="E44" t="n">
-        <v>-2.36</v>
+        <v>-2.37</v>
       </c>
       <c r="F44" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="G44" t="n">
-        <v>26.47</v>
+        <v>26.46</v>
       </c>
       <c r="H44" t="n">
-        <v>-5.25</v>
+        <v>-5.22</v>
       </c>
       <c r="I44" t="n">
         <v>0.44</v>
@@ -5296,28 +5292,28 @@
         <v>2.5</v>
       </c>
       <c r="L44" t="n">
-        <v>261.45</v>
+        <v>261.43</v>
       </c>
       <c r="M44" t="n">
-        <v>264.75</v>
+        <v>264.73</v>
       </c>
       <c r="N44" t="n">
-        <v>254.85</v>
+        <v>254.83</v>
       </c>
       <c r="O44" t="n">
-        <v>278.29</v>
+        <v>278.27</v>
       </c>
       <c r="P44" t="n">
         <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>48.49</v>
+        <v>48.47</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.93</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S44" t="n">
-        <v>-5.31</v>
+        <v>-5.32</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5336,7 +5332,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
+          <t>QQQ 8.5% · ARKK -4.51% · SPY 4.05%</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -5378,25 +5374,25 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>419.77</v>
+        <v>420.14</v>
       </c>
       <c r="D45" t="n">
         <v>71</v>
       </c>
       <c r="E45" t="n">
-        <v>3.59</v>
+        <v>3.68</v>
       </c>
       <c r="F45" t="n">
-        <v>-3.04</v>
+        <v>-2.95</v>
       </c>
       <c r="G45" t="n">
-        <v>7.91</v>
+        <v>8.01</v>
       </c>
       <c r="H45" t="n">
-        <v>-11.58</v>
+        <v>-11.45</v>
       </c>
       <c r="I45" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="J45" t="n">
         <v>10.85</v>
@@ -5405,28 +5401,28 @@
         <v>2.58</v>
       </c>
       <c r="L45" t="n">
-        <v>415.97</v>
+        <v>416.34</v>
       </c>
       <c r="M45" t="n">
-        <v>421.4</v>
+        <v>421.77</v>
       </c>
       <c r="N45" t="n">
-        <v>405.12</v>
+        <v>405.49</v>
       </c>
       <c r="O45" t="n">
-        <v>443.64</v>
+        <v>444.01</v>
       </c>
       <c r="P45" t="n">
         <v>1.63</v>
       </c>
       <c r="Q45" t="n">
-        <v>59.75</v>
+        <v>59.99</v>
       </c>
       <c r="R45" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="S45" t="n">
-        <v>-2.99</v>
+        <v>-2.9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5445,7 +5441,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
+          <t>QQQ 8.5% · ARKK -4.51% · SPY 4.05%</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5487,25 +5483,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>71.62</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E46" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.21</v>
+        <v>-1.32</v>
       </c>
       <c r="G46" t="n">
-        <v>40.43</v>
+        <v>40.27</v>
       </c>
       <c r="H46" t="n">
-        <v>-9.75</v>
+        <v>-9.82</v>
       </c>
       <c r="I46" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="J46" t="n">
         <v>2.75</v>
@@ -5514,32 +5510,32 @@
         <v>3.84</v>
       </c>
       <c r="L46" t="n">
-        <v>70.66</v>
+        <v>70.58</v>
       </c>
       <c r="M46" t="n">
-        <v>72.03</v>
+        <v>71.95</v>
       </c>
       <c r="N46" t="n">
-        <v>67.91</v>
+        <v>67.83</v>
       </c>
       <c r="O46" t="n">
-        <v>77.66</v>
+        <v>77.58</v>
       </c>
       <c r="P46" t="n">
         <v>1.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>52.77</v>
+        <v>52.58</v>
       </c>
       <c r="R46" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="S46" t="n">
-        <v>-7.18</v>
+        <v>-7.28</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5580,7 +5576,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ</t>
+          <t>Tendencia larga débil; MACD sin confirmar; Volumen bajo; Débil vs QQQ; Lejos del máximo 20D</t>
         </is>
       </c>
     </row>
@@ -5596,25 +5592,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>413.08</v>
+        <v>412.33</v>
       </c>
       <c r="D47" t="n">
         <v>62</v>
       </c>
       <c r="E47" t="n">
-        <v>-7.23</v>
+        <v>-7.4</v>
       </c>
       <c r="F47" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9</v>
+        <v>0.72</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.94</v>
+        <v>-2.1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="J47" t="n">
         <v>18.12</v>
@@ -5623,28 +5619,28 @@
         <v>4.39</v>
       </c>
       <c r="L47" t="n">
-        <v>406.74</v>
+        <v>405.99</v>
       </c>
       <c r="M47" t="n">
-        <v>415.8</v>
+        <v>415.05</v>
       </c>
       <c r="N47" t="n">
-        <v>388.62</v>
+        <v>387.87</v>
       </c>
       <c r="O47" t="n">
-        <v>452.94</v>
+        <v>452.19</v>
       </c>
       <c r="P47" t="n">
         <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>60.98</v>
+        <v>60.78</v>
       </c>
       <c r="R47" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="S47" t="n">
-        <v>-8.890000000000001</v>
+        <v>-9.06</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5663,7 +5659,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
+          <t>QQQ 8.5% · ARKK -4.51% · SPY 4.05%</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -5705,25 +5701,25 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>33.75</v>
+        <v>33.74</v>
       </c>
       <c r="D48" t="n">
         <v>69</v>
       </c>
       <c r="E48" t="n">
-        <v>5.47</v>
+        <v>5.43</v>
       </c>
       <c r="F48" t="n">
-        <v>15.66</v>
+        <v>15.62</v>
       </c>
       <c r="G48" t="n">
-        <v>8.42</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H48" t="n">
         <v>7.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="J48" t="n">
         <v>2.48</v>
@@ -5732,28 +5728,28 @@
         <v>7.36</v>
       </c>
       <c r="L48" t="n">
-        <v>32.88</v>
+        <v>32.87</v>
       </c>
       <c r="M48" t="n">
-        <v>34.12</v>
+        <v>34.11</v>
       </c>
       <c r="N48" t="n">
-        <v>30.4</v>
+        <v>30.39</v>
       </c>
       <c r="O48" t="n">
-        <v>39.21</v>
+        <v>39.2</v>
       </c>
       <c r="P48" t="n">
         <v>1.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>65.18000000000001</v>
+        <v>65.16</v>
       </c>
       <c r="R48" t="n">
-        <v>10.9</v>
+        <v>10.86</v>
       </c>
       <c r="S48" t="n">
-        <v>-7.2</v>
+        <v>-7.24</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5772,7 +5768,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
+          <t>QQQ 8.5% · ARKK -4.51% · SPY 4.05%</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -5818,22 +5814,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>86.06999999999999</v>
+        <v>86.38</v>
       </c>
       <c r="D49" t="n">
         <v>63</v>
       </c>
       <c r="E49" t="n">
-        <v>6.76</v>
+        <v>7.14</v>
       </c>
       <c r="F49" t="n">
-        <v>16.3</v>
+        <v>16.71</v>
       </c>
       <c r="G49" t="n">
-        <v>20.92</v>
+        <v>21.35</v>
       </c>
       <c r="H49" t="n">
-        <v>7.76</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="I49" t="n">
         <v>0.29</v>
@@ -5842,31 +5838,31 @@
         <v>7.61</v>
       </c>
       <c r="K49" t="n">
-        <v>8.84</v>
+        <v>8.81</v>
       </c>
       <c r="L49" t="n">
-        <v>83.41</v>
+        <v>83.72</v>
       </c>
       <c r="M49" t="n">
-        <v>87.20999999999999</v>
+        <v>87.52</v>
       </c>
       <c r="N49" t="n">
-        <v>75.8</v>
+        <v>76.11</v>
       </c>
       <c r="O49" t="n">
-        <v>102.81</v>
+        <v>103.12</v>
       </c>
       <c r="P49" t="n">
         <v>1.63</v>
       </c>
       <c r="Q49" t="n">
-        <v>65.48999999999999</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="R49" t="n">
-        <v>4.47</v>
+        <v>4.83</v>
       </c>
       <c r="S49" t="n">
-        <v>-10.64</v>
+        <v>-10.32</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5885,7 +5881,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
+          <t>QQQ 8.5% · ARKK -4.51% · SPY 4.05%</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -5931,7 +5927,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>250.55</v>
+        <v>250.54</v>
       </c>
       <c r="D50" t="n">
         <v>72</v>
@@ -5946,7 +5942,7 @@
         <v>-1.81</v>
       </c>
       <c r="H50" t="n">
-        <v>-10.65</v>
+        <v>-10.61</v>
       </c>
       <c r="I50" t="n">
         <v>0.6</v>
@@ -5958,7 +5954,7 @@
         <v>3.71</v>
       </c>
       <c r="L50" t="n">
-        <v>247.3</v>
+        <v>247.29</v>
       </c>
       <c r="M50" t="n">
         <v>251.94</v>
@@ -5967,7 +5963,7 @@
         <v>238</v>
       </c>
       <c r="O50" t="n">
-        <v>271</v>
+        <v>270.99</v>
       </c>
       <c r="P50" t="n">
         <v>1.63</v>
@@ -5976,10 +5972,10 @@
         <v>53.35</v>
       </c>
       <c r="R50" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S50" t="n">
-        <v>-5.48</v>
+        <v>-5.49</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5998,7 +5994,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
+          <t>QQQ 8.5% · ARKK -4.51% · SPY 4.05%</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -6040,25 +6036,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>740.21</v>
+        <v>740.01</v>
       </c>
       <c r="D51" t="n">
         <v>70</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.28</v>
+        <v>-0.31</v>
       </c>
       <c r="F51" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="G51" t="n">
-        <v>7.98</v>
+        <v>7.96</v>
       </c>
       <c r="H51" t="n">
-        <v>-4.46</v>
+        <v>-4.45</v>
       </c>
       <c r="I51" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="J51" t="n">
         <v>7.5</v>
@@ -6067,28 +6063,28 @@
         <v>1.01</v>
       </c>
       <c r="L51" t="n">
-        <v>737.58</v>
+        <v>737.38</v>
       </c>
       <c r="M51" t="n">
-        <v>741.34</v>
+        <v>741.14</v>
       </c>
       <c r="N51" t="n">
-        <v>730.08</v>
+        <v>729.88</v>
       </c>
       <c r="O51" t="n">
-        <v>756.72</v>
+        <v>756.52</v>
       </c>
       <c r="P51" t="n">
         <v>1.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>67.25</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="R51" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="S51" t="n">
-        <v>-1.24</v>
+        <v>-1.27</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6149,19 +6145,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>680.5700000000001</v>
+        <v>680.3200000000001</v>
       </c>
       <c r="D52" t="n">
         <v>70</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.27</v>
+        <v>-0.31</v>
       </c>
       <c r="F52" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="G52" t="n">
-        <v>7.99</v>
+        <v>7.95</v>
       </c>
       <c r="H52" t="n">
         <v>-4.46</v>
@@ -6176,28 +6172,28 @@
         <v>1.01</v>
       </c>
       <c r="L52" t="n">
-        <v>678.17</v>
+        <v>677.92</v>
       </c>
       <c r="M52" t="n">
-        <v>681.6</v>
+        <v>681.35</v>
       </c>
       <c r="N52" t="n">
-        <v>671.3</v>
+        <v>671.05</v>
       </c>
       <c r="O52" t="n">
-        <v>695.67</v>
+        <v>695.42</v>
       </c>
       <c r="P52" t="n">
         <v>1.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>67.53</v>
+        <v>67.39</v>
       </c>
       <c r="R52" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S52" t="n">
-        <v>-1.24</v>
+        <v>-1.27</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6258,22 +6254,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9.27</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="D53" t="n">
         <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>7.23</v>
+        <v>7.4</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.22</v>
+        <v>-1.06</v>
       </c>
       <c r="G53" t="n">
-        <v>-8.35</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>-9.76</v>
+        <v>-9.56</v>
       </c>
       <c r="I53" t="n">
         <v>0.74</v>
@@ -6282,31 +6278,31 @@
         <v>0.48</v>
       </c>
       <c r="K53" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="L53" t="n">
-        <v>9.109999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>9.35</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>8.619999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="P53" t="n">
         <v>1.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>56.04</v>
+        <v>56.22</v>
       </c>
       <c r="R53" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="S53" t="n">
-        <v>-6.12</v>
+        <v>-5.97</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6325,7 +6321,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
+          <t>QQQ 8.5% · ARKK -4.51% · SPY 4.05%</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -6367,22 +6363,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>45</v>
+        <v>45.03</v>
       </c>
       <c r="D54" t="n">
         <v>62</v>
       </c>
       <c r="E54" t="n">
-        <v>-4.42</v>
+        <v>-4.36</v>
       </c>
       <c r="F54" t="n">
-        <v>14.94</v>
+        <v>15.01</v>
       </c>
       <c r="G54" t="n">
-        <v>20.89</v>
+        <v>20.95</v>
       </c>
       <c r="H54" t="n">
-        <v>6.4</v>
+        <v>6.51</v>
       </c>
       <c r="I54" t="n">
         <v>0.37</v>
@@ -6394,28 +6390,28 @@
         <v>2.74</v>
       </c>
       <c r="L54" t="n">
-        <v>44.57</v>
+        <v>44.59</v>
       </c>
       <c r="M54" t="n">
-        <v>45.19</v>
+        <v>45.21</v>
       </c>
       <c r="N54" t="n">
-        <v>43.33</v>
+        <v>43.36</v>
       </c>
       <c r="O54" t="n">
-        <v>47.71</v>
+        <v>47.74</v>
       </c>
       <c r="P54" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>66.59</v>
+        <v>66.69</v>
       </c>
       <c r="R54" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="S54" t="n">
-        <v>-5.84</v>
+        <v>-5.79</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6476,22 +6472,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>207.86</v>
+        <v>207.66</v>
       </c>
       <c r="D55" t="n">
         <v>60</v>
       </c>
       <c r="E55" t="n">
-        <v>7.91</v>
+        <v>7.81</v>
       </c>
       <c r="F55" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="G55" t="n">
-        <v>26.89</v>
+        <v>26.77</v>
       </c>
       <c r="H55" t="n">
-        <v>-8.4</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="I55" t="n">
         <v>0.39</v>
@@ -6500,31 +6496,31 @@
         <v>15.04</v>
       </c>
       <c r="K55" t="n">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="L55" t="n">
-        <v>202.6</v>
+        <v>202.4</v>
       </c>
       <c r="M55" t="n">
-        <v>210.12</v>
+        <v>209.92</v>
       </c>
       <c r="N55" t="n">
-        <v>187.56</v>
+        <v>187.36</v>
       </c>
       <c r="O55" t="n">
-        <v>240.94</v>
+        <v>240.74</v>
       </c>
       <c r="P55" t="n">
         <v>1.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>50.98</v>
+        <v>50.91</v>
       </c>
       <c r="R55" t="n">
-        <v>-1.58</v>
+        <v>-1.67</v>
       </c>
       <c r="S55" t="n">
-        <v>-19.71</v>
+        <v>-19.79</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6543,7 +6539,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>QQQ 8.54% · ARKK -4.49% · SPY 4.08%</t>
+          <t>QQQ 8.5% · ARKK -4.51% · SPY 4.05%</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -6585,22 +6581,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>13.36</v>
+        <v>13.34</v>
       </c>
       <c r="D56" t="n">
         <v>72</v>
       </c>
       <c r="E56" t="n">
-        <v>4.82</v>
+        <v>4.62</v>
       </c>
       <c r="F56" t="n">
-        <v>12.88</v>
+        <v>12.66</v>
       </c>
       <c r="G56" t="n">
-        <v>66.02</v>
+        <v>65.7</v>
       </c>
       <c r="H56" t="n">
-        <v>4.34</v>
+        <v>4.16</v>
       </c>
       <c r="I56" t="n">
         <v>0.92</v>
@@ -6609,31 +6605,31 @@
         <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>7.5</v>
+        <v>7.52</v>
       </c>
       <c r="L56" t="n">
-        <v>13.01</v>
+        <v>12.99</v>
       </c>
       <c r="M56" t="n">
-        <v>13.52</v>
+        <v>13.49</v>
       </c>
       <c r="N56" t="n">
-        <v>12.01</v>
+        <v>11.99</v>
       </c>
       <c r="O56" t="n">
-        <v>15.57</v>
+        <v>15.55</v>
       </c>
       <c r="P56" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q56" t="n">
-        <v>60.33</v>
+        <v>60.17</v>
       </c>
       <c r="R56" t="n">
-        <v>9.08</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="S56" t="n">
-        <v>-3.15</v>
+        <v>-3.34</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6652,7 +6648,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>BTC-USD 1.43% · ETH-USD -5.34%</t>
+          <t>BTC-USD 1.65% · ETH-USD -5.22%</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -6682,7 +6678,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Sector no acompaña: BTC-USD 1.43% · ETH-USD -5.34%; Tendencia larga débil; MACD sin confirmar; Algo extendida sobre MA20; Volatilidad alta</t>
+          <t>Sector no acompaña: BTC-USD 1.65% · ETH-USD -5.22%; Tendencia larga débil; MACD sin confirmar; Algo extendida sobre MA20; Volatilidad alta</t>
         </is>
       </c>
     </row>
@@ -6698,22 +6694,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>253.35</v>
+        <v>253.04</v>
       </c>
       <c r="D57" t="n">
         <v>95</v>
       </c>
       <c r="E57" t="n">
-        <v>14.53</v>
+        <v>14.39</v>
       </c>
       <c r="F57" t="n">
-        <v>28.88</v>
+        <v>28.73</v>
       </c>
       <c r="G57" t="n">
-        <v>97.70999999999999</v>
+        <v>97.47</v>
       </c>
       <c r="H57" t="n">
-        <v>20.34</v>
+        <v>20.23</v>
       </c>
       <c r="I57" t="n">
         <v>1.23</v>
@@ -6725,28 +6721,28 @@
         <v>7.07</v>
       </c>
       <c r="L57" t="n">
-        <v>247.08</v>
+        <v>246.78</v>
       </c>
       <c r="M57" t="n">
-        <v>256.03</v>
+        <v>255.72</v>
       </c>
       <c r="N57" t="n">
-        <v>229.18</v>
+        <v>228.88</v>
       </c>
       <c r="O57" t="n">
-        <v>292.72</v>
+        <v>292.42</v>
       </c>
       <c r="P57" t="n">
         <v>1.63</v>
       </c>
       <c r="Q57" t="n">
-        <v>63.76</v>
+        <v>63.69</v>
       </c>
       <c r="R57" t="n">
-        <v>17.18</v>
+        <v>17.04</v>
       </c>
       <c r="S57" t="n">
-        <v>-2.35</v>
+        <v>-2.47</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6765,7 +6761,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>SOXX 19.64% · QQQ 8.54%</t>
+          <t>SOXX 19.54% · QQQ 8.5%</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6790,7 +6786,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.64% · QQQ 8.54%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
+          <t>Mercado NEUTRO +; Sector ligeramente positivo: SOXX 19.54% · QQQ 8.5%; Precio sobre MA20; MA20 sobre MA50; Tendencia larga positiva</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6811,22 +6807,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>117.69</v>
+        <v>117.96</v>
       </c>
       <c r="D58" t="n">
         <v>85</v>
       </c>
       <c r="E58" t="n">
-        <v>-2.16</v>
+        <v>-1.94</v>
       </c>
       <c r="F58" t="n">
-        <v>80.31999999999999</v>
+        <v>80.73</v>
       </c>
       <c r="G58" t="n"